--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{05F05D38-E2FE-4B5E-8C91-BE0BA9318E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{419CEAFC-AB52-442E-A468-4A1A67146EE0}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{05F05D38-E2FE-4B5E-8C91-BE0BA9318E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B4F658E-3DE6-4E08-A2FE-E5AD246CEB5E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4456" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4456" uniqueCount="1064">
   <si>
     <t>Codigo</t>
   </si>
@@ -3212,9 +3212,6 @@
   </si>
   <si>
     <t>Azul oscuro</t>
-  </si>
-  <si>
-    <t>Inactivo</t>
   </si>
 </sst>
 </file>
@@ -3749,7 +3746,7 @@
         <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>1064</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
         <v>20</v>
@@ -3778,7 +3775,7 @@
         <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>1064</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
         <v>30</v>
@@ -3807,7 +3804,7 @@
         <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>1064</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
         <v>33</v>
@@ -3836,7 +3833,7 @@
         <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>1064</v>
+        <v>16</v>
       </c>
       <c r="I8" t="s">
         <v>24</v>
@@ -3905,7 +3902,7 @@
       <c r="A11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C11" t="s">

--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61D03EC1-D552-4E1A-98FC-805D638FECA7}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE74109B-DE50-44F9-972A-891E81063039}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6111" uniqueCount="1090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6154" uniqueCount="1096">
   <si>
     <t>Codigo</t>
   </si>
@@ -3259,38 +3259,6 @@
   </si>
   <si>
     <t>Andadera para bebé con toldo ajustable, bandeja interactiva y altura regulable, diseñada para brindar seguridad, comodidad y diversión en cada paso.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">La Andadera Swim acompaña el crecimiento de tu bebé con un diseño moderno y funcional. Cuenta con asiento acolchado, bandeja con juguetes interactivos, toldo ajustable y sistema de altura regulable para adaptarse a cada etapa. Su estructura resistente y ruedas multidireccionales ofrecen estabilidad y un desplazamiento suave. 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Medidas del producto:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Alto total: 83 cm
-Alto sin toldo: 46 cm
-Largo: 74 cm
-Ancho: 69 cm
-Largo del toldo: 40 cm</t>
-    </r>
   </si>
   <si>
     <r>
@@ -3566,12 +3534,205 @@
   <si>
     <t>assets/productos/bebes/andaderapimpon/pimpongreen3.webp</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Andadera Swim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> acompaña el crecimiento de tu bebé con un diseño moderno y funcional. Cuenta con asiento acolchado, bandeja con juguetes interactivos, toldo ajustable y sistema de altura regulable para adaptarse a cada etapa. Su estructura resistente y ruedas multidireccionales ofrecen estabilidad y un desplazamiento suave. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Medidas del producto:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Alto total: 83 cm
+Alto sin toldo: 46 cm
+Largo: 74 cm
+Ancho: 69 cm
+Largo del toldo: 40 cm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Andadera didáctica</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2 en 1 que funciona como caminador y centro de actividades, ideal para estimular el aprendizaje, la coordinación y los primeros pasos del bebé.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Función 2 en 1: caminador y centro de actividades.
+Panel interactivo con sonidos y juegos.
+Estructura en plástico resistente.
+Diseño estable y seguro.
+Edad recomendada: desde los 6 meses.
+Funciona con baterías (según el modelo).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Favorece el equilibrio y la coordinación.
+Estimula el desarrollo motriz y sensorial.
+Promueve el aprendizaje mediante el juego.
+Mantiene al bebé entretenido de forma segura.
+Ideal para acompañar los primeros pasos.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Utilizar siempre bajo la supervisión de un adulto.
+Usar sobre superficies planas y seguras.
+Limpiar con un paño suave y ligeramente húmedo.
+Revisar periódicamente el estado de las piezas y accesorios antes de cada uso.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Andadera 2 en 1 Cachorro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> está diseñada para acompañar el crecimiento del bebé mientras juega y aprende. Funciona como caminador y centro de actividades, incorporando un panel interactivo con sonidos y accesorios didácticos que favorecen el desarrollo motriz, el equilibrio y la coordinación de forma divertida y segura.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/andaderacachorro/cachorro.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/andaderacachorro/cachorro2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/andaderacachorro/cachorro3.webp</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3589,6 +3750,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3614,10 +3783,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3957,7 +4127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L511"/>
+  <dimension ref="A1:L513"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4970,7 +5140,7 @@
         <v>220230</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1067</v>
+        <v>1089</v>
       </c>
       <c r="G27" t="s">
         <v>78</v>
@@ -4985,7 +5155,7 @@
         <v>1066</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="L27" t="s">
         <v>25</v>
@@ -5081,13 +5251,13 @@
         <v>220230</v>
       </c>
       <c r="G30" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H30" t="s">
         <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -5107,13 +5277,13 @@
         <v>220230</v>
       </c>
       <c r="G31" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H31" t="s">
         <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -5133,7 +5303,7 @@
         <v>220230</v>
       </c>
       <c r="G32" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
@@ -5159,7 +5329,7 @@
         <v>220230</v>
       </c>
       <c r="G33" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H33" t="s">
         <v>19</v>
@@ -5185,7 +5355,7 @@
         <v>220230</v>
       </c>
       <c r="G34" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H34" t="s">
         <v>19</v>
@@ -5211,7 +5381,7 @@
         <v>220230</v>
       </c>
       <c r="G35" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H35" t="s">
         <v>19</v>
@@ -5237,7 +5407,7 @@
         <v>220230</v>
       </c>
       <c r="G36" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H36" t="s">
         <v>19</v>
@@ -5263,7 +5433,7 @@
         <v>220230</v>
       </c>
       <c r="G37" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H37" t="s">
         <v>19</v>
@@ -5323,14 +5493,14 @@
       <c r="D39" t="s">
         <v>77</v>
       </c>
-      <c r="E39" t="s">
-        <v>25</v>
+      <c r="E39">
+        <v>185000</v>
       </c>
       <c r="F39" t="s">
-        <v>25</v>
+        <v>1092</v>
       </c>
       <c r="G39" t="s">
-        <v>25</v>
+        <v>1093</v>
       </c>
       <c r="H39" t="s">
         <v>19</v>
@@ -5339,10 +5509,10 @@
         <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>25</v>
-      </c>
-      <c r="K39" t="s">
-        <v>25</v>
+        <v>1090</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>1091</v>
       </c>
       <c r="L39" t="s">
         <v>25</v>
@@ -5350,10 +5520,10 @@
     </row>
     <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
@@ -5362,36 +5532,28 @@
         <v>77</v>
       </c>
       <c r="E40">
-        <v>119390</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>1079</v>
+        <v>185000</v>
       </c>
       <c r="G40" t="s">
-        <v>1081</v>
+        <v>1094</v>
       </c>
       <c r="H40" t="s">
         <v>19</v>
       </c>
       <c r="I40" t="s">
-        <v>40</v>
-      </c>
-      <c r="J40" t="s">
-        <v>1078</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>1080</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="K40" s="2"/>
       <c r="L40" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -5400,17 +5562,16 @@
         <v>77</v>
       </c>
       <c r="E41">
-        <v>119390</v>
-      </c>
-      <c r="F41" s="2"/>
+        <v>185000</v>
+      </c>
       <c r="G41" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="H41" t="s">
         <v>19</v>
       </c>
       <c r="I41" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" t="s">
@@ -5433,9 +5594,11 @@
       <c r="E42">
         <v>119390</v>
       </c>
-      <c r="F42" s="2"/>
+      <c r="F42" s="2" t="s">
+        <v>1078</v>
+      </c>
       <c r="G42" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="H42" t="s">
         <v>19</v>
@@ -5443,14 +5606,19 @@
       <c r="I42" t="s">
         <v>40</v>
       </c>
-      <c r="K42" s="2"/>
+      <c r="J42" t="s">
+        <v>1077</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>1079</v>
+      </c>
       <c r="L42" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B43" t="s">
         <v>88</v>
@@ -5464,31 +5632,24 @@
       <c r="E43">
         <v>119390</v>
       </c>
-      <c r="F43" t="s">
-        <v>25</v>
-      </c>
+      <c r="F43" s="2"/>
       <c r="G43" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="H43" t="s">
         <v>19</v>
       </c>
       <c r="I43" t="s">
-        <v>43</v>
-      </c>
-      <c r="J43" t="s">
-        <v>25</v>
-      </c>
-      <c r="K43" t="s">
-        <v>25</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K43" s="2"/>
       <c r="L43" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
         <v>88</v>
@@ -5502,24 +5663,17 @@
       <c r="E44">
         <v>119390</v>
       </c>
-      <c r="F44" t="s">
-        <v>25</v>
-      </c>
+      <c r="F44" s="2"/>
       <c r="G44" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="H44" t="s">
         <v>19</v>
       </c>
       <c r="I44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J44" t="s">
-        <v>25</v>
-      </c>
-      <c r="K44" t="s">
-        <v>25</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K44" s="2"/>
       <c r="L44" t="s">
         <v>25</v>
       </c>
@@ -5544,7 +5698,7 @@
         <v>25</v>
       </c>
       <c r="G45" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="H45" t="s">
         <v>19</v>
@@ -5564,7 +5718,7 @@
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B46" t="s">
         <v>88</v>
@@ -5582,13 +5736,13 @@
         <v>25</v>
       </c>
       <c r="G46" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="H46" t="s">
         <v>19</v>
       </c>
       <c r="I46" t="s">
-        <v>1069</v>
+        <v>43</v>
       </c>
       <c r="J46" t="s">
         <v>25</v>
@@ -5602,7 +5756,7 @@
     </row>
     <row r="47" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B47" t="s">
         <v>88</v>
@@ -5620,13 +5774,13 @@
         <v>25</v>
       </c>
       <c r="G47" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="H47" t="s">
         <v>19</v>
       </c>
       <c r="I47" t="s">
-        <v>1069</v>
+        <v>43</v>
       </c>
       <c r="J47" t="s">
         <v>25</v>
@@ -5658,18 +5812,15 @@
         <v>25</v>
       </c>
       <c r="G48" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="H48" t="s">
         <v>19</v>
       </c>
       <c r="I48" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="J48" t="s">
-        <v>25</v>
-      </c>
-      <c r="K48" t="s">
         <v>25</v>
       </c>
       <c r="L48" t="s">
@@ -5678,31 +5829,31 @@
     </row>
     <row r="49" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>93</v>
-      </c>
-      <c r="E49" t="s">
-        <v>25</v>
+        <v>77</v>
+      </c>
+      <c r="E49">
+        <v>119390</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>25</v>
+        <v>1087</v>
       </c>
       <c r="H49" t="s">
         <v>19</v>
       </c>
       <c r="I49" t="s">
-        <v>25</v>
+        <v>1068</v>
       </c>
       <c r="J49" t="s">
         <v>25</v>
@@ -5716,31 +5867,31 @@
     </row>
     <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>93</v>
-      </c>
-      <c r="E50" t="s">
-        <v>25</v>
+        <v>77</v>
+      </c>
+      <c r="E50">
+        <v>119390</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
       </c>
       <c r="G50" t="s">
-        <v>25</v>
+        <v>1088</v>
       </c>
       <c r="H50" t="s">
         <v>19</v>
       </c>
       <c r="I50" t="s">
-        <v>25</v>
+        <v>1068</v>
       </c>
       <c r="J50" t="s">
         <v>25</v>
@@ -5754,10 +5905,10 @@
     </row>
     <row r="51" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -5792,10 +5943,10 @@
     </row>
     <row r="52" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
@@ -5830,10 +5981,10 @@
     </row>
     <row r="53" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -5868,10 +6019,10 @@
     </row>
     <row r="54" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
@@ -5906,10 +6057,10 @@
     </row>
     <row r="55" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -5944,10 +6095,10 @@
     </row>
     <row r="56" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -5982,10 +6133,10 @@
     </row>
     <row r="57" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -5999,7 +6150,7 @@
       <c r="F57" t="s">
         <v>25</v>
       </c>
-      <c r="G57" t="s">
+      <c r="G57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H57" t="s">
@@ -6020,10 +6171,10 @@
     </row>
     <row r="58" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
@@ -6058,10 +6209,10 @@
     </row>
     <row r="59" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B59" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
@@ -6096,10 +6247,10 @@
     </row>
     <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -6134,7 +6285,7 @@
     </row>
     <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B61" t="s">
         <v>113</v>
@@ -6172,10 +6323,10 @@
     </row>
     <row r="62" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -6210,10 +6361,10 @@
     </row>
     <row r="63" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B63" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
@@ -6248,16 +6399,16 @@
     </row>
     <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B64" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="E64" t="s">
         <v>25</v>
@@ -6286,16 +6437,16 @@
     </row>
     <row r="65" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="E65" t="s">
         <v>25</v>
@@ -6324,10 +6475,10 @@
     </row>
     <row r="66" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B66" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -6362,10 +6513,10 @@
     </row>
     <row r="67" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B67" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
@@ -6400,10 +6551,10 @@
     </row>
     <row r="68" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B68" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
@@ -6438,10 +6589,10 @@
     </row>
     <row r="69" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -6476,10 +6627,10 @@
     </row>
     <row r="70" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B70" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -6514,10 +6665,10 @@
     </row>
     <row r="71" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B71" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -6552,16 +6703,16 @@
     </row>
     <row r="72" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B72" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E72" t="s">
         <v>25</v>
@@ -6590,16 +6741,16 @@
     </row>
     <row r="73" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B73" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
@@ -6628,10 +6779,10 @@
     </row>
     <row r="74" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B74" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -6666,10 +6817,10 @@
     </row>
     <row r="75" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B75" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
@@ -6704,10 +6855,10 @@
     </row>
     <row r="76" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B76" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -6742,16 +6893,16 @@
     </row>
     <row r="77" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E77" t="s">
         <v>25</v>
@@ -6780,16 +6931,16 @@
     </row>
     <row r="78" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B78" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E78" t="s">
         <v>25</v>
@@ -6818,10 +6969,10 @@
     </row>
     <row r="79" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B79" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
@@ -6856,10 +7007,10 @@
     </row>
     <row r="80" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
@@ -6894,10 +7045,10 @@
     </row>
     <row r="81" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B81" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
@@ -6932,10 +7083,10 @@
     </row>
     <row r="82" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B82" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -6970,10 +7121,10 @@
     </row>
     <row r="83" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B83" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -7008,16 +7159,16 @@
     </row>
     <row r="84" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B84" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E84" t="s">
         <v>25</v>
@@ -7046,16 +7197,16 @@
     </row>
     <row r="85" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B85" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E85" t="s">
         <v>25</v>
@@ -7084,10 +7235,10 @@
     </row>
     <row r="86" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B86" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
@@ -7122,10 +7273,10 @@
     </row>
     <row r="87" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
@@ -7160,10 +7311,10 @@
     </row>
     <row r="88" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B88" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -7198,10 +7349,10 @@
     </row>
     <row r="89" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B89" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -7236,10 +7387,10 @@
     </row>
     <row r="90" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B90" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -7274,10 +7425,10 @@
     </row>
     <row r="91" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B91" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
@@ -7312,10 +7463,10 @@
     </row>
     <row r="92" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B92" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
@@ -7350,10 +7501,10 @@
     </row>
     <row r="93" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B93" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
@@ -7388,10 +7539,10 @@
     </row>
     <row r="94" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B94" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
@@ -7426,10 +7577,10 @@
     </row>
     <row r="95" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B95" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
@@ -7464,10 +7615,10 @@
     </row>
     <row r="96" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B96" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
@@ -7502,10 +7653,10 @@
     </row>
     <row r="97" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B97" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -7540,10 +7691,10 @@
     </row>
     <row r="98" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B98" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
@@ -7578,10 +7729,10 @@
     </row>
     <row r="99" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B99" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C99" t="s">
         <v>14</v>
@@ -7616,10 +7767,10 @@
     </row>
     <row r="100" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B100" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
@@ -7654,10 +7805,10 @@
     </row>
     <row r="101" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B101" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C101" t="s">
         <v>14</v>
@@ -7692,10 +7843,10 @@
     </row>
     <row r="102" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B102" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
@@ -7730,10 +7881,10 @@
     </row>
     <row r="103" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B103" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
@@ -7768,10 +7919,10 @@
     </row>
     <row r="104" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B104" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C104" t="s">
         <v>14</v>
@@ -7779,14 +7930,14 @@
       <c r="D104" t="s">
         <v>164</v>
       </c>
-      <c r="E104">
-        <v>106156</v>
+      <c r="E104" t="s">
+        <v>25</v>
       </c>
       <c r="F104" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="G104" t="s">
-        <v>205</v>
+        <v>25</v>
       </c>
       <c r="H104" t="s">
         <v>19</v>
@@ -7795,10 +7946,10 @@
         <v>25</v>
       </c>
       <c r="J104" t="s">
-        <v>206</v>
+        <v>25</v>
       </c>
       <c r="K104" t="s">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="L104" t="s">
         <v>25</v>
@@ -7806,10 +7957,10 @@
     </row>
     <row r="105" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B105" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C105" t="s">
         <v>14</v>
@@ -7817,14 +7968,14 @@
       <c r="D105" t="s">
         <v>164</v>
       </c>
-      <c r="E105">
-        <v>106156</v>
+      <c r="E105" t="s">
+        <v>25</v>
       </c>
       <c r="F105" t="s">
         <v>25</v>
       </c>
       <c r="G105" t="s">
-        <v>208</v>
+        <v>25</v>
       </c>
       <c r="H105" t="s">
         <v>19</v>
@@ -7844,25 +7995,25 @@
     </row>
     <row r="106" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B106" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
       </c>
       <c r="D106" t="s">
-        <v>211</v>
-      </c>
-      <c r="E106" t="s">
-        <v>25</v>
+        <v>164</v>
+      </c>
+      <c r="E106">
+        <v>106156</v>
       </c>
       <c r="F106" t="s">
-        <v>25</v>
+        <v>204</v>
       </c>
       <c r="G106" t="s">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="H106" t="s">
         <v>19</v>
@@ -7871,10 +8022,10 @@
         <v>25</v>
       </c>
       <c r="J106" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="K106" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="L106" t="s">
         <v>25</v>
@@ -7882,25 +8033,25 @@
     </row>
     <row r="107" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B107" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>211</v>
-      </c>
-      <c r="E107" t="s">
-        <v>25</v>
+        <v>164</v>
+      </c>
+      <c r="E107">
+        <v>106156</v>
       </c>
       <c r="F107" t="s">
         <v>25</v>
       </c>
       <c r="G107" t="s">
-        <v>25</v>
+        <v>208</v>
       </c>
       <c r="H107" t="s">
         <v>19</v>
@@ -7920,10 +8071,10 @@
     </row>
     <row r="108" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B108" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
@@ -7958,10 +8109,10 @@
     </row>
     <row r="109" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B109" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C109" t="s">
         <v>14</v>
@@ -7996,10 +8147,10 @@
     </row>
     <row r="110" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B110" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C110" t="s">
         <v>14</v>
@@ -8034,10 +8185,10 @@
     </row>
     <row r="111" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B111" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C111" t="s">
         <v>14</v>
@@ -8072,10 +8223,10 @@
     </row>
     <row r="112" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B112" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C112" t="s">
         <v>14</v>
@@ -8110,10 +8261,10 @@
     </row>
     <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B113" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C113" t="s">
         <v>14</v>
@@ -8148,10 +8299,10 @@
     </row>
     <row r="114" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B114" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
@@ -8186,10 +8337,10 @@
     </row>
     <row r="115" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B115" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
@@ -8224,10 +8375,10 @@
     </row>
     <row r="116" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B116" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C116" t="s">
         <v>14</v>
@@ -8262,10 +8413,10 @@
     </row>
     <row r="117" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B117" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C117" t="s">
         <v>14</v>
@@ -8300,10 +8451,10 @@
     </row>
     <row r="118" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B118" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C118" t="s">
         <v>14</v>
@@ -8338,16 +8489,16 @@
     </row>
     <row r="119" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B119" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C119" t="s">
         <v>14</v>
       </c>
       <c r="D119" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="E119" t="s">
         <v>25</v>
@@ -8376,16 +8527,16 @@
     </row>
     <row r="120" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B120" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C120" t="s">
         <v>14</v>
       </c>
       <c r="D120" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
@@ -8414,10 +8565,10 @@
     </row>
     <row r="121" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B121" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C121" t="s">
         <v>14</v>
@@ -8452,10 +8603,10 @@
     </row>
     <row r="122" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B122" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
@@ -8490,10 +8641,10 @@
     </row>
     <row r="123" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B123" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C123" t="s">
         <v>14</v>
@@ -8528,16 +8679,16 @@
     </row>
     <row r="124" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B124" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C124" t="s">
         <v>14</v>
       </c>
       <c r="D124" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E124" t="s">
         <v>25</v>
@@ -8566,16 +8717,16 @@
     </row>
     <row r="125" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B125" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
       </c>
       <c r="D125" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E125" t="s">
         <v>25</v>
@@ -8604,16 +8755,16 @@
     </row>
     <row r="126" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B126" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C126" t="s">
-        <v>252</v>
+        <v>14</v>
       </c>
       <c r="D126" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E126" t="s">
         <v>25</v>
@@ -8642,16 +8793,16 @@
     </row>
     <row r="127" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B127" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C127" t="s">
-        <v>252</v>
+        <v>14</v>
       </c>
       <c r="D127" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E127" t="s">
         <v>25</v>
@@ -8680,10 +8831,10 @@
     </row>
     <row r="128" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B128" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C128" t="s">
         <v>252</v>
@@ -8718,10 +8869,10 @@
     </row>
     <row r="129" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B129" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C129" t="s">
         <v>252</v>
@@ -8756,10 +8907,10 @@
     </row>
     <row r="130" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B130" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C130" t="s">
         <v>252</v>
@@ -8794,10 +8945,10 @@
     </row>
     <row r="131" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B131" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C131" t="s">
         <v>252</v>
@@ -8832,10 +8983,10 @@
     </row>
     <row r="132" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B132" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C132" t="s">
         <v>252</v>
@@ -8870,10 +9021,10 @@
     </row>
     <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B133" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C133" t="s">
         <v>252</v>
@@ -8908,10 +9059,10 @@
     </row>
     <row r="134" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B134" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C134" t="s">
         <v>252</v>
@@ -8946,10 +9097,10 @@
     </row>
     <row r="135" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B135" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C135" t="s">
         <v>252</v>
@@ -8984,10 +9135,10 @@
     </row>
     <row r="136" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B136" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C136" t="s">
         <v>252</v>
@@ -9022,10 +9173,10 @@
     </row>
     <row r="137" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B137" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C137" t="s">
         <v>252</v>
@@ -9060,10 +9211,10 @@
     </row>
     <row r="138" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B138" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C138" t="s">
         <v>252</v>
@@ -9098,10 +9249,10 @@
     </row>
     <row r="139" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B139" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C139" t="s">
         <v>252</v>
@@ -9136,10 +9287,10 @@
     </row>
     <row r="140" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B140" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C140" t="s">
         <v>252</v>
@@ -9174,10 +9325,10 @@
     </row>
     <row r="141" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B141" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C141" t="s">
         <v>252</v>
@@ -9212,10 +9363,10 @@
     </row>
     <row r="142" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B142" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C142" t="s">
         <v>252</v>
@@ -9250,10 +9401,10 @@
     </row>
     <row r="143" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B143" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C143" t="s">
         <v>252</v>
@@ -9288,10 +9439,10 @@
     </row>
     <row r="144" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B144" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C144" t="s">
         <v>252</v>
@@ -9326,10 +9477,10 @@
     </row>
     <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B145" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C145" t="s">
         <v>252</v>
@@ -9364,10 +9515,10 @@
     </row>
     <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B146" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C146" t="s">
         <v>252</v>
@@ -9402,10 +9553,10 @@
     </row>
     <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B147" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C147" t="s">
         <v>252</v>
@@ -9440,10 +9591,10 @@
     </row>
     <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B148" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C148" t="s">
         <v>252</v>
@@ -9478,10 +9629,10 @@
     </row>
     <row r="149" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B149" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C149" t="s">
         <v>252</v>
@@ -9516,10 +9667,10 @@
     </row>
     <row r="150" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B150" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C150" t="s">
         <v>252</v>
@@ -9554,10 +9705,10 @@
     </row>
     <row r="151" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B151" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C151" t="s">
         <v>252</v>
@@ -9592,10 +9743,10 @@
     </row>
     <row r="152" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B152" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C152" t="s">
         <v>252</v>
@@ -9630,10 +9781,10 @@
     </row>
     <row r="153" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B153" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C153" t="s">
         <v>252</v>
@@ -9668,10 +9819,10 @@
     </row>
     <row r="154" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B154" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C154" t="s">
         <v>252</v>
@@ -9706,10 +9857,10 @@
     </row>
     <row r="155" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B155" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C155" t="s">
         <v>252</v>
@@ -9744,10 +9895,10 @@
     </row>
     <row r="156" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B156" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C156" t="s">
         <v>252</v>
@@ -9782,10 +9933,10 @@
     </row>
     <row r="157" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B157" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C157" t="s">
         <v>252</v>
@@ -9820,10 +9971,10 @@
     </row>
     <row r="158" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B158" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C158" t="s">
         <v>252</v>
@@ -9858,10 +10009,10 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B159" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C159" t="s">
         <v>252</v>
@@ -9896,10 +10047,10 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B160" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C160" t="s">
         <v>252</v>
@@ -9934,10 +10085,10 @@
     </row>
     <row r="161" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B161" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C161" t="s">
         <v>252</v>
@@ -9972,10 +10123,10 @@
     </row>
     <row r="162" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B162" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C162" t="s">
         <v>252</v>
@@ -10010,10 +10161,10 @@
     </row>
     <row r="163" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B163" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C163" t="s">
         <v>252</v>
@@ -10048,16 +10199,16 @@
     </row>
     <row r="164" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B164" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C164" t="s">
         <v>252</v>
       </c>
       <c r="D164" t="s">
-        <v>330</v>
+        <v>253</v>
       </c>
       <c r="E164" t="s">
         <v>25</v>
@@ -10086,16 +10237,16 @@
     </row>
     <row r="165" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B165" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C165" t="s">
         <v>252</v>
       </c>
       <c r="D165" t="s">
-        <v>330</v>
+        <v>253</v>
       </c>
       <c r="E165" t="s">
         <v>25</v>
@@ -10124,10 +10275,10 @@
     </row>
     <row r="166" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B166" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C166" t="s">
         <v>252</v>
@@ -10162,10 +10313,10 @@
     </row>
     <row r="167" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B167" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C167" t="s">
         <v>252</v>
@@ -10200,10 +10351,10 @@
     </row>
     <row r="168" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B168" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C168" t="s">
         <v>252</v>
@@ -10238,10 +10389,10 @@
     </row>
     <row r="169" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B169" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C169" t="s">
         <v>252</v>
@@ -10276,10 +10427,10 @@
     </row>
     <row r="170" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B170" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C170" t="s">
         <v>252</v>
@@ -10314,10 +10465,10 @@
     </row>
     <row r="171" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B171" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C171" t="s">
         <v>252</v>
@@ -10352,10 +10503,10 @@
     </row>
     <row r="172" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B172" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C172" t="s">
         <v>252</v>
@@ -10390,10 +10541,10 @@
     </row>
     <row r="173" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B173" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C173" t="s">
         <v>252</v>
@@ -10428,16 +10579,16 @@
     </row>
     <row r="174" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B174" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C174" t="s">
         <v>252</v>
       </c>
       <c r="D174" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="E174" t="s">
         <v>25</v>
@@ -10466,16 +10617,16 @@
     </row>
     <row r="175" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B175" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C175" t="s">
         <v>252</v>
       </c>
       <c r="D175" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="E175" t="s">
         <v>25</v>
@@ -10504,10 +10655,10 @@
     </row>
     <row r="176" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B176" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C176" t="s">
         <v>252</v>
@@ -10542,16 +10693,16 @@
     </row>
     <row r="177" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B177" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C177" t="s">
         <v>252</v>
       </c>
       <c r="D177" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="E177" t="s">
         <v>25</v>
@@ -10580,16 +10731,16 @@
     </row>
     <row r="178" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B178" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C178" t="s">
         <v>252</v>
       </c>
       <c r="D178" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="E178" t="s">
         <v>25</v>
@@ -10618,10 +10769,10 @@
     </row>
     <row r="179" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B179" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C179" t="s">
         <v>252</v>
@@ -10656,10 +10807,10 @@
     </row>
     <row r="180" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B180" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C180" t="s">
         <v>252</v>
@@ -10694,10 +10845,10 @@
     </row>
     <row r="181" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B181" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C181" t="s">
         <v>252</v>
@@ -10732,10 +10883,10 @@
     </row>
     <row r="182" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B182" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C182" t="s">
         <v>252</v>
@@ -10770,10 +10921,10 @@
     </row>
     <row r="183" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B183" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C183" t="s">
         <v>252</v>
@@ -10808,16 +10959,16 @@
     </row>
     <row r="184" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B184" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C184" t="s">
         <v>252</v>
       </c>
       <c r="D184" t="s">
-        <v>238</v>
+        <v>358</v>
       </c>
       <c r="E184" t="s">
         <v>25</v>
@@ -10846,16 +10997,16 @@
     </row>
     <row r="185" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B185" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C185" t="s">
         <v>252</v>
       </c>
       <c r="D185" t="s">
-        <v>238</v>
+        <v>358</v>
       </c>
       <c r="E185" t="s">
         <v>25</v>
@@ -10884,10 +11035,10 @@
     </row>
     <row r="186" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B186" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C186" t="s">
         <v>252</v>
@@ -10922,10 +11073,10 @@
     </row>
     <row r="187" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B187" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C187" t="s">
         <v>252</v>
@@ -10960,10 +11111,10 @@
     </row>
     <row r="188" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B188" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C188" t="s">
         <v>252</v>
@@ -10998,10 +11149,10 @@
     </row>
     <row r="189" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B189" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C189" t="s">
         <v>252</v>
@@ -11036,10 +11187,10 @@
     </row>
     <row r="190" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B190" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C190" t="s">
         <v>252</v>
@@ -11074,10 +11225,10 @@
     </row>
     <row r="191" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B191" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C191" t="s">
         <v>252</v>
@@ -11112,10 +11263,10 @@
     </row>
     <row r="192" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B192" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C192" t="s">
         <v>252</v>
@@ -11150,10 +11301,10 @@
     </row>
     <row r="193" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B193" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C193" t="s">
         <v>252</v>
@@ -11188,10 +11339,10 @@
     </row>
     <row r="194" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B194" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C194" t="s">
         <v>252</v>
@@ -11226,7 +11377,7 @@
     </row>
     <row r="195" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B195" t="s">
         <v>389</v>
@@ -11264,7 +11415,7 @@
     </row>
     <row r="196" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B196" t="s">
         <v>389</v>
@@ -11302,7 +11453,7 @@
     </row>
     <row r="197" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B197" t="s">
         <v>389</v>
@@ -11340,10 +11491,10 @@
     </row>
     <row r="198" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B198" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C198" t="s">
         <v>252</v>
@@ -11378,10 +11529,10 @@
     </row>
     <row r="199" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B199" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C199" t="s">
         <v>252</v>
@@ -11416,10 +11567,10 @@
     </row>
     <row r="200" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B200" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C200" t="s">
         <v>252</v>
@@ -11454,10 +11605,10 @@
     </row>
     <row r="201" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B201" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C201" t="s">
         <v>252</v>
@@ -11492,10 +11643,10 @@
     </row>
     <row r="202" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B202" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C202" t="s">
         <v>252</v>
@@ -11530,10 +11681,10 @@
     </row>
     <row r="203" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B203" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C203" t="s">
         <v>252</v>
@@ -11568,10 +11719,10 @@
     </row>
     <row r="204" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B204" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C204" t="s">
         <v>252</v>
@@ -11606,10 +11757,10 @@
     </row>
     <row r="205" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B205" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C205" t="s">
         <v>252</v>
@@ -11644,10 +11795,10 @@
     </row>
     <row r="206" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B206" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C206" t="s">
         <v>252</v>
@@ -11682,10 +11833,10 @@
     </row>
     <row r="207" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B207" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C207" t="s">
         <v>252</v>
@@ -11720,10 +11871,10 @@
     </row>
     <row r="208" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B208" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C208" t="s">
         <v>252</v>
@@ -11758,10 +11909,10 @@
     </row>
     <row r="209" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B209" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C209" t="s">
         <v>252</v>
@@ -11796,16 +11947,16 @@
     </row>
     <row r="210" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B210" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C210" t="s">
         <v>252</v>
       </c>
       <c r="D210" t="s">
-        <v>420</v>
+        <v>238</v>
       </c>
       <c r="E210" t="s">
         <v>25</v>
@@ -11834,16 +11985,16 @@
     </row>
     <row r="211" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B211" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C211" t="s">
         <v>252</v>
       </c>
       <c r="D211" t="s">
-        <v>420</v>
+        <v>238</v>
       </c>
       <c r="E211" t="s">
         <v>25</v>
@@ -11872,10 +12023,10 @@
     </row>
     <row r="212" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B212" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C212" t="s">
         <v>252</v>
@@ -11910,10 +12061,10 @@
     </row>
     <row r="213" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B213" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C213" t="s">
         <v>252</v>
@@ -11948,10 +12099,10 @@
     </row>
     <row r="214" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B214" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C214" t="s">
         <v>252</v>
@@ -11986,10 +12137,10 @@
     </row>
     <row r="215" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B215" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C215" t="s">
         <v>252</v>
@@ -12024,10 +12175,10 @@
     </row>
     <row r="216" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B216" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C216" t="s">
         <v>252</v>
@@ -12062,10 +12213,10 @@
     </row>
     <row r="217" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B217" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C217" t="s">
         <v>252</v>
@@ -12100,10 +12251,10 @@
     </row>
     <row r="218" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B218" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C218" t="s">
         <v>252</v>
@@ -12138,10 +12289,10 @@
     </row>
     <row r="219" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B219" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C219" t="s">
         <v>252</v>
@@ -12176,10 +12327,10 @@
     </row>
     <row r="220" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B220" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C220" t="s">
         <v>252</v>
@@ -12214,10 +12365,10 @@
     </row>
     <row r="221" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B221" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C221" t="s">
         <v>252</v>
@@ -12252,10 +12403,10 @@
     </row>
     <row r="222" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B222" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C222" t="s">
         <v>252</v>
@@ -12290,10 +12441,10 @@
     </row>
     <row r="223" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B223" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C223" t="s">
         <v>252</v>
@@ -12328,10 +12479,10 @@
     </row>
     <row r="224" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B224" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C224" t="s">
         <v>252</v>
@@ -12366,10 +12517,10 @@
     </row>
     <row r="225" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B225" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C225" t="s">
         <v>252</v>
@@ -12404,10 +12555,10 @@
     </row>
     <row r="226" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B226" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C226" t="s">
         <v>252</v>
@@ -12442,10 +12593,10 @@
     </row>
     <row r="227" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B227" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C227" t="s">
         <v>252</v>
@@ -12480,10 +12631,10 @@
     </row>
     <row r="228" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B228" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C228" t="s">
         <v>252</v>
@@ -12518,10 +12669,10 @@
     </row>
     <row r="229" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B229" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C229" t="s">
         <v>252</v>
@@ -12556,10 +12707,10 @@
     </row>
     <row r="230" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B230" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C230" t="s">
         <v>252</v>
@@ -12594,10 +12745,10 @@
     </row>
     <row r="231" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B231" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C231" t="s">
         <v>252</v>
@@ -12632,10 +12783,10 @@
     </row>
     <row r="232" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B232" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C232" t="s">
         <v>252</v>
@@ -12670,10 +12821,10 @@
     </row>
     <row r="233" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B233" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C233" t="s">
         <v>252</v>
@@ -12708,10 +12859,10 @@
     </row>
     <row r="234" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B234" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C234" t="s">
         <v>252</v>
@@ -12746,10 +12897,10 @@
     </row>
     <row r="235" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B235" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C235" t="s">
         <v>252</v>
@@ -12784,16 +12935,16 @@
     </row>
     <row r="236" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B236" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C236" t="s">
-        <v>473</v>
+        <v>252</v>
       </c>
       <c r="D236" t="s">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="E236" t="s">
         <v>25</v>
@@ -12822,16 +12973,16 @@
     </row>
     <row r="237" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B237" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C237" t="s">
-        <v>473</v>
+        <v>252</v>
       </c>
       <c r="D237" t="s">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="E237" t="s">
         <v>25</v>
@@ -12860,10 +13011,10 @@
     </row>
     <row r="238" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B238" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C238" t="s">
         <v>473</v>
@@ -12898,10 +13049,10 @@
     </row>
     <row r="239" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B239" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C239" t="s">
         <v>473</v>
@@ -12936,10 +13087,10 @@
     </row>
     <row r="240" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B240" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C240" t="s">
         <v>473</v>
@@ -12974,10 +13125,10 @@
     </row>
     <row r="241" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B241" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C241" t="s">
         <v>473</v>
@@ -13012,10 +13163,10 @@
     </row>
     <row r="242" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B242" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C242" t="s">
         <v>473</v>
@@ -13050,10 +13201,10 @@
     </row>
     <row r="243" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B243" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C243" t="s">
         <v>473</v>
@@ -13088,10 +13239,10 @@
     </row>
     <row r="244" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B244" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C244" t="s">
         <v>473</v>
@@ -13126,10 +13277,10 @@
     </row>
     <row r="245" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B245" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C245" t="s">
         <v>473</v>
@@ -13164,10 +13315,10 @@
     </row>
     <row r="246" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B246" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C246" t="s">
         <v>473</v>
@@ -13202,10 +13353,10 @@
     </row>
     <row r="247" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B247" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C247" t="s">
         <v>473</v>
@@ -13240,10 +13391,10 @@
     </row>
     <row r="248" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B248" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C248" t="s">
         <v>473</v>
@@ -13278,10 +13429,10 @@
     </row>
     <row r="249" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B249" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C249" t="s">
         <v>473</v>
@@ -13316,10 +13467,10 @@
     </row>
     <row r="250" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B250" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C250" t="s">
         <v>473</v>
@@ -13354,10 +13505,10 @@
     </row>
     <row r="251" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B251" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C251" t="s">
         <v>473</v>
@@ -13392,10 +13543,10 @@
     </row>
     <row r="252" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B252" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C252" t="s">
         <v>473</v>
@@ -13430,10 +13581,10 @@
     </row>
     <row r="253" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B253" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C253" t="s">
         <v>473</v>
@@ -13468,10 +13619,10 @@
     </row>
     <row r="254" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B254" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C254" t="s">
         <v>473</v>
@@ -13506,10 +13657,10 @@
     </row>
     <row r="255" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B255" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C255" t="s">
         <v>473</v>
@@ -13544,10 +13695,10 @@
     </row>
     <row r="256" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B256" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C256" t="s">
         <v>473</v>
@@ -13582,10 +13733,10 @@
     </row>
     <row r="257" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B257" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C257" t="s">
         <v>473</v>
@@ -13620,10 +13771,10 @@
     </row>
     <row r="258" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B258" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C258" t="s">
         <v>473</v>
@@ -13658,10 +13809,10 @@
     </row>
     <row r="259" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B259" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C259" t="s">
         <v>473</v>
@@ -13696,10 +13847,10 @@
     </row>
     <row r="260" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B260" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C260" t="s">
         <v>473</v>
@@ -13734,10 +13885,10 @@
     </row>
     <row r="261" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B261" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C261" t="s">
         <v>473</v>
@@ -13772,10 +13923,10 @@
     </row>
     <row r="262" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B262" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C262" t="s">
         <v>473</v>
@@ -13810,10 +13961,10 @@
     </row>
     <row r="263" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B263" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C263" t="s">
         <v>473</v>
@@ -13848,10 +13999,10 @@
     </row>
     <row r="264" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B264" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C264" t="s">
         <v>473</v>
@@ -13886,10 +14037,10 @@
     </row>
     <row r="265" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B265" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C265" t="s">
         <v>473</v>
@@ -13924,10 +14075,10 @@
     </row>
     <row r="266" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B266" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C266" t="s">
         <v>473</v>
@@ -13962,10 +14113,10 @@
     </row>
     <row r="267" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B267" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C267" t="s">
         <v>473</v>
@@ -14000,10 +14151,10 @@
     </row>
     <row r="268" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B268" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C268" t="s">
         <v>473</v>
@@ -14038,10 +14189,10 @@
     </row>
     <row r="269" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B269" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C269" t="s">
         <v>473</v>
@@ -14076,10 +14227,10 @@
     </row>
     <row r="270" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B270" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C270" t="s">
         <v>473</v>
@@ -14114,10 +14265,10 @@
     </row>
     <row r="271" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B271" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C271" t="s">
         <v>473</v>
@@ -14152,10 +14303,10 @@
     </row>
     <row r="272" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B272" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C272" t="s">
         <v>473</v>
@@ -14190,10 +14341,10 @@
     </row>
     <row r="273" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B273" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C273" t="s">
         <v>473</v>
@@ -14228,10 +14379,10 @@
     </row>
     <row r="274" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B274" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C274" t="s">
         <v>473</v>
@@ -14266,10 +14417,10 @@
     </row>
     <row r="275" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B275" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C275" t="s">
         <v>473</v>
@@ -14304,10 +14455,10 @@
     </row>
     <row r="276" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B276" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C276" t="s">
         <v>473</v>
@@ -14342,10 +14493,10 @@
     </row>
     <row r="277" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B277" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C277" t="s">
         <v>473</v>
@@ -14380,10 +14531,10 @@
     </row>
     <row r="278" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B278" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C278" t="s">
         <v>473</v>
@@ -14418,10 +14569,10 @@
     </row>
     <row r="279" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B279" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C279" t="s">
         <v>473</v>
@@ -14456,10 +14607,10 @@
     </row>
     <row r="280" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B280" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C280" t="s">
         <v>473</v>
@@ -14494,10 +14645,10 @@
     </row>
     <row r="281" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B281" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C281" t="s">
         <v>473</v>
@@ -14532,10 +14683,10 @@
     </row>
     <row r="282" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B282" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C282" t="s">
         <v>473</v>
@@ -14570,16 +14721,16 @@
     </row>
     <row r="283" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B283" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C283" t="s">
         <v>473</v>
       </c>
       <c r="D283" t="s">
-        <v>569</v>
+        <v>474</v>
       </c>
       <c r="E283" t="s">
         <v>25</v>
@@ -14608,16 +14759,16 @@
     </row>
     <row r="284" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B284" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C284" t="s">
         <v>473</v>
       </c>
       <c r="D284" t="s">
-        <v>569</v>
+        <v>474</v>
       </c>
       <c r="E284" t="s">
         <v>25</v>
@@ -14646,10 +14797,10 @@
     </row>
     <row r="285" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B285" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="C285" t="s">
         <v>473</v>
@@ -14684,10 +14835,10 @@
     </row>
     <row r="286" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B286" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C286" t="s">
         <v>473</v>
@@ -14722,10 +14873,10 @@
     </row>
     <row r="287" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B287" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C287" t="s">
         <v>473</v>
@@ -14760,10 +14911,10 @@
     </row>
     <row r="288" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B288" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C288" t="s">
         <v>473</v>
@@ -14798,10 +14949,10 @@
     </row>
     <row r="289" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B289" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C289" t="s">
         <v>473</v>
@@ -14836,10 +14987,10 @@
     </row>
     <row r="290" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B290" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C290" t="s">
         <v>473</v>
@@ -14874,10 +15025,10 @@
     </row>
     <row r="291" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B291" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C291" t="s">
         <v>473</v>
@@ -14912,10 +15063,10 @@
     </row>
     <row r="292" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B292" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C292" t="s">
         <v>473</v>
@@ -14950,10 +15101,10 @@
     </row>
     <row r="293" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B293" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C293" t="s">
         <v>473</v>
@@ -14988,10 +15139,10 @@
     </row>
     <row r="294" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B294" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C294" t="s">
         <v>473</v>
@@ -15026,10 +15177,10 @@
     </row>
     <row r="295" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B295" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C295" t="s">
         <v>473</v>
@@ -15064,10 +15215,10 @@
     </row>
     <row r="296" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B296" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C296" t="s">
         <v>473</v>
@@ -15102,10 +15253,10 @@
     </row>
     <row r="297" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B297" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C297" t="s">
         <v>473</v>
@@ -15140,10 +15291,10 @@
     </row>
     <row r="298" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B298" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C298" t="s">
         <v>473</v>
@@ -15178,10 +15329,10 @@
     </row>
     <row r="299" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B299" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C299" t="s">
         <v>473</v>
@@ -15216,10 +15367,10 @@
     </row>
     <row r="300" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B300" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C300" t="s">
         <v>473</v>
@@ -15254,10 +15405,10 @@
     </row>
     <row r="301" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B301" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C301" t="s">
         <v>473</v>
@@ -15292,10 +15443,10 @@
     </row>
     <row r="302" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B302" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C302" t="s">
         <v>473</v>
@@ -15330,10 +15481,10 @@
     </row>
     <row r="303" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B303" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C303" t="s">
         <v>473</v>
@@ -15368,10 +15519,10 @@
     </row>
     <row r="304" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B304" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C304" t="s">
         <v>473</v>
@@ -15406,10 +15557,10 @@
     </row>
     <row r="305" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B305" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C305" t="s">
         <v>473</v>
@@ -15444,10 +15595,10 @@
     </row>
     <row r="306" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B306" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C306" t="s">
         <v>473</v>
@@ -15482,10 +15633,10 @@
     </row>
     <row r="307" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B307" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C307" t="s">
         <v>473</v>
@@ -15520,10 +15671,10 @@
     </row>
     <row r="308" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B308" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C308" t="s">
         <v>473</v>
@@ -15558,10 +15709,10 @@
     </row>
     <row r="309" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B309" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C309" t="s">
         <v>473</v>
@@ -15596,10 +15747,10 @@
     </row>
     <row r="310" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B310" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C310" t="s">
         <v>473</v>
@@ -15634,10 +15785,10 @@
     </row>
     <row r="311" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B311" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C311" t="s">
         <v>473</v>
@@ -15672,10 +15823,10 @@
     </row>
     <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B312" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C312" t="s">
         <v>473</v>
@@ -15710,10 +15861,10 @@
     </row>
     <row r="313" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B313" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C313" t="s">
         <v>473</v>
@@ -15748,10 +15899,10 @@
     </row>
     <row r="314" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B314" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C314" t="s">
         <v>473</v>
@@ -15786,10 +15937,10 @@
     </row>
     <row r="315" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B315" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C315" t="s">
         <v>473</v>
@@ -15824,10 +15975,10 @@
     </row>
     <row r="316" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B316" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C316" t="s">
         <v>473</v>
@@ -15862,16 +16013,16 @@
     </row>
     <row r="317" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B317" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C317" t="s">
-        <v>638</v>
+        <v>473</v>
       </c>
       <c r="D317" t="s">
-        <v>25</v>
+        <v>569</v>
       </c>
       <c r="E317" t="s">
         <v>25</v>
@@ -15900,16 +16051,16 @@
     </row>
     <row r="318" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B318" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C318" t="s">
-        <v>638</v>
+        <v>473</v>
       </c>
       <c r="D318" t="s">
-        <v>25</v>
+        <v>569</v>
       </c>
       <c r="E318" t="s">
         <v>25</v>
@@ -15938,10 +16089,10 @@
     </row>
     <row r="319" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B319" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C319" t="s">
         <v>638</v>
@@ -15976,10 +16127,10 @@
     </row>
     <row r="320" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B320" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C320" t="s">
         <v>638</v>
@@ -16014,10 +16165,10 @@
     </row>
     <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B321" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C321" t="s">
         <v>638</v>
@@ -16052,10 +16203,10 @@
     </row>
     <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B322" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C322" t="s">
         <v>638</v>
@@ -16090,10 +16241,10 @@
     </row>
     <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B323" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C323" t="s">
         <v>638</v>
@@ -16128,10 +16279,10 @@
     </row>
     <row r="324" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B324" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C324" t="s">
         <v>638</v>
@@ -16166,16 +16317,16 @@
     </row>
     <row r="325" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B325" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C325" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="D325" t="s">
-        <v>656</v>
+        <v>25</v>
       </c>
       <c r="E325" t="s">
         <v>25</v>
@@ -16204,16 +16355,16 @@
     </row>
     <row r="326" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="B326" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C326" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="D326" t="s">
-        <v>656</v>
+        <v>25</v>
       </c>
       <c r="E326" t="s">
         <v>25</v>
@@ -16242,10 +16393,10 @@
     </row>
     <row r="327" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B327" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C327" t="s">
         <v>655</v>
@@ -16280,10 +16431,10 @@
     </row>
     <row r="328" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B328" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C328" t="s">
         <v>655</v>
@@ -16318,16 +16469,16 @@
     </row>
     <row r="329" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B329" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C329" t="s">
         <v>655</v>
       </c>
       <c r="D329" t="s">
-        <v>149</v>
+        <v>656</v>
       </c>
       <c r="E329" t="s">
         <v>25</v>
@@ -16356,16 +16507,16 @@
     </row>
     <row r="330" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B330" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C330" t="s">
         <v>655</v>
       </c>
       <c r="D330" t="s">
-        <v>149</v>
+        <v>656</v>
       </c>
       <c r="E330" t="s">
         <v>25</v>
@@ -16394,10 +16545,10 @@
     </row>
     <row r="331" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B331" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C331" t="s">
         <v>655</v>
@@ -16432,10 +16583,10 @@
     </row>
     <row r="332" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B332" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C332" t="s">
         <v>655</v>
@@ -16470,16 +16621,16 @@
     </row>
     <row r="333" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B333" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C333" t="s">
         <v>655</v>
       </c>
       <c r="D333" t="s">
-        <v>673</v>
+        <v>149</v>
       </c>
       <c r="E333" t="s">
         <v>25</v>
@@ -16508,16 +16659,16 @@
     </row>
     <row r="334" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="B334" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="C334" t="s">
         <v>655</v>
       </c>
       <c r="D334" t="s">
-        <v>673</v>
+        <v>149</v>
       </c>
       <c r="E334" t="s">
         <v>25</v>
@@ -16546,10 +16697,10 @@
     </row>
     <row r="335" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="B335" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="C335" t="s">
         <v>655</v>
@@ -16584,10 +16735,10 @@
     </row>
     <row r="336" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B336" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C336" t="s">
         <v>655</v>
@@ -16622,10 +16773,10 @@
     </row>
     <row r="337" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B337" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C337" t="s">
         <v>655</v>
@@ -16660,16 +16811,16 @@
     </row>
     <row r="338" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B338" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C338" t="s">
         <v>655</v>
       </c>
       <c r="D338" t="s">
-        <v>138</v>
+        <v>673</v>
       </c>
       <c r="E338" t="s">
         <v>25</v>
@@ -16698,16 +16849,16 @@
     </row>
     <row r="339" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B339" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C339" t="s">
         <v>655</v>
       </c>
       <c r="D339" t="s">
-        <v>138</v>
+        <v>673</v>
       </c>
       <c r="E339" t="s">
         <v>25</v>
@@ -16736,16 +16887,16 @@
     </row>
     <row r="340" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B340" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C340" t="s">
         <v>655</v>
       </c>
       <c r="D340" t="s">
-        <v>688</v>
+        <v>138</v>
       </c>
       <c r="E340" t="s">
         <v>25</v>
@@ -16774,16 +16925,16 @@
     </row>
     <row r="341" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="B341" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="C341" t="s">
         <v>655</v>
       </c>
       <c r="D341" t="s">
-        <v>688</v>
+        <v>138</v>
       </c>
       <c r="E341" t="s">
         <v>25</v>
@@ -16812,10 +16963,10 @@
     </row>
     <row r="342" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B342" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="C342" t="s">
         <v>655</v>
@@ -16850,10 +17001,10 @@
     </row>
     <row r="343" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B343" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C343" t="s">
         <v>655</v>
@@ -16888,16 +17039,16 @@
     </row>
     <row r="344" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B344" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C344" t="s">
-        <v>696</v>
+        <v>655</v>
       </c>
       <c r="D344" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="E344" t="s">
         <v>25</v>
@@ -16926,16 +17077,16 @@
     </row>
     <row r="345" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="B345" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C345" t="s">
-        <v>696</v>
+        <v>655</v>
       </c>
       <c r="D345" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="E345" t="s">
         <v>25</v>
@@ -16964,10 +17115,10 @@
     </row>
     <row r="346" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="B346" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="C346" t="s">
         <v>696</v>
@@ -17002,10 +17153,10 @@
     </row>
     <row r="347" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B347" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C347" t="s">
         <v>696</v>
@@ -17040,10 +17191,10 @@
     </row>
     <row r="348" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B348" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C348" t="s">
         <v>696</v>
@@ -17078,10 +17229,10 @@
     </row>
     <row r="349" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B349" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="C349" t="s">
         <v>696</v>
@@ -17116,16 +17267,16 @@
     </row>
     <row r="350" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B350" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C350" t="s">
         <v>696</v>
       </c>
       <c r="D350" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="E350" t="s">
         <v>25</v>
@@ -17154,16 +17305,16 @@
     </row>
     <row r="351" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="B351" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="C351" t="s">
         <v>696</v>
       </c>
       <c r="D351" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="E351" t="s">
         <v>25</v>
@@ -17192,10 +17343,10 @@
     </row>
     <row r="352" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="B352" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C352" t="s">
         <v>696</v>
@@ -17230,16 +17381,16 @@
     </row>
     <row r="353" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B353" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C353" t="s">
         <v>696</v>
       </c>
       <c r="D353" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="E353" t="s">
         <v>25</v>
@@ -17268,16 +17419,16 @@
     </row>
     <row r="354" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B354" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="C354" t="s">
         <v>696</v>
       </c>
       <c r="D354" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="E354" t="s">
         <v>25</v>
@@ -17306,10 +17457,10 @@
     </row>
     <row r="355" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B355" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="C355" t="s">
         <v>696</v>
@@ -17344,10 +17495,10 @@
     </row>
     <row r="356" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B356" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C356" t="s">
         <v>696</v>
@@ -17382,16 +17533,16 @@
     </row>
     <row r="357" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B357" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C357" t="s">
         <v>696</v>
       </c>
       <c r="D357" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="E357" t="s">
         <v>25</v>
@@ -17420,16 +17571,16 @@
     </row>
     <row r="358" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="B358" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C358" t="s">
         <v>696</v>
       </c>
       <c r="D358" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="E358" t="s">
         <v>25</v>
@@ -17458,10 +17609,10 @@
     </row>
     <row r="359" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B359" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C359" t="s">
         <v>696</v>
@@ -17496,16 +17647,16 @@
     </row>
     <row r="360" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B360" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C360" t="s">
         <v>696</v>
       </c>
       <c r="D360" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E360" t="s">
         <v>25</v>
@@ -17534,16 +17685,16 @@
     </row>
     <row r="361" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="B361" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="C361" t="s">
         <v>696</v>
       </c>
       <c r="D361" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E361" t="s">
         <v>25</v>
@@ -17572,10 +17723,10 @@
     </row>
     <row r="362" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B362" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C362" t="s">
         <v>696</v>
@@ -17610,10 +17761,10 @@
     </row>
     <row r="363" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B363" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C363" t="s">
         <v>696</v>
@@ -17648,10 +17799,10 @@
     </row>
     <row r="364" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B364" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C364" t="s">
         <v>696</v>
@@ -17686,16 +17837,16 @@
     </row>
     <row r="365" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B365" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C365" t="s">
         <v>696</v>
       </c>
       <c r="D365" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="E365" t="s">
         <v>25</v>
@@ -17724,16 +17875,16 @@
     </row>
     <row r="366" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B366" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C366" t="s">
         <v>696</v>
       </c>
       <c r="D366" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="E366" t="s">
         <v>25</v>
@@ -17762,10 +17913,10 @@
     </row>
     <row r="367" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="B367" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="C367" t="s">
         <v>696</v>
@@ -17800,10 +17951,10 @@
     </row>
     <row r="368" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B368" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="C368" t="s">
         <v>696</v>
@@ -17838,10 +17989,10 @@
     </row>
     <row r="369" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B369" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C369" t="s">
         <v>696</v>
@@ -17876,10 +18027,10 @@
     </row>
     <row r="370" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B370" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C370" t="s">
         <v>696</v>
@@ -17914,16 +18065,16 @@
     </row>
     <row r="371" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B371" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="C371" t="s">
         <v>696</v>
       </c>
       <c r="D371" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="E371" t="s">
         <v>25</v>
@@ -17952,16 +18103,16 @@
     </row>
     <row r="372" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B372" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="C372" t="s">
         <v>696</v>
       </c>
       <c r="D372" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="E372" t="s">
         <v>25</v>
@@ -17990,16 +18141,16 @@
     </row>
     <row r="373" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B373" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C373" t="s">
-        <v>761</v>
+        <v>696</v>
       </c>
       <c r="D373" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E373" t="s">
         <v>25</v>
@@ -18028,16 +18179,16 @@
     </row>
     <row r="374" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="B374" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C374" t="s">
-        <v>761</v>
+        <v>696</v>
       </c>
       <c r="D374" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E374" t="s">
         <v>25</v>
@@ -18066,10 +18217,10 @@
     </row>
     <row r="375" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B375" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C375" t="s">
         <v>761</v>
@@ -18104,10 +18255,10 @@
     </row>
     <row r="376" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B376" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C376" t="s">
         <v>761</v>
@@ -18142,10 +18293,10 @@
     </row>
     <row r="377" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B377" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C377" t="s">
         <v>761</v>
@@ -18180,10 +18331,10 @@
     </row>
     <row r="378" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B378" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C378" t="s">
         <v>761</v>
@@ -18218,10 +18369,10 @@
     </row>
     <row r="379" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B379" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C379" t="s">
         <v>761</v>
@@ -18256,10 +18407,10 @@
     </row>
     <row r="380" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B380" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C380" t="s">
         <v>761</v>
@@ -18294,10 +18445,10 @@
     </row>
     <row r="381" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B381" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="C381" t="s">
         <v>761</v>
@@ -18332,10 +18483,10 @@
     </row>
     <row r="382" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B382" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C382" t="s">
         <v>761</v>
@@ -18370,10 +18521,10 @@
     </row>
     <row r="383" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B383" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C383" t="s">
         <v>761</v>
@@ -18408,10 +18559,10 @@
     </row>
     <row r="384" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B384" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C384" t="s">
         <v>761</v>
@@ -18446,10 +18597,10 @@
     </row>
     <row r="385" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B385" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C385" t="s">
         <v>761</v>
@@ -18484,16 +18635,16 @@
     </row>
     <row r="386" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B386" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C386" t="s">
         <v>761</v>
       </c>
       <c r="D386" t="s">
-        <v>789</v>
+        <v>762</v>
       </c>
       <c r="E386" t="s">
         <v>25</v>
@@ -18522,16 +18673,16 @@
     </row>
     <row r="387" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="B387" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="C387" t="s">
         <v>761</v>
       </c>
       <c r="D387" t="s">
-        <v>789</v>
+        <v>762</v>
       </c>
       <c r="E387" t="s">
         <v>25</v>
@@ -18560,10 +18711,10 @@
     </row>
     <row r="388" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="B388" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C388" t="s">
         <v>761</v>
@@ -18598,10 +18749,10 @@
     </row>
     <row r="389" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B389" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="C389" t="s">
         <v>761</v>
@@ -18636,10 +18787,10 @@
     </row>
     <row r="390" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B390" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="C390" t="s">
         <v>761</v>
@@ -18674,16 +18825,16 @@
     </row>
     <row r="391" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B391" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="C391" t="s">
         <v>761</v>
       </c>
       <c r="D391" t="s">
-        <v>211</v>
+        <v>789</v>
       </c>
       <c r="E391" t="s">
         <v>25</v>
@@ -18712,16 +18863,16 @@
     </row>
     <row r="392" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B392" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="C392" t="s">
         <v>761</v>
       </c>
       <c r="D392" t="s">
-        <v>211</v>
+        <v>789</v>
       </c>
       <c r="E392" t="s">
         <v>25</v>
@@ -18750,10 +18901,10 @@
     </row>
     <row r="393" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B393" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="C393" t="s">
         <v>761</v>
@@ -18788,16 +18939,16 @@
     </row>
     <row r="394" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B394" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C394" t="s">
         <v>761</v>
       </c>
       <c r="D394" t="s">
-        <v>806</v>
+        <v>211</v>
       </c>
       <c r="E394" t="s">
         <v>25</v>
@@ -18826,16 +18977,16 @@
     </row>
     <row r="395" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B395" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C395" t="s">
         <v>761</v>
       </c>
       <c r="D395" t="s">
-        <v>806</v>
+        <v>211</v>
       </c>
       <c r="E395" t="s">
         <v>25</v>
@@ -18864,16 +19015,16 @@
     </row>
     <row r="396" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="B396" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="C396" t="s">
         <v>761</v>
       </c>
       <c r="D396" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="E396" t="s">
         <v>25</v>
@@ -18902,16 +19053,16 @@
     </row>
     <row r="397" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="B397" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="C397" t="s">
         <v>761</v>
       </c>
       <c r="D397" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="E397" t="s">
         <v>25</v>
@@ -18940,10 +19091,10 @@
     </row>
     <row r="398" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="B398" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="C398" t="s">
         <v>761</v>
@@ -18978,16 +19129,16 @@
     </row>
     <row r="399" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B399" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C399" t="s">
         <v>761</v>
       </c>
       <c r="D399" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="E399" t="s">
         <v>25</v>
@@ -19016,16 +19167,16 @@
     </row>
     <row r="400" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="B400" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="C400" t="s">
         <v>761</v>
       </c>
       <c r="D400" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="E400" t="s">
         <v>25</v>
@@ -19054,10 +19205,10 @@
     </row>
     <row r="401" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="B401" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C401" t="s">
         <v>761</v>
@@ -19092,10 +19243,10 @@
     </row>
     <row r="402" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B402" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="C402" t="s">
         <v>761</v>
@@ -19130,10 +19281,10 @@
     </row>
     <row r="403" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B403" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="C403" t="s">
         <v>761</v>
@@ -19168,10 +19319,10 @@
     </row>
     <row r="404" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B404" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="C404" t="s">
         <v>761</v>
@@ -19206,10 +19357,10 @@
     </row>
     <row r="405" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B405" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C405" t="s">
         <v>761</v>
@@ -19244,10 +19395,10 @@
     </row>
     <row r="406" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B406" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="C406" t="s">
         <v>761</v>
@@ -19282,10 +19433,10 @@
     </row>
     <row r="407" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B407" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C407" t="s">
         <v>761</v>
@@ -19320,10 +19471,10 @@
     </row>
     <row r="408" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B408" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="C408" t="s">
         <v>761</v>
@@ -19358,10 +19509,10 @@
     </row>
     <row r="409" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B409" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="C409" t="s">
         <v>761</v>
@@ -19396,10 +19547,10 @@
     </row>
     <row r="410" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B410" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="C410" t="s">
         <v>761</v>
@@ -19434,16 +19585,16 @@
     </row>
     <row r="411" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B411" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="C411" t="s">
         <v>761</v>
       </c>
       <c r="D411" t="s">
-        <v>843</v>
+        <v>818</v>
       </c>
       <c r="E411" t="s">
         <v>25</v>
@@ -19472,16 +19623,16 @@
     </row>
     <row r="412" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="B412" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="C412" t="s">
         <v>761</v>
       </c>
       <c r="D412" t="s">
-        <v>843</v>
+        <v>818</v>
       </c>
       <c r="E412" t="s">
         <v>25</v>
@@ -19510,10 +19661,10 @@
     </row>
     <row r="413" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B413" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C413" t="s">
         <v>761</v>
@@ -19548,10 +19699,10 @@
     </row>
     <row r="414" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B414" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C414" t="s">
         <v>761</v>
@@ -19586,10 +19737,10 @@
     </row>
     <row r="415" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B415" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="C415" t="s">
         <v>761</v>
@@ -19624,16 +19775,16 @@
     </row>
     <row r="416" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B416" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C416" t="s">
         <v>761</v>
       </c>
       <c r="D416" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="E416" t="s">
         <v>25</v>
@@ -19662,16 +19813,16 @@
     </row>
     <row r="417" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="B417" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C417" t="s">
         <v>761</v>
       </c>
       <c r="D417" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="E417" t="s">
         <v>25</v>
@@ -19700,16 +19851,16 @@
     </row>
     <row r="418" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="B418" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="C418" t="s">
-        <v>859</v>
+        <v>761</v>
       </c>
       <c r="D418" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="E418" t="s">
         <v>25</v>
@@ -19738,16 +19889,16 @@
     </row>
     <row r="419" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="B419" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="C419" t="s">
-        <v>859</v>
+        <v>761</v>
       </c>
       <c r="D419" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="E419" t="s">
         <v>25</v>
@@ -19776,10 +19927,10 @@
     </row>
     <row r="420" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="B420" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="C420" t="s">
         <v>859</v>
@@ -19814,10 +19965,10 @@
     </row>
     <row r="421" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B421" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="C421" t="s">
         <v>859</v>
@@ -19852,10 +20003,10 @@
     </row>
     <row r="422" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B422" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C422" t="s">
         <v>859</v>
@@ -19890,10 +20041,10 @@
     </row>
     <row r="423" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B423" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="C423" t="s">
         <v>859</v>
@@ -19928,16 +20079,16 @@
     </row>
     <row r="424" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B424" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C424" t="s">
         <v>859</v>
       </c>
       <c r="D424" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="E424" t="s">
         <v>25</v>
@@ -19966,16 +20117,16 @@
     </row>
     <row r="425" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="B425" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="C425" t="s">
         <v>859</v>
       </c>
       <c r="D425" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="E425" t="s">
         <v>25</v>
@@ -20004,10 +20155,10 @@
     </row>
     <row r="426" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="B426" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="C426" t="s">
         <v>859</v>
@@ -20042,10 +20193,10 @@
     </row>
     <row r="427" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="B427" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="C427" t="s">
         <v>859</v>
@@ -20080,10 +20231,10 @@
     </row>
     <row r="428" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="B428" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="C428" t="s">
         <v>859</v>
@@ -20118,16 +20269,16 @@
     </row>
     <row r="429" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B429" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C429" t="s">
         <v>859</v>
       </c>
       <c r="D429" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="E429" t="s">
         <v>25</v>
@@ -20156,16 +20307,16 @@
     </row>
     <row r="430" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="B430" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C430" t="s">
         <v>859</v>
       </c>
       <c r="D430" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="E430" t="s">
         <v>25</v>
@@ -20194,10 +20345,10 @@
     </row>
     <row r="431" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="B431" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="C431" t="s">
         <v>859</v>
@@ -20232,16 +20383,16 @@
     </row>
     <row r="432" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B432" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="C432" t="s">
         <v>859</v>
       </c>
       <c r="D432" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="E432" t="s">
         <v>25</v>
@@ -20270,16 +20421,16 @@
     </row>
     <row r="433" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="B433" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C433" t="s">
         <v>859</v>
       </c>
       <c r="D433" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="E433" t="s">
         <v>25</v>
@@ -20308,16 +20459,16 @@
     </row>
     <row r="434" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B434" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="C434" t="s">
         <v>859</v>
       </c>
       <c r="D434" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="E434" t="s">
         <v>25</v>
@@ -20346,16 +20497,16 @@
     </row>
     <row r="435" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="B435" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="C435" t="s">
         <v>859</v>
       </c>
       <c r="D435" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="E435" t="s">
         <v>25</v>
@@ -20384,10 +20535,10 @@
     </row>
     <row r="436" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="B436" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="C436" t="s">
         <v>859</v>
@@ -20422,10 +20573,10 @@
     </row>
     <row r="437" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B437" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="C437" t="s">
         <v>859</v>
@@ -20460,16 +20611,16 @@
     </row>
     <row r="438" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B438" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="C438" t="s">
         <v>859</v>
       </c>
       <c r="D438" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="E438" t="s">
         <v>25</v>
@@ -20498,16 +20649,16 @@
     </row>
     <row r="439" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="B439" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="C439" t="s">
         <v>859</v>
       </c>
       <c r="D439" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="E439" t="s">
         <v>25</v>
@@ -20536,10 +20687,10 @@
     </row>
     <row r="440" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="B440" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="C440" t="s">
         <v>859</v>
@@ -20574,10 +20725,10 @@
     </row>
     <row r="441" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B441" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="C441" t="s">
         <v>859</v>
@@ -20612,10 +20763,10 @@
     </row>
     <row r="442" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B442" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C442" t="s">
         <v>859</v>
@@ -20650,16 +20801,16 @@
     </row>
     <row r="443" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B443" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="C443" t="s">
-        <v>916</v>
+        <v>859</v>
       </c>
       <c r="D443" t="s">
-        <v>25</v>
+        <v>905</v>
       </c>
       <c r="E443" t="s">
         <v>25</v>
@@ -20688,16 +20839,16 @@
     </row>
     <row r="444" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="B444" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="C444" t="s">
-        <v>916</v>
+        <v>859</v>
       </c>
       <c r="D444" t="s">
-        <v>25</v>
+        <v>905</v>
       </c>
       <c r="E444" t="s">
         <v>25</v>
@@ -20726,10 +20877,10 @@
     </row>
     <row r="445" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="B445" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="C445" t="s">
         <v>916</v>
@@ -20764,10 +20915,10 @@
     </row>
     <row r="446" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B446" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="C446" t="s">
         <v>916</v>
@@ -20802,10 +20953,10 @@
     </row>
     <row r="447" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B447" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="C447" t="s">
         <v>916</v>
@@ -20840,10 +20991,10 @@
     </row>
     <row r="448" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B448" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C448" t="s">
         <v>916</v>
@@ -20878,10 +21029,10 @@
     </row>
     <row r="449" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B449" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="C449" t="s">
         <v>916</v>
@@ -20916,10 +21067,10 @@
     </row>
     <row r="450" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B450" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C450" t="s">
         <v>916</v>
@@ -20954,10 +21105,10 @@
     </row>
     <row r="451" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B451" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C451" t="s">
         <v>916</v>
@@ -20992,10 +21143,10 @@
     </row>
     <row r="452" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B452" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C452" t="s">
         <v>916</v>
@@ -21030,10 +21181,10 @@
     </row>
     <row r="453" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B453" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="C453" t="s">
         <v>916</v>
@@ -21068,10 +21219,10 @@
     </row>
     <row r="454" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B454" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C454" t="s">
         <v>916</v>
@@ -21106,10 +21257,10 @@
     </row>
     <row r="455" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="B455" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C455" t="s">
         <v>916</v>
@@ -21144,10 +21295,10 @@
     </row>
     <row r="456" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B456" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="C456" t="s">
         <v>916</v>
@@ -21182,10 +21333,10 @@
     </row>
     <row r="457" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B457" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C457" t="s">
         <v>916</v>
@@ -21220,16 +21371,16 @@
     </row>
     <row r="458" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B458" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C458" t="s">
-        <v>947</v>
+        <v>916</v>
       </c>
       <c r="D458" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E458" t="s">
         <v>25</v>
@@ -21258,16 +21409,16 @@
     </row>
     <row r="459" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B459" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="C459" t="s">
-        <v>947</v>
+        <v>916</v>
       </c>
       <c r="D459" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E459" t="s">
         <v>25</v>
@@ -21296,10 +21447,10 @@
     </row>
     <row r="460" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="B460" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="C460" t="s">
         <v>947</v>
@@ -21334,10 +21485,10 @@
     </row>
     <row r="461" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B461" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C461" t="s">
         <v>947</v>
@@ -21372,16 +21523,16 @@
     </row>
     <row r="462" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B462" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="C462" t="s">
         <v>947</v>
       </c>
       <c r="D462" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="E462" t="s">
         <v>25</v>
@@ -21410,16 +21561,16 @@
     </row>
     <row r="463" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="B463" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="C463" t="s">
         <v>947</v>
       </c>
       <c r="D463" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="E463" t="s">
         <v>25</v>
@@ -21448,10 +21599,10 @@
     </row>
     <row r="464" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="B464" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="C464" t="s">
         <v>947</v>
@@ -21486,10 +21637,10 @@
     </row>
     <row r="465" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B465" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C465" t="s">
         <v>947</v>
@@ -21524,10 +21675,10 @@
     </row>
     <row r="466" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B466" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="C466" t="s">
         <v>947</v>
@@ -21562,10 +21713,10 @@
     </row>
     <row r="467" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B467" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="C467" t="s">
         <v>947</v>
@@ -21600,10 +21751,10 @@
     </row>
     <row r="468" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="B468" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="C468" t="s">
         <v>947</v>
@@ -21638,16 +21789,16 @@
     </row>
     <row r="469" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="B469" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="C469" t="s">
-        <v>972</v>
+        <v>947</v>
       </c>
       <c r="D469" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="E469" t="s">
         <v>25</v>
@@ -21676,16 +21827,16 @@
     </row>
     <row r="470" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="B470" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="C470" t="s">
-        <v>972</v>
+        <v>947</v>
       </c>
       <c r="D470" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="E470" t="s">
         <v>25</v>
@@ -21714,10 +21865,10 @@
     </row>
     <row r="471" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="B471" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="C471" t="s">
         <v>972</v>
@@ -21752,10 +21903,10 @@
     </row>
     <row r="472" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B472" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="C472" t="s">
         <v>972</v>
@@ -21790,10 +21941,10 @@
     </row>
     <row r="473" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B473" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="C473" t="s">
         <v>972</v>
@@ -21828,10 +21979,10 @@
     </row>
     <row r="474" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B474" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="C474" t="s">
         <v>972</v>
@@ -21866,10 +22017,10 @@
     </row>
     <row r="475" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="B475" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="C475" t="s">
         <v>972</v>
@@ -21904,10 +22055,10 @@
     </row>
     <row r="476" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B476" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="C476" t="s">
         <v>972</v>
@@ -21942,16 +22093,16 @@
     </row>
     <row r="477" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B477" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="C477" t="s">
         <v>972</v>
       </c>
       <c r="D477" t="s">
-        <v>990</v>
+        <v>973</v>
       </c>
       <c r="E477" t="s">
         <v>25</v>
@@ -21980,16 +22131,16 @@
     </row>
     <row r="478" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="B478" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="C478" t="s">
         <v>972</v>
       </c>
       <c r="D478" t="s">
-        <v>990</v>
+        <v>973</v>
       </c>
       <c r="E478" t="s">
         <v>25</v>
@@ -22018,10 +22169,10 @@
     </row>
     <row r="479" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="B479" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="C479" t="s">
         <v>972</v>
@@ -22056,10 +22207,10 @@
     </row>
     <row r="480" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B480" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C480" t="s">
         <v>972</v>
@@ -22094,10 +22245,10 @@
     </row>
     <row r="481" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B481" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C481" t="s">
         <v>972</v>
@@ -22132,16 +22283,16 @@
     </row>
     <row r="482" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B482" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C482" t="s">
         <v>972</v>
       </c>
       <c r="D482" t="s">
-        <v>1001</v>
+        <v>990</v>
       </c>
       <c r="E482" t="s">
         <v>25</v>
@@ -22170,16 +22321,16 @@
     </row>
     <row r="483" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="B483" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="C483" t="s">
         <v>972</v>
       </c>
       <c r="D483" t="s">
-        <v>1001</v>
+        <v>990</v>
       </c>
       <c r="E483" t="s">
         <v>25</v>
@@ -22208,16 +22359,16 @@
     </row>
     <row r="484" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="B484" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="C484" t="s">
         <v>972</v>
       </c>
       <c r="D484" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="E484" t="s">
         <v>25</v>
@@ -22246,16 +22397,16 @@
     </row>
     <row r="485" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="B485" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="C485" t="s">
         <v>972</v>
       </c>
       <c r="D485" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="E485" t="s">
         <v>25</v>
@@ -22284,10 +22435,10 @@
     </row>
     <row r="486" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="B486" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="C486" t="s">
         <v>972</v>
@@ -22322,10 +22473,10 @@
     </row>
     <row r="487" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="B487" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="C487" t="s">
         <v>972</v>
@@ -22360,10 +22511,10 @@
     </row>
     <row r="488" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="B488" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C488" t="s">
         <v>972</v>
@@ -22398,10 +22549,10 @@
     </row>
     <row r="489" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="B489" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="C489" t="s">
         <v>972</v>
@@ -22436,16 +22587,16 @@
     </row>
     <row r="490" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="B490" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C490" t="s">
         <v>972</v>
       </c>
       <c r="D490" t="s">
-        <v>1019</v>
+        <v>1006</v>
       </c>
       <c r="E490" t="s">
         <v>25</v>
@@ -22474,16 +22625,16 @@
     </row>
     <row r="491" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="B491" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="C491" t="s">
         <v>972</v>
       </c>
       <c r="D491" t="s">
-        <v>1019</v>
+        <v>1006</v>
       </c>
       <c r="E491" t="s">
         <v>25</v>
@@ -22512,10 +22663,10 @@
     </row>
     <row r="492" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="B492" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C492" t="s">
         <v>972</v>
@@ -22550,10 +22701,10 @@
     </row>
     <row r="493" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="B493" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="C493" t="s">
         <v>972</v>
@@ -22588,16 +22739,16 @@
     </row>
     <row r="494" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B494" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="C494" t="s">
         <v>972</v>
       </c>
       <c r="D494" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="E494" t="s">
         <v>25</v>
@@ -22626,16 +22777,16 @@
     </row>
     <row r="495" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="B495" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="C495" t="s">
         <v>972</v>
       </c>
       <c r="D495" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="E495" t="s">
         <v>25</v>
@@ -22664,10 +22815,10 @@
     </row>
     <row r="496" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="B496" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="C496" t="s">
         <v>972</v>
@@ -22702,10 +22853,10 @@
     </row>
     <row r="497" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B497" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C497" t="s">
         <v>972</v>
@@ -22740,16 +22891,16 @@
     </row>
     <row r="498" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="B498" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="C498" t="s">
         <v>972</v>
       </c>
       <c r="D498" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="E498" t="s">
         <v>25</v>
@@ -22778,16 +22929,16 @@
     </row>
     <row r="499" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="B499" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="C499" t="s">
         <v>972</v>
       </c>
       <c r="D499" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="E499" t="s">
         <v>25</v>
@@ -22816,10 +22967,10 @@
     </row>
     <row r="500" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="B500" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="C500" t="s">
         <v>972</v>
@@ -22854,10 +23005,10 @@
     </row>
     <row r="501" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="B501" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="C501" t="s">
         <v>972</v>
@@ -22892,16 +23043,16 @@
     </row>
     <row r="502" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B502" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="C502" t="s">
         <v>972</v>
       </c>
       <c r="D502" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="E502" t="s">
         <v>25</v>
@@ -22930,16 +23081,16 @@
     </row>
     <row r="503" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="B503" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="C503" t="s">
         <v>972</v>
       </c>
       <c r="D503" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="E503" t="s">
         <v>25</v>
@@ -22968,10 +23119,10 @@
     </row>
     <row r="504" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="B504" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C504" t="s">
         <v>972</v>
@@ -23006,10 +23157,10 @@
     </row>
     <row r="505" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="B505" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="C505" t="s">
         <v>972</v>
@@ -23044,16 +23195,16 @@
     </row>
     <row r="506" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="B506" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C506" t="s">
         <v>972</v>
       </c>
       <c r="D506" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="E506" t="s">
         <v>25</v>
@@ -23082,16 +23233,16 @@
     </row>
     <row r="507" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="B507" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="C507" t="s">
         <v>972</v>
       </c>
       <c r="D507" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="E507" t="s">
         <v>25</v>
@@ -23120,10 +23271,10 @@
     </row>
     <row r="508" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="B508" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C508" t="s">
         <v>972</v>
@@ -23158,10 +23309,10 @@
     </row>
     <row r="509" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B509" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="C509" t="s">
         <v>972</v>
@@ -23196,10 +23347,10 @@
     </row>
     <row r="510" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="B510" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="C510" t="s">
         <v>972</v>
@@ -23234,10 +23385,10 @@
     </row>
     <row r="511" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="B511" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="C511" t="s">
         <v>972</v>
@@ -23267,6 +23418,82 @@
         <v>25</v>
       </c>
       <c r="L511" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="512" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C512" t="s">
+        <v>972</v>
+      </c>
+      <c r="D512" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E512" t="s">
+        <v>25</v>
+      </c>
+      <c r="F512" t="s">
+        <v>25</v>
+      </c>
+      <c r="G512" t="s">
+        <v>25</v>
+      </c>
+      <c r="H512" t="s">
+        <v>19</v>
+      </c>
+      <c r="I512" t="s">
+        <v>25</v>
+      </c>
+      <c r="J512" t="s">
+        <v>25</v>
+      </c>
+      <c r="K512" t="s">
+        <v>25</v>
+      </c>
+      <c r="L512" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="513" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C513" t="s">
+        <v>972</v>
+      </c>
+      <c r="D513" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E513" t="s">
+        <v>25</v>
+      </c>
+      <c r="F513" t="s">
+        <v>25</v>
+      </c>
+      <c r="G513" t="s">
+        <v>25</v>
+      </c>
+      <c r="H513" t="s">
+        <v>19</v>
+      </c>
+      <c r="I513" t="s">
+        <v>25</v>
+      </c>
+      <c r="J513" t="s">
+        <v>25</v>
+      </c>
+      <c r="K513" t="s">
+        <v>25</v>
+      </c>
+      <c r="L513" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23274,7 +23501,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L26 A38:L39 L27 G27:I27 B27:E27 G28:L28 B29:L29 B28:E28 A49:L511 A42:D42 L42 A45:D45 J45:L45 A48:D48 J48:L48 H42 F45 F48 H45 H48" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L4 A38:L38 L27 G27:I27 B27:E27 G28:L28 B29:L29 B28:E28 A51:L513 A44:D44 L44 A47:D47 J47:L47 A50:D50 J50:L50 H44 F47 F50 H47 H50 A41:D41 H41:I41 A6:L26 A5:E5 G5:L5 L41" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE74109B-DE50-44F9-972A-891E81063039}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EECDA075-CA81-418F-86CF-CF69965CC34A}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6154" uniqueCount="1096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6190" uniqueCount="1102">
   <si>
     <t>Codigo</t>
   </si>
@@ -3726,6 +3726,173 @@
   </si>
   <si>
     <t>assets/productos/bebes/andaderacachorro/cachorro3.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/andaderatigre/tigre.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/andaderatigre/tigre2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/andaderatigre/tigre3.webp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Esta </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>andadera para bebé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> combina entretenimiento y funcionalidad para acompañar sus primeros pasos. Cuenta con una bandeja interactiva con diseño de tigre, asiento acolchado, altura ajustable y ruedas multidireccionales que proporcionan un desplazamiento estable y seguro. Su diseño plegable facilita el almacenamiento cuando no está en uso.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Medidas del producto:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Alto: 55 cm aprox.
+Ancho: 60 cm aprox.
+Fondo: 65 cm aprox.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Andadera</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> para bebé con bandeja interactiva, altura ajustable y asiento acolchado, ideal para estimular el desarrollo mientras brinda comodidad y seguridad.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Estructura en metal reforzado.
+Base en plástico resistente (PP).
+Asiento acolchado removible.
+Bandeja interactiva con diseño de tigre.
+Altura ajustable.
+8 ruedas multidireccionales.
+Edad recomendada: 6 a 18 meses.
+Peso máximo soportado: 12 kg.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Favorece el equilibrio y la coordinación.
+Estimula el desarrollo psicomotor.
+Mantiene al bebé entretenido con su bandeja interactiva.
+Proporciona un desplazamiento estable y seguro.
+Diseño plegable para facilitar el almacenamiento.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Utilizar siempre bajo la supervisión de un adulto.
+Ajustar la altura para que los pies apoyen correctamente en el suelo.
+Evitar el uso en escaleras o superficies inclinadas.
+Limpiar con un paño húmedo y guardar en un lugar limpio y seco.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -4127,7 +4294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L513"/>
+  <dimension ref="A1:L515"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5455,14 +5622,14 @@
       <c r="D38" t="s">
         <v>77</v>
       </c>
-      <c r="E38" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" t="s">
-        <v>25</v>
+      <c r="E38">
+        <v>162029</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>1099</v>
       </c>
       <c r="G38" t="s">
-        <v>25</v>
+        <v>1096</v>
       </c>
       <c r="H38" t="s">
         <v>19</v>
@@ -5471,10 +5638,10 @@
         <v>25</v>
       </c>
       <c r="J38" t="s">
-        <v>25</v>
-      </c>
-      <c r="K38" t="s">
-        <v>25</v>
+        <v>1100</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>1101</v>
       </c>
       <c r="L38" t="s">
         <v>25</v>
@@ -5482,10 +5649,10 @@
     </row>
     <row r="39" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -5494,13 +5661,13 @@
         <v>77</v>
       </c>
       <c r="E39">
-        <v>185000</v>
+        <v>162029</v>
       </c>
       <c r="F39" t="s">
-        <v>1092</v>
+        <v>25</v>
       </c>
       <c r="G39" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="H39" t="s">
         <v>19</v>
@@ -5509,10 +5676,10 @@
         <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>1090</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>1091</v>
+        <v>25</v>
+      </c>
+      <c r="K39" t="s">
+        <v>25</v>
       </c>
       <c r="L39" t="s">
         <v>25</v>
@@ -5520,10 +5687,10 @@
     </row>
     <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
@@ -5532,10 +5699,13 @@
         <v>77</v>
       </c>
       <c r="E40">
-        <v>185000</v>
+        <v>162029</v>
+      </c>
+      <c r="F40" t="s">
+        <v>25</v>
       </c>
       <c r="G40" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="H40" t="s">
         <v>19</v>
@@ -5543,7 +5713,12 @@
       <c r="I40" t="s">
         <v>25</v>
       </c>
-      <c r="K40" s="2"/>
+      <c r="J40" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" t="s">
+        <v>25</v>
+      </c>
       <c r="L40" t="s">
         <v>25</v>
       </c>
@@ -5564,8 +5739,11 @@
       <c r="E41">
         <v>185000</v>
       </c>
+      <c r="F41" t="s">
+        <v>1092</v>
+      </c>
       <c r="G41" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="H41" t="s">
         <v>19</v>
@@ -5573,17 +5751,22 @@
       <c r="I41" t="s">
         <v>25</v>
       </c>
-      <c r="K41" s="2"/>
+      <c r="J41" t="s">
+        <v>1090</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>1091</v>
+      </c>
       <c r="L41" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
@@ -5592,36 +5775,28 @@
         <v>77</v>
       </c>
       <c r="E42">
-        <v>119390</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>1078</v>
+        <v>185000</v>
       </c>
       <c r="G42" t="s">
-        <v>1080</v>
+        <v>1094</v>
       </c>
       <c r="H42" t="s">
         <v>19</v>
       </c>
       <c r="I42" t="s">
-        <v>40</v>
-      </c>
-      <c r="J42" t="s">
-        <v>1077</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>1079</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="K42" s="2"/>
       <c r="L42" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
@@ -5630,17 +5805,16 @@
         <v>77</v>
       </c>
       <c r="E43">
-        <v>119390</v>
-      </c>
-      <c r="F43" s="2"/>
+        <v>185000</v>
+      </c>
       <c r="G43" t="s">
-        <v>1081</v>
+        <v>1095</v>
       </c>
       <c r="H43" t="s">
         <v>19</v>
       </c>
       <c r="I43" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" t="s">
@@ -5663,9 +5837,11 @@
       <c r="E44">
         <v>119390</v>
       </c>
-      <c r="F44" s="2"/>
+      <c r="F44" s="2" t="s">
+        <v>1078</v>
+      </c>
       <c r="G44" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="H44" t="s">
         <v>19</v>
@@ -5673,14 +5849,19 @@
       <c r="I44" t="s">
         <v>40</v>
       </c>
-      <c r="K44" s="2"/>
+      <c r="J44" t="s">
+        <v>1077</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>1079</v>
+      </c>
       <c r="L44" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
         <v>88</v>
@@ -5694,31 +5875,24 @@
       <c r="E45">
         <v>119390</v>
       </c>
-      <c r="F45" t="s">
-        <v>25</v>
-      </c>
+      <c r="F45" s="2"/>
       <c r="G45" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H45" t="s">
         <v>19</v>
       </c>
       <c r="I45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J45" t="s">
-        <v>25</v>
-      </c>
-      <c r="K45" t="s">
-        <v>25</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K45" s="2"/>
       <c r="L45" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B46" t="s">
         <v>88</v>
@@ -5732,24 +5906,17 @@
       <c r="E46">
         <v>119390</v>
       </c>
-      <c r="F46" t="s">
-        <v>25</v>
-      </c>
+      <c r="F46" s="2"/>
       <c r="G46" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H46" t="s">
         <v>19</v>
       </c>
       <c r="I46" t="s">
-        <v>43</v>
-      </c>
-      <c r="J46" t="s">
-        <v>25</v>
-      </c>
-      <c r="K46" t="s">
-        <v>25</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K46" s="2"/>
       <c r="L46" t="s">
         <v>25</v>
       </c>
@@ -5774,7 +5941,7 @@
         <v>25</v>
       </c>
       <c r="G47" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="H47" t="s">
         <v>19</v>
@@ -5794,7 +5961,7 @@
     </row>
     <row r="48" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B48" t="s">
         <v>88</v>
@@ -5812,15 +5979,18 @@
         <v>25</v>
       </c>
       <c r="G48" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="H48" t="s">
         <v>19</v>
       </c>
       <c r="I48" t="s">
-        <v>1068</v>
+        <v>43</v>
       </c>
       <c r="J48" t="s">
+        <v>25</v>
+      </c>
+      <c r="K48" t="s">
         <v>25</v>
       </c>
       <c r="L48" t="s">
@@ -5829,7 +5999,7 @@
     </row>
     <row r="49" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B49" t="s">
         <v>88</v>
@@ -5847,13 +6017,13 @@
         <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H49" t="s">
         <v>19</v>
       </c>
       <c r="I49" t="s">
-        <v>1068</v>
+        <v>43</v>
       </c>
       <c r="J49" t="s">
         <v>25</v>
@@ -5885,7 +6055,7 @@
         <v>25</v>
       </c>
       <c r="G50" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="H50" t="s">
         <v>19</v>
@@ -5896,40 +6066,37 @@
       <c r="J50" t="s">
         <v>25</v>
       </c>
-      <c r="K50" t="s">
-        <v>25</v>
-      </c>
       <c r="L50" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>93</v>
-      </c>
-      <c r="E51" t="s">
-        <v>25</v>
+        <v>77</v>
+      </c>
+      <c r="E51">
+        <v>119390</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
       </c>
       <c r="G51" t="s">
-        <v>25</v>
+        <v>1087</v>
       </c>
       <c r="H51" t="s">
         <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>25</v>
+        <v>1068</v>
       </c>
       <c r="J51" t="s">
         <v>25</v>
@@ -5943,31 +6110,31 @@
     </row>
     <row r="52" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>93</v>
-      </c>
-      <c r="E52" t="s">
-        <v>25</v>
+        <v>77</v>
+      </c>
+      <c r="E52">
+        <v>119390</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
       </c>
       <c r="G52" t="s">
-        <v>25</v>
+        <v>1088</v>
       </c>
       <c r="H52" t="s">
         <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>25</v>
+        <v>1068</v>
       </c>
       <c r="J52" t="s">
         <v>25</v>
@@ -5981,10 +6148,10 @@
     </row>
     <row r="53" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -6019,10 +6186,10 @@
     </row>
     <row r="54" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
@@ -6057,10 +6224,10 @@
     </row>
     <row r="55" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -6095,10 +6262,10 @@
     </row>
     <row r="56" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -6133,10 +6300,10 @@
     </row>
     <row r="57" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -6150,7 +6317,7 @@
       <c r="F57" t="s">
         <v>25</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" t="s">
         <v>25</v>
       </c>
       <c r="H57" t="s">
@@ -6171,10 +6338,10 @@
     </row>
     <row r="58" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
@@ -6209,10 +6376,10 @@
     </row>
     <row r="59" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
@@ -6226,7 +6393,7 @@
       <c r="F59" t="s">
         <v>25</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G59" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H59" t="s">
@@ -6247,10 +6414,10 @@
     </row>
     <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B60" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -6285,10 +6452,10 @@
     </row>
     <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B61" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -6323,10 +6490,10 @@
     </row>
     <row r="62" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -6361,7 +6528,7 @@
     </row>
     <row r="63" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B63" t="s">
         <v>113</v>
@@ -6399,10 +6566,10 @@
     </row>
     <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B64" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -6437,10 +6604,10 @@
     </row>
     <row r="65" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B65" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -6475,16 +6642,16 @@
     </row>
     <row r="66" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="E66" t="s">
         <v>25</v>
@@ -6513,16 +6680,16 @@
     </row>
     <row r="67" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B67" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="E67" t="s">
         <v>25</v>
@@ -6551,10 +6718,10 @@
     </row>
     <row r="68" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B68" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
@@ -6589,10 +6756,10 @@
     </row>
     <row r="69" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -6627,10 +6794,10 @@
     </row>
     <row r="70" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B70" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -6665,10 +6832,10 @@
     </row>
     <row r="71" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B71" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -6703,10 +6870,10 @@
     </row>
     <row r="72" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B72" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
@@ -6741,10 +6908,10 @@
     </row>
     <row r="73" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B73" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -6779,16 +6946,16 @@
     </row>
     <row r="74" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B74" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E74" t="s">
         <v>25</v>
@@ -6817,16 +6984,16 @@
     </row>
     <row r="75" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B75" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E75" t="s">
         <v>25</v>
@@ -6855,10 +7022,10 @@
     </row>
     <row r="76" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B76" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -6893,10 +7060,10 @@
     </row>
     <row r="77" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B77" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
@@ -6931,10 +7098,10 @@
     </row>
     <row r="78" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B78" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -6969,16 +7136,16 @@
     </row>
     <row r="79" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B79" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E79" t="s">
         <v>25</v>
@@ -7007,16 +7174,16 @@
     </row>
     <row r="80" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E80" t="s">
         <v>25</v>
@@ -7045,10 +7212,10 @@
     </row>
     <row r="81" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B81" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
@@ -7083,10 +7250,10 @@
     </row>
     <row r="82" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -7121,10 +7288,10 @@
     </row>
     <row r="83" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B83" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -7159,10 +7326,10 @@
     </row>
     <row r="84" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B84" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
@@ -7197,10 +7364,10 @@
     </row>
     <row r="85" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B85" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -7235,16 +7402,16 @@
     </row>
     <row r="86" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B86" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
@@ -7273,16 +7440,16 @@
     </row>
     <row r="87" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B87" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E87" t="s">
         <v>25</v>
@@ -7311,10 +7478,10 @@
     </row>
     <row r="88" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B88" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -7349,10 +7516,10 @@
     </row>
     <row r="89" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -7387,10 +7554,10 @@
     </row>
     <row r="90" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B90" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -7425,10 +7592,10 @@
     </row>
     <row r="91" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B91" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
@@ -7463,10 +7630,10 @@
     </row>
     <row r="92" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
@@ -7501,10 +7668,10 @@
     </row>
     <row r="93" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B93" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
@@ -7539,10 +7706,10 @@
     </row>
     <row r="94" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
@@ -7577,10 +7744,10 @@
     </row>
     <row r="95" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B95" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
@@ -7615,10 +7782,10 @@
     </row>
     <row r="96" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B96" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
@@ -7653,10 +7820,10 @@
     </row>
     <row r="97" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B97" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -7691,10 +7858,10 @@
     </row>
     <row r="98" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B98" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
@@ -7729,10 +7896,10 @@
     </row>
     <row r="99" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B99" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C99" t="s">
         <v>14</v>
@@ -7767,10 +7934,10 @@
     </row>
     <row r="100" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B100" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
@@ -7805,10 +7972,10 @@
     </row>
     <row r="101" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B101" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C101" t="s">
         <v>14</v>
@@ -7843,10 +8010,10 @@
     </row>
     <row r="102" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B102" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
@@ -7881,10 +8048,10 @@
     </row>
     <row r="103" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B103" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
@@ -7919,10 +8086,10 @@
     </row>
     <row r="104" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B104" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C104" t="s">
         <v>14</v>
@@ -7957,10 +8124,10 @@
     </row>
     <row r="105" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B105" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C105" t="s">
         <v>14</v>
@@ -7995,10 +8162,10 @@
     </row>
     <row r="106" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B106" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
@@ -8006,14 +8173,14 @@
       <c r="D106" t="s">
         <v>164</v>
       </c>
-      <c r="E106">
-        <v>106156</v>
+      <c r="E106" t="s">
+        <v>25</v>
       </c>
       <c r="F106" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="G106" t="s">
-        <v>205</v>
+        <v>25</v>
       </c>
       <c r="H106" t="s">
         <v>19</v>
@@ -8022,10 +8189,10 @@
         <v>25</v>
       </c>
       <c r="J106" t="s">
-        <v>206</v>
+        <v>25</v>
       </c>
       <c r="K106" t="s">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="L106" t="s">
         <v>25</v>
@@ -8033,10 +8200,10 @@
     </row>
     <row r="107" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B107" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
@@ -8044,14 +8211,14 @@
       <c r="D107" t="s">
         <v>164</v>
       </c>
-      <c r="E107">
-        <v>106156</v>
+      <c r="E107" t="s">
+        <v>25</v>
       </c>
       <c r="F107" t="s">
         <v>25</v>
       </c>
       <c r="G107" t="s">
-        <v>208</v>
+        <v>25</v>
       </c>
       <c r="H107" t="s">
         <v>19</v>
@@ -8071,25 +8238,25 @@
     </row>
     <row r="108" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B108" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>211</v>
-      </c>
-      <c r="E108" t="s">
-        <v>25</v>
+        <v>164</v>
+      </c>
+      <c r="E108">
+        <v>106156</v>
       </c>
       <c r="F108" t="s">
-        <v>25</v>
+        <v>204</v>
       </c>
       <c r="G108" t="s">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="H108" t="s">
         <v>19</v>
@@ -8098,10 +8265,10 @@
         <v>25</v>
       </c>
       <c r="J108" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="K108" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="L108" t="s">
         <v>25</v>
@@ -8109,25 +8276,25 @@
     </row>
     <row r="109" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B109" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C109" t="s">
         <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>211</v>
-      </c>
-      <c r="E109" t="s">
-        <v>25</v>
+        <v>164</v>
+      </c>
+      <c r="E109">
+        <v>106156</v>
       </c>
       <c r="F109" t="s">
         <v>25</v>
       </c>
       <c r="G109" t="s">
-        <v>25</v>
+        <v>208</v>
       </c>
       <c r="H109" t="s">
         <v>19</v>
@@ -8147,10 +8314,10 @@
     </row>
     <row r="110" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B110" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C110" t="s">
         <v>14</v>
@@ -8185,10 +8352,10 @@
     </row>
     <row r="111" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B111" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C111" t="s">
         <v>14</v>
@@ -8223,10 +8390,10 @@
     </row>
     <row r="112" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B112" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C112" t="s">
         <v>14</v>
@@ -8261,10 +8428,10 @@
     </row>
     <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B113" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C113" t="s">
         <v>14</v>
@@ -8299,10 +8466,10 @@
     </row>
     <row r="114" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B114" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
@@ -8337,10 +8504,10 @@
     </row>
     <row r="115" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B115" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
@@ -8375,10 +8542,10 @@
     </row>
     <row r="116" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B116" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C116" t="s">
         <v>14</v>
@@ -8413,10 +8580,10 @@
     </row>
     <row r="117" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B117" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C117" t="s">
         <v>14</v>
@@ -8451,10 +8618,10 @@
     </row>
     <row r="118" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B118" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C118" t="s">
         <v>14</v>
@@ -8489,10 +8656,10 @@
     </row>
     <row r="119" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B119" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C119" t="s">
         <v>14</v>
@@ -8527,10 +8694,10 @@
     </row>
     <row r="120" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B120" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C120" t="s">
         <v>14</v>
@@ -8565,16 +8732,16 @@
     </row>
     <row r="121" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B121" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C121" t="s">
         <v>14</v>
       </c>
       <c r="D121" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="E121" t="s">
         <v>25</v>
@@ -8603,16 +8770,16 @@
     </row>
     <row r="122" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B122" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="E122" t="s">
         <v>25</v>
@@ -8641,10 +8808,10 @@
     </row>
     <row r="123" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B123" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C123" t="s">
         <v>14</v>
@@ -8679,10 +8846,10 @@
     </row>
     <row r="124" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B124" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C124" t="s">
         <v>14</v>
@@ -8717,10 +8884,10 @@
     </row>
     <row r="125" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B125" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
@@ -8755,16 +8922,16 @@
     </row>
     <row r="126" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B126" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C126" t="s">
         <v>14</v>
       </c>
       <c r="D126" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E126" t="s">
         <v>25</v>
@@ -8793,16 +8960,16 @@
     </row>
     <row r="127" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B127" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C127" t="s">
         <v>14</v>
       </c>
       <c r="D127" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E127" t="s">
         <v>25</v>
@@ -8831,16 +8998,16 @@
     </row>
     <row r="128" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B128" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C128" t="s">
-        <v>252</v>
+        <v>14</v>
       </c>
       <c r="D128" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E128" t="s">
         <v>25</v>
@@ -8869,16 +9036,16 @@
     </row>
     <row r="129" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B129" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C129" t="s">
-        <v>252</v>
+        <v>14</v>
       </c>
       <c r="D129" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E129" t="s">
         <v>25</v>
@@ -8907,10 +9074,10 @@
     </row>
     <row r="130" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B130" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C130" t="s">
         <v>252</v>
@@ -8945,10 +9112,10 @@
     </row>
     <row r="131" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B131" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C131" t="s">
         <v>252</v>
@@ -8983,10 +9150,10 @@
     </row>
     <row r="132" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B132" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C132" t="s">
         <v>252</v>
@@ -9021,10 +9188,10 @@
     </row>
     <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B133" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C133" t="s">
         <v>252</v>
@@ -9059,10 +9226,10 @@
     </row>
     <row r="134" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B134" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C134" t="s">
         <v>252</v>
@@ -9097,10 +9264,10 @@
     </row>
     <row r="135" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B135" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C135" t="s">
         <v>252</v>
@@ -9135,10 +9302,10 @@
     </row>
     <row r="136" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B136" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C136" t="s">
         <v>252</v>
@@ -9173,10 +9340,10 @@
     </row>
     <row r="137" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B137" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C137" t="s">
         <v>252</v>
@@ -9211,10 +9378,10 @@
     </row>
     <row r="138" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B138" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C138" t="s">
         <v>252</v>
@@ -9249,10 +9416,10 @@
     </row>
     <row r="139" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B139" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C139" t="s">
         <v>252</v>
@@ -9287,10 +9454,10 @@
     </row>
     <row r="140" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B140" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C140" t="s">
         <v>252</v>
@@ -9325,10 +9492,10 @@
     </row>
     <row r="141" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B141" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C141" t="s">
         <v>252</v>
@@ -9363,10 +9530,10 @@
     </row>
     <row r="142" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B142" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C142" t="s">
         <v>252</v>
@@ -9401,10 +9568,10 @@
     </row>
     <row r="143" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B143" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C143" t="s">
         <v>252</v>
@@ -9439,10 +9606,10 @@
     </row>
     <row r="144" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B144" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C144" t="s">
         <v>252</v>
@@ -9477,10 +9644,10 @@
     </row>
     <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B145" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C145" t="s">
         <v>252</v>
@@ -9515,10 +9682,10 @@
     </row>
     <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B146" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C146" t="s">
         <v>252</v>
@@ -9553,10 +9720,10 @@
     </row>
     <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B147" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C147" t="s">
         <v>252</v>
@@ -9591,10 +9758,10 @@
     </row>
     <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B148" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C148" t="s">
         <v>252</v>
@@ -9629,10 +9796,10 @@
     </row>
     <row r="149" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B149" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C149" t="s">
         <v>252</v>
@@ -9667,10 +9834,10 @@
     </row>
     <row r="150" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B150" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C150" t="s">
         <v>252</v>
@@ -9705,10 +9872,10 @@
     </row>
     <row r="151" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B151" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C151" t="s">
         <v>252</v>
@@ -9743,10 +9910,10 @@
     </row>
     <row r="152" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B152" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C152" t="s">
         <v>252</v>
@@ -9781,10 +9948,10 @@
     </row>
     <row r="153" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B153" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C153" t="s">
         <v>252</v>
@@ -9819,10 +9986,10 @@
     </row>
     <row r="154" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B154" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C154" t="s">
         <v>252</v>
@@ -9857,10 +10024,10 @@
     </row>
     <row r="155" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B155" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C155" t="s">
         <v>252</v>
@@ -9895,10 +10062,10 @@
     </row>
     <row r="156" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B156" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C156" t="s">
         <v>252</v>
@@ -9933,10 +10100,10 @@
     </row>
     <row r="157" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B157" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C157" t="s">
         <v>252</v>
@@ -9971,10 +10138,10 @@
     </row>
     <row r="158" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B158" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C158" t="s">
         <v>252</v>
@@ -10009,10 +10176,10 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B159" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C159" t="s">
         <v>252</v>
@@ -10047,10 +10214,10 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B160" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C160" t="s">
         <v>252</v>
@@ -10085,10 +10252,10 @@
     </row>
     <row r="161" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B161" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C161" t="s">
         <v>252</v>
@@ -10123,10 +10290,10 @@
     </row>
     <row r="162" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B162" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C162" t="s">
         <v>252</v>
@@ -10161,10 +10328,10 @@
     </row>
     <row r="163" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B163" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C163" t="s">
         <v>252</v>
@@ -10199,10 +10366,10 @@
     </row>
     <row r="164" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B164" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C164" t="s">
         <v>252</v>
@@ -10237,10 +10404,10 @@
     </row>
     <row r="165" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B165" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C165" t="s">
         <v>252</v>
@@ -10275,16 +10442,16 @@
     </row>
     <row r="166" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B166" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C166" t="s">
         <v>252</v>
       </c>
       <c r="D166" t="s">
-        <v>330</v>
+        <v>253</v>
       </c>
       <c r="E166" t="s">
         <v>25</v>
@@ -10313,16 +10480,16 @@
     </row>
     <row r="167" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B167" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C167" t="s">
         <v>252</v>
       </c>
       <c r="D167" t="s">
-        <v>330</v>
+        <v>253</v>
       </c>
       <c r="E167" t="s">
         <v>25</v>
@@ -10351,10 +10518,10 @@
     </row>
     <row r="168" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B168" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C168" t="s">
         <v>252</v>
@@ -10389,10 +10556,10 @@
     </row>
     <row r="169" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B169" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C169" t="s">
         <v>252</v>
@@ -10427,10 +10594,10 @@
     </row>
     <row r="170" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B170" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C170" t="s">
         <v>252</v>
@@ -10465,10 +10632,10 @@
     </row>
     <row r="171" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B171" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C171" t="s">
         <v>252</v>
@@ -10503,10 +10670,10 @@
     </row>
     <row r="172" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B172" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C172" t="s">
         <v>252</v>
@@ -10541,10 +10708,10 @@
     </row>
     <row r="173" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B173" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C173" t="s">
         <v>252</v>
@@ -10579,10 +10746,10 @@
     </row>
     <row r="174" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B174" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C174" t="s">
         <v>252</v>
@@ -10617,10 +10784,10 @@
     </row>
     <row r="175" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B175" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C175" t="s">
         <v>252</v>
@@ -10655,16 +10822,16 @@
     </row>
     <row r="176" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B176" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C176" t="s">
         <v>252</v>
       </c>
       <c r="D176" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="E176" t="s">
         <v>25</v>
@@ -10693,16 +10860,16 @@
     </row>
     <row r="177" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B177" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C177" t="s">
         <v>252</v>
       </c>
       <c r="D177" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="E177" t="s">
         <v>25</v>
@@ -10731,10 +10898,10 @@
     </row>
     <row r="178" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B178" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C178" t="s">
         <v>252</v>
@@ -10769,16 +10936,16 @@
     </row>
     <row r="179" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B179" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C179" t="s">
         <v>252</v>
       </c>
       <c r="D179" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="E179" t="s">
         <v>25</v>
@@ -10807,16 +10974,16 @@
     </row>
     <row r="180" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B180" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C180" t="s">
         <v>252</v>
       </c>
       <c r="D180" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="E180" t="s">
         <v>25</v>
@@ -10845,10 +11012,10 @@
     </row>
     <row r="181" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B181" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C181" t="s">
         <v>252</v>
@@ -10883,10 +11050,10 @@
     </row>
     <row r="182" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B182" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C182" t="s">
         <v>252</v>
@@ -10921,10 +11088,10 @@
     </row>
     <row r="183" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B183" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C183" t="s">
         <v>252</v>
@@ -10959,10 +11126,10 @@
     </row>
     <row r="184" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B184" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C184" t="s">
         <v>252</v>
@@ -10997,10 +11164,10 @@
     </row>
     <row r="185" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B185" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C185" t="s">
         <v>252</v>
@@ -11035,16 +11202,16 @@
     </row>
     <row r="186" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B186" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C186" t="s">
         <v>252</v>
       </c>
       <c r="D186" t="s">
-        <v>238</v>
+        <v>358</v>
       </c>
       <c r="E186" t="s">
         <v>25</v>
@@ -11073,16 +11240,16 @@
     </row>
     <row r="187" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B187" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C187" t="s">
         <v>252</v>
       </c>
       <c r="D187" t="s">
-        <v>238</v>
+        <v>358</v>
       </c>
       <c r="E187" t="s">
         <v>25</v>
@@ -11111,10 +11278,10 @@
     </row>
     <row r="188" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B188" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C188" t="s">
         <v>252</v>
@@ -11149,10 +11316,10 @@
     </row>
     <row r="189" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B189" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C189" t="s">
         <v>252</v>
@@ -11187,10 +11354,10 @@
     </row>
     <row r="190" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B190" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C190" t="s">
         <v>252</v>
@@ -11225,10 +11392,10 @@
     </row>
     <row r="191" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B191" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C191" t="s">
         <v>252</v>
@@ -11263,10 +11430,10 @@
     </row>
     <row r="192" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B192" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C192" t="s">
         <v>252</v>
@@ -11301,10 +11468,10 @@
     </row>
     <row r="193" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B193" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C193" t="s">
         <v>252</v>
@@ -11339,10 +11506,10 @@
     </row>
     <row r="194" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B194" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C194" t="s">
         <v>252</v>
@@ -11377,10 +11544,10 @@
     </row>
     <row r="195" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B195" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C195" t="s">
         <v>252</v>
@@ -11415,10 +11582,10 @@
     </row>
     <row r="196" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B196" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C196" t="s">
         <v>252</v>
@@ -11453,7 +11620,7 @@
     </row>
     <row r="197" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B197" t="s">
         <v>389</v>
@@ -11491,7 +11658,7 @@
     </row>
     <row r="198" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B198" t="s">
         <v>389</v>
@@ -11529,7 +11696,7 @@
     </row>
     <row r="199" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B199" t="s">
         <v>389</v>
@@ -11567,10 +11734,10 @@
     </row>
     <row r="200" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B200" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C200" t="s">
         <v>252</v>
@@ -11605,10 +11772,10 @@
     </row>
     <row r="201" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B201" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C201" t="s">
         <v>252</v>
@@ -11643,10 +11810,10 @@
     </row>
     <row r="202" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B202" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C202" t="s">
         <v>252</v>
@@ -11681,10 +11848,10 @@
     </row>
     <row r="203" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B203" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C203" t="s">
         <v>252</v>
@@ -11719,10 +11886,10 @@
     </row>
     <row r="204" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B204" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C204" t="s">
         <v>252</v>
@@ -11757,10 +11924,10 @@
     </row>
     <row r="205" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B205" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C205" t="s">
         <v>252</v>
@@ -11795,10 +11962,10 @@
     </row>
     <row r="206" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B206" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C206" t="s">
         <v>252</v>
@@ -11833,10 +12000,10 @@
     </row>
     <row r="207" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B207" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C207" t="s">
         <v>252</v>
@@ -11871,10 +12038,10 @@
     </row>
     <row r="208" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B208" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C208" t="s">
         <v>252</v>
@@ -11909,10 +12076,10 @@
     </row>
     <row r="209" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B209" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C209" t="s">
         <v>252</v>
@@ -11947,10 +12114,10 @@
     </row>
     <row r="210" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B210" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C210" t="s">
         <v>252</v>
@@ -11985,10 +12152,10 @@
     </row>
     <row r="211" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B211" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C211" t="s">
         <v>252</v>
@@ -12023,16 +12190,16 @@
     </row>
     <row r="212" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B212" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C212" t="s">
         <v>252</v>
       </c>
       <c r="D212" t="s">
-        <v>420</v>
+        <v>238</v>
       </c>
       <c r="E212" t="s">
         <v>25</v>
@@ -12061,16 +12228,16 @@
     </row>
     <row r="213" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B213" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C213" t="s">
         <v>252</v>
       </c>
       <c r="D213" t="s">
-        <v>420</v>
+        <v>238</v>
       </c>
       <c r="E213" t="s">
         <v>25</v>
@@ -12099,10 +12266,10 @@
     </row>
     <row r="214" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B214" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C214" t="s">
         <v>252</v>
@@ -12137,10 +12304,10 @@
     </row>
     <row r="215" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B215" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C215" t="s">
         <v>252</v>
@@ -12175,10 +12342,10 @@
     </row>
     <row r="216" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B216" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C216" t="s">
         <v>252</v>
@@ -12213,10 +12380,10 @@
     </row>
     <row r="217" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B217" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C217" t="s">
         <v>252</v>
@@ -12251,10 +12418,10 @@
     </row>
     <row r="218" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B218" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C218" t="s">
         <v>252</v>
@@ -12289,10 +12456,10 @@
     </row>
     <row r="219" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B219" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C219" t="s">
         <v>252</v>
@@ -12327,10 +12494,10 @@
     </row>
     <row r="220" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B220" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C220" t="s">
         <v>252</v>
@@ -12365,10 +12532,10 @@
     </row>
     <row r="221" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B221" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C221" t="s">
         <v>252</v>
@@ -12403,10 +12570,10 @@
     </row>
     <row r="222" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B222" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C222" t="s">
         <v>252</v>
@@ -12441,10 +12608,10 @@
     </row>
     <row r="223" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B223" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C223" t="s">
         <v>252</v>
@@ -12479,10 +12646,10 @@
     </row>
     <row r="224" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B224" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C224" t="s">
         <v>252</v>
@@ -12517,10 +12684,10 @@
     </row>
     <row r="225" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B225" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C225" t="s">
         <v>252</v>
@@ -12555,10 +12722,10 @@
     </row>
     <row r="226" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B226" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C226" t="s">
         <v>252</v>
@@ -12593,10 +12760,10 @@
     </row>
     <row r="227" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B227" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C227" t="s">
         <v>252</v>
@@ -12631,10 +12798,10 @@
     </row>
     <row r="228" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B228" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C228" t="s">
         <v>252</v>
@@ -12669,10 +12836,10 @@
     </row>
     <row r="229" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B229" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C229" t="s">
         <v>252</v>
@@ -12707,10 +12874,10 @@
     </row>
     <row r="230" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B230" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C230" t="s">
         <v>252</v>
@@ -12745,10 +12912,10 @@
     </row>
     <row r="231" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B231" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C231" t="s">
         <v>252</v>
@@ -12783,10 +12950,10 @@
     </row>
     <row r="232" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B232" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C232" t="s">
         <v>252</v>
@@ -12821,10 +12988,10 @@
     </row>
     <row r="233" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B233" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C233" t="s">
         <v>252</v>
@@ -12859,10 +13026,10 @@
     </row>
     <row r="234" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B234" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C234" t="s">
         <v>252</v>
@@ -12897,10 +13064,10 @@
     </row>
     <row r="235" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B235" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C235" t="s">
         <v>252</v>
@@ -12935,10 +13102,10 @@
     </row>
     <row r="236" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B236" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C236" t="s">
         <v>252</v>
@@ -12973,10 +13140,10 @@
     </row>
     <row r="237" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B237" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C237" t="s">
         <v>252</v>
@@ -13011,16 +13178,16 @@
     </row>
     <row r="238" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B238" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C238" t="s">
-        <v>473</v>
+        <v>252</v>
       </c>
       <c r="D238" t="s">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="E238" t="s">
         <v>25</v>
@@ -13049,16 +13216,16 @@
     </row>
     <row r="239" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B239" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C239" t="s">
-        <v>473</v>
+        <v>252</v>
       </c>
       <c r="D239" t="s">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="E239" t="s">
         <v>25</v>
@@ -13087,10 +13254,10 @@
     </row>
     <row r="240" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B240" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C240" t="s">
         <v>473</v>
@@ -13125,10 +13292,10 @@
     </row>
     <row r="241" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B241" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C241" t="s">
         <v>473</v>
@@ -13163,10 +13330,10 @@
     </row>
     <row r="242" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B242" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C242" t="s">
         <v>473</v>
@@ -13201,10 +13368,10 @@
     </row>
     <row r="243" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B243" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C243" t="s">
         <v>473</v>
@@ -13239,10 +13406,10 @@
     </row>
     <row r="244" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B244" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C244" t="s">
         <v>473</v>
@@ -13277,10 +13444,10 @@
     </row>
     <row r="245" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B245" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C245" t="s">
         <v>473</v>
@@ -13315,10 +13482,10 @@
     </row>
     <row r="246" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B246" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C246" t="s">
         <v>473</v>
@@ -13353,10 +13520,10 @@
     </row>
     <row r="247" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B247" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C247" t="s">
         <v>473</v>
@@ -13391,10 +13558,10 @@
     </row>
     <row r="248" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B248" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C248" t="s">
         <v>473</v>
@@ -13429,10 +13596,10 @@
     </row>
     <row r="249" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B249" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C249" t="s">
         <v>473</v>
@@ -13467,10 +13634,10 @@
     </row>
     <row r="250" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B250" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C250" t="s">
         <v>473</v>
@@ -13505,10 +13672,10 @@
     </row>
     <row r="251" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B251" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C251" t="s">
         <v>473</v>
@@ -13543,10 +13710,10 @@
     </row>
     <row r="252" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B252" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C252" t="s">
         <v>473</v>
@@ -13581,10 +13748,10 @@
     </row>
     <row r="253" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B253" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C253" t="s">
         <v>473</v>
@@ -13619,10 +13786,10 @@
     </row>
     <row r="254" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B254" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C254" t="s">
         <v>473</v>
@@ -13657,10 +13824,10 @@
     </row>
     <row r="255" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B255" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C255" t="s">
         <v>473</v>
@@ -13695,10 +13862,10 @@
     </row>
     <row r="256" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B256" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C256" t="s">
         <v>473</v>
@@ -13733,10 +13900,10 @@
     </row>
     <row r="257" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B257" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C257" t="s">
         <v>473</v>
@@ -13771,10 +13938,10 @@
     </row>
     <row r="258" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B258" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C258" t="s">
         <v>473</v>
@@ -13809,10 +13976,10 @@
     </row>
     <row r="259" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B259" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C259" t="s">
         <v>473</v>
@@ -13847,10 +14014,10 @@
     </row>
     <row r="260" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B260" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C260" t="s">
         <v>473</v>
@@ -13885,10 +14052,10 @@
     </row>
     <row r="261" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B261" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C261" t="s">
         <v>473</v>
@@ -13923,10 +14090,10 @@
     </row>
     <row r="262" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B262" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C262" t="s">
         <v>473</v>
@@ -13961,10 +14128,10 @@
     </row>
     <row r="263" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B263" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C263" t="s">
         <v>473</v>
@@ -13999,10 +14166,10 @@
     </row>
     <row r="264" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B264" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C264" t="s">
         <v>473</v>
@@ -14037,10 +14204,10 @@
     </row>
     <row r="265" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B265" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C265" t="s">
         <v>473</v>
@@ -14075,10 +14242,10 @@
     </row>
     <row r="266" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B266" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C266" t="s">
         <v>473</v>
@@ -14113,10 +14280,10 @@
     </row>
     <row r="267" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B267" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C267" t="s">
         <v>473</v>
@@ -14151,10 +14318,10 @@
     </row>
     <row r="268" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B268" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C268" t="s">
         <v>473</v>
@@ -14189,10 +14356,10 @@
     </row>
     <row r="269" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B269" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C269" t="s">
         <v>473</v>
@@ -14227,10 +14394,10 @@
     </row>
     <row r="270" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B270" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C270" t="s">
         <v>473</v>
@@ -14265,10 +14432,10 @@
     </row>
     <row r="271" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B271" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C271" t="s">
         <v>473</v>
@@ -14303,10 +14470,10 @@
     </row>
     <row r="272" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B272" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C272" t="s">
         <v>473</v>
@@ -14341,10 +14508,10 @@
     </row>
     <row r="273" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B273" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C273" t="s">
         <v>473</v>
@@ -14379,10 +14546,10 @@
     </row>
     <row r="274" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B274" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C274" t="s">
         <v>473</v>
@@ -14417,10 +14584,10 @@
     </row>
     <row r="275" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B275" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C275" t="s">
         <v>473</v>
@@ -14455,10 +14622,10 @@
     </row>
     <row r="276" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B276" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C276" t="s">
         <v>473</v>
@@ -14493,10 +14660,10 @@
     </row>
     <row r="277" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B277" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C277" t="s">
         <v>473</v>
@@ -14531,10 +14698,10 @@
     </row>
     <row r="278" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B278" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C278" t="s">
         <v>473</v>
@@ -14569,10 +14736,10 @@
     </row>
     <row r="279" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B279" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C279" t="s">
         <v>473</v>
@@ -14607,10 +14774,10 @@
     </row>
     <row r="280" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B280" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C280" t="s">
         <v>473</v>
@@ -14645,10 +14812,10 @@
     </row>
     <row r="281" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B281" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C281" t="s">
         <v>473</v>
@@ -14683,10 +14850,10 @@
     </row>
     <row r="282" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B282" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C282" t="s">
         <v>473</v>
@@ -14721,10 +14888,10 @@
     </row>
     <row r="283" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B283" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C283" t="s">
         <v>473</v>
@@ -14759,10 +14926,10 @@
     </row>
     <row r="284" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B284" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C284" t="s">
         <v>473</v>
@@ -14797,16 +14964,16 @@
     </row>
     <row r="285" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B285" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C285" t="s">
         <v>473</v>
       </c>
       <c r="D285" t="s">
-        <v>569</v>
+        <v>474</v>
       </c>
       <c r="E285" t="s">
         <v>25</v>
@@ -14835,16 +15002,16 @@
     </row>
     <row r="286" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B286" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C286" t="s">
         <v>473</v>
       </c>
       <c r="D286" t="s">
-        <v>569</v>
+        <v>474</v>
       </c>
       <c r="E286" t="s">
         <v>25</v>
@@ -14873,10 +15040,10 @@
     </row>
     <row r="287" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B287" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="C287" t="s">
         <v>473</v>
@@ -14911,10 +15078,10 @@
     </row>
     <row r="288" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B288" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C288" t="s">
         <v>473</v>
@@ -14949,10 +15116,10 @@
     </row>
     <row r="289" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B289" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C289" t="s">
         <v>473</v>
@@ -14987,10 +15154,10 @@
     </row>
     <row r="290" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B290" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C290" t="s">
         <v>473</v>
@@ -15025,10 +15192,10 @@
     </row>
     <row r="291" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B291" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C291" t="s">
         <v>473</v>
@@ -15063,10 +15230,10 @@
     </row>
     <row r="292" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B292" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C292" t="s">
         <v>473</v>
@@ -15101,10 +15268,10 @@
     </row>
     <row r="293" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B293" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C293" t="s">
         <v>473</v>
@@ -15139,10 +15306,10 @@
     </row>
     <row r="294" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B294" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C294" t="s">
         <v>473</v>
@@ -15177,10 +15344,10 @@
     </row>
     <row r="295" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B295" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C295" t="s">
         <v>473</v>
@@ -15215,10 +15382,10 @@
     </row>
     <row r="296" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B296" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C296" t="s">
         <v>473</v>
@@ -15253,10 +15420,10 @@
     </row>
     <row r="297" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B297" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C297" t="s">
         <v>473</v>
@@ -15291,10 +15458,10 @@
     </row>
     <row r="298" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B298" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C298" t="s">
         <v>473</v>
@@ -15329,10 +15496,10 @@
     </row>
     <row r="299" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B299" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C299" t="s">
         <v>473</v>
@@ -15367,10 +15534,10 @@
     </row>
     <row r="300" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B300" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C300" t="s">
         <v>473</v>
@@ -15405,10 +15572,10 @@
     </row>
     <row r="301" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B301" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C301" t="s">
         <v>473</v>
@@ -15443,10 +15610,10 @@
     </row>
     <row r="302" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B302" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C302" t="s">
         <v>473</v>
@@ -15481,10 +15648,10 @@
     </row>
     <row r="303" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B303" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C303" t="s">
         <v>473</v>
@@ -15519,10 +15686,10 @@
     </row>
     <row r="304" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B304" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C304" t="s">
         <v>473</v>
@@ -15557,10 +15724,10 @@
     </row>
     <row r="305" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B305" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C305" t="s">
         <v>473</v>
@@ -15595,10 +15762,10 @@
     </row>
     <row r="306" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B306" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C306" t="s">
         <v>473</v>
@@ -15633,10 +15800,10 @@
     </row>
     <row r="307" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B307" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C307" t="s">
         <v>473</v>
@@ -15671,10 +15838,10 @@
     </row>
     <row r="308" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B308" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C308" t="s">
         <v>473</v>
@@ -15709,10 +15876,10 @@
     </row>
     <row r="309" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B309" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C309" t="s">
         <v>473</v>
@@ -15747,10 +15914,10 @@
     </row>
     <row r="310" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B310" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C310" t="s">
         <v>473</v>
@@ -15785,10 +15952,10 @@
     </row>
     <row r="311" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B311" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C311" t="s">
         <v>473</v>
@@ -15823,10 +15990,10 @@
     </row>
     <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B312" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C312" t="s">
         <v>473</v>
@@ -15861,10 +16028,10 @@
     </row>
     <row r="313" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B313" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C313" t="s">
         <v>473</v>
@@ -15899,10 +16066,10 @@
     </row>
     <row r="314" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B314" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C314" t="s">
         <v>473</v>
@@ -15937,10 +16104,10 @@
     </row>
     <row r="315" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B315" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C315" t="s">
         <v>473</v>
@@ -15975,10 +16142,10 @@
     </row>
     <row r="316" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B316" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C316" t="s">
         <v>473</v>
@@ -16013,10 +16180,10 @@
     </row>
     <row r="317" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B317" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C317" t="s">
         <v>473</v>
@@ -16051,10 +16218,10 @@
     </row>
     <row r="318" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B318" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C318" t="s">
         <v>473</v>
@@ -16089,16 +16256,16 @@
     </row>
     <row r="319" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B319" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C319" t="s">
-        <v>638</v>
+        <v>473</v>
       </c>
       <c r="D319" t="s">
-        <v>25</v>
+        <v>569</v>
       </c>
       <c r="E319" t="s">
         <v>25</v>
@@ -16127,16 +16294,16 @@
     </row>
     <row r="320" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B320" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C320" t="s">
-        <v>638</v>
+        <v>473</v>
       </c>
       <c r="D320" t="s">
-        <v>25</v>
+        <v>569</v>
       </c>
       <c r="E320" t="s">
         <v>25</v>
@@ -16165,10 +16332,10 @@
     </row>
     <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B321" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C321" t="s">
         <v>638</v>
@@ -16203,10 +16370,10 @@
     </row>
     <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B322" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C322" t="s">
         <v>638</v>
@@ -16241,10 +16408,10 @@
     </row>
     <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B323" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C323" t="s">
         <v>638</v>
@@ -16279,10 +16446,10 @@
     </row>
     <row r="324" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B324" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C324" t="s">
         <v>638</v>
@@ -16317,10 +16484,10 @@
     </row>
     <row r="325" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B325" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C325" t="s">
         <v>638</v>
@@ -16355,10 +16522,10 @@
     </row>
     <row r="326" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B326" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C326" t="s">
         <v>638</v>
@@ -16393,16 +16560,16 @@
     </row>
     <row r="327" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B327" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C327" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="D327" t="s">
-        <v>656</v>
+        <v>25</v>
       </c>
       <c r="E327" t="s">
         <v>25</v>
@@ -16431,16 +16598,16 @@
     </row>
     <row r="328" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="B328" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C328" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="D328" t="s">
-        <v>656</v>
+        <v>25</v>
       </c>
       <c r="E328" t="s">
         <v>25</v>
@@ -16469,10 +16636,10 @@
     </row>
     <row r="329" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B329" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C329" t="s">
         <v>655</v>
@@ -16507,10 +16674,10 @@
     </row>
     <row r="330" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B330" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C330" t="s">
         <v>655</v>
@@ -16545,16 +16712,16 @@
     </row>
     <row r="331" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B331" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C331" t="s">
         <v>655</v>
       </c>
       <c r="D331" t="s">
-        <v>149</v>
+        <v>656</v>
       </c>
       <c r="E331" t="s">
         <v>25</v>
@@ -16583,16 +16750,16 @@
     </row>
     <row r="332" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B332" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C332" t="s">
         <v>655</v>
       </c>
       <c r="D332" t="s">
-        <v>149</v>
+        <v>656</v>
       </c>
       <c r="E332" t="s">
         <v>25</v>
@@ -16621,10 +16788,10 @@
     </row>
     <row r="333" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B333" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C333" t="s">
         <v>655</v>
@@ -16659,10 +16826,10 @@
     </row>
     <row r="334" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B334" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C334" t="s">
         <v>655</v>
@@ -16697,16 +16864,16 @@
     </row>
     <row r="335" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B335" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C335" t="s">
         <v>655</v>
       </c>
       <c r="D335" t="s">
-        <v>673</v>
+        <v>149</v>
       </c>
       <c r="E335" t="s">
         <v>25</v>
@@ -16735,16 +16902,16 @@
     </row>
     <row r="336" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="B336" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="C336" t="s">
         <v>655</v>
       </c>
       <c r="D336" t="s">
-        <v>673</v>
+        <v>149</v>
       </c>
       <c r="E336" t="s">
         <v>25</v>
@@ -16773,10 +16940,10 @@
     </row>
     <row r="337" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="B337" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="C337" t="s">
         <v>655</v>
@@ -16811,10 +16978,10 @@
     </row>
     <row r="338" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B338" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C338" t="s">
         <v>655</v>
@@ -16849,10 +17016,10 @@
     </row>
     <row r="339" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B339" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C339" t="s">
         <v>655</v>
@@ -16887,16 +17054,16 @@
     </row>
     <row r="340" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B340" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C340" t="s">
         <v>655</v>
       </c>
       <c r="D340" t="s">
-        <v>138</v>
+        <v>673</v>
       </c>
       <c r="E340" t="s">
         <v>25</v>
@@ -16925,16 +17092,16 @@
     </row>
     <row r="341" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B341" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C341" t="s">
         <v>655</v>
       </c>
       <c r="D341" t="s">
-        <v>138</v>
+        <v>673</v>
       </c>
       <c r="E341" t="s">
         <v>25</v>
@@ -16963,16 +17130,16 @@
     </row>
     <row r="342" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B342" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C342" t="s">
         <v>655</v>
       </c>
       <c r="D342" t="s">
-        <v>688</v>
+        <v>138</v>
       </c>
       <c r="E342" t="s">
         <v>25</v>
@@ -17001,16 +17168,16 @@
     </row>
     <row r="343" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="B343" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="C343" t="s">
         <v>655</v>
       </c>
       <c r="D343" t="s">
-        <v>688</v>
+        <v>138</v>
       </c>
       <c r="E343" t="s">
         <v>25</v>
@@ -17039,10 +17206,10 @@
     </row>
     <row r="344" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B344" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="C344" t="s">
         <v>655</v>
@@ -17077,10 +17244,10 @@
     </row>
     <row r="345" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B345" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C345" t="s">
         <v>655</v>
@@ -17115,16 +17282,16 @@
     </row>
     <row r="346" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B346" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C346" t="s">
-        <v>696</v>
+        <v>655</v>
       </c>
       <c r="D346" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="E346" t="s">
         <v>25</v>
@@ -17153,16 +17320,16 @@
     </row>
     <row r="347" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="B347" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C347" t="s">
-        <v>696</v>
+        <v>655</v>
       </c>
       <c r="D347" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="E347" t="s">
         <v>25</v>
@@ -17191,10 +17358,10 @@
     </row>
     <row r="348" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="B348" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="C348" t="s">
         <v>696</v>
@@ -17229,10 +17396,10 @@
     </row>
     <row r="349" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B349" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C349" t="s">
         <v>696</v>
@@ -17267,10 +17434,10 @@
     </row>
     <row r="350" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B350" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C350" t="s">
         <v>696</v>
@@ -17305,10 +17472,10 @@
     </row>
     <row r="351" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B351" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="C351" t="s">
         <v>696</v>
@@ -17343,16 +17510,16 @@
     </row>
     <row r="352" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B352" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C352" t="s">
         <v>696</v>
       </c>
       <c r="D352" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="E352" t="s">
         <v>25</v>
@@ -17381,16 +17548,16 @@
     </row>
     <row r="353" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="B353" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="C353" t="s">
         <v>696</v>
       </c>
       <c r="D353" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="E353" t="s">
         <v>25</v>
@@ -17419,10 +17586,10 @@
     </row>
     <row r="354" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="B354" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C354" t="s">
         <v>696</v>
@@ -17457,16 +17624,16 @@
     </row>
     <row r="355" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B355" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C355" t="s">
         <v>696</v>
       </c>
       <c r="D355" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="E355" t="s">
         <v>25</v>
@@ -17495,16 +17662,16 @@
     </row>
     <row r="356" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B356" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="C356" t="s">
         <v>696</v>
       </c>
       <c r="D356" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="E356" t="s">
         <v>25</v>
@@ -17533,10 +17700,10 @@
     </row>
     <row r="357" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B357" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="C357" t="s">
         <v>696</v>
@@ -17571,10 +17738,10 @@
     </row>
     <row r="358" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B358" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C358" t="s">
         <v>696</v>
@@ -17609,16 +17776,16 @@
     </row>
     <row r="359" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B359" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C359" t="s">
         <v>696</v>
       </c>
       <c r="D359" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="E359" t="s">
         <v>25</v>
@@ -17647,16 +17814,16 @@
     </row>
     <row r="360" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="B360" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C360" t="s">
         <v>696</v>
       </c>
       <c r="D360" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="E360" t="s">
         <v>25</v>
@@ -17685,10 +17852,10 @@
     </row>
     <row r="361" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B361" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C361" t="s">
         <v>696</v>
@@ -17723,16 +17890,16 @@
     </row>
     <row r="362" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B362" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C362" t="s">
         <v>696</v>
       </c>
       <c r="D362" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E362" t="s">
         <v>25</v>
@@ -17761,16 +17928,16 @@
     </row>
     <row r="363" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="B363" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="C363" t="s">
         <v>696</v>
       </c>
       <c r="D363" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E363" t="s">
         <v>25</v>
@@ -17799,10 +17966,10 @@
     </row>
     <row r="364" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B364" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C364" t="s">
         <v>696</v>
@@ -17837,10 +18004,10 @@
     </row>
     <row r="365" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B365" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C365" t="s">
         <v>696</v>
@@ -17875,10 +18042,10 @@
     </row>
     <row r="366" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B366" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C366" t="s">
         <v>696</v>
@@ -17913,16 +18080,16 @@
     </row>
     <row r="367" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B367" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C367" t="s">
         <v>696</v>
       </c>
       <c r="D367" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="E367" t="s">
         <v>25</v>
@@ -17951,16 +18118,16 @@
     </row>
     <row r="368" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B368" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C368" t="s">
         <v>696</v>
       </c>
       <c r="D368" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="E368" t="s">
         <v>25</v>
@@ -17989,10 +18156,10 @@
     </row>
     <row r="369" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="B369" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="C369" t="s">
         <v>696</v>
@@ -18027,10 +18194,10 @@
     </row>
     <row r="370" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B370" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="C370" t="s">
         <v>696</v>
@@ -18065,10 +18232,10 @@
     </row>
     <row r="371" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B371" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C371" t="s">
         <v>696</v>
@@ -18103,10 +18270,10 @@
     </row>
     <row r="372" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B372" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C372" t="s">
         <v>696</v>
@@ -18141,16 +18308,16 @@
     </row>
     <row r="373" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B373" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="C373" t="s">
         <v>696</v>
       </c>
       <c r="D373" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="E373" t="s">
         <v>25</v>
@@ -18179,16 +18346,16 @@
     </row>
     <row r="374" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B374" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="C374" t="s">
         <v>696</v>
       </c>
       <c r="D374" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="E374" t="s">
         <v>25</v>
@@ -18217,16 +18384,16 @@
     </row>
     <row r="375" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B375" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C375" t="s">
-        <v>761</v>
+        <v>696</v>
       </c>
       <c r="D375" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E375" t="s">
         <v>25</v>
@@ -18255,16 +18422,16 @@
     </row>
     <row r="376" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="B376" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C376" t="s">
-        <v>761</v>
+        <v>696</v>
       </c>
       <c r="D376" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E376" t="s">
         <v>25</v>
@@ -18293,10 +18460,10 @@
     </row>
     <row r="377" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B377" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C377" t="s">
         <v>761</v>
@@ -18331,10 +18498,10 @@
     </row>
     <row r="378" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B378" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C378" t="s">
         <v>761</v>
@@ -18369,10 +18536,10 @@
     </row>
     <row r="379" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B379" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C379" t="s">
         <v>761</v>
@@ -18407,10 +18574,10 @@
     </row>
     <row r="380" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B380" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C380" t="s">
         <v>761</v>
@@ -18445,10 +18612,10 @@
     </row>
     <row r="381" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B381" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C381" t="s">
         <v>761</v>
@@ -18483,10 +18650,10 @@
     </row>
     <row r="382" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B382" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C382" t="s">
         <v>761</v>
@@ -18521,10 +18688,10 @@
     </row>
     <row r="383" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B383" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="C383" t="s">
         <v>761</v>
@@ -18559,10 +18726,10 @@
     </row>
     <row r="384" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B384" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C384" t="s">
         <v>761</v>
@@ -18597,10 +18764,10 @@
     </row>
     <row r="385" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B385" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C385" t="s">
         <v>761</v>
@@ -18635,10 +18802,10 @@
     </row>
     <row r="386" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B386" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C386" t="s">
         <v>761</v>
@@ -18673,10 +18840,10 @@
     </row>
     <row r="387" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B387" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C387" t="s">
         <v>761</v>
@@ -18711,16 +18878,16 @@
     </row>
     <row r="388" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B388" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C388" t="s">
         <v>761</v>
       </c>
       <c r="D388" t="s">
-        <v>789</v>
+        <v>762</v>
       </c>
       <c r="E388" t="s">
         <v>25</v>
@@ -18749,16 +18916,16 @@
     </row>
     <row r="389" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="B389" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="C389" t="s">
         <v>761</v>
       </c>
       <c r="D389" t="s">
-        <v>789</v>
+        <v>762</v>
       </c>
       <c r="E389" t="s">
         <v>25</v>
@@ -18787,10 +18954,10 @@
     </row>
     <row r="390" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="B390" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C390" t="s">
         <v>761</v>
@@ -18825,10 +18992,10 @@
     </row>
     <row r="391" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B391" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="C391" t="s">
         <v>761</v>
@@ -18863,10 +19030,10 @@
     </row>
     <row r="392" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B392" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="C392" t="s">
         <v>761</v>
@@ -18901,16 +19068,16 @@
     </row>
     <row r="393" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B393" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="C393" t="s">
         <v>761</v>
       </c>
       <c r="D393" t="s">
-        <v>211</v>
+        <v>789</v>
       </c>
       <c r="E393" t="s">
         <v>25</v>
@@ -18939,16 +19106,16 @@
     </row>
     <row r="394" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B394" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="C394" t="s">
         <v>761</v>
       </c>
       <c r="D394" t="s">
-        <v>211</v>
+        <v>789</v>
       </c>
       <c r="E394" t="s">
         <v>25</v>
@@ -18977,10 +19144,10 @@
     </row>
     <row r="395" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B395" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="C395" t="s">
         <v>761</v>
@@ -19015,16 +19182,16 @@
     </row>
     <row r="396" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B396" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C396" t="s">
         <v>761</v>
       </c>
       <c r="D396" t="s">
-        <v>806</v>
+        <v>211</v>
       </c>
       <c r="E396" t="s">
         <v>25</v>
@@ -19053,16 +19220,16 @@
     </row>
     <row r="397" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B397" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C397" t="s">
         <v>761</v>
       </c>
       <c r="D397" t="s">
-        <v>806</v>
+        <v>211</v>
       </c>
       <c r="E397" t="s">
         <v>25</v>
@@ -19091,16 +19258,16 @@
     </row>
     <row r="398" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="B398" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="C398" t="s">
         <v>761</v>
       </c>
       <c r="D398" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="E398" t="s">
         <v>25</v>
@@ -19129,16 +19296,16 @@
     </row>
     <row r="399" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="B399" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="C399" t="s">
         <v>761</v>
       </c>
       <c r="D399" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="E399" t="s">
         <v>25</v>
@@ -19167,10 +19334,10 @@
     </row>
     <row r="400" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="B400" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="C400" t="s">
         <v>761</v>
@@ -19205,16 +19372,16 @@
     </row>
     <row r="401" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B401" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C401" t="s">
         <v>761</v>
       </c>
       <c r="D401" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="E401" t="s">
         <v>25</v>
@@ -19243,16 +19410,16 @@
     </row>
     <row r="402" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="B402" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="C402" t="s">
         <v>761</v>
       </c>
       <c r="D402" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="E402" t="s">
         <v>25</v>
@@ -19281,10 +19448,10 @@
     </row>
     <row r="403" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="B403" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C403" t="s">
         <v>761</v>
@@ -19319,10 +19486,10 @@
     </row>
     <row r="404" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B404" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="C404" t="s">
         <v>761</v>
@@ -19357,10 +19524,10 @@
     </row>
     <row r="405" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B405" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="C405" t="s">
         <v>761</v>
@@ -19395,10 +19562,10 @@
     </row>
     <row r="406" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B406" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="C406" t="s">
         <v>761</v>
@@ -19433,10 +19600,10 @@
     </row>
     <row r="407" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B407" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C407" t="s">
         <v>761</v>
@@ -19471,10 +19638,10 @@
     </row>
     <row r="408" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B408" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="C408" t="s">
         <v>761</v>
@@ -19509,10 +19676,10 @@
     </row>
     <row r="409" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B409" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C409" t="s">
         <v>761</v>
@@ -19547,10 +19714,10 @@
     </row>
     <row r="410" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B410" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="C410" t="s">
         <v>761</v>
@@ -19585,10 +19752,10 @@
     </row>
     <row r="411" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B411" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="C411" t="s">
         <v>761</v>
@@ -19623,10 +19790,10 @@
     </row>
     <row r="412" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B412" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="C412" t="s">
         <v>761</v>
@@ -19661,16 +19828,16 @@
     </row>
     <row r="413" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B413" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="C413" t="s">
         <v>761</v>
       </c>
       <c r="D413" t="s">
-        <v>843</v>
+        <v>818</v>
       </c>
       <c r="E413" t="s">
         <v>25</v>
@@ -19699,16 +19866,16 @@
     </row>
     <row r="414" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="B414" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="C414" t="s">
         <v>761</v>
       </c>
       <c r="D414" t="s">
-        <v>843</v>
+        <v>818</v>
       </c>
       <c r="E414" t="s">
         <v>25</v>
@@ -19737,10 +19904,10 @@
     </row>
     <row r="415" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B415" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C415" t="s">
         <v>761</v>
@@ -19775,10 +19942,10 @@
     </row>
     <row r="416" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B416" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C416" t="s">
         <v>761</v>
@@ -19813,10 +19980,10 @@
     </row>
     <row r="417" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B417" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="C417" t="s">
         <v>761</v>
@@ -19851,16 +20018,16 @@
     </row>
     <row r="418" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B418" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C418" t="s">
         <v>761</v>
       </c>
       <c r="D418" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="E418" t="s">
         <v>25</v>
@@ -19889,16 +20056,16 @@
     </row>
     <row r="419" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="B419" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C419" t="s">
         <v>761</v>
       </c>
       <c r="D419" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="E419" t="s">
         <v>25</v>
@@ -19927,16 +20094,16 @@
     </row>
     <row r="420" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="B420" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="C420" t="s">
-        <v>859</v>
+        <v>761</v>
       </c>
       <c r="D420" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="E420" t="s">
         <v>25</v>
@@ -19965,16 +20132,16 @@
     </row>
     <row r="421" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="B421" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="C421" t="s">
-        <v>859</v>
+        <v>761</v>
       </c>
       <c r="D421" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="E421" t="s">
         <v>25</v>
@@ -20003,10 +20170,10 @@
     </row>
     <row r="422" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="B422" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="C422" t="s">
         <v>859</v>
@@ -20041,10 +20208,10 @@
     </row>
     <row r="423" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B423" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="C423" t="s">
         <v>859</v>
@@ -20079,10 +20246,10 @@
     </row>
     <row r="424" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B424" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C424" t="s">
         <v>859</v>
@@ -20117,10 +20284,10 @@
     </row>
     <row r="425" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B425" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="C425" t="s">
         <v>859</v>
@@ -20155,16 +20322,16 @@
     </row>
     <row r="426" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B426" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C426" t="s">
         <v>859</v>
       </c>
       <c r="D426" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="E426" t="s">
         <v>25</v>
@@ -20193,16 +20360,16 @@
     </row>
     <row r="427" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="B427" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="C427" t="s">
         <v>859</v>
       </c>
       <c r="D427" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="E427" t="s">
         <v>25</v>
@@ -20231,10 +20398,10 @@
     </row>
     <row r="428" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="B428" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="C428" t="s">
         <v>859</v>
@@ -20269,10 +20436,10 @@
     </row>
     <row r="429" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="B429" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="C429" t="s">
         <v>859</v>
@@ -20307,10 +20474,10 @@
     </row>
     <row r="430" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="B430" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="C430" t="s">
         <v>859</v>
@@ -20345,16 +20512,16 @@
     </row>
     <row r="431" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B431" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C431" t="s">
         <v>859</v>
       </c>
       <c r="D431" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="E431" t="s">
         <v>25</v>
@@ -20383,16 +20550,16 @@
     </row>
     <row r="432" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="B432" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C432" t="s">
         <v>859</v>
       </c>
       <c r="D432" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="E432" t="s">
         <v>25</v>
@@ -20421,10 +20588,10 @@
     </row>
     <row r="433" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="B433" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="C433" t="s">
         <v>859</v>
@@ -20459,16 +20626,16 @@
     </row>
     <row r="434" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B434" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="C434" t="s">
         <v>859</v>
       </c>
       <c r="D434" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="E434" t="s">
         <v>25</v>
@@ -20497,16 +20664,16 @@
     </row>
     <row r="435" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="B435" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C435" t="s">
         <v>859</v>
       </c>
       <c r="D435" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="E435" t="s">
         <v>25</v>
@@ -20535,16 +20702,16 @@
     </row>
     <row r="436" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B436" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="C436" t="s">
         <v>859</v>
       </c>
       <c r="D436" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="E436" t="s">
         <v>25</v>
@@ -20573,16 +20740,16 @@
     </row>
     <row r="437" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="B437" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="C437" t="s">
         <v>859</v>
       </c>
       <c r="D437" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="E437" t="s">
         <v>25</v>
@@ -20611,10 +20778,10 @@
     </row>
     <row r="438" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="B438" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="C438" t="s">
         <v>859</v>
@@ -20649,10 +20816,10 @@
     </row>
     <row r="439" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B439" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="C439" t="s">
         <v>859</v>
@@ -20687,16 +20854,16 @@
     </row>
     <row r="440" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B440" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="C440" t="s">
         <v>859</v>
       </c>
       <c r="D440" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="E440" t="s">
         <v>25</v>
@@ -20725,16 +20892,16 @@
     </row>
     <row r="441" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="B441" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="C441" t="s">
         <v>859</v>
       </c>
       <c r="D441" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="E441" t="s">
         <v>25</v>
@@ -20763,10 +20930,10 @@
     </row>
     <row r="442" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="B442" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="C442" t="s">
         <v>859</v>
@@ -20801,10 +20968,10 @@
     </row>
     <row r="443" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B443" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="C443" t="s">
         <v>859</v>
@@ -20839,10 +21006,10 @@
     </row>
     <row r="444" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B444" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C444" t="s">
         <v>859</v>
@@ -20877,16 +21044,16 @@
     </row>
     <row r="445" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B445" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="C445" t="s">
-        <v>916</v>
+        <v>859</v>
       </c>
       <c r="D445" t="s">
-        <v>25</v>
+        <v>905</v>
       </c>
       <c r="E445" t="s">
         <v>25</v>
@@ -20915,16 +21082,16 @@
     </row>
     <row r="446" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="B446" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="C446" t="s">
-        <v>916</v>
+        <v>859</v>
       </c>
       <c r="D446" t="s">
-        <v>25</v>
+        <v>905</v>
       </c>
       <c r="E446" t="s">
         <v>25</v>
@@ -20953,10 +21120,10 @@
     </row>
     <row r="447" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="B447" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="C447" t="s">
         <v>916</v>
@@ -20991,10 +21158,10 @@
     </row>
     <row r="448" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B448" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="C448" t="s">
         <v>916</v>
@@ -21029,10 +21196,10 @@
     </row>
     <row r="449" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B449" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="C449" t="s">
         <v>916</v>
@@ -21067,10 +21234,10 @@
     </row>
     <row r="450" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B450" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C450" t="s">
         <v>916</v>
@@ -21105,10 +21272,10 @@
     </row>
     <row r="451" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B451" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="C451" t="s">
         <v>916</v>
@@ -21143,10 +21310,10 @@
     </row>
     <row r="452" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B452" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C452" t="s">
         <v>916</v>
@@ -21181,10 +21348,10 @@
     </row>
     <row r="453" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B453" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C453" t="s">
         <v>916</v>
@@ -21219,10 +21386,10 @@
     </row>
     <row r="454" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B454" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C454" t="s">
         <v>916</v>
@@ -21257,10 +21424,10 @@
     </row>
     <row r="455" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B455" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="C455" t="s">
         <v>916</v>
@@ -21295,10 +21462,10 @@
     </row>
     <row r="456" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B456" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C456" t="s">
         <v>916</v>
@@ -21333,10 +21500,10 @@
     </row>
     <row r="457" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="B457" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C457" t="s">
         <v>916</v>
@@ -21371,10 +21538,10 @@
     </row>
     <row r="458" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B458" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="C458" t="s">
         <v>916</v>
@@ -21409,10 +21576,10 @@
     </row>
     <row r="459" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B459" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C459" t="s">
         <v>916</v>
@@ -21447,16 +21614,16 @@
     </row>
     <row r="460" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B460" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C460" t="s">
-        <v>947</v>
+        <v>916</v>
       </c>
       <c r="D460" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E460" t="s">
         <v>25</v>
@@ -21485,16 +21652,16 @@
     </row>
     <row r="461" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B461" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="C461" t="s">
-        <v>947</v>
+        <v>916</v>
       </c>
       <c r="D461" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E461" t="s">
         <v>25</v>
@@ -21523,10 +21690,10 @@
     </row>
     <row r="462" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="B462" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="C462" t="s">
         <v>947</v>
@@ -21561,10 +21728,10 @@
     </row>
     <row r="463" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B463" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C463" t="s">
         <v>947</v>
@@ -21599,16 +21766,16 @@
     </row>
     <row r="464" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B464" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="C464" t="s">
         <v>947</v>
       </c>
       <c r="D464" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="E464" t="s">
         <v>25</v>
@@ -21637,16 +21804,16 @@
     </row>
     <row r="465" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="B465" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="C465" t="s">
         <v>947</v>
       </c>
       <c r="D465" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="E465" t="s">
         <v>25</v>
@@ -21675,10 +21842,10 @@
     </row>
     <row r="466" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="B466" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="C466" t="s">
         <v>947</v>
@@ -21713,10 +21880,10 @@
     </row>
     <row r="467" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B467" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C467" t="s">
         <v>947</v>
@@ -21751,10 +21918,10 @@
     </row>
     <row r="468" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B468" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="C468" t="s">
         <v>947</v>
@@ -21789,10 +21956,10 @@
     </row>
     <row r="469" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B469" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="C469" t="s">
         <v>947</v>
@@ -21827,10 +21994,10 @@
     </row>
     <row r="470" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="B470" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="C470" t="s">
         <v>947</v>
@@ -21865,16 +22032,16 @@
     </row>
     <row r="471" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="B471" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="C471" t="s">
-        <v>972</v>
+        <v>947</v>
       </c>
       <c r="D471" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="E471" t="s">
         <v>25</v>
@@ -21903,16 +22070,16 @@
     </row>
     <row r="472" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="B472" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="C472" t="s">
-        <v>972</v>
+        <v>947</v>
       </c>
       <c r="D472" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="E472" t="s">
         <v>25</v>
@@ -21941,10 +22108,10 @@
     </row>
     <row r="473" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="B473" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="C473" t="s">
         <v>972</v>
@@ -21979,10 +22146,10 @@
     </row>
     <row r="474" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B474" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="C474" t="s">
         <v>972</v>
@@ -22017,10 +22184,10 @@
     </row>
     <row r="475" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B475" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="C475" t="s">
         <v>972</v>
@@ -22055,10 +22222,10 @@
     </row>
     <row r="476" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B476" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="C476" t="s">
         <v>972</v>
@@ -22093,10 +22260,10 @@
     </row>
     <row r="477" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="B477" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="C477" t="s">
         <v>972</v>
@@ -22131,10 +22298,10 @@
     </row>
     <row r="478" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B478" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="C478" t="s">
         <v>972</v>
@@ -22169,16 +22336,16 @@
     </row>
     <row r="479" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B479" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="C479" t="s">
         <v>972</v>
       </c>
       <c r="D479" t="s">
-        <v>990</v>
+        <v>973</v>
       </c>
       <c r="E479" t="s">
         <v>25</v>
@@ -22207,16 +22374,16 @@
     </row>
     <row r="480" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="B480" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="C480" t="s">
         <v>972</v>
       </c>
       <c r="D480" t="s">
-        <v>990</v>
+        <v>973</v>
       </c>
       <c r="E480" t="s">
         <v>25</v>
@@ -22245,10 +22412,10 @@
     </row>
     <row r="481" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="B481" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="C481" t="s">
         <v>972</v>
@@ -22283,10 +22450,10 @@
     </row>
     <row r="482" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B482" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C482" t="s">
         <v>972</v>
@@ -22321,10 +22488,10 @@
     </row>
     <row r="483" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B483" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C483" t="s">
         <v>972</v>
@@ -22359,16 +22526,16 @@
     </row>
     <row r="484" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B484" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C484" t="s">
         <v>972</v>
       </c>
       <c r="D484" t="s">
-        <v>1001</v>
+        <v>990</v>
       </c>
       <c r="E484" t="s">
         <v>25</v>
@@ -22397,16 +22564,16 @@
     </row>
     <row r="485" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="B485" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="C485" t="s">
         <v>972</v>
       </c>
       <c r="D485" t="s">
-        <v>1001</v>
+        <v>990</v>
       </c>
       <c r="E485" t="s">
         <v>25</v>
@@ -22435,16 +22602,16 @@
     </row>
     <row r="486" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="B486" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="C486" t="s">
         <v>972</v>
       </c>
       <c r="D486" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="E486" t="s">
         <v>25</v>
@@ -22473,16 +22640,16 @@
     </row>
     <row r="487" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="B487" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="C487" t="s">
         <v>972</v>
       </c>
       <c r="D487" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="E487" t="s">
         <v>25</v>
@@ -22511,10 +22678,10 @@
     </row>
     <row r="488" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="B488" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="C488" t="s">
         <v>972</v>
@@ -22549,10 +22716,10 @@
     </row>
     <row r="489" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="B489" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="C489" t="s">
         <v>972</v>
@@ -22587,10 +22754,10 @@
     </row>
     <row r="490" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="B490" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C490" t="s">
         <v>972</v>
@@ -22625,10 +22792,10 @@
     </row>
     <row r="491" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="B491" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="C491" t="s">
         <v>972</v>
@@ -22663,16 +22830,16 @@
     </row>
     <row r="492" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="B492" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C492" t="s">
         <v>972</v>
       </c>
       <c r="D492" t="s">
-        <v>1019</v>
+        <v>1006</v>
       </c>
       <c r="E492" t="s">
         <v>25</v>
@@ -22701,16 +22868,16 @@
     </row>
     <row r="493" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="B493" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="C493" t="s">
         <v>972</v>
       </c>
       <c r="D493" t="s">
-        <v>1019</v>
+        <v>1006</v>
       </c>
       <c r="E493" t="s">
         <v>25</v>
@@ -22739,10 +22906,10 @@
     </row>
     <row r="494" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="B494" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C494" t="s">
         <v>972</v>
@@ -22777,10 +22944,10 @@
     </row>
     <row r="495" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="B495" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="C495" t="s">
         <v>972</v>
@@ -22815,16 +22982,16 @@
     </row>
     <row r="496" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B496" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="C496" t="s">
         <v>972</v>
       </c>
       <c r="D496" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="E496" t="s">
         <v>25</v>
@@ -22853,16 +23020,16 @@
     </row>
     <row r="497" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="B497" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="C497" t="s">
         <v>972</v>
       </c>
       <c r="D497" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="E497" t="s">
         <v>25</v>
@@ -22891,10 +23058,10 @@
     </row>
     <row r="498" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="B498" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="C498" t="s">
         <v>972</v>
@@ -22929,10 +23096,10 @@
     </row>
     <row r="499" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B499" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C499" t="s">
         <v>972</v>
@@ -22967,16 +23134,16 @@
     </row>
     <row r="500" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="B500" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="C500" t="s">
         <v>972</v>
       </c>
       <c r="D500" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="E500" t="s">
         <v>25</v>
@@ -23005,16 +23172,16 @@
     </row>
     <row r="501" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="B501" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="C501" t="s">
         <v>972</v>
       </c>
       <c r="D501" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="E501" t="s">
         <v>25</v>
@@ -23043,10 +23210,10 @@
     </row>
     <row r="502" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="B502" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="C502" t="s">
         <v>972</v>
@@ -23081,10 +23248,10 @@
     </row>
     <row r="503" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="B503" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="C503" t="s">
         <v>972</v>
@@ -23119,16 +23286,16 @@
     </row>
     <row r="504" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B504" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="C504" t="s">
         <v>972</v>
       </c>
       <c r="D504" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="E504" t="s">
         <v>25</v>
@@ -23157,16 +23324,16 @@
     </row>
     <row r="505" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="B505" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="C505" t="s">
         <v>972</v>
       </c>
       <c r="D505" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="E505" t="s">
         <v>25</v>
@@ -23195,10 +23362,10 @@
     </row>
     <row r="506" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="B506" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C506" t="s">
         <v>972</v>
@@ -23233,10 +23400,10 @@
     </row>
     <row r="507" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="B507" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="C507" t="s">
         <v>972</v>
@@ -23271,16 +23438,16 @@
     </row>
     <row r="508" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="B508" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C508" t="s">
         <v>972</v>
       </c>
       <c r="D508" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="E508" t="s">
         <v>25</v>
@@ -23309,16 +23476,16 @@
     </row>
     <row r="509" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="B509" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="C509" t="s">
         <v>972</v>
       </c>
       <c r="D509" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="E509" t="s">
         <v>25</v>
@@ -23347,10 +23514,10 @@
     </row>
     <row r="510" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="B510" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C510" t="s">
         <v>972</v>
@@ -23385,10 +23552,10 @@
     </row>
     <row r="511" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B511" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="C511" t="s">
         <v>972</v>
@@ -23423,10 +23590,10 @@
     </row>
     <row r="512" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="B512" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="C512" t="s">
         <v>972</v>
@@ -23461,10 +23628,10 @@
     </row>
     <row r="513" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="B513" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="C513" t="s">
         <v>972</v>
@@ -23494,6 +23661,82 @@
         <v>25</v>
       </c>
       <c r="L513" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="514" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C514" t="s">
+        <v>972</v>
+      </c>
+      <c r="D514" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E514" t="s">
+        <v>25</v>
+      </c>
+      <c r="F514" t="s">
+        <v>25</v>
+      </c>
+      <c r="G514" t="s">
+        <v>25</v>
+      </c>
+      <c r="H514" t="s">
+        <v>19</v>
+      </c>
+      <c r="I514" t="s">
+        <v>25</v>
+      </c>
+      <c r="J514" t="s">
+        <v>25</v>
+      </c>
+      <c r="K514" t="s">
+        <v>25</v>
+      </c>
+      <c r="L514" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="515" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C515" t="s">
+        <v>972</v>
+      </c>
+      <c r="D515" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E515" t="s">
+        <v>25</v>
+      </c>
+      <c r="F515" t="s">
+        <v>25</v>
+      </c>
+      <c r="G515" t="s">
+        <v>25</v>
+      </c>
+      <c r="H515" t="s">
+        <v>19</v>
+      </c>
+      <c r="I515" t="s">
+        <v>25</v>
+      </c>
+      <c r="J515" t="s">
+        <v>25</v>
+      </c>
+      <c r="K515" t="s">
+        <v>25</v>
+      </c>
+      <c r="L515" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23501,7 +23744,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L4 A38:L38 L27 G27:I27 B27:E27 G28:L28 B29:L29 B28:E28 A51:L513 A44:D44 L44 A47:D47 J47:L47 A50:D50 J50:L50 H44 F47 F50 H47 H50 A41:D41 H41:I41 A6:L26 A5:E5 G5:L5 L41" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L4 A40:D40 L27 G27:I27 B27:E27 G28:L28 B29:L29 B28:E28 A53:L515 A46:D46 L46 A49:D49 J49:L49 A52:D52 J52:L52 H46 F49 F52 H49 H52 A43:D43 H43:I43 A6:L26 A5:E5 G5:L5 L43 F40 H40:L40" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EECDA075-CA81-418F-86CF-CF69965CC34A}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15CF4F82-960B-4EFE-A943-65D4A7A7F8C6}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6190" uniqueCount="1102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6264" uniqueCount="1111">
   <si>
     <t>Codigo</t>
   </si>
@@ -3893,6 +3893,138 @@
 Evitar el uso en escaleras o superficies inclinadas.
 Limpiar con un paño húmedo y guardar en un lugar limpio y seco.</t>
     </r>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Coche Maleta COUNTRY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ofrece un diseño moderno, ligero y resistente para acompañar cada salida con tu bebé. Fabricado con estructura 100% en aluminio, cuenta con sistema de plegado tipo maleta, reclinación ajustable, arnés de seguridad de 5 puntos y capota amplia para brindar mayor comodidad y protección.</t>
+    </r>
+  </si>
+  <si>
+    <t>Coche maleta premium con estructura en aluminio, plegado tipo maleta y reclinación ajustable, ideal para paseos cómodos, seguros y viajes.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Estructura 100% en aluminio.
+Sistema de plegado tipo maleta.
+3 posiciones de reclinación.
+Arnés de seguridad de 5 puntos.
+Llantas de caucho de alta resistencia.
+Capota tipo stroller.
+Descansapiés ajustable.
+Canasta inferior de almacenamiento.
+Mangos ergonómicos con acabado tipo cuero.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Ligero y fácil de transportar.
+Ideal para paseos y viajes.
+Mayor comodidad gracias a su reclinación ajustable.
+Excelente estabilidad con llantas de caucho.
+Diseño premium, resistente y funcional.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Limpiar la estructura y la tela con un paño húmedo.
+Revisar el sistema de plegado antes de cada uso.
+Utilizar siempre el arnés de seguridad correctamente ajustado.
+Guardar en un lugar limpio y seco cuando no esté en uso.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cochecountry/countryblack.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cochecountry/countryblack2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cochecountry/countrypink.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cochecountry/countrypink2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cochecountry/countrybeige.webp</t>
   </si>
 </sst>
 </file>
@@ -4294,7 +4426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L515"/>
+  <dimension ref="A1:L517"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4619,26 +4751,26 @@
       <c r="D9" t="s">
         <v>15</v>
       </c>
-      <c r="E9" t="s">
-        <v>25</v>
+      <c r="E9">
+        <v>635116</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>1103</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>1106</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K9" t="s">
-        <v>25</v>
+        <v>1104</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>1105</v>
       </c>
       <c r="L9" t="s">
         <v>25</v>
@@ -4646,7 +4778,7 @@
     </row>
     <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
         <v>46</v>
@@ -4657,20 +4789,20 @@
       <c r="D10" t="s">
         <v>15</v>
       </c>
-      <c r="E10" t="s">
-        <v>25</v>
+      <c r="E10">
+        <v>635116</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>1107</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J10" t="s">
         <v>25</v>
@@ -4684,7 +4816,7 @@
     </row>
     <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>46</v>
@@ -4695,20 +4827,20 @@
       <c r="D11" t="s">
         <v>15</v>
       </c>
-      <c r="E11" t="s">
-        <v>25</v>
+      <c r="E11">
+        <v>635116</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>1108</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J11" t="s">
         <v>25</v>
@@ -4722,10 +4854,10 @@
     </row>
     <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -4733,20 +4865,20 @@
       <c r="D12" t="s">
         <v>15</v>
       </c>
-      <c r="E12" t="s">
-        <v>25</v>
+      <c r="E12">
+        <v>635116</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>1109</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J12" t="s">
         <v>25</v>
@@ -4760,10 +4892,10 @@
     </row>
     <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -4771,20 +4903,20 @@
       <c r="D13" t="s">
         <v>15</v>
       </c>
-      <c r="E13" t="s">
-        <v>25</v>
+      <c r="E13">
+        <v>635116</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>1110</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
       </c>
       <c r="I13" t="s">
-        <v>25</v>
+        <v>1102</v>
       </c>
       <c r="J13" t="s">
         <v>25</v>
@@ -4798,10 +4930,10 @@
     </row>
     <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -4810,19 +4942,19 @@
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="J14" t="s">
         <v>25</v>
@@ -4836,10 +4968,10 @@
     </row>
     <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -4848,19 +4980,19 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
       </c>
       <c r="I15" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="J15" t="s">
         <v>25</v>
@@ -4874,10 +5006,10 @@
     </row>
     <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -4886,19 +5018,19 @@
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="J16" t="s">
         <v>25</v>
@@ -4912,10 +5044,10 @@
     </row>
     <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -4924,19 +5056,19 @@
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
       </c>
       <c r="I17" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="J17" t="s">
         <v>25</v>
@@ -4950,7 +5082,7 @@
     </row>
     <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
         <v>59</v>
@@ -4988,7 +5120,7 @@
     </row>
     <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
         <v>59</v>
@@ -5026,16 +5158,16 @@
     </row>
     <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
         <v>25</v>
@@ -5064,16 +5196,16 @@
     </row>
     <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
         <v>25</v>
@@ -5102,10 +5234,10 @@
     </row>
     <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -5140,10 +5272,10 @@
     </row>
     <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
@@ -5178,10 +5310,10 @@
     </row>
     <row r="24" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -5216,7 +5348,7 @@
     </row>
     <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
         <v>71</v>
@@ -5254,7 +5386,7 @@
     </row>
     <row r="26" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s">
         <v>71</v>
@@ -5292,37 +5424,37 @@
     </row>
     <row r="27" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27">
-        <v>220230</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>1089</v>
+        <v>65</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>25</v>
       </c>
       <c r="G27" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="H27" t="s">
         <v>19</v>
       </c>
       <c r="I27" t="s">
-        <v>43</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>1067</v>
+        <v>25</v>
+      </c>
+      <c r="J27" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" t="s">
+        <v>25</v>
       </c>
       <c r="L27" t="s">
         <v>25</v>
@@ -5330,28 +5462,31 @@
     </row>
     <row r="28" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28">
-        <v>220230</v>
+        <v>65</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>25</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="H28" t="s">
         <v>19</v>
       </c>
       <c r="I28" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="J28" t="s">
         <v>25</v>
@@ -5379,11 +5514,11 @@
       <c r="E29">
         <v>220230</v>
       </c>
-      <c r="F29" t="s">
-        <v>25</v>
+      <c r="F29" s="2" t="s">
+        <v>1089</v>
       </c>
       <c r="G29" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s">
         <v>19</v>
@@ -5391,11 +5526,11 @@
       <c r="I29" t="s">
         <v>43</v>
       </c>
-      <c r="J29" t="s">
-        <v>25</v>
-      </c>
-      <c r="K29" t="s">
-        <v>25</v>
+      <c r="J29" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>1067</v>
       </c>
       <c r="L29" t="s">
         <v>25</v>
@@ -5403,7 +5538,7 @@
     </row>
     <row r="30" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
         <v>76</v>
@@ -5418,18 +5553,27 @@
         <v>220230</v>
       </c>
       <c r="G30" t="s">
-        <v>1069</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s">
         <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>1068</v>
+        <v>43</v>
+      </c>
+      <c r="J30" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
         <v>76</v>
@@ -5443,19 +5587,31 @@
       <c r="E31">
         <v>220230</v>
       </c>
+      <c r="F31" t="s">
+        <v>25</v>
+      </c>
       <c r="G31" t="s">
-        <v>1070</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s">
         <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>1068</v>
+        <v>43</v>
+      </c>
+      <c r="J31" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
         <v>76</v>
@@ -5470,18 +5626,18 @@
         <v>220230</v>
       </c>
       <c r="G32" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
       </c>
       <c r="I32" t="s">
-        <v>27</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
         <v>76</v>
@@ -5496,13 +5652,13 @@
         <v>220230</v>
       </c>
       <c r="G33" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="H33" t="s">
         <v>19</v>
       </c>
       <c r="I33" t="s">
-        <v>27</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -5522,7 +5678,7 @@
         <v>220230</v>
       </c>
       <c r="G34" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H34" t="s">
         <v>19</v>
@@ -5548,7 +5704,7 @@
         <v>220230</v>
       </c>
       <c r="G35" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="H35" t="s">
         <v>19</v>
@@ -5574,7 +5730,7 @@
         <v>220230</v>
       </c>
       <c r="G36" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="H36" t="s">
         <v>19</v>
@@ -5600,7 +5756,7 @@
         <v>220230</v>
       </c>
       <c r="G37" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="H37" t="s">
         <v>19</v>
@@ -5611,10 +5767,10 @@
     </row>
     <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
         <v>14</v>
@@ -5623,36 +5779,24 @@
         <v>77</v>
       </c>
       <c r="E38">
-        <v>162029</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>1099</v>
+        <v>220230</v>
       </c>
       <c r="G38" t="s">
-        <v>1096</v>
+        <v>1075</v>
       </c>
       <c r="H38" t="s">
         <v>19</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
-      </c>
-      <c r="J38" t="s">
-        <v>1100</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>1101</v>
-      </c>
-      <c r="L38" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -5661,28 +5805,16 @@
         <v>77</v>
       </c>
       <c r="E39">
-        <v>162029</v>
-      </c>
-      <c r="F39" t="s">
-        <v>25</v>
+        <v>220230</v>
       </c>
       <c r="G39" t="s">
-        <v>1097</v>
+        <v>1076</v>
       </c>
       <c r="H39" t="s">
         <v>19</v>
       </c>
       <c r="I39" t="s">
-        <v>25</v>
-      </c>
-      <c r="J39" t="s">
-        <v>25</v>
-      </c>
-      <c r="K39" t="s">
-        <v>25</v>
-      </c>
-      <c r="L39" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -5701,11 +5833,11 @@
       <c r="E40">
         <v>162029</v>
       </c>
-      <c r="F40" t="s">
-        <v>25</v>
+      <c r="F40" s="2" t="s">
+        <v>1099</v>
       </c>
       <c r="G40" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="H40" t="s">
         <v>19</v>
@@ -5714,10 +5846,10 @@
         <v>25</v>
       </c>
       <c r="J40" t="s">
-        <v>25</v>
-      </c>
-      <c r="K40" t="s">
-        <v>25</v>
+        <v>1100</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>1101</v>
       </c>
       <c r="L40" t="s">
         <v>25</v>
@@ -5725,10 +5857,10 @@
     </row>
     <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -5737,13 +5869,13 @@
         <v>77</v>
       </c>
       <c r="E41">
-        <v>185000</v>
+        <v>162029</v>
       </c>
       <c r="F41" t="s">
-        <v>1092</v>
+        <v>25</v>
       </c>
       <c r="G41" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="H41" t="s">
         <v>19</v>
@@ -5752,10 +5884,10 @@
         <v>25</v>
       </c>
       <c r="J41" t="s">
-        <v>1090</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>1091</v>
+        <v>25</v>
+      </c>
+      <c r="K41" t="s">
+        <v>25</v>
       </c>
       <c r="L41" t="s">
         <v>25</v>
@@ -5763,10 +5895,10 @@
     </row>
     <row r="42" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
@@ -5775,10 +5907,13 @@
         <v>77</v>
       </c>
       <c r="E42">
-        <v>185000</v>
+        <v>162029</v>
+      </c>
+      <c r="F42" t="s">
+        <v>25</v>
       </c>
       <c r="G42" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="H42" t="s">
         <v>19</v>
@@ -5786,7 +5921,12 @@
       <c r="I42" t="s">
         <v>25</v>
       </c>
-      <c r="K42" s="2"/>
+      <c r="J42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" t="s">
+        <v>25</v>
+      </c>
       <c r="L42" t="s">
         <v>25</v>
       </c>
@@ -5807,8 +5947,11 @@
       <c r="E43">
         <v>185000</v>
       </c>
+      <c r="F43" t="s">
+        <v>1092</v>
+      </c>
       <c r="G43" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="H43" t="s">
         <v>19</v>
@@ -5816,17 +5959,22 @@
       <c r="I43" t="s">
         <v>25</v>
       </c>
-      <c r="K43" s="2"/>
+      <c r="J43" t="s">
+        <v>1090</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>1091</v>
+      </c>
       <c r="L43" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -5835,36 +5983,28 @@
         <v>77</v>
       </c>
       <c r="E44">
-        <v>119390</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>1078</v>
+        <v>185000</v>
       </c>
       <c r="G44" t="s">
-        <v>1080</v>
+        <v>1094</v>
       </c>
       <c r="H44" t="s">
         <v>19</v>
       </c>
       <c r="I44" t="s">
-        <v>40</v>
-      </c>
-      <c r="J44" t="s">
-        <v>1077</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>1079</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="K44" s="2"/>
       <c r="L44" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -5873,17 +6013,16 @@
         <v>77</v>
       </c>
       <c r="E45">
-        <v>119390</v>
-      </c>
-      <c r="F45" s="2"/>
+        <v>185000</v>
+      </c>
       <c r="G45" t="s">
-        <v>1081</v>
+        <v>1095</v>
       </c>
       <c r="H45" t="s">
         <v>19</v>
       </c>
       <c r="I45" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K45" s="2"/>
       <c r="L45" t="s">
@@ -5906,9 +6045,11 @@
       <c r="E46">
         <v>119390</v>
       </c>
-      <c r="F46" s="2"/>
+      <c r="F46" s="2" t="s">
+        <v>1078</v>
+      </c>
       <c r="G46" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="H46" t="s">
         <v>19</v>
@@ -5916,14 +6057,19 @@
       <c r="I46" t="s">
         <v>40</v>
       </c>
-      <c r="K46" s="2"/>
+      <c r="J46" t="s">
+        <v>1077</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>1079</v>
+      </c>
       <c r="L46" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B47" t="s">
         <v>88</v>
@@ -5937,31 +6083,24 @@
       <c r="E47">
         <v>119390</v>
       </c>
-      <c r="F47" t="s">
-        <v>25</v>
-      </c>
+      <c r="F47" s="2"/>
       <c r="G47" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H47" t="s">
         <v>19</v>
       </c>
       <c r="I47" t="s">
-        <v>43</v>
-      </c>
-      <c r="J47" t="s">
-        <v>25</v>
-      </c>
-      <c r="K47" t="s">
-        <v>25</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K47" s="2"/>
       <c r="L47" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B48" t="s">
         <v>88</v>
@@ -5975,24 +6114,17 @@
       <c r="E48">
         <v>119390</v>
       </c>
-      <c r="F48" t="s">
-        <v>25</v>
-      </c>
+      <c r="F48" s="2"/>
       <c r="G48" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H48" t="s">
         <v>19</v>
       </c>
       <c r="I48" t="s">
-        <v>43</v>
-      </c>
-      <c r="J48" t="s">
-        <v>25</v>
-      </c>
-      <c r="K48" t="s">
-        <v>25</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K48" s="2"/>
       <c r="L48" t="s">
         <v>25</v>
       </c>
@@ -6017,7 +6149,7 @@
         <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="H49" t="s">
         <v>19</v>
@@ -6037,7 +6169,7 @@
     </row>
     <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B50" t="s">
         <v>88</v>
@@ -6055,15 +6187,18 @@
         <v>25</v>
       </c>
       <c r="G50" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="H50" t="s">
         <v>19</v>
       </c>
       <c r="I50" t="s">
-        <v>1068</v>
+        <v>43</v>
       </c>
       <c r="J50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" t="s">
         <v>25</v>
       </c>
       <c r="L50" t="s">
@@ -6072,7 +6207,7 @@
     </row>
     <row r="51" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B51" t="s">
         <v>88</v>
@@ -6090,13 +6225,13 @@
         <v>25</v>
       </c>
       <c r="G51" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H51" t="s">
         <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>1068</v>
+        <v>43</v>
       </c>
       <c r="J51" t="s">
         <v>25</v>
@@ -6128,7 +6263,7 @@
         <v>25</v>
       </c>
       <c r="G52" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="H52" t="s">
         <v>19</v>
@@ -6139,40 +6274,37 @@
       <c r="J52" t="s">
         <v>25</v>
       </c>
-      <c r="K52" t="s">
-        <v>25</v>
-      </c>
       <c r="L52" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>93</v>
-      </c>
-      <c r="E53" t="s">
-        <v>25</v>
+        <v>77</v>
+      </c>
+      <c r="E53">
+        <v>119390</v>
       </c>
       <c r="F53" t="s">
         <v>25</v>
       </c>
       <c r="G53" t="s">
-        <v>25</v>
+        <v>1087</v>
       </c>
       <c r="H53" t="s">
         <v>19</v>
       </c>
       <c r="I53" t="s">
-        <v>25</v>
+        <v>1068</v>
       </c>
       <c r="J53" t="s">
         <v>25</v>
@@ -6186,31 +6318,31 @@
     </row>
     <row r="54" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>93</v>
-      </c>
-      <c r="E54" t="s">
-        <v>25</v>
+        <v>77</v>
+      </c>
+      <c r="E54">
+        <v>119390</v>
       </c>
       <c r="F54" t="s">
         <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>25</v>
+        <v>1088</v>
       </c>
       <c r="H54" t="s">
         <v>19</v>
       </c>
       <c r="I54" t="s">
-        <v>25</v>
+        <v>1068</v>
       </c>
       <c r="J54" t="s">
         <v>25</v>
@@ -6224,10 +6356,10 @@
     </row>
     <row r="55" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B55" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -6262,10 +6394,10 @@
     </row>
     <row r="56" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -6300,10 +6432,10 @@
     </row>
     <row r="57" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B57" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -6338,10 +6470,10 @@
     </row>
     <row r="58" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B58" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
@@ -6376,10 +6508,10 @@
     </row>
     <row r="59" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B59" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
@@ -6393,7 +6525,7 @@
       <c r="F59" t="s">
         <v>25</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" t="s">
         <v>25</v>
       </c>
       <c r="H59" t="s">
@@ -6414,10 +6546,10 @@
     </row>
     <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B60" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -6452,10 +6584,10 @@
     </row>
     <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B61" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -6469,7 +6601,7 @@
       <c r="F61" t="s">
         <v>25</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H61" t="s">
@@ -6490,10 +6622,10 @@
     </row>
     <row r="62" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B62" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -6528,10 +6660,10 @@
     </row>
     <row r="63" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
@@ -6566,10 +6698,10 @@
     </row>
     <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B64" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -6604,7 +6736,7 @@
     </row>
     <row r="65" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B65" t="s">
         <v>113</v>
@@ -6642,10 +6774,10 @@
     </row>
     <row r="66" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B66" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -6680,10 +6812,10 @@
     </row>
     <row r="67" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B67" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
@@ -6718,16 +6850,16 @@
     </row>
     <row r="68" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B68" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="E68" t="s">
         <v>25</v>
@@ -6756,16 +6888,16 @@
     </row>
     <row r="69" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B69" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
@@ -6794,10 +6926,10 @@
     </row>
     <row r="70" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B70" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -6832,10 +6964,10 @@
     </row>
     <row r="71" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B71" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -6870,10 +7002,10 @@
     </row>
     <row r="72" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B72" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
@@ -6908,10 +7040,10 @@
     </row>
     <row r="73" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B73" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -6946,10 +7078,10 @@
     </row>
     <row r="74" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B74" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -6984,10 +7116,10 @@
     </row>
     <row r="75" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B75" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
@@ -7022,16 +7154,16 @@
     </row>
     <row r="76" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B76" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E76" t="s">
         <v>25</v>
@@ -7060,16 +7192,16 @@
     </row>
     <row r="77" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B77" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E77" t="s">
         <v>25</v>
@@ -7098,10 +7230,10 @@
     </row>
     <row r="78" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B78" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -7136,10 +7268,10 @@
     </row>
     <row r="79" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B79" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
@@ -7174,10 +7306,10 @@
     </row>
     <row r="80" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B80" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
@@ -7212,16 +7344,16 @@
     </row>
     <row r="81" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B81" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E81" t="s">
         <v>25</v>
@@ -7250,16 +7382,16 @@
     </row>
     <row r="82" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B82" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E82" t="s">
         <v>25</v>
@@ -7288,10 +7420,10 @@
     </row>
     <row r="83" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B83" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -7326,10 +7458,10 @@
     </row>
     <row r="84" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B84" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
@@ -7364,10 +7496,10 @@
     </row>
     <row r="85" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B85" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -7402,10 +7534,10 @@
     </row>
     <row r="86" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B86" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
@@ -7440,10 +7572,10 @@
     </row>
     <row r="87" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B87" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
@@ -7478,16 +7610,16 @@
     </row>
     <row r="88" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B88" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E88" t="s">
         <v>25</v>
@@ -7516,16 +7648,16 @@
     </row>
     <row r="89" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B89" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E89" t="s">
         <v>25</v>
@@ -7554,10 +7686,10 @@
     </row>
     <row r="90" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B90" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -7592,10 +7724,10 @@
     </row>
     <row r="91" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B91" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
@@ -7630,10 +7762,10 @@
     </row>
     <row r="92" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B92" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
@@ -7668,10 +7800,10 @@
     </row>
     <row r="93" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B93" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
@@ -7706,10 +7838,10 @@
     </row>
     <row r="94" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B94" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
@@ -7744,10 +7876,10 @@
     </row>
     <row r="95" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B95" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
@@ -7782,10 +7914,10 @@
     </row>
     <row r="96" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
@@ -7820,10 +7952,10 @@
     </row>
     <row r="97" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B97" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -7858,10 +7990,10 @@
     </row>
     <row r="98" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B98" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
@@ -7896,10 +8028,10 @@
     </row>
     <row r="99" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B99" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C99" t="s">
         <v>14</v>
@@ -7934,10 +8066,10 @@
     </row>
     <row r="100" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B100" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
@@ -7972,10 +8104,10 @@
     </row>
     <row r="101" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B101" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C101" t="s">
         <v>14</v>
@@ -8010,10 +8142,10 @@
     </row>
     <row r="102" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B102" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
@@ -8048,10 +8180,10 @@
     </row>
     <row r="103" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B103" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
@@ -8086,10 +8218,10 @@
     </row>
     <row r="104" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B104" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C104" t="s">
         <v>14</v>
@@ -8124,10 +8256,10 @@
     </row>
     <row r="105" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B105" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C105" t="s">
         <v>14</v>
@@ -8162,10 +8294,10 @@
     </row>
     <row r="106" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B106" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
@@ -8200,10 +8332,10 @@
     </row>
     <row r="107" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B107" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
@@ -8238,10 +8370,10 @@
     </row>
     <row r="108" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B108" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
@@ -8249,14 +8381,14 @@
       <c r="D108" t="s">
         <v>164</v>
       </c>
-      <c r="E108">
-        <v>106156</v>
+      <c r="E108" t="s">
+        <v>25</v>
       </c>
       <c r="F108" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="G108" t="s">
-        <v>205</v>
+        <v>25</v>
       </c>
       <c r="H108" t="s">
         <v>19</v>
@@ -8265,10 +8397,10 @@
         <v>25</v>
       </c>
       <c r="J108" t="s">
-        <v>206</v>
+        <v>25</v>
       </c>
       <c r="K108" t="s">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="L108" t="s">
         <v>25</v>
@@ -8276,10 +8408,10 @@
     </row>
     <row r="109" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B109" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C109" t="s">
         <v>14</v>
@@ -8287,14 +8419,14 @@
       <c r="D109" t="s">
         <v>164</v>
       </c>
-      <c r="E109">
-        <v>106156</v>
+      <c r="E109" t="s">
+        <v>25</v>
       </c>
       <c r="F109" t="s">
         <v>25</v>
       </c>
       <c r="G109" t="s">
-        <v>208</v>
+        <v>25</v>
       </c>
       <c r="H109" t="s">
         <v>19</v>
@@ -8314,25 +8446,25 @@
     </row>
     <row r="110" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B110" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C110" t="s">
         <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>211</v>
-      </c>
-      <c r="E110" t="s">
-        <v>25</v>
+        <v>164</v>
+      </c>
+      <c r="E110">
+        <v>106156</v>
       </c>
       <c r="F110" t="s">
-        <v>25</v>
+        <v>204</v>
       </c>
       <c r="G110" t="s">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="H110" t="s">
         <v>19</v>
@@ -8341,10 +8473,10 @@
         <v>25</v>
       </c>
       <c r="J110" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="K110" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="L110" t="s">
         <v>25</v>
@@ -8352,25 +8484,25 @@
     </row>
     <row r="111" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B111" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C111" t="s">
         <v>14</v>
       </c>
       <c r="D111" t="s">
-        <v>211</v>
-      </c>
-      <c r="E111" t="s">
-        <v>25</v>
+        <v>164</v>
+      </c>
+      <c r="E111">
+        <v>106156</v>
       </c>
       <c r="F111" t="s">
         <v>25</v>
       </c>
       <c r="G111" t="s">
-        <v>25</v>
+        <v>208</v>
       </c>
       <c r="H111" t="s">
         <v>19</v>
@@ -8390,10 +8522,10 @@
     </row>
     <row r="112" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B112" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C112" t="s">
         <v>14</v>
@@ -8428,10 +8560,10 @@
     </row>
     <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B113" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C113" t="s">
         <v>14</v>
@@ -8466,10 +8598,10 @@
     </row>
     <row r="114" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B114" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
@@ -8504,10 +8636,10 @@
     </row>
     <row r="115" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B115" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
@@ -8542,10 +8674,10 @@
     </row>
     <row r="116" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B116" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C116" t="s">
         <v>14</v>
@@ -8580,10 +8712,10 @@
     </row>
     <row r="117" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B117" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C117" t="s">
         <v>14</v>
@@ -8618,10 +8750,10 @@
     </row>
     <row r="118" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B118" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C118" t="s">
         <v>14</v>
@@ -8656,10 +8788,10 @@
     </row>
     <row r="119" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B119" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C119" t="s">
         <v>14</v>
@@ -8694,10 +8826,10 @@
     </row>
     <row r="120" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B120" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C120" t="s">
         <v>14</v>
@@ -8732,10 +8864,10 @@
     </row>
     <row r="121" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B121" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C121" t="s">
         <v>14</v>
@@ -8770,10 +8902,10 @@
     </row>
     <row r="122" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B122" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
@@ -8808,16 +8940,16 @@
     </row>
     <row r="123" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B123" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C123" t="s">
         <v>14</v>
       </c>
       <c r="D123" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="E123" t="s">
         <v>25</v>
@@ -8846,16 +8978,16 @@
     </row>
     <row r="124" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B124" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C124" t="s">
         <v>14</v>
       </c>
       <c r="D124" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="E124" t="s">
         <v>25</v>
@@ -8884,10 +9016,10 @@
     </row>
     <row r="125" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B125" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
@@ -8922,10 +9054,10 @@
     </row>
     <row r="126" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B126" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C126" t="s">
         <v>14</v>
@@ -8960,10 +9092,10 @@
     </row>
     <row r="127" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B127" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C127" t="s">
         <v>14</v>
@@ -8998,16 +9130,16 @@
     </row>
     <row r="128" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B128" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C128" t="s">
         <v>14</v>
       </c>
       <c r="D128" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E128" t="s">
         <v>25</v>
@@ -9036,16 +9168,16 @@
     </row>
     <row r="129" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B129" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C129" t="s">
         <v>14</v>
       </c>
       <c r="D129" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E129" t="s">
         <v>25</v>
@@ -9074,16 +9206,16 @@
     </row>
     <row r="130" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B130" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C130" t="s">
-        <v>252</v>
+        <v>14</v>
       </c>
       <c r="D130" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E130" t="s">
         <v>25</v>
@@ -9112,16 +9244,16 @@
     </row>
     <row r="131" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B131" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C131" t="s">
-        <v>252</v>
+        <v>14</v>
       </c>
       <c r="D131" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E131" t="s">
         <v>25</v>
@@ -9150,10 +9282,10 @@
     </row>
     <row r="132" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B132" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C132" t="s">
         <v>252</v>
@@ -9188,10 +9320,10 @@
     </row>
     <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B133" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C133" t="s">
         <v>252</v>
@@ -9226,10 +9358,10 @@
     </row>
     <row r="134" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B134" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C134" t="s">
         <v>252</v>
@@ -9264,10 +9396,10 @@
     </row>
     <row r="135" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B135" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C135" t="s">
         <v>252</v>
@@ -9302,10 +9434,10 @@
     </row>
     <row r="136" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B136" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C136" t="s">
         <v>252</v>
@@ -9340,10 +9472,10 @@
     </row>
     <row r="137" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B137" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C137" t="s">
         <v>252</v>
@@ -9378,10 +9510,10 @@
     </row>
     <row r="138" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B138" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C138" t="s">
         <v>252</v>
@@ -9416,10 +9548,10 @@
     </row>
     <row r="139" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B139" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C139" t="s">
         <v>252</v>
@@ -9454,10 +9586,10 @@
     </row>
     <row r="140" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B140" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C140" t="s">
         <v>252</v>
@@ -9492,10 +9624,10 @@
     </row>
     <row r="141" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B141" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C141" t="s">
         <v>252</v>
@@ -9530,10 +9662,10 @@
     </row>
     <row r="142" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B142" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C142" t="s">
         <v>252</v>
@@ -9568,10 +9700,10 @@
     </row>
     <row r="143" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B143" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C143" t="s">
         <v>252</v>
@@ -9606,10 +9738,10 @@
     </row>
     <row r="144" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B144" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C144" t="s">
         <v>252</v>
@@ -9644,10 +9776,10 @@
     </row>
     <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B145" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C145" t="s">
         <v>252</v>
@@ -9682,10 +9814,10 @@
     </row>
     <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B146" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C146" t="s">
         <v>252</v>
@@ -9720,10 +9852,10 @@
     </row>
     <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B147" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C147" t="s">
         <v>252</v>
@@ -9758,10 +9890,10 @@
     </row>
     <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B148" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C148" t="s">
         <v>252</v>
@@ -9796,10 +9928,10 @@
     </row>
     <row r="149" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B149" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C149" t="s">
         <v>252</v>
@@ -9834,10 +9966,10 @@
     </row>
     <row r="150" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B150" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C150" t="s">
         <v>252</v>
@@ -9872,10 +10004,10 @@
     </row>
     <row r="151" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B151" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C151" t="s">
         <v>252</v>
@@ -9910,10 +10042,10 @@
     </row>
     <row r="152" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B152" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C152" t="s">
         <v>252</v>
@@ -9948,10 +10080,10 @@
     </row>
     <row r="153" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B153" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C153" t="s">
         <v>252</v>
@@ -9986,10 +10118,10 @@
     </row>
     <row r="154" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B154" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C154" t="s">
         <v>252</v>
@@ -10024,10 +10156,10 @@
     </row>
     <row r="155" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B155" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C155" t="s">
         <v>252</v>
@@ -10062,10 +10194,10 @@
     </row>
     <row r="156" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B156" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C156" t="s">
         <v>252</v>
@@ -10100,10 +10232,10 @@
     </row>
     <row r="157" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B157" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C157" t="s">
         <v>252</v>
@@ -10138,10 +10270,10 @@
     </row>
     <row r="158" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B158" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C158" t="s">
         <v>252</v>
@@ -10176,10 +10308,10 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B159" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C159" t="s">
         <v>252</v>
@@ -10214,10 +10346,10 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B160" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C160" t="s">
         <v>252</v>
@@ -10252,10 +10384,10 @@
     </row>
     <row r="161" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B161" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C161" t="s">
         <v>252</v>
@@ -10290,10 +10422,10 @@
     </row>
     <row r="162" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B162" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C162" t="s">
         <v>252</v>
@@ -10328,10 +10460,10 @@
     </row>
     <row r="163" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B163" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C163" t="s">
         <v>252</v>
@@ -10366,10 +10498,10 @@
     </row>
     <row r="164" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B164" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C164" t="s">
         <v>252</v>
@@ -10404,10 +10536,10 @@
     </row>
     <row r="165" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B165" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C165" t="s">
         <v>252</v>
@@ -10442,10 +10574,10 @@
     </row>
     <row r="166" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B166" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C166" t="s">
         <v>252</v>
@@ -10480,10 +10612,10 @@
     </row>
     <row r="167" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B167" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C167" t="s">
         <v>252</v>
@@ -10518,16 +10650,16 @@
     </row>
     <row r="168" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B168" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C168" t="s">
         <v>252</v>
       </c>
       <c r="D168" t="s">
-        <v>330</v>
+        <v>253</v>
       </c>
       <c r="E168" t="s">
         <v>25</v>
@@ -10556,16 +10688,16 @@
     </row>
     <row r="169" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B169" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C169" t="s">
         <v>252</v>
       </c>
       <c r="D169" t="s">
-        <v>330</v>
+        <v>253</v>
       </c>
       <c r="E169" t="s">
         <v>25</v>
@@ -10594,10 +10726,10 @@
     </row>
     <row r="170" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B170" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C170" t="s">
         <v>252</v>
@@ -10632,10 +10764,10 @@
     </row>
     <row r="171" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B171" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C171" t="s">
         <v>252</v>
@@ -10670,10 +10802,10 @@
     </row>
     <row r="172" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B172" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C172" t="s">
         <v>252</v>
@@ -10708,10 +10840,10 @@
     </row>
     <row r="173" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B173" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C173" t="s">
         <v>252</v>
@@ -10746,10 +10878,10 @@
     </row>
     <row r="174" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B174" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C174" t="s">
         <v>252</v>
@@ -10784,10 +10916,10 @@
     </row>
     <row r="175" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B175" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C175" t="s">
         <v>252</v>
@@ -10822,10 +10954,10 @@
     </row>
     <row r="176" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B176" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C176" t="s">
         <v>252</v>
@@ -10860,10 +10992,10 @@
     </row>
     <row r="177" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B177" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C177" t="s">
         <v>252</v>
@@ -10898,16 +11030,16 @@
     </row>
     <row r="178" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B178" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C178" t="s">
         <v>252</v>
       </c>
       <c r="D178" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="E178" t="s">
         <v>25</v>
@@ -10936,16 +11068,16 @@
     </row>
     <row r="179" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B179" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C179" t="s">
         <v>252</v>
       </c>
       <c r="D179" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="E179" t="s">
         <v>25</v>
@@ -10974,10 +11106,10 @@
     </row>
     <row r="180" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B180" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C180" t="s">
         <v>252</v>
@@ -11012,16 +11144,16 @@
     </row>
     <row r="181" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B181" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C181" t="s">
         <v>252</v>
       </c>
       <c r="D181" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="E181" t="s">
         <v>25</v>
@@ -11050,16 +11182,16 @@
     </row>
     <row r="182" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B182" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C182" t="s">
         <v>252</v>
       </c>
       <c r="D182" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="E182" t="s">
         <v>25</v>
@@ -11088,10 +11220,10 @@
     </row>
     <row r="183" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B183" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C183" t="s">
         <v>252</v>
@@ -11126,10 +11258,10 @@
     </row>
     <row r="184" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B184" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C184" t="s">
         <v>252</v>
@@ -11164,10 +11296,10 @@
     </row>
     <row r="185" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B185" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C185" t="s">
         <v>252</v>
@@ -11202,10 +11334,10 @@
     </row>
     <row r="186" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B186" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C186" t="s">
         <v>252</v>
@@ -11240,10 +11372,10 @@
     </row>
     <row r="187" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B187" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C187" t="s">
         <v>252</v>
@@ -11278,16 +11410,16 @@
     </row>
     <row r="188" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B188" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C188" t="s">
         <v>252</v>
       </c>
       <c r="D188" t="s">
-        <v>238</v>
+        <v>358</v>
       </c>
       <c r="E188" t="s">
         <v>25</v>
@@ -11316,16 +11448,16 @@
     </row>
     <row r="189" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B189" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C189" t="s">
         <v>252</v>
       </c>
       <c r="D189" t="s">
-        <v>238</v>
+        <v>358</v>
       </c>
       <c r="E189" t="s">
         <v>25</v>
@@ -11354,10 +11486,10 @@
     </row>
     <row r="190" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B190" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C190" t="s">
         <v>252</v>
@@ -11392,10 +11524,10 @@
     </row>
     <row r="191" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B191" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C191" t="s">
         <v>252</v>
@@ -11430,10 +11562,10 @@
     </row>
     <row r="192" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B192" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C192" t="s">
         <v>252</v>
@@ -11468,10 +11600,10 @@
     </row>
     <row r="193" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B193" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C193" t="s">
         <v>252</v>
@@ -11506,10 +11638,10 @@
     </row>
     <row r="194" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B194" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C194" t="s">
         <v>252</v>
@@ -11544,10 +11676,10 @@
     </row>
     <row r="195" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B195" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C195" t="s">
         <v>252</v>
@@ -11582,10 +11714,10 @@
     </row>
     <row r="196" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B196" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C196" t="s">
         <v>252</v>
@@ -11620,10 +11752,10 @@
     </row>
     <row r="197" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B197" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C197" t="s">
         <v>252</v>
@@ -11658,10 +11790,10 @@
     </row>
     <row r="198" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B198" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C198" t="s">
         <v>252</v>
@@ -11696,7 +11828,7 @@
     </row>
     <row r="199" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B199" t="s">
         <v>389</v>
@@ -11734,7 +11866,7 @@
     </row>
     <row r="200" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B200" t="s">
         <v>389</v>
@@ -11772,7 +11904,7 @@
     </row>
     <row r="201" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B201" t="s">
         <v>389</v>
@@ -11810,10 +11942,10 @@
     </row>
     <row r="202" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B202" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C202" t="s">
         <v>252</v>
@@ -11848,10 +11980,10 @@
     </row>
     <row r="203" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B203" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C203" t="s">
         <v>252</v>
@@ -11886,10 +12018,10 @@
     </row>
     <row r="204" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B204" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C204" t="s">
         <v>252</v>
@@ -11924,10 +12056,10 @@
     </row>
     <row r="205" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B205" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C205" t="s">
         <v>252</v>
@@ -11962,10 +12094,10 @@
     </row>
     <row r="206" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B206" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C206" t="s">
         <v>252</v>
@@ -12000,10 +12132,10 @@
     </row>
     <row r="207" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B207" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C207" t="s">
         <v>252</v>
@@ -12038,10 +12170,10 @@
     </row>
     <row r="208" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B208" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C208" t="s">
         <v>252</v>
@@ -12076,10 +12208,10 @@
     </row>
     <row r="209" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B209" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C209" t="s">
         <v>252</v>
@@ -12114,10 +12246,10 @@
     </row>
     <row r="210" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B210" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C210" t="s">
         <v>252</v>
@@ -12152,10 +12284,10 @@
     </row>
     <row r="211" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B211" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C211" t="s">
         <v>252</v>
@@ -12190,10 +12322,10 @@
     </row>
     <row r="212" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B212" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C212" t="s">
         <v>252</v>
@@ -12228,10 +12360,10 @@
     </row>
     <row r="213" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B213" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C213" t="s">
         <v>252</v>
@@ -12266,16 +12398,16 @@
     </row>
     <row r="214" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B214" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C214" t="s">
         <v>252</v>
       </c>
       <c r="D214" t="s">
-        <v>420</v>
+        <v>238</v>
       </c>
       <c r="E214" t="s">
         <v>25</v>
@@ -12304,16 +12436,16 @@
     </row>
     <row r="215" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B215" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C215" t="s">
         <v>252</v>
       </c>
       <c r="D215" t="s">
-        <v>420</v>
+        <v>238</v>
       </c>
       <c r="E215" t="s">
         <v>25</v>
@@ -12342,10 +12474,10 @@
     </row>
     <row r="216" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B216" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C216" t="s">
         <v>252</v>
@@ -12380,10 +12512,10 @@
     </row>
     <row r="217" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B217" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C217" t="s">
         <v>252</v>
@@ -12418,10 +12550,10 @@
     </row>
     <row r="218" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B218" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C218" t="s">
         <v>252</v>
@@ -12456,10 +12588,10 @@
     </row>
     <row r="219" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B219" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C219" t="s">
         <v>252</v>
@@ -12494,10 +12626,10 @@
     </row>
     <row r="220" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B220" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C220" t="s">
         <v>252</v>
@@ -12532,10 +12664,10 @@
     </row>
     <row r="221" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B221" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C221" t="s">
         <v>252</v>
@@ -12570,10 +12702,10 @@
     </row>
     <row r="222" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B222" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C222" t="s">
         <v>252</v>
@@ -12608,10 +12740,10 @@
     </row>
     <row r="223" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B223" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C223" t="s">
         <v>252</v>
@@ -12646,10 +12778,10 @@
     </row>
     <row r="224" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B224" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C224" t="s">
         <v>252</v>
@@ -12684,10 +12816,10 @@
     </row>
     <row r="225" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B225" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C225" t="s">
         <v>252</v>
@@ -12722,10 +12854,10 @@
     </row>
     <row r="226" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B226" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C226" t="s">
         <v>252</v>
@@ -12760,10 +12892,10 @@
     </row>
     <row r="227" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B227" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C227" t="s">
         <v>252</v>
@@ -12798,10 +12930,10 @@
     </row>
     <row r="228" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B228" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C228" t="s">
         <v>252</v>
@@ -12836,10 +12968,10 @@
     </row>
     <row r="229" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B229" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C229" t="s">
         <v>252</v>
@@ -12874,10 +13006,10 @@
     </row>
     <row r="230" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B230" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C230" t="s">
         <v>252</v>
@@ -12912,10 +13044,10 @@
     </row>
     <row r="231" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B231" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C231" t="s">
         <v>252</v>
@@ -12950,10 +13082,10 @@
     </row>
     <row r="232" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B232" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C232" t="s">
         <v>252</v>
@@ -12988,10 +13120,10 @@
     </row>
     <row r="233" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B233" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C233" t="s">
         <v>252</v>
@@ -13026,10 +13158,10 @@
     </row>
     <row r="234" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B234" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C234" t="s">
         <v>252</v>
@@ -13064,10 +13196,10 @@
     </row>
     <row r="235" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B235" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C235" t="s">
         <v>252</v>
@@ -13102,10 +13234,10 @@
     </row>
     <row r="236" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B236" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C236" t="s">
         <v>252</v>
@@ -13140,10 +13272,10 @@
     </row>
     <row r="237" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B237" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C237" t="s">
         <v>252</v>
@@ -13178,10 +13310,10 @@
     </row>
     <row r="238" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B238" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C238" t="s">
         <v>252</v>
@@ -13216,10 +13348,10 @@
     </row>
     <row r="239" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B239" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C239" t="s">
         <v>252</v>
@@ -13254,16 +13386,16 @@
     </row>
     <row r="240" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B240" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C240" t="s">
-        <v>473</v>
+        <v>252</v>
       </c>
       <c r="D240" t="s">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="E240" t="s">
         <v>25</v>
@@ -13292,16 +13424,16 @@
     </row>
     <row r="241" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B241" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C241" t="s">
-        <v>473</v>
+        <v>252</v>
       </c>
       <c r="D241" t="s">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="E241" t="s">
         <v>25</v>
@@ -13330,10 +13462,10 @@
     </row>
     <row r="242" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B242" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C242" t="s">
         <v>473</v>
@@ -13368,10 +13500,10 @@
     </row>
     <row r="243" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B243" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C243" t="s">
         <v>473</v>
@@ -13406,10 +13538,10 @@
     </row>
     <row r="244" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B244" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C244" t="s">
         <v>473</v>
@@ -13444,10 +13576,10 @@
     </row>
     <row r="245" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B245" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C245" t="s">
         <v>473</v>
@@ -13482,10 +13614,10 @@
     </row>
     <row r="246" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B246" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C246" t="s">
         <v>473</v>
@@ -13520,10 +13652,10 @@
     </row>
     <row r="247" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B247" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C247" t="s">
         <v>473</v>
@@ -13558,10 +13690,10 @@
     </row>
     <row r="248" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B248" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C248" t="s">
         <v>473</v>
@@ -13596,10 +13728,10 @@
     </row>
     <row r="249" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B249" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C249" t="s">
         <v>473</v>
@@ -13634,10 +13766,10 @@
     </row>
     <row r="250" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B250" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C250" t="s">
         <v>473</v>
@@ -13672,10 +13804,10 @@
     </row>
     <row r="251" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B251" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C251" t="s">
         <v>473</v>
@@ -13710,10 +13842,10 @@
     </row>
     <row r="252" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B252" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C252" t="s">
         <v>473</v>
@@ -13748,10 +13880,10 @@
     </row>
     <row r="253" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B253" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C253" t="s">
         <v>473</v>
@@ -13786,10 +13918,10 @@
     </row>
     <row r="254" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B254" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C254" t="s">
         <v>473</v>
@@ -13824,10 +13956,10 @@
     </row>
     <row r="255" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B255" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C255" t="s">
         <v>473</v>
@@ -13862,10 +13994,10 @@
     </row>
     <row r="256" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B256" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C256" t="s">
         <v>473</v>
@@ -13900,10 +14032,10 @@
     </row>
     <row r="257" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B257" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C257" t="s">
         <v>473</v>
@@ -13938,10 +14070,10 @@
     </row>
     <row r="258" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B258" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C258" t="s">
         <v>473</v>
@@ -13976,10 +14108,10 @@
     </row>
     <row r="259" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B259" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C259" t="s">
         <v>473</v>
@@ -14014,10 +14146,10 @@
     </row>
     <row r="260" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B260" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C260" t="s">
         <v>473</v>
@@ -14052,10 +14184,10 @@
     </row>
     <row r="261" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B261" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C261" t="s">
         <v>473</v>
@@ -14090,10 +14222,10 @@
     </row>
     <row r="262" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B262" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C262" t="s">
         <v>473</v>
@@ -14128,10 +14260,10 @@
     </row>
     <row r="263" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B263" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C263" t="s">
         <v>473</v>
@@ -14166,10 +14298,10 @@
     </row>
     <row r="264" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B264" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C264" t="s">
         <v>473</v>
@@ -14204,10 +14336,10 @@
     </row>
     <row r="265" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B265" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C265" t="s">
         <v>473</v>
@@ -14242,10 +14374,10 @@
     </row>
     <row r="266" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B266" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C266" t="s">
         <v>473</v>
@@ -14280,10 +14412,10 @@
     </row>
     <row r="267" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B267" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C267" t="s">
         <v>473</v>
@@ -14318,10 +14450,10 @@
     </row>
     <row r="268" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B268" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C268" t="s">
         <v>473</v>
@@ -14356,10 +14488,10 @@
     </row>
     <row r="269" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B269" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C269" t="s">
         <v>473</v>
@@ -14394,10 +14526,10 @@
     </row>
     <row r="270" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B270" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C270" t="s">
         <v>473</v>
@@ -14432,10 +14564,10 @@
     </row>
     <row r="271" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B271" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C271" t="s">
         <v>473</v>
@@ -14470,10 +14602,10 @@
     </row>
     <row r="272" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B272" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C272" t="s">
         <v>473</v>
@@ -14508,10 +14640,10 @@
     </row>
     <row r="273" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B273" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C273" t="s">
         <v>473</v>
@@ -14546,10 +14678,10 @@
     </row>
     <row r="274" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B274" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C274" t="s">
         <v>473</v>
@@ -14584,10 +14716,10 @@
     </row>
     <row r="275" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B275" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C275" t="s">
         <v>473</v>
@@ -14622,10 +14754,10 @@
     </row>
     <row r="276" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B276" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C276" t="s">
         <v>473</v>
@@ -14660,10 +14792,10 @@
     </row>
     <row r="277" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B277" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C277" t="s">
         <v>473</v>
@@ -14698,10 +14830,10 @@
     </row>
     <row r="278" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B278" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C278" t="s">
         <v>473</v>
@@ -14736,10 +14868,10 @@
     </row>
     <row r="279" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B279" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C279" t="s">
         <v>473</v>
@@ -14774,10 +14906,10 @@
     </row>
     <row r="280" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B280" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C280" t="s">
         <v>473</v>
@@ -14812,10 +14944,10 @@
     </row>
     <row r="281" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B281" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C281" t="s">
         <v>473</v>
@@ -14850,10 +14982,10 @@
     </row>
     <row r="282" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B282" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C282" t="s">
         <v>473</v>
@@ -14888,10 +15020,10 @@
     </row>
     <row r="283" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B283" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C283" t="s">
         <v>473</v>
@@ -14926,10 +15058,10 @@
     </row>
     <row r="284" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B284" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C284" t="s">
         <v>473</v>
@@ -14964,10 +15096,10 @@
     </row>
     <row r="285" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B285" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C285" t="s">
         <v>473</v>
@@ -15002,10 +15134,10 @@
     </row>
     <row r="286" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B286" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C286" t="s">
         <v>473</v>
@@ -15040,16 +15172,16 @@
     </row>
     <row r="287" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B287" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C287" t="s">
         <v>473</v>
       </c>
       <c r="D287" t="s">
-        <v>569</v>
+        <v>474</v>
       </c>
       <c r="E287" t="s">
         <v>25</v>
@@ -15078,16 +15210,16 @@
     </row>
     <row r="288" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B288" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C288" t="s">
         <v>473</v>
       </c>
       <c r="D288" t="s">
-        <v>569</v>
+        <v>474</v>
       </c>
       <c r="E288" t="s">
         <v>25</v>
@@ -15116,10 +15248,10 @@
     </row>
     <row r="289" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B289" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="C289" t="s">
         <v>473</v>
@@ -15154,10 +15286,10 @@
     </row>
     <row r="290" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B290" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C290" t="s">
         <v>473</v>
@@ -15192,10 +15324,10 @@
     </row>
     <row r="291" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B291" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C291" t="s">
         <v>473</v>
@@ -15230,10 +15362,10 @@
     </row>
     <row r="292" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B292" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C292" t="s">
         <v>473</v>
@@ -15268,10 +15400,10 @@
     </row>
     <row r="293" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B293" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C293" t="s">
         <v>473</v>
@@ -15306,10 +15438,10 @@
     </row>
     <row r="294" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B294" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C294" t="s">
         <v>473</v>
@@ -15344,10 +15476,10 @@
     </row>
     <row r="295" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B295" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C295" t="s">
         <v>473</v>
@@ -15382,10 +15514,10 @@
     </row>
     <row r="296" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B296" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C296" t="s">
         <v>473</v>
@@ -15420,10 +15552,10 @@
     </row>
     <row r="297" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B297" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C297" t="s">
         <v>473</v>
@@ -15458,10 +15590,10 @@
     </row>
     <row r="298" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B298" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C298" t="s">
         <v>473</v>
@@ -15496,10 +15628,10 @@
     </row>
     <row r="299" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B299" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C299" t="s">
         <v>473</v>
@@ -15534,10 +15666,10 @@
     </row>
     <row r="300" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B300" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C300" t="s">
         <v>473</v>
@@ -15572,10 +15704,10 @@
     </row>
     <row r="301" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B301" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C301" t="s">
         <v>473</v>
@@ -15610,10 +15742,10 @@
     </row>
     <row r="302" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B302" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C302" t="s">
         <v>473</v>
@@ -15648,10 +15780,10 @@
     </row>
     <row r="303" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B303" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C303" t="s">
         <v>473</v>
@@ -15686,10 +15818,10 @@
     </row>
     <row r="304" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B304" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C304" t="s">
         <v>473</v>
@@ -15724,10 +15856,10 @@
     </row>
     <row r="305" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B305" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C305" t="s">
         <v>473</v>
@@ -15762,10 +15894,10 @@
     </row>
     <row r="306" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B306" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C306" t="s">
         <v>473</v>
@@ -15800,10 +15932,10 @@
     </row>
     <row r="307" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B307" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C307" t="s">
         <v>473</v>
@@ -15838,10 +15970,10 @@
     </row>
     <row r="308" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B308" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C308" t="s">
         <v>473</v>
@@ -15876,10 +16008,10 @@
     </row>
     <row r="309" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B309" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C309" t="s">
         <v>473</v>
@@ -15914,10 +16046,10 @@
     </row>
     <row r="310" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B310" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C310" t="s">
         <v>473</v>
@@ -15952,10 +16084,10 @@
     </row>
     <row r="311" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B311" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C311" t="s">
         <v>473</v>
@@ -15990,10 +16122,10 @@
     </row>
     <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B312" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C312" t="s">
         <v>473</v>
@@ -16028,10 +16160,10 @@
     </row>
     <row r="313" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B313" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C313" t="s">
         <v>473</v>
@@ -16066,10 +16198,10 @@
     </row>
     <row r="314" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B314" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C314" t="s">
         <v>473</v>
@@ -16104,10 +16236,10 @@
     </row>
     <row r="315" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B315" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C315" t="s">
         <v>473</v>
@@ -16142,10 +16274,10 @@
     </row>
     <row r="316" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B316" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C316" t="s">
         <v>473</v>
@@ -16180,10 +16312,10 @@
     </row>
     <row r="317" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B317" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C317" t="s">
         <v>473</v>
@@ -16218,10 +16350,10 @@
     </row>
     <row r="318" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B318" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C318" t="s">
         <v>473</v>
@@ -16256,10 +16388,10 @@
     </row>
     <row r="319" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B319" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C319" t="s">
         <v>473</v>
@@ -16294,10 +16426,10 @@
     </row>
     <row r="320" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B320" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C320" t="s">
         <v>473</v>
@@ -16332,16 +16464,16 @@
     </row>
     <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B321" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C321" t="s">
-        <v>638</v>
+        <v>473</v>
       </c>
       <c r="D321" t="s">
-        <v>25</v>
+        <v>569</v>
       </c>
       <c r="E321" t="s">
         <v>25</v>
@@ -16370,16 +16502,16 @@
     </row>
     <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B322" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C322" t="s">
-        <v>638</v>
+        <v>473</v>
       </c>
       <c r="D322" t="s">
-        <v>25</v>
+        <v>569</v>
       </c>
       <c r="E322" t="s">
         <v>25</v>
@@ -16408,10 +16540,10 @@
     </row>
     <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B323" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C323" t="s">
         <v>638</v>
@@ -16446,10 +16578,10 @@
     </row>
     <row r="324" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B324" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C324" t="s">
         <v>638</v>
@@ -16484,10 +16616,10 @@
     </row>
     <row r="325" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B325" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C325" t="s">
         <v>638</v>
@@ -16522,10 +16654,10 @@
     </row>
     <row r="326" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B326" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C326" t="s">
         <v>638</v>
@@ -16560,10 +16692,10 @@
     </row>
     <row r="327" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B327" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C327" t="s">
         <v>638</v>
@@ -16598,10 +16730,10 @@
     </row>
     <row r="328" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B328" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C328" t="s">
         <v>638</v>
@@ -16636,16 +16768,16 @@
     </row>
     <row r="329" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B329" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C329" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="D329" t="s">
-        <v>656</v>
+        <v>25</v>
       </c>
       <c r="E329" t="s">
         <v>25</v>
@@ -16674,16 +16806,16 @@
     </row>
     <row r="330" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="B330" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C330" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="D330" t="s">
-        <v>656</v>
+        <v>25</v>
       </c>
       <c r="E330" t="s">
         <v>25</v>
@@ -16712,10 +16844,10 @@
     </row>
     <row r="331" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B331" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C331" t="s">
         <v>655</v>
@@ -16750,10 +16882,10 @@
     </row>
     <row r="332" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B332" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C332" t="s">
         <v>655</v>
@@ -16788,16 +16920,16 @@
     </row>
     <row r="333" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B333" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C333" t="s">
         <v>655</v>
       </c>
       <c r="D333" t="s">
-        <v>149</v>
+        <v>656</v>
       </c>
       <c r="E333" t="s">
         <v>25</v>
@@ -16826,16 +16958,16 @@
     </row>
     <row r="334" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B334" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C334" t="s">
         <v>655</v>
       </c>
       <c r="D334" t="s">
-        <v>149</v>
+        <v>656</v>
       </c>
       <c r="E334" t="s">
         <v>25</v>
@@ -16864,10 +16996,10 @@
     </row>
     <row r="335" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B335" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C335" t="s">
         <v>655</v>
@@ -16902,10 +17034,10 @@
     </row>
     <row r="336" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B336" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C336" t="s">
         <v>655</v>
@@ -16940,16 +17072,16 @@
     </row>
     <row r="337" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B337" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C337" t="s">
         <v>655</v>
       </c>
       <c r="D337" t="s">
-        <v>673</v>
+        <v>149</v>
       </c>
       <c r="E337" t="s">
         <v>25</v>
@@ -16978,16 +17110,16 @@
     </row>
     <row r="338" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="B338" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="C338" t="s">
         <v>655</v>
       </c>
       <c r="D338" t="s">
-        <v>673</v>
+        <v>149</v>
       </c>
       <c r="E338" t="s">
         <v>25</v>
@@ -17016,10 +17148,10 @@
     </row>
     <row r="339" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="B339" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="C339" t="s">
         <v>655</v>
@@ -17054,10 +17186,10 @@
     </row>
     <row r="340" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B340" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C340" t="s">
         <v>655</v>
@@ -17092,10 +17224,10 @@
     </row>
     <row r="341" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B341" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C341" t="s">
         <v>655</v>
@@ -17130,16 +17262,16 @@
     </row>
     <row r="342" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B342" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C342" t="s">
         <v>655</v>
       </c>
       <c r="D342" t="s">
-        <v>138</v>
+        <v>673</v>
       </c>
       <c r="E342" t="s">
         <v>25</v>
@@ -17168,16 +17300,16 @@
     </row>
     <row r="343" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B343" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C343" t="s">
         <v>655</v>
       </c>
       <c r="D343" t="s">
-        <v>138</v>
+        <v>673</v>
       </c>
       <c r="E343" t="s">
         <v>25</v>
@@ -17206,16 +17338,16 @@
     </row>
     <row r="344" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B344" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C344" t="s">
         <v>655</v>
       </c>
       <c r="D344" t="s">
-        <v>688</v>
+        <v>138</v>
       </c>
       <c r="E344" t="s">
         <v>25</v>
@@ -17244,16 +17376,16 @@
     </row>
     <row r="345" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="B345" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="C345" t="s">
         <v>655</v>
       </c>
       <c r="D345" t="s">
-        <v>688</v>
+        <v>138</v>
       </c>
       <c r="E345" t="s">
         <v>25</v>
@@ -17282,10 +17414,10 @@
     </row>
     <row r="346" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B346" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="C346" t="s">
         <v>655</v>
@@ -17320,10 +17452,10 @@
     </row>
     <row r="347" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B347" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C347" t="s">
         <v>655</v>
@@ -17358,16 +17490,16 @@
     </row>
     <row r="348" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B348" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C348" t="s">
-        <v>696</v>
+        <v>655</v>
       </c>
       <c r="D348" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="E348" t="s">
         <v>25</v>
@@ -17396,16 +17528,16 @@
     </row>
     <row r="349" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="B349" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C349" t="s">
-        <v>696</v>
+        <v>655</v>
       </c>
       <c r="D349" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="E349" t="s">
         <v>25</v>
@@ -17434,10 +17566,10 @@
     </row>
     <row r="350" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="B350" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="C350" t="s">
         <v>696</v>
@@ -17472,10 +17604,10 @@
     </row>
     <row r="351" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B351" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C351" t="s">
         <v>696</v>
@@ -17510,10 +17642,10 @@
     </row>
     <row r="352" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B352" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C352" t="s">
         <v>696</v>
@@ -17548,10 +17680,10 @@
     </row>
     <row r="353" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B353" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="C353" t="s">
         <v>696</v>
@@ -17586,16 +17718,16 @@
     </row>
     <row r="354" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B354" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C354" t="s">
         <v>696</v>
       </c>
       <c r="D354" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="E354" t="s">
         <v>25</v>
@@ -17624,16 +17756,16 @@
     </row>
     <row r="355" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="B355" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="C355" t="s">
         <v>696</v>
       </c>
       <c r="D355" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="E355" t="s">
         <v>25</v>
@@ -17662,10 +17794,10 @@
     </row>
     <row r="356" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="B356" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C356" t="s">
         <v>696</v>
@@ -17700,16 +17832,16 @@
     </row>
     <row r="357" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B357" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C357" t="s">
         <v>696</v>
       </c>
       <c r="D357" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="E357" t="s">
         <v>25</v>
@@ -17738,16 +17870,16 @@
     </row>
     <row r="358" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B358" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="C358" t="s">
         <v>696</v>
       </c>
       <c r="D358" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="E358" t="s">
         <v>25</v>
@@ -17776,10 +17908,10 @@
     </row>
     <row r="359" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B359" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="C359" t="s">
         <v>696</v>
@@ -17814,10 +17946,10 @@
     </row>
     <row r="360" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B360" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C360" t="s">
         <v>696</v>
@@ -17852,16 +17984,16 @@
     </row>
     <row r="361" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B361" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C361" t="s">
         <v>696</v>
       </c>
       <c r="D361" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="E361" t="s">
         <v>25</v>
@@ -17890,16 +18022,16 @@
     </row>
     <row r="362" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="B362" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C362" t="s">
         <v>696</v>
       </c>
       <c r="D362" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="E362" t="s">
         <v>25</v>
@@ -17928,10 +18060,10 @@
     </row>
     <row r="363" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B363" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C363" t="s">
         <v>696</v>
@@ -17966,16 +18098,16 @@
     </row>
     <row r="364" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B364" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C364" t="s">
         <v>696</v>
       </c>
       <c r="D364" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E364" t="s">
         <v>25</v>
@@ -18004,16 +18136,16 @@
     </row>
     <row r="365" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="B365" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="C365" t="s">
         <v>696</v>
       </c>
       <c r="D365" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E365" t="s">
         <v>25</v>
@@ -18042,10 +18174,10 @@
     </row>
     <row r="366" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B366" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C366" t="s">
         <v>696</v>
@@ -18080,10 +18212,10 @@
     </row>
     <row r="367" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B367" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C367" t="s">
         <v>696</v>
@@ -18118,10 +18250,10 @@
     </row>
     <row r="368" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B368" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C368" t="s">
         <v>696</v>
@@ -18156,16 +18288,16 @@
     </row>
     <row r="369" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B369" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C369" t="s">
         <v>696</v>
       </c>
       <c r="D369" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="E369" t="s">
         <v>25</v>
@@ -18194,16 +18326,16 @@
     </row>
     <row r="370" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B370" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C370" t="s">
         <v>696</v>
       </c>
       <c r="D370" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="E370" t="s">
         <v>25</v>
@@ -18232,10 +18364,10 @@
     </row>
     <row r="371" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="B371" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="C371" t="s">
         <v>696</v>
@@ -18270,10 +18402,10 @@
     </row>
     <row r="372" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B372" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="C372" t="s">
         <v>696</v>
@@ -18308,10 +18440,10 @@
     </row>
     <row r="373" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B373" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C373" t="s">
         <v>696</v>
@@ -18346,10 +18478,10 @@
     </row>
     <row r="374" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B374" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C374" t="s">
         <v>696</v>
@@ -18384,16 +18516,16 @@
     </row>
     <row r="375" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B375" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="C375" t="s">
         <v>696</v>
       </c>
       <c r="D375" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="E375" t="s">
         <v>25</v>
@@ -18422,16 +18554,16 @@
     </row>
     <row r="376" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B376" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="C376" t="s">
         <v>696</v>
       </c>
       <c r="D376" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="E376" t="s">
         <v>25</v>
@@ -18460,16 +18592,16 @@
     </row>
     <row r="377" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B377" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C377" t="s">
-        <v>761</v>
+        <v>696</v>
       </c>
       <c r="D377" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E377" t="s">
         <v>25</v>
@@ -18498,16 +18630,16 @@
     </row>
     <row r="378" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="B378" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C378" t="s">
-        <v>761</v>
+        <v>696</v>
       </c>
       <c r="D378" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E378" t="s">
         <v>25</v>
@@ -18536,10 +18668,10 @@
     </row>
     <row r="379" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B379" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C379" t="s">
         <v>761</v>
@@ -18574,10 +18706,10 @@
     </row>
     <row r="380" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B380" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C380" t="s">
         <v>761</v>
@@ -18612,10 +18744,10 @@
     </row>
     <row r="381" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B381" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C381" t="s">
         <v>761</v>
@@ -18650,10 +18782,10 @@
     </row>
     <row r="382" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B382" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C382" t="s">
         <v>761</v>
@@ -18688,10 +18820,10 @@
     </row>
     <row r="383" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B383" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C383" t="s">
         <v>761</v>
@@ -18726,10 +18858,10 @@
     </row>
     <row r="384" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B384" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C384" t="s">
         <v>761</v>
@@ -18764,10 +18896,10 @@
     </row>
     <row r="385" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B385" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="C385" t="s">
         <v>761</v>
@@ -18802,10 +18934,10 @@
     </row>
     <row r="386" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B386" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C386" t="s">
         <v>761</v>
@@ -18840,10 +18972,10 @@
     </row>
     <row r="387" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B387" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C387" t="s">
         <v>761</v>
@@ -18878,10 +19010,10 @@
     </row>
     <row r="388" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B388" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C388" t="s">
         <v>761</v>
@@ -18916,10 +19048,10 @@
     </row>
     <row r="389" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B389" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C389" t="s">
         <v>761</v>
@@ -18954,16 +19086,16 @@
     </row>
     <row r="390" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B390" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C390" t="s">
         <v>761</v>
       </c>
       <c r="D390" t="s">
-        <v>789</v>
+        <v>762</v>
       </c>
       <c r="E390" t="s">
         <v>25</v>
@@ -18992,16 +19124,16 @@
     </row>
     <row r="391" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="B391" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="C391" t="s">
         <v>761</v>
       </c>
       <c r="D391" t="s">
-        <v>789</v>
+        <v>762</v>
       </c>
       <c r="E391" t="s">
         <v>25</v>
@@ -19030,10 +19162,10 @@
     </row>
     <row r="392" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="B392" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C392" t="s">
         <v>761</v>
@@ -19068,10 +19200,10 @@
     </row>
     <row r="393" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B393" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="C393" t="s">
         <v>761</v>
@@ -19106,10 +19238,10 @@
     </row>
     <row r="394" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B394" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="C394" t="s">
         <v>761</v>
@@ -19144,16 +19276,16 @@
     </row>
     <row r="395" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B395" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="C395" t="s">
         <v>761</v>
       </c>
       <c r="D395" t="s">
-        <v>211</v>
+        <v>789</v>
       </c>
       <c r="E395" t="s">
         <v>25</v>
@@ -19182,16 +19314,16 @@
     </row>
     <row r="396" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B396" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="C396" t="s">
         <v>761</v>
       </c>
       <c r="D396" t="s">
-        <v>211</v>
+        <v>789</v>
       </c>
       <c r="E396" t="s">
         <v>25</v>
@@ -19220,10 +19352,10 @@
     </row>
     <row r="397" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B397" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="C397" t="s">
         <v>761</v>
@@ -19258,16 +19390,16 @@
     </row>
     <row r="398" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B398" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C398" t="s">
         <v>761</v>
       </c>
       <c r="D398" t="s">
-        <v>806</v>
+        <v>211</v>
       </c>
       <c r="E398" t="s">
         <v>25</v>
@@ -19296,16 +19428,16 @@
     </row>
     <row r="399" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B399" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C399" t="s">
         <v>761</v>
       </c>
       <c r="D399" t="s">
-        <v>806</v>
+        <v>211</v>
       </c>
       <c r="E399" t="s">
         <v>25</v>
@@ -19334,16 +19466,16 @@
     </row>
     <row r="400" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="B400" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="C400" t="s">
         <v>761</v>
       </c>
       <c r="D400" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="E400" t="s">
         <v>25</v>
@@ -19372,16 +19504,16 @@
     </row>
     <row r="401" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="B401" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="C401" t="s">
         <v>761</v>
       </c>
       <c r="D401" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="E401" t="s">
         <v>25</v>
@@ -19410,10 +19542,10 @@
     </row>
     <row r="402" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="B402" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="C402" t="s">
         <v>761</v>
@@ -19448,16 +19580,16 @@
     </row>
     <row r="403" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B403" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C403" t="s">
         <v>761</v>
       </c>
       <c r="D403" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="E403" t="s">
         <v>25</v>
@@ -19486,16 +19618,16 @@
     </row>
     <row r="404" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="B404" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="C404" t="s">
         <v>761</v>
       </c>
       <c r="D404" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="E404" t="s">
         <v>25</v>
@@ -19524,10 +19656,10 @@
     </row>
     <row r="405" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="B405" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C405" t="s">
         <v>761</v>
@@ -19562,10 +19694,10 @@
     </row>
     <row r="406" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B406" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="C406" t="s">
         <v>761</v>
@@ -19600,10 +19732,10 @@
     </row>
     <row r="407" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B407" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="C407" t="s">
         <v>761</v>
@@ -19638,10 +19770,10 @@
     </row>
     <row r="408" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B408" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="C408" t="s">
         <v>761</v>
@@ -19676,10 +19808,10 @@
     </row>
     <row r="409" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B409" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C409" t="s">
         <v>761</v>
@@ -19714,10 +19846,10 @@
     </row>
     <row r="410" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B410" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="C410" t="s">
         <v>761</v>
@@ -19752,10 +19884,10 @@
     </row>
     <row r="411" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B411" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C411" t="s">
         <v>761</v>
@@ -19790,10 +19922,10 @@
     </row>
     <row r="412" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B412" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="C412" t="s">
         <v>761</v>
@@ -19828,10 +19960,10 @@
     </row>
     <row r="413" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B413" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="C413" t="s">
         <v>761</v>
@@ -19866,10 +19998,10 @@
     </row>
     <row r="414" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B414" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="C414" t="s">
         <v>761</v>
@@ -19904,16 +20036,16 @@
     </row>
     <row r="415" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B415" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="C415" t="s">
         <v>761</v>
       </c>
       <c r="D415" t="s">
-        <v>843</v>
+        <v>818</v>
       </c>
       <c r="E415" t="s">
         <v>25</v>
@@ -19942,16 +20074,16 @@
     </row>
     <row r="416" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="B416" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="C416" t="s">
         <v>761</v>
       </c>
       <c r="D416" t="s">
-        <v>843</v>
+        <v>818</v>
       </c>
       <c r="E416" t="s">
         <v>25</v>
@@ -19980,10 +20112,10 @@
     </row>
     <row r="417" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B417" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C417" t="s">
         <v>761</v>
@@ -20018,10 +20150,10 @@
     </row>
     <row r="418" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B418" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C418" t="s">
         <v>761</v>
@@ -20056,10 +20188,10 @@
     </row>
     <row r="419" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B419" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="C419" t="s">
         <v>761</v>
@@ -20094,16 +20226,16 @@
     </row>
     <row r="420" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B420" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C420" t="s">
         <v>761</v>
       </c>
       <c r="D420" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="E420" t="s">
         <v>25</v>
@@ -20132,16 +20264,16 @@
     </row>
     <row r="421" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="B421" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C421" t="s">
         <v>761</v>
       </c>
       <c r="D421" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="E421" t="s">
         <v>25</v>
@@ -20170,16 +20302,16 @@
     </row>
     <row r="422" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="B422" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="C422" t="s">
-        <v>859</v>
+        <v>761</v>
       </c>
       <c r="D422" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="E422" t="s">
         <v>25</v>
@@ -20208,16 +20340,16 @@
     </row>
     <row r="423" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="B423" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="C423" t="s">
-        <v>859</v>
+        <v>761</v>
       </c>
       <c r="D423" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="E423" t="s">
         <v>25</v>
@@ -20246,10 +20378,10 @@
     </row>
     <row r="424" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="B424" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="C424" t="s">
         <v>859</v>
@@ -20284,10 +20416,10 @@
     </row>
     <row r="425" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B425" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="C425" t="s">
         <v>859</v>
@@ -20322,10 +20454,10 @@
     </row>
     <row r="426" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B426" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C426" t="s">
         <v>859</v>
@@ -20360,10 +20492,10 @@
     </row>
     <row r="427" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B427" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="C427" t="s">
         <v>859</v>
@@ -20398,16 +20530,16 @@
     </row>
     <row r="428" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B428" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C428" t="s">
         <v>859</v>
       </c>
       <c r="D428" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="E428" t="s">
         <v>25</v>
@@ -20436,16 +20568,16 @@
     </row>
     <row r="429" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="B429" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="C429" t="s">
         <v>859</v>
       </c>
       <c r="D429" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="E429" t="s">
         <v>25</v>
@@ -20474,10 +20606,10 @@
     </row>
     <row r="430" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="B430" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="C430" t="s">
         <v>859</v>
@@ -20512,10 +20644,10 @@
     </row>
     <row r="431" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="B431" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="C431" t="s">
         <v>859</v>
@@ -20550,10 +20682,10 @@
     </row>
     <row r="432" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="B432" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="C432" t="s">
         <v>859</v>
@@ -20588,16 +20720,16 @@
     </row>
     <row r="433" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B433" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C433" t="s">
         <v>859</v>
       </c>
       <c r="D433" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="E433" t="s">
         <v>25</v>
@@ -20626,16 +20758,16 @@
     </row>
     <row r="434" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="B434" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C434" t="s">
         <v>859</v>
       </c>
       <c r="D434" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="E434" t="s">
         <v>25</v>
@@ -20664,10 +20796,10 @@
     </row>
     <row r="435" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="B435" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="C435" t="s">
         <v>859</v>
@@ -20702,16 +20834,16 @@
     </row>
     <row r="436" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B436" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="C436" t="s">
         <v>859</v>
       </c>
       <c r="D436" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="E436" t="s">
         <v>25</v>
@@ -20740,16 +20872,16 @@
     </row>
     <row r="437" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="B437" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C437" t="s">
         <v>859</v>
       </c>
       <c r="D437" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="E437" t="s">
         <v>25</v>
@@ -20778,16 +20910,16 @@
     </row>
     <row r="438" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B438" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="C438" t="s">
         <v>859</v>
       </c>
       <c r="D438" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="E438" t="s">
         <v>25</v>
@@ -20816,16 +20948,16 @@
     </row>
     <row r="439" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="B439" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="C439" t="s">
         <v>859</v>
       </c>
       <c r="D439" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="E439" t="s">
         <v>25</v>
@@ -20854,10 +20986,10 @@
     </row>
     <row r="440" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="B440" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="C440" t="s">
         <v>859</v>
@@ -20892,10 +21024,10 @@
     </row>
     <row r="441" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B441" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="C441" t="s">
         <v>859</v>
@@ -20930,16 +21062,16 @@
     </row>
     <row r="442" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B442" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="C442" t="s">
         <v>859</v>
       </c>
       <c r="D442" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="E442" t="s">
         <v>25</v>
@@ -20968,16 +21100,16 @@
     </row>
     <row r="443" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="B443" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="C443" t="s">
         <v>859</v>
       </c>
       <c r="D443" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="E443" t="s">
         <v>25</v>
@@ -21006,10 +21138,10 @@
     </row>
     <row r="444" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="B444" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="C444" t="s">
         <v>859</v>
@@ -21044,10 +21176,10 @@
     </row>
     <row r="445" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B445" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="C445" t="s">
         <v>859</v>
@@ -21082,10 +21214,10 @@
     </row>
     <row r="446" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B446" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C446" t="s">
         <v>859</v>
@@ -21120,16 +21252,16 @@
     </row>
     <row r="447" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B447" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="C447" t="s">
-        <v>916</v>
+        <v>859</v>
       </c>
       <c r="D447" t="s">
-        <v>25</v>
+        <v>905</v>
       </c>
       <c r="E447" t="s">
         <v>25</v>
@@ -21158,16 +21290,16 @@
     </row>
     <row r="448" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="B448" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="C448" t="s">
-        <v>916</v>
+        <v>859</v>
       </c>
       <c r="D448" t="s">
-        <v>25</v>
+        <v>905</v>
       </c>
       <c r="E448" t="s">
         <v>25</v>
@@ -21196,10 +21328,10 @@
     </row>
     <row r="449" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="B449" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="C449" t="s">
         <v>916</v>
@@ -21234,10 +21366,10 @@
     </row>
     <row r="450" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B450" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="C450" t="s">
         <v>916</v>
@@ -21272,10 +21404,10 @@
     </row>
     <row r="451" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B451" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="C451" t="s">
         <v>916</v>
@@ -21310,10 +21442,10 @@
     </row>
     <row r="452" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B452" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C452" t="s">
         <v>916</v>
@@ -21348,10 +21480,10 @@
     </row>
     <row r="453" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B453" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="C453" t="s">
         <v>916</v>
@@ -21386,10 +21518,10 @@
     </row>
     <row r="454" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B454" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C454" t="s">
         <v>916</v>
@@ -21424,10 +21556,10 @@
     </row>
     <row r="455" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B455" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C455" t="s">
         <v>916</v>
@@ -21462,10 +21594,10 @@
     </row>
     <row r="456" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B456" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C456" t="s">
         <v>916</v>
@@ -21500,10 +21632,10 @@
     </row>
     <row r="457" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B457" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="C457" t="s">
         <v>916</v>
@@ -21538,10 +21670,10 @@
     </row>
     <row r="458" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B458" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C458" t="s">
         <v>916</v>
@@ -21576,10 +21708,10 @@
     </row>
     <row r="459" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="B459" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C459" t="s">
         <v>916</v>
@@ -21614,10 +21746,10 @@
     </row>
     <row r="460" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B460" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="C460" t="s">
         <v>916</v>
@@ -21652,10 +21784,10 @@
     </row>
     <row r="461" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B461" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C461" t="s">
         <v>916</v>
@@ -21690,16 +21822,16 @@
     </row>
     <row r="462" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B462" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C462" t="s">
-        <v>947</v>
+        <v>916</v>
       </c>
       <c r="D462" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E462" t="s">
         <v>25</v>
@@ -21728,16 +21860,16 @@
     </row>
     <row r="463" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B463" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="C463" t="s">
-        <v>947</v>
+        <v>916</v>
       </c>
       <c r="D463" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E463" t="s">
         <v>25</v>
@@ -21766,10 +21898,10 @@
     </row>
     <row r="464" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="B464" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="C464" t="s">
         <v>947</v>
@@ -21804,10 +21936,10 @@
     </row>
     <row r="465" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B465" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C465" t="s">
         <v>947</v>
@@ -21842,16 +21974,16 @@
     </row>
     <row r="466" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B466" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="C466" t="s">
         <v>947</v>
       </c>
       <c r="D466" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="E466" t="s">
         <v>25</v>
@@ -21880,16 +22012,16 @@
     </row>
     <row r="467" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="B467" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="C467" t="s">
         <v>947</v>
       </c>
       <c r="D467" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="E467" t="s">
         <v>25</v>
@@ -21918,10 +22050,10 @@
     </row>
     <row r="468" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="B468" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="C468" t="s">
         <v>947</v>
@@ -21956,10 +22088,10 @@
     </row>
     <row r="469" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B469" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C469" t="s">
         <v>947</v>
@@ -21994,10 +22126,10 @@
     </row>
     <row r="470" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B470" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="C470" t="s">
         <v>947</v>
@@ -22032,10 +22164,10 @@
     </row>
     <row r="471" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B471" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="C471" t="s">
         <v>947</v>
@@ -22070,10 +22202,10 @@
     </row>
     <row r="472" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="B472" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="C472" t="s">
         <v>947</v>
@@ -22108,16 +22240,16 @@
     </row>
     <row r="473" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="B473" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="C473" t="s">
-        <v>972</v>
+        <v>947</v>
       </c>
       <c r="D473" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="E473" t="s">
         <v>25</v>
@@ -22146,16 +22278,16 @@
     </row>
     <row r="474" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="B474" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="C474" t="s">
-        <v>972</v>
+        <v>947</v>
       </c>
       <c r="D474" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="E474" t="s">
         <v>25</v>
@@ -22184,10 +22316,10 @@
     </row>
     <row r="475" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="B475" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="C475" t="s">
         <v>972</v>
@@ -22222,10 +22354,10 @@
     </row>
     <row r="476" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B476" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="C476" t="s">
         <v>972</v>
@@ -22260,10 +22392,10 @@
     </row>
     <row r="477" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B477" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="C477" t="s">
         <v>972</v>
@@ -22298,10 +22430,10 @@
     </row>
     <row r="478" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B478" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="C478" t="s">
         <v>972</v>
@@ -22336,10 +22468,10 @@
     </row>
     <row r="479" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="B479" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="C479" t="s">
         <v>972</v>
@@ -22374,10 +22506,10 @@
     </row>
     <row r="480" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B480" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="C480" t="s">
         <v>972</v>
@@ -22412,16 +22544,16 @@
     </row>
     <row r="481" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B481" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="C481" t="s">
         <v>972</v>
       </c>
       <c r="D481" t="s">
-        <v>990</v>
+        <v>973</v>
       </c>
       <c r="E481" t="s">
         <v>25</v>
@@ -22450,16 +22582,16 @@
     </row>
     <row r="482" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="B482" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="C482" t="s">
         <v>972</v>
       </c>
       <c r="D482" t="s">
-        <v>990</v>
+        <v>973</v>
       </c>
       <c r="E482" t="s">
         <v>25</v>
@@ -22488,10 +22620,10 @@
     </row>
     <row r="483" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="B483" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="C483" t="s">
         <v>972</v>
@@ -22526,10 +22658,10 @@
     </row>
     <row r="484" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B484" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C484" t="s">
         <v>972</v>
@@ -22564,10 +22696,10 @@
     </row>
     <row r="485" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B485" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C485" t="s">
         <v>972</v>
@@ -22602,16 +22734,16 @@
     </row>
     <row r="486" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B486" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C486" t="s">
         <v>972</v>
       </c>
       <c r="D486" t="s">
-        <v>1001</v>
+        <v>990</v>
       </c>
       <c r="E486" t="s">
         <v>25</v>
@@ -22640,16 +22772,16 @@
     </row>
     <row r="487" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="B487" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="C487" t="s">
         <v>972</v>
       </c>
       <c r="D487" t="s">
-        <v>1001</v>
+        <v>990</v>
       </c>
       <c r="E487" t="s">
         <v>25</v>
@@ -22678,16 +22810,16 @@
     </row>
     <row r="488" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="B488" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="C488" t="s">
         <v>972</v>
       </c>
       <c r="D488" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="E488" t="s">
         <v>25</v>
@@ -22716,16 +22848,16 @@
     </row>
     <row r="489" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="B489" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="C489" t="s">
         <v>972</v>
       </c>
       <c r="D489" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="E489" t="s">
         <v>25</v>
@@ -22754,10 +22886,10 @@
     </row>
     <row r="490" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="B490" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="C490" t="s">
         <v>972</v>
@@ -22792,10 +22924,10 @@
     </row>
     <row r="491" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="B491" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="C491" t="s">
         <v>972</v>
@@ -22830,10 +22962,10 @@
     </row>
     <row r="492" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="B492" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C492" t="s">
         <v>972</v>
@@ -22868,10 +23000,10 @@
     </row>
     <row r="493" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="B493" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="C493" t="s">
         <v>972</v>
@@ -22906,16 +23038,16 @@
     </row>
     <row r="494" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="B494" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C494" t="s">
         <v>972</v>
       </c>
       <c r="D494" t="s">
-        <v>1019</v>
+        <v>1006</v>
       </c>
       <c r="E494" t="s">
         <v>25</v>
@@ -22944,16 +23076,16 @@
     </row>
     <row r="495" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="B495" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="C495" t="s">
         <v>972</v>
       </c>
       <c r="D495" t="s">
-        <v>1019</v>
+        <v>1006</v>
       </c>
       <c r="E495" t="s">
         <v>25</v>
@@ -22982,10 +23114,10 @@
     </row>
     <row r="496" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="B496" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C496" t="s">
         <v>972</v>
@@ -23020,10 +23152,10 @@
     </row>
     <row r="497" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="B497" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="C497" t="s">
         <v>972</v>
@@ -23058,16 +23190,16 @@
     </row>
     <row r="498" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B498" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="C498" t="s">
         <v>972</v>
       </c>
       <c r="D498" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="E498" t="s">
         <v>25</v>
@@ -23096,16 +23228,16 @@
     </row>
     <row r="499" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="B499" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="C499" t="s">
         <v>972</v>
       </c>
       <c r="D499" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="E499" t="s">
         <v>25</v>
@@ -23134,10 +23266,10 @@
     </row>
     <row r="500" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="B500" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="C500" t="s">
         <v>972</v>
@@ -23172,10 +23304,10 @@
     </row>
     <row r="501" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B501" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C501" t="s">
         <v>972</v>
@@ -23210,16 +23342,16 @@
     </row>
     <row r="502" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="B502" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="C502" t="s">
         <v>972</v>
       </c>
       <c r="D502" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="E502" t="s">
         <v>25</v>
@@ -23248,16 +23380,16 @@
     </row>
     <row r="503" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="B503" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="C503" t="s">
         <v>972</v>
       </c>
       <c r="D503" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="E503" t="s">
         <v>25</v>
@@ -23286,10 +23418,10 @@
     </row>
     <row r="504" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="B504" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="C504" t="s">
         <v>972</v>
@@ -23324,10 +23456,10 @@
     </row>
     <row r="505" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="B505" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="C505" t="s">
         <v>972</v>
@@ -23362,16 +23494,16 @@
     </row>
     <row r="506" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B506" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="C506" t="s">
         <v>972</v>
       </c>
       <c r="D506" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="E506" t="s">
         <v>25</v>
@@ -23400,16 +23532,16 @@
     </row>
     <row r="507" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="B507" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="C507" t="s">
         <v>972</v>
       </c>
       <c r="D507" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="E507" t="s">
         <v>25</v>
@@ -23438,10 +23570,10 @@
     </row>
     <row r="508" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="B508" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C508" t="s">
         <v>972</v>
@@ -23476,10 +23608,10 @@
     </row>
     <row r="509" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="B509" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="C509" t="s">
         <v>972</v>
@@ -23514,16 +23646,16 @@
     </row>
     <row r="510" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="B510" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C510" t="s">
         <v>972</v>
       </c>
       <c r="D510" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="E510" t="s">
         <v>25</v>
@@ -23552,16 +23684,16 @@
     </row>
     <row r="511" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="B511" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="C511" t="s">
         <v>972</v>
       </c>
       <c r="D511" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="E511" t="s">
         <v>25</v>
@@ -23590,10 +23722,10 @@
     </row>
     <row r="512" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="B512" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C512" t="s">
         <v>972</v>
@@ -23628,10 +23760,10 @@
     </row>
     <row r="513" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B513" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="C513" t="s">
         <v>972</v>
@@ -23666,10 +23798,10 @@
     </row>
     <row r="514" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="B514" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="C514" t="s">
         <v>972</v>
@@ -23704,10 +23836,10 @@
     </row>
     <row r="515" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="B515" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="C515" t="s">
         <v>972</v>
@@ -23737,6 +23869,82 @@
         <v>25</v>
       </c>
       <c r="L515" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="516" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C516" t="s">
+        <v>972</v>
+      </c>
+      <c r="D516" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E516" t="s">
+        <v>25</v>
+      </c>
+      <c r="F516" t="s">
+        <v>25</v>
+      </c>
+      <c r="G516" t="s">
+        <v>25</v>
+      </c>
+      <c r="H516" t="s">
+        <v>19</v>
+      </c>
+      <c r="I516" t="s">
+        <v>25</v>
+      </c>
+      <c r="J516" t="s">
+        <v>25</v>
+      </c>
+      <c r="K516" t="s">
+        <v>25</v>
+      </c>
+      <c r="L516" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="517" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C517" t="s">
+        <v>972</v>
+      </c>
+      <c r="D517" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E517" t="s">
+        <v>25</v>
+      </c>
+      <c r="F517" t="s">
+        <v>25</v>
+      </c>
+      <c r="G517" t="s">
+        <v>25</v>
+      </c>
+      <c r="H517" t="s">
+        <v>19</v>
+      </c>
+      <c r="I517" t="s">
+        <v>25</v>
+      </c>
+      <c r="J517" t="s">
+        <v>25</v>
+      </c>
+      <c r="K517" t="s">
+        <v>25</v>
+      </c>
+      <c r="L517" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23744,7 +23952,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L4 A40:D40 L27 G27:I27 B27:E27 G28:L28 B29:L29 B28:E28 A53:L515 A46:D46 L46 A49:D49 J49:L49 A52:D52 J52:L52 H46 F49 F52 H49 H52 A43:D43 H43:I43 A6:L26 A5:E5 G5:L5 L43 F40 H40:L40" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L4 A42:D42 L29 G29:I29 B29:E29 G30:L30 B31:L31 B30:E30 A55:L517 A48:D48 L48 A51:D51 J51:L51 A54:D54 J54:L54 H48 F51 F54 H51 H54 A45:D45 H45:I45 A6:L8 A5:E5 G5:L5 L45 F42 H42:L42 A14:L28 B11:D11 F11 A12:D13 F13 J11:L11 F12 J12:L12 J13:L13 H11 H12 H13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="252" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0411DC04-E357-44FA-B69B-DCD662450104}"/>
+  <xr:revisionPtr revIDLastSave="313" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE1A5C1D-AAE3-433A-9151-18AB774E65E1}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6336" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6373" uniqueCount="1133">
   <si>
     <t>Codigo</t>
   </si>
@@ -4174,6 +4174,324 @@
 Revisar periódicamente ruedas y sistema de seguridad.
 Guardar en un lugar limpio y seco cuando no esté en uso.</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Coche Maleta City</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> está diseñado para ofrecer seguridad, confort y practicidad en cada salida. Su sistema de plegado tipo maleta facilita el transporte y almacenamiento, mientras que su reclinación ajustable, triple amortiguación y arnés de 5 puntos brindan un paseo cómodo y seguro para tu bebé. Además, incorpora una amplia capota protectora y canastilla inferior para mayor funcionalidad.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Coche Maleta City</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> plegable con arnés de 5 puntos, múltiples posiciones de reclinación y triple amortiguación, ideal para paseos y viajes con total comodidad.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Estructura metálica reforzada.
+Sistema de plegado tipo maleta.
+Arnés de seguridad de 5 puntos.
+Múltiples posiciones de reclinación.
+Triple sistema de amortiguación.
+Llantas en goma comprimida de alta resistencia.
+Descansapiés ajustable.
+Capota tipo stroller extendida.
+Canastilla inferior portaobjetos.
+Incluye cubrepiés.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Fácil de transportar y almacenar.
+Paseos más cómodos gracias a su amortiguación.
+Mayor seguridad con arnés de 5 puntos.
+Excelente estabilidad en diferentes superficies.
+Ideal para el uso diario, viajes y caminatas.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Limpiar la estructura y la tela con un paño húmedo.
+Verificar el sistema de plegado antes de cada uso.
+Ajustar el arnés correctamente durante el paseo.
+Guardar en un lugar limpio y seco cuando no esté en uso.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cochecity/cityblue.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cochecity/cityblack.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cochecity/citypink.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cochecity/citygris.webp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Triciclo Coche Paseador 5 en 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> está diseñado para adaptarse al crecimiento de tu bebé, ofreciendo cinco modos de uso en un solo producto. Cuenta con estructura resistente, asiento acolchado, capota ajustable, cinturón de seguridad y barra protectora para brindar mayor comodidad y seguridad en cada paseo. Ideal para el uso diario y salidas en familia.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Medidas del producto:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Alto: 100 cm aprox.
+Largo: 95 cm aprox.
+Ancho: 50 cm aprox.
+Peso: 10 - 11 kg aprox.</t>
+    </r>
+  </si>
+  <si>
+    <t>Negro con Amarillo</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Diseño multifuncional 5 en 1.
+Capota ajustable.
+Asiento acolchado.
+Cinturón de seguridad y barra protectora.
+Estructura resistente.
+Canastilla trasera portaobjetos.
+Portabotellas integrado.
+Edad recomendada: desde los 12 meses.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Se adapta al crecimiento del niño.
+Brinda mayor seguridad y comodidad durante los paseos.
+Ideal para paseos familiares y uso diario.
+Amplio espacio para transportar accesorios.
+Fácil de maniobrar y cómodo para padres e hijos.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Utilizar siempre el cinturón de seguridad durante el uso.
+Ajustar la capota según las condiciones del clima.
+Limpiar la estructura y la tela con un paño húmedo.
+Revisar periódicamente ruedas y uniones antes de cada paseo.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Triciclo coche paseador 5 en 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con capota ajustable, asiento acolchado y sistema multifuncional que acompaña el crecimiento del bebé en cada etapa.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/coche5en1/5en1negro.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/coche5en1/5en1azul.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/coche5en1/5en1azul2.webp</t>
   </si>
 </sst>
 </file>
@@ -4575,7 +4893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L520"/>
+  <dimension ref="A1:L524"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5353,26 +5671,26 @@
       <c r="D21" t="s">
         <v>15</v>
       </c>
-      <c r="E21" t="s">
-        <v>25</v>
+      <c r="E21">
+        <v>562875</v>
       </c>
       <c r="F21" t="s">
-        <v>25</v>
+        <v>1119</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>1122</v>
       </c>
       <c r="H21" t="s">
         <v>19</v>
       </c>
       <c r="I21" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J21" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" t="s">
-        <v>25</v>
+        <v>1120</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>1121</v>
       </c>
       <c r="L21" t="s">
         <v>25</v>
@@ -5391,20 +5709,20 @@
       <c r="D22" t="s">
         <v>15</v>
       </c>
-      <c r="E22" t="s">
-        <v>25</v>
+      <c r="E22">
+        <v>562875</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>1123</v>
       </c>
       <c r="H22" t="s">
         <v>19</v>
       </c>
       <c r="I22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J22" t="s">
         <v>25</v>
@@ -5429,20 +5747,20 @@
       <c r="D23" t="s">
         <v>15</v>
       </c>
-      <c r="E23" t="s">
-        <v>25</v>
+      <c r="E23">
+        <v>562875</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>1124</v>
       </c>
       <c r="H23" t="s">
         <v>19</v>
       </c>
       <c r="I23" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="J23" t="s">
         <v>25</v>
@@ -5467,20 +5785,20 @@
       <c r="D24" t="s">
         <v>15</v>
       </c>
-      <c r="E24" t="s">
-        <v>25</v>
+      <c r="E24">
+        <v>562875</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>1125</v>
       </c>
       <c r="H24" t="s">
         <v>19</v>
       </c>
       <c r="I24" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J24" t="s">
         <v>25</v>
@@ -5505,26 +5823,26 @@
       <c r="D25" t="s">
         <v>64</v>
       </c>
-      <c r="E25" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" t="s">
-        <v>25</v>
+      <c r="E25">
+        <v>596949</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>1126</v>
       </c>
       <c r="G25" t="s">
-        <v>25</v>
+        <v>1130</v>
       </c>
       <c r="H25" t="s">
         <v>19</v>
       </c>
       <c r="I25" t="s">
-        <v>25</v>
+        <v>1127</v>
       </c>
       <c r="J25" t="s">
-        <v>25</v>
-      </c>
-      <c r="K25" t="s">
-        <v>25</v>
+        <v>1129</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>1128</v>
       </c>
       <c r="L25" t="s">
         <v>25</v>
@@ -5532,10 +5850,10 @@
     </row>
     <row r="26" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -5543,37 +5861,30 @@
       <c r="D26" t="s">
         <v>64</v>
       </c>
-      <c r="E26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" t="s">
-        <v>25</v>
-      </c>
+      <c r="E26">
+        <v>596949</v>
+      </c>
+      <c r="F26" s="2"/>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>1131</v>
       </c>
       <c r="H26" t="s">
         <v>19</v>
       </c>
       <c r="I26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" t="s">
-        <v>25</v>
-      </c>
-      <c r="K26" t="s">
-        <v>25</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="K26" s="2"/>
       <c r="L26" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -5581,37 +5892,30 @@
       <c r="D27" t="s">
         <v>64</v>
       </c>
-      <c r="E27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" t="s">
-        <v>25</v>
-      </c>
+      <c r="E27">
+        <v>596949</v>
+      </c>
+      <c r="F27" s="2"/>
       <c r="G27" t="s">
-        <v>25</v>
+        <v>1132</v>
       </c>
       <c r="H27" t="s">
         <v>19</v>
       </c>
       <c r="I27" t="s">
-        <v>25</v>
-      </c>
-      <c r="J27" t="s">
-        <v>25</v>
-      </c>
-      <c r="K27" t="s">
-        <v>25</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="K27" s="2"/>
       <c r="L27" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -5646,10 +5950,10 @@
     </row>
     <row r="29" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
@@ -5684,7 +5988,7 @@
     </row>
     <row r="30" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
         <v>70</v>
@@ -5710,9 +6014,6 @@
       <c r="I30" t="s">
         <v>25</v>
       </c>
-      <c r="J30" t="s">
-        <v>25</v>
-      </c>
       <c r="K30" t="s">
         <v>25</v>
       </c>
@@ -5722,7 +6023,7 @@
     </row>
     <row r="31" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
         <v>70</v>
@@ -5760,37 +6061,37 @@
     </row>
     <row r="32" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
-      </c>
-      <c r="E32">
-        <v>220230</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>1088</v>
+        <v>64</v>
+      </c>
+      <c r="E32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
+        <v>25</v>
       </c>
       <c r="G32" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
       </c>
       <c r="I32" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>1066</v>
+        <v>25</v>
+      </c>
+      <c r="J32" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" t="s">
+        <v>25</v>
       </c>
       <c r="L32" t="s">
         <v>25</v>
@@ -5798,28 +6099,31 @@
     </row>
     <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33">
-        <v>220230</v>
+        <v>64</v>
+      </c>
+      <c r="E33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" t="s">
+        <v>25</v>
       </c>
       <c r="G33" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="H33" t="s">
         <v>19</v>
       </c>
       <c r="I33" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="J33" t="s">
         <v>25</v>
@@ -5847,11 +6151,11 @@
       <c r="E34">
         <v>220230</v>
       </c>
-      <c r="F34" t="s">
-        <v>25</v>
+      <c r="F34" s="2" t="s">
+        <v>1088</v>
       </c>
       <c r="G34" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s">
         <v>19</v>
@@ -5859,11 +6163,11 @@
       <c r="I34" t="s">
         <v>42</v>
       </c>
-      <c r="J34" t="s">
-        <v>25</v>
-      </c>
-      <c r="K34" t="s">
-        <v>25</v>
+      <c r="J34" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>1066</v>
       </c>
       <c r="L34" t="s">
         <v>25</v>
@@ -5871,7 +6175,7 @@
     </row>
     <row r="35" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
         <v>75</v>
@@ -5886,18 +6190,27 @@
         <v>220230</v>
       </c>
       <c r="G35" t="s">
-        <v>1068</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s">
         <v>19</v>
       </c>
       <c r="I35" t="s">
-        <v>1067</v>
+        <v>42</v>
+      </c>
+      <c r="J35" t="s">
+        <v>25</v>
+      </c>
+      <c r="K35" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
         <v>75</v>
@@ -5911,19 +6224,31 @@
       <c r="E36">
         <v>220230</v>
       </c>
+      <c r="F36" t="s">
+        <v>25</v>
+      </c>
       <c r="G36" t="s">
-        <v>1069</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s">
         <v>19</v>
       </c>
       <c r="I36" t="s">
-        <v>1067</v>
+        <v>42</v>
+      </c>
+      <c r="J36" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B37" t="s">
         <v>75</v>
@@ -5938,18 +6263,18 @@
         <v>220230</v>
       </c>
       <c r="G37" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="H37" t="s">
         <v>19</v>
       </c>
       <c r="I37" t="s">
-        <v>27</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B38" t="s">
         <v>75</v>
@@ -5964,13 +6289,13 @@
         <v>220230</v>
       </c>
       <c r="G38" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H38" t="s">
         <v>19</v>
       </c>
       <c r="I38" t="s">
-        <v>27</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -5990,7 +6315,7 @@
         <v>220230</v>
       </c>
       <c r="G39" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="H39" t="s">
         <v>19</v>
@@ -6016,7 +6341,7 @@
         <v>220230</v>
       </c>
       <c r="G40" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H40" t="s">
         <v>19</v>
@@ -6042,7 +6367,7 @@
         <v>220230</v>
       </c>
       <c r="G41" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="H41" t="s">
         <v>19</v>
@@ -6068,7 +6393,7 @@
         <v>220230</v>
       </c>
       <c r="G42" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="H42" t="s">
         <v>19</v>
@@ -6079,10 +6404,10 @@
     </row>
     <row r="43" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
@@ -6091,36 +6416,24 @@
         <v>76</v>
       </c>
       <c r="E43">
-        <v>162029</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>1098</v>
+        <v>220230</v>
       </c>
       <c r="G43" t="s">
-        <v>1095</v>
+        <v>1074</v>
       </c>
       <c r="H43" t="s">
         <v>19</v>
       </c>
       <c r="I43" t="s">
-        <v>25</v>
-      </c>
-      <c r="J43" t="s">
-        <v>1099</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="L43" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -6129,28 +6442,16 @@
         <v>76</v>
       </c>
       <c r="E44">
-        <v>162029</v>
-      </c>
-      <c r="F44" t="s">
-        <v>25</v>
+        <v>220230</v>
       </c>
       <c r="G44" t="s">
-        <v>1096</v>
+        <v>1075</v>
       </c>
       <c r="H44" t="s">
         <v>19</v>
       </c>
       <c r="I44" t="s">
-        <v>25</v>
-      </c>
-      <c r="J44" t="s">
-        <v>25</v>
-      </c>
-      <c r="K44" t="s">
-        <v>25</v>
-      </c>
-      <c r="L44" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -6169,11 +6470,11 @@
       <c r="E45">
         <v>162029</v>
       </c>
-      <c r="F45" t="s">
-        <v>25</v>
+      <c r="F45" s="2" t="s">
+        <v>1098</v>
       </c>
       <c r="G45" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H45" t="s">
         <v>19</v>
@@ -6182,10 +6483,10 @@
         <v>25</v>
       </c>
       <c r="J45" t="s">
-        <v>25</v>
-      </c>
-      <c r="K45" t="s">
-        <v>25</v>
+        <v>1099</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>1100</v>
       </c>
       <c r="L45" t="s">
         <v>25</v>
@@ -6193,10 +6494,10 @@
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B46" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -6205,13 +6506,13 @@
         <v>76</v>
       </c>
       <c r="E46">
-        <v>185000</v>
+        <v>162029</v>
       </c>
       <c r="F46" t="s">
-        <v>1091</v>
+        <v>25</v>
       </c>
       <c r="G46" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="H46" t="s">
         <v>19</v>
@@ -6220,10 +6521,10 @@
         <v>25</v>
       </c>
       <c r="J46" t="s">
-        <v>1089</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>1090</v>
+        <v>25</v>
+      </c>
+      <c r="K46" t="s">
+        <v>25</v>
       </c>
       <c r="L46" t="s">
         <v>25</v>
@@ -6231,10 +6532,10 @@
     </row>
     <row r="47" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -6243,10 +6544,13 @@
         <v>76</v>
       </c>
       <c r="E47">
-        <v>185000</v>
+        <v>162029</v>
+      </c>
+      <c r="F47" t="s">
+        <v>25</v>
       </c>
       <c r="G47" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="H47" t="s">
         <v>19</v>
@@ -6254,7 +6558,12 @@
       <c r="I47" t="s">
         <v>25</v>
       </c>
-      <c r="K47" s="2"/>
+      <c r="J47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" t="s">
+        <v>25</v>
+      </c>
       <c r="L47" t="s">
         <v>25</v>
       </c>
@@ -6275,8 +6584,11 @@
       <c r="E48">
         <v>185000</v>
       </c>
+      <c r="F48" t="s">
+        <v>1091</v>
+      </c>
       <c r="G48" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="H48" t="s">
         <v>19</v>
@@ -6284,17 +6596,22 @@
       <c r="I48" t="s">
         <v>25</v>
       </c>
-      <c r="K48" s="2"/>
+      <c r="J48" t="s">
+        <v>1089</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>1090</v>
+      </c>
       <c r="L48" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B49" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
@@ -6303,36 +6620,28 @@
         <v>76</v>
       </c>
       <c r="E49">
-        <v>119390</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>1077</v>
+        <v>185000</v>
       </c>
       <c r="G49" t="s">
-        <v>1079</v>
+        <v>1093</v>
       </c>
       <c r="H49" t="s">
         <v>19</v>
       </c>
       <c r="I49" t="s">
-        <v>39</v>
-      </c>
-      <c r="J49" t="s">
-        <v>1076</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>1078</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="K49" s="2"/>
       <c r="L49" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B50" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
@@ -6341,17 +6650,16 @@
         <v>76</v>
       </c>
       <c r="E50">
-        <v>119390</v>
-      </c>
-      <c r="F50" s="2"/>
+        <v>185000</v>
+      </c>
       <c r="G50" t="s">
-        <v>1080</v>
+        <v>1094</v>
       </c>
       <c r="H50" t="s">
         <v>19</v>
       </c>
       <c r="I50" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" t="s">
@@ -6374,9 +6682,11 @@
       <c r="E51">
         <v>119390</v>
       </c>
-      <c r="F51" s="2"/>
+      <c r="F51" s="2" t="s">
+        <v>1077</v>
+      </c>
       <c r="G51" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="H51" t="s">
         <v>19</v>
@@ -6384,14 +6694,19 @@
       <c r="I51" t="s">
         <v>39</v>
       </c>
-      <c r="K51" s="2"/>
+      <c r="J51" t="s">
+        <v>1076</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>1078</v>
+      </c>
       <c r="L51" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B52" t="s">
         <v>87</v>
@@ -6405,31 +6720,24 @@
       <c r="E52">
         <v>119390</v>
       </c>
-      <c r="F52" t="s">
-        <v>25</v>
-      </c>
+      <c r="F52" s="2"/>
       <c r="G52" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="H52" t="s">
         <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>42</v>
-      </c>
-      <c r="J52" t="s">
-        <v>25</v>
-      </c>
-      <c r="K52" t="s">
-        <v>25</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="K52" s="2"/>
       <c r="L52" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B53" t="s">
         <v>87</v>
@@ -6443,24 +6751,17 @@
       <c r="E53">
         <v>119390</v>
       </c>
-      <c r="F53" t="s">
-        <v>25</v>
-      </c>
+      <c r="F53" s="2"/>
       <c r="G53" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H53" t="s">
         <v>19</v>
       </c>
       <c r="I53" t="s">
-        <v>42</v>
-      </c>
-      <c r="J53" t="s">
-        <v>25</v>
-      </c>
-      <c r="K53" t="s">
-        <v>25</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="K53" s="2"/>
       <c r="L53" t="s">
         <v>25</v>
       </c>
@@ -6485,7 +6786,7 @@
         <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H54" t="s">
         <v>19</v>
@@ -6505,7 +6806,7 @@
     </row>
     <row r="55" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B55" t="s">
         <v>87</v>
@@ -6523,15 +6824,18 @@
         <v>25</v>
       </c>
       <c r="G55" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="H55" t="s">
         <v>19</v>
       </c>
       <c r="I55" t="s">
-        <v>1067</v>
+        <v>42</v>
       </c>
       <c r="J55" t="s">
+        <v>25</v>
+      </c>
+      <c r="K55" t="s">
         <v>25</v>
       </c>
       <c r="L55" t="s">
@@ -6540,7 +6844,7 @@
     </row>
     <row r="56" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56" t="s">
         <v>87</v>
@@ -6558,13 +6862,13 @@
         <v>25</v>
       </c>
       <c r="G56" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="H56" t="s">
         <v>19</v>
       </c>
       <c r="I56" t="s">
-        <v>1067</v>
+        <v>42</v>
       </c>
       <c r="J56" t="s">
         <v>25</v>
@@ -6596,7 +6900,7 @@
         <v>25</v>
       </c>
       <c r="G57" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H57" t="s">
         <v>19</v>
@@ -6607,40 +6911,37 @@
       <c r="J57" t="s">
         <v>25</v>
       </c>
-      <c r="K57" t="s">
-        <v>25</v>
-      </c>
       <c r="L57" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B58" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>92</v>
-      </c>
-      <c r="E58" t="s">
-        <v>25</v>
+        <v>76</v>
+      </c>
+      <c r="E58">
+        <v>119390</v>
       </c>
       <c r="F58" t="s">
         <v>25</v>
       </c>
       <c r="G58" t="s">
-        <v>25</v>
+        <v>1086</v>
       </c>
       <c r="H58" t="s">
         <v>19</v>
       </c>
       <c r="I58" t="s">
-        <v>25</v>
+        <v>1067</v>
       </c>
       <c r="J58" t="s">
         <v>25</v>
@@ -6654,31 +6955,31 @@
     </row>
     <row r="59" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>92</v>
-      </c>
-      <c r="E59" t="s">
-        <v>25</v>
+        <v>76</v>
+      </c>
+      <c r="E59">
+        <v>119390</v>
       </c>
       <c r="F59" t="s">
         <v>25</v>
       </c>
       <c r="G59" t="s">
-        <v>25</v>
+        <v>1087</v>
       </c>
       <c r="H59" t="s">
         <v>19</v>
       </c>
       <c r="I59" t="s">
-        <v>25</v>
+        <v>1067</v>
       </c>
       <c r="J59" t="s">
         <v>25</v>
@@ -6692,10 +6993,10 @@
     </row>
     <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B60" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -6730,10 +7031,10 @@
     </row>
     <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -6768,10 +7069,10 @@
     </row>
     <row r="62" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B62" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -6806,10 +7107,10 @@
     </row>
     <row r="63" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B63" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
@@ -6844,10 +7145,10 @@
     </row>
     <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -6861,7 +7162,7 @@
       <c r="F64" t="s">
         <v>25</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" t="s">
         <v>25</v>
       </c>
       <c r="H64" t="s">
@@ -6882,10 +7183,10 @@
     </row>
     <row r="65" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -6920,10 +7221,10 @@
     </row>
     <row r="66" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -6937,7 +7238,7 @@
       <c r="F66" t="s">
         <v>25</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G66" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H66" t="s">
@@ -6958,10 +7259,10 @@
     </row>
     <row r="67" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B67" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
@@ -6996,10 +7297,10 @@
     </row>
     <row r="68" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B68" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
@@ -7034,10 +7335,10 @@
     </row>
     <row r="69" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -7072,7 +7373,7 @@
     </row>
     <row r="70" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B70" t="s">
         <v>112</v>
@@ -7110,10 +7411,10 @@
     </row>
     <row r="71" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -7148,10 +7449,10 @@
     </row>
     <row r="72" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B72" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
@@ -7186,16 +7487,16 @@
     </row>
     <row r="73" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B73" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
@@ -7224,16 +7525,16 @@
     </row>
     <row r="74" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B74" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="E74" t="s">
         <v>25</v>
@@ -7262,10 +7563,10 @@
     </row>
     <row r="75" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B75" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
@@ -7300,10 +7601,10 @@
     </row>
     <row r="76" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B76" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -7338,10 +7639,10 @@
     </row>
     <row r="77" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B77" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
@@ -7376,10 +7677,10 @@
     </row>
     <row r="78" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B78" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -7414,10 +7715,10 @@
     </row>
     <row r="79" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B79" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
@@ -7452,10 +7753,10 @@
     </row>
     <row r="80" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B80" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
@@ -7490,16 +7791,16 @@
     </row>
     <row r="81" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B81" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E81" t="s">
         <v>25</v>
@@ -7528,16 +7829,16 @@
     </row>
     <row r="82" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B82" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E82" t="s">
         <v>25</v>
@@ -7566,10 +7867,10 @@
     </row>
     <row r="83" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B83" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -7604,10 +7905,10 @@
     </row>
     <row r="84" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B84" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
@@ -7642,10 +7943,10 @@
     </row>
     <row r="85" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B85" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -7680,16 +7981,16 @@
     </row>
     <row r="86" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B86" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
@@ -7718,16 +8019,16 @@
     </row>
     <row r="87" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B87" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E87" t="s">
         <v>25</v>
@@ -7756,10 +8057,10 @@
     </row>
     <row r="88" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B88" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -7794,10 +8095,10 @@
     </row>
     <row r="89" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B89" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -7832,10 +8133,10 @@
     </row>
     <row r="90" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B90" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -7870,10 +8171,10 @@
     </row>
     <row r="91" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B91" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
@@ -7908,10 +8209,10 @@
     </row>
     <row r="92" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B92" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
@@ -7946,16 +8247,16 @@
     </row>
     <row r="93" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B93" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="E93" t="s">
         <v>25</v>
@@ -7984,16 +8285,16 @@
     </row>
     <row r="94" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B94" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="E94" t="s">
         <v>25</v>
@@ -8022,10 +8323,10 @@
     </row>
     <row r="95" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B95" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
@@ -8060,10 +8361,10 @@
     </row>
     <row r="96" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B96" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
@@ -8098,10 +8399,10 @@
     </row>
     <row r="97" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B97" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -8136,10 +8437,10 @@
     </row>
     <row r="98" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B98" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
@@ -8174,10 +8475,10 @@
     </row>
     <row r="99" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B99" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C99" t="s">
         <v>14</v>
@@ -8212,10 +8513,10 @@
     </row>
     <row r="100" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B100" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
@@ -8250,10 +8551,10 @@
     </row>
     <row r="101" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B101" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C101" t="s">
         <v>14</v>
@@ -8288,10 +8589,10 @@
     </row>
     <row r="102" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B102" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
@@ -8326,10 +8627,10 @@
     </row>
     <row r="103" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B103" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
@@ -8364,10 +8665,10 @@
     </row>
     <row r="104" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B104" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C104" t="s">
         <v>14</v>
@@ -8402,10 +8703,10 @@
     </row>
     <row r="105" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B105" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C105" t="s">
         <v>14</v>
@@ -8440,10 +8741,10 @@
     </row>
     <row r="106" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B106" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
@@ -8478,10 +8779,10 @@
     </row>
     <row r="107" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B107" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
@@ -8516,10 +8817,10 @@
     </row>
     <row r="108" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B108" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
@@ -8554,10 +8855,10 @@
     </row>
     <row r="109" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B109" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C109" t="s">
         <v>14</v>
@@ -8592,10 +8893,10 @@
     </row>
     <row r="110" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B110" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C110" t="s">
         <v>14</v>
@@ -8630,10 +8931,10 @@
     </row>
     <row r="111" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B111" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C111" t="s">
         <v>14</v>
@@ -8668,10 +8969,10 @@
     </row>
     <row r="112" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B112" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C112" t="s">
         <v>14</v>
@@ -8706,10 +9007,10 @@
     </row>
     <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B113" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C113" t="s">
         <v>14</v>
@@ -8717,14 +9018,14 @@
       <c r="D113" t="s">
         <v>163</v>
       </c>
-      <c r="E113">
-        <v>106156</v>
+      <c r="E113" t="s">
+        <v>25</v>
       </c>
       <c r="F113" t="s">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="G113" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="H113" t="s">
         <v>19</v>
@@ -8733,10 +9034,10 @@
         <v>25</v>
       </c>
       <c r="J113" t="s">
-        <v>205</v>
+        <v>25</v>
       </c>
       <c r="K113" t="s">
-        <v>206</v>
+        <v>25</v>
       </c>
       <c r="L113" t="s">
         <v>25</v>
@@ -8744,10 +9045,10 @@
     </row>
     <row r="114" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B114" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
@@ -8755,14 +9056,14 @@
       <c r="D114" t="s">
         <v>163</v>
       </c>
-      <c r="E114">
-        <v>106156</v>
+      <c r="E114" t="s">
+        <v>25</v>
       </c>
       <c r="F114" t="s">
         <v>25</v>
       </c>
       <c r="G114" t="s">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="H114" t="s">
         <v>19</v>
@@ -8782,25 +9083,25 @@
     </row>
     <row r="115" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B115" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
       </c>
       <c r="D115" t="s">
-        <v>210</v>
-      </c>
-      <c r="E115" t="s">
-        <v>25</v>
+        <v>163</v>
+      </c>
+      <c r="E115">
+        <v>106156</v>
       </c>
       <c r="F115" t="s">
-        <v>25</v>
+        <v>203</v>
       </c>
       <c r="G115" t="s">
-        <v>25</v>
+        <v>204</v>
       </c>
       <c r="H115" t="s">
         <v>19</v>
@@ -8809,10 +9110,10 @@
         <v>25</v>
       </c>
       <c r="J115" t="s">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="K115" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="L115" t="s">
         <v>25</v>
@@ -8820,25 +9121,25 @@
     </row>
     <row r="116" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B116" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C116" t="s">
         <v>14</v>
       </c>
       <c r="D116" t="s">
-        <v>210</v>
-      </c>
-      <c r="E116" t="s">
-        <v>25</v>
+        <v>163</v>
+      </c>
+      <c r="E116">
+        <v>106156</v>
       </c>
       <c r="F116" t="s">
         <v>25</v>
       </c>
       <c r="G116" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="H116" t="s">
         <v>19</v>
@@ -8858,10 +9159,10 @@
     </row>
     <row r="117" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B117" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C117" t="s">
         <v>14</v>
@@ -8896,10 +9197,10 @@
     </row>
     <row r="118" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B118" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C118" t="s">
         <v>14</v>
@@ -8934,10 +9235,10 @@
     </row>
     <row r="119" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B119" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C119" t="s">
         <v>14</v>
@@ -8972,10 +9273,10 @@
     </row>
     <row r="120" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B120" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C120" t="s">
         <v>14</v>
@@ -9010,10 +9311,10 @@
     </row>
     <row r="121" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B121" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C121" t="s">
         <v>14</v>
@@ -9048,10 +9349,10 @@
     </row>
     <row r="122" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B122" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
@@ -9086,10 +9387,10 @@
     </row>
     <row r="123" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B123" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C123" t="s">
         <v>14</v>
@@ -9124,10 +9425,10 @@
     </row>
     <row r="124" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B124" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C124" t="s">
         <v>14</v>
@@ -9162,10 +9463,10 @@
     </row>
     <row r="125" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B125" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
@@ -9200,10 +9501,10 @@
     </row>
     <row r="126" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B126" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C126" t="s">
         <v>14</v>
@@ -9238,10 +9539,10 @@
     </row>
     <row r="127" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B127" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C127" t="s">
         <v>14</v>
@@ -9276,16 +9577,16 @@
     </row>
     <row r="128" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B128" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C128" t="s">
         <v>14</v>
       </c>
       <c r="D128" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="E128" t="s">
         <v>25</v>
@@ -9314,16 +9615,16 @@
     </row>
     <row r="129" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B129" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C129" t="s">
         <v>14</v>
       </c>
       <c r="D129" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="E129" t="s">
         <v>25</v>
@@ -9352,10 +9653,10 @@
     </row>
     <row r="130" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B130" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C130" t="s">
         <v>14</v>
@@ -9390,10 +9691,10 @@
     </row>
     <row r="131" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B131" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C131" t="s">
         <v>14</v>
@@ -9428,10 +9729,10 @@
     </row>
     <row r="132" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B132" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C132" t="s">
         <v>14</v>
@@ -9466,16 +9767,16 @@
     </row>
     <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B133" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C133" t="s">
         <v>14</v>
       </c>
       <c r="D133" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E133" t="s">
         <v>25</v>
@@ -9504,16 +9805,16 @@
     </row>
     <row r="134" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B134" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C134" t="s">
         <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E134" t="s">
         <v>25</v>
@@ -9542,16 +9843,16 @@
     </row>
     <row r="135" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B135" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C135" t="s">
-        <v>251</v>
+        <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E135" t="s">
         <v>25</v>
@@ -9580,16 +9881,16 @@
     </row>
     <row r="136" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B136" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C136" t="s">
-        <v>251</v>
+        <v>14</v>
       </c>
       <c r="D136" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E136" t="s">
         <v>25</v>
@@ -9618,10 +9919,10 @@
     </row>
     <row r="137" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B137" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C137" t="s">
         <v>251</v>
@@ -9656,10 +9957,10 @@
     </row>
     <row r="138" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B138" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C138" t="s">
         <v>251</v>
@@ -9694,10 +9995,10 @@
     </row>
     <row r="139" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B139" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C139" t="s">
         <v>251</v>
@@ -9732,10 +10033,10 @@
     </row>
     <row r="140" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B140" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C140" t="s">
         <v>251</v>
@@ -9770,10 +10071,10 @@
     </row>
     <row r="141" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B141" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C141" t="s">
         <v>251</v>
@@ -9808,10 +10109,10 @@
     </row>
     <row r="142" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B142" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C142" t="s">
         <v>251</v>
@@ -9846,10 +10147,10 @@
     </row>
     <row r="143" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B143" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C143" t="s">
         <v>251</v>
@@ -9884,10 +10185,10 @@
     </row>
     <row r="144" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B144" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C144" t="s">
         <v>251</v>
@@ -9922,10 +10223,10 @@
     </row>
     <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B145" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C145" t="s">
         <v>251</v>
@@ -9960,10 +10261,10 @@
     </row>
     <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B146" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C146" t="s">
         <v>251</v>
@@ -9998,10 +10299,10 @@
     </row>
     <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B147" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C147" t="s">
         <v>251</v>
@@ -10036,10 +10337,10 @@
     </row>
     <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B148" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C148" t="s">
         <v>251</v>
@@ -10074,10 +10375,10 @@
     </row>
     <row r="149" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B149" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C149" t="s">
         <v>251</v>
@@ -10112,10 +10413,10 @@
     </row>
     <row r="150" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B150" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C150" t="s">
         <v>251</v>
@@ -10150,10 +10451,10 @@
     </row>
     <row r="151" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B151" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C151" t="s">
         <v>251</v>
@@ -10188,10 +10489,10 @@
     </row>
     <row r="152" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B152" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C152" t="s">
         <v>251</v>
@@ -10226,10 +10527,10 @@
     </row>
     <row r="153" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B153" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C153" t="s">
         <v>251</v>
@@ -10264,10 +10565,10 @@
     </row>
     <row r="154" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B154" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C154" t="s">
         <v>251</v>
@@ -10302,10 +10603,10 @@
     </row>
     <row r="155" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B155" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C155" t="s">
         <v>251</v>
@@ -10340,10 +10641,10 @@
     </row>
     <row r="156" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B156" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C156" t="s">
         <v>251</v>
@@ -10378,10 +10679,10 @@
     </row>
     <row r="157" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B157" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C157" t="s">
         <v>251</v>
@@ -10416,10 +10717,10 @@
     </row>
     <row r="158" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B158" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C158" t="s">
         <v>251</v>
@@ -10454,10 +10755,10 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B159" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C159" t="s">
         <v>251</v>
@@ -10492,10 +10793,10 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B160" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C160" t="s">
         <v>251</v>
@@ -10530,10 +10831,10 @@
     </row>
     <row r="161" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B161" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C161" t="s">
         <v>251</v>
@@ -10568,10 +10869,10 @@
     </row>
     <row r="162" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B162" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C162" t="s">
         <v>251</v>
@@ -10606,10 +10907,10 @@
     </row>
     <row r="163" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B163" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C163" t="s">
         <v>251</v>
@@ -10644,10 +10945,10 @@
     </row>
     <row r="164" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B164" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C164" t="s">
         <v>251</v>
@@ -10682,10 +10983,10 @@
     </row>
     <row r="165" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B165" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C165" t="s">
         <v>251</v>
@@ -10720,10 +11021,10 @@
     </row>
     <row r="166" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B166" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C166" t="s">
         <v>251</v>
@@ -10758,10 +11059,10 @@
     </row>
     <row r="167" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B167" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C167" t="s">
         <v>251</v>
@@ -10796,10 +11097,10 @@
     </row>
     <row r="168" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B168" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C168" t="s">
         <v>251</v>
@@ -10834,10 +11135,10 @@
     </row>
     <row r="169" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B169" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C169" t="s">
         <v>251</v>
@@ -10872,10 +11173,10 @@
     </row>
     <row r="170" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B170" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C170" t="s">
         <v>251</v>
@@ -10910,10 +11211,10 @@
     </row>
     <row r="171" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B171" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C171" t="s">
         <v>251</v>
@@ -10948,10 +11249,10 @@
     </row>
     <row r="172" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B172" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C172" t="s">
         <v>251</v>
@@ -10986,16 +11287,16 @@
     </row>
     <row r="173" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B173" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C173" t="s">
         <v>251</v>
       </c>
       <c r="D173" t="s">
-        <v>329</v>
+        <v>252</v>
       </c>
       <c r="E173" t="s">
         <v>25</v>
@@ -11024,16 +11325,16 @@
     </row>
     <row r="174" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B174" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C174" t="s">
         <v>251</v>
       </c>
       <c r="D174" t="s">
-        <v>329</v>
+        <v>252</v>
       </c>
       <c r="E174" t="s">
         <v>25</v>
@@ -11062,10 +11363,10 @@
     </row>
     <row r="175" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B175" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C175" t="s">
         <v>251</v>
@@ -11100,10 +11401,10 @@
     </row>
     <row r="176" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B176" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C176" t="s">
         <v>251</v>
@@ -11138,10 +11439,10 @@
     </row>
     <row r="177" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B177" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C177" t="s">
         <v>251</v>
@@ -11176,10 +11477,10 @@
     </row>
     <row r="178" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B178" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C178" t="s">
         <v>251</v>
@@ -11214,10 +11515,10 @@
     </row>
     <row r="179" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B179" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C179" t="s">
         <v>251</v>
@@ -11252,10 +11553,10 @@
     </row>
     <row r="180" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B180" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C180" t="s">
         <v>251</v>
@@ -11290,10 +11591,10 @@
     </row>
     <row r="181" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B181" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C181" t="s">
         <v>251</v>
@@ -11328,10 +11629,10 @@
     </row>
     <row r="182" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B182" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C182" t="s">
         <v>251</v>
@@ -11366,16 +11667,16 @@
     </row>
     <row r="183" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B183" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C183" t="s">
         <v>251</v>
       </c>
       <c r="D183" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="E183" t="s">
         <v>25</v>
@@ -11404,16 +11705,16 @@
     </row>
     <row r="184" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B184" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C184" t="s">
         <v>251</v>
       </c>
       <c r="D184" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="E184" t="s">
         <v>25</v>
@@ -11442,10 +11743,10 @@
     </row>
     <row r="185" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B185" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C185" t="s">
         <v>251</v>
@@ -11480,16 +11781,16 @@
     </row>
     <row r="186" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B186" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C186" t="s">
         <v>251</v>
       </c>
       <c r="D186" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="E186" t="s">
         <v>25</v>
@@ -11518,16 +11819,16 @@
     </row>
     <row r="187" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B187" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C187" t="s">
         <v>251</v>
       </c>
       <c r="D187" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="E187" t="s">
         <v>25</v>
@@ -11556,10 +11857,10 @@
     </row>
     <row r="188" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B188" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C188" t="s">
         <v>251</v>
@@ -11594,10 +11895,10 @@
     </row>
     <row r="189" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B189" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C189" t="s">
         <v>251</v>
@@ -11632,10 +11933,10 @@
     </row>
     <row r="190" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B190" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C190" t="s">
         <v>251</v>
@@ -11670,10 +11971,10 @@
     </row>
     <row r="191" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B191" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C191" t="s">
         <v>251</v>
@@ -11708,10 +12009,10 @@
     </row>
     <row r="192" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B192" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C192" t="s">
         <v>251</v>
@@ -11746,16 +12047,16 @@
     </row>
     <row r="193" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B193" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C193" t="s">
         <v>251</v>
       </c>
       <c r="D193" t="s">
-        <v>237</v>
+        <v>357</v>
       </c>
       <c r="E193" t="s">
         <v>25</v>
@@ -11784,16 +12085,16 @@
     </row>
     <row r="194" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B194" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C194" t="s">
         <v>251</v>
       </c>
       <c r="D194" t="s">
-        <v>237</v>
+        <v>357</v>
       </c>
       <c r="E194" t="s">
         <v>25</v>
@@ -11822,10 +12123,10 @@
     </row>
     <row r="195" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B195" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C195" t="s">
         <v>251</v>
@@ -11860,10 +12161,10 @@
     </row>
     <row r="196" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B196" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C196" t="s">
         <v>251</v>
@@ -11898,10 +12199,10 @@
     </row>
     <row r="197" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B197" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C197" t="s">
         <v>251</v>
@@ -11936,10 +12237,10 @@
     </row>
     <row r="198" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B198" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C198" t="s">
         <v>251</v>
@@ -11974,10 +12275,10 @@
     </row>
     <row r="199" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B199" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C199" t="s">
         <v>251</v>
@@ -12012,10 +12313,10 @@
     </row>
     <row r="200" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B200" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C200" t="s">
         <v>251</v>
@@ -12050,10 +12351,10 @@
     </row>
     <row r="201" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B201" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C201" t="s">
         <v>251</v>
@@ -12088,10 +12389,10 @@
     </row>
     <row r="202" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B202" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C202" t="s">
         <v>251</v>
@@ -12126,10 +12427,10 @@
     </row>
     <row r="203" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B203" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C203" t="s">
         <v>251</v>
@@ -12164,7 +12465,7 @@
     </row>
     <row r="204" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B204" t="s">
         <v>388</v>
@@ -12202,7 +12503,7 @@
     </row>
     <row r="205" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B205" t="s">
         <v>388</v>
@@ -12240,7 +12541,7 @@
     </row>
     <row r="206" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B206" t="s">
         <v>388</v>
@@ -12278,10 +12579,10 @@
     </row>
     <row r="207" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B207" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C207" t="s">
         <v>251</v>
@@ -12316,10 +12617,10 @@
     </row>
     <row r="208" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B208" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C208" t="s">
         <v>251</v>
@@ -12354,10 +12655,10 @@
     </row>
     <row r="209" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B209" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C209" t="s">
         <v>251</v>
@@ -12392,10 +12693,10 @@
     </row>
     <row r="210" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B210" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C210" t="s">
         <v>251</v>
@@ -12430,10 +12731,10 @@
     </row>
     <row r="211" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B211" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C211" t="s">
         <v>251</v>
@@ -12468,10 +12769,10 @@
     </row>
     <row r="212" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B212" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C212" t="s">
         <v>251</v>
@@ -12506,10 +12807,10 @@
     </row>
     <row r="213" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B213" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C213" t="s">
         <v>251</v>
@@ -12544,10 +12845,10 @@
     </row>
     <row r="214" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B214" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C214" t="s">
         <v>251</v>
@@ -12582,10 +12883,10 @@
     </row>
     <row r="215" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B215" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C215" t="s">
         <v>251</v>
@@ -12620,10 +12921,10 @@
     </row>
     <row r="216" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B216" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C216" t="s">
         <v>251</v>
@@ -12658,10 +12959,10 @@
     </row>
     <row r="217" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B217" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C217" t="s">
         <v>251</v>
@@ -12696,10 +12997,10 @@
     </row>
     <row r="218" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B218" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C218" t="s">
         <v>251</v>
@@ -12734,16 +13035,16 @@
     </row>
     <row r="219" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B219" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C219" t="s">
         <v>251</v>
       </c>
       <c r="D219" t="s">
-        <v>419</v>
+        <v>237</v>
       </c>
       <c r="E219" t="s">
         <v>25</v>
@@ -12772,16 +13073,16 @@
     </row>
     <row r="220" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B220" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C220" t="s">
         <v>251</v>
       </c>
       <c r="D220" t="s">
-        <v>419</v>
+        <v>237</v>
       </c>
       <c r="E220" t="s">
         <v>25</v>
@@ -12810,10 +13111,10 @@
     </row>
     <row r="221" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B221" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C221" t="s">
         <v>251</v>
@@ -12848,10 +13149,10 @@
     </row>
     <row r="222" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B222" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C222" t="s">
         <v>251</v>
@@ -12886,10 +13187,10 @@
     </row>
     <row r="223" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B223" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C223" t="s">
         <v>251</v>
@@ -12924,10 +13225,10 @@
     </row>
     <row r="224" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B224" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C224" t="s">
         <v>251</v>
@@ -12962,10 +13263,10 @@
     </row>
     <row r="225" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B225" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C225" t="s">
         <v>251</v>
@@ -13000,10 +13301,10 @@
     </row>
     <row r="226" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B226" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C226" t="s">
         <v>251</v>
@@ -13038,10 +13339,10 @@
     </row>
     <row r="227" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B227" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C227" t="s">
         <v>251</v>
@@ -13076,10 +13377,10 @@
     </row>
     <row r="228" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B228" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C228" t="s">
         <v>251</v>
@@ -13114,10 +13415,10 @@
     </row>
     <row r="229" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B229" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C229" t="s">
         <v>251</v>
@@ -13152,10 +13453,10 @@
     </row>
     <row r="230" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B230" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C230" t="s">
         <v>251</v>
@@ -13190,10 +13491,10 @@
     </row>
     <row r="231" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B231" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C231" t="s">
         <v>251</v>
@@ -13228,10 +13529,10 @@
     </row>
     <row r="232" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B232" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C232" t="s">
         <v>251</v>
@@ -13266,10 +13567,10 @@
     </row>
     <row r="233" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B233" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C233" t="s">
         <v>251</v>
@@ -13304,10 +13605,10 @@
     </row>
     <row r="234" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B234" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C234" t="s">
         <v>251</v>
@@ -13342,10 +13643,10 @@
     </row>
     <row r="235" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B235" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C235" t="s">
         <v>251</v>
@@ -13380,10 +13681,10 @@
     </row>
     <row r="236" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B236" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C236" t="s">
         <v>251</v>
@@ -13418,10 +13719,10 @@
     </row>
     <row r="237" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B237" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C237" t="s">
         <v>251</v>
@@ -13456,10 +13757,10 @@
     </row>
     <row r="238" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B238" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C238" t="s">
         <v>251</v>
@@ -13494,10 +13795,10 @@
     </row>
     <row r="239" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B239" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C239" t="s">
         <v>251</v>
@@ -13532,10 +13833,10 @@
     </row>
     <row r="240" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B240" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C240" t="s">
         <v>251</v>
@@ -13570,10 +13871,10 @@
     </row>
     <row r="241" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B241" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C241" t="s">
         <v>251</v>
@@ -13608,10 +13909,10 @@
     </row>
     <row r="242" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B242" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C242" t="s">
         <v>251</v>
@@ -13646,10 +13947,10 @@
     </row>
     <row r="243" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B243" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C243" t="s">
         <v>251</v>
@@ -13684,10 +13985,10 @@
     </row>
     <row r="244" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B244" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C244" t="s">
         <v>251</v>
@@ -13722,16 +14023,16 @@
     </row>
     <row r="245" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B245" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C245" t="s">
-        <v>472</v>
+        <v>251</v>
       </c>
       <c r="D245" t="s">
-        <v>473</v>
+        <v>419</v>
       </c>
       <c r="E245" t="s">
         <v>25</v>
@@ -13760,16 +14061,16 @@
     </row>
     <row r="246" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B246" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C246" t="s">
-        <v>472</v>
+        <v>251</v>
       </c>
       <c r="D246" t="s">
-        <v>473</v>
+        <v>419</v>
       </c>
       <c r="E246" t="s">
         <v>25</v>
@@ -13798,10 +14099,10 @@
     </row>
     <row r="247" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B247" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C247" t="s">
         <v>472</v>
@@ -13836,10 +14137,10 @@
     </row>
     <row r="248" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B248" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C248" t="s">
         <v>472</v>
@@ -13874,10 +14175,10 @@
     </row>
     <row r="249" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B249" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C249" t="s">
         <v>472</v>
@@ -13912,10 +14213,10 @@
     </row>
     <row r="250" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B250" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C250" t="s">
         <v>472</v>
@@ -13950,10 +14251,10 @@
     </row>
     <row r="251" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B251" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C251" t="s">
         <v>472</v>
@@ -13988,10 +14289,10 @@
     </row>
     <row r="252" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B252" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C252" t="s">
         <v>472</v>
@@ -14026,10 +14327,10 @@
     </row>
     <row r="253" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B253" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C253" t="s">
         <v>472</v>
@@ -14064,10 +14365,10 @@
     </row>
     <row r="254" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B254" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C254" t="s">
         <v>472</v>
@@ -14102,10 +14403,10 @@
     </row>
     <row r="255" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B255" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C255" t="s">
         <v>472</v>
@@ -14140,10 +14441,10 @@
     </row>
     <row r="256" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B256" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C256" t="s">
         <v>472</v>
@@ -14178,10 +14479,10 @@
     </row>
     <row r="257" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B257" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C257" t="s">
         <v>472</v>
@@ -14216,10 +14517,10 @@
     </row>
     <row r="258" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B258" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C258" t="s">
         <v>472</v>
@@ -14254,10 +14555,10 @@
     </row>
     <row r="259" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B259" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C259" t="s">
         <v>472</v>
@@ -14292,10 +14593,10 @@
     </row>
     <row r="260" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B260" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C260" t="s">
         <v>472</v>
@@ -14330,10 +14631,10 @@
     </row>
     <row r="261" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B261" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C261" t="s">
         <v>472</v>
@@ -14368,10 +14669,10 @@
     </row>
     <row r="262" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B262" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C262" t="s">
         <v>472</v>
@@ -14406,10 +14707,10 @@
     </row>
     <row r="263" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B263" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C263" t="s">
         <v>472</v>
@@ -14444,10 +14745,10 @@
     </row>
     <row r="264" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B264" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C264" t="s">
         <v>472</v>
@@ -14482,10 +14783,10 @@
     </row>
     <row r="265" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B265" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C265" t="s">
         <v>472</v>
@@ -14520,10 +14821,10 @@
     </row>
     <row r="266" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B266" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C266" t="s">
         <v>472</v>
@@ -14558,10 +14859,10 @@
     </row>
     <row r="267" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B267" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C267" t="s">
         <v>472</v>
@@ -14596,10 +14897,10 @@
     </row>
     <row r="268" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B268" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C268" t="s">
         <v>472</v>
@@ -14634,10 +14935,10 @@
     </row>
     <row r="269" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B269" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C269" t="s">
         <v>472</v>
@@ -14672,10 +14973,10 @@
     </row>
     <row r="270" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B270" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C270" t="s">
         <v>472</v>
@@ -14710,10 +15011,10 @@
     </row>
     <row r="271" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B271" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C271" t="s">
         <v>472</v>
@@ -14748,10 +15049,10 @@
     </row>
     <row r="272" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B272" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C272" t="s">
         <v>472</v>
@@ -14786,10 +15087,10 @@
     </row>
     <row r="273" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B273" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C273" t="s">
         <v>472</v>
@@ -14824,10 +15125,10 @@
     </row>
     <row r="274" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B274" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C274" t="s">
         <v>472</v>
@@ -14862,10 +15163,10 @@
     </row>
     <row r="275" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B275" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C275" t="s">
         <v>472</v>
@@ -14900,10 +15201,10 @@
     </row>
     <row r="276" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B276" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C276" t="s">
         <v>472</v>
@@ -14938,10 +15239,10 @@
     </row>
     <row r="277" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B277" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C277" t="s">
         <v>472</v>
@@ -14976,10 +15277,10 @@
     </row>
     <row r="278" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B278" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C278" t="s">
         <v>472</v>
@@ -15014,10 +15315,10 @@
     </row>
     <row r="279" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B279" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C279" t="s">
         <v>472</v>
@@ -15052,10 +15353,10 @@
     </row>
     <row r="280" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B280" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C280" t="s">
         <v>472</v>
@@ -15090,10 +15391,10 @@
     </row>
     <row r="281" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B281" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C281" t="s">
         <v>472</v>
@@ -15128,10 +15429,10 @@
     </row>
     <row r="282" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B282" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C282" t="s">
         <v>472</v>
@@ -15166,10 +15467,10 @@
     </row>
     <row r="283" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B283" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C283" t="s">
         <v>472</v>
@@ -15204,10 +15505,10 @@
     </row>
     <row r="284" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B284" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C284" t="s">
         <v>472</v>
@@ -15242,10 +15543,10 @@
     </row>
     <row r="285" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B285" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C285" t="s">
         <v>472</v>
@@ -15280,10 +15581,10 @@
     </row>
     <row r="286" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B286" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C286" t="s">
         <v>472</v>
@@ -15318,10 +15619,10 @@
     </row>
     <row r="287" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B287" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C287" t="s">
         <v>472</v>
@@ -15356,10 +15657,10 @@
     </row>
     <row r="288" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B288" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C288" t="s">
         <v>472</v>
@@ -15394,10 +15695,10 @@
     </row>
     <row r="289" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B289" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C289" t="s">
         <v>472</v>
@@ -15432,10 +15733,10 @@
     </row>
     <row r="290" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B290" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C290" t="s">
         <v>472</v>
@@ -15470,10 +15771,10 @@
     </row>
     <row r="291" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B291" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C291" t="s">
         <v>472</v>
@@ -15508,16 +15809,16 @@
     </row>
     <row r="292" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B292" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C292" t="s">
         <v>472</v>
       </c>
       <c r="D292" t="s">
-        <v>568</v>
+        <v>473</v>
       </c>
       <c r="E292" t="s">
         <v>25</v>
@@ -15546,16 +15847,16 @@
     </row>
     <row r="293" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B293" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="C293" t="s">
         <v>472</v>
       </c>
       <c r="D293" t="s">
-        <v>568</v>
+        <v>473</v>
       </c>
       <c r="E293" t="s">
         <v>25</v>
@@ -15584,10 +15885,10 @@
     </row>
     <row r="294" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B294" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="C294" t="s">
         <v>472</v>
@@ -15622,10 +15923,10 @@
     </row>
     <row r="295" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B295" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C295" t="s">
         <v>472</v>
@@ -15660,10 +15961,10 @@
     </row>
     <row r="296" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B296" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C296" t="s">
         <v>472</v>
@@ -15698,10 +15999,10 @@
     </row>
     <row r="297" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B297" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C297" t="s">
         <v>472</v>
@@ -15736,10 +16037,10 @@
     </row>
     <row r="298" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B298" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C298" t="s">
         <v>472</v>
@@ -15774,10 +16075,10 @@
     </row>
     <row r="299" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B299" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C299" t="s">
         <v>472</v>
@@ -15812,10 +16113,10 @@
     </row>
     <row r="300" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B300" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C300" t="s">
         <v>472</v>
@@ -15850,10 +16151,10 @@
     </row>
     <row r="301" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B301" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C301" t="s">
         <v>472</v>
@@ -15888,10 +16189,10 @@
     </row>
     <row r="302" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B302" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C302" t="s">
         <v>472</v>
@@ -15926,10 +16227,10 @@
     </row>
     <row r="303" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B303" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C303" t="s">
         <v>472</v>
@@ -15964,10 +16265,10 @@
     </row>
     <row r="304" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B304" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C304" t="s">
         <v>472</v>
@@ -16002,10 +16303,10 @@
     </row>
     <row r="305" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B305" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C305" t="s">
         <v>472</v>
@@ -16040,10 +16341,10 @@
     </row>
     <row r="306" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B306" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C306" t="s">
         <v>472</v>
@@ -16078,10 +16379,10 @@
     </row>
     <row r="307" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B307" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C307" t="s">
         <v>472</v>
@@ -16116,10 +16417,10 @@
     </row>
     <row r="308" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B308" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C308" t="s">
         <v>472</v>
@@ -16154,10 +16455,10 @@
     </row>
     <row r="309" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B309" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C309" t="s">
         <v>472</v>
@@ -16192,10 +16493,10 @@
     </row>
     <row r="310" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B310" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C310" t="s">
         <v>472</v>
@@ -16230,10 +16531,10 @@
     </row>
     <row r="311" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B311" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C311" t="s">
         <v>472</v>
@@ -16268,10 +16569,10 @@
     </row>
     <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B312" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C312" t="s">
         <v>472</v>
@@ -16306,10 +16607,10 @@
     </row>
     <row r="313" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B313" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C313" t="s">
         <v>472</v>
@@ -16344,10 +16645,10 @@
     </row>
     <row r="314" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B314" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C314" t="s">
         <v>472</v>
@@ -16382,10 +16683,10 @@
     </row>
     <row r="315" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B315" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C315" t="s">
         <v>472</v>
@@ -16420,10 +16721,10 @@
     </row>
     <row r="316" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B316" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C316" t="s">
         <v>472</v>
@@ -16458,10 +16759,10 @@
     </row>
     <row r="317" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B317" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C317" t="s">
         <v>472</v>
@@ -16496,10 +16797,10 @@
     </row>
     <row r="318" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B318" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C318" t="s">
         <v>472</v>
@@ -16534,10 +16835,10 @@
     </row>
     <row r="319" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B319" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C319" t="s">
         <v>472</v>
@@ -16572,10 +16873,10 @@
     </row>
     <row r="320" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B320" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C320" t="s">
         <v>472</v>
@@ -16610,10 +16911,10 @@
     </row>
     <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B321" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C321" t="s">
         <v>472</v>
@@ -16648,10 +16949,10 @@
     </row>
     <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B322" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C322" t="s">
         <v>472</v>
@@ -16686,10 +16987,10 @@
     </row>
     <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B323" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C323" t="s">
         <v>472</v>
@@ -16724,10 +17025,10 @@
     </row>
     <row r="324" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B324" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C324" t="s">
         <v>472</v>
@@ -16762,10 +17063,10 @@
     </row>
     <row r="325" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B325" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C325" t="s">
         <v>472</v>
@@ -16800,16 +17101,16 @@
     </row>
     <row r="326" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B326" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C326" t="s">
-        <v>637</v>
+        <v>472</v>
       </c>
       <c r="D326" t="s">
-        <v>25</v>
+        <v>568</v>
       </c>
       <c r="E326" t="s">
         <v>25</v>
@@ -16838,16 +17139,16 @@
     </row>
     <row r="327" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B327" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C327" t="s">
-        <v>637</v>
+        <v>472</v>
       </c>
       <c r="D327" t="s">
-        <v>25</v>
+        <v>568</v>
       </c>
       <c r="E327" t="s">
         <v>25</v>
@@ -16876,10 +17177,10 @@
     </row>
     <row r="328" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="B328" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="C328" t="s">
         <v>637</v>
@@ -16914,10 +17215,10 @@
     </row>
     <row r="329" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B329" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C329" t="s">
         <v>637</v>
@@ -16952,10 +17253,10 @@
     </row>
     <row r="330" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B330" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C330" t="s">
         <v>637</v>
@@ -16990,10 +17291,10 @@
     </row>
     <row r="331" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B331" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C331" t="s">
         <v>637</v>
@@ -17028,10 +17329,10 @@
     </row>
     <row r="332" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B332" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C332" t="s">
         <v>637</v>
@@ -17066,10 +17367,10 @@
     </row>
     <row r="333" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B333" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C333" t="s">
         <v>637</v>
@@ -17104,16 +17405,16 @@
     </row>
     <row r="334" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B334" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C334" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="D334" t="s">
-        <v>655</v>
+        <v>25</v>
       </c>
       <c r="E334" t="s">
         <v>25</v>
@@ -17142,16 +17443,16 @@
     </row>
     <row r="335" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="B335" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="C335" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="D335" t="s">
-        <v>655</v>
+        <v>25</v>
       </c>
       <c r="E335" t="s">
         <v>25</v>
@@ -17180,10 +17481,10 @@
     </row>
     <row r="336" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="B336" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C336" t="s">
         <v>654</v>
@@ -17218,10 +17519,10 @@
     </row>
     <row r="337" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B337" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C337" t="s">
         <v>654</v>
@@ -17256,16 +17557,16 @@
     </row>
     <row r="338" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B338" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C338" t="s">
         <v>654</v>
       </c>
       <c r="D338" t="s">
-        <v>148</v>
+        <v>655</v>
       </c>
       <c r="E338" t="s">
         <v>25</v>
@@ -17294,16 +17595,16 @@
     </row>
     <row r="339" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B339" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C339" t="s">
         <v>654</v>
       </c>
       <c r="D339" t="s">
-        <v>148</v>
+        <v>655</v>
       </c>
       <c r="E339" t="s">
         <v>25</v>
@@ -17332,10 +17633,10 @@
     </row>
     <row r="340" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B340" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C340" t="s">
         <v>654</v>
@@ -17370,10 +17671,10 @@
     </row>
     <row r="341" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B341" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C341" t="s">
         <v>654</v>
@@ -17408,16 +17709,16 @@
     </row>
     <row r="342" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B342" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C342" t="s">
         <v>654</v>
       </c>
       <c r="D342" t="s">
-        <v>672</v>
+        <v>148</v>
       </c>
       <c r="E342" t="s">
         <v>25</v>
@@ -17446,16 +17747,16 @@
     </row>
     <row r="343" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="B343" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="C343" t="s">
         <v>654</v>
       </c>
       <c r="D343" t="s">
-        <v>672</v>
+        <v>148</v>
       </c>
       <c r="E343" t="s">
         <v>25</v>
@@ -17484,10 +17785,10 @@
     </row>
     <row r="344" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B344" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="C344" t="s">
         <v>654</v>
@@ -17522,10 +17823,10 @@
     </row>
     <row r="345" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B345" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C345" t="s">
         <v>654</v>
@@ -17560,10 +17861,10 @@
     </row>
     <row r="346" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B346" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C346" t="s">
         <v>654</v>
@@ -17598,16 +17899,16 @@
     </row>
     <row r="347" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B347" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C347" t="s">
         <v>654</v>
       </c>
       <c r="D347" t="s">
-        <v>137</v>
+        <v>672</v>
       </c>
       <c r="E347" t="s">
         <v>25</v>
@@ -17636,16 +17937,16 @@
     </row>
     <row r="348" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B348" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C348" t="s">
         <v>654</v>
       </c>
       <c r="D348" t="s">
-        <v>137</v>
+        <v>672</v>
       </c>
       <c r="E348" t="s">
         <v>25</v>
@@ -17674,16 +17975,16 @@
     </row>
     <row r="349" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B349" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C349" t="s">
         <v>654</v>
       </c>
       <c r="D349" t="s">
-        <v>687</v>
+        <v>137</v>
       </c>
       <c r="E349" t="s">
         <v>25</v>
@@ -17712,16 +18013,16 @@
     </row>
     <row r="350" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="B350" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C350" t="s">
         <v>654</v>
       </c>
       <c r="D350" t="s">
-        <v>687</v>
+        <v>137</v>
       </c>
       <c r="E350" t="s">
         <v>25</v>
@@ -17750,10 +18051,10 @@
     </row>
     <row r="351" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="B351" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C351" t="s">
         <v>654</v>
@@ -17788,10 +18089,10 @@
     </row>
     <row r="352" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B352" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C352" t="s">
         <v>654</v>
@@ -17826,16 +18127,16 @@
     </row>
     <row r="353" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B353" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C353" t="s">
-        <v>695</v>
+        <v>654</v>
       </c>
       <c r="D353" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="E353" t="s">
         <v>25</v>
@@ -17864,16 +18165,16 @@
     </row>
     <row r="354" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="B354" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C354" t="s">
-        <v>695</v>
+        <v>654</v>
       </c>
       <c r="D354" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="E354" t="s">
         <v>25</v>
@@ -17902,10 +18203,10 @@
     </row>
     <row r="355" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="B355" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="C355" t="s">
         <v>695</v>
@@ -17940,10 +18241,10 @@
     </row>
     <row r="356" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B356" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C356" t="s">
         <v>695</v>
@@ -17978,10 +18279,10 @@
     </row>
     <row r="357" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B357" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="C357" t="s">
         <v>695</v>
@@ -18016,10 +18317,10 @@
     </row>
     <row r="358" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B358" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C358" t="s">
         <v>695</v>
@@ -18054,16 +18355,16 @@
     </row>
     <row r="359" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B359" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C359" t="s">
         <v>695</v>
       </c>
       <c r="D359" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="E359" t="s">
         <v>25</v>
@@ -18092,16 +18393,16 @@
     </row>
     <row r="360" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B360" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="C360" t="s">
         <v>695</v>
       </c>
       <c r="D360" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="E360" t="s">
         <v>25</v>
@@ -18130,10 +18431,10 @@
     </row>
     <row r="361" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="B361" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="C361" t="s">
         <v>695</v>
@@ -18168,16 +18469,16 @@
     </row>
     <row r="362" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B362" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C362" t="s">
         <v>695</v>
       </c>
       <c r="D362" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="E362" t="s">
         <v>25</v>
@@ -18206,16 +18507,16 @@
     </row>
     <row r="363" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B363" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="C363" t="s">
         <v>695</v>
       </c>
       <c r="D363" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="E363" t="s">
         <v>25</v>
@@ -18244,10 +18545,10 @@
     </row>
     <row r="364" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="B364" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="C364" t="s">
         <v>695</v>
@@ -18282,10 +18583,10 @@
     </row>
     <row r="365" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B365" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="C365" t="s">
         <v>695</v>
@@ -18320,16 +18621,16 @@
     </row>
     <row r="366" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B366" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="C366" t="s">
         <v>695</v>
       </c>
       <c r="D366" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="E366" t="s">
         <v>25</v>
@@ -18358,16 +18659,16 @@
     </row>
     <row r="367" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="B367" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C367" t="s">
         <v>695</v>
       </c>
       <c r="D367" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="E367" t="s">
         <v>25</v>
@@ -18396,10 +18697,10 @@
     </row>
     <row r="368" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B368" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C368" t="s">
         <v>695</v>
@@ -18434,16 +18735,16 @@
     </row>
     <row r="369" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B369" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C369" t="s">
         <v>695</v>
       </c>
       <c r="D369" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E369" t="s">
         <v>25</v>
@@ -18472,16 +18773,16 @@
     </row>
     <row r="370" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B370" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C370" t="s">
         <v>695</v>
       </c>
       <c r="D370" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E370" t="s">
         <v>25</v>
@@ -18510,10 +18811,10 @@
     </row>
     <row r="371" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="B371" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="C371" t="s">
         <v>695</v>
@@ -18548,10 +18849,10 @@
     </row>
     <row r="372" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B372" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="C372" t="s">
         <v>695</v>
@@ -18586,10 +18887,10 @@
     </row>
     <row r="373" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B373" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C373" t="s">
         <v>695</v>
@@ -18624,16 +18925,16 @@
     </row>
     <row r="374" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B374" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C374" t="s">
         <v>695</v>
       </c>
       <c r="D374" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="E374" t="s">
         <v>25</v>
@@ -18662,16 +18963,16 @@
     </row>
     <row r="375" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="B375" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C375" t="s">
         <v>695</v>
       </c>
       <c r="D375" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="E375" t="s">
         <v>25</v>
@@ -18700,10 +19001,10 @@
     </row>
     <row r="376" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="B376" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="C376" t="s">
         <v>695</v>
@@ -18738,10 +19039,10 @@
     </row>
     <row r="377" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B377" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="C377" t="s">
         <v>695</v>
@@ -18776,10 +19077,10 @@
     </row>
     <row r="378" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B378" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C378" t="s">
         <v>695</v>
@@ -18814,10 +19115,10 @@
     </row>
     <row r="379" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B379" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C379" t="s">
         <v>695</v>
@@ -18852,16 +19153,16 @@
     </row>
     <row r="380" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B380" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="C380" t="s">
         <v>695</v>
       </c>
       <c r="D380" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="E380" t="s">
         <v>25</v>
@@ -18890,16 +19191,16 @@
     </row>
     <row r="381" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="B381" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C381" t="s">
         <v>695</v>
       </c>
       <c r="D381" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="E381" t="s">
         <v>25</v>
@@ -18928,16 +19229,16 @@
     </row>
     <row r="382" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="B382" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="C382" t="s">
-        <v>760</v>
+        <v>695</v>
       </c>
       <c r="D382" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="E382" t="s">
         <v>25</v>
@@ -18966,16 +19267,16 @@
     </row>
     <row r="383" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="B383" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="C383" t="s">
-        <v>760</v>
+        <v>695</v>
       </c>
       <c r="D383" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="E383" t="s">
         <v>25</v>
@@ -19004,10 +19305,10 @@
     </row>
     <row r="384" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="B384" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="C384" t="s">
         <v>760</v>
@@ -19042,10 +19343,10 @@
     </row>
     <row r="385" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B385" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C385" t="s">
         <v>760</v>
@@ -19080,10 +19381,10 @@
     </row>
     <row r="386" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="B386" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="C386" t="s">
         <v>760</v>
@@ -19118,10 +19419,10 @@
     </row>
     <row r="387" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B387" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C387" t="s">
         <v>760</v>
@@ -19156,10 +19457,10 @@
     </row>
     <row r="388" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B388" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C388" t="s">
         <v>760</v>
@@ -19194,10 +19495,10 @@
     </row>
     <row r="389" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B389" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="C389" t="s">
         <v>760</v>
@@ -19232,10 +19533,10 @@
     </row>
     <row r="390" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B390" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C390" t="s">
         <v>760</v>
@@ -19270,10 +19571,10 @@
     </row>
     <row r="391" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B391" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C391" t="s">
         <v>760</v>
@@ -19308,10 +19609,10 @@
     </row>
     <row r="392" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B392" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="C392" t="s">
         <v>760</v>
@@ -19346,10 +19647,10 @@
     </row>
     <row r="393" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B393" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C393" t="s">
         <v>760</v>
@@ -19384,10 +19685,10 @@
     </row>
     <row r="394" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B394" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C394" t="s">
         <v>760</v>
@@ -19422,16 +19723,16 @@
     </row>
     <row r="395" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B395" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="C395" t="s">
         <v>760</v>
       </c>
       <c r="D395" t="s">
-        <v>788</v>
+        <v>761</v>
       </c>
       <c r="E395" t="s">
         <v>25</v>
@@ -19460,16 +19761,16 @@
     </row>
     <row r="396" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="B396" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C396" t="s">
         <v>760</v>
       </c>
       <c r="D396" t="s">
-        <v>788</v>
+        <v>761</v>
       </c>
       <c r="E396" t="s">
         <v>25</v>
@@ -19498,10 +19799,10 @@
     </row>
     <row r="397" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="B397" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="C397" t="s">
         <v>760</v>
@@ -19536,10 +19837,10 @@
     </row>
     <row r="398" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B398" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="C398" t="s">
         <v>760</v>
@@ -19574,10 +19875,10 @@
     </row>
     <row r="399" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B399" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="C399" t="s">
         <v>760</v>
@@ -19612,16 +19913,16 @@
     </row>
     <row r="400" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="B400" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="C400" t="s">
         <v>760</v>
       </c>
       <c r="D400" t="s">
-        <v>210</v>
+        <v>788</v>
       </c>
       <c r="E400" t="s">
         <v>25</v>
@@ -19650,16 +19951,16 @@
     </row>
     <row r="401" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B401" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="C401" t="s">
         <v>760</v>
       </c>
       <c r="D401" t="s">
-        <v>210</v>
+        <v>788</v>
       </c>
       <c r="E401" t="s">
         <v>25</v>
@@ -19688,10 +19989,10 @@
     </row>
     <row r="402" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B402" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="C402" t="s">
         <v>760</v>
@@ -19726,16 +20027,16 @@
     </row>
     <row r="403" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B403" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C403" t="s">
         <v>760</v>
       </c>
       <c r="D403" t="s">
-        <v>805</v>
+        <v>210</v>
       </c>
       <c r="E403" t="s">
         <v>25</v>
@@ -19764,16 +20065,16 @@
     </row>
     <row r="404" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="B404" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="C404" t="s">
         <v>760</v>
       </c>
       <c r="D404" t="s">
-        <v>805</v>
+        <v>210</v>
       </c>
       <c r="E404" t="s">
         <v>25</v>
@@ -19802,16 +20103,16 @@
     </row>
     <row r="405" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="B405" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C405" t="s">
         <v>760</v>
       </c>
       <c r="D405" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="E405" t="s">
         <v>25</v>
@@ -19840,16 +20141,16 @@
     </row>
     <row r="406" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="B406" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="C406" t="s">
         <v>760</v>
       </c>
       <c r="D406" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="E406" t="s">
         <v>25</v>
@@ -19878,10 +20179,10 @@
     </row>
     <row r="407" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="B407" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C407" t="s">
         <v>760</v>
@@ -19916,16 +20217,16 @@
     </row>
     <row r="408" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B408" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C408" t="s">
         <v>760</v>
       </c>
       <c r="D408" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="E408" t="s">
         <v>25</v>
@@ -19954,16 +20255,16 @@
     </row>
     <row r="409" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="B409" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C409" t="s">
         <v>760</v>
       </c>
       <c r="D409" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="E409" t="s">
         <v>25</v>
@@ -19992,10 +20293,10 @@
     </row>
     <row r="410" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="B410" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="C410" t="s">
         <v>760</v>
@@ -20030,10 +20331,10 @@
     </row>
     <row r="411" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B411" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="C411" t="s">
         <v>760</v>
@@ -20068,10 +20369,10 @@
     </row>
     <row r="412" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B412" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="C412" t="s">
         <v>760</v>
@@ -20106,10 +20407,10 @@
     </row>
     <row r="413" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="B413" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C413" t="s">
         <v>760</v>
@@ -20144,10 +20445,10 @@
     </row>
     <row r="414" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B414" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="C414" t="s">
         <v>760</v>
@@ -20182,10 +20483,10 @@
     </row>
     <row r="415" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B415" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C415" t="s">
         <v>760</v>
@@ -20220,10 +20521,10 @@
     </row>
     <row r="416" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B416" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="C416" t="s">
         <v>760</v>
@@ -20258,10 +20559,10 @@
     </row>
     <row r="417" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B417" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C417" t="s">
         <v>760</v>
@@ -20296,10 +20597,10 @@
     </row>
     <row r="418" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B418" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="C418" t="s">
         <v>760</v>
@@ -20334,10 +20635,10 @@
     </row>
     <row r="419" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B419" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C419" t="s">
         <v>760</v>
@@ -20372,16 +20673,16 @@
     </row>
     <row r="420" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B420" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="C420" t="s">
         <v>760</v>
       </c>
       <c r="D420" t="s">
-        <v>842</v>
+        <v>817</v>
       </c>
       <c r="E420" t="s">
         <v>25</v>
@@ -20410,16 +20711,16 @@
     </row>
     <row r="421" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B421" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="C421" t="s">
         <v>760</v>
       </c>
       <c r="D421" t="s">
-        <v>842</v>
+        <v>817</v>
       </c>
       <c r="E421" t="s">
         <v>25</v>
@@ -20448,10 +20749,10 @@
     </row>
     <row r="422" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="B422" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="C422" t="s">
         <v>760</v>
@@ -20486,10 +20787,10 @@
     </row>
     <row r="423" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B423" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="C423" t="s">
         <v>760</v>
@@ -20524,10 +20825,10 @@
     </row>
     <row r="424" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="B424" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="C424" t="s">
         <v>760</v>
@@ -20562,16 +20863,16 @@
     </row>
     <row r="425" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B425" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="C425" t="s">
         <v>760</v>
       </c>
       <c r="D425" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
       <c r="E425" t="s">
         <v>25</v>
@@ -20600,16 +20901,16 @@
     </row>
     <row r="426" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="B426" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="C426" t="s">
         <v>760</v>
       </c>
       <c r="D426" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
       <c r="E426" t="s">
         <v>25</v>
@@ -20638,16 +20939,16 @@
     </row>
     <row r="427" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="B427" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="C427" t="s">
-        <v>858</v>
+        <v>760</v>
       </c>
       <c r="D427" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="E427" t="s">
         <v>25</v>
@@ -20676,16 +20977,16 @@
     </row>
     <row r="428" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="B428" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="C428" t="s">
-        <v>858</v>
+        <v>760</v>
       </c>
       <c r="D428" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="E428" t="s">
         <v>25</v>
@@ -20714,10 +21015,10 @@
     </row>
     <row r="429" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="B429" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="C429" t="s">
         <v>858</v>
@@ -20752,10 +21053,10 @@
     </row>
     <row r="430" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B430" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="C430" t="s">
         <v>858</v>
@@ -20790,10 +21091,10 @@
     </row>
     <row r="431" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B431" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="C431" t="s">
         <v>858</v>
@@ -20828,10 +21129,10 @@
     </row>
     <row r="432" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="B432" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="C432" t="s">
         <v>858</v>
@@ -20866,16 +21167,16 @@
     </row>
     <row r="433" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="B433" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C433" t="s">
         <v>858</v>
       </c>
       <c r="D433" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="E433" t="s">
         <v>25</v>
@@ -20904,16 +21205,16 @@
     </row>
     <row r="434" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="B434" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C434" t="s">
         <v>858</v>
       </c>
       <c r="D434" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="E434" t="s">
         <v>25</v>
@@ -20942,10 +21243,10 @@
     </row>
     <row r="435" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="B435" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="C435" t="s">
         <v>858</v>
@@ -20980,10 +21281,10 @@
     </row>
     <row r="436" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="B436" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="C436" t="s">
         <v>858</v>
@@ -21018,10 +21319,10 @@
     </row>
     <row r="437" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B437" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C437" t="s">
         <v>858</v>
@@ -21056,16 +21357,16 @@
     </row>
     <row r="438" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="B438" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="C438" t="s">
         <v>858</v>
       </c>
       <c r="D438" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
       <c r="E438" t="s">
         <v>25</v>
@@ -21094,16 +21395,16 @@
     </row>
     <row r="439" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="B439" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="C439" t="s">
         <v>858</v>
       </c>
       <c r="D439" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
       <c r="E439" t="s">
         <v>25</v>
@@ -21132,10 +21433,10 @@
     </row>
     <row r="440" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="B440" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="C440" t="s">
         <v>858</v>
@@ -21170,16 +21471,16 @@
     </row>
     <row r="441" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B441" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="C441" t="s">
         <v>858</v>
       </c>
       <c r="D441" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="E441" t="s">
         <v>25</v>
@@ -21208,16 +21509,16 @@
     </row>
     <row r="442" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="B442" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="C442" t="s">
         <v>858</v>
       </c>
       <c r="D442" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="E442" t="s">
         <v>25</v>
@@ -21246,16 +21547,16 @@
     </row>
     <row r="443" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="B443" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="C443" t="s">
         <v>858</v>
       </c>
       <c r="D443" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="E443" t="s">
         <v>25</v>
@@ -21284,16 +21585,16 @@
     </row>
     <row r="444" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="B444" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="C444" t="s">
         <v>858</v>
       </c>
       <c r="D444" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="E444" t="s">
         <v>25</v>
@@ -21322,10 +21623,10 @@
     </row>
     <row r="445" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="B445" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="C445" t="s">
         <v>858</v>
@@ -21360,10 +21661,10 @@
     </row>
     <row r="446" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B446" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="C446" t="s">
         <v>858</v>
@@ -21398,16 +21699,16 @@
     </row>
     <row r="447" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B447" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="C447" t="s">
         <v>858</v>
       </c>
       <c r="D447" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="E447" t="s">
         <v>25</v>
@@ -21436,16 +21737,16 @@
     </row>
     <row r="448" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="B448" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="C448" t="s">
         <v>858</v>
       </c>
       <c r="D448" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="E448" t="s">
         <v>25</v>
@@ -21474,10 +21775,10 @@
     </row>
     <row r="449" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="B449" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="C449" t="s">
         <v>858</v>
@@ -21512,10 +21813,10 @@
     </row>
     <row r="450" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="B450" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="C450" t="s">
         <v>858</v>
@@ -21550,10 +21851,10 @@
     </row>
     <row r="451" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="B451" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="C451" t="s">
         <v>858</v>
@@ -21588,16 +21889,16 @@
     </row>
     <row r="452" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B452" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="C452" t="s">
-        <v>915</v>
+        <v>858</v>
       </c>
       <c r="D452" t="s">
-        <v>25</v>
+        <v>904</v>
       </c>
       <c r="E452" t="s">
         <v>25</v>
@@ -21626,16 +21927,16 @@
     </row>
     <row r="453" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="B453" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="C453" t="s">
-        <v>915</v>
+        <v>858</v>
       </c>
       <c r="D453" t="s">
-        <v>25</v>
+        <v>904</v>
       </c>
       <c r="E453" t="s">
         <v>25</v>
@@ -21664,10 +21965,10 @@
     </row>
     <row r="454" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="B454" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="C454" t="s">
         <v>915</v>
@@ -21702,10 +22003,10 @@
     </row>
     <row r="455" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B455" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="C455" t="s">
         <v>915</v>
@@ -21740,10 +22041,10 @@
     </row>
     <row r="456" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B456" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C456" t="s">
         <v>915</v>
@@ -21778,10 +22079,10 @@
     </row>
     <row r="457" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B457" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="C457" t="s">
         <v>915</v>
@@ -21816,10 +22117,10 @@
     </row>
     <row r="458" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B458" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C458" t="s">
         <v>915</v>
@@ -21854,10 +22155,10 @@
     </row>
     <row r="459" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B459" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C459" t="s">
         <v>915</v>
@@ -21892,10 +22193,10 @@
     </row>
     <row r="460" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B460" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="C460" t="s">
         <v>915</v>
@@ -21930,10 +22231,10 @@
     </row>
     <row r="461" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B461" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="C461" t="s">
         <v>915</v>
@@ -21968,10 +22269,10 @@
     </row>
     <row r="462" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B462" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="C462" t="s">
         <v>915</v>
@@ -22006,10 +22307,10 @@
     </row>
     <row r="463" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="B463" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="C463" t="s">
         <v>915</v>
@@ -22044,10 +22345,10 @@
     </row>
     <row r="464" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B464" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="C464" t="s">
         <v>915</v>
@@ -22082,10 +22383,10 @@
     </row>
     <row r="465" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B465" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="C465" t="s">
         <v>915</v>
@@ -22120,10 +22421,10 @@
     </row>
     <row r="466" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B466" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="C466" t="s">
         <v>915</v>
@@ -22158,16 +22459,16 @@
     </row>
     <row r="467" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B467" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="C467" t="s">
-        <v>946</v>
+        <v>915</v>
       </c>
       <c r="D467" t="s">
-        <v>947</v>
+        <v>25</v>
       </c>
       <c r="E467" t="s">
         <v>25</v>
@@ -22196,16 +22497,16 @@
     </row>
     <row r="468" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="B468" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="C468" t="s">
-        <v>946</v>
+        <v>915</v>
       </c>
       <c r="D468" t="s">
-        <v>947</v>
+        <v>25</v>
       </c>
       <c r="E468" t="s">
         <v>25</v>
@@ -22234,10 +22535,10 @@
     </row>
     <row r="469" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="B469" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="C469" t="s">
         <v>946</v>
@@ -22272,10 +22573,10 @@
     </row>
     <row r="470" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B470" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="C470" t="s">
         <v>946</v>
@@ -22310,16 +22611,16 @@
     </row>
     <row r="471" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B471" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="C471" t="s">
         <v>946</v>
       </c>
       <c r="D471" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
       <c r="E471" t="s">
         <v>25</v>
@@ -22348,16 +22649,16 @@
     </row>
     <row r="472" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="B472" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="C472" t="s">
         <v>946</v>
       </c>
       <c r="D472" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
       <c r="E472" t="s">
         <v>25</v>
@@ -22386,10 +22687,10 @@
     </row>
     <row r="473" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="B473" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="C473" t="s">
         <v>946</v>
@@ -22424,10 +22725,10 @@
     </row>
     <row r="474" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B474" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C474" t="s">
         <v>946</v>
@@ -22462,10 +22763,10 @@
     </row>
     <row r="475" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="B475" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="C475" t="s">
         <v>946</v>
@@ -22500,10 +22801,10 @@
     </row>
     <row r="476" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B476" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="C476" t="s">
         <v>946</v>
@@ -22538,10 +22839,10 @@
     </row>
     <row r="477" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B477" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="C477" t="s">
         <v>946</v>
@@ -22576,16 +22877,16 @@
     </row>
     <row r="478" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B478" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C478" t="s">
-        <v>971</v>
+        <v>946</v>
       </c>
       <c r="D478" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="E478" t="s">
         <v>25</v>
@@ -22614,16 +22915,16 @@
     </row>
     <row r="479" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="B479" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="C479" t="s">
-        <v>971</v>
+        <v>946</v>
       </c>
       <c r="D479" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="E479" t="s">
         <v>25</v>
@@ -22652,10 +22953,10 @@
     </row>
     <row r="480" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="B480" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="C480" t="s">
         <v>971</v>
@@ -22690,10 +22991,10 @@
     </row>
     <row r="481" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B481" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C481" t="s">
         <v>971</v>
@@ -22728,10 +23029,10 @@
     </row>
     <row r="482" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="B482" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="C482" t="s">
         <v>971</v>
@@ -22766,10 +23067,10 @@
     </row>
     <row r="483" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B483" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="C483" t="s">
         <v>971</v>
@@ -22804,10 +23105,10 @@
     </row>
     <row r="484" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="B484" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="C484" t="s">
         <v>971</v>
@@ -22842,10 +23143,10 @@
     </row>
     <row r="485" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B485" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="C485" t="s">
         <v>971</v>
@@ -22880,16 +23181,16 @@
     </row>
     <row r="486" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="B486" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="C486" t="s">
         <v>971</v>
       </c>
       <c r="D486" t="s">
-        <v>989</v>
+        <v>972</v>
       </c>
       <c r="E486" t="s">
         <v>25</v>
@@ -22918,16 +23219,16 @@
     </row>
     <row r="487" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="B487" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="C487" t="s">
         <v>971</v>
       </c>
       <c r="D487" t="s">
-        <v>989</v>
+        <v>972</v>
       </c>
       <c r="E487" t="s">
         <v>25</v>
@@ -22956,10 +23257,10 @@
     </row>
     <row r="488" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="B488" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="C488" t="s">
         <v>971</v>
@@ -22994,10 +23295,10 @@
     </row>
     <row r="489" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="B489" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="C489" t="s">
         <v>971</v>
@@ -23032,10 +23333,10 @@
     </row>
     <row r="490" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="B490" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="C490" t="s">
         <v>971</v>
@@ -23070,16 +23371,16 @@
     </row>
     <row r="491" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B491" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="C491" t="s">
         <v>971</v>
       </c>
       <c r="D491" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="E491" t="s">
         <v>25</v>
@@ -23108,16 +23409,16 @@
     </row>
     <row r="492" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="B492" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="C492" t="s">
         <v>971</v>
       </c>
       <c r="D492" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="E492" t="s">
         <v>25</v>
@@ -23146,16 +23447,16 @@
     </row>
     <row r="493" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="B493" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="C493" t="s">
         <v>971</v>
       </c>
       <c r="D493" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="E493" t="s">
         <v>25</v>
@@ -23184,16 +23485,16 @@
     </row>
     <row r="494" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="B494" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="C494" t="s">
         <v>971</v>
       </c>
       <c r="D494" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="E494" t="s">
         <v>25</v>
@@ -23222,10 +23523,10 @@
     </row>
     <row r="495" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="B495" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="C495" t="s">
         <v>971</v>
@@ -23260,10 +23561,10 @@
     </row>
     <row r="496" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="B496" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="C496" t="s">
         <v>971</v>
@@ -23298,10 +23599,10 @@
     </row>
     <row r="497" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="B497" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="C497" t="s">
         <v>971</v>
@@ -23336,10 +23637,10 @@
     </row>
     <row r="498" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="B498" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="C498" t="s">
         <v>971</v>
@@ -23374,16 +23675,16 @@
     </row>
     <row r="499" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B499" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C499" t="s">
         <v>971</v>
       </c>
       <c r="D499" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="E499" t="s">
         <v>25</v>
@@ -23412,16 +23713,16 @@
     </row>
     <row r="500" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="B500" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="C500" t="s">
         <v>971</v>
       </c>
       <c r="D500" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="E500" t="s">
         <v>25</v>
@@ -23450,10 +23751,10 @@
     </row>
     <row r="501" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="B501" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C501" t="s">
         <v>971</v>
@@ -23488,10 +23789,10 @@
     </row>
     <row r="502" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="B502" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="C502" t="s">
         <v>971</v>
@@ -23526,16 +23827,16 @@
     </row>
     <row r="503" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="B503" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="C503" t="s">
         <v>971</v>
       </c>
       <c r="D503" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="E503" t="s">
         <v>25</v>
@@ -23564,16 +23865,16 @@
     </row>
     <row r="504" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="B504" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="C504" t="s">
         <v>971</v>
       </c>
       <c r="D504" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="E504" t="s">
         <v>25</v>
@@ -23602,10 +23903,10 @@
     </row>
     <row r="505" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="B505" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="C505" t="s">
         <v>971</v>
@@ -23640,10 +23941,10 @@
     </row>
     <row r="506" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="B506" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="C506" t="s">
         <v>971</v>
@@ -23678,16 +23979,16 @@
     </row>
     <row r="507" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="B507" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="C507" t="s">
         <v>971</v>
       </c>
       <c r="D507" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
       <c r="E507" t="s">
         <v>25</v>
@@ -23716,16 +24017,16 @@
     </row>
     <row r="508" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="B508" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="C508" t="s">
         <v>971</v>
       </c>
       <c r="D508" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
       <c r="E508" t="s">
         <v>25</v>
@@ -23754,10 +24055,10 @@
     </row>
     <row r="509" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="B509" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="C509" t="s">
         <v>971</v>
@@ -23792,10 +24093,10 @@
     </row>
     <row r="510" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="B510" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="C510" t="s">
         <v>971</v>
@@ -23830,16 +24131,16 @@
     </row>
     <row r="511" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="B511" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="C511" t="s">
         <v>971</v>
       </c>
       <c r="D511" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
       <c r="E511" t="s">
         <v>25</v>
@@ -23868,16 +24169,16 @@
     </row>
     <row r="512" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="B512" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="C512" t="s">
         <v>971</v>
       </c>
       <c r="D512" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
       <c r="E512" t="s">
         <v>25</v>
@@ -23906,10 +24207,10 @@
     </row>
     <row r="513" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="B513" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="C513" t="s">
         <v>971</v>
@@ -23944,10 +24245,10 @@
     </row>
     <row r="514" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="B514" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C514" t="s">
         <v>971</v>
@@ -23982,16 +24283,16 @@
     </row>
     <row r="515" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="B515" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="C515" t="s">
         <v>971</v>
       </c>
       <c r="D515" t="s">
-        <v>1054</v>
+        <v>1045</v>
       </c>
       <c r="E515" t="s">
         <v>25</v>
@@ -24020,16 +24321,16 @@
     </row>
     <row r="516" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="B516" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="C516" t="s">
         <v>971</v>
       </c>
       <c r="D516" t="s">
-        <v>1054</v>
+        <v>1045</v>
       </c>
       <c r="E516" t="s">
         <v>25</v>
@@ -24058,10 +24359,10 @@
     </row>
     <row r="517" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="B517" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="C517" t="s">
         <v>971</v>
@@ -24096,10 +24397,10 @@
     </row>
     <row r="518" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="B518" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="C518" t="s">
         <v>971</v>
@@ -24134,10 +24435,10 @@
     </row>
     <row r="519" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="B519" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="C519" t="s">
         <v>971</v>
@@ -24172,10 +24473,10 @@
     </row>
     <row r="520" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="B520" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="C520" t="s">
         <v>971</v>
@@ -24208,11 +24509,89 @@
         <v>25</v>
       </c>
     </row>
+    <row r="521" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C521" t="s">
+        <v>971</v>
+      </c>
+      <c r="D521" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E521" t="s">
+        <v>25</v>
+      </c>
+      <c r="F521" t="s">
+        <v>25</v>
+      </c>
+      <c r="G521" t="s">
+        <v>25</v>
+      </c>
+      <c r="H521" t="s">
+        <v>19</v>
+      </c>
+      <c r="I521" t="s">
+        <v>25</v>
+      </c>
+      <c r="J521" t="s">
+        <v>25</v>
+      </c>
+      <c r="K521" t="s">
+        <v>25</v>
+      </c>
+      <c r="L521" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="522" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C522" t="s">
+        <v>971</v>
+      </c>
+      <c r="D522" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E522" t="s">
+        <v>25</v>
+      </c>
+      <c r="F522" t="s">
+        <v>25</v>
+      </c>
+      <c r="G522" t="s">
+        <v>25</v>
+      </c>
+      <c r="H522" t="s">
+        <v>19</v>
+      </c>
+      <c r="I522" t="s">
+        <v>25</v>
+      </c>
+      <c r="J522" t="s">
+        <v>25</v>
+      </c>
+      <c r="K522" t="s">
+        <v>25</v>
+      </c>
+      <c r="L522" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="523" spans="1:12" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="524" spans="1:12" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L3 A45:D45 L32 G32:I32 B32:E32 G33:L33 B34:L34 B33:E33 A58:L520 A51:D51 L51 A54:D54 J54:L54 A57:D57 J57:L57 H51 F54 F57 H54 H57 A48:D48 H48:I48 A5:L7 A4:E4 G4:L4 L48 F45 H45:L45 A19:L31 B10:D10 F10 A11:D12 F12 J10:L10 F11 J11:L11 J12:L12 H10 H11 H12 B17:D17 B18:D18 F17 F18 H17 H18 J17:L17 K18:L18" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L3 A47:D47 L34 G34:I34 B34:E34 G35:L35 B36:L36 B35:E35 A60:L522 A53:D53 L53 A56:D56 J56:L56 A59:D59 J59:L59 H53 F56 F59 H56 H59 A50:D50 H50:I50 A5:L7 A4:E4 G4:L4 L50 F47 H47:L47 A19:L20 B10:D10 F10 A11:D12 F12 J10:L10 F11 J11:L11 J12:L12 H10 H11 H12 B17:D17 B18:D18 F17 F18 H17 H18 J17:L17 K18:L18 A28:L29 A21:D21 H21 A22:D24 F24 L21 F22 J22:L22 F23 J23:L23 J24:L24 A31:L33 A30:I30 K30:L30 H24 H22 H23 A25:D25 H25 L25" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="482" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C254E25-176C-4422-A675-63A6C82CEA67}"/>
+  <xr:revisionPtr revIDLastSave="499" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4286774C-7385-4310-B3C3-0B0CBF44D6D2}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6635" uniqueCount="1170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6689" uniqueCount="1176">
   <si>
     <t>Codigo</t>
   </si>
@@ -5314,6 +5314,149 @@
   </si>
   <si>
     <t>Mecedora 3 en 1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuna Colecho Nevada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Multifuncional está diseñada para mantener a tu bebé cerca durante el descanso, ofreciendo comodidad y seguridad en todo momento. Su diseño multifuncional incluye función colecho, dos niveles de altura, cambiador, móvil con juguetes, toldillo protector y ruedas con freno para facilitar su uso y transporte. Ideal para el descanso diario y los primeros meses de crecimiento.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Cuna colecho multifuncional </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>con toldillo, cambiador y ruedas con freno, diseñada para brindar comodidad, seguridad y practicidad durante los primeros meses del bebé.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Función colecho adaptable a la cama.
+Dos niveles de altura.
+Toldillo protector.
+Móvil con juguetes.
+Cambiador integrado.
+Bolsa para transporte.
+Ruedas con freno.
+Bolsillos organizadores.
+Estructura metálica con tela resistente.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Mantiene al bebé cerca durante la noche.
+Facilita el cuidado diario gracias a sus accesorios.
+Ideal para espacios pequeños y viajes.
+Fácil de mover y transportar.
+Diseño práctico y multifuncional.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Utilizar siempre sobre una superficie firme y nivelada.
+Activar los frenos antes de colocar al bebé.
+Limpiar la tela y la estructura con un paño húmedo.
+Revisar periódicamente las uniones y accesorios antes de cada uso.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/colechonevada/nevadagris.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/colechonevada/nevadablack.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/colechonevada/nevadapink.webp</t>
   </si>
 </sst>
 </file>
@@ -8767,26 +8910,26 @@
       <c r="D85" t="s">
         <v>92</v>
       </c>
-      <c r="E85" t="s">
-        <v>25</v>
+      <c r="E85">
+        <v>545748</v>
       </c>
       <c r="F85" t="s">
-        <v>25</v>
+        <v>1170</v>
       </c>
       <c r="G85" t="s">
-        <v>25</v>
+        <v>1173</v>
       </c>
       <c r="H85" t="s">
         <v>19</v>
       </c>
       <c r="I85" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J85" t="s">
-        <v>25</v>
-      </c>
-      <c r="K85" t="s">
-        <v>25</v>
+        <v>1171</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>1172</v>
       </c>
       <c r="L85" t="s">
         <v>25</v>
@@ -8794,7 +8937,7 @@
     </row>
     <row r="86" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B86" t="s">
         <v>104</v>
@@ -8805,20 +8948,20 @@
       <c r="D86" t="s">
         <v>92</v>
       </c>
-      <c r="E86" t="s">
-        <v>25</v>
+      <c r="E86">
+        <v>545748</v>
       </c>
       <c r="F86" t="s">
         <v>25</v>
       </c>
       <c r="G86" t="s">
-        <v>25</v>
+        <v>1175</v>
       </c>
       <c r="H86" t="s">
         <v>19</v>
       </c>
       <c r="I86" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="J86" t="s">
         <v>25</v>
@@ -8832,7 +8975,7 @@
     </row>
     <row r="87" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B87" t="s">
         <v>104</v>
@@ -8843,20 +8986,20 @@
       <c r="D87" t="s">
         <v>92</v>
       </c>
-      <c r="E87" t="s">
-        <v>25</v>
+      <c r="E87">
+        <v>545748</v>
       </c>
       <c r="F87" t="s">
         <v>25</v>
       </c>
       <c r="G87" t="s">
-        <v>25</v>
+        <v>1174</v>
       </c>
       <c r="H87" t="s">
         <v>19</v>
       </c>
       <c r="I87" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J87" t="s">
         <v>25</v>
@@ -25974,7 +26117,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 B37:E37 G38:L38 B39:L39 B38:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 F10 A11:D12 F12 J10:L10 F11 J11:L11 J12:L12 H10 H11 H12 B17:D17 B18:D18 F17 F18 H17 H18 J17:L17 K18:L18 A28:G28 A21:D21 H21 A22:D24 F24 L21 F22 J22:L22 F23 J23:L23 J24:L24 A34:D36 A33:D33 L33 H24 H22 H23 A25:D25 H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F36 F34 J34:L34 F35 J35:L35 J36:L36 H33 H36 H34 H35 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67 J67:L67 A68 J68:L68 A72 J72:L72 A73 J73:L73 F72 F73:G73 F67:G67 F68:G68 C72:D72 C68:D68 C67:D67 C73:D73 H72 A74 A85:L537 A84 I84:L84 C74:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 B37:E37 G38:L38 B39:L39 B38:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 F10 A11:D12 F12 J10:L10 F11 J11:L11 J12:L12 H10 H11 H12 B17:D17 B18:D18 F17 F18 H17 H18 J17:L17 K18:L18 A28:G28 A21:D21 H21 A22:D24 F24 L21 F22 J22:L22 F23 J23:L23 J24:L24 A34:D36 A33:D33 L33 H24 H22 H23 A25:D25 H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F36 F34 J34:L34 F35 J35:L35 J36:L36 H33 H36 H34 H35 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67 J67:L67 A68 J68:L68 A72 J72:L72 A73 J73:L73 F72 F73:G73 F67:G67 F68:G68 C72:D72 C68:D68 C67:D67 C73:D73 H72 A74 A88:L537 A84 I84:L84 C74:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="499" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4286774C-7385-4310-B3C3-0B0CBF44D6D2}"/>
+  <xr:revisionPtr revIDLastSave="574" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6895DBD-C684-4DDF-8233-C33D2BCA10CF}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6689" uniqueCount="1176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6862" uniqueCount="1198">
   <si>
     <t>Codigo</t>
   </si>
@@ -5457,6 +5457,492 @@
   </si>
   <si>
     <t>assets/productos/bebes/colechonevada/nevadapink.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cunamecedora/cuna1.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cunamecedora/cuna2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cunamecedora/cuna3.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/cunamecedora/cuna4.webp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuna Mecedora Mastela</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> REF. 30911 ofrece un espacio acogedor y seguro para el descanso del bebé. Su diseño incorpora función mecedora, capota protectora, laterales en malla transpirable y un colchón acolchado que favorecen la comodidad y la ventilación. Es ideal para acompañar las rutinas de sueño y descanso durante los primeros meses de vida.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuna mecedora</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mastela con función de balanceo, capota protectora y laterales en malla, diseñada para brindar un descanso seguro y cómodo desde los primeros días del bebé.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Función de cuna y mecedora.
+Estructura metálica y plástica resistente.
+Laterales en malla transpirable.
+Capota protectora.
+Colchón acolchado incluido.
+Uso recomendado para recién nacidos y primeros meses.
+Incluye manual de instalación.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Favorece un descanso cómodo y relajante.
+Permite una mejor circulación del aire.
+Facilita la supervisión del bebé gracias a sus laterales en malla.
+Ideal para dormitorios y espacios reducidos.
+Diseño práctico, moderno y funcional.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Utilizar siempre sobre superficies firmes y niveladas.
+Mantener las telas limpias siguiendo las recomendaciones del fabricante.
+Revisar periódicamente la estabilidad de la estructura.
+No dejar al bebé sin supervisión durante su uso.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/sillavibradora/musical1.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/sillavibradora/musical2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/sillavibradora/musical3.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/sillavibradora/musical4.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/sillavibradora/musical5.webp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Silla Mecedora Vibradora y Musical</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> para Bebé combina descanso, juego y relajación en un solo producto. Cuenta con función de mecedora, modo fijo, vibración, música y barra de juguetes desmontable para estimular el desarrollo del bebé. Su diseño compacto, resistente y plegable la hace ideal para el uso diario en el hogar.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Medidas del producto:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ancho: 46 cm
+Alto: 49 cm
+Largo: 65 cm
+Peso: 3 kg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Silla mecedora </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>para bebé con vibración, música y barra de juguetes, diseñada para brindar descanso, entretenimiento y comodidad desde los primeros meses.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Función mecedora y silla fija.
+Vibración y música integradas.
+Barra de juguetes desmontable.
+Estructura en hierro y plástico de alta resistencia.
+Diseño compacto y plegable.
+Soporta hasta 18 kg.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Ayuda a relajar y entretener al bebé.
+Estimula el desarrollo sensorial y la curiosidad.
+Fácil de transportar y almacenar.
+Ideal para recién nacidos y bebés en crecimiento.
+Perfecta para el descanso y los momentos de juego.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Utilizar siempre bajo la supervisión de un adulto.
+Verificar el ajuste de la estructura antes de cada uso.
+Limpiar la tela y la estructura con un paño húmedo.
+No exceder el peso máximo recomendado.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Set Lava Teteros </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">está diseñado para facilitar la limpieza de teteros y accesorios del bebé. Incluye diferentes cepillos y escobillas para llegar a cada rincón, ayudando a mantener una higiene adecuada. Está fabricado con materiales resistentes, ligeros y libres de BPA, ideales para el uso diario.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Contenido del set:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cepillo principal para teteros.
+Cepillo mediano.
+Cepillo para boquillas.
+Escobillas para detalles.
+Accesorios para válvulas y piezas pequeñas.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Fabricado en plástico y esponja.
+Material libre de BPA.
+Compatible con teteros de diferentes tamaños.
+Incluye varios accesorios de limpieza.
+Diseño ligero y práctico.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Permite una limpieza profunda de teteros y accesorios.
+Llega fácilmente a zonas difíciles.
+Ayuda a mantener una mejor higiene para el bebé.
+Resistente y fácil de utilizar.
+Ideal para el uso diario.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Lavar los cepillos después de cada uso.
+Dejar secar completamente antes de guardar.
+Reemplazar los cepillos cuando presenten desgaste.
+Conservar en un lugar limpio y seco.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Set lava teteros</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con múltiples accesorios para limpiar teteros, boquillas y piezas pequeñas de forma práctica, segura y libre de BPA.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/setlavateteros/lavatetepink.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/setlavateteros/lavatetepink2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/setlavateteros/lavateteblue.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/setlavateteros/lavateteblue2.webp</t>
   </si>
 </sst>
 </file>
@@ -5849,7 +6335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L539"/>
+  <dimension ref="A1:L548"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -9024,14 +9510,14 @@
       <c r="D88" t="s">
         <v>92</v>
       </c>
-      <c r="E88" t="s">
-        <v>25</v>
+      <c r="E88">
+        <v>716338</v>
       </c>
       <c r="F88" t="s">
-        <v>25</v>
+        <v>1180</v>
       </c>
       <c r="G88" t="s">
-        <v>25</v>
+        <v>1176</v>
       </c>
       <c r="H88" t="s">
         <v>19</v>
@@ -9040,10 +9526,10 @@
         <v>25</v>
       </c>
       <c r="J88" t="s">
-        <v>25</v>
-      </c>
-      <c r="K88" t="s">
-        <v>25</v>
+        <v>1181</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>1182</v>
       </c>
       <c r="L88" t="s">
         <v>25</v>
@@ -9051,10 +9537,10 @@
     </row>
     <row r="89" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B89" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -9062,14 +9548,14 @@
       <c r="D89" t="s">
         <v>92</v>
       </c>
-      <c r="E89" t="s">
-        <v>25</v>
+      <c r="E89">
+        <v>716338</v>
       </c>
       <c r="F89" t="s">
         <v>25</v>
       </c>
       <c r="G89" t="s">
-        <v>25</v>
+        <v>1177</v>
       </c>
       <c r="H89" t="s">
         <v>19</v>
@@ -9089,25 +9575,25 @@
     </row>
     <row r="90" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B90" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
-      </c>
-      <c r="E90" t="s">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="E90">
+        <v>716338</v>
       </c>
       <c r="F90" t="s">
         <v>25</v>
       </c>
       <c r="G90" t="s">
-        <v>25</v>
+        <v>1178</v>
       </c>
       <c r="H90" t="s">
         <v>19</v>
@@ -9127,25 +9613,25 @@
     </row>
     <row r="91" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B91" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>113</v>
-      </c>
-      <c r="E91" t="s">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="E91">
+        <v>716338</v>
       </c>
       <c r="F91" t="s">
         <v>25</v>
       </c>
       <c r="G91" t="s">
-        <v>25</v>
+        <v>1179</v>
       </c>
       <c r="H91" t="s">
         <v>19</v>
@@ -9165,25 +9651,25 @@
     </row>
     <row r="92" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B92" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>113</v>
-      </c>
-      <c r="E92" t="s">
-        <v>25</v>
-      </c>
-      <c r="F92" t="s">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="E92">
+        <v>162000</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>1188</v>
       </c>
       <c r="G92" t="s">
-        <v>25</v>
+        <v>1183</v>
       </c>
       <c r="H92" t="s">
         <v>19</v>
@@ -9192,10 +9678,10 @@
         <v>25</v>
       </c>
       <c r="J92" t="s">
-        <v>25</v>
-      </c>
-      <c r="K92" t="s">
-        <v>25</v>
+        <v>1189</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>1190</v>
       </c>
       <c r="L92" t="s">
         <v>25</v>
@@ -9203,25 +9689,25 @@
     </row>
     <row r="93" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B93" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
-      </c>
-      <c r="E93" t="s">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="E93">
+        <v>162000</v>
       </c>
       <c r="F93" t="s">
         <v>25</v>
       </c>
       <c r="G93" t="s">
-        <v>25</v>
+        <v>1184</v>
       </c>
       <c r="H93" t="s">
         <v>19</v>
@@ -9241,25 +9727,25 @@
     </row>
     <row r="94" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>113</v>
-      </c>
-      <c r="E94" t="s">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="E94">
+        <v>162000</v>
       </c>
       <c r="F94" t="s">
         <v>25</v>
       </c>
       <c r="G94" t="s">
-        <v>25</v>
+        <v>1185</v>
       </c>
       <c r="H94" t="s">
         <v>19</v>
@@ -9279,25 +9765,25 @@
     </row>
     <row r="95" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
-      </c>
-      <c r="E95" t="s">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="E95">
+        <v>162000</v>
       </c>
       <c r="F95" t="s">
         <v>25</v>
       </c>
       <c r="G95" t="s">
-        <v>25</v>
+        <v>1186</v>
       </c>
       <c r="H95" t="s">
         <v>19</v>
@@ -9317,25 +9803,25 @@
     </row>
     <row r="96" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="B96" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
-      </c>
-      <c r="E96" t="s">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="E96">
+        <v>162000</v>
       </c>
       <c r="F96" t="s">
         <v>25</v>
       </c>
       <c r="G96" t="s">
-        <v>25</v>
+        <v>1187</v>
       </c>
       <c r="H96" t="s">
         <v>19</v>
@@ -9355,10 +9841,10 @@
     </row>
     <row r="97" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -9376,7 +9862,7 @@
         <v>25</v>
       </c>
       <c r="H97" t="s">
-        <v>19</v>
+        <v>1131</v>
       </c>
       <c r="I97" t="s">
         <v>25</v>
@@ -9393,16 +9879,16 @@
     </row>
     <row r="98" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B98" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E98" t="s">
         <v>25</v>
@@ -9414,15 +9900,12 @@
         <v>25</v>
       </c>
       <c r="H98" t="s">
-        <v>19</v>
+        <v>1131</v>
       </c>
       <c r="I98" t="s">
         <v>25</v>
       </c>
       <c r="J98" t="s">
-        <v>25</v>
-      </c>
-      <c r="K98" t="s">
         <v>25</v>
       </c>
       <c r="L98" t="s">
@@ -9431,16 +9914,16 @@
     </row>
     <row r="99" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B99" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C99" t="s">
         <v>14</v>
       </c>
       <c r="D99" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
@@ -9452,7 +9935,7 @@
         <v>25</v>
       </c>
       <c r="H99" t="s">
-        <v>19</v>
+        <v>1131</v>
       </c>
       <c r="I99" t="s">
         <v>25</v>
@@ -9469,31 +9952,31 @@
     </row>
     <row r="100" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B100" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>129</v>
-      </c>
-      <c r="E100" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="E100">
+        <v>59965</v>
       </c>
       <c r="F100" t="s">
         <v>25</v>
       </c>
       <c r="G100" t="s">
-        <v>25</v>
+        <v>1196</v>
       </c>
       <c r="H100" t="s">
         <v>19</v>
       </c>
       <c r="I100" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J100" t="s">
         <v>25</v>
@@ -9507,31 +9990,31 @@
     </row>
     <row r="101" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="B101" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C101" t="s">
         <v>14</v>
       </c>
       <c r="D101" t="s">
-        <v>129</v>
-      </c>
-      <c r="E101" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="E101">
+        <v>59965</v>
       </c>
       <c r="F101" t="s">
         <v>25</v>
       </c>
       <c r="G101" t="s">
-        <v>25</v>
+        <v>1197</v>
       </c>
       <c r="H101" t="s">
         <v>19</v>
       </c>
       <c r="I101" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J101" t="s">
         <v>25</v>
@@ -9545,37 +10028,37 @@
     </row>
     <row r="102" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B102" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>129</v>
-      </c>
-      <c r="E102" t="s">
-        <v>25</v>
-      </c>
-      <c r="F102" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="E102">
+        <v>59965</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>1191</v>
       </c>
       <c r="G102" t="s">
-        <v>25</v>
+        <v>1194</v>
       </c>
       <c r="H102" t="s">
         <v>19</v>
       </c>
       <c r="I102" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="J102" t="s">
-        <v>25</v>
-      </c>
-      <c r="K102" t="s">
-        <v>25</v>
+        <v>1193</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>1192</v>
       </c>
       <c r="L102" t="s">
         <v>25</v>
@@ -9583,36 +10066,33 @@
     </row>
     <row r="103" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B103" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>140</v>
-      </c>
-      <c r="E103" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="E103">
+        <v>59965</v>
       </c>
       <c r="F103" t="s">
         <v>25</v>
       </c>
       <c r="G103" t="s">
-        <v>25</v>
+        <v>1195</v>
       </c>
       <c r="H103" t="s">
         <v>19</v>
       </c>
       <c r="I103" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="J103" t="s">
-        <v>25</v>
-      </c>
-      <c r="K103" t="s">
         <v>25</v>
       </c>
       <c r="L103" t="s">
@@ -9621,24 +10101,21 @@
     </row>
     <row r="104" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B104" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C104" t="s">
         <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="E104" t="s">
         <v>25</v>
       </c>
       <c r="F104" t="s">
-        <v>25</v>
-      </c>
-      <c r="G104" t="s">
         <v>25</v>
       </c>
       <c r="H104" t="s">
@@ -9659,16 +10136,16 @@
     </row>
     <row r="105" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="B105" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C105" t="s">
         <v>14</v>
       </c>
       <c r="D105" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="E105" t="s">
         <v>25</v>
@@ -9697,16 +10174,16 @@
     </row>
     <row r="106" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="B106" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
       </c>
       <c r="D106" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="E106" t="s">
         <v>25</v>
@@ -9735,16 +10212,16 @@
     </row>
     <row r="107" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="B107" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E107" t="s">
         <v>25</v>
@@ -9773,16 +10250,16 @@
     </row>
     <row r="108" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="B108" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E108" t="s">
         <v>25</v>
@@ -9811,16 +10288,16 @@
     </row>
     <row r="109" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="B109" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C109" t="s">
         <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E109" t="s">
         <v>25</v>
@@ -9849,16 +10326,16 @@
     </row>
     <row r="110" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="B110" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="C110" t="s">
         <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="E110" t="s">
         <v>25</v>
@@ -9887,16 +10364,16 @@
     </row>
     <row r="111" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="B111" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C111" t="s">
         <v>14</v>
       </c>
       <c r="D111" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="E111" t="s">
         <v>25</v>
@@ -9925,16 +10402,16 @@
     </row>
     <row r="112" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="B112" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C112" t="s">
         <v>14</v>
       </c>
       <c r="D112" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E112" t="s">
         <v>25</v>
@@ -9963,16 +10440,16 @@
     </row>
     <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="B113" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="C113" t="s">
         <v>14</v>
       </c>
       <c r="D113" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E113" t="s">
         <v>25</v>
@@ -10001,16 +10478,16 @@
     </row>
     <row r="114" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="B114" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
@@ -10039,16 +10516,16 @@
     </row>
     <row r="115" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B115" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
       </c>
       <c r="D115" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
@@ -10077,16 +10554,16 @@
     </row>
     <row r="116" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B116" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C116" t="s">
         <v>14</v>
       </c>
       <c r="D116" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E116" t="s">
         <v>25</v>
@@ -10115,16 +10592,16 @@
     </row>
     <row r="117" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="B117" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="C117" t="s">
         <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E117" t="s">
         <v>25</v>
@@ -10153,16 +10630,16 @@
     </row>
     <row r="118" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="B118" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="C118" t="s">
         <v>14</v>
       </c>
       <c r="D118" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
@@ -10191,10 +10668,10 @@
     </row>
     <row r="119" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="B119" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="C119" t="s">
         <v>14</v>
@@ -10229,10 +10706,10 @@
     </row>
     <row r="120" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="B120" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="C120" t="s">
         <v>14</v>
@@ -10267,10 +10744,10 @@
     </row>
     <row r="121" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B121" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="C121" t="s">
         <v>14</v>
@@ -10305,10 +10782,10 @@
     </row>
     <row r="122" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B122" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
@@ -10343,10 +10820,10 @@
     </row>
     <row r="123" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="B123" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="C123" t="s">
         <v>14</v>
@@ -10381,10 +10858,10 @@
     </row>
     <row r="124" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B124" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="C124" t="s">
         <v>14</v>
@@ -10419,10 +10896,10 @@
     </row>
     <row r="125" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="B125" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
@@ -10457,10 +10934,10 @@
     </row>
     <row r="126" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="B126" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="C126" t="s">
         <v>14</v>
@@ -10495,10 +10972,10 @@
     </row>
     <row r="127" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="B127" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="C127" t="s">
         <v>14</v>
@@ -10533,10 +11010,10 @@
     </row>
     <row r="128" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="B128" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="C128" t="s">
         <v>14</v>
@@ -10571,10 +11048,10 @@
     </row>
     <row r="129" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="B129" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="C129" t="s">
         <v>14</v>
@@ -10609,10 +11086,10 @@
     </row>
     <row r="130" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="C130" t="s">
         <v>14</v>
@@ -10620,14 +11097,14 @@
       <c r="D130" t="s">
         <v>155</v>
       </c>
-      <c r="E130">
-        <v>106156</v>
+      <c r="E130" t="s">
+        <v>25</v>
       </c>
       <c r="F130" t="s">
-        <v>195</v>
+        <v>25</v>
       </c>
       <c r="G130" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="H130" t="s">
         <v>19</v>
@@ -10636,10 +11113,10 @@
         <v>25</v>
       </c>
       <c r="J130" t="s">
-        <v>197</v>
+        <v>25</v>
       </c>
       <c r="K130" t="s">
-        <v>198</v>
+        <v>25</v>
       </c>
       <c r="L130" t="s">
         <v>25</v>
@@ -10647,10 +11124,10 @@
     </row>
     <row r="131" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C131" t="s">
         <v>14</v>
@@ -10658,14 +11135,14 @@
       <c r="D131" t="s">
         <v>155</v>
       </c>
-      <c r="E131">
-        <v>106156</v>
+      <c r="E131" t="s">
+        <v>25</v>
       </c>
       <c r="F131" t="s">
         <v>25</v>
       </c>
       <c r="G131" t="s">
-        <v>199</v>
+        <v>25</v>
       </c>
       <c r="H131" t="s">
         <v>19</v>
@@ -10685,16 +11162,16 @@
     </row>
     <row r="132" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="C132" t="s">
         <v>14</v>
       </c>
       <c r="D132" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E132" t="s">
         <v>25</v>
@@ -10723,16 +11200,16 @@
     </row>
     <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="B133" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="C133" t="s">
         <v>14</v>
       </c>
       <c r="D133" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E133" t="s">
         <v>25</v>
@@ -10761,16 +11238,16 @@
     </row>
     <row r="134" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="B134" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="C134" t="s">
         <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E134" t="s">
         <v>25</v>
@@ -10799,16 +11276,16 @@
     </row>
     <row r="135" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="B135" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="C135" t="s">
         <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E135" t="s">
         <v>25</v>
@@ -10837,16 +11314,16 @@
     </row>
     <row r="136" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="B136" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="C136" t="s">
         <v>14</v>
       </c>
       <c r="D136" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E136" t="s">
         <v>25</v>
@@ -10875,16 +11352,16 @@
     </row>
     <row r="137" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="B137" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C137" t="s">
         <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
@@ -10913,16 +11390,16 @@
     </row>
     <row r="138" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="B138" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="C138" t="s">
         <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E138" t="s">
         <v>25</v>
@@ -10951,25 +11428,25 @@
     </row>
     <row r="139" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="B139" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="C139" t="s">
         <v>14</v>
       </c>
       <c r="D139" t="s">
-        <v>202</v>
-      </c>
-      <c r="E139" t="s">
-        <v>25</v>
+        <v>155</v>
+      </c>
+      <c r="E139">
+        <v>106156</v>
       </c>
       <c r="F139" t="s">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="G139" t="s">
-        <v>25</v>
+        <v>196</v>
       </c>
       <c r="H139" t="s">
         <v>19</v>
@@ -10978,10 +11455,10 @@
         <v>25</v>
       </c>
       <c r="J139" t="s">
-        <v>25</v>
+        <v>197</v>
       </c>
       <c r="K139" t="s">
-        <v>25</v>
+        <v>198</v>
       </c>
       <c r="L139" t="s">
         <v>25</v>
@@ -10989,25 +11466,25 @@
     </row>
     <row r="140" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="B140" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="C140" t="s">
         <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>202</v>
-      </c>
-      <c r="E140" t="s">
-        <v>25</v>
+        <v>155</v>
+      </c>
+      <c r="E140">
+        <v>106156</v>
       </c>
       <c r="F140" t="s">
         <v>25</v>
       </c>
       <c r="G140" t="s">
-        <v>25</v>
+        <v>199</v>
       </c>
       <c r="H140" t="s">
         <v>19</v>
@@ -11027,10 +11504,10 @@
     </row>
     <row r="141" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="B141" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="C141" t="s">
         <v>14</v>
@@ -11065,10 +11542,10 @@
     </row>
     <row r="142" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="B142" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="C142" t="s">
         <v>14</v>
@@ -11103,10 +11580,10 @@
     </row>
     <row r="143" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="B143" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="C143" t="s">
         <v>14</v>
@@ -11141,10 +11618,10 @@
     </row>
     <row r="144" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="B144" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="C144" t="s">
         <v>14</v>
@@ -11179,16 +11656,16 @@
     </row>
     <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="B145" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="C145" t="s">
         <v>14</v>
       </c>
       <c r="D145" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="E145" t="s">
         <v>25</v>
@@ -11217,16 +11694,16 @@
     </row>
     <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="B146" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="C146" t="s">
         <v>14</v>
       </c>
       <c r="D146" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="E146" t="s">
         <v>25</v>
@@ -11255,16 +11732,16 @@
     </row>
     <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="B147" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="C147" t="s">
         <v>14</v>
       </c>
       <c r="D147" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="E147" t="s">
         <v>25</v>
@@ -11293,16 +11770,16 @@
     </row>
     <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="B148" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C148" t="s">
         <v>14</v>
       </c>
       <c r="D148" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="E148" t="s">
         <v>25</v>
@@ -11331,16 +11808,16 @@
     </row>
     <row r="149" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="B149" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="C149" t="s">
         <v>14</v>
       </c>
       <c r="D149" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="E149" t="s">
         <v>25</v>
@@ -11369,16 +11846,16 @@
     </row>
     <row r="150" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="B150" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="C150" t="s">
         <v>14</v>
       </c>
       <c r="D150" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="E150" t="s">
         <v>25</v>
@@ -11407,16 +11884,16 @@
     </row>
     <row r="151" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="B151" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="C151" t="s">
         <v>14</v>
       </c>
       <c r="D151" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="E151" t="s">
         <v>25</v>
@@ -11445,16 +11922,16 @@
     </row>
     <row r="152" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="B152" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C152" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D152" t="s">
-        <v>244</v>
+        <v>202</v>
       </c>
       <c r="E152" t="s">
         <v>25</v>
@@ -11483,16 +11960,16 @@
     </row>
     <row r="153" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="B153" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="C153" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D153" t="s">
-        <v>244</v>
+        <v>202</v>
       </c>
       <c r="E153" t="s">
         <v>25</v>
@@ -11521,16 +11998,16 @@
     </row>
     <row r="154" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="B154" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="C154" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D154" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E154" t="s">
         <v>25</v>
@@ -11559,16 +12036,16 @@
     </row>
     <row r="155" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="B155" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="C155" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D155" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E155" t="s">
         <v>25</v>
@@ -11597,16 +12074,16 @@
     </row>
     <row r="156" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B156" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="C156" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D156" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E156" t="s">
         <v>25</v>
@@ -11635,16 +12112,16 @@
     </row>
     <row r="157" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B157" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="C157" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D157" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E157" t="s">
         <v>25</v>
@@ -11673,16 +12150,16 @@
     </row>
     <row r="158" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="B158" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="C158" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D158" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E158" t="s">
         <v>25</v>
@@ -11711,16 +12188,16 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="B159" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="C159" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D159" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E159" t="s">
         <v>25</v>
@@ -11749,16 +12226,16 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="B160" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="C160" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D160" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E160" t="s">
         <v>25</v>
@@ -11787,10 +12264,10 @@
     </row>
     <row r="161" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="B161" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="C161" t="s">
         <v>243</v>
@@ -11825,10 +12302,10 @@
     </row>
     <row r="162" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="B162" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="C162" t="s">
         <v>243</v>
@@ -11863,10 +12340,10 @@
     </row>
     <row r="163" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="B163" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="C163" t="s">
         <v>243</v>
@@ -11901,10 +12378,10 @@
     </row>
     <row r="164" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="B164" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="C164" t="s">
         <v>243</v>
@@ -11939,10 +12416,10 @@
     </row>
     <row r="165" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="B165" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="C165" t="s">
         <v>243</v>
@@ -11977,10 +12454,10 @@
     </row>
     <row r="166" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="B166" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="C166" t="s">
         <v>243</v>
@@ -12015,10 +12492,10 @@
     </row>
     <row r="167" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="B167" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="C167" t="s">
         <v>243</v>
@@ -12053,10 +12530,10 @@
     </row>
     <row r="168" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="B168" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="C168" t="s">
         <v>243</v>
@@ -12091,10 +12568,10 @@
     </row>
     <row r="169" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="B169" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="C169" t="s">
         <v>243</v>
@@ -12129,10 +12606,10 @@
     </row>
     <row r="170" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="B170" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="C170" t="s">
         <v>243</v>
@@ -12167,10 +12644,10 @@
     </row>
     <row r="171" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="B171" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="C171" t="s">
         <v>243</v>
@@ -12205,10 +12682,10 @@
     </row>
     <row r="172" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="B172" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="C172" t="s">
         <v>243</v>
@@ -12243,10 +12720,10 @@
     </row>
     <row r="173" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="B173" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="C173" t="s">
         <v>243</v>
@@ -12281,10 +12758,10 @@
     </row>
     <row r="174" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="B174" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="C174" t="s">
         <v>243</v>
@@ -12319,10 +12796,10 @@
     </row>
     <row r="175" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="B175" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="C175" t="s">
         <v>243</v>
@@ -12357,10 +12834,10 @@
     </row>
     <row r="176" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="B176" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="C176" t="s">
         <v>243</v>
@@ -12395,10 +12872,10 @@
     </row>
     <row r="177" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="B177" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="C177" t="s">
         <v>243</v>
@@ -12433,10 +12910,10 @@
     </row>
     <row r="178" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="B178" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="C178" t="s">
         <v>243</v>
@@ -12471,10 +12948,10 @@
     </row>
     <row r="179" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B179" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="C179" t="s">
         <v>243</v>
@@ -12509,10 +12986,10 @@
     </row>
     <row r="180" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="B180" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="C180" t="s">
         <v>243</v>
@@ -12547,10 +13024,10 @@
     </row>
     <row r="181" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="B181" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="C181" t="s">
         <v>243</v>
@@ -12585,10 +13062,10 @@
     </row>
     <row r="182" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="B182" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="C182" t="s">
         <v>243</v>
@@ -12623,10 +13100,10 @@
     </row>
     <row r="183" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="B183" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="C183" t="s">
         <v>243</v>
@@ -12661,10 +13138,10 @@
     </row>
     <row r="184" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="B184" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="C184" t="s">
         <v>243</v>
@@ -12699,10 +13176,10 @@
     </row>
     <row r="185" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="B185" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="C185" t="s">
         <v>243</v>
@@ -12737,10 +13214,10 @@
     </row>
     <row r="186" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="B186" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="C186" t="s">
         <v>243</v>
@@ -12775,10 +13252,10 @@
     </row>
     <row r="187" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="B187" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="C187" t="s">
         <v>243</v>
@@ -12813,10 +13290,10 @@
     </row>
     <row r="188" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="B188" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="C188" t="s">
         <v>243</v>
@@ -12851,10 +13328,10 @@
     </row>
     <row r="189" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="B189" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="C189" t="s">
         <v>243</v>
@@ -12889,16 +13366,16 @@
     </row>
     <row r="190" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="B190" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="C190" t="s">
         <v>243</v>
       </c>
       <c r="D190" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E190" t="s">
         <v>25</v>
@@ -12927,16 +13404,16 @@
     </row>
     <row r="191" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="B191" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="C191" t="s">
         <v>243</v>
       </c>
       <c r="D191" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E191" t="s">
         <v>25</v>
@@ -12965,16 +13442,16 @@
     </row>
     <row r="192" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="B192" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="C192" t="s">
         <v>243</v>
       </c>
       <c r="D192" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E192" t="s">
         <v>25</v>
@@ -13003,16 +13480,16 @@
     </row>
     <row r="193" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="B193" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="C193" t="s">
         <v>243</v>
       </c>
       <c r="D193" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E193" t="s">
         <v>25</v>
@@ -13041,16 +13518,16 @@
     </row>
     <row r="194" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="B194" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="C194" t="s">
         <v>243</v>
       </c>
       <c r="D194" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E194" t="s">
         <v>25</v>
@@ -13079,16 +13556,16 @@
     </row>
     <row r="195" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B195" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="C195" t="s">
         <v>243</v>
       </c>
       <c r="D195" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E195" t="s">
         <v>25</v>
@@ -13117,16 +13594,16 @@
     </row>
     <row r="196" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="B196" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="C196" t="s">
         <v>243</v>
       </c>
       <c r="D196" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E196" t="s">
         <v>25</v>
@@ -13155,16 +13632,16 @@
     </row>
     <row r="197" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="B197" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="C197" t="s">
         <v>243</v>
       </c>
       <c r="D197" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E197" t="s">
         <v>25</v>
@@ -13193,16 +13670,16 @@
     </row>
     <row r="198" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="B198" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="C198" t="s">
         <v>243</v>
       </c>
       <c r="D198" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E198" t="s">
         <v>25</v>
@@ -13231,10 +13708,10 @@
     </row>
     <row r="199" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B199" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="C199" t="s">
         <v>243</v>
@@ -13269,16 +13746,16 @@
     </row>
     <row r="200" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="B200" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="C200" t="s">
         <v>243</v>
       </c>
       <c r="D200" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="E200" t="s">
         <v>25</v>
@@ -13307,16 +13784,16 @@
     </row>
     <row r="201" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="B201" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="C201" t="s">
         <v>243</v>
       </c>
       <c r="D201" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="E201" t="s">
         <v>25</v>
@@ -13345,16 +13822,16 @@
     </row>
     <row r="202" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="B202" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="C202" t="s">
         <v>243</v>
       </c>
       <c r="D202" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="E202" t="s">
         <v>25</v>
@@ -13383,16 +13860,16 @@
     </row>
     <row r="203" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="B203" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="C203" t="s">
         <v>243</v>
       </c>
       <c r="D203" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E203" t="s">
         <v>25</v>
@@ -13421,16 +13898,16 @@
     </row>
     <row r="204" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="B204" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="C204" t="s">
         <v>243</v>
       </c>
       <c r="D204" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E204" t="s">
         <v>25</v>
@@ -13459,16 +13936,16 @@
     </row>
     <row r="205" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="B205" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="C205" t="s">
         <v>243</v>
       </c>
       <c r="D205" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E205" t="s">
         <v>25</v>
@@ -13497,16 +13974,16 @@
     </row>
     <row r="206" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="B206" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="C206" t="s">
         <v>243</v>
       </c>
       <c r="D206" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E206" t="s">
         <v>25</v>
@@ -13535,16 +14012,16 @@
     </row>
     <row r="207" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="B207" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="C207" t="s">
         <v>243</v>
       </c>
       <c r="D207" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E207" t="s">
         <v>25</v>
@@ -13573,16 +14050,16 @@
     </row>
     <row r="208" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="B208" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="C208" t="s">
         <v>243</v>
       </c>
       <c r="D208" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E208" t="s">
         <v>25</v>
@@ -13611,16 +14088,16 @@
     </row>
     <row r="209" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B209" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="C209" t="s">
         <v>243</v>
       </c>
       <c r="D209" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="E209" t="s">
         <v>25</v>
@@ -13649,16 +14126,16 @@
     </row>
     <row r="210" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="B210" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="C210" t="s">
         <v>243</v>
       </c>
       <c r="D210" t="s">
-        <v>229</v>
+        <v>342</v>
       </c>
       <c r="E210" t="s">
         <v>25</v>
@@ -13687,16 +14164,16 @@
     </row>
     <row r="211" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="B211" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C211" t="s">
         <v>243</v>
       </c>
       <c r="D211" t="s">
-        <v>229</v>
+        <v>342</v>
       </c>
       <c r="E211" t="s">
         <v>25</v>
@@ -13725,16 +14202,16 @@
     </row>
     <row r="212" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="B212" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="C212" t="s">
         <v>243</v>
       </c>
       <c r="D212" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E212" t="s">
         <v>25</v>
@@ -13763,16 +14240,16 @@
     </row>
     <row r="213" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="B213" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="C213" t="s">
         <v>243</v>
       </c>
       <c r="D213" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E213" t="s">
         <v>25</v>
@@ -13801,16 +14278,16 @@
     </row>
     <row r="214" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="B214" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="C214" t="s">
         <v>243</v>
       </c>
       <c r="D214" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E214" t="s">
         <v>25</v>
@@ -13839,16 +14316,16 @@
     </row>
     <row r="215" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="B215" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="C215" t="s">
         <v>243</v>
       </c>
       <c r="D215" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E215" t="s">
         <v>25</v>
@@ -13877,16 +14354,16 @@
     </row>
     <row r="216" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="B216" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="C216" t="s">
         <v>243</v>
       </c>
       <c r="D216" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E216" t="s">
         <v>25</v>
@@ -13915,16 +14392,16 @@
     </row>
     <row r="217" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="B217" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="C217" t="s">
         <v>243</v>
       </c>
       <c r="D217" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E217" t="s">
         <v>25</v>
@@ -13953,16 +14430,16 @@
     </row>
     <row r="218" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="B218" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C218" t="s">
         <v>243</v>
       </c>
       <c r="D218" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E218" t="s">
         <v>25</v>
@@ -13991,10 +14468,10 @@
     </row>
     <row r="219" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="B219" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="C219" t="s">
         <v>243</v>
@@ -14029,10 +14506,10 @@
     </row>
     <row r="220" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B220" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="C220" t="s">
         <v>243</v>
@@ -14067,10 +14544,10 @@
     </row>
     <row r="221" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="B221" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="C221" t="s">
         <v>243</v>
@@ -14105,10 +14582,10 @@
     </row>
     <row r="222" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="B222" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="C222" t="s">
         <v>243</v>
@@ -14143,10 +14620,10 @@
     </row>
     <row r="223" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="B223" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C223" t="s">
         <v>243</v>
@@ -14181,10 +14658,10 @@
     </row>
     <row r="224" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="B224" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="C224" t="s">
         <v>243</v>
@@ -14219,10 +14696,10 @@
     </row>
     <row r="225" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B225" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="C225" t="s">
         <v>243</v>
@@ -14257,10 +14734,10 @@
     </row>
     <row r="226" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="B226" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="C226" t="s">
         <v>243</v>
@@ -14295,10 +14772,10 @@
     </row>
     <row r="227" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B227" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="C227" t="s">
         <v>243</v>
@@ -14333,10 +14810,10 @@
     </row>
     <row r="228" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="B228" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C228" t="s">
         <v>243</v>
@@ -14371,10 +14848,10 @@
     </row>
     <row r="229" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="B229" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="C229" t="s">
         <v>243</v>
@@ -14409,10 +14886,10 @@
     </row>
     <row r="230" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="B230" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="C230" t="s">
         <v>243</v>
@@ -14447,10 +14924,10 @@
     </row>
     <row r="231" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="B231" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="C231" t="s">
         <v>243</v>
@@ -14485,10 +14962,10 @@
     </row>
     <row r="232" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="B232" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
       <c r="C232" t="s">
         <v>243</v>
@@ -14523,10 +15000,10 @@
     </row>
     <row r="233" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="B233" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="C233" t="s">
         <v>243</v>
@@ -14561,10 +15038,10 @@
     </row>
     <row r="234" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="B234" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="C234" t="s">
         <v>243</v>
@@ -14599,10 +15076,10 @@
     </row>
     <row r="235" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="B235" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="C235" t="s">
         <v>243</v>
@@ -14637,16 +15114,16 @@
     </row>
     <row r="236" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="B236" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="C236" t="s">
         <v>243</v>
       </c>
       <c r="D236" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E236" t="s">
         <v>25</v>
@@ -14675,16 +15152,16 @@
     </row>
     <row r="237" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="B237" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="C237" t="s">
         <v>243</v>
       </c>
       <c r="D237" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E237" t="s">
         <v>25</v>
@@ -14713,16 +15190,16 @@
     </row>
     <row r="238" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="B238" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="C238" t="s">
         <v>243</v>
       </c>
       <c r="D238" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E238" t="s">
         <v>25</v>
@@ -14751,16 +15228,16 @@
     </row>
     <row r="239" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="B239" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="C239" t="s">
         <v>243</v>
       </c>
       <c r="D239" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E239" t="s">
         <v>25</v>
@@ -14789,16 +15266,16 @@
     </row>
     <row r="240" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="B240" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="C240" t="s">
         <v>243</v>
       </c>
       <c r="D240" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E240" t="s">
         <v>25</v>
@@ -14827,16 +15304,16 @@
     </row>
     <row r="241" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="B241" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="C241" t="s">
         <v>243</v>
       </c>
       <c r="D241" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E241" t="s">
         <v>25</v>
@@ -14865,16 +15342,16 @@
     </row>
     <row r="242" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="B242" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="C242" t="s">
         <v>243</v>
       </c>
       <c r="D242" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E242" t="s">
         <v>25</v>
@@ -14903,16 +15380,16 @@
     </row>
     <row r="243" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="B243" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="C243" t="s">
         <v>243</v>
       </c>
       <c r="D243" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E243" t="s">
         <v>25</v>
@@ -14941,16 +15418,16 @@
     </row>
     <row r="244" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="B244" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="C244" t="s">
         <v>243</v>
       </c>
       <c r="D244" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E244" t="s">
         <v>25</v>
@@ -14979,10 +15456,10 @@
     </row>
     <row r="245" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="B245" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="C245" t="s">
         <v>243</v>
@@ -15017,10 +15494,10 @@
     </row>
     <row r="246" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="B246" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="C246" t="s">
         <v>243</v>
@@ -15055,10 +15532,10 @@
     </row>
     <row r="247" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="B247" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="C247" t="s">
         <v>243</v>
@@ -15093,10 +15570,10 @@
     </row>
     <row r="248" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B248" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="C248" t="s">
         <v>243</v>
@@ -15131,10 +15608,10 @@
     </row>
     <row r="249" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="B249" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="C249" t="s">
         <v>243</v>
@@ -15169,10 +15646,10 @@
     </row>
     <row r="250" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="B250" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="C250" t="s">
         <v>243</v>
@@ -15207,10 +15684,10 @@
     </row>
     <row r="251" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B251" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="C251" t="s">
         <v>243</v>
@@ -15245,10 +15722,10 @@
     </row>
     <row r="252" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="B252" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="C252" t="s">
         <v>243</v>
@@ -15283,10 +15760,10 @@
     </row>
     <row r="253" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="B253" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C253" t="s">
         <v>243</v>
@@ -15321,10 +15798,10 @@
     </row>
     <row r="254" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="B254" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="C254" t="s">
         <v>243</v>
@@ -15359,10 +15836,10 @@
     </row>
     <row r="255" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="B255" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="C255" t="s">
         <v>243</v>
@@ -15397,10 +15874,10 @@
     </row>
     <row r="256" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="B256" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="C256" t="s">
         <v>243</v>
@@ -15435,10 +15912,10 @@
     </row>
     <row r="257" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="B257" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="C257" t="s">
         <v>243</v>
@@ -15473,10 +15950,10 @@
     </row>
     <row r="258" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="B258" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="C258" t="s">
         <v>243</v>
@@ -15511,10 +15988,10 @@
     </row>
     <row r="259" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="B259" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="C259" t="s">
         <v>243</v>
@@ -15549,10 +16026,10 @@
     </row>
     <row r="260" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="B260" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="C260" t="s">
         <v>243</v>
@@ -15587,10 +16064,10 @@
     </row>
     <row r="261" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="B261" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="C261" t="s">
         <v>243</v>
@@ -15625,16 +16102,16 @@
     </row>
     <row r="262" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="B262" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="C262" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D262" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E262" t="s">
         <v>25</v>
@@ -15663,16 +16140,16 @@
     </row>
     <row r="263" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="B263" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="C263" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D263" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E263" t="s">
         <v>25</v>
@@ -15701,16 +16178,16 @@
     </row>
     <row r="264" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="B264" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="C264" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D264" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E264" t="s">
         <v>25</v>
@@ -15739,16 +16216,16 @@
     </row>
     <row r="265" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="B265" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="C265" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D265" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E265" t="s">
         <v>25</v>
@@ -15777,16 +16254,16 @@
     </row>
     <row r="266" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="B266" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="C266" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D266" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E266" t="s">
         <v>25</v>
@@ -15815,16 +16292,16 @@
     </row>
     <row r="267" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="B267" t="s">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="C267" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D267" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E267" t="s">
         <v>25</v>
@@ -15853,16 +16330,16 @@
     </row>
     <row r="268" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="B268" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="C268" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D268" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E268" t="s">
         <v>25</v>
@@ -15891,16 +16368,16 @@
     </row>
     <row r="269" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="B269" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="C269" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D269" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E269" t="s">
         <v>25</v>
@@ -15929,16 +16406,16 @@
     </row>
     <row r="270" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B270" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="C270" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D270" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E270" t="s">
         <v>25</v>
@@ -15967,10 +16444,10 @@
     </row>
     <row r="271" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="B271" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="C271" t="s">
         <v>464</v>
@@ -16005,10 +16482,10 @@
     </row>
     <row r="272" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="B272" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="C272" t="s">
         <v>464</v>
@@ -16043,10 +16520,10 @@
     </row>
     <row r="273" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="B273" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="C273" t="s">
         <v>464</v>
@@ -16081,10 +16558,10 @@
     </row>
     <row r="274" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="B274" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="C274" t="s">
         <v>464</v>
@@ -16119,10 +16596,10 @@
     </row>
     <row r="275" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="B275" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="C275" t="s">
         <v>464</v>
@@ -16157,10 +16634,10 @@
     </row>
     <row r="276" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B276" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="C276" t="s">
         <v>464</v>
@@ -16195,10 +16672,10 @@
     </row>
     <row r="277" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="B277" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="C277" t="s">
         <v>464</v>
@@ -16233,10 +16710,10 @@
     </row>
     <row r="278" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="B278" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="C278" t="s">
         <v>464</v>
@@ -16271,10 +16748,10 @@
     </row>
     <row r="279" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="B279" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="C279" t="s">
         <v>464</v>
@@ -16309,10 +16786,10 @@
     </row>
     <row r="280" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="B280" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="C280" t="s">
         <v>464</v>
@@ -16347,10 +16824,10 @@
     </row>
     <row r="281" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="B281" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="C281" t="s">
         <v>464</v>
@@ -16385,10 +16862,10 @@
     </row>
     <row r="282" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="B282" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="C282" t="s">
         <v>464</v>
@@ -16423,10 +16900,10 @@
     </row>
     <row r="283" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="B283" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="C283" t="s">
         <v>464</v>
@@ -16461,10 +16938,10 @@
     </row>
     <row r="284" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="B284" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="C284" t="s">
         <v>464</v>
@@ -16499,10 +16976,10 @@
     </row>
     <row r="285" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="B285" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="C285" t="s">
         <v>464</v>
@@ -16537,10 +17014,10 @@
     </row>
     <row r="286" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="B286" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="C286" t="s">
         <v>464</v>
@@ -16575,10 +17052,10 @@
     </row>
     <row r="287" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="B287" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="C287" t="s">
         <v>464</v>
@@ -16613,10 +17090,10 @@
     </row>
     <row r="288" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="B288" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="C288" t="s">
         <v>464</v>
@@ -16651,10 +17128,10 @@
     </row>
     <row r="289" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="B289" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="C289" t="s">
         <v>464</v>
@@ -16689,10 +17166,10 @@
     </row>
     <row r="290" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="B290" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="C290" t="s">
         <v>464</v>
@@ -16727,10 +17204,10 @@
     </row>
     <row r="291" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="B291" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="C291" t="s">
         <v>464</v>
@@ -16765,10 +17242,10 @@
     </row>
     <row r="292" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="B292" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="C292" t="s">
         <v>464</v>
@@ -16803,10 +17280,10 @@
     </row>
     <row r="293" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="B293" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="C293" t="s">
         <v>464</v>
@@ -16841,10 +17318,10 @@
     </row>
     <row r="294" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>528</v>
+        <v>510</v>
       </c>
       <c r="B294" t="s">
-        <v>529</v>
+        <v>511</v>
       </c>
       <c r="C294" t="s">
         <v>464</v>
@@ -16879,10 +17356,10 @@
     </row>
     <row r="295" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="B295" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="C295" t="s">
         <v>464</v>
@@ -16917,10 +17394,10 @@
     </row>
     <row r="296" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="B296" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="C296" t="s">
         <v>464</v>
@@ -16955,10 +17432,10 @@
     </row>
     <row r="297" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="B297" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="C297" t="s">
         <v>464</v>
@@ -16993,10 +17470,10 @@
     </row>
     <row r="298" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="B298" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="C298" t="s">
         <v>464</v>
@@ -17031,10 +17508,10 @@
     </row>
     <row r="299" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="B299" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="C299" t="s">
         <v>464</v>
@@ -17069,10 +17546,10 @@
     </row>
     <row r="300" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="B300" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="C300" t="s">
         <v>464</v>
@@ -17107,10 +17584,10 @@
     </row>
     <row r="301" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="B301" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="C301" t="s">
         <v>464</v>
@@ -17145,10 +17622,10 @@
     </row>
     <row r="302" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="B302" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="C302" t="s">
         <v>464</v>
@@ -17183,10 +17660,10 @@
     </row>
     <row r="303" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="B303" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="C303" t="s">
         <v>464</v>
@@ -17221,10 +17698,10 @@
     </row>
     <row r="304" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="B304" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="C304" t="s">
         <v>464</v>
@@ -17259,10 +17736,10 @@
     </row>
     <row r="305" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="B305" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="C305" t="s">
         <v>464</v>
@@ -17297,10 +17774,10 @@
     </row>
     <row r="306" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="B306" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="C306" t="s">
         <v>464</v>
@@ -17335,10 +17812,10 @@
     </row>
     <row r="307" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="B307" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="C307" t="s">
         <v>464</v>
@@ -17373,10 +17850,10 @@
     </row>
     <row r="308" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="B308" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="C308" t="s">
         <v>464</v>
@@ -17411,16 +17888,16 @@
     </row>
     <row r="309" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="B309" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="C309" t="s">
         <v>464</v>
       </c>
       <c r="D309" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E309" t="s">
         <v>25</v>
@@ -17449,16 +17926,16 @@
     </row>
     <row r="310" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="B310" t="s">
-        <v>562</v>
+        <v>543</v>
       </c>
       <c r="C310" t="s">
         <v>464</v>
       </c>
       <c r="D310" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E310" t="s">
         <v>25</v>
@@ -17487,16 +17964,16 @@
     </row>
     <row r="311" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="B311" t="s">
-        <v>564</v>
+        <v>545</v>
       </c>
       <c r="C311" t="s">
         <v>464</v>
       </c>
       <c r="D311" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E311" t="s">
         <v>25</v>
@@ -17525,16 +18002,16 @@
     </row>
     <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="B312" t="s">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="C312" t="s">
         <v>464</v>
       </c>
       <c r="D312" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E312" t="s">
         <v>25</v>
@@ -17563,16 +18040,16 @@
     </row>
     <row r="313" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>567</v>
+        <v>548</v>
       </c>
       <c r="B313" t="s">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="C313" t="s">
         <v>464</v>
       </c>
       <c r="D313" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E313" t="s">
         <v>25</v>
@@ -17601,16 +18078,16 @@
     </row>
     <row r="314" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="B314" t="s">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="C314" t="s">
         <v>464</v>
       </c>
       <c r="D314" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E314" t="s">
         <v>25</v>
@@ -17639,16 +18116,16 @@
     </row>
     <row r="315" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
       <c r="B315" t="s">
-        <v>572</v>
+        <v>553</v>
       </c>
       <c r="C315" t="s">
         <v>464</v>
       </c>
       <c r="D315" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E315" t="s">
         <v>25</v>
@@ -17677,16 +18154,16 @@
     </row>
     <row r="316" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
       <c r="B316" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
       <c r="C316" t="s">
         <v>464</v>
       </c>
       <c r="D316" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E316" t="s">
         <v>25</v>
@@ -17715,16 +18192,16 @@
     </row>
     <row r="317" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
       <c r="B317" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="C317" t="s">
         <v>464</v>
       </c>
       <c r="D317" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E317" t="s">
         <v>25</v>
@@ -17753,10 +18230,10 @@
     </row>
     <row r="318" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>577</v>
+        <v>558</v>
       </c>
       <c r="B318" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
       <c r="C318" t="s">
         <v>464</v>
@@ -17791,10 +18268,10 @@
     </row>
     <row r="319" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="B319" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
       <c r="C319" t="s">
         <v>464</v>
@@ -17829,10 +18306,10 @@
     </row>
     <row r="320" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="B320" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="C320" t="s">
         <v>464</v>
@@ -17867,10 +18344,10 @@
     </row>
     <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="B321" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="C321" t="s">
         <v>464</v>
@@ -17905,10 +18382,10 @@
     </row>
     <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="B322" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="C322" t="s">
         <v>464</v>
@@ -17943,10 +18420,10 @@
     </row>
     <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="B323" t="s">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="C323" t="s">
         <v>464</v>
@@ -17981,10 +18458,10 @@
     </row>
     <row r="324" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="B324" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="C324" t="s">
         <v>464</v>
@@ -18019,10 +18496,10 @@
     </row>
     <row r="325" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="B325" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="C325" t="s">
         <v>464</v>
@@ -18057,10 +18534,10 @@
     </row>
     <row r="326" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>593</v>
+        <v>575</v>
       </c>
       <c r="B326" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="C326" t="s">
         <v>464</v>
@@ -18095,10 +18572,10 @@
     </row>
     <row r="327" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="B327" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="C327" t="s">
         <v>464</v>
@@ -18133,10 +18610,10 @@
     </row>
     <row r="328" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B328" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="C328" t="s">
         <v>464</v>
@@ -18171,10 +18648,10 @@
     </row>
     <row r="329" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="B329" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="C329" t="s">
         <v>464</v>
@@ -18209,10 +18686,10 @@
     </row>
     <row r="330" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="B330" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="C330" t="s">
         <v>464</v>
@@ -18247,10 +18724,10 @@
     </row>
     <row r="331" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="B331" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="C331" t="s">
         <v>464</v>
@@ -18285,10 +18762,10 @@
     </row>
     <row r="332" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="B332" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="C332" t="s">
         <v>464</v>
@@ -18323,10 +18800,10 @@
     </row>
     <row r="333" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="B333" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="C333" t="s">
         <v>464</v>
@@ -18361,10 +18838,10 @@
     </row>
     <row r="334" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="B334" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="C334" t="s">
         <v>464</v>
@@ -18399,10 +18876,10 @@
     </row>
     <row r="335" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="B335" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="C335" t="s">
         <v>464</v>
@@ -18437,10 +18914,10 @@
     </row>
     <row r="336" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="B336" t="s">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="C336" t="s">
         <v>464</v>
@@ -18475,10 +18952,10 @@
     </row>
     <row r="337" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="B337" t="s">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="C337" t="s">
         <v>464</v>
@@ -18513,10 +18990,10 @@
     </row>
     <row r="338" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>617</v>
+        <v>599</v>
       </c>
       <c r="B338" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="C338" t="s">
         <v>464</v>
@@ -18551,10 +19028,10 @@
     </row>
     <row r="339" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="B339" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="C339" t="s">
         <v>464</v>
@@ -18589,10 +19066,10 @@
     </row>
     <row r="340" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>621</v>
+        <v>603</v>
       </c>
       <c r="B340" t="s">
-        <v>622</v>
+        <v>604</v>
       </c>
       <c r="C340" t="s">
         <v>464</v>
@@ -18627,10 +19104,10 @@
     </row>
     <row r="341" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="B341" t="s">
-        <v>624</v>
+        <v>606</v>
       </c>
       <c r="C341" t="s">
         <v>464</v>
@@ -18665,10 +19142,10 @@
     </row>
     <row r="342" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="B342" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="C342" t="s">
         <v>464</v>
@@ -18703,16 +19180,16 @@
     </row>
     <row r="343" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="B343" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="C343" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D343" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E343" t="s">
         <v>25</v>
@@ -18741,16 +19218,16 @@
     </row>
     <row r="344" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>630</v>
+        <v>611</v>
       </c>
       <c r="B344" t="s">
-        <v>631</v>
+        <v>612</v>
       </c>
       <c r="C344" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D344" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E344" t="s">
         <v>25</v>
@@ -18779,16 +19256,16 @@
     </row>
     <row r="345" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="B345" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="C345" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D345" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E345" t="s">
         <v>25</v>
@@ -18817,16 +19294,16 @@
     </row>
     <row r="346" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="B346" t="s">
-        <v>635</v>
+        <v>616</v>
       </c>
       <c r="C346" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D346" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E346" t="s">
         <v>25</v>
@@ -18855,16 +19332,16 @@
     </row>
     <row r="347" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>636</v>
+        <v>617</v>
       </c>
       <c r="B347" t="s">
-        <v>637</v>
+        <v>618</v>
       </c>
       <c r="C347" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D347" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E347" t="s">
         <v>25</v>
@@ -18893,16 +19370,16 @@
     </row>
     <row r="348" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>638</v>
+        <v>619</v>
       </c>
       <c r="B348" t="s">
-        <v>639</v>
+        <v>620</v>
       </c>
       <c r="C348" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D348" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E348" t="s">
         <v>25</v>
@@ -18931,16 +19408,16 @@
     </row>
     <row r="349" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>640</v>
+        <v>621</v>
       </c>
       <c r="B349" t="s">
-        <v>641</v>
+        <v>622</v>
       </c>
       <c r="C349" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D349" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E349" t="s">
         <v>25</v>
@@ -18969,16 +19446,16 @@
     </row>
     <row r="350" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>642</v>
+        <v>623</v>
       </c>
       <c r="B350" t="s">
-        <v>643</v>
+        <v>624</v>
       </c>
       <c r="C350" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D350" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E350" t="s">
         <v>25</v>
@@ -19007,16 +19484,16 @@
     </row>
     <row r="351" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>644</v>
+        <v>625</v>
       </c>
       <c r="B351" t="s">
-        <v>645</v>
+        <v>626</v>
       </c>
       <c r="C351" t="s">
-        <v>646</v>
+        <v>464</v>
       </c>
       <c r="D351" t="s">
-        <v>647</v>
+        <v>560</v>
       </c>
       <c r="E351" t="s">
         <v>25</v>
@@ -19045,16 +19522,16 @@
     </row>
     <row r="352" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="B352" t="s">
-        <v>649</v>
+        <v>628</v>
       </c>
       <c r="C352" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D352" t="s">
-        <v>647</v>
+        <v>25</v>
       </c>
       <c r="E352" t="s">
         <v>25</v>
@@ -19083,16 +19560,16 @@
     </row>
     <row r="353" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="B353" t="s">
-        <v>651</v>
+        <v>631</v>
       </c>
       <c r="C353" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D353" t="s">
-        <v>647</v>
+        <v>25</v>
       </c>
       <c r="E353" t="s">
         <v>25</v>
@@ -19121,16 +19598,16 @@
     </row>
     <row r="354" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>652</v>
+        <v>632</v>
       </c>
       <c r="B354" t="s">
-        <v>653</v>
+        <v>633</v>
       </c>
       <c r="C354" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D354" t="s">
-        <v>647</v>
+        <v>25</v>
       </c>
       <c r="E354" t="s">
         <v>25</v>
@@ -19159,16 +19636,16 @@
     </row>
     <row r="355" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>654</v>
+        <v>634</v>
       </c>
       <c r="B355" t="s">
-        <v>655</v>
+        <v>635</v>
       </c>
       <c r="C355" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D355" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="E355" t="s">
         <v>25</v>
@@ -19197,16 +19674,16 @@
     </row>
     <row r="356" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>656</v>
+        <v>636</v>
       </c>
       <c r="B356" t="s">
-        <v>657</v>
+        <v>637</v>
       </c>
       <c r="C356" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D356" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="E356" t="s">
         <v>25</v>
@@ -19235,16 +19712,16 @@
     </row>
     <row r="357" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>658</v>
+        <v>638</v>
       </c>
       <c r="B357" t="s">
-        <v>659</v>
+        <v>639</v>
       </c>
       <c r="C357" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D357" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="E357" t="s">
         <v>25</v>
@@ -19273,16 +19750,16 @@
     </row>
     <row r="358" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B358" t="s">
-        <v>661</v>
+        <v>641</v>
       </c>
       <c r="C358" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D358" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="E358" t="s">
         <v>25</v>
@@ -19311,16 +19788,16 @@
     </row>
     <row r="359" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>662</v>
+        <v>642</v>
       </c>
       <c r="B359" t="s">
-        <v>663</v>
+        <v>643</v>
       </c>
       <c r="C359" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D359" t="s">
-        <v>664</v>
+        <v>25</v>
       </c>
       <c r="E359" t="s">
         <v>25</v>
@@ -19349,16 +19826,16 @@
     </row>
     <row r="360" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>665</v>
+        <v>644</v>
       </c>
       <c r="B360" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="C360" t="s">
         <v>646</v>
       </c>
       <c r="D360" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="E360" t="s">
         <v>25</v>
@@ -19387,16 +19864,16 @@
     </row>
     <row r="361" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>667</v>
+        <v>648</v>
       </c>
       <c r="B361" t="s">
-        <v>668</v>
+        <v>649</v>
       </c>
       <c r="C361" t="s">
         <v>646</v>
       </c>
       <c r="D361" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="E361" t="s">
         <v>25</v>
@@ -19425,16 +19902,16 @@
     </row>
     <row r="362" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>669</v>
+        <v>650</v>
       </c>
       <c r="B362" t="s">
-        <v>670</v>
+        <v>651</v>
       </c>
       <c r="C362" t="s">
         <v>646</v>
       </c>
       <c r="D362" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="E362" t="s">
         <v>25</v>
@@ -19463,16 +19940,16 @@
     </row>
     <row r="363" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>671</v>
+        <v>652</v>
       </c>
       <c r="B363" t="s">
-        <v>672</v>
+        <v>653</v>
       </c>
       <c r="C363" t="s">
         <v>646</v>
       </c>
       <c r="D363" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="E363" t="s">
         <v>25</v>
@@ -19501,16 +19978,16 @@
     </row>
     <row r="364" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>673</v>
+        <v>654</v>
       </c>
       <c r="B364" t="s">
-        <v>674</v>
+        <v>655</v>
       </c>
       <c r="C364" t="s">
         <v>646</v>
       </c>
       <c r="D364" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E364" t="s">
         <v>25</v>
@@ -19539,16 +20016,16 @@
     </row>
     <row r="365" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>675</v>
+        <v>656</v>
       </c>
       <c r="B365" t="s">
-        <v>676</v>
+        <v>657</v>
       </c>
       <c r="C365" t="s">
         <v>646</v>
       </c>
       <c r="D365" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E365" t="s">
         <v>25</v>
@@ -19577,16 +20054,16 @@
     </row>
     <row r="366" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>677</v>
+        <v>658</v>
       </c>
       <c r="B366" t="s">
-        <v>678</v>
+        <v>659</v>
       </c>
       <c r="C366" t="s">
         <v>646</v>
       </c>
       <c r="D366" t="s">
-        <v>679</v>
+        <v>140</v>
       </c>
       <c r="E366" t="s">
         <v>25</v>
@@ -19615,16 +20092,16 @@
     </row>
     <row r="367" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="B367" t="s">
-        <v>681</v>
+        <v>661</v>
       </c>
       <c r="C367" t="s">
         <v>646</v>
       </c>
       <c r="D367" t="s">
-        <v>679</v>
+        <v>140</v>
       </c>
       <c r="E367" t="s">
         <v>25</v>
@@ -19653,16 +20130,16 @@
     </row>
     <row r="368" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>682</v>
+        <v>662</v>
       </c>
       <c r="B368" t="s">
-        <v>683</v>
+        <v>663</v>
       </c>
       <c r="C368" t="s">
         <v>646</v>
       </c>
       <c r="D368" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="E368" t="s">
         <v>25</v>
@@ -19691,16 +20168,16 @@
     </row>
     <row r="369" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
       <c r="B369" t="s">
-        <v>684</v>
+        <v>666</v>
       </c>
       <c r="C369" t="s">
         <v>646</v>
       </c>
       <c r="D369" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="E369" t="s">
         <v>25</v>
@@ -19729,16 +20206,16 @@
     </row>
     <row r="370" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>685</v>
+        <v>667</v>
       </c>
       <c r="B370" t="s">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="C370" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D370" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="E370" t="s">
         <v>25</v>
@@ -19767,16 +20244,16 @@
     </row>
     <row r="371" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>689</v>
+        <v>669</v>
       </c>
       <c r="B371" t="s">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="C371" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D371" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="E371" t="s">
         <v>25</v>
@@ -19805,16 +20282,16 @@
     </row>
     <row r="372" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>691</v>
+        <v>671</v>
       </c>
       <c r="B372" t="s">
-        <v>692</v>
+        <v>672</v>
       </c>
       <c r="C372" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D372" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="E372" t="s">
         <v>25</v>
@@ -19843,16 +20320,16 @@
     </row>
     <row r="373" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>693</v>
+        <v>673</v>
       </c>
       <c r="B373" t="s">
-        <v>694</v>
+        <v>674</v>
       </c>
       <c r="C373" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D373" t="s">
-        <v>688</v>
+        <v>129</v>
       </c>
       <c r="E373" t="s">
         <v>25</v>
@@ -19881,16 +20358,16 @@
     </row>
     <row r="374" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
       <c r="B374" t="s">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="C374" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D374" t="s">
-        <v>688</v>
+        <v>129</v>
       </c>
       <c r="E374" t="s">
         <v>25</v>
@@ -19919,16 +20396,16 @@
     </row>
     <row r="375" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>697</v>
+        <v>677</v>
       </c>
       <c r="B375" t="s">
-        <v>698</v>
+        <v>678</v>
       </c>
       <c r="C375" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D375" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="E375" t="s">
         <v>25</v>
@@ -19957,16 +20434,16 @@
     </row>
     <row r="376" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>699</v>
+        <v>680</v>
       </c>
       <c r="B376" t="s">
-        <v>700</v>
+        <v>681</v>
       </c>
       <c r="C376" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D376" t="s">
-        <v>701</v>
+        <v>679</v>
       </c>
       <c r="E376" t="s">
         <v>25</v>
@@ -19995,16 +20472,16 @@
     </row>
     <row r="377" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>702</v>
+        <v>682</v>
       </c>
       <c r="B377" t="s">
-        <v>703</v>
+        <v>683</v>
       </c>
       <c r="C377" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D377" t="s">
-        <v>701</v>
+        <v>679</v>
       </c>
       <c r="E377" t="s">
         <v>25</v>
@@ -20033,16 +20510,16 @@
     </row>
     <row r="378" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>704</v>
+        <v>682</v>
       </c>
       <c r="B378" t="s">
-        <v>705</v>
+        <v>684</v>
       </c>
       <c r="C378" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D378" t="s">
-        <v>701</v>
+        <v>679</v>
       </c>
       <c r="E378" t="s">
         <v>25</v>
@@ -20071,16 +20548,16 @@
     </row>
     <row r="379" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
       <c r="B379" t="s">
-        <v>707</v>
+        <v>686</v>
       </c>
       <c r="C379" t="s">
         <v>687</v>
       </c>
       <c r="D379" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="E379" t="s">
         <v>25</v>
@@ -20109,16 +20586,16 @@
     </row>
     <row r="380" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>709</v>
+        <v>689</v>
       </c>
       <c r="B380" t="s">
-        <v>710</v>
+        <v>690</v>
       </c>
       <c r="C380" t="s">
         <v>687</v>
       </c>
       <c r="D380" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="E380" t="s">
         <v>25</v>
@@ -20147,16 +20624,16 @@
     </row>
     <row r="381" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="B381" t="s">
-        <v>712</v>
+        <v>692</v>
       </c>
       <c r="C381" t="s">
         <v>687</v>
       </c>
       <c r="D381" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="E381" t="s">
         <v>25</v>
@@ -20185,16 +20662,16 @@
     </row>
     <row r="382" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>713</v>
+        <v>693</v>
       </c>
       <c r="B382" t="s">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="C382" t="s">
         <v>687</v>
       </c>
       <c r="D382" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="E382" t="s">
         <v>25</v>
@@ -20223,16 +20700,16 @@
     </row>
     <row r="383" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>715</v>
+        <v>695</v>
       </c>
       <c r="B383" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
       <c r="C383" t="s">
         <v>687</v>
       </c>
       <c r="D383" t="s">
-        <v>717</v>
+        <v>688</v>
       </c>
       <c r="E383" t="s">
         <v>25</v>
@@ -20261,16 +20738,16 @@
     </row>
     <row r="384" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>718</v>
+        <v>697</v>
       </c>
       <c r="B384" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="C384" t="s">
         <v>687</v>
       </c>
       <c r="D384" t="s">
-        <v>717</v>
+        <v>688</v>
       </c>
       <c r="E384" t="s">
         <v>25</v>
@@ -20299,16 +20776,16 @@
     </row>
     <row r="385" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>719</v>
+        <v>699</v>
       </c>
       <c r="B385" t="s">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="C385" t="s">
         <v>687</v>
       </c>
       <c r="D385" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="E385" t="s">
         <v>25</v>
@@ -20337,16 +20814,16 @@
     </row>
     <row r="386" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>721</v>
+        <v>702</v>
       </c>
       <c r="B386" t="s">
-        <v>722</v>
+        <v>703</v>
       </c>
       <c r="C386" t="s">
         <v>687</v>
       </c>
       <c r="D386" t="s">
-        <v>723</v>
+        <v>701</v>
       </c>
       <c r="E386" t="s">
         <v>25</v>
@@ -20375,16 +20852,16 @@
     </row>
     <row r="387" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>724</v>
+        <v>704</v>
       </c>
       <c r="B387" t="s">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="C387" t="s">
         <v>687</v>
       </c>
       <c r="D387" t="s">
-        <v>723</v>
+        <v>701</v>
       </c>
       <c r="E387" t="s">
         <v>25</v>
@@ -20413,16 +20890,16 @@
     </row>
     <row r="388" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>726</v>
+        <v>706</v>
       </c>
       <c r="B388" t="s">
-        <v>727</v>
+        <v>707</v>
       </c>
       <c r="C388" t="s">
         <v>687</v>
       </c>
       <c r="D388" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="E388" t="s">
         <v>25</v>
@@ -20451,16 +20928,16 @@
     </row>
     <row r="389" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>728</v>
+        <v>709</v>
       </c>
       <c r="B389" t="s">
-        <v>729</v>
+        <v>710</v>
       </c>
       <c r="C389" t="s">
         <v>687</v>
       </c>
       <c r="D389" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="E389" t="s">
         <v>25</v>
@@ -20489,16 +20966,16 @@
     </row>
     <row r="390" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="B390" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
       <c r="C390" t="s">
         <v>687</v>
       </c>
       <c r="D390" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="E390" t="s">
         <v>25</v>
@@ -20527,16 +21004,16 @@
     </row>
     <row r="391" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
       <c r="B391" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
       <c r="C391" t="s">
         <v>687</v>
       </c>
       <c r="D391" t="s">
-        <v>734</v>
+        <v>708</v>
       </c>
       <c r="E391" t="s">
         <v>25</v>
@@ -20565,16 +21042,16 @@
     </row>
     <row r="392" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>735</v>
+        <v>715</v>
       </c>
       <c r="B392" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="C392" t="s">
         <v>687</v>
       </c>
       <c r="D392" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="E392" t="s">
         <v>25</v>
@@ -20603,16 +21080,16 @@
     </row>
     <row r="393" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="B393" t="s">
-        <v>738</v>
+        <v>716</v>
       </c>
       <c r="C393" t="s">
         <v>687</v>
       </c>
       <c r="D393" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="E393" t="s">
         <v>25</v>
@@ -20641,16 +21118,16 @@
     </row>
     <row r="394" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>739</v>
+        <v>719</v>
       </c>
       <c r="B394" t="s">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="C394" t="s">
         <v>687</v>
       </c>
       <c r="D394" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="E394" t="s">
         <v>25</v>
@@ -20679,16 +21156,16 @@
     </row>
     <row r="395" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>741</v>
+        <v>721</v>
       </c>
       <c r="B395" t="s">
-        <v>742</v>
+        <v>722</v>
       </c>
       <c r="C395" t="s">
         <v>687</v>
       </c>
       <c r="D395" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="E395" t="s">
         <v>25</v>
@@ -20717,16 +21194,16 @@
     </row>
     <row r="396" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>743</v>
+        <v>724</v>
       </c>
       <c r="B396" t="s">
-        <v>744</v>
+        <v>725</v>
       </c>
       <c r="C396" t="s">
         <v>687</v>
       </c>
       <c r="D396" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="E396" t="s">
         <v>25</v>
@@ -20755,16 +21232,16 @@
     </row>
     <row r="397" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>745</v>
+        <v>726</v>
       </c>
       <c r="B397" t="s">
-        <v>746</v>
+        <v>727</v>
       </c>
       <c r="C397" t="s">
         <v>687</v>
       </c>
       <c r="D397" t="s">
-        <v>747</v>
+        <v>723</v>
       </c>
       <c r="E397" t="s">
         <v>25</v>
@@ -20793,16 +21270,16 @@
     </row>
     <row r="398" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>748</v>
+        <v>728</v>
       </c>
       <c r="B398" t="s">
-        <v>749</v>
+        <v>729</v>
       </c>
       <c r="C398" t="s">
         <v>687</v>
       </c>
       <c r="D398" t="s">
-        <v>747</v>
+        <v>723</v>
       </c>
       <c r="E398" t="s">
         <v>25</v>
@@ -20831,16 +21308,16 @@
     </row>
     <row r="399" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="B399" t="s">
-        <v>751</v>
+        <v>731</v>
       </c>
       <c r="C399" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D399" t="s">
-        <v>753</v>
+        <v>723</v>
       </c>
       <c r="E399" t="s">
         <v>25</v>
@@ -20869,16 +21346,16 @@
     </row>
     <row r="400" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>754</v>
+        <v>732</v>
       </c>
       <c r="B400" t="s">
-        <v>755</v>
+        <v>733</v>
       </c>
       <c r="C400" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D400" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E400" t="s">
         <v>25</v>
@@ -20907,16 +21384,16 @@
     </row>
     <row r="401" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>756</v>
+        <v>735</v>
       </c>
       <c r="B401" t="s">
-        <v>757</v>
+        <v>736</v>
       </c>
       <c r="C401" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D401" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E401" t="s">
         <v>25</v>
@@ -20945,16 +21422,16 @@
     </row>
     <row r="402" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>758</v>
+        <v>737</v>
       </c>
       <c r="B402" t="s">
-        <v>759</v>
+        <v>738</v>
       </c>
       <c r="C402" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D402" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E402" t="s">
         <v>25</v>
@@ -20983,16 +21460,16 @@
     </row>
     <row r="403" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>760</v>
+        <v>739</v>
       </c>
       <c r="B403" t="s">
-        <v>761</v>
+        <v>740</v>
       </c>
       <c r="C403" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D403" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E403" t="s">
         <v>25</v>
@@ -21021,16 +21498,16 @@
     </row>
     <row r="404" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>762</v>
+        <v>741</v>
       </c>
       <c r="B404" t="s">
-        <v>763</v>
+        <v>742</v>
       </c>
       <c r="C404" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D404" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E404" t="s">
         <v>25</v>
@@ -21059,16 +21536,16 @@
     </row>
     <row r="405" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>764</v>
+        <v>743</v>
       </c>
       <c r="B405" t="s">
-        <v>765</v>
+        <v>744</v>
       </c>
       <c r="C405" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D405" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E405" t="s">
         <v>25</v>
@@ -21097,16 +21574,16 @@
     </row>
     <row r="406" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="B406" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="C406" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D406" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="E406" t="s">
         <v>25</v>
@@ -21135,16 +21612,16 @@
     </row>
     <row r="407" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>768</v>
+        <v>748</v>
       </c>
       <c r="B407" t="s">
-        <v>769</v>
+        <v>749</v>
       </c>
       <c r="C407" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D407" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="E407" t="s">
         <v>25</v>
@@ -21173,10 +21650,10 @@
     </row>
     <row r="408" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="B408" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="C408" t="s">
         <v>752</v>
@@ -21211,10 +21688,10 @@
     </row>
     <row r="409" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="B409" t="s">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="C409" t="s">
         <v>752</v>
@@ -21249,10 +21726,10 @@
     </row>
     <row r="410" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="B410" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="C410" t="s">
         <v>752</v>
@@ -21287,10 +21764,10 @@
     </row>
     <row r="411" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="B411" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="C411" t="s">
         <v>752</v>
@@ -21325,16 +21802,16 @@
     </row>
     <row r="412" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>778</v>
+        <v>760</v>
       </c>
       <c r="B412" t="s">
-        <v>779</v>
+        <v>761</v>
       </c>
       <c r="C412" t="s">
         <v>752</v>
       </c>
       <c r="D412" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="E412" t="s">
         <v>25</v>
@@ -21363,16 +21840,16 @@
     </row>
     <row r="413" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="B413" t="s">
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="C413" t="s">
         <v>752</v>
       </c>
       <c r="D413" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="E413" t="s">
         <v>25</v>
@@ -21401,16 +21878,16 @@
     </row>
     <row r="414" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="B414" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="C414" t="s">
         <v>752</v>
       </c>
       <c r="D414" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="E414" t="s">
         <v>25</v>
@@ -21439,16 +21916,16 @@
     </row>
     <row r="415" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="B415" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="C415" t="s">
         <v>752</v>
       </c>
       <c r="D415" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="E415" t="s">
         <v>25</v>
@@ -21477,16 +21954,16 @@
     </row>
     <row r="416" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="B416" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="C416" t="s">
         <v>752</v>
       </c>
       <c r="D416" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="E416" t="s">
         <v>25</v>
@@ -21515,16 +21992,16 @@
     </row>
     <row r="417" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="B417" t="s">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="C417" t="s">
         <v>752</v>
       </c>
       <c r="D417" t="s">
-        <v>202</v>
+        <v>753</v>
       </c>
       <c r="E417" t="s">
         <v>25</v>
@@ -21553,16 +22030,16 @@
     </row>
     <row r="418" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="B418" t="s">
-        <v>792</v>
+        <v>773</v>
       </c>
       <c r="C418" t="s">
         <v>752</v>
       </c>
       <c r="D418" t="s">
-        <v>202</v>
+        <v>753</v>
       </c>
       <c r="E418" t="s">
         <v>25</v>
@@ -21591,16 +22068,16 @@
     </row>
     <row r="419" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>793</v>
+        <v>774</v>
       </c>
       <c r="B419" t="s">
-        <v>794</v>
+        <v>775</v>
       </c>
       <c r="C419" t="s">
         <v>752</v>
       </c>
       <c r="D419" t="s">
-        <v>202</v>
+        <v>753</v>
       </c>
       <c r="E419" t="s">
         <v>25</v>
@@ -21629,16 +22106,16 @@
     </row>
     <row r="420" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="B420" t="s">
-        <v>796</v>
+        <v>777</v>
       </c>
       <c r="C420" t="s">
         <v>752</v>
       </c>
       <c r="D420" t="s">
-        <v>797</v>
+        <v>753</v>
       </c>
       <c r="E420" t="s">
         <v>25</v>
@@ -21667,16 +22144,16 @@
     </row>
     <row r="421" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>798</v>
+        <v>778</v>
       </c>
       <c r="B421" t="s">
-        <v>799</v>
+        <v>779</v>
       </c>
       <c r="C421" t="s">
         <v>752</v>
       </c>
       <c r="D421" t="s">
-        <v>797</v>
+        <v>780</v>
       </c>
       <c r="E421" t="s">
         <v>25</v>
@@ -21705,16 +22182,16 @@
     </row>
     <row r="422" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>800</v>
+        <v>781</v>
       </c>
       <c r="B422" t="s">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="C422" t="s">
         <v>752</v>
       </c>
       <c r="D422" t="s">
-        <v>802</v>
+        <v>780</v>
       </c>
       <c r="E422" t="s">
         <v>25</v>
@@ -21743,16 +22220,16 @@
     </row>
     <row r="423" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>803</v>
+        <v>783</v>
       </c>
       <c r="B423" t="s">
-        <v>804</v>
+        <v>784</v>
       </c>
       <c r="C423" t="s">
         <v>752</v>
       </c>
       <c r="D423" t="s">
-        <v>802</v>
+        <v>780</v>
       </c>
       <c r="E423" t="s">
         <v>25</v>
@@ -21781,16 +22258,16 @@
     </row>
     <row r="424" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>805</v>
+        <v>785</v>
       </c>
       <c r="B424" t="s">
-        <v>806</v>
+        <v>786</v>
       </c>
       <c r="C424" t="s">
         <v>752</v>
       </c>
       <c r="D424" t="s">
-        <v>802</v>
+        <v>780</v>
       </c>
       <c r="E424" t="s">
         <v>25</v>
@@ -21819,16 +22296,16 @@
     </row>
     <row r="425" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>807</v>
+        <v>787</v>
       </c>
       <c r="B425" t="s">
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="C425" t="s">
         <v>752</v>
       </c>
       <c r="D425" t="s">
-        <v>809</v>
+        <v>780</v>
       </c>
       <c r="E425" t="s">
         <v>25</v>
@@ -21857,16 +22334,16 @@
     </row>
     <row r="426" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="B426" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="C426" t="s">
         <v>752</v>
       </c>
       <c r="D426" t="s">
-        <v>809</v>
+        <v>202</v>
       </c>
       <c r="E426" t="s">
         <v>25</v>
@@ -21895,16 +22372,16 @@
     </row>
     <row r="427" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>812</v>
+        <v>791</v>
       </c>
       <c r="B427" t="s">
-        <v>813</v>
+        <v>792</v>
       </c>
       <c r="C427" t="s">
         <v>752</v>
       </c>
       <c r="D427" t="s">
-        <v>809</v>
+        <v>202</v>
       </c>
       <c r="E427" t="s">
         <v>25</v>
@@ -21933,16 +22410,16 @@
     </row>
     <row r="428" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>814</v>
+        <v>793</v>
       </c>
       <c r="B428" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="C428" t="s">
         <v>752</v>
       </c>
       <c r="D428" t="s">
-        <v>809</v>
+        <v>202</v>
       </c>
       <c r="E428" t="s">
         <v>25</v>
@@ -21971,16 +22448,16 @@
     </row>
     <row r="429" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>816</v>
+        <v>795</v>
       </c>
       <c r="B429" t="s">
-        <v>817</v>
+        <v>796</v>
       </c>
       <c r="C429" t="s">
         <v>752</v>
       </c>
       <c r="D429" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="E429" t="s">
         <v>25</v>
@@ -22009,16 +22486,16 @@
     </row>
     <row r="430" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>818</v>
+        <v>798</v>
       </c>
       <c r="B430" t="s">
-        <v>819</v>
+        <v>799</v>
       </c>
       <c r="C430" t="s">
         <v>752</v>
       </c>
       <c r="D430" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="E430" t="s">
         <v>25</v>
@@ -22047,16 +22524,16 @@
     </row>
     <row r="431" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B431" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="C431" t="s">
         <v>752</v>
       </c>
       <c r="D431" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="E431" t="s">
         <v>25</v>
@@ -22085,16 +22562,16 @@
     </row>
     <row r="432" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>822</v>
+        <v>803</v>
       </c>
       <c r="B432" t="s">
-        <v>823</v>
+        <v>804</v>
       </c>
       <c r="C432" t="s">
         <v>752</v>
       </c>
       <c r="D432" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="E432" t="s">
         <v>25</v>
@@ -22123,16 +22600,16 @@
     </row>
     <row r="433" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>824</v>
+        <v>805</v>
       </c>
       <c r="B433" t="s">
-        <v>825</v>
+        <v>806</v>
       </c>
       <c r="C433" t="s">
         <v>752</v>
       </c>
       <c r="D433" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="E433" t="s">
         <v>25</v>
@@ -22161,10 +22638,10 @@
     </row>
     <row r="434" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>826</v>
+        <v>807</v>
       </c>
       <c r="B434" t="s">
-        <v>827</v>
+        <v>808</v>
       </c>
       <c r="C434" t="s">
         <v>752</v>
@@ -22199,10 +22676,10 @@
     </row>
     <row r="435" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>828</v>
+        <v>810</v>
       </c>
       <c r="B435" t="s">
-        <v>829</v>
+        <v>811</v>
       </c>
       <c r="C435" t="s">
         <v>752</v>
@@ -22237,10 +22714,10 @@
     </row>
     <row r="436" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>830</v>
+        <v>812</v>
       </c>
       <c r="B436" t="s">
-        <v>831</v>
+        <v>813</v>
       </c>
       <c r="C436" t="s">
         <v>752</v>
@@ -22275,16 +22752,16 @@
     </row>
     <row r="437" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>832</v>
+        <v>814</v>
       </c>
       <c r="B437" t="s">
-        <v>833</v>
+        <v>815</v>
       </c>
       <c r="C437" t="s">
         <v>752</v>
       </c>
       <c r="D437" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="E437" t="s">
         <v>25</v>
@@ -22313,16 +22790,16 @@
     </row>
     <row r="438" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>835</v>
+        <v>816</v>
       </c>
       <c r="B438" t="s">
-        <v>836</v>
+        <v>817</v>
       </c>
       <c r="C438" t="s">
         <v>752</v>
       </c>
       <c r="D438" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="E438" t="s">
         <v>25</v>
@@ -22351,16 +22828,16 @@
     </row>
     <row r="439" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>837</v>
+        <v>818</v>
       </c>
       <c r="B439" t="s">
-        <v>838</v>
+        <v>819</v>
       </c>
       <c r="C439" t="s">
         <v>752</v>
       </c>
       <c r="D439" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="E439" t="s">
         <v>25</v>
@@ -22389,16 +22866,16 @@
     </row>
     <row r="440" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>839</v>
+        <v>820</v>
       </c>
       <c r="B440" t="s">
-        <v>840</v>
+        <v>821</v>
       </c>
       <c r="C440" t="s">
         <v>752</v>
       </c>
       <c r="D440" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="E440" t="s">
         <v>25</v>
@@ -22427,16 +22904,16 @@
     </row>
     <row r="441" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>841</v>
+        <v>822</v>
       </c>
       <c r="B441" t="s">
-        <v>842</v>
+        <v>823</v>
       </c>
       <c r="C441" t="s">
         <v>752</v>
       </c>
       <c r="D441" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="E441" t="s">
         <v>25</v>
@@ -22465,16 +22942,16 @@
     </row>
     <row r="442" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>843</v>
+        <v>824</v>
       </c>
       <c r="B442" t="s">
-        <v>844</v>
+        <v>825</v>
       </c>
       <c r="C442" t="s">
         <v>752</v>
       </c>
       <c r="D442" t="s">
-        <v>845</v>
+        <v>809</v>
       </c>
       <c r="E442" t="s">
         <v>25</v>
@@ -22503,16 +22980,16 @@
     </row>
     <row r="443" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>846</v>
+        <v>826</v>
       </c>
       <c r="B443" t="s">
-        <v>847</v>
+        <v>827</v>
       </c>
       <c r="C443" t="s">
         <v>752</v>
       </c>
       <c r="D443" t="s">
-        <v>845</v>
+        <v>809</v>
       </c>
       <c r="E443" t="s">
         <v>25</v>
@@ -22541,16 +23018,16 @@
     </row>
     <row r="444" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>848</v>
+        <v>828</v>
       </c>
       <c r="B444" t="s">
-        <v>849</v>
+        <v>829</v>
       </c>
       <c r="C444" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D444" t="s">
-        <v>851</v>
+        <v>809</v>
       </c>
       <c r="E444" t="s">
         <v>25</v>
@@ -22579,16 +23056,16 @@
     </row>
     <row r="445" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>852</v>
+        <v>830</v>
       </c>
       <c r="B445" t="s">
-        <v>853</v>
+        <v>831</v>
       </c>
       <c r="C445" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D445" t="s">
-        <v>851</v>
+        <v>809</v>
       </c>
       <c r="E445" t="s">
         <v>25</v>
@@ -22617,16 +23094,16 @@
     </row>
     <row r="446" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>854</v>
+        <v>832</v>
       </c>
       <c r="B446" t="s">
-        <v>855</v>
+        <v>833</v>
       </c>
       <c r="C446" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D446" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="E446" t="s">
         <v>25</v>
@@ -22655,16 +23132,16 @@
     </row>
     <row r="447" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>856</v>
+        <v>835</v>
       </c>
       <c r="B447" t="s">
-        <v>857</v>
+        <v>836</v>
       </c>
       <c r="C447" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D447" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="E447" t="s">
         <v>25</v>
@@ -22693,16 +23170,16 @@
     </row>
     <row r="448" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>858</v>
+        <v>837</v>
       </c>
       <c r="B448" t="s">
-        <v>859</v>
+        <v>838</v>
       </c>
       <c r="C448" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D448" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="E448" t="s">
         <v>25</v>
@@ -22731,16 +23208,16 @@
     </row>
     <row r="449" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>860</v>
+        <v>839</v>
       </c>
       <c r="B449" t="s">
-        <v>861</v>
+        <v>840</v>
       </c>
       <c r="C449" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D449" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="E449" t="s">
         <v>25</v>
@@ -22769,16 +23246,16 @@
     </row>
     <row r="450" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>862</v>
+        <v>841</v>
       </c>
       <c r="B450" t="s">
-        <v>863</v>
+        <v>842</v>
       </c>
       <c r="C450" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D450" t="s">
-        <v>864</v>
+        <v>834</v>
       </c>
       <c r="E450" t="s">
         <v>25</v>
@@ -22807,16 +23284,16 @@
     </row>
     <row r="451" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>865</v>
+        <v>843</v>
       </c>
       <c r="B451" t="s">
-        <v>866</v>
+        <v>844</v>
       </c>
       <c r="C451" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D451" t="s">
-        <v>864</v>
+        <v>845</v>
       </c>
       <c r="E451" t="s">
         <v>25</v>
@@ -22845,16 +23322,16 @@
     </row>
     <row r="452" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>867</v>
+        <v>846</v>
       </c>
       <c r="B452" t="s">
-        <v>868</v>
+        <v>847</v>
       </c>
       <c r="C452" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D452" t="s">
-        <v>864</v>
+        <v>845</v>
       </c>
       <c r="E452" t="s">
         <v>25</v>
@@ -22883,16 +23360,16 @@
     </row>
     <row r="453" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>869</v>
+        <v>848</v>
       </c>
       <c r="B453" t="s">
-        <v>870</v>
+        <v>849</v>
       </c>
       <c r="C453" t="s">
         <v>850</v>
       </c>
       <c r="D453" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="E453" t="s">
         <v>25</v>
@@ -22921,16 +23398,16 @@
     </row>
     <row r="454" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>871</v>
+        <v>852</v>
       </c>
       <c r="B454" t="s">
-        <v>872</v>
+        <v>853</v>
       </c>
       <c r="C454" t="s">
         <v>850</v>
       </c>
       <c r="D454" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="E454" t="s">
         <v>25</v>
@@ -22959,16 +23436,16 @@
     </row>
     <row r="455" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>873</v>
+        <v>854</v>
       </c>
       <c r="B455" t="s">
-        <v>874</v>
+        <v>855</v>
       </c>
       <c r="C455" t="s">
         <v>850</v>
       </c>
       <c r="D455" t="s">
-        <v>875</v>
+        <v>851</v>
       </c>
       <c r="E455" t="s">
         <v>25</v>
@@ -22997,16 +23474,16 @@
     </row>
     <row r="456" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>876</v>
+        <v>856</v>
       </c>
       <c r="B456" t="s">
-        <v>877</v>
+        <v>857</v>
       </c>
       <c r="C456" t="s">
         <v>850</v>
       </c>
       <c r="D456" t="s">
-        <v>875</v>
+        <v>851</v>
       </c>
       <c r="E456" t="s">
         <v>25</v>
@@ -23035,16 +23512,16 @@
     </row>
     <row r="457" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>878</v>
+        <v>858</v>
       </c>
       <c r="B457" t="s">
-        <v>879</v>
+        <v>859</v>
       </c>
       <c r="C457" t="s">
         <v>850</v>
       </c>
       <c r="D457" t="s">
-        <v>875</v>
+        <v>851</v>
       </c>
       <c r="E457" t="s">
         <v>25</v>
@@ -23073,16 +23550,16 @@
     </row>
     <row r="458" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>880</v>
+        <v>860</v>
       </c>
       <c r="B458" t="s">
-        <v>881</v>
+        <v>861</v>
       </c>
       <c r="C458" t="s">
         <v>850</v>
       </c>
       <c r="D458" t="s">
-        <v>882</v>
+        <v>851</v>
       </c>
       <c r="E458" t="s">
         <v>25</v>
@@ -23111,16 +23588,16 @@
     </row>
     <row r="459" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>883</v>
+        <v>862</v>
       </c>
       <c r="B459" t="s">
-        <v>884</v>
+        <v>863</v>
       </c>
       <c r="C459" t="s">
         <v>850</v>
       </c>
       <c r="D459" t="s">
-        <v>882</v>
+        <v>864</v>
       </c>
       <c r="E459" t="s">
         <v>25</v>
@@ -23149,16 +23626,16 @@
     </row>
     <row r="460" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>885</v>
+        <v>865</v>
       </c>
       <c r="B460" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
       <c r="C460" t="s">
         <v>850</v>
       </c>
       <c r="D460" t="s">
-        <v>887</v>
+        <v>864</v>
       </c>
       <c r="E460" t="s">
         <v>25</v>
@@ -23187,16 +23664,16 @@
     </row>
     <row r="461" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>888</v>
+        <v>867</v>
       </c>
       <c r="B461" t="s">
-        <v>889</v>
+        <v>868</v>
       </c>
       <c r="C461" t="s">
         <v>850</v>
       </c>
       <c r="D461" t="s">
-        <v>887</v>
+        <v>864</v>
       </c>
       <c r="E461" t="s">
         <v>25</v>
@@ -23225,16 +23702,16 @@
     </row>
     <row r="462" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>890</v>
+        <v>869</v>
       </c>
       <c r="B462" t="s">
-        <v>891</v>
+        <v>870</v>
       </c>
       <c r="C462" t="s">
         <v>850</v>
       </c>
       <c r="D462" t="s">
-        <v>887</v>
+        <v>864</v>
       </c>
       <c r="E462" t="s">
         <v>25</v>
@@ -23263,16 +23740,16 @@
     </row>
     <row r="463" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>892</v>
+        <v>871</v>
       </c>
       <c r="B463" t="s">
-        <v>893</v>
+        <v>872</v>
       </c>
       <c r="C463" t="s">
         <v>850</v>
       </c>
       <c r="D463" t="s">
-        <v>887</v>
+        <v>864</v>
       </c>
       <c r="E463" t="s">
         <v>25</v>
@@ -23301,16 +23778,16 @@
     </row>
     <row r="464" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>894</v>
+        <v>873</v>
       </c>
       <c r="B464" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="C464" t="s">
         <v>850</v>
       </c>
       <c r="D464" t="s">
-        <v>896</v>
+        <v>875</v>
       </c>
       <c r="E464" t="s">
         <v>25</v>
@@ -23339,16 +23816,16 @@
     </row>
     <row r="465" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="B465" t="s">
-        <v>898</v>
+        <v>877</v>
       </c>
       <c r="C465" t="s">
         <v>850</v>
       </c>
       <c r="D465" t="s">
-        <v>896</v>
+        <v>875</v>
       </c>
       <c r="E465" t="s">
         <v>25</v>
@@ -23377,16 +23854,16 @@
     </row>
     <row r="466" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>899</v>
+        <v>878</v>
       </c>
       <c r="B466" t="s">
-        <v>900</v>
+        <v>879</v>
       </c>
       <c r="C466" t="s">
         <v>850</v>
       </c>
       <c r="D466" t="s">
-        <v>896</v>
+        <v>875</v>
       </c>
       <c r="E466" t="s">
         <v>25</v>
@@ -23415,16 +23892,16 @@
     </row>
     <row r="467" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>901</v>
+        <v>880</v>
       </c>
       <c r="B467" t="s">
-        <v>902</v>
+        <v>881</v>
       </c>
       <c r="C467" t="s">
         <v>850</v>
       </c>
       <c r="D467" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
       <c r="E467" t="s">
         <v>25</v>
@@ -23453,16 +23930,16 @@
     </row>
     <row r="468" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>903</v>
+        <v>883</v>
       </c>
       <c r="B468" t="s">
-        <v>904</v>
+        <v>884</v>
       </c>
       <c r="C468" t="s">
         <v>850</v>
       </c>
       <c r="D468" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
       <c r="E468" t="s">
         <v>25</v>
@@ -23491,16 +23968,16 @@
     </row>
     <row r="469" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>905</v>
+        <v>885</v>
       </c>
       <c r="B469" t="s">
-        <v>906</v>
+        <v>886</v>
       </c>
       <c r="C469" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D469" t="s">
-        <v>25</v>
+        <v>887</v>
       </c>
       <c r="E469" t="s">
         <v>25</v>
@@ -23529,16 +24006,16 @@
     </row>
     <row r="470" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>908</v>
+        <v>888</v>
       </c>
       <c r="B470" t="s">
-        <v>909</v>
+        <v>889</v>
       </c>
       <c r="C470" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D470" t="s">
-        <v>25</v>
+        <v>887</v>
       </c>
       <c r="E470" t="s">
         <v>25</v>
@@ -23567,16 +24044,16 @@
     </row>
     <row r="471" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="B471" t="s">
-        <v>911</v>
+        <v>891</v>
       </c>
       <c r="C471" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D471" t="s">
-        <v>25</v>
+        <v>887</v>
       </c>
       <c r="E471" t="s">
         <v>25</v>
@@ -23605,16 +24082,16 @@
     </row>
     <row r="472" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>912</v>
+        <v>892</v>
       </c>
       <c r="B472" t="s">
-        <v>913</v>
+        <v>893</v>
       </c>
       <c r="C472" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D472" t="s">
-        <v>25</v>
+        <v>887</v>
       </c>
       <c r="E472" t="s">
         <v>25</v>
@@ -23643,16 +24120,16 @@
     </row>
     <row r="473" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>914</v>
+        <v>894</v>
       </c>
       <c r="B473" t="s">
-        <v>915</v>
+        <v>895</v>
       </c>
       <c r="C473" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D473" t="s">
-        <v>25</v>
+        <v>896</v>
       </c>
       <c r="E473" t="s">
         <v>25</v>
@@ -23681,16 +24158,16 @@
     </row>
     <row r="474" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>916</v>
+        <v>897</v>
       </c>
       <c r="B474" t="s">
-        <v>917</v>
+        <v>898</v>
       </c>
       <c r="C474" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D474" t="s">
-        <v>25</v>
+        <v>896</v>
       </c>
       <c r="E474" t="s">
         <v>25</v>
@@ -23719,16 +24196,16 @@
     </row>
     <row r="475" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="B475" t="s">
-        <v>919</v>
+        <v>900</v>
       </c>
       <c r="C475" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D475" t="s">
-        <v>25</v>
+        <v>896</v>
       </c>
       <c r="E475" t="s">
         <v>25</v>
@@ -23757,16 +24234,16 @@
     </row>
     <row r="476" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>920</v>
+        <v>901</v>
       </c>
       <c r="B476" t="s">
-        <v>921</v>
+        <v>902</v>
       </c>
       <c r="C476" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D476" t="s">
-        <v>25</v>
+        <v>896</v>
       </c>
       <c r="E476" t="s">
         <v>25</v>
@@ -23795,16 +24272,16 @@
     </row>
     <row r="477" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>922</v>
+        <v>903</v>
       </c>
       <c r="B477" t="s">
-        <v>923</v>
+        <v>904</v>
       </c>
       <c r="C477" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D477" t="s">
-        <v>25</v>
+        <v>896</v>
       </c>
       <c r="E477" t="s">
         <v>25</v>
@@ -23833,10 +24310,10 @@
     </row>
     <row r="478" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="B478" t="s">
-        <v>925</v>
+        <v>906</v>
       </c>
       <c r="C478" t="s">
         <v>907</v>
@@ -23871,10 +24348,10 @@
     </row>
     <row r="479" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="B479" t="s">
-        <v>927</v>
+        <v>909</v>
       </c>
       <c r="C479" t="s">
         <v>907</v>
@@ -23909,10 +24386,10 @@
     </row>
     <row r="480" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="B480" t="s">
-        <v>929</v>
+        <v>911</v>
       </c>
       <c r="C480" t="s">
         <v>907</v>
@@ -23947,10 +24424,10 @@
     </row>
     <row r="481" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="B481" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="C481" t="s">
         <v>907</v>
@@ -23985,10 +24462,10 @@
     </row>
     <row r="482" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="B482" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="C482" t="s">
         <v>907</v>
@@ -24023,10 +24500,10 @@
     </row>
     <row r="483" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>934</v>
+        <v>916</v>
       </c>
       <c r="B483" t="s">
-        <v>935</v>
+        <v>917</v>
       </c>
       <c r="C483" t="s">
         <v>907</v>
@@ -24061,16 +24538,16 @@
     </row>
     <row r="484" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>936</v>
+        <v>918</v>
       </c>
       <c r="B484" t="s">
-        <v>937</v>
+        <v>919</v>
       </c>
       <c r="C484" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D484" t="s">
-        <v>939</v>
+        <v>25</v>
       </c>
       <c r="E484" t="s">
         <v>25</v>
@@ -24099,16 +24576,16 @@
     </row>
     <row r="485" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>940</v>
+        <v>920</v>
       </c>
       <c r="B485" t="s">
-        <v>941</v>
+        <v>921</v>
       </c>
       <c r="C485" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D485" t="s">
-        <v>939</v>
+        <v>25</v>
       </c>
       <c r="E485" t="s">
         <v>25</v>
@@ -24137,16 +24614,16 @@
     </row>
     <row r="486" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>942</v>
+        <v>922</v>
       </c>
       <c r="B486" t="s">
-        <v>943</v>
+        <v>923</v>
       </c>
       <c r="C486" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D486" t="s">
-        <v>939</v>
+        <v>25</v>
       </c>
       <c r="E486" t="s">
         <v>25</v>
@@ -24175,16 +24652,16 @@
     </row>
     <row r="487" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="B487" t="s">
-        <v>945</v>
+        <v>925</v>
       </c>
       <c r="C487" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D487" t="s">
-        <v>939</v>
+        <v>25</v>
       </c>
       <c r="E487" t="s">
         <v>25</v>
@@ -24213,16 +24690,16 @@
     </row>
     <row r="488" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
       <c r="B488" t="s">
-        <v>947</v>
+        <v>927</v>
       </c>
       <c r="C488" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D488" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E488" t="s">
         <v>25</v>
@@ -24251,16 +24728,16 @@
     </row>
     <row r="489" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>949</v>
+        <v>928</v>
       </c>
       <c r="B489" t="s">
-        <v>950</v>
+        <v>929</v>
       </c>
       <c r="C489" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D489" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E489" t="s">
         <v>25</v>
@@ -24289,16 +24766,16 @@
     </row>
     <row r="490" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>951</v>
+        <v>930</v>
       </c>
       <c r="B490" t="s">
-        <v>952</v>
+        <v>931</v>
       </c>
       <c r="C490" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D490" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E490" t="s">
         <v>25</v>
@@ -24327,16 +24804,16 @@
     </row>
     <row r="491" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>953</v>
+        <v>932</v>
       </c>
       <c r="B491" t="s">
-        <v>954</v>
+        <v>933</v>
       </c>
       <c r="C491" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D491" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E491" t="s">
         <v>25</v>
@@ -24365,16 +24842,16 @@
     </row>
     <row r="492" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>955</v>
+        <v>934</v>
       </c>
       <c r="B492" t="s">
-        <v>956</v>
+        <v>935</v>
       </c>
       <c r="C492" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D492" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E492" t="s">
         <v>25</v>
@@ -24403,16 +24880,16 @@
     </row>
     <row r="493" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>957</v>
+        <v>936</v>
       </c>
       <c r="B493" t="s">
-        <v>958</v>
+        <v>937</v>
       </c>
       <c r="C493" t="s">
         <v>938</v>
       </c>
       <c r="D493" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="E493" t="s">
         <v>25</v>
@@ -24441,16 +24918,16 @@
     </row>
     <row r="494" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>959</v>
+        <v>940</v>
       </c>
       <c r="B494" t="s">
-        <v>960</v>
+        <v>941</v>
       </c>
       <c r="C494" t="s">
         <v>938</v>
       </c>
       <c r="D494" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="E494" t="s">
         <v>25</v>
@@ -24479,16 +24956,16 @@
     </row>
     <row r="495" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>961</v>
+        <v>942</v>
       </c>
       <c r="B495" t="s">
-        <v>962</v>
+        <v>943</v>
       </c>
       <c r="C495" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D495" t="s">
-        <v>964</v>
+        <v>939</v>
       </c>
       <c r="E495" t="s">
         <v>25</v>
@@ -24517,16 +24994,16 @@
     </row>
     <row r="496" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>965</v>
+        <v>944</v>
       </c>
       <c r="B496" t="s">
-        <v>966</v>
+        <v>945</v>
       </c>
       <c r="C496" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D496" t="s">
-        <v>964</v>
+        <v>939</v>
       </c>
       <c r="E496" t="s">
         <v>25</v>
@@ -24555,16 +25032,16 @@
     </row>
     <row r="497" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>967</v>
+        <v>946</v>
       </c>
       <c r="B497" t="s">
-        <v>968</v>
+        <v>947</v>
       </c>
       <c r="C497" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D497" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E497" t="s">
         <v>25</v>
@@ -24593,16 +25070,16 @@
     </row>
     <row r="498" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="B498" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="C498" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D498" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E498" t="s">
         <v>25</v>
@@ -24631,16 +25108,16 @@
     </row>
     <row r="499" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>971</v>
+        <v>951</v>
       </c>
       <c r="B499" t="s">
-        <v>972</v>
+        <v>952</v>
       </c>
       <c r="C499" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D499" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E499" t="s">
         <v>25</v>
@@ -24669,16 +25146,16 @@
     </row>
     <row r="500" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>973</v>
+        <v>953</v>
       </c>
       <c r="B500" t="s">
-        <v>974</v>
+        <v>954</v>
       </c>
       <c r="C500" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D500" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E500" t="s">
         <v>25</v>
@@ -24707,16 +25184,16 @@
     </row>
     <row r="501" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>975</v>
+        <v>955</v>
       </c>
       <c r="B501" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="C501" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D501" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E501" t="s">
         <v>25</v>
@@ -24745,16 +25222,16 @@
     </row>
     <row r="502" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="B502" t="s">
-        <v>978</v>
+        <v>958</v>
       </c>
       <c r="C502" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D502" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E502" t="s">
         <v>25</v>
@@ -24783,16 +25260,16 @@
     </row>
     <row r="503" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>979</v>
+        <v>959</v>
       </c>
       <c r="B503" t="s">
-        <v>980</v>
+        <v>960</v>
       </c>
       <c r="C503" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D503" t="s">
-        <v>981</v>
+        <v>948</v>
       </c>
       <c r="E503" t="s">
         <v>25</v>
@@ -24821,16 +25298,16 @@
     </row>
     <row r="504" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>982</v>
+        <v>961</v>
       </c>
       <c r="B504" t="s">
-        <v>983</v>
+        <v>962</v>
       </c>
       <c r="C504" t="s">
         <v>963</v>
       </c>
       <c r="D504" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
       <c r="E504" t="s">
         <v>25</v>
@@ -24859,16 +25336,16 @@
     </row>
     <row r="505" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>984</v>
+        <v>965</v>
       </c>
       <c r="B505" t="s">
-        <v>985</v>
+        <v>966</v>
       </c>
       <c r="C505" t="s">
         <v>963</v>
       </c>
       <c r="D505" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
       <c r="E505" t="s">
         <v>25</v>
@@ -24897,16 +25374,16 @@
     </row>
     <row r="506" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>986</v>
+        <v>967</v>
       </c>
       <c r="B506" t="s">
-        <v>987</v>
+        <v>968</v>
       </c>
       <c r="C506" t="s">
         <v>963</v>
       </c>
       <c r="D506" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
       <c r="E506" t="s">
         <v>25</v>
@@ -24935,16 +25412,16 @@
     </row>
     <row r="507" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>988</v>
+        <v>969</v>
       </c>
       <c r="B507" t="s">
-        <v>989</v>
+        <v>970</v>
       </c>
       <c r="C507" t="s">
         <v>963</v>
       </c>
       <c r="D507" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
       <c r="E507" t="s">
         <v>25</v>
@@ -24973,16 +25450,16 @@
     </row>
     <row r="508" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>990</v>
+        <v>971</v>
       </c>
       <c r="B508" t="s">
-        <v>991</v>
+        <v>972</v>
       </c>
       <c r="C508" t="s">
         <v>963</v>
       </c>
       <c r="D508" t="s">
-        <v>992</v>
+        <v>964</v>
       </c>
       <c r="E508" t="s">
         <v>25</v>
@@ -25011,16 +25488,16 @@
     </row>
     <row r="509" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="B509" t="s">
-        <v>994</v>
+        <v>974</v>
       </c>
       <c r="C509" t="s">
         <v>963</v>
       </c>
       <c r="D509" t="s">
-        <v>992</v>
+        <v>964</v>
       </c>
       <c r="E509" t="s">
         <v>25</v>
@@ -25049,16 +25526,16 @@
     </row>
     <row r="510" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>995</v>
+        <v>975</v>
       </c>
       <c r="B510" t="s">
-        <v>996</v>
+        <v>976</v>
       </c>
       <c r="C510" t="s">
         <v>963</v>
       </c>
       <c r="D510" t="s">
-        <v>997</v>
+        <v>964</v>
       </c>
       <c r="E510" t="s">
         <v>25</v>
@@ -25087,16 +25564,16 @@
     </row>
     <row r="511" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>998</v>
+        <v>977</v>
       </c>
       <c r="B511" t="s">
-        <v>999</v>
+        <v>978</v>
       </c>
       <c r="C511" t="s">
         <v>963</v>
       </c>
       <c r="D511" t="s">
-        <v>997</v>
+        <v>964</v>
       </c>
       <c r="E511" t="s">
         <v>25</v>
@@ -25125,16 +25602,16 @@
     </row>
     <row r="512" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1000</v>
+        <v>979</v>
       </c>
       <c r="B512" t="s">
-        <v>1001</v>
+        <v>980</v>
       </c>
       <c r="C512" t="s">
         <v>963</v>
       </c>
       <c r="D512" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E512" t="s">
         <v>25</v>
@@ -25163,16 +25640,16 @@
     </row>
     <row r="513" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>1002</v>
+        <v>982</v>
       </c>
       <c r="B513" t="s">
-        <v>1003</v>
+        <v>983</v>
       </c>
       <c r="C513" t="s">
         <v>963</v>
       </c>
       <c r="D513" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E513" t="s">
         <v>25</v>
@@ -25201,16 +25678,16 @@
     </row>
     <row r="514" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>1004</v>
+        <v>984</v>
       </c>
       <c r="B514" t="s">
-        <v>1005</v>
+        <v>985</v>
       </c>
       <c r="C514" t="s">
         <v>963</v>
       </c>
       <c r="D514" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E514" t="s">
         <v>25</v>
@@ -25239,16 +25716,16 @@
     </row>
     <row r="515" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>1006</v>
+        <v>986</v>
       </c>
       <c r="B515" t="s">
-        <v>1007</v>
+        <v>987</v>
       </c>
       <c r="C515" t="s">
         <v>963</v>
       </c>
       <c r="D515" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E515" t="s">
         <v>25</v>
@@ -25277,16 +25754,16 @@
     </row>
     <row r="516" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>1008</v>
+        <v>988</v>
       </c>
       <c r="B516" t="s">
-        <v>1009</v>
+        <v>989</v>
       </c>
       <c r="C516" t="s">
         <v>963</v>
       </c>
       <c r="D516" t="s">
-        <v>1010</v>
+        <v>981</v>
       </c>
       <c r="E516" t="s">
         <v>25</v>
@@ -25315,16 +25792,16 @@
     </row>
     <row r="517" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>1011</v>
+        <v>990</v>
       </c>
       <c r="B517" t="s">
-        <v>1012</v>
+        <v>991</v>
       </c>
       <c r="C517" t="s">
         <v>963</v>
       </c>
       <c r="D517" t="s">
-        <v>1010</v>
+        <v>992</v>
       </c>
       <c r="E517" t="s">
         <v>25</v>
@@ -25353,16 +25830,16 @@
     </row>
     <row r="518" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="B518" t="s">
-        <v>1014</v>
+        <v>994</v>
       </c>
       <c r="C518" t="s">
         <v>963</v>
       </c>
       <c r="D518" t="s">
-        <v>1010</v>
+        <v>992</v>
       </c>
       <c r="E518" t="s">
         <v>25</v>
@@ -25391,16 +25868,16 @@
     </row>
     <row r="519" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>1015</v>
+        <v>995</v>
       </c>
       <c r="B519" t="s">
-        <v>1016</v>
+        <v>996</v>
       </c>
       <c r="C519" t="s">
         <v>963</v>
       </c>
       <c r="D519" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="E519" t="s">
         <v>25</v>
@@ -25429,16 +25906,16 @@
     </row>
     <row r="520" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>1017</v>
+        <v>998</v>
       </c>
       <c r="B520" t="s">
-        <v>1018</v>
+        <v>999</v>
       </c>
       <c r="C520" t="s">
         <v>963</v>
       </c>
       <c r="D520" t="s">
-        <v>1019</v>
+        <v>997</v>
       </c>
       <c r="E520" t="s">
         <v>25</v>
@@ -25467,16 +25944,16 @@
     </row>
     <row r="521" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>1020</v>
+        <v>1000</v>
       </c>
       <c r="B521" t="s">
-        <v>1021</v>
+        <v>1001</v>
       </c>
       <c r="C521" t="s">
         <v>963</v>
       </c>
       <c r="D521" t="s">
-        <v>1019</v>
+        <v>997</v>
       </c>
       <c r="E521" t="s">
         <v>25</v>
@@ -25505,16 +25982,16 @@
     </row>
     <row r="522" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>1022</v>
+        <v>1002</v>
       </c>
       <c r="B522" t="s">
-        <v>1023</v>
+        <v>1003</v>
       </c>
       <c r="C522" t="s">
         <v>963</v>
       </c>
       <c r="D522" t="s">
-        <v>1019</v>
+        <v>997</v>
       </c>
       <c r="E522" t="s">
         <v>25</v>
@@ -25543,16 +26020,16 @@
     </row>
     <row r="523" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="B523" t="s">
-        <v>1025</v>
+        <v>1005</v>
       </c>
       <c r="C523" t="s">
         <v>963</v>
       </c>
       <c r="D523" t="s">
-        <v>1019</v>
+        <v>997</v>
       </c>
       <c r="E523" t="s">
         <v>25</v>
@@ -25581,16 +26058,16 @@
     </row>
     <row r="524" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1026</v>
+        <v>1006</v>
       </c>
       <c r="B524" t="s">
-        <v>1027</v>
+        <v>1007</v>
       </c>
       <c r="C524" t="s">
         <v>963</v>
       </c>
       <c r="D524" t="s">
-        <v>1028</v>
+        <v>997</v>
       </c>
       <c r="E524" t="s">
         <v>25</v>
@@ -25619,16 +26096,16 @@
     </row>
     <row r="525" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1029</v>
+        <v>1008</v>
       </c>
       <c r="B525" t="s">
-        <v>1030</v>
+        <v>1009</v>
       </c>
       <c r="C525" t="s">
         <v>963</v>
       </c>
       <c r="D525" t="s">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="E525" t="s">
         <v>25</v>
@@ -25657,16 +26134,16 @@
     </row>
     <row r="526" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1031</v>
+        <v>1011</v>
       </c>
       <c r="B526" t="s">
-        <v>1032</v>
+        <v>1012</v>
       </c>
       <c r="C526" t="s">
         <v>963</v>
       </c>
       <c r="D526" t="s">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="E526" t="s">
         <v>25</v>
@@ -25695,16 +26172,16 @@
     </row>
     <row r="527" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1033</v>
+        <v>1013</v>
       </c>
       <c r="B527" t="s">
-        <v>1034</v>
+        <v>1014</v>
       </c>
       <c r="C527" t="s">
         <v>963</v>
       </c>
       <c r="D527" t="s">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="E527" t="s">
         <v>25</v>
@@ -25733,16 +26210,16 @@
     </row>
     <row r="528" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1035</v>
+        <v>1015</v>
       </c>
       <c r="B528" t="s">
-        <v>1036</v>
+        <v>1016</v>
       </c>
       <c r="C528" t="s">
         <v>963</v>
       </c>
       <c r="D528" t="s">
-        <v>1037</v>
+        <v>1010</v>
       </c>
       <c r="E528" t="s">
         <v>25</v>
@@ -25771,16 +26248,16 @@
     </row>
     <row r="529" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1038</v>
+        <v>1017</v>
       </c>
       <c r="B529" t="s">
-        <v>1039</v>
+        <v>1018</v>
       </c>
       <c r="C529" t="s">
         <v>963</v>
       </c>
       <c r="D529" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="E529" t="s">
         <v>25</v>
@@ -25809,16 +26286,16 @@
     </row>
     <row r="530" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="B530" t="s">
-        <v>1041</v>
+        <v>1021</v>
       </c>
       <c r="C530" t="s">
         <v>963</v>
       </c>
       <c r="D530" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="E530" t="s">
         <v>25</v>
@@ -25847,16 +26324,16 @@
     </row>
     <row r="531" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1042</v>
+        <v>1022</v>
       </c>
       <c r="B531" t="s">
-        <v>1043</v>
+        <v>1023</v>
       </c>
       <c r="C531" t="s">
         <v>963</v>
       </c>
       <c r="D531" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="E531" t="s">
         <v>25</v>
@@ -25885,16 +26362,16 @@
     </row>
     <row r="532" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1044</v>
+        <v>1024</v>
       </c>
       <c r="B532" t="s">
-        <v>1045</v>
+        <v>1025</v>
       </c>
       <c r="C532" t="s">
         <v>963</v>
       </c>
       <c r="D532" t="s">
-        <v>1046</v>
+        <v>1019</v>
       </c>
       <c r="E532" t="s">
         <v>25</v>
@@ -25923,16 +26400,16 @@
     </row>
     <row r="533" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1047</v>
+        <v>1026</v>
       </c>
       <c r="B533" t="s">
-        <v>1048</v>
+        <v>1027</v>
       </c>
       <c r="C533" t="s">
         <v>963</v>
       </c>
       <c r="D533" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="E533" t="s">
         <v>25</v>
@@ -25961,16 +26438,16 @@
     </row>
     <row r="534" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1049</v>
+        <v>1029</v>
       </c>
       <c r="B534" t="s">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="C534" t="s">
         <v>963</v>
       </c>
       <c r="D534" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="E534" t="s">
         <v>25</v>
@@ -25999,16 +26476,16 @@
     </row>
     <row r="535" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1051</v>
+        <v>1031</v>
       </c>
       <c r="B535" t="s">
-        <v>1052</v>
+        <v>1032</v>
       </c>
       <c r="C535" t="s">
         <v>963</v>
       </c>
       <c r="D535" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="E535" t="s">
         <v>25</v>
@@ -26037,16 +26514,16 @@
     </row>
     <row r="536" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1053</v>
+        <v>1033</v>
       </c>
       <c r="B536" t="s">
-        <v>1054</v>
+        <v>1034</v>
       </c>
       <c r="C536" t="s">
         <v>963</v>
       </c>
       <c r="D536" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="E536" t="s">
         <v>25</v>
@@ -26075,49 +26552,391 @@
     </row>
     <row r="537" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1055</v>
+        <v>1035</v>
       </c>
       <c r="B537" t="s">
-        <v>1056</v>
+        <v>1036</v>
       </c>
       <c r="C537" t="s">
         <v>963</v>
       </c>
       <c r="D537" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E537" t="s">
+        <v>25</v>
+      </c>
+      <c r="F537" t="s">
+        <v>25</v>
+      </c>
+      <c r="G537" t="s">
+        <v>25</v>
+      </c>
+      <c r="H537" t="s">
+        <v>19</v>
+      </c>
+      <c r="I537" t="s">
+        <v>25</v>
+      </c>
+      <c r="J537" t="s">
+        <v>25</v>
+      </c>
+      <c r="K537" t="s">
+        <v>25</v>
+      </c>
+      <c r="L537" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="538" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C538" t="s">
+        <v>963</v>
+      </c>
+      <c r="D538" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E538" t="s">
+        <v>25</v>
+      </c>
+      <c r="F538" t="s">
+        <v>25</v>
+      </c>
+      <c r="G538" t="s">
+        <v>25</v>
+      </c>
+      <c r="H538" t="s">
+        <v>19</v>
+      </c>
+      <c r="I538" t="s">
+        <v>25</v>
+      </c>
+      <c r="J538" t="s">
+        <v>25</v>
+      </c>
+      <c r="K538" t="s">
+        <v>25</v>
+      </c>
+      <c r="L538" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="539" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C539" t="s">
+        <v>963</v>
+      </c>
+      <c r="D539" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E539" t="s">
+        <v>25</v>
+      </c>
+      <c r="F539" t="s">
+        <v>25</v>
+      </c>
+      <c r="G539" t="s">
+        <v>25</v>
+      </c>
+      <c r="H539" t="s">
+        <v>19</v>
+      </c>
+      <c r="I539" t="s">
+        <v>25</v>
+      </c>
+      <c r="J539" t="s">
+        <v>25</v>
+      </c>
+      <c r="K539" t="s">
+        <v>25</v>
+      </c>
+      <c r="L539" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="540" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C540" t="s">
+        <v>963</v>
+      </c>
+      <c r="D540" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E540" t="s">
+        <v>25</v>
+      </c>
+      <c r="F540" t="s">
+        <v>25</v>
+      </c>
+      <c r="G540" t="s">
+        <v>25</v>
+      </c>
+      <c r="H540" t="s">
+        <v>19</v>
+      </c>
+      <c r="I540" t="s">
+        <v>25</v>
+      </c>
+      <c r="J540" t="s">
+        <v>25</v>
+      </c>
+      <c r="K540" t="s">
+        <v>25</v>
+      </c>
+      <c r="L540" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="541" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C541" t="s">
+        <v>963</v>
+      </c>
+      <c r="D541" t="s">
         <v>1046</v>
       </c>
-      <c r="E537" t="s">
-        <v>25</v>
-      </c>
-      <c r="F537" t="s">
-        <v>25</v>
-      </c>
-      <c r="G537" t="s">
-        <v>25</v>
-      </c>
-      <c r="H537" t="s">
-        <v>19</v>
-      </c>
-      <c r="I537" t="s">
-        <v>25</v>
-      </c>
-      <c r="J537" t="s">
-        <v>25</v>
-      </c>
-      <c r="K537" t="s">
-        <v>25</v>
-      </c>
-      <c r="L537" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="538" spans="1:12" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="539" spans="1:12" ht="15.75" x14ac:dyDescent="0.25"/>
+      <c r="E541" t="s">
+        <v>25</v>
+      </c>
+      <c r="F541" t="s">
+        <v>25</v>
+      </c>
+      <c r="G541" t="s">
+        <v>25</v>
+      </c>
+      <c r="H541" t="s">
+        <v>19</v>
+      </c>
+      <c r="I541" t="s">
+        <v>25</v>
+      </c>
+      <c r="J541" t="s">
+        <v>25</v>
+      </c>
+      <c r="K541" t="s">
+        <v>25</v>
+      </c>
+      <c r="L541" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="542" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C542" t="s">
+        <v>963</v>
+      </c>
+      <c r="D542" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E542" t="s">
+        <v>25</v>
+      </c>
+      <c r="F542" t="s">
+        <v>25</v>
+      </c>
+      <c r="G542" t="s">
+        <v>25</v>
+      </c>
+      <c r="H542" t="s">
+        <v>19</v>
+      </c>
+      <c r="I542" t="s">
+        <v>25</v>
+      </c>
+      <c r="J542" t="s">
+        <v>25</v>
+      </c>
+      <c r="K542" t="s">
+        <v>25</v>
+      </c>
+      <c r="L542" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="543" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C543" t="s">
+        <v>963</v>
+      </c>
+      <c r="D543" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E543" t="s">
+        <v>25</v>
+      </c>
+      <c r="F543" t="s">
+        <v>25</v>
+      </c>
+      <c r="G543" t="s">
+        <v>25</v>
+      </c>
+      <c r="H543" t="s">
+        <v>19</v>
+      </c>
+      <c r="I543" t="s">
+        <v>25</v>
+      </c>
+      <c r="J543" t="s">
+        <v>25</v>
+      </c>
+      <c r="K543" t="s">
+        <v>25</v>
+      </c>
+      <c r="L543" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="544" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C544" t="s">
+        <v>963</v>
+      </c>
+      <c r="D544" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E544" t="s">
+        <v>25</v>
+      </c>
+      <c r="F544" t="s">
+        <v>25</v>
+      </c>
+      <c r="G544" t="s">
+        <v>25</v>
+      </c>
+      <c r="H544" t="s">
+        <v>19</v>
+      </c>
+      <c r="I544" t="s">
+        <v>25</v>
+      </c>
+      <c r="J544" t="s">
+        <v>25</v>
+      </c>
+      <c r="K544" t="s">
+        <v>25</v>
+      </c>
+      <c r="L544" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="545" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C545" t="s">
+        <v>963</v>
+      </c>
+      <c r="D545" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E545" t="s">
+        <v>25</v>
+      </c>
+      <c r="F545" t="s">
+        <v>25</v>
+      </c>
+      <c r="G545" t="s">
+        <v>25</v>
+      </c>
+      <c r="H545" t="s">
+        <v>19</v>
+      </c>
+      <c r="I545" t="s">
+        <v>25</v>
+      </c>
+      <c r="J545" t="s">
+        <v>25</v>
+      </c>
+      <c r="K545" t="s">
+        <v>25</v>
+      </c>
+      <c r="L545" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="546" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C546" t="s">
+        <v>963</v>
+      </c>
+      <c r="D546" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E546" t="s">
+        <v>25</v>
+      </c>
+      <c r="F546" t="s">
+        <v>25</v>
+      </c>
+      <c r="G546" t="s">
+        <v>25</v>
+      </c>
+      <c r="H546" t="s">
+        <v>19</v>
+      </c>
+      <c r="I546" t="s">
+        <v>25</v>
+      </c>
+      <c r="J546" t="s">
+        <v>25</v>
+      </c>
+      <c r="K546" t="s">
+        <v>25</v>
+      </c>
+      <c r="L546" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="547" spans="1:12" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="548" spans="1:12" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 B37:E37 G38:L38 B39:L39 B38:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 F10 A11:D12 F12 J10:L10 F11 J11:L11 J12:L12 H10 H11 H12 B17:D17 B18:D18 F17 F18 H17 H18 J17:L17 K18:L18 A28:G28 A21:D21 H21 A22:D24 F24 L21 F22 J22:L22 F23 J23:L23 J24:L24 A34:D36 A33:D33 L33 H24 H22 H23 A25:D25 H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F36 F34 J34:L34 F35 J35:L35 J36:L36 H33 H36 H34 H35 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67 J67:L67 A68 J68:L68 A72 J72:L72 A73 J73:L73 F72 F73:G73 F67:G67 F68:G68 C72:D72 C68:D68 C67:D67 C73:D73 H72 A74 A88:L537 A84 I84:L84 C74:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 B37:E37 G38:L38 B39:L39 B38:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 F10 A11:D12 F12 J10:L10 F11 J11:L11 J12:L12 H10 H11 H12 B17:D17 B18:D18 F17 F18 H17 H18 J17:L17 K18:L18 A28:G28 A21:D21 H21 A22:D24 F24 L21 F22 J22:L22 F23 J23:L23 J24:L24 A34:D36 A33:D33 L33 H24 H22 H23 A25:D25 H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F36 F34 J34:L34 F35 J35:L35 J36:L36 H33 H36 H34 H35 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67 J67:L67 A68 J68:L68 A72 J72:L72 A73 J73:L73 F72 F73:G73 F67:G67 F68:G68 C72:D72 C68:D68 C67:D67 C73:D73 H72 A74 A97:G97 A84 I84:L84 C74:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87 A91:D91 F91 H91:L91 A99:G99 A98:G98 L98 A96:D96 F96 H96:L96 A105:L546 I97:L97 I98:J98 I99:L99 A101:D101 F101 A104:F104 H104:L104 J101:L101 H101" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="574" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6895DBD-C684-4DDF-8233-C33D2BCA10CF}"/>
+  <xr:revisionPtr revIDLastSave="619" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AE2B1A7-3786-4D1D-B820-54C5856AA436}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6862" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6982" uniqueCount="1213">
   <si>
     <t>Codigo</t>
   </si>
@@ -5943,6 +5943,347 @@
   </si>
   <si>
     <t>assets/productos/bebes/setlavateteros/lavateteblue2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/lavateteroselectrico/tetelec.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/lavateteroselectrico/tetelec2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/lavateteroselectrico/tetelec3.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/lavateteroselectrico/tetelec4.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/lavateteroselectrico/tetelec5.webp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limpiador Eléctrico Multifuncional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> para Teteros facilita la limpieza de teteros, biberones, vasos, pajillas y accesorios del bebé gracias a su sistema de rotación automática y sus diferentes cabezales intercambiables. Su diseño compacto, recargable por USB y portátil lo convierte en un aliado práctico para el hogar o los viajes.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Incluye:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Limpiador eléctrico recargable.
+Cepillo principal para teteros.
+Cepillo pequeño intercambiable.
+Limpiador para pajillas.
+Accesorio de limpieza adicional.
+Base organizadora.
+Cable de carga USB.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limpiador eléctrico</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> recargable para teteros y accesorios, con cabezales intercambiables y carga USB para una limpieza rápida y profunda.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Sistema de rotación automática.
+Recargable mediante cable USB.
+Batería integrada.
+Cabezales intercambiables.
+Material plástico resistente.
+Diseño portátil y compacto.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Limpieza rápida y profunda.
+Elimina residuos de difícil acceso.
+Ideal para teteros, vasos y accesorios.
+Fácil de transportar y almacenar.
+Ayuda a mantener una mejor higiene para el bebé.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Limpiar los cabezales después de cada uso.
+Utilizar agua tibia y jabón suave.
+Cargar únicamente con el cable USB incluido.
+Guardar en un lugar limpio y seco.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/pañaleracambiador/pañal.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/pañaleracambiador/pañal2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/pañaleracambiador/pañal3.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/pañaleracambiador/pañal4.webp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Pañalera 3 en 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ofrece practicidad y comodidad para cada salida con tu bebé. Funciona como bolso, pañalera y cambiador tipo cuna portátil, permitiendo cambiar al bebé en cualquier lugar. Cuenta con compartimentos térmicos para biberones, amplio espacio de almacenamiento y un diseño resistente, ligero e impermeable.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Medidas:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Bolso: 41 × 30 × 19 cm.
+Cuna desplegable: 76 × 23 cm.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pañalera 3 en 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con cambiador tipo cuna, compartimentos térmicos y diseño impermeable, ideal para las salidas con tu bebé.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Diseño 3 en 1: bolso, pañalera y cambiador.
+Compartimentos térmicos para biberones.
+Material impermeable y resistente.
+Fácil de limpiar.
+Diseño ligero y amplio.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Permite cambiar al bebé en cualquier lugar.
+Mantiene los accesorios organizados.
+Conserva la temperatura de los biberones.
+Ideal para viajes, paseos y uso diario.
+Cómoda de transportar.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Limpiar con un paño húmedo y jabón suave.
+No lavar con productos abrasivos.
+Dejar secar completamente antes de guardar.
+Almacenar en un lugar limpio y seco.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -6335,7 +6676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L548"/>
+  <dimension ref="A1:L555"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -10112,11 +10453,14 @@
       <c r="D104" t="s">
         <v>113</v>
       </c>
-      <c r="E104" t="s">
-        <v>25</v>
-      </c>
-      <c r="F104" t="s">
-        <v>25</v>
+      <c r="E104">
+        <v>85278</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G104" t="s">
+        <v>1198</v>
       </c>
       <c r="H104" t="s">
         <v>19</v>
@@ -10125,10 +10469,10 @@
         <v>25</v>
       </c>
       <c r="J104" t="s">
-        <v>25</v>
-      </c>
-      <c r="K104" t="s">
-        <v>25</v>
+        <v>1204</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>1205</v>
       </c>
       <c r="L104" t="s">
         <v>25</v>
@@ -10136,10 +10480,10 @@
     </row>
     <row r="105" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B105" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C105" t="s">
         <v>14</v>
@@ -10147,14 +10491,14 @@
       <c r="D105" t="s">
         <v>113</v>
       </c>
-      <c r="E105" t="s">
-        <v>25</v>
+      <c r="E105">
+        <v>85278</v>
       </c>
       <c r="F105" t="s">
         <v>25</v>
       </c>
       <c r="G105" t="s">
-        <v>25</v>
+        <v>1199</v>
       </c>
       <c r="H105" t="s">
         <v>19</v>
@@ -10174,10 +10518,10 @@
     </row>
     <row r="106" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
@@ -10185,14 +10529,14 @@
       <c r="D106" t="s">
         <v>113</v>
       </c>
-      <c r="E106" t="s">
-        <v>25</v>
+      <c r="E106">
+        <v>85278</v>
       </c>
       <c r="F106" t="s">
         <v>25</v>
       </c>
       <c r="G106" t="s">
-        <v>25</v>
+        <v>1200</v>
       </c>
       <c r="H106" t="s">
         <v>19</v>
@@ -10212,25 +10556,25 @@
     </row>
     <row r="107" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>129</v>
-      </c>
-      <c r="E107" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="E107">
+        <v>85278</v>
       </c>
       <c r="F107" t="s">
         <v>25</v>
       </c>
       <c r="G107" t="s">
-        <v>25</v>
+        <v>1201</v>
       </c>
       <c r="H107" t="s">
         <v>19</v>
@@ -10250,25 +10594,25 @@
     </row>
     <row r="108" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B108" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>129</v>
-      </c>
-      <c r="E108" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="E108">
+        <v>85278</v>
       </c>
       <c r="F108" t="s">
         <v>25</v>
       </c>
       <c r="G108" t="s">
-        <v>25</v>
+        <v>1202</v>
       </c>
       <c r="H108" t="s">
         <v>19</v>
@@ -10288,25 +10632,25 @@
     </row>
     <row r="109" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C109" t="s">
         <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>129</v>
-      </c>
-      <c r="E109" t="s">
-        <v>25</v>
-      </c>
-      <c r="F109" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="E109">
+        <v>93250</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>1210</v>
       </c>
       <c r="G109" t="s">
-        <v>25</v>
+        <v>1206</v>
       </c>
       <c r="H109" t="s">
         <v>19</v>
@@ -10315,10 +10659,10 @@
         <v>25</v>
       </c>
       <c r="J109" t="s">
-        <v>25</v>
-      </c>
-      <c r="K109" t="s">
-        <v>25</v>
+        <v>1211</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>1212</v>
       </c>
       <c r="L109" t="s">
         <v>25</v>
@@ -10326,25 +10670,25 @@
     </row>
     <row r="110" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B110" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C110" t="s">
         <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>129</v>
-      </c>
-      <c r="E110" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="E110">
+        <v>93250</v>
       </c>
       <c r="F110" t="s">
         <v>25</v>
       </c>
       <c r="G110" t="s">
-        <v>25</v>
+        <v>1207</v>
       </c>
       <c r="H110" t="s">
         <v>19</v>
@@ -10364,25 +10708,25 @@
     </row>
     <row r="111" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B111" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C111" t="s">
         <v>14</v>
       </c>
       <c r="D111" t="s">
-        <v>129</v>
-      </c>
-      <c r="E111" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="E111">
+        <v>93250</v>
       </c>
       <c r="F111" t="s">
         <v>25</v>
       </c>
       <c r="G111" t="s">
-        <v>25</v>
+        <v>1208</v>
       </c>
       <c r="H111" t="s">
         <v>19</v>
@@ -10402,25 +10746,25 @@
     </row>
     <row r="112" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B112" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C112" t="s">
         <v>14</v>
       </c>
       <c r="D112" t="s">
-        <v>140</v>
-      </c>
-      <c r="E112" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="E112">
+        <v>93250</v>
       </c>
       <c r="F112" t="s">
         <v>25</v>
       </c>
       <c r="G112" t="s">
-        <v>25</v>
+        <v>1209</v>
       </c>
       <c r="H112" t="s">
         <v>19</v>
@@ -10440,16 +10784,16 @@
     </row>
     <row r="113" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="B113" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C113" t="s">
         <v>14</v>
       </c>
       <c r="D113" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="E113" t="s">
         <v>25</v>
@@ -10461,7 +10805,7 @@
         <v>25</v>
       </c>
       <c r="H113" t="s">
-        <v>19</v>
+        <v>1131</v>
       </c>
       <c r="I113" t="s">
         <v>25</v>
@@ -10478,16 +10822,16 @@
     </row>
     <row r="114" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="B114" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
@@ -10516,16 +10860,16 @@
     </row>
     <row r="115" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B115" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
       </c>
       <c r="D115" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
@@ -10554,16 +10898,16 @@
     </row>
     <row r="116" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B116" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C116" t="s">
         <v>14</v>
       </c>
       <c r="D116" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E116" t="s">
         <v>25</v>
@@ -10592,16 +10936,16 @@
     </row>
     <row r="117" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="B117" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C117" t="s">
         <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E117" t="s">
         <v>25</v>
@@ -10630,16 +10974,16 @@
     </row>
     <row r="118" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B118" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C118" t="s">
         <v>14</v>
       </c>
       <c r="D118" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
@@ -10668,16 +11012,16 @@
     </row>
     <row r="119" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="B119" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C119" t="s">
         <v>14</v>
       </c>
       <c r="D119" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E119" t="s">
         <v>25</v>
@@ -10706,16 +11050,16 @@
     </row>
     <row r="120" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="B120" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="C120" t="s">
         <v>14</v>
       </c>
       <c r="D120" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
@@ -10744,16 +11088,16 @@
     </row>
     <row r="121" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="B121" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C121" t="s">
         <v>14</v>
       </c>
       <c r="D121" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E121" t="s">
         <v>25</v>
@@ -10782,16 +11126,16 @@
     </row>
     <row r="122" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B122" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E122" t="s">
         <v>25</v>
@@ -10820,16 +11164,16 @@
     </row>
     <row r="123" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="B123" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C123" t="s">
         <v>14</v>
       </c>
       <c r="D123" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E123" t="s">
         <v>25</v>
@@ -10858,16 +11202,16 @@
     </row>
     <row r="124" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="B124" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C124" t="s">
         <v>14</v>
       </c>
       <c r="D124" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E124" t="s">
         <v>25</v>
@@ -10896,16 +11240,16 @@
     </row>
     <row r="125" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="B125" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
       </c>
       <c r="D125" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E125" t="s">
         <v>25</v>
@@ -10934,10 +11278,10 @@
     </row>
     <row r="126" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="B126" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="C126" t="s">
         <v>14</v>
@@ -10972,10 +11316,10 @@
     </row>
     <row r="127" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="B127" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="C127" t="s">
         <v>14</v>
@@ -11010,10 +11354,10 @@
     </row>
     <row r="128" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B128" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C128" t="s">
         <v>14</v>
@@ -11048,10 +11392,10 @@
     </row>
     <row r="129" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="B129" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C129" t="s">
         <v>14</v>
@@ -11086,10 +11430,10 @@
     </row>
     <row r="130" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="B130" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C130" t="s">
         <v>14</v>
@@ -11124,10 +11468,10 @@
     </row>
     <row r="131" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B131" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="C131" t="s">
         <v>14</v>
@@ -11162,10 +11506,10 @@
     </row>
     <row r="132" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="B132" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C132" t="s">
         <v>14</v>
@@ -11200,10 +11544,10 @@
     </row>
     <row r="133" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B133" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C133" t="s">
         <v>14</v>
@@ -11238,10 +11582,10 @@
     </row>
     <row r="134" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="B134" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C134" t="s">
         <v>14</v>
@@ -11276,10 +11620,10 @@
     </row>
     <row r="135" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="B135" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C135" t="s">
         <v>14</v>
@@ -11314,10 +11658,10 @@
     </row>
     <row r="136" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B136" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C136" t="s">
         <v>14</v>
@@ -11352,10 +11696,10 @@
     </row>
     <row r="137" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="B137" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C137" t="s">
         <v>14</v>
@@ -11390,10 +11734,10 @@
     </row>
     <row r="138" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="B138" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C138" t="s">
         <v>14</v>
@@ -11428,10 +11772,10 @@
     </row>
     <row r="139" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="B139" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="C139" t="s">
         <v>14</v>
@@ -11439,14 +11783,14 @@
       <c r="D139" t="s">
         <v>155</v>
       </c>
-      <c r="E139">
-        <v>106156</v>
+      <c r="E139" t="s">
+        <v>25</v>
       </c>
       <c r="F139" t="s">
-        <v>195</v>
+        <v>25</v>
       </c>
       <c r="G139" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="H139" t="s">
         <v>19</v>
@@ -11455,10 +11799,10 @@
         <v>25</v>
       </c>
       <c r="J139" t="s">
-        <v>197</v>
+        <v>25</v>
       </c>
       <c r="K139" t="s">
-        <v>198</v>
+        <v>25</v>
       </c>
       <c r="L139" t="s">
         <v>25</v>
@@ -11466,10 +11810,10 @@
     </row>
     <row r="140" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B140" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C140" t="s">
         <v>14</v>
@@ -11477,14 +11821,14 @@
       <c r="D140" t="s">
         <v>155</v>
       </c>
-      <c r="E140">
-        <v>106156</v>
+      <c r="E140" t="s">
+        <v>25</v>
       </c>
       <c r="F140" t="s">
         <v>25</v>
       </c>
       <c r="G140" t="s">
-        <v>199</v>
+        <v>25</v>
       </c>
       <c r="H140" t="s">
         <v>19</v>
@@ -11504,16 +11848,16 @@
     </row>
     <row r="141" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="B141" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C141" t="s">
         <v>14</v>
       </c>
       <c r="D141" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E141" t="s">
         <v>25</v>
@@ -11542,16 +11886,16 @@
     </row>
     <row r="142" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B142" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="C142" t="s">
         <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E142" t="s">
         <v>25</v>
@@ -11580,16 +11924,16 @@
     </row>
     <row r="143" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="B143" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="C143" t="s">
         <v>14</v>
       </c>
       <c r="D143" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E143" t="s">
         <v>25</v>
@@ -11618,16 +11962,16 @@
     </row>
     <row r="144" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="B144" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="C144" t="s">
         <v>14</v>
       </c>
       <c r="D144" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E144" t="s">
         <v>25</v>
@@ -11656,16 +12000,16 @@
     </row>
     <row r="145" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="B145" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C145" t="s">
         <v>14</v>
       </c>
       <c r="D145" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="E145" t="s">
         <v>25</v>
@@ -11694,25 +12038,25 @@
     </row>
     <row r="146" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="B146" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="C146" t="s">
         <v>14</v>
       </c>
       <c r="D146" t="s">
-        <v>202</v>
-      </c>
-      <c r="E146" t="s">
-        <v>25</v>
+        <v>155</v>
+      </c>
+      <c r="E146">
+        <v>106156</v>
       </c>
       <c r="F146" t="s">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="G146" t="s">
-        <v>25</v>
+        <v>196</v>
       </c>
       <c r="H146" t="s">
         <v>19</v>
@@ -11721,10 +12065,10 @@
         <v>25</v>
       </c>
       <c r="J146" t="s">
-        <v>25</v>
+        <v>197</v>
       </c>
       <c r="K146" t="s">
-        <v>25</v>
+        <v>198</v>
       </c>
       <c r="L146" t="s">
         <v>25</v>
@@ -11732,25 +12076,25 @@
     </row>
     <row r="147" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="B147" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C147" t="s">
         <v>14</v>
       </c>
       <c r="D147" t="s">
-        <v>202</v>
-      </c>
-      <c r="E147" t="s">
-        <v>25</v>
+        <v>155</v>
+      </c>
+      <c r="E147">
+        <v>106156</v>
       </c>
       <c r="F147" t="s">
         <v>25</v>
       </c>
       <c r="G147" t="s">
-        <v>25</v>
+        <v>199</v>
       </c>
       <c r="H147" t="s">
         <v>19</v>
@@ -11770,10 +12114,10 @@
     </row>
     <row r="148" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="B148" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C148" t="s">
         <v>14</v>
@@ -11808,10 +12152,10 @@
     </row>
     <row r="149" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B149" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C149" t="s">
         <v>14</v>
@@ -11846,10 +12190,10 @@
     </row>
     <row r="150" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="B150" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C150" t="s">
         <v>14</v>
@@ -11884,10 +12228,10 @@
     </row>
     <row r="151" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B151" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C151" t="s">
         <v>14</v>
@@ -11922,10 +12266,10 @@
     </row>
     <row r="152" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="B152" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C152" t="s">
         <v>14</v>
@@ -11960,10 +12304,10 @@
     </row>
     <row r="153" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B153" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="C153" t="s">
         <v>14</v>
@@ -11998,16 +12342,16 @@
     </row>
     <row r="154" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B154" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C154" t="s">
         <v>14</v>
       </c>
       <c r="D154" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="E154" t="s">
         <v>25</v>
@@ -12036,16 +12380,16 @@
     </row>
     <row r="155" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B155" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="C155" t="s">
         <v>14</v>
       </c>
       <c r="D155" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="E155" t="s">
         <v>25</v>
@@ -12074,16 +12418,16 @@
     </row>
     <row r="156" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="B156" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="C156" t="s">
         <v>14</v>
       </c>
       <c r="D156" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="E156" t="s">
         <v>25</v>
@@ -12112,16 +12456,16 @@
     </row>
     <row r="157" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B157" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C157" t="s">
         <v>14</v>
       </c>
       <c r="D157" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="E157" t="s">
         <v>25</v>
@@ -12150,16 +12494,16 @@
     </row>
     <row r="158" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="B158" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="C158" t="s">
         <v>14</v>
       </c>
       <c r="D158" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="E158" t="s">
         <v>25</v>
@@ -12188,16 +12532,16 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B159" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C159" t="s">
         <v>14</v>
       </c>
       <c r="D159" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="E159" t="s">
         <v>25</v>
@@ -12226,16 +12570,16 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="B160" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="C160" t="s">
         <v>14</v>
       </c>
       <c r="D160" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="E160" t="s">
         <v>25</v>
@@ -12264,16 +12608,16 @@
     </row>
     <row r="161" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="B161" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="C161" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D161" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E161" t="s">
         <v>25</v>
@@ -12302,16 +12646,16 @@
     </row>
     <row r="162" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="B162" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="C162" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D162" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E162" t="s">
         <v>25</v>
@@ -12340,16 +12684,16 @@
     </row>
     <row r="163" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="B163" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C163" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D163" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E163" t="s">
         <v>25</v>
@@ -12378,16 +12722,16 @@
     </row>
     <row r="164" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="B164" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="C164" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D164" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E164" t="s">
         <v>25</v>
@@ -12416,16 +12760,16 @@
     </row>
     <row r="165" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B165" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="C165" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D165" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E165" t="s">
         <v>25</v>
@@ -12454,16 +12798,16 @@
     </row>
     <row r="166" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="B166" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="C166" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D166" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E166" t="s">
         <v>25</v>
@@ -12492,16 +12836,16 @@
     </row>
     <row r="167" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="B167" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="C167" t="s">
-        <v>243</v>
+        <v>14</v>
       </c>
       <c r="D167" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E167" t="s">
         <v>25</v>
@@ -12530,10 +12874,10 @@
     </row>
     <row r="168" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="B168" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="C168" t="s">
         <v>243</v>
@@ -12568,10 +12912,10 @@
     </row>
     <row r="169" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="B169" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="C169" t="s">
         <v>243</v>
@@ -12606,10 +12950,10 @@
     </row>
     <row r="170" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B170" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="C170" t="s">
         <v>243</v>
@@ -12644,10 +12988,10 @@
     </row>
     <row r="171" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="B171" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="C171" t="s">
         <v>243</v>
@@ -12682,10 +13026,10 @@
     </row>
     <row r="172" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="B172" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C172" t="s">
         <v>243</v>
@@ -12720,10 +13064,10 @@
     </row>
     <row r="173" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="B173" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C173" t="s">
         <v>243</v>
@@ -12758,10 +13102,10 @@
     </row>
     <row r="174" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="B174" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="C174" t="s">
         <v>243</v>
@@ -12796,10 +13140,10 @@
     </row>
     <row r="175" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="B175" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="C175" t="s">
         <v>243</v>
@@ -12834,10 +13178,10 @@
     </row>
     <row r="176" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B176" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="C176" t="s">
         <v>243</v>
@@ -12872,10 +13216,10 @@
     </row>
     <row r="177" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="B177" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="C177" t="s">
         <v>243</v>
@@ -12910,10 +13254,10 @@
     </row>
     <row r="178" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B178" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C178" t="s">
         <v>243</v>
@@ -12948,10 +13292,10 @@
     </row>
     <row r="179" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="B179" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="C179" t="s">
         <v>243</v>
@@ -12986,10 +13330,10 @@
     </row>
     <row r="180" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="B180" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="C180" t="s">
         <v>243</v>
@@ -13024,10 +13368,10 @@
     </row>
     <row r="181" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B181" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="C181" t="s">
         <v>243</v>
@@ -13062,10 +13406,10 @@
     </row>
     <row r="182" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="B182" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="C182" t="s">
         <v>243</v>
@@ -13100,10 +13444,10 @@
     </row>
     <row r="183" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="B183" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="C183" t="s">
         <v>243</v>
@@ -13138,10 +13482,10 @@
     </row>
     <row r="184" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B184" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="C184" t="s">
         <v>243</v>
@@ -13176,10 +13520,10 @@
     </row>
     <row r="185" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B185" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="C185" t="s">
         <v>243</v>
@@ -13214,10 +13558,10 @@
     </row>
     <row r="186" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B186" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="C186" t="s">
         <v>243</v>
@@ -13252,10 +13596,10 @@
     </row>
     <row r="187" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="B187" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="C187" t="s">
         <v>243</v>
@@ -13290,10 +13634,10 @@
     </row>
     <row r="188" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="B188" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="C188" t="s">
         <v>243</v>
@@ -13328,10 +13672,10 @@
     </row>
     <row r="189" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="B189" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C189" t="s">
         <v>243</v>
@@ -13366,10 +13710,10 @@
     </row>
     <row r="190" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="B190" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="C190" t="s">
         <v>243</v>
@@ -13404,10 +13748,10 @@
     </row>
     <row r="191" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B191" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="C191" t="s">
         <v>243</v>
@@ -13442,10 +13786,10 @@
     </row>
     <row r="192" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="B192" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="C192" t="s">
         <v>243</v>
@@ -13480,10 +13824,10 @@
     </row>
     <row r="193" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B193" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="C193" t="s">
         <v>243</v>
@@ -13518,10 +13862,10 @@
     </row>
     <row r="194" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="B194" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="C194" t="s">
         <v>243</v>
@@ -13556,10 +13900,10 @@
     </row>
     <row r="195" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B195" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="C195" t="s">
         <v>243</v>
@@ -13594,10 +13938,10 @@
     </row>
     <row r="196" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="B196" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="C196" t="s">
         <v>243</v>
@@ -13632,10 +13976,10 @@
     </row>
     <row r="197" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="B197" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="C197" t="s">
         <v>243</v>
@@ -13670,10 +14014,10 @@
     </row>
     <row r="198" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="B198" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="C198" t="s">
         <v>243</v>
@@ -13708,16 +14052,16 @@
     </row>
     <row r="199" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="B199" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="C199" t="s">
         <v>243</v>
       </c>
       <c r="D199" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E199" t="s">
         <v>25</v>
@@ -13746,16 +14090,16 @@
     </row>
     <row r="200" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="B200" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="C200" t="s">
         <v>243</v>
       </c>
       <c r="D200" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E200" t="s">
         <v>25</v>
@@ -13784,16 +14128,16 @@
     </row>
     <row r="201" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="B201" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="C201" t="s">
         <v>243</v>
       </c>
       <c r="D201" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E201" t="s">
         <v>25</v>
@@ -13822,16 +14166,16 @@
     </row>
     <row r="202" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="B202" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="C202" t="s">
         <v>243</v>
       </c>
       <c r="D202" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E202" t="s">
         <v>25</v>
@@ -13860,16 +14204,16 @@
     </row>
     <row r="203" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="B203" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="C203" t="s">
         <v>243</v>
       </c>
       <c r="D203" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E203" t="s">
         <v>25</v>
@@ -13898,16 +14242,16 @@
     </row>
     <row r="204" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="B204" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="C204" t="s">
         <v>243</v>
       </c>
       <c r="D204" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E204" t="s">
         <v>25</v>
@@ -13936,16 +14280,16 @@
     </row>
     <row r="205" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="B205" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C205" t="s">
         <v>243</v>
       </c>
       <c r="D205" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="E205" t="s">
         <v>25</v>
@@ -13974,10 +14318,10 @@
     </row>
     <row r="206" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="B206" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="C206" t="s">
         <v>243</v>
@@ -14012,10 +14356,10 @@
     </row>
     <row r="207" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="B207" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="C207" t="s">
         <v>243</v>
@@ -14050,10 +14394,10 @@
     </row>
     <row r="208" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="B208" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="C208" t="s">
         <v>243</v>
@@ -14088,16 +14432,16 @@
     </row>
     <row r="209" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B209" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="C209" t="s">
         <v>243</v>
       </c>
       <c r="D209" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="E209" t="s">
         <v>25</v>
@@ -14126,16 +14470,16 @@
     </row>
     <row r="210" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="B210" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C210" t="s">
         <v>243</v>
       </c>
       <c r="D210" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="E210" t="s">
         <v>25</v>
@@ -14164,16 +14508,16 @@
     </row>
     <row r="211" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="B211" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="C211" t="s">
         <v>243</v>
       </c>
       <c r="D211" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="E211" t="s">
         <v>25</v>
@@ -14202,16 +14546,16 @@
     </row>
     <row r="212" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="B212" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C212" t="s">
         <v>243</v>
       </c>
       <c r="D212" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E212" t="s">
         <v>25</v>
@@ -14240,16 +14584,16 @@
     </row>
     <row r="213" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="B213" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C213" t="s">
         <v>243</v>
       </c>
       <c r="D213" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E213" t="s">
         <v>25</v>
@@ -14278,16 +14622,16 @@
     </row>
     <row r="214" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="B214" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="C214" t="s">
         <v>243</v>
       </c>
       <c r="D214" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E214" t="s">
         <v>25</v>
@@ -14316,16 +14660,16 @@
     </row>
     <row r="215" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="B215" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="C215" t="s">
         <v>243</v>
       </c>
       <c r="D215" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E215" t="s">
         <v>25</v>
@@ -14354,16 +14698,16 @@
     </row>
     <row r="216" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="B216" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="C216" t="s">
         <v>243</v>
       </c>
       <c r="D216" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="E216" t="s">
         <v>25</v>
@@ -14392,16 +14736,16 @@
     </row>
     <row r="217" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="B217" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C217" t="s">
         <v>243</v>
       </c>
       <c r="D217" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="E217" t="s">
         <v>25</v>
@@ -14430,16 +14774,16 @@
     </row>
     <row r="218" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="B218" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="C218" t="s">
         <v>243</v>
       </c>
       <c r="D218" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="E218" t="s">
         <v>25</v>
@@ -14468,16 +14812,16 @@
     </row>
     <row r="219" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="B219" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="C219" t="s">
         <v>243</v>
       </c>
       <c r="D219" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E219" t="s">
         <v>25</v>
@@ -14506,16 +14850,16 @@
     </row>
     <row r="220" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B220" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="C220" t="s">
         <v>243</v>
       </c>
       <c r="D220" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E220" t="s">
         <v>25</v>
@@ -14544,16 +14888,16 @@
     </row>
     <row r="221" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="B221" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="C221" t="s">
         <v>243</v>
       </c>
       <c r="D221" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E221" t="s">
         <v>25</v>
@@ -14582,16 +14926,16 @@
     </row>
     <row r="222" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="B222" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C222" t="s">
         <v>243</v>
       </c>
       <c r="D222" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E222" t="s">
         <v>25</v>
@@ -14620,16 +14964,16 @@
     </row>
     <row r="223" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="B223" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="C223" t="s">
         <v>243</v>
       </c>
       <c r="D223" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E223" t="s">
         <v>25</v>
@@ -14658,16 +15002,16 @@
     </row>
     <row r="224" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="B224" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="C224" t="s">
         <v>243</v>
       </c>
       <c r="D224" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E224" t="s">
         <v>25</v>
@@ -14696,16 +15040,16 @@
     </row>
     <row r="225" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="B225" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="C225" t="s">
         <v>243</v>
       </c>
       <c r="D225" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="E225" t="s">
         <v>25</v>
@@ -14734,10 +15078,10 @@
     </row>
     <row r="226" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="B226" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="C226" t="s">
         <v>243</v>
@@ -14772,10 +15116,10 @@
     </row>
     <row r="227" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B227" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="C227" t="s">
         <v>243</v>
@@ -14810,10 +15154,10 @@
     </row>
     <row r="228" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="B228" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="C228" t="s">
         <v>243</v>
@@ -14848,10 +15192,10 @@
     </row>
     <row r="229" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="B229" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="C229" t="s">
         <v>243</v>
@@ -14886,10 +15230,10 @@
     </row>
     <row r="230" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B230" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C230" t="s">
         <v>243</v>
@@ -14924,10 +15268,10 @@
     </row>
     <row r="231" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="B231" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C231" t="s">
         <v>243</v>
@@ -14962,10 +15306,10 @@
     </row>
     <row r="232" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B232" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C232" t="s">
         <v>243</v>
@@ -15000,10 +15344,10 @@
     </row>
     <row r="233" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B233" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C233" t="s">
         <v>243</v>
@@ -15038,10 +15382,10 @@
     </row>
     <row r="234" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B234" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C234" t="s">
         <v>243</v>
@@ -15076,10 +15420,10 @@
     </row>
     <row r="235" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B235" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C235" t="s">
         <v>243</v>
@@ -15114,10 +15458,10 @@
     </row>
     <row r="236" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B236" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="C236" t="s">
         <v>243</v>
@@ -15152,10 +15496,10 @@
     </row>
     <row r="237" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="B237" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C237" t="s">
         <v>243</v>
@@ -15190,10 +15534,10 @@
     </row>
     <row r="238" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="B238" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="C238" t="s">
         <v>243</v>
@@ -15228,10 +15572,10 @@
     </row>
     <row r="239" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="B239" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="C239" t="s">
         <v>243</v>
@@ -15266,10 +15610,10 @@
     </row>
     <row r="240" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="B240" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="C240" t="s">
         <v>243</v>
@@ -15304,10 +15648,10 @@
     </row>
     <row r="241" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="B241" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="C241" t="s">
         <v>243</v>
@@ -15342,10 +15686,10 @@
     </row>
     <row r="242" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B242" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="C242" t="s">
         <v>243</v>
@@ -15380,10 +15724,10 @@
     </row>
     <row r="243" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="B243" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="C243" t="s">
         <v>243</v>
@@ -15418,10 +15762,10 @@
     </row>
     <row r="244" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="B244" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="C244" t="s">
         <v>243</v>
@@ -15456,16 +15800,16 @@
     </row>
     <row r="245" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="B245" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="C245" t="s">
         <v>243</v>
       </c>
       <c r="D245" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E245" t="s">
         <v>25</v>
@@ -15494,16 +15838,16 @@
     </row>
     <row r="246" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="B246" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="C246" t="s">
         <v>243</v>
       </c>
       <c r="D246" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E246" t="s">
         <v>25</v>
@@ -15532,16 +15876,16 @@
     </row>
     <row r="247" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="B247" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="C247" t="s">
         <v>243</v>
       </c>
       <c r="D247" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E247" t="s">
         <v>25</v>
@@ -15570,16 +15914,16 @@
     </row>
     <row r="248" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="B248" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="C248" t="s">
         <v>243</v>
       </c>
       <c r="D248" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E248" t="s">
         <v>25</v>
@@ -15608,16 +15952,16 @@
     </row>
     <row r="249" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="B249" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="C249" t="s">
         <v>243</v>
       </c>
       <c r="D249" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E249" t="s">
         <v>25</v>
@@ -15646,16 +15990,16 @@
     </row>
     <row r="250" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="B250" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="C250" t="s">
         <v>243</v>
       </c>
       <c r="D250" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E250" t="s">
         <v>25</v>
@@ -15684,16 +16028,16 @@
     </row>
     <row r="251" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="B251" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="C251" t="s">
         <v>243</v>
       </c>
       <c r="D251" t="s">
-        <v>411</v>
+        <v>229</v>
       </c>
       <c r="E251" t="s">
         <v>25</v>
@@ -15722,10 +16066,10 @@
     </row>
     <row r="252" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="B252" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="C252" t="s">
         <v>243</v>
@@ -15760,10 +16104,10 @@
     </row>
     <row r="253" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="B253" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="C253" t="s">
         <v>243</v>
@@ -15798,10 +16142,10 @@
     </row>
     <row r="254" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="B254" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="C254" t="s">
         <v>243</v>
@@ -15836,10 +16180,10 @@
     </row>
     <row r="255" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="B255" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="C255" t="s">
         <v>243</v>
@@ -15874,10 +16218,10 @@
     </row>
     <row r="256" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="B256" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="C256" t="s">
         <v>243</v>
@@ -15912,10 +16256,10 @@
     </row>
     <row r="257" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="B257" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="C257" t="s">
         <v>243</v>
@@ -15950,10 +16294,10 @@
     </row>
     <row r="258" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="B258" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="C258" t="s">
         <v>243</v>
@@ -15988,10 +16332,10 @@
     </row>
     <row r="259" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="B259" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="C259" t="s">
         <v>243</v>
@@ -16026,10 +16370,10 @@
     </row>
     <row r="260" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="B260" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="C260" t="s">
         <v>243</v>
@@ -16064,10 +16408,10 @@
     </row>
     <row r="261" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="B261" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="C261" t="s">
         <v>243</v>
@@ -16102,10 +16446,10 @@
     </row>
     <row r="262" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="B262" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="C262" t="s">
         <v>243</v>
@@ -16140,10 +16484,10 @@
     </row>
     <row r="263" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="B263" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="C263" t="s">
         <v>243</v>
@@ -16178,10 +16522,10 @@
     </row>
     <row r="264" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="B264" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="C264" t="s">
         <v>243</v>
@@ -16216,10 +16560,10 @@
     </row>
     <row r="265" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="B265" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="C265" t="s">
         <v>243</v>
@@ -16254,10 +16598,10 @@
     </row>
     <row r="266" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="B266" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="C266" t="s">
         <v>243</v>
@@ -16292,10 +16636,10 @@
     </row>
     <row r="267" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="B267" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="C267" t="s">
         <v>243</v>
@@ -16330,10 +16674,10 @@
     </row>
     <row r="268" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="B268" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="C268" t="s">
         <v>243</v>
@@ -16368,10 +16712,10 @@
     </row>
     <row r="269" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="B269" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="C269" t="s">
         <v>243</v>
@@ -16406,10 +16750,10 @@
     </row>
     <row r="270" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="B270" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="C270" t="s">
         <v>243</v>
@@ -16444,16 +16788,16 @@
     </row>
     <row r="271" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="B271" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="C271" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D271" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E271" t="s">
         <v>25</v>
@@ -16482,16 +16826,16 @@
     </row>
     <row r="272" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="B272" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="C272" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D272" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E272" t="s">
         <v>25</v>
@@ -16520,16 +16864,16 @@
     </row>
     <row r="273" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="B273" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="C273" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D273" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E273" t="s">
         <v>25</v>
@@ -16558,16 +16902,16 @@
     </row>
     <row r="274" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="B274" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="C274" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D274" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E274" t="s">
         <v>25</v>
@@ -16596,16 +16940,16 @@
     </row>
     <row r="275" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="B275" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="C275" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D275" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E275" t="s">
         <v>25</v>
@@ -16634,16 +16978,16 @@
     </row>
     <row r="276" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="B276" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="C276" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D276" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E276" t="s">
         <v>25</v>
@@ -16672,16 +17016,16 @@
     </row>
     <row r="277" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="B277" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="C277" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="D277" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="E277" t="s">
         <v>25</v>
@@ -16710,10 +17054,10 @@
     </row>
     <row r="278" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="B278" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="C278" t="s">
         <v>464</v>
@@ -16748,10 +17092,10 @@
     </row>
     <row r="279" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="B279" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="C279" t="s">
         <v>464</v>
@@ -16786,10 +17130,10 @@
     </row>
     <row r="280" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="B280" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="C280" t="s">
         <v>464</v>
@@ -16824,10 +17168,10 @@
     </row>
     <row r="281" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="B281" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C281" t="s">
         <v>464</v>
@@ -16862,10 +17206,10 @@
     </row>
     <row r="282" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="B282" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="C282" t="s">
         <v>464</v>
@@ -16900,10 +17244,10 @@
     </row>
     <row r="283" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="B283" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="C283" t="s">
         <v>464</v>
@@ -16938,10 +17282,10 @@
     </row>
     <row r="284" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="B284" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="C284" t="s">
         <v>464</v>
@@ -16976,10 +17320,10 @@
     </row>
     <row r="285" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="B285" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="C285" t="s">
         <v>464</v>
@@ -17014,10 +17358,10 @@
     </row>
     <row r="286" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="B286" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="C286" t="s">
         <v>464</v>
@@ -17052,10 +17396,10 @@
     </row>
     <row r="287" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="B287" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="C287" t="s">
         <v>464</v>
@@ -17090,10 +17434,10 @@
     </row>
     <row r="288" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="B288" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="C288" t="s">
         <v>464</v>
@@ -17128,10 +17472,10 @@
     </row>
     <row r="289" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="B289" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="C289" t="s">
         <v>464</v>
@@ -17166,10 +17510,10 @@
     </row>
     <row r="290" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="B290" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="C290" t="s">
         <v>464</v>
@@ -17204,10 +17548,10 @@
     </row>
     <row r="291" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="B291" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="C291" t="s">
         <v>464</v>
@@ -17242,10 +17586,10 @@
     </row>
     <row r="292" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="B292" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="C292" t="s">
         <v>464</v>
@@ -17280,10 +17624,10 @@
     </row>
     <row r="293" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="B293" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="C293" t="s">
         <v>464</v>
@@ -17318,10 +17662,10 @@
     </row>
     <row r="294" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="B294" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="C294" t="s">
         <v>464</v>
@@ -17356,10 +17700,10 @@
     </row>
     <row r="295" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="B295" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="C295" t="s">
         <v>464</v>
@@ -17394,10 +17738,10 @@
     </row>
     <row r="296" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="B296" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="C296" t="s">
         <v>464</v>
@@ -17432,10 +17776,10 @@
     </row>
     <row r="297" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="B297" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="C297" t="s">
         <v>464</v>
@@ -17470,10 +17814,10 @@
     </row>
     <row r="298" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="B298" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="C298" t="s">
         <v>464</v>
@@ -17508,10 +17852,10 @@
     </row>
     <row r="299" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="B299" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="C299" t="s">
         <v>464</v>
@@ -17546,10 +17890,10 @@
     </row>
     <row r="300" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="B300" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="C300" t="s">
         <v>464</v>
@@ -17584,10 +17928,10 @@
     </row>
     <row r="301" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="B301" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="C301" t="s">
         <v>464</v>
@@ -17622,10 +17966,10 @@
     </row>
     <row r="302" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="B302" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="C302" t="s">
         <v>464</v>
@@ -17660,10 +18004,10 @@
     </row>
     <row r="303" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="B303" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="C303" t="s">
         <v>464</v>
@@ -17698,10 +18042,10 @@
     </row>
     <row r="304" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="B304" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="C304" t="s">
         <v>464</v>
@@ -17736,10 +18080,10 @@
     </row>
     <row r="305" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="B305" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="C305" t="s">
         <v>464</v>
@@ -17774,10 +18118,10 @@
     </row>
     <row r="306" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="B306" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="C306" t="s">
         <v>464</v>
@@ -17812,10 +18156,10 @@
     </row>
     <row r="307" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="B307" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="C307" t="s">
         <v>464</v>
@@ -17850,10 +18194,10 @@
     </row>
     <row r="308" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="B308" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="C308" t="s">
         <v>464</v>
@@ -17888,10 +18232,10 @@
     </row>
     <row r="309" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="B309" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="C309" t="s">
         <v>464</v>
@@ -17926,10 +18270,10 @@
     </row>
     <row r="310" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="B310" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="C310" t="s">
         <v>464</v>
@@ -17964,10 +18308,10 @@
     </row>
     <row r="311" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="B311" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="C311" t="s">
         <v>464</v>
@@ -18002,10 +18346,10 @@
     </row>
     <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="B312" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="C312" t="s">
         <v>464</v>
@@ -18040,10 +18384,10 @@
     </row>
     <row r="313" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="B313" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="C313" t="s">
         <v>464</v>
@@ -18078,10 +18422,10 @@
     </row>
     <row r="314" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="B314" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="C314" t="s">
         <v>464</v>
@@ -18116,10 +18460,10 @@
     </row>
     <row r="315" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="B315" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="C315" t="s">
         <v>464</v>
@@ -18154,10 +18498,10 @@
     </row>
     <row r="316" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="B316" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="C316" t="s">
         <v>464</v>
@@ -18192,10 +18536,10 @@
     </row>
     <row r="317" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="B317" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C317" t="s">
         <v>464</v>
@@ -18230,16 +18574,16 @@
     </row>
     <row r="318" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="B318" t="s">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="C318" t="s">
         <v>464</v>
       </c>
       <c r="D318" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E318" t="s">
         <v>25</v>
@@ -18268,16 +18612,16 @@
     </row>
     <row r="319" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="B319" t="s">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="C319" t="s">
         <v>464</v>
       </c>
       <c r="D319" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E319" t="s">
         <v>25</v>
@@ -18306,16 +18650,16 @@
     </row>
     <row r="320" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="B320" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="C320" t="s">
         <v>464</v>
       </c>
       <c r="D320" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E320" t="s">
         <v>25</v>
@@ -18344,16 +18688,16 @@
     </row>
     <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="B321" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="C321" t="s">
         <v>464</v>
       </c>
       <c r="D321" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E321" t="s">
         <v>25</v>
@@ -18382,16 +18726,16 @@
     </row>
     <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="B322" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="C322" t="s">
         <v>464</v>
       </c>
       <c r="D322" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E322" t="s">
         <v>25</v>
@@ -18420,16 +18764,16 @@
     </row>
     <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="B323" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="C323" t="s">
         <v>464</v>
       </c>
       <c r="D323" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E323" t="s">
         <v>25</v>
@@ -18458,16 +18802,16 @@
     </row>
     <row r="324" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="B324" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="C324" t="s">
         <v>464</v>
       </c>
       <c r="D324" t="s">
-        <v>560</v>
+        <v>465</v>
       </c>
       <c r="E324" t="s">
         <v>25</v>
@@ -18496,10 +18840,10 @@
     </row>
     <row r="325" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="B325" t="s">
-        <v>574</v>
+        <v>559</v>
       </c>
       <c r="C325" t="s">
         <v>464</v>
@@ -18534,10 +18878,10 @@
     </row>
     <row r="326" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="B326" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="C326" t="s">
         <v>464</v>
@@ -18572,10 +18916,10 @@
     </row>
     <row r="327" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="B327" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="C327" t="s">
         <v>464</v>
@@ -18610,10 +18954,10 @@
     </row>
     <row r="328" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="B328" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="C328" t="s">
         <v>464</v>
@@ -18648,10 +18992,10 @@
     </row>
     <row r="329" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="B329" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="C329" t="s">
         <v>464</v>
@@ -18686,10 +19030,10 @@
     </row>
     <row r="330" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="B330" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="C330" t="s">
         <v>464</v>
@@ -18724,10 +19068,10 @@
     </row>
     <row r="331" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="B331" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="C331" t="s">
         <v>464</v>
@@ -18762,10 +19106,10 @@
     </row>
     <row r="332" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="B332" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="C332" t="s">
         <v>464</v>
@@ -18800,10 +19144,10 @@
     </row>
     <row r="333" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="B333" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="C333" t="s">
         <v>464</v>
@@ -18838,10 +19182,10 @@
     </row>
     <row r="334" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="B334" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="C334" t="s">
         <v>464</v>
@@ -18876,10 +19220,10 @@
     </row>
     <row r="335" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="B335" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="C335" t="s">
         <v>464</v>
@@ -18914,10 +19258,10 @@
     </row>
     <row r="336" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="B336" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="C336" t="s">
         <v>464</v>
@@ -18952,10 +19296,10 @@
     </row>
     <row r="337" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="B337" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="C337" t="s">
         <v>464</v>
@@ -18990,10 +19334,10 @@
     </row>
     <row r="338" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="B338" t="s">
-        <v>600</v>
+        <v>586</v>
       </c>
       <c r="C338" t="s">
         <v>464</v>
@@ -19028,10 +19372,10 @@
     </row>
     <row r="339" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="B339" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="C339" t="s">
         <v>464</v>
@@ -19066,10 +19410,10 @@
     </row>
     <row r="340" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="B340" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="C340" t="s">
         <v>464</v>
@@ -19104,10 +19448,10 @@
     </row>
     <row r="341" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="B341" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="C341" t="s">
         <v>464</v>
@@ -19142,10 +19486,10 @@
     </row>
     <row r="342" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="B342" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="C342" t="s">
         <v>464</v>
@@ -19180,10 +19524,10 @@
     </row>
     <row r="343" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="B343" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="C343" t="s">
         <v>464</v>
@@ -19218,10 +19562,10 @@
     </row>
     <row r="344" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="B344" t="s">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="C344" t="s">
         <v>464</v>
@@ -19256,10 +19600,10 @@
     </row>
     <row r="345" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="B345" t="s">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="C345" t="s">
         <v>464</v>
@@ -19294,10 +19638,10 @@
     </row>
     <row r="346" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="B346" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="C346" t="s">
         <v>464</v>
@@ -19332,10 +19676,10 @@
     </row>
     <row r="347" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="B347" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="C347" t="s">
         <v>464</v>
@@ -19370,10 +19714,10 @@
     </row>
     <row r="348" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="B348" t="s">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="C348" t="s">
         <v>464</v>
@@ -19408,10 +19752,10 @@
     </row>
     <row r="349" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="B349" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="C349" t="s">
         <v>464</v>
@@ -19446,10 +19790,10 @@
     </row>
     <row r="350" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="B350" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="C350" t="s">
         <v>464</v>
@@ -19484,10 +19828,10 @@
     </row>
     <row r="351" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="B351" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
       <c r="C351" t="s">
         <v>464</v>
@@ -19522,16 +19866,16 @@
     </row>
     <row r="352" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="B352" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="C352" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D352" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E352" t="s">
         <v>25</v>
@@ -19560,16 +19904,16 @@
     </row>
     <row r="353" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>630</v>
+        <v>615</v>
       </c>
       <c r="B353" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="C353" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D353" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E353" t="s">
         <v>25</v>
@@ -19598,16 +19942,16 @@
     </row>
     <row r="354" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="B354" t="s">
-        <v>633</v>
+        <v>618</v>
       </c>
       <c r="C354" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D354" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E354" t="s">
         <v>25</v>
@@ -19636,16 +19980,16 @@
     </row>
     <row r="355" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>634</v>
+        <v>619</v>
       </c>
       <c r="B355" t="s">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="C355" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D355" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E355" t="s">
         <v>25</v>
@@ -19674,16 +20018,16 @@
     </row>
     <row r="356" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>636</v>
+        <v>621</v>
       </c>
       <c r="B356" t="s">
-        <v>637</v>
+        <v>622</v>
       </c>
       <c r="C356" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D356" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E356" t="s">
         <v>25</v>
@@ -19712,16 +20056,16 @@
     </row>
     <row r="357" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="B357" t="s">
-        <v>639</v>
+        <v>624</v>
       </c>
       <c r="C357" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D357" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E357" t="s">
         <v>25</v>
@@ -19750,16 +20094,16 @@
     </row>
     <row r="358" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>640</v>
+        <v>625</v>
       </c>
       <c r="B358" t="s">
-        <v>641</v>
+        <v>626</v>
       </c>
       <c r="C358" t="s">
-        <v>629</v>
+        <v>464</v>
       </c>
       <c r="D358" t="s">
-        <v>25</v>
+        <v>560</v>
       </c>
       <c r="E358" t="s">
         <v>25</v>
@@ -19788,10 +20132,10 @@
     </row>
     <row r="359" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
       <c r="B359" t="s">
-        <v>643</v>
+        <v>628</v>
       </c>
       <c r="C359" t="s">
         <v>629</v>
@@ -19826,16 +20170,16 @@
     </row>
     <row r="360" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="B360" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="C360" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D360" t="s">
-        <v>647</v>
+        <v>25</v>
       </c>
       <c r="E360" t="s">
         <v>25</v>
@@ -19864,16 +20208,16 @@
     </row>
     <row r="361" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="B361" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="C361" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D361" t="s">
-        <v>647</v>
+        <v>25</v>
       </c>
       <c r="E361" t="s">
         <v>25</v>
@@ -19902,16 +20246,16 @@
     </row>
     <row r="362" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="B362" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C362" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D362" t="s">
-        <v>647</v>
+        <v>25</v>
       </c>
       <c r="E362" t="s">
         <v>25</v>
@@ -19940,16 +20284,16 @@
     </row>
     <row r="363" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="B363" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="C363" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D363" t="s">
-        <v>647</v>
+        <v>25</v>
       </c>
       <c r="E363" t="s">
         <v>25</v>
@@ -19978,16 +20322,16 @@
     </row>
     <row r="364" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="B364" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="C364" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D364" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="E364" t="s">
         <v>25</v>
@@ -20016,16 +20360,16 @@
     </row>
     <row r="365" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="B365" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="C365" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D365" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="E365" t="s">
         <v>25</v>
@@ -20054,16 +20398,16 @@
     </row>
     <row r="366" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>658</v>
+        <v>642</v>
       </c>
       <c r="B366" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="C366" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="D366" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="E366" t="s">
         <v>25</v>
@@ -20092,16 +20436,16 @@
     </row>
     <row r="367" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="B367" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="C367" t="s">
         <v>646</v>
       </c>
       <c r="D367" t="s">
-        <v>140</v>
+        <v>647</v>
       </c>
       <c r="E367" t="s">
         <v>25</v>
@@ -20130,16 +20474,16 @@
     </row>
     <row r="368" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="B368" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="C368" t="s">
         <v>646</v>
       </c>
       <c r="D368" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="E368" t="s">
         <v>25</v>
@@ -20168,16 +20512,16 @@
     </row>
     <row r="369" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>665</v>
+        <v>650</v>
       </c>
       <c r="B369" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="C369" t="s">
         <v>646</v>
       </c>
       <c r="D369" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="E369" t="s">
         <v>25</v>
@@ -20206,16 +20550,16 @@
     </row>
     <row r="370" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="B370" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="C370" t="s">
         <v>646</v>
       </c>
       <c r="D370" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="E370" t="s">
         <v>25</v>
@@ -20244,16 +20588,16 @@
     </row>
     <row r="371" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="B371" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="C371" t="s">
         <v>646</v>
       </c>
       <c r="D371" t="s">
-        <v>664</v>
+        <v>140</v>
       </c>
       <c r="E371" t="s">
         <v>25</v>
@@ -20282,16 +20626,16 @@
     </row>
     <row r="372" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="B372" t="s">
-        <v>672</v>
+        <v>657</v>
       </c>
       <c r="C372" t="s">
         <v>646</v>
       </c>
       <c r="D372" t="s">
-        <v>664</v>
+        <v>140</v>
       </c>
       <c r="E372" t="s">
         <v>25</v>
@@ -20320,16 +20664,16 @@
     </row>
     <row r="373" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="B373" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="C373" t="s">
         <v>646</v>
       </c>
       <c r="D373" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E373" t="s">
         <v>25</v>
@@ -20358,16 +20702,16 @@
     </row>
     <row r="374" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="B374" t="s">
-        <v>676</v>
+        <v>661</v>
       </c>
       <c r="C374" t="s">
         <v>646</v>
       </c>
       <c r="D374" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E374" t="s">
         <v>25</v>
@@ -20396,16 +20740,16 @@
     </row>
     <row r="375" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="B375" t="s">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="C375" t="s">
         <v>646</v>
       </c>
       <c r="D375" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="E375" t="s">
         <v>25</v>
@@ -20434,16 +20778,16 @@
     </row>
     <row r="376" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>680</v>
+        <v>665</v>
       </c>
       <c r="B376" t="s">
-        <v>681</v>
+        <v>666</v>
       </c>
       <c r="C376" t="s">
         <v>646</v>
       </c>
       <c r="D376" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="E376" t="s">
         <v>25</v>
@@ -20472,16 +20816,16 @@
     </row>
     <row r="377" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>682</v>
+        <v>667</v>
       </c>
       <c r="B377" t="s">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="C377" t="s">
         <v>646</v>
       </c>
       <c r="D377" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="E377" t="s">
         <v>25</v>
@@ -20510,16 +20854,16 @@
     </row>
     <row r="378" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="B378" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="C378" t="s">
         <v>646</v>
       </c>
       <c r="D378" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="E378" t="s">
         <v>25</v>
@@ -20548,16 +20892,16 @@
     </row>
     <row r="379" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="B379" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="C379" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D379" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="E379" t="s">
         <v>25</v>
@@ -20586,16 +20930,16 @@
     </row>
     <row r="380" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="B380" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="C380" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D380" t="s">
-        <v>688</v>
+        <v>129</v>
       </c>
       <c r="E380" t="s">
         <v>25</v>
@@ -20624,16 +20968,16 @@
     </row>
     <row r="381" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>691</v>
+        <v>675</v>
       </c>
       <c r="B381" t="s">
-        <v>692</v>
+        <v>676</v>
       </c>
       <c r="C381" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D381" t="s">
-        <v>688</v>
+        <v>129</v>
       </c>
       <c r="E381" t="s">
         <v>25</v>
@@ -20662,16 +21006,16 @@
     </row>
     <row r="382" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>693</v>
+        <v>677</v>
       </c>
       <c r="B382" t="s">
-        <v>694</v>
+        <v>678</v>
       </c>
       <c r="C382" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D382" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="E382" t="s">
         <v>25</v>
@@ -20700,16 +21044,16 @@
     </row>
     <row r="383" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="B383" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="C383" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D383" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="E383" t="s">
         <v>25</v>
@@ -20738,16 +21082,16 @@
     </row>
     <row r="384" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="B384" t="s">
-        <v>698</v>
+        <v>683</v>
       </c>
       <c r="C384" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D384" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="E384" t="s">
         <v>25</v>
@@ -20776,16 +21120,16 @@
     </row>
     <row r="385" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
       <c r="B385" t="s">
-        <v>700</v>
+        <v>684</v>
       </c>
       <c r="C385" t="s">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="D385" t="s">
-        <v>701</v>
+        <v>679</v>
       </c>
       <c r="E385" t="s">
         <v>25</v>
@@ -20814,16 +21158,16 @@
     </row>
     <row r="386" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="B386" t="s">
-        <v>703</v>
+        <v>686</v>
       </c>
       <c r="C386" t="s">
         <v>687</v>
       </c>
       <c r="D386" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="E386" t="s">
         <v>25</v>
@@ -20852,16 +21196,16 @@
     </row>
     <row r="387" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>704</v>
+        <v>689</v>
       </c>
       <c r="B387" t="s">
-        <v>705</v>
+        <v>690</v>
       </c>
       <c r="C387" t="s">
         <v>687</v>
       </c>
       <c r="D387" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="E387" t="s">
         <v>25</v>
@@ -20890,16 +21234,16 @@
     </row>
     <row r="388" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>706</v>
+        <v>691</v>
       </c>
       <c r="B388" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="C388" t="s">
         <v>687</v>
       </c>
       <c r="D388" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="E388" t="s">
         <v>25</v>
@@ -20928,16 +21272,16 @@
     </row>
     <row r="389" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>709</v>
+        <v>693</v>
       </c>
       <c r="B389" t="s">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="C389" t="s">
         <v>687</v>
       </c>
       <c r="D389" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="E389" t="s">
         <v>25</v>
@@ -20966,16 +21310,16 @@
     </row>
     <row r="390" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="B390" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="C390" t="s">
         <v>687</v>
       </c>
       <c r="D390" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="E390" t="s">
         <v>25</v>
@@ -21004,16 +21348,16 @@
     </row>
     <row r="391" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="B391" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="C391" t="s">
         <v>687</v>
       </c>
       <c r="D391" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="E391" t="s">
         <v>25</v>
@@ -21042,16 +21386,16 @@
     </row>
     <row r="392" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="B392" t="s">
-        <v>716</v>
+        <v>700</v>
       </c>
       <c r="C392" t="s">
         <v>687</v>
       </c>
       <c r="D392" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="E392" t="s">
         <v>25</v>
@@ -21080,16 +21424,16 @@
     </row>
     <row r="393" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="B393" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="C393" t="s">
         <v>687</v>
       </c>
       <c r="D393" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="E393" t="s">
         <v>25</v>
@@ -21118,16 +21462,16 @@
     </row>
     <row r="394" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>719</v>
+        <v>704</v>
       </c>
       <c r="B394" t="s">
-        <v>720</v>
+        <v>705</v>
       </c>
       <c r="C394" t="s">
         <v>687</v>
       </c>
       <c r="D394" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="E394" t="s">
         <v>25</v>
@@ -21156,16 +21500,16 @@
     </row>
     <row r="395" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="B395" t="s">
-        <v>722</v>
+        <v>707</v>
       </c>
       <c r="C395" t="s">
         <v>687</v>
       </c>
       <c r="D395" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="E395" t="s">
         <v>25</v>
@@ -21194,16 +21538,16 @@
     </row>
     <row r="396" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>724</v>
+        <v>709</v>
       </c>
       <c r="B396" t="s">
-        <v>725</v>
+        <v>710</v>
       </c>
       <c r="C396" t="s">
         <v>687</v>
       </c>
       <c r="D396" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="E396" t="s">
         <v>25</v>
@@ -21232,16 +21576,16 @@
     </row>
     <row r="397" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>726</v>
+        <v>711</v>
       </c>
       <c r="B397" t="s">
-        <v>727</v>
+        <v>712</v>
       </c>
       <c r="C397" t="s">
         <v>687</v>
       </c>
       <c r="D397" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="E397" t="s">
         <v>25</v>
@@ -21270,16 +21614,16 @@
     </row>
     <row r="398" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>728</v>
+        <v>713</v>
       </c>
       <c r="B398" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
       <c r="C398" t="s">
         <v>687</v>
       </c>
       <c r="D398" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="E398" t="s">
         <v>25</v>
@@ -21308,16 +21652,16 @@
     </row>
     <row r="399" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="B399" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="C399" t="s">
         <v>687</v>
       </c>
       <c r="D399" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="E399" t="s">
         <v>25</v>
@@ -21346,16 +21690,16 @@
     </row>
     <row r="400" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="B400" t="s">
-        <v>733</v>
+        <v>716</v>
       </c>
       <c r="C400" t="s">
         <v>687</v>
       </c>
       <c r="D400" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="E400" t="s">
         <v>25</v>
@@ -21384,16 +21728,16 @@
     </row>
     <row r="401" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>735</v>
+        <v>719</v>
       </c>
       <c r="B401" t="s">
-        <v>736</v>
+        <v>720</v>
       </c>
       <c r="C401" t="s">
         <v>687</v>
       </c>
       <c r="D401" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="E401" t="s">
         <v>25</v>
@@ -21422,16 +21766,16 @@
     </row>
     <row r="402" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
       <c r="B402" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
       <c r="C402" t="s">
         <v>687</v>
       </c>
       <c r="D402" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="E402" t="s">
         <v>25</v>
@@ -21460,16 +21804,16 @@
     </row>
     <row r="403" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>739</v>
+        <v>724</v>
       </c>
       <c r="B403" t="s">
-        <v>740</v>
+        <v>725</v>
       </c>
       <c r="C403" t="s">
         <v>687</v>
       </c>
       <c r="D403" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="E403" t="s">
         <v>25</v>
@@ -21498,16 +21842,16 @@
     </row>
     <row r="404" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>741</v>
+        <v>726</v>
       </c>
       <c r="B404" t="s">
-        <v>742</v>
+        <v>727</v>
       </c>
       <c r="C404" t="s">
         <v>687</v>
       </c>
       <c r="D404" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="E404" t="s">
         <v>25</v>
@@ -21536,16 +21880,16 @@
     </row>
     <row r="405" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>743</v>
+        <v>728</v>
       </c>
       <c r="B405" t="s">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="C405" t="s">
         <v>687</v>
       </c>
       <c r="D405" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="E405" t="s">
         <v>25</v>
@@ -21574,16 +21918,16 @@
     </row>
     <row r="406" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="B406" t="s">
-        <v>746</v>
+        <v>731</v>
       </c>
       <c r="C406" t="s">
         <v>687</v>
       </c>
       <c r="D406" t="s">
-        <v>747</v>
+        <v>723</v>
       </c>
       <c r="E406" t="s">
         <v>25</v>
@@ -21612,16 +21956,16 @@
     </row>
     <row r="407" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
       <c r="B407" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
       <c r="C407" t="s">
         <v>687</v>
       </c>
       <c r="D407" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="E407" t="s">
         <v>25</v>
@@ -21650,16 +21994,16 @@
     </row>
     <row r="408" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="B408" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
       <c r="C408" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D408" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E408" t="s">
         <v>25</v>
@@ -21688,16 +22032,16 @@
     </row>
     <row r="409" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>754</v>
+        <v>737</v>
       </c>
       <c r="B409" t="s">
-        <v>755</v>
+        <v>738</v>
       </c>
       <c r="C409" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D409" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E409" t="s">
         <v>25</v>
@@ -21726,16 +22070,16 @@
     </row>
     <row r="410" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>756</v>
+        <v>739</v>
       </c>
       <c r="B410" t="s">
-        <v>757</v>
+        <v>740</v>
       </c>
       <c r="C410" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D410" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E410" t="s">
         <v>25</v>
@@ -21764,16 +22108,16 @@
     </row>
     <row r="411" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>758</v>
+        <v>741</v>
       </c>
       <c r="B411" t="s">
-        <v>759</v>
+        <v>742</v>
       </c>
       <c r="C411" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D411" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E411" t="s">
         <v>25</v>
@@ -21802,16 +22146,16 @@
     </row>
     <row r="412" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>760</v>
+        <v>743</v>
       </c>
       <c r="B412" t="s">
-        <v>761</v>
+        <v>744</v>
       </c>
       <c r="C412" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D412" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E412" t="s">
         <v>25</v>
@@ -21840,16 +22184,16 @@
     </row>
     <row r="413" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="B413" t="s">
-        <v>763</v>
+        <v>746</v>
       </c>
       <c r="C413" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D413" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="E413" t="s">
         <v>25</v>
@@ -21878,16 +22222,16 @@
     </row>
     <row r="414" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="B414" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="C414" t="s">
-        <v>752</v>
+        <v>687</v>
       </c>
       <c r="D414" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="E414" t="s">
         <v>25</v>
@@ -21916,10 +22260,10 @@
     </row>
     <row r="415" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="B415" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="C415" t="s">
         <v>752</v>
@@ -21954,10 +22298,10 @@
     </row>
     <row r="416" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="B416" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="C416" t="s">
         <v>752</v>
@@ -21992,10 +22336,10 @@
     </row>
     <row r="417" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="B417" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="C417" t="s">
         <v>752</v>
@@ -22030,10 +22374,10 @@
     </row>
     <row r="418" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>772</v>
+        <v>758</v>
       </c>
       <c r="B418" t="s">
-        <v>773</v>
+        <v>759</v>
       </c>
       <c r="C418" t="s">
         <v>752</v>
@@ -22068,10 +22412,10 @@
     </row>
     <row r="419" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="B419" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="C419" t="s">
         <v>752</v>
@@ -22106,10 +22450,10 @@
     </row>
     <row r="420" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="B420" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="C420" t="s">
         <v>752</v>
@@ -22144,16 +22488,16 @@
     </row>
     <row r="421" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>778</v>
+        <v>764</v>
       </c>
       <c r="B421" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="C421" t="s">
         <v>752</v>
       </c>
       <c r="D421" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="E421" t="s">
         <v>25</v>
@@ -22182,16 +22526,16 @@
     </row>
     <row r="422" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="B422" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="C422" t="s">
         <v>752</v>
       </c>
       <c r="D422" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="E422" t="s">
         <v>25</v>
@@ -22220,16 +22564,16 @@
     </row>
     <row r="423" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="B423" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="C423" t="s">
         <v>752</v>
       </c>
       <c r="D423" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="E423" t="s">
         <v>25</v>
@@ -22258,16 +22602,16 @@
     </row>
     <row r="424" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="B424" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="C424" t="s">
         <v>752</v>
       </c>
       <c r="D424" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="E424" t="s">
         <v>25</v>
@@ -22296,16 +22640,16 @@
     </row>
     <row r="425" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
       <c r="B425" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="C425" t="s">
         <v>752</v>
       </c>
       <c r="D425" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="E425" t="s">
         <v>25</v>
@@ -22334,16 +22678,16 @@
     </row>
     <row r="426" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="B426" t="s">
-        <v>790</v>
+        <v>775</v>
       </c>
       <c r="C426" t="s">
         <v>752</v>
       </c>
       <c r="D426" t="s">
-        <v>202</v>
+        <v>753</v>
       </c>
       <c r="E426" t="s">
         <v>25</v>
@@ -22372,16 +22716,16 @@
     </row>
     <row r="427" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="B427" t="s">
-        <v>792</v>
+        <v>777</v>
       </c>
       <c r="C427" t="s">
         <v>752</v>
       </c>
       <c r="D427" t="s">
-        <v>202</v>
+        <v>753</v>
       </c>
       <c r="E427" t="s">
         <v>25</v>
@@ -22410,16 +22754,16 @@
     </row>
     <row r="428" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="B428" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="C428" t="s">
         <v>752</v>
       </c>
       <c r="D428" t="s">
-        <v>202</v>
+        <v>780</v>
       </c>
       <c r="E428" t="s">
         <v>25</v>
@@ -22448,16 +22792,16 @@
     </row>
     <row r="429" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="B429" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="C429" t="s">
         <v>752</v>
       </c>
       <c r="D429" t="s">
-        <v>797</v>
+        <v>780</v>
       </c>
       <c r="E429" t="s">
         <v>25</v>
@@ -22486,16 +22830,16 @@
     </row>
     <row r="430" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>798</v>
+        <v>783</v>
       </c>
       <c r="B430" t="s">
-        <v>799</v>
+        <v>784</v>
       </c>
       <c r="C430" t="s">
         <v>752</v>
       </c>
       <c r="D430" t="s">
-        <v>797</v>
+        <v>780</v>
       </c>
       <c r="E430" t="s">
         <v>25</v>
@@ -22524,16 +22868,16 @@
     </row>
     <row r="431" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>800</v>
+        <v>785</v>
       </c>
       <c r="B431" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="C431" t="s">
         <v>752</v>
       </c>
       <c r="D431" t="s">
-        <v>802</v>
+        <v>780</v>
       </c>
       <c r="E431" t="s">
         <v>25</v>
@@ -22562,16 +22906,16 @@
     </row>
     <row r="432" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>803</v>
+        <v>787</v>
       </c>
       <c r="B432" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="C432" t="s">
         <v>752</v>
       </c>
       <c r="D432" t="s">
-        <v>802</v>
+        <v>780</v>
       </c>
       <c r="E432" t="s">
         <v>25</v>
@@ -22600,16 +22944,16 @@
     </row>
     <row r="433" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="B433" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="C433" t="s">
         <v>752</v>
       </c>
       <c r="D433" t="s">
-        <v>802</v>
+        <v>202</v>
       </c>
       <c r="E433" t="s">
         <v>25</v>
@@ -22638,16 +22982,16 @@
     </row>
     <row r="434" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>807</v>
+        <v>791</v>
       </c>
       <c r="B434" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="C434" t="s">
         <v>752</v>
       </c>
       <c r="D434" t="s">
-        <v>809</v>
+        <v>202</v>
       </c>
       <c r="E434" t="s">
         <v>25</v>
@@ -22676,16 +23020,16 @@
     </row>
     <row r="435" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>810</v>
+        <v>793</v>
       </c>
       <c r="B435" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
       <c r="C435" t="s">
         <v>752</v>
       </c>
       <c r="D435" t="s">
-        <v>809</v>
+        <v>202</v>
       </c>
       <c r="E435" t="s">
         <v>25</v>
@@ -22714,16 +23058,16 @@
     </row>
     <row r="436" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>812</v>
+        <v>795</v>
       </c>
       <c r="B436" t="s">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="C436" t="s">
         <v>752</v>
       </c>
       <c r="D436" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="E436" t="s">
         <v>25</v>
@@ -22752,16 +23096,16 @@
     </row>
     <row r="437" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>814</v>
+        <v>798</v>
       </c>
       <c r="B437" t="s">
-        <v>815</v>
+        <v>799</v>
       </c>
       <c r="C437" t="s">
         <v>752</v>
       </c>
       <c r="D437" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="E437" t="s">
         <v>25</v>
@@ -22790,16 +23134,16 @@
     </row>
     <row r="438" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>816</v>
+        <v>800</v>
       </c>
       <c r="B438" t="s">
-        <v>817</v>
+        <v>801</v>
       </c>
       <c r="C438" t="s">
         <v>752</v>
       </c>
       <c r="D438" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="E438" t="s">
         <v>25</v>
@@ -22828,16 +23172,16 @@
     </row>
     <row r="439" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>818</v>
+        <v>803</v>
       </c>
       <c r="B439" t="s">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="C439" t="s">
         <v>752</v>
       </c>
       <c r="D439" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="E439" t="s">
         <v>25</v>
@@ -22866,16 +23210,16 @@
     </row>
     <row r="440" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="B440" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="C440" t="s">
         <v>752</v>
       </c>
       <c r="D440" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="E440" t="s">
         <v>25</v>
@@ -22904,10 +23248,10 @@
     </row>
     <row r="441" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="B441" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="C441" t="s">
         <v>752</v>
@@ -22942,10 +23286,10 @@
     </row>
     <row r="442" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="B442" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="C442" t="s">
         <v>752</v>
@@ -22980,10 +23324,10 @@
     </row>
     <row r="443" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="B443" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="C443" t="s">
         <v>752</v>
@@ -23018,10 +23362,10 @@
     </row>
     <row r="444" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>828</v>
+        <v>814</v>
       </c>
       <c r="B444" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
       <c r="C444" t="s">
         <v>752</v>
@@ -23056,10 +23400,10 @@
     </row>
     <row r="445" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>830</v>
+        <v>816</v>
       </c>
       <c r="B445" t="s">
-        <v>831</v>
+        <v>817</v>
       </c>
       <c r="C445" t="s">
         <v>752</v>
@@ -23094,16 +23438,16 @@
     </row>
     <row r="446" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
       <c r="B446" t="s">
-        <v>833</v>
+        <v>819</v>
       </c>
       <c r="C446" t="s">
         <v>752</v>
       </c>
       <c r="D446" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="E446" t="s">
         <v>25</v>
@@ -23132,16 +23476,16 @@
     </row>
     <row r="447" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>835</v>
+        <v>820</v>
       </c>
       <c r="B447" t="s">
-        <v>836</v>
+        <v>821</v>
       </c>
       <c r="C447" t="s">
         <v>752</v>
       </c>
       <c r="D447" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="E447" t="s">
         <v>25</v>
@@ -23170,16 +23514,16 @@
     </row>
     <row r="448" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="B448" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="C448" t="s">
         <v>752</v>
       </c>
       <c r="D448" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="E448" t="s">
         <v>25</v>
@@ -23208,16 +23552,16 @@
     </row>
     <row r="449" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>839</v>
+        <v>824</v>
       </c>
       <c r="B449" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="C449" t="s">
         <v>752</v>
       </c>
       <c r="D449" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="E449" t="s">
         <v>25</v>
@@ -23246,16 +23590,16 @@
     </row>
     <row r="450" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>841</v>
+        <v>826</v>
       </c>
       <c r="B450" t="s">
-        <v>842</v>
+        <v>827</v>
       </c>
       <c r="C450" t="s">
         <v>752</v>
       </c>
       <c r="D450" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="E450" t="s">
         <v>25</v>
@@ -23284,16 +23628,16 @@
     </row>
     <row r="451" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>843</v>
+        <v>828</v>
       </c>
       <c r="B451" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="C451" t="s">
         <v>752</v>
       </c>
       <c r="D451" t="s">
-        <v>845</v>
+        <v>809</v>
       </c>
       <c r="E451" t="s">
         <v>25</v>
@@ -23322,16 +23666,16 @@
     </row>
     <row r="452" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>846</v>
+        <v>830</v>
       </c>
       <c r="B452" t="s">
-        <v>847</v>
+        <v>831</v>
       </c>
       <c r="C452" t="s">
         <v>752</v>
       </c>
       <c r="D452" t="s">
-        <v>845</v>
+        <v>809</v>
       </c>
       <c r="E452" t="s">
         <v>25</v>
@@ -23360,16 +23704,16 @@
     </row>
     <row r="453" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="B453" t="s">
-        <v>849</v>
+        <v>833</v>
       </c>
       <c r="C453" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D453" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="E453" t="s">
         <v>25</v>
@@ -23398,16 +23742,16 @@
     </row>
     <row r="454" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>852</v>
+        <v>835</v>
       </c>
       <c r="B454" t="s">
-        <v>853</v>
+        <v>836</v>
       </c>
       <c r="C454" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D454" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="E454" t="s">
         <v>25</v>
@@ -23436,16 +23780,16 @@
     </row>
     <row r="455" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>854</v>
+        <v>837</v>
       </c>
       <c r="B455" t="s">
-        <v>855</v>
+        <v>838</v>
       </c>
       <c r="C455" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D455" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="E455" t="s">
         <v>25</v>
@@ -23474,16 +23818,16 @@
     </row>
     <row r="456" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>856</v>
+        <v>839</v>
       </c>
       <c r="B456" t="s">
-        <v>857</v>
+        <v>840</v>
       </c>
       <c r="C456" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D456" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="E456" t="s">
         <v>25</v>
@@ -23512,16 +23856,16 @@
     </row>
     <row r="457" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>858</v>
+        <v>841</v>
       </c>
       <c r="B457" t="s">
-        <v>859</v>
+        <v>842</v>
       </c>
       <c r="C457" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D457" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="E457" t="s">
         <v>25</v>
@@ -23550,16 +23894,16 @@
     </row>
     <row r="458" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>860</v>
+        <v>843</v>
       </c>
       <c r="B458" t="s">
-        <v>861</v>
+        <v>844</v>
       </c>
       <c r="C458" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D458" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="E458" t="s">
         <v>25</v>
@@ -23588,16 +23932,16 @@
     </row>
     <row r="459" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>862</v>
+        <v>846</v>
       </c>
       <c r="B459" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="C459" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="D459" t="s">
-        <v>864</v>
+        <v>845</v>
       </c>
       <c r="E459" t="s">
         <v>25</v>
@@ -23626,16 +23970,16 @@
     </row>
     <row r="460" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>865</v>
+        <v>848</v>
       </c>
       <c r="B460" t="s">
-        <v>866</v>
+        <v>849</v>
       </c>
       <c r="C460" t="s">
         <v>850</v>
       </c>
       <c r="D460" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="E460" t="s">
         <v>25</v>
@@ -23664,16 +24008,16 @@
     </row>
     <row r="461" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="B461" t="s">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="C461" t="s">
         <v>850</v>
       </c>
       <c r="D461" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="E461" t="s">
         <v>25</v>
@@ -23702,16 +24046,16 @@
     </row>
     <row r="462" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>869</v>
+        <v>854</v>
       </c>
       <c r="B462" t="s">
-        <v>870</v>
+        <v>855</v>
       </c>
       <c r="C462" t="s">
         <v>850</v>
       </c>
       <c r="D462" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="E462" t="s">
         <v>25</v>
@@ -23740,16 +24084,16 @@
     </row>
     <row r="463" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
       <c r="B463" t="s">
-        <v>872</v>
+        <v>857</v>
       </c>
       <c r="C463" t="s">
         <v>850</v>
       </c>
       <c r="D463" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="E463" t="s">
         <v>25</v>
@@ -23778,16 +24122,16 @@
     </row>
     <row r="464" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>873</v>
+        <v>858</v>
       </c>
       <c r="B464" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
       <c r="C464" t="s">
         <v>850</v>
       </c>
       <c r="D464" t="s">
-        <v>875</v>
+        <v>851</v>
       </c>
       <c r="E464" t="s">
         <v>25</v>
@@ -23816,16 +24160,16 @@
     </row>
     <row r="465" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>876</v>
+        <v>860</v>
       </c>
       <c r="B465" t="s">
-        <v>877</v>
+        <v>861</v>
       </c>
       <c r="C465" t="s">
         <v>850</v>
       </c>
       <c r="D465" t="s">
-        <v>875</v>
+        <v>851</v>
       </c>
       <c r="E465" t="s">
         <v>25</v>
@@ -23854,16 +24198,16 @@
     </row>
     <row r="466" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>878</v>
+        <v>862</v>
       </c>
       <c r="B466" t="s">
-        <v>879</v>
+        <v>863</v>
       </c>
       <c r="C466" t="s">
         <v>850</v>
       </c>
       <c r="D466" t="s">
-        <v>875</v>
+        <v>864</v>
       </c>
       <c r="E466" t="s">
         <v>25</v>
@@ -23892,16 +24236,16 @@
     </row>
     <row r="467" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="B467" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="C467" t="s">
         <v>850</v>
       </c>
       <c r="D467" t="s">
-        <v>882</v>
+        <v>864</v>
       </c>
       <c r="E467" t="s">
         <v>25</v>
@@ -23930,16 +24274,16 @@
     </row>
     <row r="468" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>883</v>
+        <v>867</v>
       </c>
       <c r="B468" t="s">
-        <v>884</v>
+        <v>868</v>
       </c>
       <c r="C468" t="s">
         <v>850</v>
       </c>
       <c r="D468" t="s">
-        <v>882</v>
+        <v>864</v>
       </c>
       <c r="E468" t="s">
         <v>25</v>
@@ -23968,16 +24312,16 @@
     </row>
     <row r="469" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>885</v>
+        <v>869</v>
       </c>
       <c r="B469" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="C469" t="s">
         <v>850</v>
       </c>
       <c r="D469" t="s">
-        <v>887</v>
+        <v>864</v>
       </c>
       <c r="E469" t="s">
         <v>25</v>
@@ -24006,16 +24350,16 @@
     </row>
     <row r="470" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>888</v>
+        <v>871</v>
       </c>
       <c r="B470" t="s">
-        <v>889</v>
+        <v>872</v>
       </c>
       <c r="C470" t="s">
         <v>850</v>
       </c>
       <c r="D470" t="s">
-        <v>887</v>
+        <v>864</v>
       </c>
       <c r="E470" t="s">
         <v>25</v>
@@ -24044,16 +24388,16 @@
     </row>
     <row r="471" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>890</v>
+        <v>873</v>
       </c>
       <c r="B471" t="s">
-        <v>891</v>
+        <v>874</v>
       </c>
       <c r="C471" t="s">
         <v>850</v>
       </c>
       <c r="D471" t="s">
-        <v>887</v>
+        <v>875</v>
       </c>
       <c r="E471" t="s">
         <v>25</v>
@@ -24082,16 +24426,16 @@
     </row>
     <row r="472" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>892</v>
+        <v>876</v>
       </c>
       <c r="B472" t="s">
-        <v>893</v>
+        <v>877</v>
       </c>
       <c r="C472" t="s">
         <v>850</v>
       </c>
       <c r="D472" t="s">
-        <v>887</v>
+        <v>875</v>
       </c>
       <c r="E472" t="s">
         <v>25</v>
@@ -24120,16 +24464,16 @@
     </row>
     <row r="473" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>894</v>
+        <v>878</v>
       </c>
       <c r="B473" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
       <c r="C473" t="s">
         <v>850</v>
       </c>
       <c r="D473" t="s">
-        <v>896</v>
+        <v>875</v>
       </c>
       <c r="E473" t="s">
         <v>25</v>
@@ -24158,16 +24502,16 @@
     </row>
     <row r="474" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>897</v>
+        <v>880</v>
       </c>
       <c r="B474" t="s">
-        <v>898</v>
+        <v>881</v>
       </c>
       <c r="C474" t="s">
         <v>850</v>
       </c>
       <c r="D474" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
       <c r="E474" t="s">
         <v>25</v>
@@ -24196,16 +24540,16 @@
     </row>
     <row r="475" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>899</v>
+        <v>883</v>
       </c>
       <c r="B475" t="s">
-        <v>900</v>
+        <v>884</v>
       </c>
       <c r="C475" t="s">
         <v>850</v>
       </c>
       <c r="D475" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
       <c r="E475" t="s">
         <v>25</v>
@@ -24234,16 +24578,16 @@
     </row>
     <row r="476" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>901</v>
+        <v>885</v>
       </c>
       <c r="B476" t="s">
-        <v>902</v>
+        <v>886</v>
       </c>
       <c r="C476" t="s">
         <v>850</v>
       </c>
       <c r="D476" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="E476" t="s">
         <v>25</v>
@@ -24272,16 +24616,16 @@
     </row>
     <row r="477" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>903</v>
+        <v>888</v>
       </c>
       <c r="B477" t="s">
-        <v>904</v>
+        <v>889</v>
       </c>
       <c r="C477" t="s">
         <v>850</v>
       </c>
       <c r="D477" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="E477" t="s">
         <v>25</v>
@@ -24310,16 +24654,16 @@
     </row>
     <row r="478" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>905</v>
+        <v>890</v>
       </c>
       <c r="B478" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="C478" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D478" t="s">
-        <v>25</v>
+        <v>887</v>
       </c>
       <c r="E478" t="s">
         <v>25</v>
@@ -24348,16 +24692,16 @@
     </row>
     <row r="479" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>908</v>
+        <v>892</v>
       </c>
       <c r="B479" t="s">
-        <v>909</v>
+        <v>893</v>
       </c>
       <c r="C479" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D479" t="s">
-        <v>25</v>
+        <v>887</v>
       </c>
       <c r="E479" t="s">
         <v>25</v>
@@ -24386,16 +24730,16 @@
     </row>
     <row r="480" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>910</v>
+        <v>894</v>
       </c>
       <c r="B480" t="s">
-        <v>911</v>
+        <v>895</v>
       </c>
       <c r="C480" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D480" t="s">
-        <v>25</v>
+        <v>896</v>
       </c>
       <c r="E480" t="s">
         <v>25</v>
@@ -24424,16 +24768,16 @@
     </row>
     <row r="481" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="B481" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="C481" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D481" t="s">
-        <v>25</v>
+        <v>896</v>
       </c>
       <c r="E481" t="s">
         <v>25</v>
@@ -24462,16 +24806,16 @@
     </row>
     <row r="482" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="B482" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="C482" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D482" t="s">
-        <v>25</v>
+        <v>896</v>
       </c>
       <c r="E482" t="s">
         <v>25</v>
@@ -24500,16 +24844,16 @@
     </row>
     <row r="483" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="B483" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="C483" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D483" t="s">
-        <v>25</v>
+        <v>896</v>
       </c>
       <c r="E483" t="s">
         <v>25</v>
@@ -24538,16 +24882,16 @@
     </row>
     <row r="484" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
       <c r="B484" t="s">
-        <v>919</v>
+        <v>904</v>
       </c>
       <c r="C484" t="s">
-        <v>907</v>
+        <v>850</v>
       </c>
       <c r="D484" t="s">
-        <v>25</v>
+        <v>896</v>
       </c>
       <c r="E484" t="s">
         <v>25</v>
@@ -24576,10 +24920,10 @@
     </row>
     <row r="485" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="B485" t="s">
-        <v>921</v>
+        <v>906</v>
       </c>
       <c r="C485" t="s">
         <v>907</v>
@@ -24614,10 +24958,10 @@
     </row>
     <row r="486" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>922</v>
+        <v>908</v>
       </c>
       <c r="B486" t="s">
-        <v>923</v>
+        <v>909</v>
       </c>
       <c r="C486" t="s">
         <v>907</v>
@@ -24652,10 +24996,10 @@
     </row>
     <row r="487" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>924</v>
+        <v>910</v>
       </c>
       <c r="B487" t="s">
-        <v>925</v>
+        <v>911</v>
       </c>
       <c r="C487" t="s">
         <v>907</v>
@@ -24690,10 +25034,10 @@
     </row>
     <row r="488" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>926</v>
+        <v>912</v>
       </c>
       <c r="B488" t="s">
-        <v>927</v>
+        <v>913</v>
       </c>
       <c r="C488" t="s">
         <v>907</v>
@@ -24728,10 +25072,10 @@
     </row>
     <row r="489" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B489" t="s">
-        <v>929</v>
+        <v>915</v>
       </c>
       <c r="C489" t="s">
         <v>907</v>
@@ -24766,10 +25110,10 @@
     </row>
     <row r="490" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>930</v>
+        <v>916</v>
       </c>
       <c r="B490" t="s">
-        <v>931</v>
+        <v>917</v>
       </c>
       <c r="C490" t="s">
         <v>907</v>
@@ -24804,10 +25148,10 @@
     </row>
     <row r="491" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>932</v>
+        <v>918</v>
       </c>
       <c r="B491" t="s">
-        <v>933</v>
+        <v>919</v>
       </c>
       <c r="C491" t="s">
         <v>907</v>
@@ -24842,10 +25186,10 @@
     </row>
     <row r="492" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>934</v>
+        <v>920</v>
       </c>
       <c r="B492" t="s">
-        <v>935</v>
+        <v>921</v>
       </c>
       <c r="C492" t="s">
         <v>907</v>
@@ -24880,16 +25224,16 @@
     </row>
     <row r="493" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>936</v>
+        <v>922</v>
       </c>
       <c r="B493" t="s">
-        <v>937</v>
+        <v>923</v>
       </c>
       <c r="C493" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D493" t="s">
-        <v>939</v>
+        <v>25</v>
       </c>
       <c r="E493" t="s">
         <v>25</v>
@@ -24918,16 +25262,16 @@
     </row>
     <row r="494" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>940</v>
+        <v>924</v>
       </c>
       <c r="B494" t="s">
-        <v>941</v>
+        <v>925</v>
       </c>
       <c r="C494" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D494" t="s">
-        <v>939</v>
+        <v>25</v>
       </c>
       <c r="E494" t="s">
         <v>25</v>
@@ -24956,16 +25300,16 @@
     </row>
     <row r="495" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>942</v>
+        <v>926</v>
       </c>
       <c r="B495" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
       <c r="C495" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D495" t="s">
-        <v>939</v>
+        <v>25</v>
       </c>
       <c r="E495" t="s">
         <v>25</v>
@@ -24994,16 +25338,16 @@
     </row>
     <row r="496" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>944</v>
+        <v>928</v>
       </c>
       <c r="B496" t="s">
-        <v>945</v>
+        <v>929</v>
       </c>
       <c r="C496" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D496" t="s">
-        <v>939</v>
+        <v>25</v>
       </c>
       <c r="E496" t="s">
         <v>25</v>
@@ -25032,16 +25376,16 @@
     </row>
     <row r="497" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>946</v>
+        <v>930</v>
       </c>
       <c r="B497" t="s">
-        <v>947</v>
+        <v>931</v>
       </c>
       <c r="C497" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D497" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E497" t="s">
         <v>25</v>
@@ -25070,16 +25414,16 @@
     </row>
     <row r="498" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>949</v>
+        <v>932</v>
       </c>
       <c r="B498" t="s">
-        <v>950</v>
+        <v>933</v>
       </c>
       <c r="C498" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D498" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E498" t="s">
         <v>25</v>
@@ -25108,16 +25452,16 @@
     </row>
     <row r="499" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>951</v>
+        <v>934</v>
       </c>
       <c r="B499" t="s">
-        <v>952</v>
+        <v>935</v>
       </c>
       <c r="C499" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="D499" t="s">
-        <v>948</v>
+        <v>25</v>
       </c>
       <c r="E499" t="s">
         <v>25</v>
@@ -25146,16 +25490,16 @@
     </row>
     <row r="500" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>953</v>
+        <v>936</v>
       </c>
       <c r="B500" t="s">
-        <v>954</v>
+        <v>937</v>
       </c>
       <c r="C500" t="s">
         <v>938</v>
       </c>
       <c r="D500" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="E500" t="s">
         <v>25</v>
@@ -25184,16 +25528,16 @@
     </row>
     <row r="501" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>955</v>
+        <v>940</v>
       </c>
       <c r="B501" t="s">
-        <v>956</v>
+        <v>941</v>
       </c>
       <c r="C501" t="s">
         <v>938</v>
       </c>
       <c r="D501" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="E501" t="s">
         <v>25</v>
@@ -25222,16 +25566,16 @@
     </row>
     <row r="502" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>957</v>
+        <v>942</v>
       </c>
       <c r="B502" t="s">
-        <v>958</v>
+        <v>943</v>
       </c>
       <c r="C502" t="s">
         <v>938</v>
       </c>
       <c r="D502" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="E502" t="s">
         <v>25</v>
@@ -25260,16 +25604,16 @@
     </row>
     <row r="503" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>959</v>
+        <v>944</v>
       </c>
       <c r="B503" t="s">
-        <v>960</v>
+        <v>945</v>
       </c>
       <c r="C503" t="s">
         <v>938</v>
       </c>
       <c r="D503" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="E503" t="s">
         <v>25</v>
@@ -25298,16 +25642,16 @@
     </row>
     <row r="504" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
       <c r="B504" t="s">
-        <v>962</v>
+        <v>947</v>
       </c>
       <c r="C504" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D504" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E504" t="s">
         <v>25</v>
@@ -25336,16 +25680,16 @@
     </row>
     <row r="505" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="B505" t="s">
-        <v>966</v>
+        <v>950</v>
       </c>
       <c r="C505" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D505" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E505" t="s">
         <v>25</v>
@@ -25374,16 +25718,16 @@
     </row>
     <row r="506" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>967</v>
+        <v>951</v>
       </c>
       <c r="B506" t="s">
-        <v>968</v>
+        <v>952</v>
       </c>
       <c r="C506" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D506" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E506" t="s">
         <v>25</v>
@@ -25412,16 +25756,16 @@
     </row>
     <row r="507" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>969</v>
+        <v>953</v>
       </c>
       <c r="B507" t="s">
-        <v>970</v>
+        <v>954</v>
       </c>
       <c r="C507" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D507" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E507" t="s">
         <v>25</v>
@@ -25450,16 +25794,16 @@
     </row>
     <row r="508" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="B508" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="C508" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D508" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E508" t="s">
         <v>25</v>
@@ -25488,16 +25832,16 @@
     </row>
     <row r="509" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="B509" t="s">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="C509" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D509" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E509" t="s">
         <v>25</v>
@@ -25526,16 +25870,16 @@
     </row>
     <row r="510" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="B510" t="s">
-        <v>976</v>
+        <v>960</v>
       </c>
       <c r="C510" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="D510" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E510" t="s">
         <v>25</v>
@@ -25564,10 +25908,10 @@
     </row>
     <row r="511" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
       <c r="B511" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
       <c r="C511" t="s">
         <v>963</v>
@@ -25602,16 +25946,16 @@
     </row>
     <row r="512" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>979</v>
+        <v>965</v>
       </c>
       <c r="B512" t="s">
-        <v>980</v>
+        <v>966</v>
       </c>
       <c r="C512" t="s">
         <v>963</v>
       </c>
       <c r="D512" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
       <c r="E512" t="s">
         <v>25</v>
@@ -25640,16 +25984,16 @@
     </row>
     <row r="513" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
       <c r="B513" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="C513" t="s">
         <v>963</v>
       </c>
       <c r="D513" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
       <c r="E513" t="s">
         <v>25</v>
@@ -25678,16 +26022,16 @@
     </row>
     <row r="514" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>984</v>
+        <v>969</v>
       </c>
       <c r="B514" t="s">
-        <v>985</v>
+        <v>970</v>
       </c>
       <c r="C514" t="s">
         <v>963</v>
       </c>
       <c r="D514" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
       <c r="E514" t="s">
         <v>25</v>
@@ -25716,16 +26060,16 @@
     </row>
     <row r="515" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>986</v>
+        <v>971</v>
       </c>
       <c r="B515" t="s">
-        <v>987</v>
+        <v>972</v>
       </c>
       <c r="C515" t="s">
         <v>963</v>
       </c>
       <c r="D515" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
       <c r="E515" t="s">
         <v>25</v>
@@ -25754,16 +26098,16 @@
     </row>
     <row r="516" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>988</v>
+        <v>973</v>
       </c>
       <c r="B516" t="s">
-        <v>989</v>
+        <v>974</v>
       </c>
       <c r="C516" t="s">
         <v>963</v>
       </c>
       <c r="D516" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
       <c r="E516" t="s">
         <v>25</v>
@@ -25792,16 +26136,16 @@
     </row>
     <row r="517" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>990</v>
+        <v>975</v>
       </c>
       <c r="B517" t="s">
-        <v>991</v>
+        <v>976</v>
       </c>
       <c r="C517" t="s">
         <v>963</v>
       </c>
       <c r="D517" t="s">
-        <v>992</v>
+        <v>964</v>
       </c>
       <c r="E517" t="s">
         <v>25</v>
@@ -25830,16 +26174,16 @@
     </row>
     <row r="518" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="B518" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="C518" t="s">
         <v>963</v>
       </c>
       <c r="D518" t="s">
-        <v>992</v>
+        <v>964</v>
       </c>
       <c r="E518" t="s">
         <v>25</v>
@@ -25868,16 +26212,16 @@
     </row>
     <row r="519" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="B519" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="C519" t="s">
         <v>963</v>
       </c>
       <c r="D519" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E519" t="s">
         <v>25</v>
@@ -25906,16 +26250,16 @@
     </row>
     <row r="520" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="B520" t="s">
-        <v>999</v>
+        <v>983</v>
       </c>
       <c r="C520" t="s">
         <v>963</v>
       </c>
       <c r="D520" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E520" t="s">
         <v>25</v>
@@ -25944,16 +26288,16 @@
     </row>
     <row r="521" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="B521" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="C521" t="s">
         <v>963</v>
       </c>
       <c r="D521" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E521" t="s">
         <v>25</v>
@@ -25982,16 +26326,16 @@
     </row>
     <row r="522" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>1002</v>
+        <v>986</v>
       </c>
       <c r="B522" t="s">
-        <v>1003</v>
+        <v>987</v>
       </c>
       <c r="C522" t="s">
         <v>963</v>
       </c>
       <c r="D522" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E522" t="s">
         <v>25</v>
@@ -26020,16 +26364,16 @@
     </row>
     <row r="523" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1004</v>
+        <v>988</v>
       </c>
       <c r="B523" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="C523" t="s">
         <v>963</v>
       </c>
       <c r="D523" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E523" t="s">
         <v>25</v>
@@ -26058,16 +26402,16 @@
     </row>
     <row r="524" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="B524" t="s">
-        <v>1007</v>
+        <v>991</v>
       </c>
       <c r="C524" t="s">
         <v>963</v>
       </c>
       <c r="D524" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="E524" t="s">
         <v>25</v>
@@ -26096,16 +26440,16 @@
     </row>
     <row r="525" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1008</v>
+        <v>993</v>
       </c>
       <c r="B525" t="s">
-        <v>1009</v>
+        <v>994</v>
       </c>
       <c r="C525" t="s">
         <v>963</v>
       </c>
       <c r="D525" t="s">
-        <v>1010</v>
+        <v>992</v>
       </c>
       <c r="E525" t="s">
         <v>25</v>
@@ -26134,16 +26478,16 @@
     </row>
     <row r="526" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1011</v>
+        <v>995</v>
       </c>
       <c r="B526" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="C526" t="s">
         <v>963</v>
       </c>
       <c r="D526" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="E526" t="s">
         <v>25</v>
@@ -26172,16 +26516,16 @@
     </row>
     <row r="527" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1013</v>
+        <v>998</v>
       </c>
       <c r="B527" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="C527" t="s">
         <v>963</v>
       </c>
       <c r="D527" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="E527" t="s">
         <v>25</v>
@@ -26210,16 +26554,16 @@
     </row>
     <row r="528" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1015</v>
+        <v>1000</v>
       </c>
       <c r="B528" t="s">
-        <v>1016</v>
+        <v>1001</v>
       </c>
       <c r="C528" t="s">
         <v>963</v>
       </c>
       <c r="D528" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="E528" t="s">
         <v>25</v>
@@ -26248,16 +26592,16 @@
     </row>
     <row r="529" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1017</v>
+        <v>1002</v>
       </c>
       <c r="B529" t="s">
-        <v>1018</v>
+        <v>1003</v>
       </c>
       <c r="C529" t="s">
         <v>963</v>
       </c>
       <c r="D529" t="s">
-        <v>1019</v>
+        <v>997</v>
       </c>
       <c r="E529" t="s">
         <v>25</v>
@@ -26286,16 +26630,16 @@
     </row>
     <row r="530" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1020</v>
+        <v>1004</v>
       </c>
       <c r="B530" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="C530" t="s">
         <v>963</v>
       </c>
       <c r="D530" t="s">
-        <v>1019</v>
+        <v>997</v>
       </c>
       <c r="E530" t="s">
         <v>25</v>
@@ -26324,16 +26668,16 @@
     </row>
     <row r="531" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="B531" t="s">
-        <v>1023</v>
+        <v>1007</v>
       </c>
       <c r="C531" t="s">
         <v>963</v>
       </c>
       <c r="D531" t="s">
-        <v>1019</v>
+        <v>997</v>
       </c>
       <c r="E531" t="s">
         <v>25</v>
@@ -26362,16 +26706,16 @@
     </row>
     <row r="532" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1024</v>
+        <v>1008</v>
       </c>
       <c r="B532" t="s">
-        <v>1025</v>
+        <v>1009</v>
       </c>
       <c r="C532" t="s">
         <v>963</v>
       </c>
       <c r="D532" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="E532" t="s">
         <v>25</v>
@@ -26400,16 +26744,16 @@
     </row>
     <row r="533" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1026</v>
+        <v>1011</v>
       </c>
       <c r="B533" t="s">
-        <v>1027</v>
+        <v>1012</v>
       </c>
       <c r="C533" t="s">
         <v>963</v>
       </c>
       <c r="D533" t="s">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="E533" t="s">
         <v>25</v>
@@ -26438,16 +26782,16 @@
     </row>
     <row r="534" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
       <c r="B534" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
       <c r="C534" t="s">
         <v>963</v>
       </c>
       <c r="D534" t="s">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="E534" t="s">
         <v>25</v>
@@ -26476,16 +26820,16 @@
     </row>
     <row r="535" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1031</v>
+        <v>1015</v>
       </c>
       <c r="B535" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
       <c r="C535" t="s">
         <v>963</v>
       </c>
       <c r="D535" t="s">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="E535" t="s">
         <v>25</v>
@@ -26514,16 +26858,16 @@
     </row>
     <row r="536" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1033</v>
+        <v>1017</v>
       </c>
       <c r="B536" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="C536" t="s">
         <v>963</v>
       </c>
       <c r="D536" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="E536" t="s">
         <v>25</v>
@@ -26552,16 +26896,16 @@
     </row>
     <row r="537" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1035</v>
+        <v>1020</v>
       </c>
       <c r="B537" t="s">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="C537" t="s">
         <v>963</v>
       </c>
       <c r="D537" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="E537" t="s">
         <v>25</v>
@@ -26590,16 +26934,16 @@
     </row>
     <row r="538" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1038</v>
+        <v>1022</v>
       </c>
       <c r="B538" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="C538" t="s">
         <v>963</v>
       </c>
       <c r="D538" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="E538" t="s">
         <v>25</v>
@@ -26628,16 +26972,16 @@
     </row>
     <row r="539" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="B539" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
       <c r="C539" t="s">
         <v>963</v>
       </c>
       <c r="D539" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="E539" t="s">
         <v>25</v>
@@ -26666,16 +27010,16 @@
     </row>
     <row r="540" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="B540" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="C540" t="s">
         <v>963</v>
       </c>
       <c r="D540" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="E540" t="s">
         <v>25</v>
@@ -26704,16 +27048,16 @@
     </row>
     <row r="541" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1044</v>
+        <v>1029</v>
       </c>
       <c r="B541" t="s">
-        <v>1045</v>
+        <v>1030</v>
       </c>
       <c r="C541" t="s">
         <v>963</v>
       </c>
       <c r="D541" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="E541" t="s">
         <v>25</v>
@@ -26742,16 +27086,16 @@
     </row>
     <row r="542" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1047</v>
+        <v>1031</v>
       </c>
       <c r="B542" t="s">
-        <v>1048</v>
+        <v>1032</v>
       </c>
       <c r="C542" t="s">
         <v>963</v>
       </c>
       <c r="D542" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="E542" t="s">
         <v>25</v>
@@ -26780,16 +27124,16 @@
     </row>
     <row r="543" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>1049</v>
+        <v>1033</v>
       </c>
       <c r="B543" t="s">
-        <v>1050</v>
+        <v>1034</v>
       </c>
       <c r="C543" t="s">
         <v>963</v>
       </c>
       <c r="D543" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="E543" t="s">
         <v>25</v>
@@ -26818,16 +27162,16 @@
     </row>
     <row r="544" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1051</v>
+        <v>1035</v>
       </c>
       <c r="B544" t="s">
-        <v>1052</v>
+        <v>1036</v>
       </c>
       <c r="C544" t="s">
         <v>963</v>
       </c>
       <c r="D544" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="E544" t="s">
         <v>25</v>
@@ -26856,16 +27200,16 @@
     </row>
     <row r="545" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="B545" t="s">
-        <v>1054</v>
+        <v>1039</v>
       </c>
       <c r="C545" t="s">
         <v>963</v>
       </c>
       <c r="D545" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="E545" t="s">
         <v>25</v>
@@ -26894,49 +27238,315 @@
     </row>
     <row r="546" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1055</v>
+        <v>1040</v>
       </c>
       <c r="B546" t="s">
-        <v>1056</v>
+        <v>1041</v>
       </c>
       <c r="C546" t="s">
         <v>963</v>
       </c>
       <c r="D546" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E546" t="s">
+        <v>25</v>
+      </c>
+      <c r="F546" t="s">
+        <v>25</v>
+      </c>
+      <c r="G546" t="s">
+        <v>25</v>
+      </c>
+      <c r="H546" t="s">
+        <v>19</v>
+      </c>
+      <c r="I546" t="s">
+        <v>25</v>
+      </c>
+      <c r="J546" t="s">
+        <v>25</v>
+      </c>
+      <c r="K546" t="s">
+        <v>25</v>
+      </c>
+      <c r="L546" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="547" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C547" t="s">
+        <v>963</v>
+      </c>
+      <c r="D547" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E547" t="s">
+        <v>25</v>
+      </c>
+      <c r="F547" t="s">
+        <v>25</v>
+      </c>
+      <c r="G547" t="s">
+        <v>25</v>
+      </c>
+      <c r="H547" t="s">
+        <v>19</v>
+      </c>
+      <c r="I547" t="s">
+        <v>25</v>
+      </c>
+      <c r="J547" t="s">
+        <v>25</v>
+      </c>
+      <c r="K547" t="s">
+        <v>25</v>
+      </c>
+      <c r="L547" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="548" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C548" t="s">
+        <v>963</v>
+      </c>
+      <c r="D548" t="s">
         <v>1046</v>
       </c>
-      <c r="E546" t="s">
-        <v>25</v>
-      </c>
-      <c r="F546" t="s">
-        <v>25</v>
-      </c>
-      <c r="G546" t="s">
-        <v>25</v>
-      </c>
-      <c r="H546" t="s">
-        <v>19</v>
-      </c>
-      <c r="I546" t="s">
-        <v>25</v>
-      </c>
-      <c r="J546" t="s">
-        <v>25</v>
-      </c>
-      <c r="K546" t="s">
-        <v>25</v>
-      </c>
-      <c r="L546" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="547" spans="1:12" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="548" spans="1:12" ht="15.75" x14ac:dyDescent="0.25"/>
+      <c r="E548" t="s">
+        <v>25</v>
+      </c>
+      <c r="F548" t="s">
+        <v>25</v>
+      </c>
+      <c r="G548" t="s">
+        <v>25</v>
+      </c>
+      <c r="H548" t="s">
+        <v>19</v>
+      </c>
+      <c r="I548" t="s">
+        <v>25</v>
+      </c>
+      <c r="J548" t="s">
+        <v>25</v>
+      </c>
+      <c r="K548" t="s">
+        <v>25</v>
+      </c>
+      <c r="L548" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="549" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C549" t="s">
+        <v>963</v>
+      </c>
+      <c r="D549" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E549" t="s">
+        <v>25</v>
+      </c>
+      <c r="F549" t="s">
+        <v>25</v>
+      </c>
+      <c r="G549" t="s">
+        <v>25</v>
+      </c>
+      <c r="H549" t="s">
+        <v>19</v>
+      </c>
+      <c r="I549" t="s">
+        <v>25</v>
+      </c>
+      <c r="J549" t="s">
+        <v>25</v>
+      </c>
+      <c r="K549" t="s">
+        <v>25</v>
+      </c>
+      <c r="L549" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="550" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C550" t="s">
+        <v>963</v>
+      </c>
+      <c r="D550" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E550" t="s">
+        <v>25</v>
+      </c>
+      <c r="F550" t="s">
+        <v>25</v>
+      </c>
+      <c r="G550" t="s">
+        <v>25</v>
+      </c>
+      <c r="H550" t="s">
+        <v>19</v>
+      </c>
+      <c r="I550" t="s">
+        <v>25</v>
+      </c>
+      <c r="J550" t="s">
+        <v>25</v>
+      </c>
+      <c r="K550" t="s">
+        <v>25</v>
+      </c>
+      <c r="L550" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="551" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C551" t="s">
+        <v>963</v>
+      </c>
+      <c r="D551" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E551" t="s">
+        <v>25</v>
+      </c>
+      <c r="F551" t="s">
+        <v>25</v>
+      </c>
+      <c r="G551" t="s">
+        <v>25</v>
+      </c>
+      <c r="H551" t="s">
+        <v>19</v>
+      </c>
+      <c r="I551" t="s">
+        <v>25</v>
+      </c>
+      <c r="J551" t="s">
+        <v>25</v>
+      </c>
+      <c r="K551" t="s">
+        <v>25</v>
+      </c>
+      <c r="L551" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="552" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C552" t="s">
+        <v>963</v>
+      </c>
+      <c r="D552" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E552" t="s">
+        <v>25</v>
+      </c>
+      <c r="F552" t="s">
+        <v>25</v>
+      </c>
+      <c r="G552" t="s">
+        <v>25</v>
+      </c>
+      <c r="H552" t="s">
+        <v>19</v>
+      </c>
+      <c r="I552" t="s">
+        <v>25</v>
+      </c>
+      <c r="J552" t="s">
+        <v>25</v>
+      </c>
+      <c r="K552" t="s">
+        <v>25</v>
+      </c>
+      <c r="L552" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="553" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C553" t="s">
+        <v>963</v>
+      </c>
+      <c r="D553" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E553" t="s">
+        <v>25</v>
+      </c>
+      <c r="F553" t="s">
+        <v>25</v>
+      </c>
+      <c r="G553" t="s">
+        <v>25</v>
+      </c>
+      <c r="H553" t="s">
+        <v>19</v>
+      </c>
+      <c r="I553" t="s">
+        <v>25</v>
+      </c>
+      <c r="J553" t="s">
+        <v>25</v>
+      </c>
+      <c r="K553" t="s">
+        <v>25</v>
+      </c>
+      <c r="L553" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="554" spans="1:12" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="555" spans="1:12" ht="15.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 B37:E37 G38:L38 B39:L39 B38:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 F10 A11:D12 F12 J10:L10 F11 J11:L11 J12:L12 H10 H11 H12 B17:D17 B18:D18 F17 F18 H17 H18 J17:L17 K18:L18 A28:G28 A21:D21 H21 A22:D24 F24 L21 F22 J22:L22 F23 J23:L23 J24:L24 A34:D36 A33:D33 L33 H24 H22 H23 A25:D25 H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F36 F34 J34:L34 F35 J35:L35 J36:L36 H33 H36 H34 H35 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67 J67:L67 A68 J68:L68 A72 J72:L72 A73 J73:L73 F72 F73:G73 F67:G67 F68:G68 C72:D72 C68:D68 C67:D67 C73:D73 H72 A74 A97:G97 A84 I84:L84 C74:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87 A91:D91 F91 H91:L91 A99:G99 A98:G98 L98 A96:D96 F96 H96:L96 A105:L546 I97:L97 I98:J98 I99:L99 A101:D101 F101 A104:F104 H104:L104 J101:L101 H101" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 B37:E37 G38:L38 B39:L39 B38:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 F10 A11:D12 F12 J10:L10 F11 J11:L11 J12:L12 H10 H11 H12 B17:D17 B18:D18 F17 F18 H17 H18 J17:L17 K18:L18 A28:G28 A21:D21 H21 A22:D24 F24 L21 F22 J22:L22 F23 J23:L23 J24:L24 A34:D36 A33:D33 L33 H24 H22 H23 A25:D25 H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F36 F34 J34:L34 F35 J35:L35 J36:L36 H33 H36 H34 H35 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67 J67:L67 A68 J68:L68 A72 J72:L72 A73 J73:L73 F72 F73:G73 F67:G67 F68:G68 C72:D72 C68:D68 C67:D67 C73:D73 H72 A74 A97:G97 A84 I84:L84 C74:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87 A91:D91 F91 H91:L91 A99:G99 A98:G98 L98 A96:D96 F96 H96:L96 A114:L553 I97:L97 I98:J98 I99:L99 A101:D101 F101 A104:D104 H104:I104 J101:L101 H101 L104 A109:D109 H109:I109 L109 A113:G113 I113:L113" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="675" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58462605-7E05-4219-8AAE-0E80F0824FC9}"/>
+  <xr:revisionPtr revIDLastSave="701" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2186EC46-EFD0-414C-B71F-248AC37D1579}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6572" uniqueCount="1229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6629" uniqueCount="1238">
   <si>
     <t>Codigo</t>
   </si>
@@ -6473,32 +6473,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">La </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Silla para Carro ISOFIX Giratoria 360°</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ofrece un sistema de anclaje seguro que facilita la instalación y brinda mayor estabilidad en cada trayecto. Su giro de 360°, protección lateral reforzada y asiento acolchado proporcionan comodidad y seguridad, adaptándose al crecimiento del niño desde los primeros meses de vida.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="12"/>
@@ -6601,6 +6575,347 @@
 Limpiar el tapizado siguiendo las recomendaciones del fabricante.
 No exceder el peso máximo recomendado.</t>
     </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/monitorwifi/monitor.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/monitorwifi/monitor2.webp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Silla para Carro ISOFIX Giratoria 360°</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ofrece un sistema de anclaje seguro que facilita la instalación y brinda mayor estabilidad en cada trayecto. Su giro de 360°, protección lateral reforzada y asiento acolchado proporcionan comodidad y seguridad, adaptándose al crecimiento del niño desde los primeros meses de vida.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Medidas:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Alto: 60 cm.
+Ancho: 45 cm.
+Profundidad: 50 cm.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Monitor Bebé WiFi C14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> te permite mantenerte conectado con tu bebé en todo momento gracias a su cámara de alta definición y conexión WiFi. Controla la visualización desde tu celular, escucha y habla mediante audio bidireccional, y disfruta de una vigilancia confiable tanto de día como de noche. Su diseño compacto y fácil configuración lo convierten en una excelente opción para el hogar.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Monitor para bebé WiFi con cámara HD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, audio bidireccional y control desde la aplicación móvil, ideal para supervisar a tu bebé en tiempo real desde cualquier lugar.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Cámara HD con transmisión de video en tiempo real.
+Conexión WiFi con control desde aplicación móvil.
+Audio bidireccional (escucha y habla).
+Monitoreo remoto desde cualquier lugar.
+Diseño compacto y fácil de instalar.
+Incluye cámara, base, cable de alimentación y manual.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Beneficios:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Supervisa a tu bebé desde el celular en tiempo real.
+Comunicación directa mediante audio bidireccional.
+Visión clara para monitoreo diurno y nocturno.
+Instalación rápida y configuración sencilla.
+También puede utilizarse para vigilar mascotas o espacios del hogar.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Instalar la cámara en un lugar seguro y con buena visibilidad.
+Mantener el equipo conectado a una red WiFi estable.
+Limpiar la cámara con un paño suave y seco.
+Evitar el contacto con agua o humedad excesiva.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Silla de bebé para carro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con diseño ergonómico y acolchado confortable, ideal para brindar seguridad y comodidad durante los desplazamientos diarios y viajes en familia.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La Silla de Bebé para Carro REF: DD2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> está diseñada para ofrecer un viaje seguro y confortable desde los primeros trayectos. Su estructura resistente, diseño ergonómico y acolchado suave proporcionan el soporte necesario para que el bebé viaje cómodo y protegido. Es una opción práctica, ligera y fácil de mantener, ideal para el uso diario.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Importante:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Este producto se despacha en el color disponible en bodega al momento de la compra. Los colores mostrados en las imágenes son únicamente de referencia y pueden variar según la disponibilidad.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Diseño ergonómico para mayor comodidad.
+Estructura resistente y ligera.
+Acolchado suave para mayor confort.
+Materiales fáciles de limpiar.
+Ideal para transporte infantil.
+Fácil instalación según las instrucciones del fabricante.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Brinda seguridad y estabilidad durante cada viaje.
+Mantiene al bebé cómodo en recorridos cortos y largos.
+Diseño ligero y fácil de transportar.
+Fácil mantenimiento gracias a sus materiales de limpieza sencilla.
+Acompaña el crecimiento del bebé con comodidad y protección.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Verificar siempre la correcta instalación antes de cada viaje.
+Ajustar adecuadamente los sistemas de sujeción.
+Limpiar regularmente la superficie con un paño húmedo y productos suaves.
+Revisar periódicamente el estado de la estructura y los sistemas de seguridad antes de su uso.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/sillacarrodd2/silladd2.webp</t>
   </si>
 </sst>
 </file>
@@ -6996,7 +7311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L561"/>
+  <dimension ref="A1:L562"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -11450,8 +11765,8 @@
       <c r="E122">
         <v>818672</v>
       </c>
-      <c r="F122" t="s">
-        <v>1226</v>
+      <c r="F122" s="1" t="s">
+        <v>1230</v>
       </c>
       <c r="G122" t="s">
         <v>1223</v>
@@ -11463,10 +11778,10 @@
         <v>25</v>
       </c>
       <c r="J122" t="s">
+        <v>1226</v>
+      </c>
+      <c r="K122" s="1" t="s">
         <v>1227</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>1228</v>
       </c>
       <c r="L122" t="s">
         <v>25</v>
@@ -11561,14 +11876,14 @@
       <c r="D125" t="s">
         <v>128</v>
       </c>
-      <c r="E125" t="s">
-        <v>25</v>
+      <c r="E125">
+        <v>213196</v>
       </c>
       <c r="F125" t="s">
-        <v>25</v>
+        <v>1231</v>
       </c>
       <c r="G125" t="s">
-        <v>25</v>
+        <v>1228</v>
       </c>
       <c r="H125" t="s">
         <v>19</v>
@@ -11576,8 +11891,11 @@
       <c r="I125" t="s">
         <v>25</v>
       </c>
-      <c r="K125" t="s">
-        <v>25</v>
+      <c r="J125" t="s">
+        <v>1232</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>1233</v>
       </c>
       <c r="L125" t="s">
         <v>25</v>
@@ -11585,10 +11903,10 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B126" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C126" t="s">
         <v>14</v>
@@ -11596,22 +11914,16 @@
       <c r="D126" t="s">
         <v>128</v>
       </c>
-      <c r="E126" t="s">
-        <v>25</v>
-      </c>
-      <c r="F126" t="s">
-        <v>25</v>
+      <c r="E126">
+        <v>213196</v>
       </c>
       <c r="G126" t="s">
-        <v>25</v>
+        <v>1229</v>
       </c>
       <c r="H126" t="s">
         <v>19</v>
       </c>
       <c r="I126" t="s">
-        <v>25</v>
-      </c>
-      <c r="J126" t="s">
         <v>25</v>
       </c>
       <c r="K126" t="s">
@@ -11623,25 +11935,25 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C127" t="s">
         <v>14</v>
       </c>
       <c r="D127" t="s">
-        <v>138</v>
-      </c>
-      <c r="E127" t="s">
-        <v>25</v>
-      </c>
-      <c r="F127" t="s">
-        <v>25</v>
+        <v>128</v>
+      </c>
+      <c r="E127">
+        <v>324058</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>1235</v>
       </c>
       <c r="G127" t="s">
-        <v>25</v>
+        <v>1237</v>
       </c>
       <c r="H127" t="s">
         <v>19</v>
@@ -11650,10 +11962,10 @@
         <v>25</v>
       </c>
       <c r="J127" t="s">
-        <v>25</v>
-      </c>
-      <c r="K127" t="s">
-        <v>25</v>
+        <v>1234</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>1236</v>
       </c>
       <c r="L127" t="s">
         <v>25</v>
@@ -11661,10 +11973,10 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B128" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C128" t="s">
         <v>14</v>
@@ -11682,7 +11994,7 @@
         <v>25</v>
       </c>
       <c r="H128" t="s">
-        <v>19</v>
+        <v>1129</v>
       </c>
       <c r="I128" t="s">
         <v>25</v>
@@ -11699,10 +12011,10 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B129" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C129" t="s">
         <v>14</v>
@@ -11737,10 +12049,10 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B130" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C130" t="s">
         <v>14</v>
@@ -11775,10 +12087,10 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B131" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C131" t="s">
         <v>14</v>
@@ -11813,10 +12125,10 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B132" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C132" t="s">
         <v>14</v>
@@ -11851,10 +12163,10 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B133" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C133" t="s">
         <v>14</v>
@@ -11889,16 +12201,16 @@
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B134" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C134" t="s">
         <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E134" t="s">
         <v>25</v>
@@ -11927,10 +12239,10 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C135" t="s">
         <v>14</v>
@@ -11965,10 +12277,10 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B136" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C136" t="s">
         <v>14</v>
@@ -12003,10 +12315,10 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B137" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C137" t="s">
         <v>14</v>
@@ -12041,10 +12353,10 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B138" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C138" t="s">
         <v>14</v>
@@ -12079,10 +12391,10 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B139" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C139" t="s">
         <v>14</v>
@@ -12117,10 +12429,10 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B140" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C140" t="s">
         <v>14</v>
@@ -12155,10 +12467,10 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B141" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C141" t="s">
         <v>14</v>
@@ -12193,10 +12505,10 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B142" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C142" t="s">
         <v>14</v>
@@ -12231,10 +12543,10 @@
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B143" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C143" t="s">
         <v>14</v>
@@ -12269,10 +12581,10 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C144" t="s">
         <v>14</v>
@@ -12307,7 +12619,7 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B145" t="s">
         <v>173</v>
@@ -12345,10 +12657,10 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B146" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C146" t="s">
         <v>14</v>
@@ -12383,10 +12695,10 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B147" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C147" t="s">
         <v>14</v>
@@ -12421,10 +12733,10 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B148" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C148" t="s">
         <v>14</v>
@@ -12459,10 +12771,10 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B149" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C149" t="s">
         <v>14</v>
@@ -12497,10 +12809,10 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B150" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C150" t="s">
         <v>14</v>
@@ -12535,10 +12847,10 @@
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B151" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C151" t="s">
         <v>14</v>
@@ -12573,10 +12885,10 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B152" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C152" t="s">
         <v>14</v>
@@ -12611,10 +12923,10 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B153" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C153" t="s">
         <v>14</v>
@@ -12649,10 +12961,10 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B154" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C154" t="s">
         <v>14</v>
@@ -12660,14 +12972,14 @@
       <c r="D154" t="s">
         <v>153</v>
       </c>
-      <c r="E154">
-        <v>106156</v>
+      <c r="E154" t="s">
+        <v>25</v>
       </c>
       <c r="F154" t="s">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="G154" t="s">
-        <v>194</v>
+        <v>25</v>
       </c>
       <c r="H154" t="s">
         <v>19</v>
@@ -12676,10 +12988,10 @@
         <v>25</v>
       </c>
       <c r="J154" t="s">
-        <v>195</v>
+        <v>25</v>
       </c>
       <c r="K154" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="L154" t="s">
         <v>25</v>
@@ -12702,10 +13014,10 @@
         <v>106156</v>
       </c>
       <c r="F155" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="G155" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H155" t="s">
         <v>19</v>
@@ -12714,10 +13026,10 @@
         <v>25</v>
       </c>
       <c r="J155" t="s">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="K155" t="s">
-        <v>25</v>
+        <v>196</v>
       </c>
       <c r="L155" t="s">
         <v>25</v>
@@ -12725,25 +13037,25 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B156" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C156" t="s">
         <v>14</v>
       </c>
       <c r="D156" t="s">
-        <v>200</v>
-      </c>
-      <c r="E156" t="s">
-        <v>25</v>
+        <v>153</v>
+      </c>
+      <c r="E156">
+        <v>106156</v>
       </c>
       <c r="F156" t="s">
         <v>25</v>
       </c>
       <c r="G156" t="s">
-        <v>25</v>
+        <v>197</v>
       </c>
       <c r="H156" t="s">
         <v>19</v>
@@ -12763,10 +13075,10 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B157" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C157" t="s">
         <v>14</v>
@@ -12801,10 +13113,10 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B158" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C158" t="s">
         <v>14</v>
@@ -12839,10 +13151,10 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B159" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C159" t="s">
         <v>14</v>
@@ -12877,10 +13189,10 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B160" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C160" t="s">
         <v>14</v>
@@ -12915,10 +13227,10 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B161" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C161" t="s">
         <v>14</v>
@@ -12953,10 +13265,10 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B162" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C162" t="s">
         <v>14</v>
@@ -12991,10 +13303,10 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B163" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C163" t="s">
         <v>14</v>
@@ -13029,10 +13341,10 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B164" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C164" t="s">
         <v>14</v>
@@ -13067,10 +13379,10 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B165" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C165" t="s">
         <v>14</v>
@@ -13105,10 +13417,10 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B166" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C166" t="s">
         <v>14</v>
@@ -13143,10 +13455,10 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B167" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C167" t="s">
         <v>14</v>
@@ -13181,10 +13493,10 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B168" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C168" t="s">
         <v>14</v>
@@ -13219,16 +13531,16 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B169" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C169" t="s">
         <v>14</v>
       </c>
       <c r="D169" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E169" t="s">
         <v>25</v>
@@ -13257,7 +13569,7 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B170" t="s">
         <v>226</v>
@@ -13295,10 +13607,10 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B171" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C171" t="s">
         <v>14</v>
@@ -13333,7 +13645,7 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B172" t="s">
         <v>230</v>
@@ -13371,10 +13683,10 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B173" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C173" t="s">
         <v>14</v>
@@ -13409,16 +13721,16 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B174" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C174" t="s">
         <v>14</v>
       </c>
       <c r="D174" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E174" t="s">
         <v>25</v>
@@ -13447,10 +13759,10 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B175" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C175" t="s">
         <v>14</v>
@@ -13485,16 +13797,16 @@
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B176" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C176" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D176" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E176" t="s">
         <v>25</v>
@@ -13523,10 +13835,10 @@
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B177" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C177" t="s">
         <v>241</v>
@@ -13561,10 +13873,10 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B178" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C178" t="s">
         <v>241</v>
@@ -13599,10 +13911,10 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B179" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C179" t="s">
         <v>241</v>
@@ -13637,10 +13949,10 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B180" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C180" t="s">
         <v>241</v>
@@ -13675,10 +13987,10 @@
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B181" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C181" t="s">
         <v>241</v>
@@ -13713,10 +14025,10 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B182" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C182" t="s">
         <v>241</v>
@@ -13751,10 +14063,10 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B183" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C183" t="s">
         <v>241</v>
@@ -13789,10 +14101,10 @@
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B184" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C184" t="s">
         <v>241</v>
@@ -13827,10 +14139,10 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B185" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C185" t="s">
         <v>241</v>
@@ -13865,10 +14177,10 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B186" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C186" t="s">
         <v>241</v>
@@ -13903,10 +14215,10 @@
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B187" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C187" t="s">
         <v>241</v>
@@ -13941,10 +14253,10 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B188" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C188" t="s">
         <v>241</v>
@@ -13979,10 +14291,10 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B189" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C189" t="s">
         <v>241</v>
@@ -14017,10 +14329,10 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B190" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C190" t="s">
         <v>241</v>
@@ -14055,10 +14367,10 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B191" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C191" t="s">
         <v>241</v>
@@ -14093,10 +14405,10 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B192" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C192" t="s">
         <v>241</v>
@@ -14131,10 +14443,10 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B193" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C193" t="s">
         <v>241</v>
@@ -14169,10 +14481,10 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B194" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C194" t="s">
         <v>241</v>
@@ -14207,10 +14519,10 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B195" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C195" t="s">
         <v>241</v>
@@ -14245,10 +14557,10 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B196" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C196" t="s">
         <v>241</v>
@@ -14283,10 +14595,10 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B197" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C197" t="s">
         <v>241</v>
@@ -14321,10 +14633,10 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B198" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C198" t="s">
         <v>241</v>
@@ -14359,10 +14671,10 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B199" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C199" t="s">
         <v>241</v>
@@ -14397,10 +14709,10 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B200" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C200" t="s">
         <v>241</v>
@@ -14435,10 +14747,10 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B201" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C201" t="s">
         <v>241</v>
@@ -14473,10 +14785,10 @@
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B202" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C202" t="s">
         <v>241</v>
@@ -14511,10 +14823,10 @@
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B203" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C203" t="s">
         <v>241</v>
@@ -14549,10 +14861,10 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B204" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C204" t="s">
         <v>241</v>
@@ -14587,10 +14899,10 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B205" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C205" t="s">
         <v>241</v>
@@ -14625,10 +14937,10 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B206" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C206" t="s">
         <v>241</v>
@@ -14663,10 +14975,10 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B207" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C207" t="s">
         <v>241</v>
@@ -14701,10 +15013,10 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B208" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C208" t="s">
         <v>241</v>
@@ -14739,10 +15051,10 @@
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B209" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C209" t="s">
         <v>241</v>
@@ -14777,10 +15089,10 @@
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B210" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C210" t="s">
         <v>241</v>
@@ -14815,10 +15127,10 @@
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B211" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C211" t="s">
         <v>241</v>
@@ -14853,10 +15165,10 @@
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B212" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C212" t="s">
         <v>241</v>
@@ -14891,10 +15203,10 @@
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B213" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C213" t="s">
         <v>241</v>
@@ -14929,16 +15241,16 @@
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B214" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C214" t="s">
         <v>241</v>
       </c>
       <c r="D214" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E214" t="s">
         <v>25</v>
@@ -14967,10 +15279,10 @@
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B215" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C215" t="s">
         <v>241</v>
@@ -15005,10 +15317,10 @@
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B216" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C216" t="s">
         <v>241</v>
@@ -15043,10 +15355,10 @@
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B217" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C217" t="s">
         <v>241</v>
@@ -15081,10 +15393,10 @@
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B218" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C218" t="s">
         <v>241</v>
@@ -15119,10 +15431,10 @@
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B219" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C219" t="s">
         <v>241</v>
@@ -15157,10 +15469,10 @@
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B220" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C220" t="s">
         <v>241</v>
@@ -15195,10 +15507,10 @@
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B221" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C221" t="s">
         <v>241</v>
@@ -15233,10 +15545,10 @@
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B222" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C222" t="s">
         <v>241</v>
@@ -15271,10 +15583,10 @@
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B223" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C223" t="s">
         <v>241</v>
@@ -15309,16 +15621,16 @@
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B224" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C224" t="s">
         <v>241</v>
       </c>
       <c r="D224" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="E224" t="s">
         <v>25</v>
@@ -15347,10 +15659,10 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B225" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C225" t="s">
         <v>241</v>
@@ -15385,10 +15697,10 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B226" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C226" t="s">
         <v>241</v>
@@ -15423,16 +15735,16 @@
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B227" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C227" t="s">
         <v>241</v>
       </c>
       <c r="D227" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E227" t="s">
         <v>25</v>
@@ -15461,10 +15773,10 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B228" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C228" t="s">
         <v>241</v>
@@ -15499,10 +15811,10 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B229" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C229" t="s">
         <v>241</v>
@@ -15537,10 +15849,10 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B230" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C230" t="s">
         <v>241</v>
@@ -15575,10 +15887,10 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B231" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C231" t="s">
         <v>241</v>
@@ -15613,10 +15925,10 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B232" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C232" t="s">
         <v>241</v>
@@ -15651,10 +15963,10 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B233" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C233" t="s">
         <v>241</v>
@@ -15689,16 +16001,16 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B234" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C234" t="s">
         <v>241</v>
       </c>
       <c r="D234" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E234" t="s">
         <v>25</v>
@@ -15727,10 +16039,10 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B235" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C235" t="s">
         <v>241</v>
@@ -15765,10 +16077,10 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B236" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C236" t="s">
         <v>241</v>
@@ -15803,10 +16115,10 @@
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B237" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C237" t="s">
         <v>241</v>
@@ -15841,10 +16153,10 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B238" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C238" t="s">
         <v>241</v>
@@ -15879,10 +16191,10 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B239" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C239" t="s">
         <v>241</v>
@@ -15917,10 +16229,10 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B240" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C240" t="s">
         <v>241</v>
@@ -15955,10 +16267,10 @@
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B241" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C241" t="s">
         <v>241</v>
@@ -15993,7 +16305,7 @@
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B242" t="s">
         <v>375</v>
@@ -16031,10 +16343,10 @@
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B243" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C243" t="s">
         <v>241</v>
@@ -16069,7 +16381,7 @@
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B244" t="s">
         <v>378</v>
@@ -16107,7 +16419,7 @@
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B245" t="s">
         <v>378</v>
@@ -16145,7 +16457,7 @@
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B246" t="s">
         <v>378</v>
@@ -16183,7 +16495,7 @@
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B247" t="s">
         <v>378</v>
@@ -16221,10 +16533,10 @@
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B248" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C248" t="s">
         <v>241</v>
@@ -16259,10 +16571,10 @@
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B249" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C249" t="s">
         <v>241</v>
@@ -16297,10 +16609,10 @@
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B250" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C250" t="s">
         <v>241</v>
@@ -16335,10 +16647,10 @@
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B251" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C251" t="s">
         <v>241</v>
@@ -16373,10 +16685,10 @@
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B252" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C252" t="s">
         <v>241</v>
@@ -16411,10 +16723,10 @@
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B253" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C253" t="s">
         <v>241</v>
@@ -16449,10 +16761,10 @@
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B254" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C254" t="s">
         <v>241</v>
@@ -16487,10 +16799,10 @@
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B255" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C255" t="s">
         <v>241</v>
@@ -16525,10 +16837,10 @@
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B256" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C256" t="s">
         <v>241</v>
@@ -16563,10 +16875,10 @@
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B257" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C257" t="s">
         <v>241</v>
@@ -16601,10 +16913,10 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B258" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C258" t="s">
         <v>241</v>
@@ -16639,10 +16951,10 @@
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B259" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C259" t="s">
         <v>241</v>
@@ -16677,16 +16989,16 @@
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B260" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C260" t="s">
         <v>241</v>
       </c>
       <c r="D260" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E260" t="s">
         <v>25</v>
@@ -16715,10 +17027,10 @@
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B261" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C261" t="s">
         <v>241</v>
@@ -16753,10 +17065,10 @@
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B262" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C262" t="s">
         <v>241</v>
@@ -16791,10 +17103,10 @@
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B263" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C263" t="s">
         <v>241</v>
@@ -16829,10 +17141,10 @@
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B264" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C264" t="s">
         <v>241</v>
@@ -16867,10 +17179,10 @@
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B265" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C265" t="s">
         <v>241</v>
@@ -16905,10 +17217,10 @@
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B266" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C266" t="s">
         <v>241</v>
@@ -16943,10 +17255,10 @@
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B267" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C267" t="s">
         <v>241</v>
@@ -16981,10 +17293,10 @@
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B268" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C268" t="s">
         <v>241</v>
@@ -17019,10 +17331,10 @@
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B269" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C269" t="s">
         <v>241</v>
@@ -17057,10 +17369,10 @@
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B270" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C270" t="s">
         <v>241</v>
@@ -17095,10 +17407,10 @@
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B271" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C271" t="s">
         <v>241</v>
@@ -17133,10 +17445,10 @@
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B272" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C272" t="s">
         <v>241</v>
@@ -17171,10 +17483,10 @@
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B273" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C273" t="s">
         <v>241</v>
@@ -17209,10 +17521,10 @@
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B274" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C274" t="s">
         <v>241</v>
@@ -17247,10 +17559,10 @@
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B275" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C275" t="s">
         <v>241</v>
@@ -17285,10 +17597,10 @@
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B276" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C276" t="s">
         <v>241</v>
@@ -17323,10 +17635,10 @@
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B277" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C277" t="s">
         <v>241</v>
@@ -17361,10 +17673,10 @@
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B278" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C278" t="s">
         <v>241</v>
@@ -17399,10 +17711,10 @@
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B279" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C279" t="s">
         <v>241</v>
@@ -17437,10 +17749,10 @@
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B280" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C280" t="s">
         <v>241</v>
@@ -17475,10 +17787,10 @@
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B281" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C281" t="s">
         <v>241</v>
@@ -17513,10 +17825,10 @@
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B282" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C282" t="s">
         <v>241</v>
@@ -17551,10 +17863,10 @@
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B283" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C283" t="s">
         <v>241</v>
@@ -17589,10 +17901,10 @@
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B284" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C284" t="s">
         <v>241</v>
@@ -17627,10 +17939,10 @@
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B285" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C285" t="s">
         <v>241</v>
@@ -17665,16 +17977,16 @@
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B286" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C286" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D286" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E286" t="s">
         <v>25</v>
@@ -17703,10 +18015,10 @@
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B287" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C287" t="s">
         <v>462</v>
@@ -17741,10 +18053,10 @@
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B288" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C288" t="s">
         <v>462</v>
@@ -17779,10 +18091,10 @@
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B289" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C289" t="s">
         <v>462</v>
@@ -17817,10 +18129,10 @@
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B290" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C290" t="s">
         <v>462</v>
@@ -17855,10 +18167,10 @@
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B291" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C291" t="s">
         <v>462</v>
@@ -17893,10 +18205,10 @@
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B292" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C292" t="s">
         <v>462</v>
@@ -17931,10 +18243,10 @@
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B293" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C293" t="s">
         <v>462</v>
@@ -17969,10 +18281,10 @@
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B294" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C294" t="s">
         <v>462</v>
@@ -18007,10 +18319,10 @@
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B295" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C295" t="s">
         <v>462</v>
@@ -18045,10 +18357,10 @@
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B296" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C296" t="s">
         <v>462</v>
@@ -18083,10 +18395,10 @@
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B297" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C297" t="s">
         <v>462</v>
@@ -18121,10 +18433,10 @@
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B298" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C298" t="s">
         <v>462</v>
@@ -18159,10 +18471,10 @@
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B299" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C299" t="s">
         <v>462</v>
@@ -18197,10 +18509,10 @@
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B300" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C300" t="s">
         <v>462</v>
@@ -18235,10 +18547,10 @@
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B301" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C301" t="s">
         <v>462</v>
@@ -18273,10 +18585,10 @@
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B302" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C302" t="s">
         <v>462</v>
@@ -18311,10 +18623,10 @@
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B303" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C303" t="s">
         <v>462</v>
@@ -18349,10 +18661,10 @@
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B304" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C304" t="s">
         <v>462</v>
@@ -18387,10 +18699,10 @@
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B305" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C305" t="s">
         <v>462</v>
@@ -18425,10 +18737,10 @@
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B306" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C306" t="s">
         <v>462</v>
@@ -18463,10 +18775,10 @@
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B307" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C307" t="s">
         <v>462</v>
@@ -18501,10 +18813,10 @@
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B308" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C308" t="s">
         <v>462</v>
@@ -18539,10 +18851,10 @@
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B309" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C309" t="s">
         <v>462</v>
@@ -18577,10 +18889,10 @@
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B310" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C310" t="s">
         <v>462</v>
@@ -18615,10 +18927,10 @@
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B311" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C311" t="s">
         <v>462</v>
@@ -18653,10 +18965,10 @@
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B312" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C312" t="s">
         <v>462</v>
@@ -18691,10 +19003,10 @@
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B313" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C313" t="s">
         <v>462</v>
@@ -18729,10 +19041,10 @@
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B314" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C314" t="s">
         <v>462</v>
@@ -18767,10 +19079,10 @@
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B315" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C315" t="s">
         <v>462</v>
@@ -18805,10 +19117,10 @@
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B316" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C316" t="s">
         <v>462</v>
@@ -18843,10 +19155,10 @@
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B317" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C317" t="s">
         <v>462</v>
@@ -18881,10 +19193,10 @@
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B318" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C318" t="s">
         <v>462</v>
@@ -18919,10 +19231,10 @@
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B319" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C319" t="s">
         <v>462</v>
@@ -18957,10 +19269,10 @@
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B320" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C320" t="s">
         <v>462</v>
@@ -18995,10 +19307,10 @@
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B321" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C321" t="s">
         <v>462</v>
@@ -19033,10 +19345,10 @@
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B322" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C322" t="s">
         <v>462</v>
@@ -19071,10 +19383,10 @@
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B323" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C323" t="s">
         <v>462</v>
@@ -19109,10 +19421,10 @@
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B324" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C324" t="s">
         <v>462</v>
@@ -19147,10 +19459,10 @@
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B325" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C325" t="s">
         <v>462</v>
@@ -19185,10 +19497,10 @@
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B326" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C326" t="s">
         <v>462</v>
@@ -19223,10 +19535,10 @@
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B327" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C327" t="s">
         <v>462</v>
@@ -19261,10 +19573,10 @@
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B328" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C328" t="s">
         <v>462</v>
@@ -19299,10 +19611,10 @@
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B329" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C329" t="s">
         <v>462</v>
@@ -19337,10 +19649,10 @@
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B330" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C330" t="s">
         <v>462</v>
@@ -19375,10 +19687,10 @@
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B331" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C331" t="s">
         <v>462</v>
@@ -19413,10 +19725,10 @@
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B332" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C332" t="s">
         <v>462</v>
@@ -19451,16 +19763,16 @@
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B333" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C333" t="s">
         <v>462</v>
       </c>
       <c r="D333" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E333" t="s">
         <v>25</v>
@@ -19489,10 +19801,10 @@
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B334" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C334" t="s">
         <v>462</v>
@@ -19527,10 +19839,10 @@
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B335" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C335" t="s">
         <v>462</v>
@@ -19565,10 +19877,10 @@
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B336" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C336" t="s">
         <v>462</v>
@@ -19603,10 +19915,10 @@
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B337" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C337" t="s">
         <v>462</v>
@@ -19641,10 +19953,10 @@
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B338" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C338" t="s">
         <v>462</v>
@@ -19679,10 +19991,10 @@
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B339" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C339" t="s">
         <v>462</v>
@@ -19717,10 +20029,10 @@
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B340" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C340" t="s">
         <v>462</v>
@@ -19755,10 +20067,10 @@
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B341" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C341" t="s">
         <v>462</v>
@@ -19793,10 +20105,10 @@
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B342" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C342" t="s">
         <v>462</v>
@@ -19831,10 +20143,10 @@
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B343" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C343" t="s">
         <v>462</v>
@@ -19869,10 +20181,10 @@
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B344" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C344" t="s">
         <v>462</v>
@@ -19907,10 +20219,10 @@
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B345" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C345" t="s">
         <v>462</v>
@@ -19945,10 +20257,10 @@
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B346" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C346" t="s">
         <v>462</v>
@@ -19983,10 +20295,10 @@
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B347" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C347" t="s">
         <v>462</v>
@@ -20021,10 +20333,10 @@
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B348" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C348" t="s">
         <v>462</v>
@@ -20059,10 +20371,10 @@
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B349" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C349" t="s">
         <v>462</v>
@@ -20097,10 +20409,10 @@
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B350" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C350" t="s">
         <v>462</v>
@@ -20135,10 +20447,10 @@
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B351" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C351" t="s">
         <v>462</v>
@@ -20173,10 +20485,10 @@
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B352" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C352" t="s">
         <v>462</v>
@@ -20211,10 +20523,10 @@
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B353" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C353" t="s">
         <v>462</v>
@@ -20249,10 +20561,10 @@
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B354" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C354" t="s">
         <v>462</v>
@@ -20287,10 +20599,10 @@
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B355" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C355" t="s">
         <v>462</v>
@@ -20325,10 +20637,10 @@
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B356" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C356" t="s">
         <v>462</v>
@@ -20363,10 +20675,10 @@
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B357" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C357" t="s">
         <v>462</v>
@@ -20401,10 +20713,10 @@
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B358" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C358" t="s">
         <v>462</v>
@@ -20439,10 +20751,10 @@
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B359" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C359" t="s">
         <v>462</v>
@@ -20477,10 +20789,10 @@
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B360" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C360" t="s">
         <v>462</v>
@@ -20515,10 +20827,10 @@
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B361" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C361" t="s">
         <v>462</v>
@@ -20553,10 +20865,10 @@
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B362" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C362" t="s">
         <v>462</v>
@@ -20591,10 +20903,10 @@
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B363" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C363" t="s">
         <v>462</v>
@@ -20629,10 +20941,10 @@
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B364" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C364" t="s">
         <v>462</v>
@@ -20667,10 +20979,10 @@
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B365" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C365" t="s">
         <v>462</v>
@@ -20705,10 +21017,10 @@
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B366" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C366" t="s">
         <v>462</v>
@@ -20743,16 +21055,16 @@
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B367" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C367" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D367" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E367" t="s">
         <v>25</v>
@@ -20781,10 +21093,10 @@
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B368" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C368" t="s">
         <v>627</v>
@@ -20819,10 +21131,10 @@
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B369" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C369" t="s">
         <v>627</v>
@@ -20857,10 +21169,10 @@
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B370" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C370" t="s">
         <v>627</v>
@@ -20895,10 +21207,10 @@
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B371" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C371" t="s">
         <v>627</v>
@@ -20933,10 +21245,10 @@
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B372" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C372" t="s">
         <v>627</v>
@@ -20971,10 +21283,10 @@
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B373" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C373" t="s">
         <v>627</v>
@@ -21009,10 +21321,10 @@
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B374" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C374" t="s">
         <v>627</v>
@@ -21047,16 +21359,16 @@
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B375" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C375" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D375" t="s">
-        <v>645</v>
+        <v>25</v>
       </c>
       <c r="E375" t="s">
         <v>25</v>
@@ -21085,10 +21397,10 @@
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B376" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C376" t="s">
         <v>644</v>
@@ -21123,10 +21435,10 @@
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B377" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C377" t="s">
         <v>644</v>
@@ -21161,10 +21473,10 @@
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B378" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C378" t="s">
         <v>644</v>
@@ -21199,16 +21511,16 @@
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B379" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C379" t="s">
         <v>644</v>
       </c>
       <c r="D379" t="s">
-        <v>138</v>
+        <v>645</v>
       </c>
       <c r="E379" t="s">
         <v>25</v>
@@ -21237,10 +21549,10 @@
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B380" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C380" t="s">
         <v>644</v>
@@ -21275,10 +21587,10 @@
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B381" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C381" t="s">
         <v>644</v>
@@ -21313,10 +21625,10 @@
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B382" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C382" t="s">
         <v>644</v>
@@ -21351,16 +21663,16 @@
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B383" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C383" t="s">
         <v>644</v>
       </c>
       <c r="D383" t="s">
-        <v>662</v>
+        <v>138</v>
       </c>
       <c r="E383" t="s">
         <v>25</v>
@@ -21389,10 +21701,10 @@
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B384" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C384" t="s">
         <v>644</v>
@@ -21427,10 +21739,10 @@
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B385" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C385" t="s">
         <v>644</v>
@@ -21465,10 +21777,10 @@
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B386" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C386" t="s">
         <v>644</v>
@@ -21503,10 +21815,10 @@
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B387" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C387" t="s">
         <v>644</v>
@@ -21541,16 +21853,16 @@
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B388" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C388" t="s">
         <v>644</v>
       </c>
       <c r="D388" t="s">
-        <v>128</v>
+        <v>662</v>
       </c>
       <c r="E388" t="s">
         <v>25</v>
@@ -21579,10 +21891,10 @@
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B389" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C389" t="s">
         <v>644</v>
@@ -21617,16 +21929,16 @@
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B390" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C390" t="s">
         <v>644</v>
       </c>
       <c r="D390" t="s">
-        <v>677</v>
+        <v>128</v>
       </c>
       <c r="E390" t="s">
         <v>25</v>
@@ -21655,10 +21967,10 @@
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B391" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C391" t="s">
         <v>644</v>
@@ -21693,10 +22005,10 @@
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B392" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C392" t="s">
         <v>644</v>
@@ -21734,7 +22046,7 @@
         <v>680</v>
       </c>
       <c r="B393" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C393" t="s">
         <v>644</v>
@@ -21769,16 +22081,16 @@
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B394" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C394" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D394" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="E394" t="s">
         <v>25</v>
@@ -21807,10 +22119,10 @@
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B395" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C395" t="s">
         <v>685</v>
@@ -21845,10 +22157,10 @@
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B396" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C396" t="s">
         <v>685</v>
@@ -21883,10 +22195,10 @@
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B397" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C397" t="s">
         <v>685</v>
@@ -21921,10 +22233,10 @@
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B398" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C398" t="s">
         <v>685</v>
@@ -21959,10 +22271,10 @@
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B399" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C399" t="s">
         <v>685</v>
@@ -21997,16 +22309,16 @@
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B400" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C400" t="s">
         <v>685</v>
       </c>
       <c r="D400" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="E400" t="s">
         <v>25</v>
@@ -22035,10 +22347,10 @@
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B401" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C401" t="s">
         <v>685</v>
@@ -22073,10 +22385,10 @@
     </row>
     <row r="402" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B402" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C402" t="s">
         <v>685</v>
@@ -22111,16 +22423,16 @@
     </row>
     <row r="403" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B403" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C403" t="s">
         <v>685</v>
       </c>
       <c r="D403" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="E403" t="s">
         <v>25</v>
@@ -22149,10 +22461,10 @@
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B404" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C404" t="s">
         <v>685</v>
@@ -22187,10 +22499,10 @@
     </row>
     <row r="405" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B405" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C405" t="s">
         <v>685</v>
@@ -22225,10 +22537,10 @@
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B406" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C406" t="s">
         <v>685</v>
@@ -22263,16 +22575,16 @@
     </row>
     <row r="407" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B407" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C407" t="s">
         <v>685</v>
       </c>
       <c r="D407" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="E407" t="s">
         <v>25</v>
@@ -22301,7 +22613,7 @@
     </row>
     <row r="408" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B408" t="s">
         <v>714</v>
@@ -22339,10 +22651,10 @@
     </row>
     <row r="409" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B409" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C409" t="s">
         <v>685</v>
@@ -22377,16 +22689,16 @@
     </row>
     <row r="410" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B410" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C410" t="s">
         <v>685</v>
       </c>
       <c r="D410" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="E410" t="s">
         <v>25</v>
@@ -22415,10 +22727,10 @@
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B411" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C411" t="s">
         <v>685</v>
@@ -22453,10 +22765,10 @@
     </row>
     <row r="412" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B412" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C412" t="s">
         <v>685</v>
@@ -22491,10 +22803,10 @@
     </row>
     <row r="413" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B413" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C413" t="s">
         <v>685</v>
@@ -22529,10 +22841,10 @@
     </row>
     <row r="414" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B414" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C414" t="s">
         <v>685</v>
@@ -22567,16 +22879,16 @@
     </row>
     <row r="415" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B415" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C415" t="s">
         <v>685</v>
       </c>
       <c r="D415" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="E415" t="s">
         <v>25</v>
@@ -22605,10 +22917,10 @@
     </row>
     <row r="416" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B416" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C416" t="s">
         <v>685</v>
@@ -22643,10 +22955,10 @@
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B417" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C417" t="s">
         <v>685</v>
@@ -22681,10 +22993,10 @@
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B418" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C418" t="s">
         <v>685</v>
@@ -22719,10 +23031,10 @@
     </row>
     <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B419" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C419" t="s">
         <v>685</v>
@@ -22757,10 +23069,10 @@
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B420" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C420" t="s">
         <v>685</v>
@@ -22795,16 +23107,16 @@
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B421" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C421" t="s">
         <v>685</v>
       </c>
       <c r="D421" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="E421" t="s">
         <v>25</v>
@@ -22833,10 +23145,10 @@
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B422" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C422" t="s">
         <v>685</v>
@@ -22871,16 +23183,16 @@
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B423" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C423" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D423" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="E423" t="s">
         <v>25</v>
@@ -22909,10 +23221,10 @@
     </row>
     <row r="424" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B424" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C424" t="s">
         <v>750</v>
@@ -22947,10 +23259,10 @@
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B425" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C425" t="s">
         <v>750</v>
@@ -22985,10 +23297,10 @@
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B426" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C426" t="s">
         <v>750</v>
@@ -23023,10 +23335,10 @@
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B427" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C427" t="s">
         <v>750</v>
@@ -23061,10 +23373,10 @@
     </row>
     <row r="428" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B428" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C428" t="s">
         <v>750</v>
@@ -23099,10 +23411,10 @@
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B429" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C429" t="s">
         <v>750</v>
@@ -23137,10 +23449,10 @@
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B430" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C430" t="s">
         <v>750</v>
@@ -23175,10 +23487,10 @@
     </row>
     <row r="431" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B431" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C431" t="s">
         <v>750</v>
@@ -23213,10 +23525,10 @@
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B432" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C432" t="s">
         <v>750</v>
@@ -23251,10 +23563,10 @@
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B433" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C433" t="s">
         <v>750</v>
@@ -23289,10 +23601,10 @@
     </row>
     <row r="434" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B434" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C434" t="s">
         <v>750</v>
@@ -23327,10 +23639,10 @@
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B435" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C435" t="s">
         <v>750</v>
@@ -23365,16 +23677,16 @@
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B436" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C436" t="s">
         <v>750</v>
       </c>
       <c r="D436" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="E436" t="s">
         <v>25</v>
@@ -23403,10 +23715,10 @@
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B437" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C437" t="s">
         <v>750</v>
@@ -23441,10 +23753,10 @@
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B438" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C438" t="s">
         <v>750</v>
@@ -23479,10 +23791,10 @@
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B439" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C439" t="s">
         <v>750</v>
@@ -23517,10 +23829,10 @@
     </row>
     <row r="440" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B440" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C440" t="s">
         <v>750</v>
@@ -23555,16 +23867,16 @@
     </row>
     <row r="441" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B441" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C441" t="s">
         <v>750</v>
       </c>
       <c r="D441" t="s">
-        <v>200</v>
+        <v>778</v>
       </c>
       <c r="E441" t="s">
         <v>25</v>
@@ -23593,10 +23905,10 @@
     </row>
     <row r="442" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B442" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C442" t="s">
         <v>750</v>
@@ -23631,10 +23943,10 @@
     </row>
     <row r="443" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B443" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C443" t="s">
         <v>750</v>
@@ -23669,16 +23981,16 @@
     </row>
     <row r="444" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B444" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C444" t="s">
         <v>750</v>
       </c>
       <c r="D444" t="s">
-        <v>795</v>
+        <v>200</v>
       </c>
       <c r="E444" t="s">
         <v>25</v>
@@ -23707,10 +24019,10 @@
     </row>
     <row r="445" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B445" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C445" t="s">
         <v>750</v>
@@ -23745,16 +24057,16 @@
     </row>
     <row r="446" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B446" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C446" t="s">
         <v>750</v>
       </c>
       <c r="D446" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="E446" t="s">
         <v>25</v>
@@ -23783,10 +24095,10 @@
     </row>
     <row r="447" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B447" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C447" t="s">
         <v>750</v>
@@ -23821,10 +24133,10 @@
     </row>
     <row r="448" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B448" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C448" t="s">
         <v>750</v>
@@ -23859,16 +24171,16 @@
     </row>
     <row r="449" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B449" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C449" t="s">
         <v>750</v>
       </c>
       <c r="D449" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="E449" t="s">
         <v>25</v>
@@ -23897,10 +24209,10 @@
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B450" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C450" t="s">
         <v>750</v>
@@ -23935,10 +24247,10 @@
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B451" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C451" t="s">
         <v>750</v>
@@ -23973,10 +24285,10 @@
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B452" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C452" t="s">
         <v>750</v>
@@ -24011,10 +24323,10 @@
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B453" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C453" t="s">
         <v>750</v>
@@ -24049,10 +24361,10 @@
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B454" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C454" t="s">
         <v>750</v>
@@ -24087,10 +24399,10 @@
     </row>
     <row r="455" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B455" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C455" t="s">
         <v>750</v>
@@ -24125,10 +24437,10 @@
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B456" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C456" t="s">
         <v>750</v>
@@ -24163,10 +24475,10 @@
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B457" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C457" t="s">
         <v>750</v>
@@ -24201,10 +24513,10 @@
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B458" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C458" t="s">
         <v>750</v>
@@ -24239,10 +24551,10 @@
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B459" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C459" t="s">
         <v>750</v>
@@ -24277,10 +24589,10 @@
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B460" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C460" t="s">
         <v>750</v>
@@ -24315,16 +24627,16 @@
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B461" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C461" t="s">
         <v>750</v>
       </c>
       <c r="D461" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="E461" t="s">
         <v>25</v>
@@ -24353,10 +24665,10 @@
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B462" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C462" t="s">
         <v>750</v>
@@ -24391,10 +24703,10 @@
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B463" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C463" t="s">
         <v>750</v>
@@ -24429,10 +24741,10 @@
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B464" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C464" t="s">
         <v>750</v>
@@ -24467,10 +24779,10 @@
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B465" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C465" t="s">
         <v>750</v>
@@ -24505,16 +24817,16 @@
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B466" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C466" t="s">
         <v>750</v>
       </c>
       <c r="D466" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
       <c r="E466" t="s">
         <v>25</v>
@@ -24543,10 +24855,10 @@
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B467" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C467" t="s">
         <v>750</v>
@@ -24581,16 +24893,16 @@
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B468" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C468" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D468" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="E468" t="s">
         <v>25</v>
@@ -24619,10 +24931,10 @@
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B469" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="C469" t="s">
         <v>848</v>
@@ -24657,10 +24969,10 @@
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B470" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C470" t="s">
         <v>848</v>
@@ -24695,10 +25007,10 @@
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B471" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C471" t="s">
         <v>848</v>
@@ -24733,10 +25045,10 @@
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B472" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C472" t="s">
         <v>848</v>
@@ -24771,10 +25083,10 @@
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B473" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C473" t="s">
         <v>848</v>
@@ -24809,16 +25121,16 @@
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B474" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C474" t="s">
         <v>848</v>
       </c>
       <c r="D474" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="E474" t="s">
         <v>25</v>
@@ -24847,10 +25159,10 @@
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B475" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C475" t="s">
         <v>848</v>
@@ -24885,10 +25197,10 @@
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B476" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C476" t="s">
         <v>848</v>
@@ -24923,10 +25235,10 @@
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B477" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C477" t="s">
         <v>848</v>
@@ -24961,10 +25273,10 @@
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B478" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C478" t="s">
         <v>848</v>
@@ -24999,16 +25311,16 @@
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B479" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C479" t="s">
         <v>848</v>
       </c>
       <c r="D479" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
       <c r="E479" t="s">
         <v>25</v>
@@ -25037,10 +25349,10 @@
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B480" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="C480" t="s">
         <v>848</v>
@@ -25075,10 +25387,10 @@
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B481" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C481" t="s">
         <v>848</v>
@@ -25113,16 +25425,16 @@
     </row>
     <row r="482" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B482" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C482" t="s">
         <v>848</v>
       </c>
       <c r="D482" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="E482" t="s">
         <v>25</v>
@@ -25151,10 +25463,10 @@
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="B483" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C483" t="s">
         <v>848</v>
@@ -25189,16 +25501,16 @@
     </row>
     <row r="484" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B484" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C484" t="s">
         <v>848</v>
       </c>
       <c r="D484" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="E484" t="s">
         <v>25</v>
@@ -25227,10 +25539,10 @@
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B485" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="C485" t="s">
         <v>848</v>
@@ -25265,10 +25577,10 @@
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B486" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C486" t="s">
         <v>848</v>
@@ -25303,10 +25615,10 @@
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B487" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C487" t="s">
         <v>848</v>
@@ -25341,16 +25653,16 @@
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B488" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C488" t="s">
         <v>848</v>
       </c>
       <c r="D488" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="E488" t="s">
         <v>25</v>
@@ -25379,10 +25691,10 @@
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="B489" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="C489" t="s">
         <v>848</v>
@@ -25417,10 +25729,10 @@
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B490" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C490" t="s">
         <v>848</v>
@@ -25455,10 +25767,10 @@
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B491" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C491" t="s">
         <v>848</v>
@@ -25493,10 +25805,10 @@
     </row>
     <row r="492" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B492" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C492" t="s">
         <v>848</v>
@@ -25531,16 +25843,16 @@
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B493" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C493" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D493" t="s">
-        <v>25</v>
+        <v>894</v>
       </c>
       <c r="E493" t="s">
         <v>25</v>
@@ -25569,10 +25881,10 @@
     </row>
     <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B494" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="C494" t="s">
         <v>905</v>
@@ -25607,10 +25919,10 @@
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B495" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C495" t="s">
         <v>905</v>
@@ -25645,10 +25957,10 @@
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B496" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C496" t="s">
         <v>905</v>
@@ -25683,10 +25995,10 @@
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B497" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C497" t="s">
         <v>905</v>
@@ -25721,10 +26033,10 @@
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B498" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C498" t="s">
         <v>905</v>
@@ -25759,10 +26071,10 @@
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B499" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C499" t="s">
         <v>905</v>
@@ -25797,10 +26109,10 @@
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B500" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C500" t="s">
         <v>905</v>
@@ -25835,10 +26147,10 @@
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B501" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C501" t="s">
         <v>905</v>
@@ -25873,10 +26185,10 @@
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B502" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C502" t="s">
         <v>905</v>
@@ -25911,10 +26223,10 @@
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B503" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C503" t="s">
         <v>905</v>
@@ -25949,10 +26261,10 @@
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B504" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C504" t="s">
         <v>905</v>
@@ -25987,10 +26299,10 @@
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B505" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C505" t="s">
         <v>905</v>
@@ -26025,10 +26337,10 @@
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B506" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C506" t="s">
         <v>905</v>
@@ -26063,10 +26375,10 @@
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B507" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C507" t="s">
         <v>905</v>
@@ -26101,16 +26413,16 @@
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B508" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C508" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D508" t="s">
-        <v>937</v>
+        <v>25</v>
       </c>
       <c r="E508" t="s">
         <v>25</v>
@@ -26139,10 +26451,10 @@
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B509" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="C509" t="s">
         <v>936</v>
@@ -26177,10 +26489,10 @@
     </row>
     <row r="510" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B510" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C510" t="s">
         <v>936</v>
@@ -26215,10 +26527,10 @@
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B511" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C511" t="s">
         <v>936</v>
@@ -26253,16 +26565,16 @@
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B512" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C512" t="s">
         <v>936</v>
       </c>
       <c r="D512" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="E512" t="s">
         <v>25</v>
@@ -26291,10 +26603,10 @@
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B513" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C513" t="s">
         <v>936</v>
@@ -26329,10 +26641,10 @@
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B514" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C514" t="s">
         <v>936</v>
@@ -26367,10 +26679,10 @@
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B515" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C515" t="s">
         <v>936</v>
@@ -26405,10 +26717,10 @@
     </row>
     <row r="516" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B516" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C516" t="s">
         <v>936</v>
@@ -26443,10 +26755,10 @@
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B517" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C517" t="s">
         <v>936</v>
@@ -26481,10 +26793,10 @@
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B518" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C518" t="s">
         <v>936</v>
@@ -26519,16 +26831,16 @@
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B519" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C519" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D519" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E519" t="s">
         <v>25</v>
@@ -26557,10 +26869,10 @@
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="B520" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="C520" t="s">
         <v>961</v>
@@ -26595,10 +26907,10 @@
     </row>
     <row r="521" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B521" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C521" t="s">
         <v>961</v>
@@ -26633,10 +26945,10 @@
     </row>
     <row r="522" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B522" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C522" t="s">
         <v>961</v>
@@ -26671,10 +26983,10 @@
     </row>
     <row r="523" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B523" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C523" t="s">
         <v>961</v>
@@ -26709,10 +27021,10 @@
     </row>
     <row r="524" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B524" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C524" t="s">
         <v>961</v>
@@ -26747,10 +27059,10 @@
     </row>
     <row r="525" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B525" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C525" t="s">
         <v>961</v>
@@ -26785,10 +27097,10 @@
     </row>
     <row r="526" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B526" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C526" t="s">
         <v>961</v>
@@ -26823,16 +27135,16 @@
     </row>
     <row r="527" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B527" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C527" t="s">
         <v>961</v>
       </c>
       <c r="D527" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E527" t="s">
         <v>25</v>
@@ -26861,10 +27173,10 @@
     </row>
     <row r="528" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B528" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="C528" t="s">
         <v>961</v>
@@ -26899,10 +27211,10 @@
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B529" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C529" t="s">
         <v>961</v>
@@ -26937,10 +27249,10 @@
     </row>
     <row r="530" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B530" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C530" t="s">
         <v>961</v>
@@ -26975,10 +27287,10 @@
     </row>
     <row r="531" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B531" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C531" t="s">
         <v>961</v>
@@ -27013,16 +27325,16 @@
     </row>
     <row r="532" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B532" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C532" t="s">
         <v>961</v>
       </c>
       <c r="D532" t="s">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="E532" t="s">
         <v>25</v>
@@ -27051,10 +27363,10 @@
     </row>
     <row r="533" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="B533" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="C533" t="s">
         <v>961</v>
@@ -27089,16 +27401,16 @@
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B534" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C534" t="s">
         <v>961</v>
       </c>
       <c r="D534" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="E534" t="s">
         <v>25</v>
@@ -27127,10 +27439,10 @@
     </row>
     <row r="535" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="B535" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="C535" t="s">
         <v>961</v>
@@ -27165,10 +27477,10 @@
     </row>
     <row r="536" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B536" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C536" t="s">
         <v>961</v>
@@ -27203,10 +27515,10 @@
     </row>
     <row r="537" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B537" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C537" t="s">
         <v>961</v>
@@ -27241,10 +27553,10 @@
     </row>
     <row r="538" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B538" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C538" t="s">
         <v>961</v>
@@ -27279,10 +27591,10 @@
     </row>
     <row r="539" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B539" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C539" t="s">
         <v>961</v>
@@ -27317,16 +27629,16 @@
     </row>
     <row r="540" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B540" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C540" t="s">
         <v>961</v>
       </c>
       <c r="D540" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="E540" t="s">
         <v>25</v>
@@ -27355,10 +27667,10 @@
     </row>
     <row r="541" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="B541" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="C541" t="s">
         <v>961</v>
@@ -27393,10 +27705,10 @@
     </row>
     <row r="542" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B542" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C542" t="s">
         <v>961</v>
@@ -27431,10 +27743,10 @@
     </row>
     <row r="543" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B543" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C543" t="s">
         <v>961</v>
@@ -27469,16 +27781,16 @@
     </row>
     <row r="544" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B544" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C544" t="s">
         <v>961</v>
       </c>
       <c r="D544" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="E544" t="s">
         <v>25</v>
@@ -27507,10 +27819,10 @@
     </row>
     <row r="545" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="B545" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="C545" t="s">
         <v>961</v>
@@ -27545,10 +27857,10 @@
     </row>
     <row r="546" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B546" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C546" t="s">
         <v>961</v>
@@ -27583,10 +27895,10 @@
     </row>
     <row r="547" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B547" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C547" t="s">
         <v>961</v>
@@ -27621,16 +27933,16 @@
     </row>
     <row r="548" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B548" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C548" t="s">
         <v>961</v>
       </c>
       <c r="D548" t="s">
-        <v>1026</v>
+        <v>1017</v>
       </c>
       <c r="E548" t="s">
         <v>25</v>
@@ -27659,10 +27971,10 @@
     </row>
     <row r="549" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="B549" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="C549" t="s">
         <v>961</v>
@@ -27697,10 +28009,10 @@
     </row>
     <row r="550" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B550" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C550" t="s">
         <v>961</v>
@@ -27735,10 +28047,10 @@
     </row>
     <row r="551" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B551" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C551" t="s">
         <v>961</v>
@@ -27773,16 +28085,16 @@
     </row>
     <row r="552" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B552" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C552" t="s">
         <v>961</v>
       </c>
       <c r="D552" t="s">
-        <v>1035</v>
+        <v>1026</v>
       </c>
       <c r="E552" t="s">
         <v>25</v>
@@ -27811,10 +28123,10 @@
     </row>
     <row r="553" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="B553" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="C553" t="s">
         <v>961</v>
@@ -27849,10 +28161,10 @@
     </row>
     <row r="554" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B554" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C554" t="s">
         <v>961</v>
@@ -27887,10 +28199,10 @@
     </row>
     <row r="555" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B555" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C555" t="s">
         <v>961</v>
@@ -27925,16 +28237,16 @@
     </row>
     <row r="556" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B556" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C556" t="s">
         <v>961</v>
       </c>
       <c r="D556" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="E556" t="s">
         <v>25</v>
@@ -27963,10 +28275,10 @@
     </row>
     <row r="557" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="B557" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="C557" t="s">
         <v>961</v>
@@ -28001,10 +28313,10 @@
     </row>
     <row r="558" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B558" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C558" t="s">
         <v>961</v>
@@ -28039,10 +28351,10 @@
     </row>
     <row r="559" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B559" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C559" t="s">
         <v>961</v>
@@ -28077,10 +28389,10 @@
     </row>
     <row r="560" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B560" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C560" t="s">
         <v>961</v>
@@ -28115,10 +28427,10 @@
     </row>
     <row r="561" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B561" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C561" t="s">
         <v>961</v>
@@ -28148,6 +28460,44 @@
         <v>25</v>
       </c>
       <c r="L561" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C562" t="s">
+        <v>961</v>
+      </c>
+      <c r="D562" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E562" t="s">
+        <v>25</v>
+      </c>
+      <c r="F562" t="s">
+        <v>25</v>
+      </c>
+      <c r="G562" t="s">
+        <v>25</v>
+      </c>
+      <c r="H562" t="s">
+        <v>19</v>
+      </c>
+      <c r="I562" t="s">
+        <v>25</v>
+      </c>
+      <c r="J562" t="s">
+        <v>25</v>
+      </c>
+      <c r="K562" t="s">
+        <v>25</v>
+      </c>
+      <c r="L562" t="s">
         <v>25</v>
       </c>
     </row>
@@ -28156,7 +28506,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 G38:L38 B39:L39 B37:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 A11:D12 F10:F12 J10:L12 H10:H12 B17:D18 F17:F18 H17:H18 J17:L17 K18:L18 A28:G28 L21 F22:F24 J22:L24 A33:D36 L33 A21:D25 H21:H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F34:F36 J34:L36 H33:H36 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67:A68 J67:L68 J72:L73 F72 F73:G73 F67:G68 C67:D68 H72 A72:A74 A84 I84:L84 C72:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87 A91:D91 F91 H91:L91 A97:G99 L98 A96:D96 F96 H96:L96 A122:D122 I97:L97 I98:J98 I99:L99 A101:D101 F101 A104:D104 H104:I104 J101:L101 H101 L104 A109:D109 H109:I109 L109 A113:G113 I113:L113 A117 F117 C117:D117 A121 C121:D121 F121 J117:L117 J121:L121 A126:L561 A125:I125 K125:L125 H117 H121 H122:I122 L122" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 G38:L38 B39:L39 B37:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 A11:D12 F10:F12 J10:L12 H10:H12 B17:D18 F17:F18 H17:H18 J17:L17 K18:L18 A28:G28 L21 F22:F24 J22:L24 A33:D36 L33 A21:D25 H21:H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F34:F36 J34:L36 H33:H36 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67:A68 J67:L68 J72:L73 F72 F73:G73 F67:G68 C67:D68 H72 A72:A74 A84 I84:L84 C72:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87 A91:D91 F91 H91:L91 A97:G99 L98 A96:D96 F96 H96:L96 A122:D122 I97:L97 I98:J98 I99:L99 A101:D101 F101 A104:D104 H104:I104 J101:L101 H101 L104 A109:D109 H109:I109 L109 A113:G113 I113:L113 A117 F117 C117:D117 A121 C121:D121 F121 J117:L117 J121:L121 A129:L562 A126:D126 K126:L126 H117 H121 H122:I122 L122 H126:I126 A127:D127 H127:I127 L127 A128:G128 I128:L128" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="701" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2186EC46-EFD0-414C-B71F-248AC37D1579}"/>
+  <xr:revisionPtr revIDLastSave="790" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD3D704-27E6-4F4D-8804-86BB7BA3CC5D}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6629" uniqueCount="1238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6947" uniqueCount="1262">
   <si>
     <t>Codigo</t>
   </si>
@@ -6916,6 +6916,618 @@
   </si>
   <si>
     <t>assets/productos/bebes/sillacarrodd2/silladd2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/tinainflable/tinainflableniño.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/tinainflable/tinainflableniño2.webp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tina Inflable para Bebé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> está diseñada para ofrecer una experiencia de baño cómoda y segura desde los primeros meses. Su respaldo ergonómico y base antideslizante brindan mayor estabilidad y confort, mientras que su diseño inflable permite guardarla y transportarla fácilmente. Además, incorpora detalles prácticos como indicador de nivel de agua, bolsillo lateral para accesorios y válvula de drenaje para facilitar su uso y limpieza.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tina inflable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>para bebé con respaldo ergonómico, base antideslizante y diseño portátil, ideal para brindar un baño cómodo, seguro y divertido en casa o durante los viajes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Diseño inflable con respaldo ergonómico.
+Base antideslizante para mayor estabilidad.
+Indicador de nivel de agua.
+Bolsillo lateral para accesorios de baño.
+Válvula inferior para un drenaje rápido y sencillo.
+Fabricada en PVC y plástico resistente.
+Edad recomendada: de 0 a 3 años.
+Incluye parche de reparación.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Brinda mayor comodidad y seguridad durante el baño.
+Fácil de inflar, desinflar, guardar y transportar.
+Puede utilizarse en casa o durante viajes.
+Diseño acolchado que proporciona mayor confort para el bebé.
+Facilita el momento del baño gracias a sus accesorios prácticos.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Inflar con una presión moderada para prolongar su vida útil.
+Secar completamente antes de guardarla.
+Limpiar con un paño suave, agua y jabón neutro.
+Utilizar siempre bajo la supervisión de un adulto.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Las </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rodilleras Acolchadas para Bebé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> son el complemento ideal para acompañar a los pequeños durante sus primeros desplazamientos. Gracias a su acolchado con superficie antideslizante, ayudan a proteger las rodillas de golpes, raspaduras y el contacto con superficies frías o duras mientras el bebé explora su entorno.
+Su material suave, elástico y transpirable se adapta cómodamente a las piernas del bebé sin limitar el movimiento, ofreciendo mayor comodidad durante el gateo. Además, su diseño ligero y adorable las convierte en un accesorio práctico para el uso diario.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Rodilleras acolchadas para bebé </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>con superficie antideslizante, diseñadas para proteger las rodillas durante la etapa de gateo, brindando comodidad, seguridad y libertad de movimiento.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Superficie acolchada con diseño antideslizante.
+Material suave, flexible y transpirable.
+Composición: 95% algodón y 5% silicona spandex.
+Talla única con ajuste cómodo.
+Edad recomendada: de 6 a 24 meses.
+Ideales para bebés en etapa de gateo.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Protegen las rodillas durante el gateo.
+Ayudan a reducir golpes y raspaduras.
+Mejoran el agarre sobre superficies lisas.
+Se adaptan cómodamente sin limitar el movimiento.
+Mantienen las rodillas limpias mientras el bebé juega y explora.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Lavar a mano o en ciclo delicado con agua fría.
+No utilizar blanqueadores ni productos abrasivos.
+Secar al aire libre y evitar altas temperaturas.
+Utilizar siempre bajo la supervisión de un adulto.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/rodilleras/rodilleras.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/rodilleras/rodilleras2.webp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bañera Plegable para Bebé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> está diseñada para ofrecer una experiencia de baño cómoda, segura y práctica. Gracias a su sistema de plegado tipo acordeón, ocupa muy poco espacio cuando no está en uso, siendo ideal para hogares con espacios reducidos o para llevar durante los viajes.
+Cuenta con un cojín antideslizante que brinda mayor comodidad al bebé, patas estables para una mejor seguridad, tapón de drenaje que facilita el vaciado del agua y un diseño resistente pensado para acompañar el crecimiento del bebé desde el nacimiento hasta aproximadamente los 3 años.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Importante: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Este producto se despacha en el color disponible en bodega al momento de la compra. Los colores mostrados en las imágenes son únicamente de referencia y pueden variar según la disponibilidad.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bañera plegable para bebé</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con cojín antideslizante, patas estables y diseño compacto, ideal para brindar un baño seguro, cómodo y fácil de almacenar desde el nacimiento hasta los 3 años.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Sistema de plegado compacto tipo acordeón.
+Cojín de baño antideslizante.
+Patas estables con base antideslizante.
+Tapón de drenaje para vaciado rápido.
+Espesor plegada de aproximadamente 7 cm.
+Edad recomendada: desde el nacimiento hasta los 3 años.
+Incluye bañera plegable, cojín de baño y manual de uso.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Brinda un baño cómodo y seguro para el bebé.
+Fácil de guardar gracias a su diseño plegable.
+Ideal para espacios pequeños y viajes.
+Cojín ergonómico que ayuda a evitar resbalones.
+Vaciado del agua rápido y práctico mediante el tapón de drenaje.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Lavar con agua tibia y jabón neutro después de cada uso.
+Secar completamente el cojín y la bañera antes de guardarlos.
+Utilizar siempre sobre una superficie firme y nivelada.
+Supervisar al bebé en todo momento durante el baño.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/bañeraplegable/bañera.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/bañeraplegable/bañera2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/bañeraplegable/bañera3.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/bañeraplegable/bañera4.webp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Asiento Reductor Plegable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">para Inodoro Infantil es el compañero ideal para la etapa de aprendizaje del baño. Su diseño compacto y liviano permite llevarlo fácilmente en viajes, paseos o utilizarlo en cualquier baño del hogar, brindando comodidad, higiene y seguridad a los niños durante esta importante etapa de crecimiento.
+Cuenta con un sistema de plegado práctico, superficie antisalpicaduras y clips de seguridad que ayudan a mantener el asiento firme sobre el inodoro, ofreciendo una experiencia más estable y cómoda. Es compatible con la mayoría de sanitarios redondos y alargados, facilitando su instalación en pocos segundos.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Importante: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Este producto se despacha en el color disponible en bodega al momento de la compra. Los colores mostrados en las imágenes son únicamente de referencia y pueden variar según la disponibilidad.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Asiento reductor plegable para entrenamiento de baño</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, compatible con la mayoría de inodoros, ligero, portátil y antideslizante, ideal para acompañar a los pequeños en la transición del pañal al baño con mayor seguridad y confianza.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Asiento reductor plegable para entrenamiento de baño.
+Compatible con inodoros redondos y alargados.
+Sistema de clips antideslizantes para mayor estabilidad.
+Diseño compacto y portátil.
+Superficie antisalpicaduras.
+Dimensiones plegado: aproximadamente 19 × 13 × 5 cm.
+Peso aproximado: 300 g.
+Incluye asiento plegable, manual de uso y funda o bolsa de transporte (según disponibilidad del lote).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Facilita la transición del pañal al inodoro.
+Se instala y retira fácilmente.
+Ligero y fácil de transportar.
+Ideal para uso en casa, viajes o salidas.
+Brinda mayor seguridad y confianza al niño durante el entrenamiento.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Limpiar después de cada uso con agua tibia y jabón neutro.
+Secar completamente antes de plegarlo y guardarlo.
+Verificar que los clips de seguridad estén correctamente ajustados antes de cada uso.
+Utilizar siempre bajo la supervisión de un adulto.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/inodoroentrena/asientoinodoro.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/inodoroentrena/asientoinodoro2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/inodoroentrena/asientoinodoro3.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/inodoroentrena/asientoinodoro4.webp</t>
   </si>
 </sst>
 </file>
@@ -7311,7 +7923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L562"/>
+  <dimension ref="A1:L570"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -12022,14 +12634,14 @@
       <c r="D129" t="s">
         <v>138</v>
       </c>
-      <c r="E129" t="s">
-        <v>25</v>
+      <c r="E129">
+        <v>92500</v>
       </c>
       <c r="F129" t="s">
-        <v>25</v>
+        <v>1240</v>
       </c>
       <c r="G129" t="s">
-        <v>25</v>
+        <v>1238</v>
       </c>
       <c r="H129" t="s">
         <v>19</v>
@@ -12038,10 +12650,10 @@
         <v>25</v>
       </c>
       <c r="J129" t="s">
-        <v>25</v>
-      </c>
-      <c r="K129" t="s">
-        <v>25</v>
+        <v>1241</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>1242</v>
       </c>
       <c r="L129" t="s">
         <v>25</v>
@@ -12049,10 +12661,10 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B130" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C130" t="s">
         <v>14</v>
@@ -12060,14 +12672,14 @@
       <c r="D130" t="s">
         <v>138</v>
       </c>
-      <c r="E130" t="s">
-        <v>25</v>
+      <c r="E130">
+        <v>92500</v>
       </c>
       <c r="F130" t="s">
         <v>25</v>
       </c>
       <c r="G130" t="s">
-        <v>25</v>
+        <v>1239</v>
       </c>
       <c r="H130" t="s">
         <v>19</v>
@@ -12087,10 +12699,10 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B131" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C131" t="s">
         <v>14</v>
@@ -12108,7 +12720,7 @@
         <v>25</v>
       </c>
       <c r="H131" t="s">
-        <v>19</v>
+        <v>1129</v>
       </c>
       <c r="I131" t="s">
         <v>25</v>
@@ -12125,10 +12737,10 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B132" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C132" t="s">
         <v>14</v>
@@ -12146,7 +12758,7 @@
         <v>25</v>
       </c>
       <c r="H132" t="s">
-        <v>19</v>
+        <v>1129</v>
       </c>
       <c r="I132" t="s">
         <v>25</v>
@@ -12163,10 +12775,10 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B133" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C133" t="s">
         <v>14</v>
@@ -12174,14 +12786,14 @@
       <c r="D133" t="s">
         <v>138</v>
       </c>
-      <c r="E133" t="s">
-        <v>25</v>
-      </c>
-      <c r="F133" t="s">
-        <v>25</v>
+      <c r="E133">
+        <v>15280</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>1243</v>
       </c>
       <c r="G133" t="s">
-        <v>25</v>
+        <v>1246</v>
       </c>
       <c r="H133" t="s">
         <v>19</v>
@@ -12190,10 +12802,10 @@
         <v>25</v>
       </c>
       <c r="J133" t="s">
-        <v>25</v>
-      </c>
-      <c r="K133" t="s">
-        <v>25</v>
+        <v>1244</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>1245</v>
       </c>
       <c r="L133" t="s">
         <v>25</v>
@@ -12201,10 +12813,10 @@
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B134" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C134" t="s">
         <v>14</v>
@@ -12212,14 +12824,14 @@
       <c r="D134" t="s">
         <v>138</v>
       </c>
-      <c r="E134" t="s">
-        <v>25</v>
+      <c r="E134">
+        <v>15280</v>
       </c>
       <c r="F134" t="s">
         <v>25</v>
       </c>
       <c r="G134" t="s">
-        <v>25</v>
+        <v>1247</v>
       </c>
       <c r="H134" t="s">
         <v>19</v>
@@ -12239,25 +12851,25 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B135" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C135" t="s">
         <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>153</v>
-      </c>
-      <c r="E135" t="s">
-        <v>25</v>
-      </c>
-      <c r="F135" t="s">
-        <v>25</v>
+        <v>138</v>
+      </c>
+      <c r="E135">
+        <v>182085</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>1248</v>
       </c>
       <c r="G135" t="s">
-        <v>25</v>
+        <v>1251</v>
       </c>
       <c r="H135" t="s">
         <v>19</v>
@@ -12266,10 +12878,10 @@
         <v>25</v>
       </c>
       <c r="J135" t="s">
-        <v>25</v>
-      </c>
-      <c r="K135" t="s">
-        <v>25</v>
+        <v>1249</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>1250</v>
       </c>
       <c r="L135" t="s">
         <v>25</v>
@@ -12277,25 +12889,25 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B136" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C136" t="s">
         <v>14</v>
       </c>
       <c r="D136" t="s">
-        <v>153</v>
-      </c>
-      <c r="E136" t="s">
-        <v>25</v>
+        <v>138</v>
+      </c>
+      <c r="E136">
+        <v>182085</v>
       </c>
       <c r="F136" t="s">
         <v>25</v>
       </c>
       <c r="G136" t="s">
-        <v>25</v>
+        <v>1252</v>
       </c>
       <c r="H136" t="s">
         <v>19</v>
@@ -12315,25 +12927,25 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B137" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C137" t="s">
         <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>153</v>
-      </c>
-      <c r="E137" t="s">
-        <v>25</v>
+        <v>138</v>
+      </c>
+      <c r="E137">
+        <v>182085</v>
       </c>
       <c r="F137" t="s">
         <v>25</v>
       </c>
       <c r="G137" t="s">
-        <v>25</v>
+        <v>1253</v>
       </c>
       <c r="H137" t="s">
         <v>19</v>
@@ -12353,31 +12965,25 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B138" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C138" t="s">
         <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>153</v>
-      </c>
-      <c r="E138" t="s">
-        <v>25</v>
-      </c>
-      <c r="F138" t="s">
-        <v>25</v>
+        <v>138</v>
+      </c>
+      <c r="E138">
+        <v>182085</v>
       </c>
       <c r="G138" t="s">
-        <v>25</v>
+        <v>1254</v>
       </c>
       <c r="H138" t="s">
         <v>19</v>
-      </c>
-      <c r="I138" t="s">
-        <v>25</v>
       </c>
       <c r="J138" t="s">
         <v>25</v>
@@ -12391,25 +12997,25 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B139" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C139" t="s">
         <v>14</v>
       </c>
       <c r="D139" t="s">
-        <v>153</v>
-      </c>
-      <c r="E139" t="s">
-        <v>25</v>
-      </c>
-      <c r="F139" t="s">
-        <v>25</v>
+        <v>138</v>
+      </c>
+      <c r="E139">
+        <v>119156</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>1255</v>
       </c>
       <c r="G139" t="s">
-        <v>25</v>
+        <v>1258</v>
       </c>
       <c r="H139" t="s">
         <v>19</v>
@@ -12418,10 +13024,10 @@
         <v>25</v>
       </c>
       <c r="J139" t="s">
-        <v>25</v>
-      </c>
-      <c r="K139" t="s">
-        <v>25</v>
+        <v>1256</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>1257</v>
       </c>
       <c r="L139" t="s">
         <v>25</v>
@@ -12429,25 +13035,25 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B140" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C140" t="s">
         <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>153</v>
-      </c>
-      <c r="E140" t="s">
-        <v>25</v>
+        <v>138</v>
+      </c>
+      <c r="E140">
+        <v>119156</v>
       </c>
       <c r="F140" t="s">
         <v>25</v>
       </c>
       <c r="G140" t="s">
-        <v>25</v>
+        <v>1259</v>
       </c>
       <c r="H140" t="s">
         <v>19</v>
@@ -12467,25 +13073,25 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="B141" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C141" t="s">
         <v>14</v>
       </c>
       <c r="D141" t="s">
-        <v>153</v>
-      </c>
-      <c r="E141" t="s">
-        <v>25</v>
+        <v>138</v>
+      </c>
+      <c r="E141">
+        <v>119156</v>
       </c>
       <c r="F141" t="s">
         <v>25</v>
       </c>
       <c r="G141" t="s">
-        <v>25</v>
+        <v>1260</v>
       </c>
       <c r="H141" t="s">
         <v>19</v>
@@ -12505,25 +13111,25 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="C142" t="s">
         <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>153</v>
-      </c>
-      <c r="E142" t="s">
-        <v>25</v>
+        <v>138</v>
+      </c>
+      <c r="E142">
+        <v>119156</v>
       </c>
       <c r="F142" t="s">
         <v>25</v>
       </c>
       <c r="G142" t="s">
-        <v>25</v>
+        <v>1261</v>
       </c>
       <c r="H142" t="s">
         <v>19</v>
@@ -12543,10 +13149,10 @@
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="B143" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C143" t="s">
         <v>14</v>
@@ -12581,10 +13187,10 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B144" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C144" t="s">
         <v>14</v>
@@ -12619,10 +13225,10 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="B145" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="C145" t="s">
         <v>14</v>
@@ -12657,10 +13263,10 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="B146" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C146" t="s">
         <v>14</v>
@@ -12695,10 +13301,10 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="B147" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C147" t="s">
         <v>14</v>
@@ -12733,10 +13339,10 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B148" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C148" t="s">
         <v>14</v>
@@ -12771,10 +13377,10 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="B149" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C149" t="s">
         <v>14</v>
@@ -12809,10 +13415,10 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="B150" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C150" t="s">
         <v>14</v>
@@ -12847,10 +13453,10 @@
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="B151" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="C151" t="s">
         <v>14</v>
@@ -12885,10 +13491,10 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B152" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="C152" t="s">
         <v>14</v>
@@ -12923,10 +13529,10 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B153" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="C153" t="s">
         <v>14</v>
@@ -12961,10 +13567,10 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B154" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="C154" t="s">
         <v>14</v>
@@ -12999,10 +13605,10 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="B155" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="C155" t="s">
         <v>14</v>
@@ -13010,14 +13616,14 @@
       <c r="D155" t="s">
         <v>153</v>
       </c>
-      <c r="E155">
-        <v>106156</v>
+      <c r="E155" t="s">
+        <v>25</v>
       </c>
       <c r="F155" t="s">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="G155" t="s">
-        <v>194</v>
+        <v>25</v>
       </c>
       <c r="H155" t="s">
         <v>19</v>
@@ -13026,10 +13632,10 @@
         <v>25</v>
       </c>
       <c r="J155" t="s">
-        <v>195</v>
+        <v>25</v>
       </c>
       <c r="K155" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="L155" t="s">
         <v>25</v>
@@ -13037,10 +13643,10 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="B156" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C156" t="s">
         <v>14</v>
@@ -13048,14 +13654,14 @@
       <c r="D156" t="s">
         <v>153</v>
       </c>
-      <c r="E156">
-        <v>106156</v>
+      <c r="E156" t="s">
+        <v>25</v>
       </c>
       <c r="F156" t="s">
         <v>25</v>
       </c>
       <c r="G156" t="s">
-        <v>197</v>
+        <v>25</v>
       </c>
       <c r="H156" t="s">
         <v>19</v>
@@ -13075,16 +13681,16 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="B157" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="C157" t="s">
         <v>14</v>
       </c>
       <c r="D157" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="E157" t="s">
         <v>25</v>
@@ -13113,16 +13719,16 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="B158" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="C158" t="s">
         <v>14</v>
       </c>
       <c r="D158" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="E158" t="s">
         <v>25</v>
@@ -13151,16 +13757,16 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="B159" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="C159" t="s">
         <v>14</v>
       </c>
       <c r="D159" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="E159" t="s">
         <v>25</v>
@@ -13189,16 +13795,16 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="B160" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="C160" t="s">
         <v>14</v>
       </c>
       <c r="D160" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="E160" t="s">
         <v>25</v>
@@ -13227,16 +13833,16 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="B161" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="C161" t="s">
         <v>14</v>
       </c>
       <c r="D161" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="E161" t="s">
         <v>25</v>
@@ -13265,16 +13871,16 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="B162" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="C162" t="s">
         <v>14</v>
       </c>
       <c r="D162" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="E162" t="s">
         <v>25</v>
@@ -13303,25 +13909,25 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="B163" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="C163" t="s">
         <v>14</v>
       </c>
       <c r="D163" t="s">
-        <v>200</v>
-      </c>
-      <c r="E163" t="s">
-        <v>25</v>
+        <v>153</v>
+      </c>
+      <c r="E163">
+        <v>106156</v>
       </c>
       <c r="F163" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="G163" t="s">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="H163" t="s">
         <v>19</v>
@@ -13330,10 +13936,10 @@
         <v>25</v>
       </c>
       <c r="J163" t="s">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="K163" t="s">
-        <v>25</v>
+        <v>196</v>
       </c>
       <c r="L163" t="s">
         <v>25</v>
@@ -13341,25 +13947,25 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="B164" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="C164" t="s">
         <v>14</v>
       </c>
       <c r="D164" t="s">
-        <v>200</v>
-      </c>
-      <c r="E164" t="s">
-        <v>25</v>
+        <v>153</v>
+      </c>
+      <c r="E164">
+        <v>106156</v>
       </c>
       <c r="F164" t="s">
         <v>25</v>
       </c>
       <c r="G164" t="s">
-        <v>25</v>
+        <v>197</v>
       </c>
       <c r="H164" t="s">
         <v>19</v>
@@ -13379,10 +13985,10 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="B165" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="C165" t="s">
         <v>14</v>
@@ -13417,10 +14023,10 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="B166" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="C166" t="s">
         <v>14</v>
@@ -13455,10 +14061,10 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="B167" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C167" t="s">
         <v>14</v>
@@ -13493,10 +14099,10 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="B168" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C168" t="s">
         <v>14</v>
@@ -13531,10 +14137,10 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="B169" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C169" t="s">
         <v>14</v>
@@ -13569,16 +14175,16 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="B170" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="C170" t="s">
         <v>14</v>
       </c>
       <c r="D170" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E170" t="s">
         <v>25</v>
@@ -13607,16 +14213,16 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="B171" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="C171" t="s">
         <v>14</v>
       </c>
       <c r="D171" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E171" t="s">
         <v>25</v>
@@ -13645,16 +14251,16 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="B172" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C172" t="s">
         <v>14</v>
       </c>
       <c r="D172" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E172" t="s">
         <v>25</v>
@@ -13683,16 +14289,16 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="B173" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C173" t="s">
         <v>14</v>
       </c>
       <c r="D173" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E173" t="s">
         <v>25</v>
@@ -13721,16 +14327,16 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="B174" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C174" t="s">
         <v>14</v>
       </c>
       <c r="D174" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E174" t="s">
         <v>25</v>
@@ -13759,16 +14365,16 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="B175" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C175" t="s">
         <v>14</v>
       </c>
       <c r="D175" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="E175" t="s">
         <v>25</v>
@@ -13797,16 +14403,16 @@
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="B176" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="C176" t="s">
         <v>14</v>
       </c>
       <c r="D176" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="E176" t="s">
         <v>25</v>
@@ -13835,16 +14441,16 @@
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="B177" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="C177" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D177" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="E177" t="s">
         <v>25</v>
@@ -13873,16 +14479,16 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="B178" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="C178" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D178" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="E178" t="s">
         <v>25</v>
@@ -13911,16 +14517,16 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B179" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="C179" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D179" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="E179" t="s">
         <v>25</v>
@@ -13949,16 +14555,16 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="B180" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="C180" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D180" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="E180" t="s">
         <v>25</v>
@@ -13987,16 +14593,16 @@
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="B181" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="C181" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D181" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="E181" t="s">
         <v>25</v>
@@ -14025,16 +14631,16 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="B182" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="C182" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D182" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="E182" t="s">
         <v>25</v>
@@ -14063,16 +14669,16 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="B183" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="C183" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D183" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E183" t="s">
         <v>25</v>
@@ -14101,16 +14707,16 @@
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="B184" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C184" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D184" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E184" t="s">
         <v>25</v>
@@ -14139,10 +14745,10 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="B185" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="C185" t="s">
         <v>241</v>
@@ -14177,10 +14783,10 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="B186" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C186" t="s">
         <v>241</v>
@@ -14215,10 +14821,10 @@
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="B187" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="C187" t="s">
         <v>241</v>
@@ -14253,10 +14859,10 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="B188" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="C188" t="s">
         <v>241</v>
@@ -14291,10 +14897,10 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="B189" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C189" t="s">
         <v>241</v>
@@ -14329,10 +14935,10 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="B190" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="C190" t="s">
         <v>241</v>
@@ -14367,10 +14973,10 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="B191" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="C191" t="s">
         <v>241</v>
@@ -14405,10 +15011,10 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="B192" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="C192" t="s">
         <v>241</v>
@@ -14443,10 +15049,10 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="B193" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="C193" t="s">
         <v>241</v>
@@ -14481,10 +15087,10 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="B194" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="C194" t="s">
         <v>241</v>
@@ -14519,10 +15125,10 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="B195" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="C195" t="s">
         <v>241</v>
@@ -14557,10 +15163,10 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="B196" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="C196" t="s">
         <v>241</v>
@@ -14595,10 +15201,10 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="B197" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="C197" t="s">
         <v>241</v>
@@ -14633,10 +15239,10 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="B198" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="C198" t="s">
         <v>241</v>
@@ -14671,10 +15277,10 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="B199" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="C199" t="s">
         <v>241</v>
@@ -14709,10 +15315,10 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="B200" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="C200" t="s">
         <v>241</v>
@@ -14747,10 +15353,10 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="B201" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="C201" t="s">
         <v>241</v>
@@ -14785,10 +15391,10 @@
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="B202" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C202" t="s">
         <v>241</v>
@@ -14823,10 +15429,10 @@
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="B203" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="C203" t="s">
         <v>241</v>
@@ -14861,10 +15467,10 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="B204" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="C204" t="s">
         <v>241</v>
@@ -14899,10 +15505,10 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="B205" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="C205" t="s">
         <v>241</v>
@@ -14937,10 +15543,10 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="B206" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="C206" t="s">
         <v>241</v>
@@ -14975,10 +15581,10 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="B207" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="C207" t="s">
         <v>241</v>
@@ -15013,10 +15619,10 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="B208" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="C208" t="s">
         <v>241</v>
@@ -15051,10 +15657,10 @@
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="B209" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="C209" t="s">
         <v>241</v>
@@ -15089,10 +15695,10 @@
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="B210" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="C210" t="s">
         <v>241</v>
@@ -15127,10 +15733,10 @@
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="B211" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="C211" t="s">
         <v>241</v>
@@ -15165,10 +15771,10 @@
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B212" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="C212" t="s">
         <v>241</v>
@@ -15203,10 +15809,10 @@
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="B213" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="C213" t="s">
         <v>241</v>
@@ -15241,10 +15847,10 @@
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="B214" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="C214" t="s">
         <v>241</v>
@@ -15279,16 +15885,16 @@
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="B215" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C215" t="s">
         <v>241</v>
       </c>
       <c r="D215" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E215" t="s">
         <v>25</v>
@@ -15317,16 +15923,16 @@
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="B216" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="C216" t="s">
         <v>241</v>
       </c>
       <c r="D216" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E216" t="s">
         <v>25</v>
@@ -15355,16 +15961,16 @@
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="B217" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="C217" t="s">
         <v>241</v>
       </c>
       <c r="D217" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E217" t="s">
         <v>25</v>
@@ -15393,16 +15999,16 @@
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="B218" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="C218" t="s">
         <v>241</v>
       </c>
       <c r="D218" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E218" t="s">
         <v>25</v>
@@ -15431,16 +16037,16 @@
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="B219" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="C219" t="s">
         <v>241</v>
       </c>
       <c r="D219" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E219" t="s">
         <v>25</v>
@@ -15469,16 +16075,16 @@
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="B220" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="C220" t="s">
         <v>241</v>
       </c>
       <c r="D220" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E220" t="s">
         <v>25</v>
@@ -15507,16 +16113,16 @@
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="B221" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="C221" t="s">
         <v>241</v>
       </c>
       <c r="D221" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E221" t="s">
         <v>25</v>
@@ -15545,16 +16151,16 @@
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B222" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="C222" t="s">
         <v>241</v>
       </c>
       <c r="D222" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E222" t="s">
         <v>25</v>
@@ -15583,10 +16189,10 @@
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="B223" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="C223" t="s">
         <v>241</v>
@@ -15621,10 +16227,10 @@
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="B224" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="C224" t="s">
         <v>241</v>
@@ -15659,16 +16265,16 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="B225" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="C225" t="s">
         <v>241</v>
       </c>
       <c r="D225" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="E225" t="s">
         <v>25</v>
@@ -15697,16 +16303,16 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="B226" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="C226" t="s">
         <v>241</v>
       </c>
       <c r="D226" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="E226" t="s">
         <v>25</v>
@@ -15735,16 +16341,16 @@
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="B227" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="C227" t="s">
         <v>241</v>
       </c>
       <c r="D227" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="E227" t="s">
         <v>25</v>
@@ -15773,16 +16379,16 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="B228" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="C228" t="s">
         <v>241</v>
       </c>
       <c r="D228" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="E228" t="s">
         <v>25</v>
@@ -15811,16 +16417,16 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="B229" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C229" t="s">
         <v>241</v>
       </c>
       <c r="D229" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="E229" t="s">
         <v>25</v>
@@ -15849,16 +16455,16 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="B230" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="C230" t="s">
         <v>241</v>
       </c>
       <c r="D230" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="E230" t="s">
         <v>25</v>
@@ -15887,16 +16493,16 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="B231" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="C231" t="s">
         <v>241</v>
       </c>
       <c r="D231" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="E231" t="s">
         <v>25</v>
@@ -15925,16 +16531,16 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="B232" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="C232" t="s">
         <v>241</v>
       </c>
       <c r="D232" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="E232" t="s">
         <v>25</v>
@@ -15963,16 +16569,16 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="B233" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="C233" t="s">
         <v>241</v>
       </c>
       <c r="D233" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E233" t="s">
         <v>25</v>
@@ -16001,16 +16607,16 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="B234" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="C234" t="s">
         <v>241</v>
       </c>
       <c r="D234" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E234" t="s">
         <v>25</v>
@@ -16039,16 +16645,16 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B235" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="C235" t="s">
         <v>241</v>
       </c>
       <c r="D235" t="s">
-        <v>227</v>
+        <v>340</v>
       </c>
       <c r="E235" t="s">
         <v>25</v>
@@ -16077,16 +16683,16 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B236" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C236" t="s">
         <v>241</v>
       </c>
       <c r="D236" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E236" t="s">
         <v>25</v>
@@ -16115,16 +16721,16 @@
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="B237" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="C237" t="s">
         <v>241</v>
       </c>
       <c r="D237" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E237" t="s">
         <v>25</v>
@@ -16153,16 +16759,16 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="B238" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="C238" t="s">
         <v>241</v>
       </c>
       <c r="D238" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E238" t="s">
         <v>25</v>
@@ -16191,16 +16797,16 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="B239" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="C239" t="s">
         <v>241</v>
       </c>
       <c r="D239" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E239" t="s">
         <v>25</v>
@@ -16229,16 +16835,16 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="B240" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="C240" t="s">
         <v>241</v>
       </c>
       <c r="D240" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E240" t="s">
         <v>25</v>
@@ -16267,16 +16873,16 @@
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="B241" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="C241" t="s">
         <v>241</v>
       </c>
       <c r="D241" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E241" t="s">
         <v>25</v>
@@ -16305,16 +16911,16 @@
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="B242" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C242" t="s">
         <v>241</v>
       </c>
       <c r="D242" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E242" t="s">
         <v>25</v>
@@ -16343,10 +16949,10 @@
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="B243" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="C243" t="s">
         <v>241</v>
@@ -16381,10 +16987,10 @@
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="B244" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="C244" t="s">
         <v>241</v>
@@ -16419,10 +17025,10 @@
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="B245" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="C245" t="s">
         <v>241</v>
@@ -16457,10 +17063,10 @@
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B246" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C246" t="s">
         <v>241</v>
@@ -16495,10 +17101,10 @@
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="B247" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C247" t="s">
         <v>241</v>
@@ -16533,10 +17139,10 @@
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B248" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C248" t="s">
         <v>241</v>
@@ -16571,10 +17177,10 @@
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="B249" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="C249" t="s">
         <v>241</v>
@@ -16609,10 +17215,10 @@
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="B250" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="C250" t="s">
         <v>241</v>
@@ -16647,10 +17253,10 @@
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="B251" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="C251" t="s">
         <v>241</v>
@@ -16685,10 +17291,10 @@
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="B252" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="C252" t="s">
         <v>241</v>
@@ -16723,10 +17329,10 @@
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="B253" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="C253" t="s">
         <v>241</v>
@@ -16761,10 +17367,10 @@
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="B254" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="C254" t="s">
         <v>241</v>
@@ -16799,10 +17405,10 @@
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="B255" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C255" t="s">
         <v>241</v>
@@ -16837,10 +17443,10 @@
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="B256" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C256" t="s">
         <v>241</v>
@@ -16875,10 +17481,10 @@
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="B257" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="C257" t="s">
         <v>241</v>
@@ -16913,10 +17519,10 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="B258" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="C258" t="s">
         <v>241</v>
@@ -16951,10 +17557,10 @@
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="B259" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="C259" t="s">
         <v>241</v>
@@ -16989,10 +17595,10 @@
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="B260" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="C260" t="s">
         <v>241</v>
@@ -17027,16 +17633,16 @@
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="B261" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="C261" t="s">
         <v>241</v>
       </c>
       <c r="D261" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E261" t="s">
         <v>25</v>
@@ -17065,16 +17671,16 @@
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="B262" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="C262" t="s">
         <v>241</v>
       </c>
       <c r="D262" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E262" t="s">
         <v>25</v>
@@ -17103,16 +17709,16 @@
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B263" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C263" t="s">
         <v>241</v>
       </c>
       <c r="D263" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E263" t="s">
         <v>25</v>
@@ -17141,16 +17747,16 @@
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="B264" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="C264" t="s">
         <v>241</v>
       </c>
       <c r="D264" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E264" t="s">
         <v>25</v>
@@ -17179,16 +17785,16 @@
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="B265" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="C265" t="s">
         <v>241</v>
       </c>
       <c r="D265" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E265" t="s">
         <v>25</v>
@@ -17217,16 +17823,16 @@
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="B266" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="C266" t="s">
         <v>241</v>
       </c>
       <c r="D266" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E266" t="s">
         <v>25</v>
@@ -17255,16 +17861,16 @@
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="B267" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="C267" t="s">
         <v>241</v>
       </c>
       <c r="D267" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E267" t="s">
         <v>25</v>
@@ -17293,16 +17899,16 @@
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="B268" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="C268" t="s">
         <v>241</v>
       </c>
       <c r="D268" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E268" t="s">
         <v>25</v>
@@ -17331,10 +17937,10 @@
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="B269" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="C269" t="s">
         <v>241</v>
@@ -17369,10 +17975,10 @@
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="B270" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="C270" t="s">
         <v>241</v>
@@ -17407,10 +18013,10 @@
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="B271" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C271" t="s">
         <v>241</v>
@@ -17445,10 +18051,10 @@
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="B272" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="C272" t="s">
         <v>241</v>
@@ -17483,10 +18089,10 @@
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="B273" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="C273" t="s">
         <v>241</v>
@@ -17521,10 +18127,10 @@
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="B274" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="C274" t="s">
         <v>241</v>
@@ -17559,10 +18165,10 @@
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="B275" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="C275" t="s">
         <v>241</v>
@@ -17597,10 +18203,10 @@
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="B276" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="C276" t="s">
         <v>241</v>
@@ -17635,10 +18241,10 @@
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B277" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="C277" t="s">
         <v>241</v>
@@ -17673,10 +18279,10 @@
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="B278" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="C278" t="s">
         <v>241</v>
@@ -17711,10 +18317,10 @@
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="B279" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="C279" t="s">
         <v>241</v>
@@ -17749,10 +18355,10 @@
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="B280" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="C280" t="s">
         <v>241</v>
@@ -17787,10 +18393,10 @@
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="B281" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="C281" t="s">
         <v>241</v>
@@ -17825,10 +18431,10 @@
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="B282" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="C282" t="s">
         <v>241</v>
@@ -17863,10 +18469,10 @@
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="B283" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="C283" t="s">
         <v>241</v>
@@ -17901,10 +18507,10 @@
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="B284" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="C284" t="s">
         <v>241</v>
@@ -17939,10 +18545,10 @@
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="B285" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="C285" t="s">
         <v>241</v>
@@ -17977,10 +18583,10 @@
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="B286" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="C286" t="s">
         <v>241</v>
@@ -18015,16 +18621,16 @@
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="B287" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="C287" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D287" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E287" t="s">
         <v>25</v>
@@ -18053,16 +18659,16 @@
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="B288" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="C288" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D288" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E288" t="s">
         <v>25</v>
@@ -18091,16 +18697,16 @@
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="B289" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="C289" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D289" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E289" t="s">
         <v>25</v>
@@ -18129,16 +18735,16 @@
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="B290" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="C290" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D290" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E290" t="s">
         <v>25</v>
@@ -18167,16 +18773,16 @@
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="B291" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="C291" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D291" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E291" t="s">
         <v>25</v>
@@ -18205,16 +18811,16 @@
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="B292" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="C292" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D292" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E292" t="s">
         <v>25</v>
@@ -18243,16 +18849,16 @@
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="B293" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="C293" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D293" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E293" t="s">
         <v>25</v>
@@ -18281,16 +18887,16 @@
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="B294" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="C294" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D294" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E294" t="s">
         <v>25</v>
@@ -18319,10 +18925,10 @@
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="B295" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="C295" t="s">
         <v>462</v>
@@ -18357,10 +18963,10 @@
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="B296" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="C296" t="s">
         <v>462</v>
@@ -18395,10 +19001,10 @@
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="B297" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="C297" t="s">
         <v>462</v>
@@ -18433,10 +19039,10 @@
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="B298" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="C298" t="s">
         <v>462</v>
@@ -18471,10 +19077,10 @@
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="B299" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="C299" t="s">
         <v>462</v>
@@ -18509,10 +19115,10 @@
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="B300" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="C300" t="s">
         <v>462</v>
@@ -18547,10 +19153,10 @@
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="B301" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="C301" t="s">
         <v>462</v>
@@ -18585,10 +19191,10 @@
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="B302" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="C302" t="s">
         <v>462</v>
@@ -18623,10 +19229,10 @@
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="B303" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="C303" t="s">
         <v>462</v>
@@ -18661,10 +19267,10 @@
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="B304" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="C304" t="s">
         <v>462</v>
@@ -18699,10 +19305,10 @@
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="B305" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="C305" t="s">
         <v>462</v>
@@ -18737,10 +19343,10 @@
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="B306" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="C306" t="s">
         <v>462</v>
@@ -18775,10 +19381,10 @@
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="B307" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="C307" t="s">
         <v>462</v>
@@ -18813,10 +19419,10 @@
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="B308" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="C308" t="s">
         <v>462</v>
@@ -18851,10 +19457,10 @@
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="B309" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="C309" t="s">
         <v>462</v>
@@ -18889,10 +19495,10 @@
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="B310" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="C310" t="s">
         <v>462</v>
@@ -18927,10 +19533,10 @@
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="B311" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="C311" t="s">
         <v>462</v>
@@ -18965,10 +19571,10 @@
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="B312" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="C312" t="s">
         <v>462</v>
@@ -19003,10 +19609,10 @@
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="B313" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="C313" t="s">
         <v>462</v>
@@ -19041,10 +19647,10 @@
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="B314" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="C314" t="s">
         <v>462</v>
@@ -19079,10 +19685,10 @@
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="B315" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="C315" t="s">
         <v>462</v>
@@ -19117,10 +19723,10 @@
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="B316" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="C316" t="s">
         <v>462</v>
@@ -19155,10 +19761,10 @@
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="B317" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C317" t="s">
         <v>462</v>
@@ -19193,10 +19799,10 @@
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="B318" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="C318" t="s">
         <v>462</v>
@@ -19231,10 +19837,10 @@
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="B319" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="C319" t="s">
         <v>462</v>
@@ -19269,10 +19875,10 @@
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="B320" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="C320" t="s">
         <v>462</v>
@@ -19307,10 +19913,10 @@
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="B321" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="C321" t="s">
         <v>462</v>
@@ -19345,10 +19951,10 @@
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="B322" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="C322" t="s">
         <v>462</v>
@@ -19383,10 +19989,10 @@
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="B323" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="C323" t="s">
         <v>462</v>
@@ -19421,10 +20027,10 @@
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="B324" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="C324" t="s">
         <v>462</v>
@@ -19459,10 +20065,10 @@
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="B325" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="C325" t="s">
         <v>462</v>
@@ -19497,10 +20103,10 @@
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="B326" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="C326" t="s">
         <v>462</v>
@@ -19535,10 +20141,10 @@
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="B327" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="C327" t="s">
         <v>462</v>
@@ -19573,10 +20179,10 @@
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="B328" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="C328" t="s">
         <v>462</v>
@@ -19611,10 +20217,10 @@
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="B329" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="C329" t="s">
         <v>462</v>
@@ -19649,10 +20255,10 @@
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="B330" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="C330" t="s">
         <v>462</v>
@@ -19687,10 +20293,10 @@
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="B331" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="C331" t="s">
         <v>462</v>
@@ -19725,10 +20331,10 @@
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="B332" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="C332" t="s">
         <v>462</v>
@@ -19763,10 +20369,10 @@
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="B333" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="C333" t="s">
         <v>462</v>
@@ -19801,16 +20407,16 @@
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="B334" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="C334" t="s">
         <v>462</v>
       </c>
       <c r="D334" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E334" t="s">
         <v>25</v>
@@ -19839,16 +20445,16 @@
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="B335" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="C335" t="s">
         <v>462</v>
       </c>
       <c r="D335" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E335" t="s">
         <v>25</v>
@@ -19877,16 +20483,16 @@
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="B336" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="C336" t="s">
         <v>462</v>
       </c>
       <c r="D336" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E336" t="s">
         <v>25</v>
@@ -19915,16 +20521,16 @@
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="B337" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="C337" t="s">
         <v>462</v>
       </c>
       <c r="D337" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E337" t="s">
         <v>25</v>
@@ -19953,16 +20559,16 @@
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="B338" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="C338" t="s">
         <v>462</v>
       </c>
       <c r="D338" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E338" t="s">
         <v>25</v>
@@ -19991,16 +20597,16 @@
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
       <c r="B339" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="C339" t="s">
         <v>462</v>
       </c>
       <c r="D339" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E339" t="s">
         <v>25</v>
@@ -20029,16 +20635,16 @@
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="B340" t="s">
-        <v>570</v>
+        <v>553</v>
       </c>
       <c r="C340" t="s">
         <v>462</v>
       </c>
       <c r="D340" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E340" t="s">
         <v>25</v>
@@ -20067,16 +20673,16 @@
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>571</v>
+        <v>554</v>
       </c>
       <c r="B341" t="s">
-        <v>572</v>
+        <v>555</v>
       </c>
       <c r="C341" t="s">
         <v>462</v>
       </c>
       <c r="D341" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E341" t="s">
         <v>25</v>
@@ -20105,10 +20711,10 @@
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>573</v>
+        <v>556</v>
       </c>
       <c r="B342" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="C342" t="s">
         <v>462</v>
@@ -20143,10 +20749,10 @@
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="B343" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="C343" t="s">
         <v>462</v>
@@ -20181,10 +20787,10 @@
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="B344" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="C344" t="s">
         <v>462</v>
@@ -20219,10 +20825,10 @@
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="B345" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="C345" t="s">
         <v>462</v>
@@ -20257,10 +20863,10 @@
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="B346" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="C346" t="s">
         <v>462</v>
@@ -20295,10 +20901,10 @@
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="B347" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="C347" t="s">
         <v>462</v>
@@ -20333,10 +20939,10 @@
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="B348" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="C348" t="s">
         <v>462</v>
@@ -20371,10 +20977,10 @@
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="B349" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="C349" t="s">
         <v>462</v>
@@ -20409,10 +21015,10 @@
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="B350" t="s">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="C350" t="s">
         <v>462</v>
@@ -20447,10 +21053,10 @@
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="B351" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="C351" t="s">
         <v>462</v>
@@ -20485,10 +21091,10 @@
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="B352" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="C352" t="s">
         <v>462</v>
@@ -20523,10 +21129,10 @@
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="B353" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="C353" t="s">
         <v>462</v>
@@ -20561,10 +21167,10 @@
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
       <c r="B354" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="C354" t="s">
         <v>462</v>
@@ -20599,10 +21205,10 @@
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="B355" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="C355" t="s">
         <v>462</v>
@@ -20637,10 +21243,10 @@
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="B356" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="C356" t="s">
         <v>462</v>
@@ -20675,10 +21281,10 @@
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="B357" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="C357" t="s">
         <v>462</v>
@@ -20713,10 +21319,10 @@
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="B358" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="C358" t="s">
         <v>462</v>
@@ -20751,10 +21357,10 @@
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="B359" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="C359" t="s">
         <v>462</v>
@@ -20789,10 +21395,10 @@
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="B360" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="C360" t="s">
         <v>462</v>
@@ -20827,10 +21433,10 @@
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="B361" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="C361" t="s">
         <v>462</v>
@@ -20865,10 +21471,10 @@
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="B362" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="C362" t="s">
         <v>462</v>
@@ -20903,10 +21509,10 @@
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="B363" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="C363" t="s">
         <v>462</v>
@@ -20941,10 +21547,10 @@
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="B364" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="C364" t="s">
         <v>462</v>
@@ -20979,10 +21585,10 @@
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="B365" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="C365" t="s">
         <v>462</v>
@@ -21017,10 +21623,10 @@
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="B366" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="C366" t="s">
         <v>462</v>
@@ -21055,10 +21661,10 @@
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="B367" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="C367" t="s">
         <v>462</v>
@@ -21093,16 +21699,16 @@
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="B368" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="C368" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D368" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E368" t="s">
         <v>25</v>
@@ -21131,16 +21737,16 @@
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="B369" t="s">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="C369" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D369" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E369" t="s">
         <v>25</v>
@@ -21169,16 +21775,16 @@
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="B370" t="s">
-        <v>631</v>
+        <v>614</v>
       </c>
       <c r="C370" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D370" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E370" t="s">
         <v>25</v>
@@ -21207,16 +21813,16 @@
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="B371" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="C371" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D371" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E371" t="s">
         <v>25</v>
@@ -21245,16 +21851,16 @@
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="B372" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="C372" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D372" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E372" t="s">
         <v>25</v>
@@ -21283,16 +21889,16 @@
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="B373" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="C373" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D373" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E373" t="s">
         <v>25</v>
@@ -21321,16 +21927,16 @@
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="B374" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="C374" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D374" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E374" t="s">
         <v>25</v>
@@ -21359,16 +21965,16 @@
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="B375" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="C375" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D375" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E375" t="s">
         <v>25</v>
@@ -21397,16 +22003,16 @@
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="B376" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="C376" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D376" t="s">
-        <v>645</v>
+        <v>25</v>
       </c>
       <c r="E376" t="s">
         <v>25</v>
@@ -21435,16 +22041,16 @@
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>646</v>
+        <v>628</v>
       </c>
       <c r="B377" t="s">
-        <v>647</v>
+        <v>629</v>
       </c>
       <c r="C377" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D377" t="s">
-        <v>645</v>
+        <v>25</v>
       </c>
       <c r="E377" t="s">
         <v>25</v>
@@ -21473,16 +22079,16 @@
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>648</v>
+        <v>630</v>
       </c>
       <c r="B378" t="s">
-        <v>649</v>
+        <v>631</v>
       </c>
       <c r="C378" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D378" t="s">
-        <v>645</v>
+        <v>25</v>
       </c>
       <c r="E378" t="s">
         <v>25</v>
@@ -21511,16 +22117,16 @@
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>650</v>
+        <v>632</v>
       </c>
       <c r="B379" t="s">
-        <v>651</v>
+        <v>633</v>
       </c>
       <c r="C379" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D379" t="s">
-        <v>645</v>
+        <v>25</v>
       </c>
       <c r="E379" t="s">
         <v>25</v>
@@ -21549,16 +22155,16 @@
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="B380" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="C380" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D380" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="E380" t="s">
         <v>25</v>
@@ -21587,16 +22193,16 @@
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="B381" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="C381" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D381" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="E381" t="s">
         <v>25</v>
@@ -21625,16 +22231,16 @@
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="B382" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="C382" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D382" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="E382" t="s">
         <v>25</v>
@@ -21663,16 +22269,16 @@
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="B383" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="C383" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D383" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="E383" t="s">
         <v>25</v>
@@ -21701,16 +22307,16 @@
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>660</v>
+        <v>642</v>
       </c>
       <c r="B384" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="C384" t="s">
         <v>644</v>
       </c>
       <c r="D384" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
       <c r="E384" t="s">
         <v>25</v>
@@ -21739,16 +22345,16 @@
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
       <c r="B385" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="C385" t="s">
         <v>644</v>
       </c>
       <c r="D385" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
       <c r="E385" t="s">
         <v>25</v>
@@ -21777,16 +22383,16 @@
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="B386" t="s">
-        <v>666</v>
+        <v>649</v>
       </c>
       <c r="C386" t="s">
         <v>644</v>
       </c>
       <c r="D386" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
       <c r="E386" t="s">
         <v>25</v>
@@ -21815,16 +22421,16 @@
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="B387" t="s">
-        <v>668</v>
+        <v>651</v>
       </c>
       <c r="C387" t="s">
         <v>644</v>
       </c>
       <c r="D387" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
       <c r="E387" t="s">
         <v>25</v>
@@ -21853,16 +22459,16 @@
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>669</v>
+        <v>652</v>
       </c>
       <c r="B388" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
       <c r="C388" t="s">
         <v>644</v>
       </c>
       <c r="D388" t="s">
-        <v>662</v>
+        <v>138</v>
       </c>
       <c r="E388" t="s">
         <v>25</v>
@@ -21891,16 +22497,16 @@
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="B389" t="s">
-        <v>672</v>
+        <v>655</v>
       </c>
       <c r="C389" t="s">
         <v>644</v>
       </c>
       <c r="D389" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E389" t="s">
         <v>25</v>
@@ -21929,16 +22535,16 @@
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>673</v>
+        <v>656</v>
       </c>
       <c r="B390" t="s">
-        <v>674</v>
+        <v>657</v>
       </c>
       <c r="C390" t="s">
         <v>644</v>
       </c>
       <c r="D390" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E390" t="s">
         <v>25</v>
@@ -21967,16 +22573,16 @@
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
       <c r="B391" t="s">
-        <v>676</v>
+        <v>659</v>
       </c>
       <c r="C391" t="s">
         <v>644</v>
       </c>
       <c r="D391" t="s">
-        <v>677</v>
+        <v>138</v>
       </c>
       <c r="E391" t="s">
         <v>25</v>
@@ -22005,16 +22611,16 @@
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="B392" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
       <c r="C392" t="s">
         <v>644</v>
       </c>
       <c r="D392" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="E392" t="s">
         <v>25</v>
@@ -22043,16 +22649,16 @@
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
       <c r="B393" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="C393" t="s">
         <v>644</v>
       </c>
       <c r="D393" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="E393" t="s">
         <v>25</v>
@@ -22081,16 +22687,16 @@
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>680</v>
+        <v>665</v>
       </c>
       <c r="B394" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="C394" t="s">
         <v>644</v>
       </c>
       <c r="D394" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="E394" t="s">
         <v>25</v>
@@ -22119,16 +22725,16 @@
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="B395" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="C395" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D395" t="s">
-        <v>686</v>
+        <v>662</v>
       </c>
       <c r="E395" t="s">
         <v>25</v>
@@ -22157,16 +22763,16 @@
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="B396" t="s">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="C396" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D396" t="s">
-        <v>686</v>
+        <v>662</v>
       </c>
       <c r="E396" t="s">
         <v>25</v>
@@ -22195,16 +22801,16 @@
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="B397" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="C397" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D397" t="s">
-        <v>686</v>
+        <v>128</v>
       </c>
       <c r="E397" t="s">
         <v>25</v>
@@ -22233,16 +22839,16 @@
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="B398" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="C398" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D398" t="s">
-        <v>686</v>
+        <v>128</v>
       </c>
       <c r="E398" t="s">
         <v>25</v>
@@ -22271,16 +22877,16 @@
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
       <c r="B399" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="C399" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D399" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="E399" t="s">
         <v>25</v>
@@ -22309,16 +22915,16 @@
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="B400" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
       <c r="C400" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D400" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="E400" t="s">
         <v>25</v>
@@ -22347,16 +22953,16 @@
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
       <c r="B401" t="s">
-        <v>698</v>
+        <v>681</v>
       </c>
       <c r="C401" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D401" t="s">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="E401" t="s">
         <v>25</v>
@@ -22385,16 +22991,16 @@
     </row>
     <row r="402" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="B402" t="s">
-        <v>701</v>
+        <v>682</v>
       </c>
       <c r="C402" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D402" t="s">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="E402" t="s">
         <v>25</v>
@@ -22423,16 +23029,16 @@
     </row>
     <row r="403" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>702</v>
+        <v>683</v>
       </c>
       <c r="B403" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="C403" t="s">
         <v>685</v>
       </c>
       <c r="D403" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="E403" t="s">
         <v>25</v>
@@ -22461,16 +23067,16 @@
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>704</v>
+        <v>687</v>
       </c>
       <c r="B404" t="s">
-        <v>705</v>
+        <v>688</v>
       </c>
       <c r="C404" t="s">
         <v>685</v>
       </c>
       <c r="D404" t="s">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="E404" t="s">
         <v>25</v>
@@ -22499,16 +23105,16 @@
     </row>
     <row r="405" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="B405" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="C405" t="s">
         <v>685</v>
       </c>
       <c r="D405" t="s">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="E405" t="s">
         <v>25</v>
@@ -22537,16 +23143,16 @@
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="B406" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="C406" t="s">
         <v>685</v>
       </c>
       <c r="D406" t="s">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="E406" t="s">
         <v>25</v>
@@ -22575,16 +23181,16 @@
     </row>
     <row r="407" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="B407" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="C407" t="s">
         <v>685</v>
       </c>
       <c r="D407" t="s">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="E407" t="s">
         <v>25</v>
@@ -22613,16 +23219,16 @@
     </row>
     <row r="408" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="B408" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="C408" t="s">
         <v>685</v>
       </c>
       <c r="D408" t="s">
-        <v>715</v>
+        <v>686</v>
       </c>
       <c r="E408" t="s">
         <v>25</v>
@@ -22651,16 +23257,16 @@
     </row>
     <row r="409" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>716</v>
+        <v>697</v>
       </c>
       <c r="B409" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="C409" t="s">
         <v>685</v>
       </c>
       <c r="D409" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="E409" t="s">
         <v>25</v>
@@ -22689,16 +23295,16 @@
     </row>
     <row r="410" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>717</v>
+        <v>700</v>
       </c>
       <c r="B410" t="s">
-        <v>718</v>
+        <v>701</v>
       </c>
       <c r="C410" t="s">
         <v>685</v>
       </c>
       <c r="D410" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="E410" t="s">
         <v>25</v>
@@ -22727,16 +23333,16 @@
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>719</v>
+        <v>702</v>
       </c>
       <c r="B411" t="s">
-        <v>720</v>
+        <v>703</v>
       </c>
       <c r="C411" t="s">
         <v>685</v>
       </c>
       <c r="D411" t="s">
-        <v>721</v>
+        <v>699</v>
       </c>
       <c r="E411" t="s">
         <v>25</v>
@@ -22765,16 +23371,16 @@
     </row>
     <row r="412" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="B412" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="C412" t="s">
         <v>685</v>
       </c>
       <c r="D412" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="E412" t="s">
         <v>25</v>
@@ -22803,16 +23409,16 @@
     </row>
     <row r="413" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="B413" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="C413" t="s">
         <v>685</v>
       </c>
       <c r="D413" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="E413" t="s">
         <v>25</v>
@@ -22841,16 +23447,16 @@
     </row>
     <row r="414" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="B414" t="s">
-        <v>727</v>
+        <v>710</v>
       </c>
       <c r="C414" t="s">
         <v>685</v>
       </c>
       <c r="D414" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="E414" t="s">
         <v>25</v>
@@ -22879,16 +23485,16 @@
     </row>
     <row r="415" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="B415" t="s">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="C415" t="s">
         <v>685</v>
       </c>
       <c r="D415" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="E415" t="s">
         <v>25</v>
@@ -22917,16 +23523,16 @@
     </row>
     <row r="416" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>730</v>
+        <v>713</v>
       </c>
       <c r="B416" t="s">
-        <v>731</v>
+        <v>714</v>
       </c>
       <c r="C416" t="s">
         <v>685</v>
       </c>
       <c r="D416" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="E416" t="s">
         <v>25</v>
@@ -22955,16 +23561,16 @@
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>733</v>
+        <v>716</v>
       </c>
       <c r="B417" t="s">
-        <v>734</v>
+        <v>714</v>
       </c>
       <c r="C417" t="s">
         <v>685</v>
       </c>
       <c r="D417" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="E417" t="s">
         <v>25</v>
@@ -22993,16 +23599,16 @@
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="B418" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="C418" t="s">
         <v>685</v>
       </c>
       <c r="D418" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="E418" t="s">
         <v>25</v>
@@ -23031,16 +23637,16 @@
     </row>
     <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="B419" t="s">
-        <v>738</v>
+        <v>720</v>
       </c>
       <c r="C419" t="s">
         <v>685</v>
       </c>
       <c r="D419" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="E419" t="s">
         <v>25</v>
@@ -23069,16 +23675,16 @@
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>739</v>
+        <v>722</v>
       </c>
       <c r="B420" t="s">
-        <v>740</v>
+        <v>723</v>
       </c>
       <c r="C420" t="s">
         <v>685</v>
       </c>
       <c r="D420" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="E420" t="s">
         <v>25</v>
@@ -23107,16 +23713,16 @@
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>741</v>
+        <v>724</v>
       </c>
       <c r="B421" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="C421" t="s">
         <v>685</v>
       </c>
       <c r="D421" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="E421" t="s">
         <v>25</v>
@@ -23145,16 +23751,16 @@
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>743</v>
+        <v>726</v>
       </c>
       <c r="B422" t="s">
-        <v>744</v>
+        <v>727</v>
       </c>
       <c r="C422" t="s">
         <v>685</v>
       </c>
       <c r="D422" t="s">
-        <v>745</v>
+        <v>721</v>
       </c>
       <c r="E422" t="s">
         <v>25</v>
@@ -23183,16 +23789,16 @@
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
       <c r="B423" t="s">
-        <v>747</v>
+        <v>729</v>
       </c>
       <c r="C423" t="s">
         <v>685</v>
       </c>
       <c r="D423" t="s">
-        <v>745</v>
+        <v>721</v>
       </c>
       <c r="E423" t="s">
         <v>25</v>
@@ -23221,16 +23827,16 @@
     </row>
     <row r="424" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="B424" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="C424" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D424" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="E424" t="s">
         <v>25</v>
@@ -23259,16 +23865,16 @@
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="B425" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="C425" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D425" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="E425" t="s">
         <v>25</v>
@@ -23297,16 +23903,16 @@
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="B426" t="s">
-        <v>755</v>
+        <v>736</v>
       </c>
       <c r="C426" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D426" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="E426" t="s">
         <v>25</v>
@@ -23335,16 +23941,16 @@
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>756</v>
+        <v>737</v>
       </c>
       <c r="B427" t="s">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="C427" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D427" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="E427" t="s">
         <v>25</v>
@@ -23373,16 +23979,16 @@
     </row>
     <row r="428" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="B428" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="C428" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D428" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="E428" t="s">
         <v>25</v>
@@ -23411,16 +24017,16 @@
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="B429" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="C429" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D429" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="E429" t="s">
         <v>25</v>
@@ -23449,16 +24055,16 @@
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="B430" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
       <c r="C430" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D430" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="E430" t="s">
         <v>25</v>
@@ -23487,16 +24093,16 @@
     </row>
     <row r="431" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="B431" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="C431" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D431" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="E431" t="s">
         <v>25</v>
@@ -23525,10 +24131,10 @@
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>766</v>
+        <v>748</v>
       </c>
       <c r="B432" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="C432" t="s">
         <v>750</v>
@@ -23563,10 +24169,10 @@
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="B433" t="s">
-        <v>769</v>
+        <v>753</v>
       </c>
       <c r="C433" t="s">
         <v>750</v>
@@ -23601,10 +24207,10 @@
     </row>
     <row r="434" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="B434" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="C434" t="s">
         <v>750</v>
@@ -23639,10 +24245,10 @@
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="B435" t="s">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="C435" t="s">
         <v>750</v>
@@ -23677,10 +24283,10 @@
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>774</v>
+        <v>758</v>
       </c>
       <c r="B436" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="C436" t="s">
         <v>750</v>
@@ -23715,16 +24321,16 @@
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="B437" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="C437" t="s">
         <v>750</v>
       </c>
       <c r="D437" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="E437" t="s">
         <v>25</v>
@@ -23753,16 +24359,16 @@
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>779</v>
+        <v>762</v>
       </c>
       <c r="B438" t="s">
-        <v>780</v>
+        <v>763</v>
       </c>
       <c r="C438" t="s">
         <v>750</v>
       </c>
       <c r="D438" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="E438" t="s">
         <v>25</v>
@@ -23791,16 +24397,16 @@
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>781</v>
+        <v>764</v>
       </c>
       <c r="B439" t="s">
-        <v>782</v>
+        <v>765</v>
       </c>
       <c r="C439" t="s">
         <v>750</v>
       </c>
       <c r="D439" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="E439" t="s">
         <v>25</v>
@@ -23829,16 +24435,16 @@
     </row>
     <row r="440" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>783</v>
+        <v>766</v>
       </c>
       <c r="B440" t="s">
-        <v>784</v>
+        <v>767</v>
       </c>
       <c r="C440" t="s">
         <v>750</v>
       </c>
       <c r="D440" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="E440" t="s">
         <v>25</v>
@@ -23867,16 +24473,16 @@
     </row>
     <row r="441" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>785</v>
+        <v>768</v>
       </c>
       <c r="B441" t="s">
-        <v>786</v>
+        <v>769</v>
       </c>
       <c r="C441" t="s">
         <v>750</v>
       </c>
       <c r="D441" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="E441" t="s">
         <v>25</v>
@@ -23905,16 +24511,16 @@
     </row>
     <row r="442" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>787</v>
+        <v>770</v>
       </c>
       <c r="B442" t="s">
-        <v>788</v>
+        <v>771</v>
       </c>
       <c r="C442" t="s">
         <v>750</v>
       </c>
       <c r="D442" t="s">
-        <v>200</v>
+        <v>751</v>
       </c>
       <c r="E442" t="s">
         <v>25</v>
@@ -23943,16 +24549,16 @@
     </row>
     <row r="443" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>789</v>
+        <v>772</v>
       </c>
       <c r="B443" t="s">
-        <v>790</v>
+        <v>773</v>
       </c>
       <c r="C443" t="s">
         <v>750</v>
       </c>
       <c r="D443" t="s">
-        <v>200</v>
+        <v>751</v>
       </c>
       <c r="E443" t="s">
         <v>25</v>
@@ -23981,16 +24587,16 @@
     </row>
     <row r="444" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>791</v>
+        <v>774</v>
       </c>
       <c r="B444" t="s">
-        <v>792</v>
+        <v>775</v>
       </c>
       <c r="C444" t="s">
         <v>750</v>
       </c>
       <c r="D444" t="s">
-        <v>200</v>
+        <v>751</v>
       </c>
       <c r="E444" t="s">
         <v>25</v>
@@ -24019,16 +24625,16 @@
     </row>
     <row r="445" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>793</v>
+        <v>776</v>
       </c>
       <c r="B445" t="s">
-        <v>794</v>
+        <v>777</v>
       </c>
       <c r="C445" t="s">
         <v>750</v>
       </c>
       <c r="D445" t="s">
-        <v>795</v>
+        <v>778</v>
       </c>
       <c r="E445" t="s">
         <v>25</v>
@@ -24057,16 +24663,16 @@
     </row>
     <row r="446" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="B446" t="s">
-        <v>797</v>
+        <v>780</v>
       </c>
       <c r="C446" t="s">
         <v>750</v>
       </c>
       <c r="D446" t="s">
-        <v>795</v>
+        <v>778</v>
       </c>
       <c r="E446" t="s">
         <v>25</v>
@@ -24095,16 +24701,16 @@
     </row>
     <row r="447" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>798</v>
+        <v>781</v>
       </c>
       <c r="B447" t="s">
-        <v>799</v>
+        <v>782</v>
       </c>
       <c r="C447" t="s">
         <v>750</v>
       </c>
       <c r="D447" t="s">
-        <v>800</v>
+        <v>778</v>
       </c>
       <c r="E447" t="s">
         <v>25</v>
@@ -24133,16 +24739,16 @@
     </row>
     <row r="448" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>801</v>
+        <v>783</v>
       </c>
       <c r="B448" t="s">
-        <v>802</v>
+        <v>784</v>
       </c>
       <c r="C448" t="s">
         <v>750</v>
       </c>
       <c r="D448" t="s">
-        <v>800</v>
+        <v>778</v>
       </c>
       <c r="E448" t="s">
         <v>25</v>
@@ -24171,16 +24777,16 @@
     </row>
     <row r="449" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>803</v>
+        <v>785</v>
       </c>
       <c r="B449" t="s">
-        <v>804</v>
+        <v>786</v>
       </c>
       <c r="C449" t="s">
         <v>750</v>
       </c>
       <c r="D449" t="s">
-        <v>800</v>
+        <v>778</v>
       </c>
       <c r="E449" t="s">
         <v>25</v>
@@ -24209,16 +24815,16 @@
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>805</v>
+        <v>787</v>
       </c>
       <c r="B450" t="s">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="C450" t="s">
         <v>750</v>
       </c>
       <c r="D450" t="s">
-        <v>807</v>
+        <v>200</v>
       </c>
       <c r="E450" t="s">
         <v>25</v>
@@ -24247,16 +24853,16 @@
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>808</v>
+        <v>789</v>
       </c>
       <c r="B451" t="s">
-        <v>809</v>
+        <v>790</v>
       </c>
       <c r="C451" t="s">
         <v>750</v>
       </c>
       <c r="D451" t="s">
-        <v>807</v>
+        <v>200</v>
       </c>
       <c r="E451" t="s">
         <v>25</v>
@@ -24285,16 +24891,16 @@
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="B452" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="C452" t="s">
         <v>750</v>
       </c>
       <c r="D452" t="s">
-        <v>807</v>
+        <v>200</v>
       </c>
       <c r="E452" t="s">
         <v>25</v>
@@ -24323,16 +24929,16 @@
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>812</v>
+        <v>793</v>
       </c>
       <c r="B453" t="s">
-        <v>813</v>
+        <v>794</v>
       </c>
       <c r="C453" t="s">
         <v>750</v>
       </c>
       <c r="D453" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="E453" t="s">
         <v>25</v>
@@ -24361,16 +24967,16 @@
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>814</v>
+        <v>796</v>
       </c>
       <c r="B454" t="s">
-        <v>815</v>
+        <v>797</v>
       </c>
       <c r="C454" t="s">
         <v>750</v>
       </c>
       <c r="D454" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="E454" t="s">
         <v>25</v>
@@ -24399,16 +25005,16 @@
     </row>
     <row r="455" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>816</v>
+        <v>798</v>
       </c>
       <c r="B455" t="s">
-        <v>817</v>
+        <v>799</v>
       </c>
       <c r="C455" t="s">
         <v>750</v>
       </c>
       <c r="D455" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="E455" t="s">
         <v>25</v>
@@ -24437,16 +25043,16 @@
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>818</v>
+        <v>801</v>
       </c>
       <c r="B456" t="s">
-        <v>819</v>
+        <v>802</v>
       </c>
       <c r="C456" t="s">
         <v>750</v>
       </c>
       <c r="D456" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="E456" t="s">
         <v>25</v>
@@ -24475,16 +25081,16 @@
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>820</v>
+        <v>803</v>
       </c>
       <c r="B457" t="s">
-        <v>821</v>
+        <v>804</v>
       </c>
       <c r="C457" t="s">
         <v>750</v>
       </c>
       <c r="D457" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="E457" t="s">
         <v>25</v>
@@ -24513,10 +25119,10 @@
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
       <c r="B458" t="s">
-        <v>823</v>
+        <v>806</v>
       </c>
       <c r="C458" t="s">
         <v>750</v>
@@ -24551,10 +25157,10 @@
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>824</v>
+        <v>808</v>
       </c>
       <c r="B459" t="s">
-        <v>825</v>
+        <v>809</v>
       </c>
       <c r="C459" t="s">
         <v>750</v>
@@ -24589,10 +25195,10 @@
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="B460" t="s">
-        <v>827</v>
+        <v>811</v>
       </c>
       <c r="C460" t="s">
         <v>750</v>
@@ -24627,10 +25233,10 @@
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>828</v>
+        <v>812</v>
       </c>
       <c r="B461" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
       <c r="C461" t="s">
         <v>750</v>
@@ -24665,16 +25271,16 @@
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="B462" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="C462" t="s">
         <v>750</v>
       </c>
       <c r="D462" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="E462" t="s">
         <v>25</v>
@@ -24703,16 +25309,16 @@
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>833</v>
+        <v>816</v>
       </c>
       <c r="B463" t="s">
-        <v>834</v>
+        <v>817</v>
       </c>
       <c r="C463" t="s">
         <v>750</v>
       </c>
       <c r="D463" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="E463" t="s">
         <v>25</v>
@@ -24741,16 +25347,16 @@
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>835</v>
+        <v>818</v>
       </c>
       <c r="B464" t="s">
-        <v>836</v>
+        <v>819</v>
       </c>
       <c r="C464" t="s">
         <v>750</v>
       </c>
       <c r="D464" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="E464" t="s">
         <v>25</v>
@@ -24779,16 +25385,16 @@
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>837</v>
+        <v>820</v>
       </c>
       <c r="B465" t="s">
-        <v>838</v>
+        <v>821</v>
       </c>
       <c r="C465" t="s">
         <v>750</v>
       </c>
       <c r="D465" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="E465" t="s">
         <v>25</v>
@@ -24817,16 +25423,16 @@
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
       <c r="B466" t="s">
-        <v>840</v>
+        <v>823</v>
       </c>
       <c r="C466" t="s">
         <v>750</v>
       </c>
       <c r="D466" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="E466" t="s">
         <v>25</v>
@@ -24855,16 +25461,16 @@
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>841</v>
+        <v>824</v>
       </c>
       <c r="B467" t="s">
-        <v>842</v>
+        <v>825</v>
       </c>
       <c r="C467" t="s">
         <v>750</v>
       </c>
       <c r="D467" t="s">
-        <v>843</v>
+        <v>807</v>
       </c>
       <c r="E467" t="s">
         <v>25</v>
@@ -24893,16 +25499,16 @@
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>844</v>
+        <v>826</v>
       </c>
       <c r="B468" t="s">
-        <v>845</v>
+        <v>827</v>
       </c>
       <c r="C468" t="s">
         <v>750</v>
       </c>
       <c r="D468" t="s">
-        <v>843</v>
+        <v>807</v>
       </c>
       <c r="E468" t="s">
         <v>25</v>
@@ -24931,16 +25537,16 @@
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>846</v>
+        <v>828</v>
       </c>
       <c r="B469" t="s">
-        <v>847</v>
+        <v>829</v>
       </c>
       <c r="C469" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D469" t="s">
-        <v>849</v>
+        <v>807</v>
       </c>
       <c r="E469" t="s">
         <v>25</v>
@@ -24969,16 +25575,16 @@
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="B470" t="s">
-        <v>851</v>
+        <v>831</v>
       </c>
       <c r="C470" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D470" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="E470" t="s">
         <v>25</v>
@@ -25007,16 +25613,16 @@
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>852</v>
+        <v>833</v>
       </c>
       <c r="B471" t="s">
-        <v>853</v>
+        <v>834</v>
       </c>
       <c r="C471" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D471" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="E471" t="s">
         <v>25</v>
@@ -25045,16 +25651,16 @@
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="B472" t="s">
-        <v>855</v>
+        <v>836</v>
       </c>
       <c r="C472" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D472" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="E472" t="s">
         <v>25</v>
@@ -25083,16 +25689,16 @@
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>856</v>
+        <v>837</v>
       </c>
       <c r="B473" t="s">
-        <v>857</v>
+        <v>838</v>
       </c>
       <c r="C473" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D473" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="E473" t="s">
         <v>25</v>
@@ -25121,16 +25727,16 @@
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="B474" t="s">
-        <v>859</v>
+        <v>840</v>
       </c>
       <c r="C474" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D474" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="E474" t="s">
         <v>25</v>
@@ -25159,16 +25765,16 @@
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>860</v>
+        <v>841</v>
       </c>
       <c r="B475" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="C475" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D475" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="E475" t="s">
         <v>25</v>
@@ -25197,16 +25803,16 @@
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>863</v>
+        <v>844</v>
       </c>
       <c r="B476" t="s">
-        <v>864</v>
+        <v>845</v>
       </c>
       <c r="C476" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D476" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="E476" t="s">
         <v>25</v>
@@ -25235,16 +25841,16 @@
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>865</v>
+        <v>846</v>
       </c>
       <c r="B477" t="s">
-        <v>866</v>
+        <v>847</v>
       </c>
       <c r="C477" t="s">
         <v>848</v>
       </c>
       <c r="D477" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="E477" t="s">
         <v>25</v>
@@ -25273,16 +25879,16 @@
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>867</v>
+        <v>850</v>
       </c>
       <c r="B478" t="s">
-        <v>868</v>
+        <v>851</v>
       </c>
       <c r="C478" t="s">
         <v>848</v>
       </c>
       <c r="D478" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="E478" t="s">
         <v>25</v>
@@ -25311,16 +25917,16 @@
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>869</v>
+        <v>852</v>
       </c>
       <c r="B479" t="s">
-        <v>870</v>
+        <v>853</v>
       </c>
       <c r="C479" t="s">
         <v>848</v>
       </c>
       <c r="D479" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="E479" t="s">
         <v>25</v>
@@ -25349,16 +25955,16 @@
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>871</v>
+        <v>854</v>
       </c>
       <c r="B480" t="s">
-        <v>872</v>
+        <v>855</v>
       </c>
       <c r="C480" t="s">
         <v>848</v>
       </c>
       <c r="D480" t="s">
-        <v>873</v>
+        <v>849</v>
       </c>
       <c r="E480" t="s">
         <v>25</v>
@@ -25387,16 +25993,16 @@
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>874</v>
+        <v>856</v>
       </c>
       <c r="B481" t="s">
-        <v>875</v>
+        <v>857</v>
       </c>
       <c r="C481" t="s">
         <v>848</v>
       </c>
       <c r="D481" t="s">
-        <v>873</v>
+        <v>849</v>
       </c>
       <c r="E481" t="s">
         <v>25</v>
@@ -25425,16 +26031,16 @@
     </row>
     <row r="482" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>876</v>
+        <v>858</v>
       </c>
       <c r="B482" t="s">
-        <v>877</v>
+        <v>859</v>
       </c>
       <c r="C482" t="s">
         <v>848</v>
       </c>
       <c r="D482" t="s">
-        <v>873</v>
+        <v>849</v>
       </c>
       <c r="E482" t="s">
         <v>25</v>
@@ -25463,16 +26069,16 @@
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>878</v>
+        <v>860</v>
       </c>
       <c r="B483" t="s">
-        <v>879</v>
+        <v>861</v>
       </c>
       <c r="C483" t="s">
         <v>848</v>
       </c>
       <c r="D483" t="s">
-        <v>880</v>
+        <v>862</v>
       </c>
       <c r="E483" t="s">
         <v>25</v>
@@ -25501,16 +26107,16 @@
     </row>
     <row r="484" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>881</v>
+        <v>863</v>
       </c>
       <c r="B484" t="s">
-        <v>882</v>
+        <v>864</v>
       </c>
       <c r="C484" t="s">
         <v>848</v>
       </c>
       <c r="D484" t="s">
-        <v>880</v>
+        <v>862</v>
       </c>
       <c r="E484" t="s">
         <v>25</v>
@@ -25539,16 +26145,16 @@
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>883</v>
+        <v>865</v>
       </c>
       <c r="B485" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="C485" t="s">
         <v>848</v>
       </c>
       <c r="D485" t="s">
-        <v>885</v>
+        <v>862</v>
       </c>
       <c r="E485" t="s">
         <v>25</v>
@@ -25577,16 +26183,16 @@
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>886</v>
+        <v>867</v>
       </c>
       <c r="B486" t="s">
-        <v>887</v>
+        <v>868</v>
       </c>
       <c r="C486" t="s">
         <v>848</v>
       </c>
       <c r="D486" t="s">
-        <v>885</v>
+        <v>862</v>
       </c>
       <c r="E486" t="s">
         <v>25</v>
@@ -25615,16 +26221,16 @@
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>888</v>
+        <v>869</v>
       </c>
       <c r="B487" t="s">
-        <v>889</v>
+        <v>870</v>
       </c>
       <c r="C487" t="s">
         <v>848</v>
       </c>
       <c r="D487" t="s">
-        <v>885</v>
+        <v>862</v>
       </c>
       <c r="E487" t="s">
         <v>25</v>
@@ -25653,16 +26259,16 @@
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>890</v>
+        <v>871</v>
       </c>
       <c r="B488" t="s">
-        <v>891</v>
+        <v>872</v>
       </c>
       <c r="C488" t="s">
         <v>848</v>
       </c>
       <c r="D488" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="E488" t="s">
         <v>25</v>
@@ -25691,16 +26297,16 @@
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>892</v>
+        <v>874</v>
       </c>
       <c r="B489" t="s">
-        <v>893</v>
+        <v>875</v>
       </c>
       <c r="C489" t="s">
         <v>848</v>
       </c>
       <c r="D489" t="s">
-        <v>894</v>
+        <v>873</v>
       </c>
       <c r="E489" t="s">
         <v>25</v>
@@ -25729,16 +26335,16 @@
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>895</v>
+        <v>876</v>
       </c>
       <c r="B490" t="s">
-        <v>896</v>
+        <v>877</v>
       </c>
       <c r="C490" t="s">
         <v>848</v>
       </c>
       <c r="D490" t="s">
-        <v>894</v>
+        <v>873</v>
       </c>
       <c r="E490" t="s">
         <v>25</v>
@@ -25767,16 +26373,16 @@
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>897</v>
+        <v>878</v>
       </c>
       <c r="B491" t="s">
-        <v>898</v>
+        <v>879</v>
       </c>
       <c r="C491" t="s">
         <v>848</v>
       </c>
       <c r="D491" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
       <c r="E491" t="s">
         <v>25</v>
@@ -25805,16 +26411,16 @@
     </row>
     <row r="492" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>899</v>
+        <v>881</v>
       </c>
       <c r="B492" t="s">
-        <v>900</v>
+        <v>882</v>
       </c>
       <c r="C492" t="s">
         <v>848</v>
       </c>
       <c r="D492" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
       <c r="E492" t="s">
         <v>25</v>
@@ -25843,16 +26449,16 @@
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>901</v>
+        <v>883</v>
       </c>
       <c r="B493" t="s">
-        <v>902</v>
+        <v>884</v>
       </c>
       <c r="C493" t="s">
         <v>848</v>
       </c>
       <c r="D493" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="E493" t="s">
         <v>25</v>
@@ -25881,16 +26487,16 @@
     </row>
     <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>903</v>
+        <v>886</v>
       </c>
       <c r="B494" t="s">
-        <v>904</v>
+        <v>887</v>
       </c>
       <c r="C494" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D494" t="s">
-        <v>25</v>
+        <v>885</v>
       </c>
       <c r="E494" t="s">
         <v>25</v>
@@ -25919,16 +26525,16 @@
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>906</v>
+        <v>888</v>
       </c>
       <c r="B495" t="s">
-        <v>907</v>
+        <v>889</v>
       </c>
       <c r="C495" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D495" t="s">
-        <v>25</v>
+        <v>885</v>
       </c>
       <c r="E495" t="s">
         <v>25</v>
@@ -25957,16 +26563,16 @@
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>908</v>
+        <v>890</v>
       </c>
       <c r="B496" t="s">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="C496" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D496" t="s">
-        <v>25</v>
+        <v>885</v>
       </c>
       <c r="E496" t="s">
         <v>25</v>
@@ -25995,16 +26601,16 @@
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="B497" t="s">
-        <v>911</v>
+        <v>893</v>
       </c>
       <c r="C497" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D497" t="s">
-        <v>25</v>
+        <v>894</v>
       </c>
       <c r="E497" t="s">
         <v>25</v>
@@ -26033,16 +26639,16 @@
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>912</v>
+        <v>895</v>
       </c>
       <c r="B498" t="s">
-        <v>913</v>
+        <v>896</v>
       </c>
       <c r="C498" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D498" t="s">
-        <v>25</v>
+        <v>894</v>
       </c>
       <c r="E498" t="s">
         <v>25</v>
@@ -26071,16 +26677,16 @@
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>914</v>
+        <v>897</v>
       </c>
       <c r="B499" t="s">
-        <v>915</v>
+        <v>898</v>
       </c>
       <c r="C499" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D499" t="s">
-        <v>25</v>
+        <v>894</v>
       </c>
       <c r="E499" t="s">
         <v>25</v>
@@ -26109,16 +26715,16 @@
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>916</v>
+        <v>899</v>
       </c>
       <c r="B500" t="s">
-        <v>917</v>
+        <v>900</v>
       </c>
       <c r="C500" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D500" t="s">
-        <v>25</v>
+        <v>894</v>
       </c>
       <c r="E500" t="s">
         <v>25</v>
@@ -26147,16 +26753,16 @@
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>918</v>
+        <v>901</v>
       </c>
       <c r="B501" t="s">
-        <v>919</v>
+        <v>902</v>
       </c>
       <c r="C501" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D501" t="s">
-        <v>25</v>
+        <v>894</v>
       </c>
       <c r="E501" t="s">
         <v>25</v>
@@ -26185,10 +26791,10 @@
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>920</v>
+        <v>903</v>
       </c>
       <c r="B502" t="s">
-        <v>921</v>
+        <v>904</v>
       </c>
       <c r="C502" t="s">
         <v>905</v>
@@ -26223,10 +26829,10 @@
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>922</v>
+        <v>906</v>
       </c>
       <c r="B503" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
       <c r="C503" t="s">
         <v>905</v>
@@ -26261,10 +26867,10 @@
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>924</v>
+        <v>908</v>
       </c>
       <c r="B504" t="s">
-        <v>925</v>
+        <v>909</v>
       </c>
       <c r="C504" t="s">
         <v>905</v>
@@ -26299,10 +26905,10 @@
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>926</v>
+        <v>910</v>
       </c>
       <c r="B505" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
       <c r="C505" t="s">
         <v>905</v>
@@ -26337,10 +26943,10 @@
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>928</v>
+        <v>912</v>
       </c>
       <c r="B506" t="s">
-        <v>929</v>
+        <v>913</v>
       </c>
       <c r="C506" t="s">
         <v>905</v>
@@ -26375,10 +26981,10 @@
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>930</v>
+        <v>914</v>
       </c>
       <c r="B507" t="s">
-        <v>931</v>
+        <v>915</v>
       </c>
       <c r="C507" t="s">
         <v>905</v>
@@ -26413,10 +27019,10 @@
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>932</v>
+        <v>916</v>
       </c>
       <c r="B508" t="s">
-        <v>933</v>
+        <v>917</v>
       </c>
       <c r="C508" t="s">
         <v>905</v>
@@ -26451,16 +27057,16 @@
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>934</v>
+        <v>918</v>
       </c>
       <c r="B509" t="s">
-        <v>935</v>
+        <v>919</v>
       </c>
       <c r="C509" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D509" t="s">
-        <v>937</v>
+        <v>25</v>
       </c>
       <c r="E509" t="s">
         <v>25</v>
@@ -26489,16 +27095,16 @@
     </row>
     <row r="510" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>938</v>
+        <v>920</v>
       </c>
       <c r="B510" t="s">
-        <v>939</v>
+        <v>921</v>
       </c>
       <c r="C510" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D510" t="s">
-        <v>937</v>
+        <v>25</v>
       </c>
       <c r="E510" t="s">
         <v>25</v>
@@ -26527,16 +27133,16 @@
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>940</v>
+        <v>922</v>
       </c>
       <c r="B511" t="s">
-        <v>941</v>
+        <v>923</v>
       </c>
       <c r="C511" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D511" t="s">
-        <v>937</v>
+        <v>25</v>
       </c>
       <c r="E511" t="s">
         <v>25</v>
@@ -26565,16 +27171,16 @@
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>942</v>
+        <v>924</v>
       </c>
       <c r="B512" t="s">
-        <v>943</v>
+        <v>925</v>
       </c>
       <c r="C512" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D512" t="s">
-        <v>937</v>
+        <v>25</v>
       </c>
       <c r="E512" t="s">
         <v>25</v>
@@ -26603,16 +27209,16 @@
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>944</v>
+        <v>926</v>
       </c>
       <c r="B513" t="s">
-        <v>945</v>
+        <v>927</v>
       </c>
       <c r="C513" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D513" t="s">
-        <v>946</v>
+        <v>25</v>
       </c>
       <c r="E513" t="s">
         <v>25</v>
@@ -26641,16 +27247,16 @@
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>947</v>
+        <v>928</v>
       </c>
       <c r="B514" t="s">
-        <v>948</v>
+        <v>929</v>
       </c>
       <c r="C514" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D514" t="s">
-        <v>946</v>
+        <v>25</v>
       </c>
       <c r="E514" t="s">
         <v>25</v>
@@ -26679,16 +27285,16 @@
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="B515" t="s">
-        <v>950</v>
+        <v>931</v>
       </c>
       <c r="C515" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D515" t="s">
-        <v>946</v>
+        <v>25</v>
       </c>
       <c r="E515" t="s">
         <v>25</v>
@@ -26717,16 +27323,16 @@
     </row>
     <row r="516" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>951</v>
+        <v>932</v>
       </c>
       <c r="B516" t="s">
-        <v>952</v>
+        <v>933</v>
       </c>
       <c r="C516" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D516" t="s">
-        <v>946</v>
+        <v>25</v>
       </c>
       <c r="E516" t="s">
         <v>25</v>
@@ -26755,16 +27361,16 @@
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>953</v>
+        <v>934</v>
       </c>
       <c r="B517" t="s">
-        <v>954</v>
+        <v>935</v>
       </c>
       <c r="C517" t="s">
         <v>936</v>
       </c>
       <c r="D517" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="E517" t="s">
         <v>25</v>
@@ -26793,16 +27399,16 @@
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>955</v>
+        <v>938</v>
       </c>
       <c r="B518" t="s">
-        <v>956</v>
+        <v>939</v>
       </c>
       <c r="C518" t="s">
         <v>936</v>
       </c>
       <c r="D518" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="E518" t="s">
         <v>25</v>
@@ -26831,16 +27437,16 @@
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>957</v>
+        <v>940</v>
       </c>
       <c r="B519" t="s">
-        <v>958</v>
+        <v>941</v>
       </c>
       <c r="C519" t="s">
         <v>936</v>
       </c>
       <c r="D519" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="E519" t="s">
         <v>25</v>
@@ -26869,16 +27475,16 @@
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>959</v>
+        <v>942</v>
       </c>
       <c r="B520" t="s">
-        <v>960</v>
+        <v>943</v>
       </c>
       <c r="C520" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D520" t="s">
-        <v>962</v>
+        <v>937</v>
       </c>
       <c r="E520" t="s">
         <v>25</v>
@@ -26907,16 +27513,16 @@
     </row>
     <row r="521" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>963</v>
+        <v>944</v>
       </c>
       <c r="B521" t="s">
-        <v>964</v>
+        <v>945</v>
       </c>
       <c r="C521" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D521" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E521" t="s">
         <v>25</v>
@@ -26945,16 +27551,16 @@
     </row>
     <row r="522" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B522" t="s">
-        <v>966</v>
+        <v>948</v>
       </c>
       <c r="C522" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D522" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E522" t="s">
         <v>25</v>
@@ -26983,16 +27589,16 @@
     </row>
     <row r="523" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="B523" t="s">
-        <v>968</v>
+        <v>950</v>
       </c>
       <c r="C523" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D523" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E523" t="s">
         <v>25</v>
@@ -27021,16 +27627,16 @@
     </row>
     <row r="524" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>969</v>
+        <v>951</v>
       </c>
       <c r="B524" t="s">
-        <v>970</v>
+        <v>952</v>
       </c>
       <c r="C524" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D524" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E524" t="s">
         <v>25</v>
@@ -27059,16 +27665,16 @@
     </row>
     <row r="525" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>971</v>
+        <v>953</v>
       </c>
       <c r="B525" t="s">
-        <v>972</v>
+        <v>954</v>
       </c>
       <c r="C525" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D525" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E525" t="s">
         <v>25</v>
@@ -27097,16 +27703,16 @@
     </row>
     <row r="526" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>973</v>
+        <v>955</v>
       </c>
       <c r="B526" t="s">
-        <v>974</v>
+        <v>956</v>
       </c>
       <c r="C526" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D526" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E526" t="s">
         <v>25</v>
@@ -27135,16 +27741,16 @@
     </row>
     <row r="527" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>975</v>
+        <v>957</v>
       </c>
       <c r="B527" t="s">
-        <v>976</v>
+        <v>958</v>
       </c>
       <c r="C527" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D527" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E527" t="s">
         <v>25</v>
@@ -27173,16 +27779,16 @@
     </row>
     <row r="528" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>977</v>
+        <v>959</v>
       </c>
       <c r="B528" t="s">
-        <v>978</v>
+        <v>960</v>
       </c>
       <c r="C528" t="s">
         <v>961</v>
       </c>
       <c r="D528" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E528" t="s">
         <v>25</v>
@@ -27211,16 +27817,16 @@
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>980</v>
+        <v>963</v>
       </c>
       <c r="B529" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
       <c r="C529" t="s">
         <v>961</v>
       </c>
       <c r="D529" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E529" t="s">
         <v>25</v>
@@ -27249,16 +27855,16 @@
     </row>
     <row r="530" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>982</v>
+        <v>965</v>
       </c>
       <c r="B530" t="s">
-        <v>983</v>
+        <v>966</v>
       </c>
       <c r="C530" t="s">
         <v>961</v>
       </c>
       <c r="D530" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E530" t="s">
         <v>25</v>
@@ -27287,16 +27893,16 @@
     </row>
     <row r="531" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>984</v>
+        <v>967</v>
       </c>
       <c r="B531" t="s">
-        <v>985</v>
+        <v>968</v>
       </c>
       <c r="C531" t="s">
         <v>961</v>
       </c>
       <c r="D531" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E531" t="s">
         <v>25</v>
@@ -27325,16 +27931,16 @@
     </row>
     <row r="532" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>986</v>
+        <v>969</v>
       </c>
       <c r="B532" t="s">
-        <v>987</v>
+        <v>970</v>
       </c>
       <c r="C532" t="s">
         <v>961</v>
       </c>
       <c r="D532" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E532" t="s">
         <v>25</v>
@@ -27363,16 +27969,16 @@
     </row>
     <row r="533" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>988</v>
+        <v>971</v>
       </c>
       <c r="B533" t="s">
-        <v>989</v>
+        <v>972</v>
       </c>
       <c r="C533" t="s">
         <v>961</v>
       </c>
       <c r="D533" t="s">
-        <v>990</v>
+        <v>962</v>
       </c>
       <c r="E533" t="s">
         <v>25</v>
@@ -27401,16 +28007,16 @@
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>991</v>
+        <v>973</v>
       </c>
       <c r="B534" t="s">
-        <v>992</v>
+        <v>974</v>
       </c>
       <c r="C534" t="s">
         <v>961</v>
       </c>
       <c r="D534" t="s">
-        <v>990</v>
+        <v>962</v>
       </c>
       <c r="E534" t="s">
         <v>25</v>
@@ -27439,16 +28045,16 @@
     </row>
     <row r="535" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>993</v>
+        <v>975</v>
       </c>
       <c r="B535" t="s">
-        <v>994</v>
+        <v>976</v>
       </c>
       <c r="C535" t="s">
         <v>961</v>
       </c>
       <c r="D535" t="s">
-        <v>995</v>
+        <v>962</v>
       </c>
       <c r="E535" t="s">
         <v>25</v>
@@ -27477,16 +28083,16 @@
     </row>
     <row r="536" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>996</v>
+        <v>977</v>
       </c>
       <c r="B536" t="s">
-        <v>997</v>
+        <v>978</v>
       </c>
       <c r="C536" t="s">
         <v>961</v>
       </c>
       <c r="D536" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="E536" t="s">
         <v>25</v>
@@ -27515,16 +28121,16 @@
     </row>
     <row r="537" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>998</v>
+        <v>980</v>
       </c>
       <c r="B537" t="s">
-        <v>999</v>
+        <v>981</v>
       </c>
       <c r="C537" t="s">
         <v>961</v>
       </c>
       <c r="D537" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="E537" t="s">
         <v>25</v>
@@ -27553,16 +28159,16 @@
     </row>
     <row r="538" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1000</v>
+        <v>982</v>
       </c>
       <c r="B538" t="s">
-        <v>1001</v>
+        <v>983</v>
       </c>
       <c r="C538" t="s">
         <v>961</v>
       </c>
       <c r="D538" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="E538" t="s">
         <v>25</v>
@@ -27591,16 +28197,16 @@
     </row>
     <row r="539" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1002</v>
+        <v>984</v>
       </c>
       <c r="B539" t="s">
-        <v>1003</v>
+        <v>985</v>
       </c>
       <c r="C539" t="s">
         <v>961</v>
       </c>
       <c r="D539" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="E539" t="s">
         <v>25</v>
@@ -27629,16 +28235,16 @@
     </row>
     <row r="540" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1004</v>
+        <v>986</v>
       </c>
       <c r="B540" t="s">
-        <v>1005</v>
+        <v>987</v>
       </c>
       <c r="C540" t="s">
         <v>961</v>
       </c>
       <c r="D540" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="E540" t="s">
         <v>25</v>
@@ -27667,16 +28273,16 @@
     </row>
     <row r="541" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1006</v>
+        <v>988</v>
       </c>
       <c r="B541" t="s">
-        <v>1007</v>
+        <v>989</v>
       </c>
       <c r="C541" t="s">
         <v>961</v>
       </c>
       <c r="D541" t="s">
-        <v>1008</v>
+        <v>990</v>
       </c>
       <c r="E541" t="s">
         <v>25</v>
@@ -27705,16 +28311,16 @@
     </row>
     <row r="542" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1009</v>
+        <v>991</v>
       </c>
       <c r="B542" t="s">
-        <v>1010</v>
+        <v>992</v>
       </c>
       <c r="C542" t="s">
         <v>961</v>
       </c>
       <c r="D542" t="s">
-        <v>1008</v>
+        <v>990</v>
       </c>
       <c r="E542" t="s">
         <v>25</v>
@@ -27743,16 +28349,16 @@
     </row>
     <row r="543" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>1011</v>
+        <v>993</v>
       </c>
       <c r="B543" t="s">
-        <v>1012</v>
+        <v>994</v>
       </c>
       <c r="C543" t="s">
         <v>961</v>
       </c>
       <c r="D543" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="E543" t="s">
         <v>25</v>
@@ -27781,16 +28387,16 @@
     </row>
     <row r="544" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1013</v>
+        <v>996</v>
       </c>
       <c r="B544" t="s">
-        <v>1014</v>
+        <v>997</v>
       </c>
       <c r="C544" t="s">
         <v>961</v>
       </c>
       <c r="D544" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="E544" t="s">
         <v>25</v>
@@ -27819,16 +28425,16 @@
     </row>
     <row r="545" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1015</v>
+        <v>998</v>
       </c>
       <c r="B545" t="s">
-        <v>1016</v>
+        <v>999</v>
       </c>
       <c r="C545" t="s">
         <v>961</v>
       </c>
       <c r="D545" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="E545" t="s">
         <v>25</v>
@@ -27857,16 +28463,16 @@
     </row>
     <row r="546" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1018</v>
+        <v>1000</v>
       </c>
       <c r="B546" t="s">
-        <v>1019</v>
+        <v>1001</v>
       </c>
       <c r="C546" t="s">
         <v>961</v>
       </c>
       <c r="D546" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="E546" t="s">
         <v>25</v>
@@ -27895,16 +28501,16 @@
     </row>
     <row r="547" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1020</v>
+        <v>1002</v>
       </c>
       <c r="B547" t="s">
-        <v>1021</v>
+        <v>1003</v>
       </c>
       <c r="C547" t="s">
         <v>961</v>
       </c>
       <c r="D547" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="E547" t="s">
         <v>25</v>
@@ -27933,16 +28539,16 @@
     </row>
     <row r="548" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1022</v>
+        <v>1004</v>
       </c>
       <c r="B548" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="C548" t="s">
         <v>961</v>
       </c>
       <c r="D548" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="E548" t="s">
         <v>25</v>
@@ -27971,16 +28577,16 @@
     </row>
     <row r="549" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1024</v>
+        <v>1006</v>
       </c>
       <c r="B549" t="s">
-        <v>1025</v>
+        <v>1007</v>
       </c>
       <c r="C549" t="s">
         <v>961</v>
       </c>
       <c r="D549" t="s">
-        <v>1026</v>
+        <v>1008</v>
       </c>
       <c r="E549" t="s">
         <v>25</v>
@@ -28009,16 +28615,16 @@
     </row>
     <row r="550" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1027</v>
+        <v>1009</v>
       </c>
       <c r="B550" t="s">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="C550" t="s">
         <v>961</v>
       </c>
       <c r="D550" t="s">
-        <v>1026</v>
+        <v>1008</v>
       </c>
       <c r="E550" t="s">
         <v>25</v>
@@ -28047,16 +28653,16 @@
     </row>
     <row r="551" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1029</v>
+        <v>1011</v>
       </c>
       <c r="B551" t="s">
-        <v>1030</v>
+        <v>1012</v>
       </c>
       <c r="C551" t="s">
         <v>961</v>
       </c>
       <c r="D551" t="s">
-        <v>1026</v>
+        <v>1008</v>
       </c>
       <c r="E551" t="s">
         <v>25</v>
@@ -28085,16 +28691,16 @@
     </row>
     <row r="552" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="B552" t="s">
-        <v>1032</v>
+        <v>1014</v>
       </c>
       <c r="C552" t="s">
         <v>961</v>
       </c>
       <c r="D552" t="s">
-        <v>1026</v>
+        <v>1008</v>
       </c>
       <c r="E552" t="s">
         <v>25</v>
@@ -28123,16 +28729,16 @@
     </row>
     <row r="553" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1033</v>
+        <v>1015</v>
       </c>
       <c r="B553" t="s">
-        <v>1034</v>
+        <v>1016</v>
       </c>
       <c r="C553" t="s">
         <v>961</v>
       </c>
       <c r="D553" t="s">
-        <v>1035</v>
+        <v>1017</v>
       </c>
       <c r="E553" t="s">
         <v>25</v>
@@ -28161,16 +28767,16 @@
     </row>
     <row r="554" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1036</v>
+        <v>1018</v>
       </c>
       <c r="B554" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="C554" t="s">
         <v>961</v>
       </c>
       <c r="D554" t="s">
-        <v>1035</v>
+        <v>1017</v>
       </c>
       <c r="E554" t="s">
         <v>25</v>
@@ -28199,16 +28805,16 @@
     </row>
     <row r="555" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="B555" t="s">
-        <v>1039</v>
+        <v>1021</v>
       </c>
       <c r="C555" t="s">
         <v>961</v>
       </c>
       <c r="D555" t="s">
-        <v>1035</v>
+        <v>1017</v>
       </c>
       <c r="E555" t="s">
         <v>25</v>
@@ -28237,16 +28843,16 @@
     </row>
     <row r="556" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>1040</v>
+        <v>1022</v>
       </c>
       <c r="B556" t="s">
-        <v>1041</v>
+        <v>1023</v>
       </c>
       <c r="C556" t="s">
         <v>961</v>
       </c>
       <c r="D556" t="s">
-        <v>1035</v>
+        <v>1017</v>
       </c>
       <c r="E556" t="s">
         <v>25</v>
@@ -28275,16 +28881,16 @@
     </row>
     <row r="557" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
       <c r="B557" t="s">
-        <v>1043</v>
+        <v>1025</v>
       </c>
       <c r="C557" t="s">
         <v>961</v>
       </c>
       <c r="D557" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="E557" t="s">
         <v>25</v>
@@ -28313,16 +28919,16 @@
     </row>
     <row r="558" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>1045</v>
+        <v>1027</v>
       </c>
       <c r="B558" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="C558" t="s">
         <v>961</v>
       </c>
       <c r="D558" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="E558" t="s">
         <v>25</v>
@@ -28351,16 +28957,16 @@
     </row>
     <row r="559" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>1047</v>
+        <v>1029</v>
       </c>
       <c r="B559" t="s">
-        <v>1048</v>
+        <v>1030</v>
       </c>
       <c r="C559" t="s">
         <v>961</v>
       </c>
       <c r="D559" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="E559" t="s">
         <v>25</v>
@@ -28389,16 +28995,16 @@
     </row>
     <row r="560" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1049</v>
+        <v>1031</v>
       </c>
       <c r="B560" t="s">
-        <v>1050</v>
+        <v>1032</v>
       </c>
       <c r="C560" t="s">
         <v>961</v>
       </c>
       <c r="D560" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="E560" t="s">
         <v>25</v>
@@ -28427,16 +29033,16 @@
     </row>
     <row r="561" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1051</v>
+        <v>1033</v>
       </c>
       <c r="B561" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="C561" t="s">
         <v>961</v>
       </c>
       <c r="D561" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="E561" t="s">
         <v>25</v>
@@ -28465,39 +29071,343 @@
     </row>
     <row r="562" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>1053</v>
+        <v>1036</v>
       </c>
       <c r="B562" t="s">
-        <v>1054</v>
+        <v>1037</v>
       </c>
       <c r="C562" t="s">
         <v>961</v>
       </c>
       <c r="D562" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E562" t="s">
+        <v>25</v>
+      </c>
+      <c r="F562" t="s">
+        <v>25</v>
+      </c>
+      <c r="G562" t="s">
+        <v>25</v>
+      </c>
+      <c r="H562" t="s">
+        <v>19</v>
+      </c>
+      <c r="I562" t="s">
+        <v>25</v>
+      </c>
+      <c r="J562" t="s">
+        <v>25</v>
+      </c>
+      <c r="K562" t="s">
+        <v>25</v>
+      </c>
+      <c r="L562" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C563" t="s">
+        <v>961</v>
+      </c>
+      <c r="D563" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E563" t="s">
+        <v>25</v>
+      </c>
+      <c r="F563" t="s">
+        <v>25</v>
+      </c>
+      <c r="G563" t="s">
+        <v>25</v>
+      </c>
+      <c r="H563" t="s">
+        <v>19</v>
+      </c>
+      <c r="I563" t="s">
+        <v>25</v>
+      </c>
+      <c r="J563" t="s">
+        <v>25</v>
+      </c>
+      <c r="K563" t="s">
+        <v>25</v>
+      </c>
+      <c r="L563" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C564" t="s">
+        <v>961</v>
+      </c>
+      <c r="D564" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E564" t="s">
+        <v>25</v>
+      </c>
+      <c r="F564" t="s">
+        <v>25</v>
+      </c>
+      <c r="G564" t="s">
+        <v>25</v>
+      </c>
+      <c r="H564" t="s">
+        <v>19</v>
+      </c>
+      <c r="I564" t="s">
+        <v>25</v>
+      </c>
+      <c r="J564" t="s">
+        <v>25</v>
+      </c>
+      <c r="K564" t="s">
+        <v>25</v>
+      </c>
+      <c r="L564" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C565" t="s">
+        <v>961</v>
+      </c>
+      <c r="D565" t="s">
         <v>1044</v>
       </c>
-      <c r="E562" t="s">
-        <v>25</v>
-      </c>
-      <c r="F562" t="s">
-        <v>25</v>
-      </c>
-      <c r="G562" t="s">
-        <v>25</v>
-      </c>
-      <c r="H562" t="s">
-        <v>19</v>
-      </c>
-      <c r="I562" t="s">
-        <v>25</v>
-      </c>
-      <c r="J562" t="s">
-        <v>25</v>
-      </c>
-      <c r="K562" t="s">
-        <v>25</v>
-      </c>
-      <c r="L562" t="s">
+      <c r="E565" t="s">
+        <v>25</v>
+      </c>
+      <c r="F565" t="s">
+        <v>25</v>
+      </c>
+      <c r="G565" t="s">
+        <v>25</v>
+      </c>
+      <c r="H565" t="s">
+        <v>19</v>
+      </c>
+      <c r="I565" t="s">
+        <v>25</v>
+      </c>
+      <c r="J565" t="s">
+        <v>25</v>
+      </c>
+      <c r="K565" t="s">
+        <v>25</v>
+      </c>
+      <c r="L565" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C566" t="s">
+        <v>961</v>
+      </c>
+      <c r="D566" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E566" t="s">
+        <v>25</v>
+      </c>
+      <c r="F566" t="s">
+        <v>25</v>
+      </c>
+      <c r="G566" t="s">
+        <v>25</v>
+      </c>
+      <c r="H566" t="s">
+        <v>19</v>
+      </c>
+      <c r="I566" t="s">
+        <v>25</v>
+      </c>
+      <c r="J566" t="s">
+        <v>25</v>
+      </c>
+      <c r="K566" t="s">
+        <v>25</v>
+      </c>
+      <c r="L566" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C567" t="s">
+        <v>961</v>
+      </c>
+      <c r="D567" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E567" t="s">
+        <v>25</v>
+      </c>
+      <c r="F567" t="s">
+        <v>25</v>
+      </c>
+      <c r="G567" t="s">
+        <v>25</v>
+      </c>
+      <c r="H567" t="s">
+        <v>19</v>
+      </c>
+      <c r="I567" t="s">
+        <v>25</v>
+      </c>
+      <c r="J567" t="s">
+        <v>25</v>
+      </c>
+      <c r="K567" t="s">
+        <v>25</v>
+      </c>
+      <c r="L567" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C568" t="s">
+        <v>961</v>
+      </c>
+      <c r="D568" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E568" t="s">
+        <v>25</v>
+      </c>
+      <c r="F568" t="s">
+        <v>25</v>
+      </c>
+      <c r="G568" t="s">
+        <v>25</v>
+      </c>
+      <c r="H568" t="s">
+        <v>19</v>
+      </c>
+      <c r="I568" t="s">
+        <v>25</v>
+      </c>
+      <c r="J568" t="s">
+        <v>25</v>
+      </c>
+      <c r="K568" t="s">
+        <v>25</v>
+      </c>
+      <c r="L568" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C569" t="s">
+        <v>961</v>
+      </c>
+      <c r="D569" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E569" t="s">
+        <v>25</v>
+      </c>
+      <c r="F569" t="s">
+        <v>25</v>
+      </c>
+      <c r="G569" t="s">
+        <v>25</v>
+      </c>
+      <c r="H569" t="s">
+        <v>19</v>
+      </c>
+      <c r="I569" t="s">
+        <v>25</v>
+      </c>
+      <c r="J569" t="s">
+        <v>25</v>
+      </c>
+      <c r="K569" t="s">
+        <v>25</v>
+      </c>
+      <c r="L569" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C570" t="s">
+        <v>961</v>
+      </c>
+      <c r="D570" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E570" t="s">
+        <v>25</v>
+      </c>
+      <c r="F570" t="s">
+        <v>25</v>
+      </c>
+      <c r="G570" t="s">
+        <v>25</v>
+      </c>
+      <c r="H570" t="s">
+        <v>19</v>
+      </c>
+      <c r="I570" t="s">
+        <v>25</v>
+      </c>
+      <c r="J570" t="s">
+        <v>25</v>
+      </c>
+      <c r="K570" t="s">
+        <v>25</v>
+      </c>
+      <c r="L570" t="s">
         <v>25</v>
       </c>
     </row>
@@ -28506,7 +29416,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 G38:L38 B39:L39 B37:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 A11:D12 F10:F12 J10:L12 H10:H12 B17:D18 F17:F18 H17:H18 J17:L17 K18:L18 A28:G28 L21 F22:F24 J22:L24 A33:D36 L33 A21:D25 H21:H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F34:F36 J34:L36 H33:H36 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67:A68 J67:L68 J72:L73 F72 F73:G73 F67:G68 C67:D68 H72 A72:A74 A84 I84:L84 C72:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87 A91:D91 F91 H91:L91 A97:G99 L98 A96:D96 F96 H96:L96 A122:D122 I97:L97 I98:J98 I99:L99 A101:D101 F101 A104:D104 H104:I104 J101:L101 H101 L104 A109:D109 H109:I109 L109 A113:G113 I113:L113 A117 F117 C117:D117 A121 C121:D121 F121 J117:L117 J121:L121 A129:L562 A126:D126 K126:L126 H117 H121 H122:I122 L122 H126:I126 A127:D127 H127:I127 L127 A128:G128 I128:L128" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 G38:L38 B39:L39 B37:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 A11:D12 F10:F12 J10:L12 H10:H12 B17:D18 F17:F18 H17:H18 J17:L17 K18:L18 A28:G28 L21 F22:F24 J22:L24 A33:D36 L33 A21:D25 H21:H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F34:F36 J34:L36 H33:H36 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67:A68 J67:L68 J72:L73 F72 F73:G73 F67:G68 C67:D68 H72 A72:A74 A84 I84:L84 C72:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87 A91:D91 F91 H91:L91 A97:G99 L98 A96:D96 F96 H96:L96 A122:D122 I97:L97 I98:J98 I99:L99 A101:D101 F101 A104:D104 H104:I104 J101:L101 H101 L104 A109:D109 H109:I109 L109 A113:G113 I113:L113 A117 F117 C117:D117 A121 C121:D121 F121 J117:L117 J121:L121 A138:D138 A126:D126 K126:L126 H117 H121 H122:I122 L122 H126:I126 A127:D127 H127:I127 L127 A128:G128 I128:L128 A130:D130 F130 H130:L130 A131:G131 I131:L131 A132:G132 I132:L132 A134:D134 F134 H134:L134 A143:L570 A142:D142 F142 H138 J138:L138 H142:L142" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="790" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD3D704-27E6-4F4D-8804-86BB7BA3CC5D}"/>
+  <xr:revisionPtr revIDLastSave="833" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13383E5D-3742-426D-AFE5-1CBAA2D5F1AA}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6947" uniqueCount="1262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="1276">
   <si>
     <t>Codigo</t>
   </si>
@@ -7528,6 +7528,386 @@
   </si>
   <si>
     <t>assets/productos/bebes/inodoroentrena/asientoinodoro4.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/casamuñecas/casamuñecas.webp</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La Casa de Muñecas My Happy Family</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es el escenario perfecto para que los pequeños den vida a su imaginación. Con un diseño amplio, varios ambientes y accesorios decorativos, permite recrear diferentes espacios del hogar y crear historias llenas de creatividad y diversión.
+Su estructura está diseñada para un fácil armado y una gran estabilidad, ofreciendo un juguete resistente que acompañará innumerables momentos de juego. Es ideal para desarrollar la imaginación, la creatividad, la comunicación y el juego simbólico, convirtiéndose en un regalo perfecto para cumpleaños, Navidad o cualquier ocasión especial.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Casa de muñecas My Happy Family </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>con múltiples habitaciones y accesorios, diseñada para estimular la imaginación, el juego creativo y el desarrollo de habilidades mientras los niños crean historias y viven horas de diversión.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Casa de muñecas de varios niveles.
+Múltiples habitaciones para recrear diferentes ambientes.
+Incluye accesorios decorativos para complementar el juego.
+Estructura resistente y de fácil ensamblaje.
+Fabricada con materiales seguros y duraderos.
+Recomendada para niños mayores de 3 años.
+Ideal para juego individual o en familia.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Beneficios:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Estimula la imaginación y la creatividad.
+Favorece el desarrollo del juego simbólico.
+Ayuda a fortalecer habilidades sociales y de comunicación.
+Permite crear diferentes escenarios e historias.
+Regalo ideal para cumpleaños y ocasiones especiales.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Contenido del empaque:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1 Casa de muñecas My Happy Family.
+Accesorios decorativos incluidos (según versión del producto).
+Manual de armado.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Importante:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Las muñecas y algunos accesorios pueden variar según el lote de fabricación. Las imágenes son ilustrativas y algunos colores o detalles pueden cambiar según disponibilidad.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Armar sobre una superficie plana.
+Limpiar con un paño suave ligeramente húmedo.
+No utilizar productos abrasivos.
+Se recomienda el uso bajo la supervisión de un adulto cuando sea utilizado por niños pequeños.
+Contiene piezas pequeñas. No recomendado para menores de 3 años.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/bebes/castillocrystal/castillocrystal.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/castillocrystal/castillocrystal2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/castillocrystal/castillocrystal3.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/castillocrystal/castillocrystal4.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/castillocrystal/castillocrystal5.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/castillocrystal/castillocrystal6.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/bebes/castillocrystal/castillocrystal7.webp</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>El Castillo Crystal Palace Princesa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es un increíble centro de juego diseñado para transportar a los pequeños a un mundo lleno de magia, imaginación y aventuras. Su hermoso diseño tipo palacio, acompañado de luces y efectos de sonido, hace que cada momento de juego sea aún más emocionante y realista.
+Gracias a su formato portátil y fácil de transportar, los niños podrán llevar su castillo favorito a cualquier lugar. Es perfecto para estimular el juego de roles, desarrollar la creatividad y compartir momentos de diversión en familia o con amigos.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Castillo Crystal Palace Princesa </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>con luces, sonidos y diseño portátil, ideal para que los niños creen historias llenas de imaginación, desarrollen su creatividad y disfruten horas de diversión con sus personajes favoritos.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Castillo portátil estilo princesa.
+Luces y efectos de sonido integrados.
+Diseño colorido con múltiples espacios de juego.
+Fácil de transportar y almacenar.
+Estructura resistente y de fácil armado.
+Fabricado con materiales seguros y duraderos.
+Recomendado para niños mayores de 3 años.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Estimula la imaginación y la creatividad.
+Favorece el juego simbólico y de roles.
+Ayuda al desarrollo de habilidades sociales.
+Luces y sonidos que hacen la experiencia más divertida.
+Regalo ideal para cumpleaños, Navidad y ocasiones especiales.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Contenido del empaque:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1 Castillo Crystal Palace Princesa.
+Accesorios decorativos (según versión del producto).
+Manual de armado.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Importante:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Las muñecas, accesorios y elementos decorativos pueden variar según el lote de fabricación. Las imágenes son ilustrativas y algunos colores o detalles pueden cambiar de acuerdo con la disponibilidad.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Cuidados:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Armar sobre una superficie plana y estable.
+Limpiar con un paño suave ligeramente húmedo.
+No sumergir los componentes electrónicos en agua.
+Retirar las baterías si no se utilizará durante un periodo prolongado.
+Se recomienda el uso bajo la supervisión de un adulto. Contiene piezas pequeñas; no recomendado para menores de 3 años.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -7923,7 +8303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L570"/>
+  <dimension ref="A1:L576"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -13170,7 +13550,7 @@
         <v>25</v>
       </c>
       <c r="H143" t="s">
-        <v>19</v>
+        <v>1129</v>
       </c>
       <c r="I143" t="s">
         <v>25</v>
@@ -13198,14 +13578,14 @@
       <c r="D144" t="s">
         <v>153</v>
       </c>
-      <c r="E144" t="s">
-        <v>25</v>
-      </c>
-      <c r="F144" t="s">
-        <v>25</v>
+      <c r="E144">
+        <v>336984</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>1263</v>
       </c>
       <c r="G144" t="s">
-        <v>25</v>
+        <v>1262</v>
       </c>
       <c r="H144" t="s">
         <v>19</v>
@@ -13214,10 +13594,10 @@
         <v>25</v>
       </c>
       <c r="J144" t="s">
-        <v>25</v>
-      </c>
-      <c r="K144" t="s">
-        <v>25</v>
+        <v>1264</v>
+      </c>
+      <c r="K144" s="1" t="s">
+        <v>1265</v>
       </c>
       <c r="L144" t="s">
         <v>25</v>
@@ -13236,14 +13616,14 @@
       <c r="D145" t="s">
         <v>153</v>
       </c>
-      <c r="E145" t="s">
-        <v>25</v>
-      </c>
-      <c r="F145" t="s">
-        <v>25</v>
+      <c r="E145">
+        <v>411869</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>1273</v>
       </c>
       <c r="G145" t="s">
-        <v>25</v>
+        <v>1267</v>
       </c>
       <c r="H145" t="s">
         <v>19</v>
@@ -13252,10 +13632,10 @@
         <v>25</v>
       </c>
       <c r="J145" t="s">
-        <v>25</v>
-      </c>
-      <c r="K145" t="s">
-        <v>25</v>
+        <v>1274</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>1275</v>
       </c>
       <c r="L145" t="s">
         <v>25</v>
@@ -13263,10 +13643,10 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B146" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C146" t="s">
         <v>14</v>
@@ -13274,14 +13654,14 @@
       <c r="D146" t="s">
         <v>153</v>
       </c>
-      <c r="E146" t="s">
-        <v>25</v>
+      <c r="E146">
+        <v>411869</v>
       </c>
       <c r="F146" t="s">
         <v>25</v>
       </c>
       <c r="G146" t="s">
-        <v>25</v>
+        <v>1266</v>
       </c>
       <c r="H146" t="s">
         <v>19</v>
@@ -13301,10 +13681,10 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B147" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C147" t="s">
         <v>14</v>
@@ -13312,14 +13692,14 @@
       <c r="D147" t="s">
         <v>153</v>
       </c>
-      <c r="E147" t="s">
-        <v>25</v>
+      <c r="E147">
+        <v>411869</v>
       </c>
       <c r="F147" t="s">
         <v>25</v>
       </c>
       <c r="G147" t="s">
-        <v>25</v>
+        <v>1268</v>
       </c>
       <c r="H147" t="s">
         <v>19</v>
@@ -13339,10 +13719,10 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B148" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C148" t="s">
         <v>14</v>
@@ -13350,14 +13730,14 @@
       <c r="D148" t="s">
         <v>153</v>
       </c>
-      <c r="E148" t="s">
-        <v>25</v>
+      <c r="E148">
+        <v>411869</v>
       </c>
       <c r="F148" t="s">
         <v>25</v>
       </c>
       <c r="G148" t="s">
-        <v>25</v>
+        <v>1269</v>
       </c>
       <c r="H148" t="s">
         <v>19</v>
@@ -13377,10 +13757,10 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C149" t="s">
         <v>14</v>
@@ -13388,14 +13768,14 @@
       <c r="D149" t="s">
         <v>153</v>
       </c>
-      <c r="E149" t="s">
-        <v>25</v>
+      <c r="E149">
+        <v>411869</v>
       </c>
       <c r="F149" t="s">
         <v>25</v>
       </c>
       <c r="G149" t="s">
-        <v>25</v>
+        <v>1270</v>
       </c>
       <c r="H149" t="s">
         <v>19</v>
@@ -13415,10 +13795,10 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B150" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C150" t="s">
         <v>14</v>
@@ -13426,14 +13806,14 @@
       <c r="D150" t="s">
         <v>153</v>
       </c>
-      <c r="E150" t="s">
-        <v>25</v>
+      <c r="E150">
+        <v>411869</v>
       </c>
       <c r="F150" t="s">
         <v>25</v>
       </c>
       <c r="G150" t="s">
-        <v>25</v>
+        <v>1271</v>
       </c>
       <c r="H150" t="s">
         <v>19</v>
@@ -13453,10 +13833,10 @@
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C151" t="s">
         <v>14</v>
@@ -13464,14 +13844,14 @@
       <c r="D151" t="s">
         <v>153</v>
       </c>
-      <c r="E151" t="s">
-        <v>25</v>
+      <c r="E151">
+        <v>411869</v>
       </c>
       <c r="F151" t="s">
         <v>25</v>
       </c>
       <c r="G151" t="s">
-        <v>25</v>
+        <v>1272</v>
       </c>
       <c r="H151" t="s">
         <v>19</v>
@@ -13491,10 +13871,10 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B152" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C152" t="s">
         <v>14</v>
@@ -13529,10 +13909,10 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C153" t="s">
         <v>14</v>
@@ -13567,10 +13947,10 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B154" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C154" t="s">
         <v>14</v>
@@ -13605,10 +13985,10 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B155" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="C155" t="s">
         <v>14</v>
@@ -13622,9 +14002,6 @@
       <c r="F155" t="s">
         <v>25</v>
       </c>
-      <c r="G155" t="s">
-        <v>25</v>
-      </c>
       <c r="H155" t="s">
         <v>19</v>
       </c>
@@ -13643,10 +14020,10 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B156" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C156" t="s">
         <v>14</v>
@@ -13660,9 +14037,6 @@
       <c r="F156" t="s">
         <v>25</v>
       </c>
-      <c r="G156" t="s">
-        <v>25</v>
-      </c>
       <c r="H156" t="s">
         <v>19</v>
       </c>
@@ -13681,10 +14055,10 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B157" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C157" t="s">
         <v>14</v>
@@ -13719,10 +14093,10 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B158" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C158" t="s">
         <v>14</v>
@@ -13757,10 +14131,10 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B159" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="C159" t="s">
         <v>14</v>
@@ -13795,10 +14169,10 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B160" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C160" t="s">
         <v>14</v>
@@ -13833,10 +14207,10 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B161" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C161" t="s">
         <v>14</v>
@@ -13871,10 +14245,10 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="B162" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C162" t="s">
         <v>14</v>
@@ -13909,10 +14283,10 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B163" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="C163" t="s">
         <v>14</v>
@@ -13920,14 +14294,14 @@
       <c r="D163" t="s">
         <v>153</v>
       </c>
-      <c r="E163">
-        <v>106156</v>
+      <c r="E163" t="s">
+        <v>25</v>
       </c>
       <c r="F163" t="s">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="G163" t="s">
-        <v>194</v>
+        <v>25</v>
       </c>
       <c r="H163" t="s">
         <v>19</v>
@@ -13936,10 +14310,10 @@
         <v>25</v>
       </c>
       <c r="J163" t="s">
-        <v>195</v>
+        <v>25</v>
       </c>
       <c r="K163" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="L163" t="s">
         <v>25</v>
@@ -13947,10 +14321,10 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B164" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C164" t="s">
         <v>14</v>
@@ -13958,14 +14332,14 @@
       <c r="D164" t="s">
         <v>153</v>
       </c>
-      <c r="E164">
-        <v>106156</v>
+      <c r="E164" t="s">
+        <v>25</v>
       </c>
       <c r="F164" t="s">
         <v>25</v>
       </c>
       <c r="G164" t="s">
-        <v>197</v>
+        <v>25</v>
       </c>
       <c r="H164" t="s">
         <v>19</v>
@@ -13985,16 +14359,16 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="B165" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C165" t="s">
         <v>14</v>
       </c>
       <c r="D165" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="E165" t="s">
         <v>25</v>
@@ -14023,16 +14397,16 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="B166" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="C166" t="s">
         <v>14</v>
       </c>
       <c r="D166" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="E166" t="s">
         <v>25</v>
@@ -14061,16 +14435,16 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="B167" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C167" t="s">
         <v>14</v>
       </c>
       <c r="D167" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="E167" t="s">
         <v>25</v>
@@ -14099,16 +14473,16 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="B168" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="C168" t="s">
         <v>14</v>
       </c>
       <c r="D168" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="E168" t="s">
         <v>25</v>
@@ -14137,25 +14511,25 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="B169" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="C169" t="s">
         <v>14</v>
       </c>
       <c r="D169" t="s">
-        <v>200</v>
-      </c>
-      <c r="E169" t="s">
-        <v>25</v>
+        <v>153</v>
+      </c>
+      <c r="E169">
+        <v>106156</v>
       </c>
       <c r="F169" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="G169" t="s">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="H169" t="s">
         <v>19</v>
@@ -14164,10 +14538,10 @@
         <v>25</v>
       </c>
       <c r="J169" t="s">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="K169" t="s">
-        <v>25</v>
+        <v>196</v>
       </c>
       <c r="L169" t="s">
         <v>25</v>
@@ -14175,25 +14549,25 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="B170" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C170" t="s">
         <v>14</v>
       </c>
       <c r="D170" t="s">
-        <v>200</v>
-      </c>
-      <c r="E170" t="s">
-        <v>25</v>
+        <v>153</v>
+      </c>
+      <c r="E170">
+        <v>106156</v>
       </c>
       <c r="F170" t="s">
         <v>25</v>
       </c>
       <c r="G170" t="s">
-        <v>25</v>
+        <v>197</v>
       </c>
       <c r="H170" t="s">
         <v>19</v>
@@ -14213,10 +14587,10 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="B171" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="C171" t="s">
         <v>14</v>
@@ -14251,10 +14625,10 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B172" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="C172" t="s">
         <v>14</v>
@@ -14289,10 +14663,10 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B173" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="C173" t="s">
         <v>14</v>
@@ -14327,10 +14701,10 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B174" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="C174" t="s">
         <v>14</v>
@@ -14365,10 +14739,10 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B175" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C175" t="s">
         <v>14</v>
@@ -14403,10 +14777,10 @@
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B176" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="C176" t="s">
         <v>14</v>
@@ -14441,10 +14815,10 @@
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B177" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="C177" t="s">
         <v>14</v>
@@ -14479,16 +14853,16 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B178" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="C178" t="s">
         <v>14</v>
       </c>
       <c r="D178" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E178" t="s">
         <v>25</v>
@@ -14517,16 +14891,16 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="B179" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C179" t="s">
         <v>14</v>
       </c>
       <c r="D179" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E179" t="s">
         <v>25</v>
@@ -14555,16 +14929,16 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B180" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C180" t="s">
         <v>14</v>
       </c>
       <c r="D180" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E180" t="s">
         <v>25</v>
@@ -14593,16 +14967,16 @@
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B181" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C181" t="s">
         <v>14</v>
       </c>
       <c r="D181" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E181" t="s">
         <v>25</v>
@@ -14631,16 +15005,16 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B182" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="C182" t="s">
         <v>14</v>
       </c>
       <c r="D182" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E182" t="s">
         <v>25</v>
@@ -14669,16 +15043,16 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B183" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="C183" t="s">
         <v>14</v>
       </c>
       <c r="D183" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="E183" t="s">
         <v>25</v>
@@ -14707,16 +15081,16 @@
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B184" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="C184" t="s">
         <v>14</v>
       </c>
       <c r="D184" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E184" t="s">
         <v>25</v>
@@ -14745,16 +15119,16 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B185" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="C185" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D185" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="E185" t="s">
         <v>25</v>
@@ -14783,16 +15157,16 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B186" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="C186" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D186" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="E186" t="s">
         <v>25</v>
@@ -14821,16 +15195,16 @@
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B187" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="C187" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D187" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="E187" t="s">
         <v>25</v>
@@ -14859,16 +15233,16 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="B188" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="C188" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D188" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="E188" t="s">
         <v>25</v>
@@ -14897,16 +15271,16 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="B189" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="C189" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D189" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E189" t="s">
         <v>25</v>
@@ -14935,16 +15309,16 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="B190" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C190" t="s">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="D190" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E190" t="s">
         <v>25</v>
@@ -14973,10 +15347,10 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B191" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C191" t="s">
         <v>241</v>
@@ -15011,10 +15385,10 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="B192" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C192" t="s">
         <v>241</v>
@@ -15049,10 +15423,10 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B193" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="C193" t="s">
         <v>241</v>
@@ -15087,10 +15461,10 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B194" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="C194" t="s">
         <v>241</v>
@@ -15125,10 +15499,10 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B195" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C195" t="s">
         <v>241</v>
@@ -15163,10 +15537,10 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B196" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="C196" t="s">
         <v>241</v>
@@ -15201,10 +15575,10 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B197" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C197" t="s">
         <v>241</v>
@@ -15239,10 +15613,10 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B198" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="C198" t="s">
         <v>241</v>
@@ -15277,10 +15651,10 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B199" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="C199" t="s">
         <v>241</v>
@@ -15315,10 +15689,10 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="B200" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C200" t="s">
         <v>241</v>
@@ -15353,10 +15727,10 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B201" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C201" t="s">
         <v>241</v>
@@ -15391,10 +15765,10 @@
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B202" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C202" t="s">
         <v>241</v>
@@ -15429,10 +15803,10 @@
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B203" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C203" t="s">
         <v>241</v>
@@ -15467,10 +15841,10 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B204" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C204" t="s">
         <v>241</v>
@@ -15505,10 +15879,10 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="B205" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C205" t="s">
         <v>241</v>
@@ -15543,10 +15917,10 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B206" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="C206" t="s">
         <v>241</v>
@@ -15581,10 +15955,10 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B207" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C207" t="s">
         <v>241</v>
@@ -15619,10 +15993,10 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B208" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C208" t="s">
         <v>241</v>
@@ -15657,10 +16031,10 @@
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="B209" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C209" t="s">
         <v>241</v>
@@ -15695,10 +16069,10 @@
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B210" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C210" t="s">
         <v>241</v>
@@ -15733,10 +16107,10 @@
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B211" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C211" t="s">
         <v>241</v>
@@ -15771,10 +16145,10 @@
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="B212" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C212" t="s">
         <v>241</v>
@@ -15809,10 +16183,10 @@
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="B213" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="C213" t="s">
         <v>241</v>
@@ -15847,10 +16221,10 @@
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="B214" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="C214" t="s">
         <v>241</v>
@@ -15885,10 +16259,10 @@
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="B215" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C215" t="s">
         <v>241</v>
@@ -15923,10 +16297,10 @@
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B216" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C216" t="s">
         <v>241</v>
@@ -15961,10 +16335,10 @@
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="B217" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="C217" t="s">
         <v>241</v>
@@ -15999,10 +16373,10 @@
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="B218" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="C218" t="s">
         <v>241</v>
@@ -16037,10 +16411,10 @@
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="B219" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C219" t="s">
         <v>241</v>
@@ -16075,10 +16449,10 @@
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="B220" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C220" t="s">
         <v>241</v>
@@ -16113,10 +16487,10 @@
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="B221" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C221" t="s">
         <v>241</v>
@@ -16151,10 +16525,10 @@
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="B222" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C222" t="s">
         <v>241</v>
@@ -16189,16 +16563,16 @@
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="B223" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C223" t="s">
         <v>241</v>
       </c>
       <c r="D223" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E223" t="s">
         <v>25</v>
@@ -16227,16 +16601,16 @@
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="B224" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="C224" t="s">
         <v>241</v>
       </c>
       <c r="D224" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E224" t="s">
         <v>25</v>
@@ -16265,16 +16639,16 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="B225" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C225" t="s">
         <v>241</v>
       </c>
       <c r="D225" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E225" t="s">
         <v>25</v>
@@ -16303,16 +16677,16 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="B226" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="C226" t="s">
         <v>241</v>
       </c>
       <c r="D226" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E226" t="s">
         <v>25</v>
@@ -16341,16 +16715,16 @@
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="B227" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="C227" t="s">
         <v>241</v>
       </c>
       <c r="D227" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E227" t="s">
         <v>25</v>
@@ -16379,16 +16753,16 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="B228" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="C228" t="s">
         <v>241</v>
       </c>
       <c r="D228" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="E228" t="s">
         <v>25</v>
@@ -16417,10 +16791,10 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="B229" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="C229" t="s">
         <v>241</v>
@@ -16455,10 +16829,10 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="B230" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C230" t="s">
         <v>241</v>
@@ -16493,10 +16867,10 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="B231" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="C231" t="s">
         <v>241</v>
@@ -16531,10 +16905,10 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="B232" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C232" t="s">
         <v>241</v>
@@ -16569,16 +16943,16 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="B233" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="C233" t="s">
         <v>241</v>
       </c>
       <c r="D233" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="E233" t="s">
         <v>25</v>
@@ -16607,16 +16981,16 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="B234" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="C234" t="s">
         <v>241</v>
       </c>
       <c r="D234" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="E234" t="s">
         <v>25</v>
@@ -16645,16 +17019,16 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="B235" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C235" t="s">
         <v>241</v>
       </c>
       <c r="D235" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="E235" t="s">
         <v>25</v>
@@ -16683,16 +17057,16 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="B236" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="C236" t="s">
         <v>241</v>
       </c>
       <c r="D236" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="E236" t="s">
         <v>25</v>
@@ -16721,16 +17095,16 @@
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="B237" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C237" t="s">
         <v>241</v>
       </c>
       <c r="D237" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="E237" t="s">
         <v>25</v>
@@ -16759,16 +17133,16 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="B238" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="C238" t="s">
         <v>241</v>
       </c>
       <c r="D238" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="E238" t="s">
         <v>25</v>
@@ -16797,16 +17171,16 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="B239" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="C239" t="s">
         <v>241</v>
       </c>
       <c r="D239" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E239" t="s">
         <v>25</v>
@@ -16835,16 +17209,16 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="B240" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="C240" t="s">
         <v>241</v>
       </c>
       <c r="D240" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E240" t="s">
         <v>25</v>
@@ -16873,16 +17247,16 @@
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="B241" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="C241" t="s">
         <v>241</v>
       </c>
       <c r="D241" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E241" t="s">
         <v>25</v>
@@ -16911,10 +17285,10 @@
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="B242" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C242" t="s">
         <v>241</v>
@@ -16949,16 +17323,16 @@
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B243" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="C243" t="s">
         <v>241</v>
       </c>
       <c r="D243" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E243" t="s">
         <v>25</v>
@@ -16987,16 +17361,16 @@
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="B244" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="C244" t="s">
         <v>241</v>
       </c>
       <c r="D244" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E244" t="s">
         <v>25</v>
@@ -17025,16 +17399,16 @@
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B245" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C245" t="s">
         <v>241</v>
       </c>
       <c r="D245" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E245" t="s">
         <v>25</v>
@@ -17063,16 +17437,16 @@
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="B246" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="C246" t="s">
         <v>241</v>
       </c>
       <c r="D246" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E246" t="s">
         <v>25</v>
@@ -17101,16 +17475,16 @@
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="B247" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="C247" t="s">
         <v>241</v>
       </c>
       <c r="D247" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E247" t="s">
         <v>25</v>
@@ -17139,16 +17513,16 @@
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="B248" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C248" t="s">
         <v>241</v>
       </c>
       <c r="D248" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="E248" t="s">
         <v>25</v>
@@ -17177,10 +17551,10 @@
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="B249" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="C249" t="s">
         <v>241</v>
@@ -17215,10 +17589,10 @@
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B250" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C250" t="s">
         <v>241</v>
@@ -17253,10 +17627,10 @@
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B251" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C251" t="s">
         <v>241</v>
@@ -17291,10 +17665,10 @@
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="B252" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C252" t="s">
         <v>241</v>
@@ -17329,10 +17703,10 @@
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="B253" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C253" t="s">
         <v>241</v>
@@ -17367,10 +17741,10 @@
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="B254" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C254" t="s">
         <v>241</v>
@@ -17405,10 +17779,10 @@
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B255" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C255" t="s">
         <v>241</v>
@@ -17443,10 +17817,10 @@
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B256" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C256" t="s">
         <v>241</v>
@@ -17481,10 +17855,10 @@
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B257" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="C257" t="s">
         <v>241</v>
@@ -17519,10 +17893,10 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B258" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C258" t="s">
         <v>241</v>
@@ -17557,10 +17931,10 @@
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B259" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C259" t="s">
         <v>241</v>
@@ -17595,10 +17969,10 @@
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B260" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="C260" t="s">
         <v>241</v>
@@ -17633,10 +18007,10 @@
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B261" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="C261" t="s">
         <v>241</v>
@@ -17671,10 +18045,10 @@
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="B262" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="C262" t="s">
         <v>241</v>
@@ -17709,10 +18083,10 @@
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="B263" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="C263" t="s">
         <v>241</v>
@@ -17747,10 +18121,10 @@
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="B264" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="C264" t="s">
         <v>241</v>
@@ -17785,10 +18159,10 @@
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="B265" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="C265" t="s">
         <v>241</v>
@@ -17823,10 +18197,10 @@
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="B266" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="C266" t="s">
         <v>241</v>
@@ -17861,10 +18235,10 @@
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="B267" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="C267" t="s">
         <v>241</v>
@@ -17899,10 +18273,10 @@
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B268" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="C268" t="s">
         <v>241</v>
@@ -17937,16 +18311,16 @@
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B269" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="C269" t="s">
         <v>241</v>
       </c>
       <c r="D269" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E269" t="s">
         <v>25</v>
@@ -17975,16 +18349,16 @@
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="B270" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="C270" t="s">
         <v>241</v>
       </c>
       <c r="D270" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E270" t="s">
         <v>25</v>
@@ -18013,16 +18387,16 @@
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="B271" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="C271" t="s">
         <v>241</v>
       </c>
       <c r="D271" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E271" t="s">
         <v>25</v>
@@ -18051,16 +18425,16 @@
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="B272" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="C272" t="s">
         <v>241</v>
       </c>
       <c r="D272" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E272" t="s">
         <v>25</v>
@@ -18089,16 +18463,16 @@
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="B273" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="C273" t="s">
         <v>241</v>
       </c>
       <c r="D273" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E273" t="s">
         <v>25</v>
@@ -18127,16 +18501,16 @@
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="B274" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="C274" t="s">
         <v>241</v>
       </c>
       <c r="D274" t="s">
-        <v>409</v>
+        <v>227</v>
       </c>
       <c r="E274" t="s">
         <v>25</v>
@@ -18165,10 +18539,10 @@
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B275" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="C275" t="s">
         <v>241</v>
@@ -18203,10 +18577,10 @@
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="B276" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="C276" t="s">
         <v>241</v>
@@ -18241,10 +18615,10 @@
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B277" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C277" t="s">
         <v>241</v>
@@ -18279,10 +18653,10 @@
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="B278" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="C278" t="s">
         <v>241</v>
@@ -18317,10 +18691,10 @@
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="B279" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C279" t="s">
         <v>241</v>
@@ -18355,10 +18729,10 @@
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B280" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="C280" t="s">
         <v>241</v>
@@ -18393,10 +18767,10 @@
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="B281" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C281" t="s">
         <v>241</v>
@@ -18431,10 +18805,10 @@
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="B282" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="C282" t="s">
         <v>241</v>
@@ -18469,10 +18843,10 @@
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="B283" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C283" t="s">
         <v>241</v>
@@ -18507,10 +18881,10 @@
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="B284" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="C284" t="s">
         <v>241</v>
@@ -18545,10 +18919,10 @@
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="B285" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C285" t="s">
         <v>241</v>
@@ -18583,10 +18957,10 @@
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="B286" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C286" t="s">
         <v>241</v>
@@ -18621,10 +18995,10 @@
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="B287" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C287" t="s">
         <v>241</v>
@@ -18659,10 +19033,10 @@
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="B288" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="C288" t="s">
         <v>241</v>
@@ -18697,10 +19071,10 @@
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="B289" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="C289" t="s">
         <v>241</v>
@@ -18735,10 +19109,10 @@
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="B290" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="C290" t="s">
         <v>241</v>
@@ -18773,10 +19147,10 @@
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B291" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="C291" t="s">
         <v>241</v>
@@ -18811,10 +19185,10 @@
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="B292" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C292" t="s">
         <v>241</v>
@@ -18849,10 +19223,10 @@
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="B293" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="C293" t="s">
         <v>241</v>
@@ -18887,10 +19261,10 @@
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B294" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="C294" t="s">
         <v>241</v>
@@ -18925,16 +19299,16 @@
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B295" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C295" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D295" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E295" t="s">
         <v>25</v>
@@ -18963,16 +19337,16 @@
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="B296" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="C296" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D296" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E296" t="s">
         <v>25</v>
@@ -19001,16 +19375,16 @@
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="B297" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="C297" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D297" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E297" t="s">
         <v>25</v>
@@ -19039,16 +19413,16 @@
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="B298" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="C298" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D298" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E298" t="s">
         <v>25</v>
@@ -19077,16 +19451,16 @@
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="B299" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="C299" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D299" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E299" t="s">
         <v>25</v>
@@ -19115,16 +19489,16 @@
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="B300" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="C300" t="s">
-        <v>462</v>
+        <v>241</v>
       </c>
       <c r="D300" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="E300" t="s">
         <v>25</v>
@@ -19153,10 +19527,10 @@
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="B301" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="C301" t="s">
         <v>462</v>
@@ -19191,10 +19565,10 @@
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B302" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="C302" t="s">
         <v>462</v>
@@ -19229,10 +19603,10 @@
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="B303" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C303" t="s">
         <v>462</v>
@@ -19267,10 +19641,10 @@
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="B304" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="C304" t="s">
         <v>462</v>
@@ -19305,10 +19679,10 @@
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="B305" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C305" t="s">
         <v>462</v>
@@ -19343,10 +19717,10 @@
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="B306" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="C306" t="s">
         <v>462</v>
@@ -19381,10 +19755,10 @@
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="B307" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="C307" t="s">
         <v>462</v>
@@ -19419,10 +19793,10 @@
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B308" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="C308" t="s">
         <v>462</v>
@@ -19457,10 +19831,10 @@
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="B309" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="C309" t="s">
         <v>462</v>
@@ -19495,10 +19869,10 @@
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="B310" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C310" t="s">
         <v>462</v>
@@ -19533,10 +19907,10 @@
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="B311" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="C311" t="s">
         <v>462</v>
@@ -19571,10 +19945,10 @@
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="B312" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="C312" t="s">
         <v>462</v>
@@ -19609,10 +19983,10 @@
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="B313" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="C313" t="s">
         <v>462</v>
@@ -19647,10 +20021,10 @@
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="B314" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="C314" t="s">
         <v>462</v>
@@ -19685,10 +20059,10 @@
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="B315" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="C315" t="s">
         <v>462</v>
@@ -19723,10 +20097,10 @@
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="B316" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="C316" t="s">
         <v>462</v>
@@ -19761,10 +20135,10 @@
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="B317" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="C317" t="s">
         <v>462</v>
@@ -19799,10 +20173,10 @@
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="B318" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="C318" t="s">
         <v>462</v>
@@ -19837,10 +20211,10 @@
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="B319" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="C319" t="s">
         <v>462</v>
@@ -19875,10 +20249,10 @@
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="B320" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="C320" t="s">
         <v>462</v>
@@ -19913,10 +20287,10 @@
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="B321" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="C321" t="s">
         <v>462</v>
@@ -19951,10 +20325,10 @@
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="B322" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C322" t="s">
         <v>462</v>
@@ -19989,10 +20363,10 @@
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="B323" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="C323" t="s">
         <v>462</v>
@@ -20027,10 +20401,10 @@
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="B324" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C324" t="s">
         <v>462</v>
@@ -20065,10 +20439,10 @@
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="B325" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="C325" t="s">
         <v>462</v>
@@ -20103,10 +20477,10 @@
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="B326" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="C326" t="s">
         <v>462</v>
@@ -20141,10 +20515,10 @@
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="B327" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C327" t="s">
         <v>462</v>
@@ -20179,10 +20553,10 @@
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="B328" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="C328" t="s">
         <v>462</v>
@@ -20217,10 +20591,10 @@
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="B329" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="C329" t="s">
         <v>462</v>
@@ -20255,10 +20629,10 @@
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="B330" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="C330" t="s">
         <v>462</v>
@@ -20293,10 +20667,10 @@
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="B331" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="C331" t="s">
         <v>462</v>
@@ -20331,10 +20705,10 @@
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="B332" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="C332" t="s">
         <v>462</v>
@@ -20369,10 +20743,10 @@
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="B333" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="C333" t="s">
         <v>462</v>
@@ -20407,10 +20781,10 @@
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="B334" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="C334" t="s">
         <v>462</v>
@@ -20445,10 +20819,10 @@
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="B335" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="C335" t="s">
         <v>462</v>
@@ -20483,10 +20857,10 @@
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="B336" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="C336" t="s">
         <v>462</v>
@@ -20521,10 +20895,10 @@
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="B337" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C337" t="s">
         <v>462</v>
@@ -20559,10 +20933,10 @@
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="B338" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C338" t="s">
         <v>462</v>
@@ -20597,10 +20971,10 @@
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="B339" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="C339" t="s">
         <v>462</v>
@@ -20635,10 +21009,10 @@
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="B340" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="C340" t="s">
         <v>462</v>
@@ -20673,10 +21047,10 @@
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="B341" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="C341" t="s">
         <v>462</v>
@@ -20711,16 +21085,16 @@
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="B342" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C342" t="s">
         <v>462</v>
       </c>
       <c r="D342" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E342" t="s">
         <v>25</v>
@@ -20749,16 +21123,16 @@
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="B343" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="C343" t="s">
         <v>462</v>
       </c>
       <c r="D343" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E343" t="s">
         <v>25</v>
@@ -20787,16 +21161,16 @@
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="B344" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="C344" t="s">
         <v>462</v>
       </c>
       <c r="D344" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E344" t="s">
         <v>25</v>
@@ -20825,16 +21199,16 @@
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="B345" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="C345" t="s">
         <v>462</v>
       </c>
       <c r="D345" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E345" t="s">
         <v>25</v>
@@ -20863,16 +21237,16 @@
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="B346" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="C346" t="s">
         <v>462</v>
       </c>
       <c r="D346" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E346" t="s">
         <v>25</v>
@@ -20901,16 +21275,16 @@
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="B347" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="C347" t="s">
         <v>462</v>
       </c>
       <c r="D347" t="s">
-        <v>558</v>
+        <v>463</v>
       </c>
       <c r="E347" t="s">
         <v>25</v>
@@ -20939,10 +21313,10 @@
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="B348" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="C348" t="s">
         <v>462</v>
@@ -20977,10 +21351,10 @@
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="B349" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C349" t="s">
         <v>462</v>
@@ -21015,10 +21389,10 @@
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="B350" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C350" t="s">
         <v>462</v>
@@ -21053,10 +21427,10 @@
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="B351" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C351" t="s">
         <v>462</v>
@@ -21091,10 +21465,10 @@
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="B352" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C352" t="s">
         <v>462</v>
@@ -21129,10 +21503,10 @@
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="B353" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="C353" t="s">
         <v>462</v>
@@ -21167,10 +21541,10 @@
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="B354" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="C354" t="s">
         <v>462</v>
@@ -21205,10 +21579,10 @@
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="B355" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="C355" t="s">
         <v>462</v>
@@ -21243,10 +21617,10 @@
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="B356" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="C356" t="s">
         <v>462</v>
@@ -21281,10 +21655,10 @@
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="B357" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="C357" t="s">
         <v>462</v>
@@ -21319,10 +21693,10 @@
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="B358" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="C358" t="s">
         <v>462</v>
@@ -21357,10 +21731,10 @@
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="B359" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="C359" t="s">
         <v>462</v>
@@ -21395,10 +21769,10 @@
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="B360" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="C360" t="s">
         <v>462</v>
@@ -21433,10 +21807,10 @@
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="B361" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="C361" t="s">
         <v>462</v>
@@ -21471,10 +21845,10 @@
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="B362" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="C362" t="s">
         <v>462</v>
@@ -21509,10 +21883,10 @@
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="B363" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="C363" t="s">
         <v>462</v>
@@ -21547,10 +21921,10 @@
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="B364" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="C364" t="s">
         <v>462</v>
@@ -21585,10 +21959,10 @@
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B365" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C365" t="s">
         <v>462</v>
@@ -21623,10 +21997,10 @@
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="B366" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="C366" t="s">
         <v>462</v>
@@ -21661,10 +22035,10 @@
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="B367" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="C367" t="s">
         <v>462</v>
@@ -21699,10 +22073,10 @@
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="B368" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C368" t="s">
         <v>462</v>
@@ -21737,10 +22111,10 @@
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="B369" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="C369" t="s">
         <v>462</v>
@@ -21775,10 +22149,10 @@
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="B370" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="C370" t="s">
         <v>462</v>
@@ -21813,10 +22187,10 @@
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="B371" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C371" t="s">
         <v>462</v>
@@ -21851,10 +22225,10 @@
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="B372" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="C372" t="s">
         <v>462</v>
@@ -21889,10 +22263,10 @@
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="B373" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="C373" t="s">
         <v>462</v>
@@ -21927,10 +22301,10 @@
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="B374" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C374" t="s">
         <v>462</v>
@@ -21965,10 +22339,10 @@
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B375" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C375" t="s">
         <v>462</v>
@@ -22003,16 +22377,16 @@
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="B376" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C376" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D376" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E376" t="s">
         <v>25</v>
@@ -22041,16 +22415,16 @@
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="B377" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="C377" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D377" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E377" t="s">
         <v>25</v>
@@ -22079,16 +22453,16 @@
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="B378" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="C378" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D378" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E378" t="s">
         <v>25</v>
@@ -22117,16 +22491,16 @@
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="B379" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="C379" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D379" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E379" t="s">
         <v>25</v>
@@ -22155,16 +22529,16 @@
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="B380" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="C380" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D380" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E380" t="s">
         <v>25</v>
@@ -22193,16 +22567,16 @@
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="B381" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="C381" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="D381" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="E381" t="s">
         <v>25</v>
@@ -22231,10 +22605,10 @@
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="B382" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="C382" t="s">
         <v>627</v>
@@ -22269,10 +22643,10 @@
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="B383" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="C383" t="s">
         <v>627</v>
@@ -22307,16 +22681,16 @@
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="B384" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="C384" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D384" t="s">
-        <v>645</v>
+        <v>25</v>
       </c>
       <c r="E384" t="s">
         <v>25</v>
@@ -22345,16 +22719,16 @@
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="B385" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="C385" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D385" t="s">
-        <v>645</v>
+        <v>25</v>
       </c>
       <c r="E385" t="s">
         <v>25</v>
@@ -22383,16 +22757,16 @@
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="B386" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="C386" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D386" t="s">
-        <v>645</v>
+        <v>25</v>
       </c>
       <c r="E386" t="s">
         <v>25</v>
@@ -22421,16 +22795,16 @@
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="B387" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="C387" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D387" t="s">
-        <v>645</v>
+        <v>25</v>
       </c>
       <c r="E387" t="s">
         <v>25</v>
@@ -22459,16 +22833,16 @@
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="B388" t="s">
-        <v>653</v>
+        <v>639</v>
       </c>
       <c r="C388" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D388" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="E388" t="s">
         <v>25</v>
@@ -22497,16 +22871,16 @@
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="B389" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="C389" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D389" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="E389" t="s">
         <v>25</v>
@@ -22535,16 +22909,16 @@
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="B390" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="C390" t="s">
         <v>644</v>
       </c>
       <c r="D390" t="s">
-        <v>138</v>
+        <v>645</v>
       </c>
       <c r="E390" t="s">
         <v>25</v>
@@ -22573,16 +22947,16 @@
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="B391" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="C391" t="s">
         <v>644</v>
       </c>
       <c r="D391" t="s">
-        <v>138</v>
+        <v>645</v>
       </c>
       <c r="E391" t="s">
         <v>25</v>
@@ -22611,16 +22985,16 @@
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="B392" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="C392" t="s">
         <v>644</v>
       </c>
       <c r="D392" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
       <c r="E392" t="s">
         <v>25</v>
@@ -22649,16 +23023,16 @@
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="B393" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="C393" t="s">
         <v>644</v>
       </c>
       <c r="D393" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
       <c r="E393" t="s">
         <v>25</v>
@@ -22687,16 +23061,16 @@
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="B394" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="C394" t="s">
         <v>644</v>
       </c>
       <c r="D394" t="s">
-        <v>662</v>
+        <v>138</v>
       </c>
       <c r="E394" t="s">
         <v>25</v>
@@ -22725,16 +23099,16 @@
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="B395" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="C395" t="s">
         <v>644</v>
       </c>
       <c r="D395" t="s">
-        <v>662</v>
+        <v>138</v>
       </c>
       <c r="E395" t="s">
         <v>25</v>
@@ -22763,16 +23137,16 @@
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="B396" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="C396" t="s">
         <v>644</v>
       </c>
       <c r="D396" t="s">
-        <v>662</v>
+        <v>138</v>
       </c>
       <c r="E396" t="s">
         <v>25</v>
@@ -22801,16 +23175,16 @@
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="B397" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="C397" t="s">
         <v>644</v>
       </c>
       <c r="D397" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E397" t="s">
         <v>25</v>
@@ -22839,16 +23213,16 @@
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="B398" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C398" t="s">
         <v>644</v>
       </c>
       <c r="D398" t="s">
-        <v>128</v>
+        <v>662</v>
       </c>
       <c r="E398" t="s">
         <v>25</v>
@@ -22877,16 +23251,16 @@
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="B399" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="C399" t="s">
         <v>644</v>
       </c>
       <c r="D399" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="E399" t="s">
         <v>25</v>
@@ -22915,16 +23289,16 @@
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="B400" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="C400" t="s">
         <v>644</v>
       </c>
       <c r="D400" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="E400" t="s">
         <v>25</v>
@@ -22953,16 +23327,16 @@
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="B401" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="C401" t="s">
         <v>644</v>
       </c>
       <c r="D401" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="E401" t="s">
         <v>25</v>
@@ -22991,16 +23365,16 @@
     </row>
     <row r="402" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="B402" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="C402" t="s">
         <v>644</v>
       </c>
       <c r="D402" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="E402" t="s">
         <v>25</v>
@@ -23029,16 +23403,16 @@
     </row>
     <row r="403" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="B403" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="C403" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D403" t="s">
-        <v>686</v>
+        <v>128</v>
       </c>
       <c r="E403" t="s">
         <v>25</v>
@@ -23067,16 +23441,16 @@
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="B404" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="C404" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D404" t="s">
-        <v>686</v>
+        <v>128</v>
       </c>
       <c r="E404" t="s">
         <v>25</v>
@@ -23105,16 +23479,16 @@
     </row>
     <row r="405" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="B405" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="C405" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D405" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="E405" t="s">
         <v>25</v>
@@ -23143,16 +23517,16 @@
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="B406" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="C406" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D406" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="E406" t="s">
         <v>25</v>
@@ -23181,16 +23555,16 @@
     </row>
     <row r="407" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="B407" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="C407" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D407" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="E407" t="s">
         <v>25</v>
@@ -23219,16 +23593,16 @@
     </row>
     <row r="408" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="B408" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="C408" t="s">
-        <v>685</v>
+        <v>644</v>
       </c>
       <c r="D408" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="E408" t="s">
         <v>25</v>
@@ -23257,16 +23631,16 @@
     </row>
     <row r="409" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="B409" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="C409" t="s">
         <v>685</v>
       </c>
       <c r="D409" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="E409" t="s">
         <v>25</v>
@@ -23295,16 +23669,16 @@
     </row>
     <row r="410" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="B410" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="C410" t="s">
         <v>685</v>
       </c>
       <c r="D410" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="E410" t="s">
         <v>25</v>
@@ -23333,16 +23707,16 @@
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="B411" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="C411" t="s">
         <v>685</v>
       </c>
       <c r="D411" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="E411" t="s">
         <v>25</v>
@@ -23371,16 +23745,16 @@
     </row>
     <row r="412" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="B412" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="C412" t="s">
         <v>685</v>
       </c>
       <c r="D412" t="s">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="E412" t="s">
         <v>25</v>
@@ -23409,16 +23783,16 @@
     </row>
     <row r="413" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="B413" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="C413" t="s">
         <v>685</v>
       </c>
       <c r="D413" t="s">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="E413" t="s">
         <v>25</v>
@@ -23447,16 +23821,16 @@
     </row>
     <row r="414" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="B414" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="C414" t="s">
         <v>685</v>
       </c>
       <c r="D414" t="s">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="E414" t="s">
         <v>25</v>
@@ -23485,16 +23859,16 @@
     </row>
     <row r="415" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="B415" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="C415" t="s">
         <v>685</v>
       </c>
       <c r="D415" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="E415" t="s">
         <v>25</v>
@@ -23523,16 +23897,16 @@
     </row>
     <row r="416" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="B416" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="C416" t="s">
         <v>685</v>
       </c>
       <c r="D416" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="E416" t="s">
         <v>25</v>
@@ -23561,16 +23935,16 @@
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="B417" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="C417" t="s">
         <v>685</v>
       </c>
       <c r="D417" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="E417" t="s">
         <v>25</v>
@@ -23599,16 +23973,16 @@
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="B418" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="C418" t="s">
         <v>685</v>
       </c>
       <c r="D418" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="E418" t="s">
         <v>25</v>
@@ -23637,16 +24011,16 @@
     </row>
     <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="B419" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="C419" t="s">
         <v>685</v>
       </c>
       <c r="D419" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="E419" t="s">
         <v>25</v>
@@ -23675,16 +24049,16 @@
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="B420" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="C420" t="s">
         <v>685</v>
       </c>
       <c r="D420" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="E420" t="s">
         <v>25</v>
@@ -23713,16 +24087,16 @@
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="B421" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="C421" t="s">
         <v>685</v>
       </c>
       <c r="D421" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="E421" t="s">
         <v>25</v>
@@ -23751,16 +24125,16 @@
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="B422" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="C422" t="s">
         <v>685</v>
       </c>
       <c r="D422" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="E422" t="s">
         <v>25</v>
@@ -23789,16 +24163,16 @@
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="B423" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
       <c r="C423" t="s">
         <v>685</v>
       </c>
       <c r="D423" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="E423" t="s">
         <v>25</v>
@@ -23827,16 +24201,16 @@
     </row>
     <row r="424" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="B424" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="C424" t="s">
         <v>685</v>
       </c>
       <c r="D424" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="E424" t="s">
         <v>25</v>
@@ -23865,16 +24239,16 @@
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="B425" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="C425" t="s">
         <v>685</v>
       </c>
       <c r="D425" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="E425" t="s">
         <v>25</v>
@@ -23903,16 +24277,16 @@
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="B426" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="C426" t="s">
         <v>685</v>
       </c>
       <c r="D426" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="E426" t="s">
         <v>25</v>
@@ -23941,16 +24315,16 @@
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="B427" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="C427" t="s">
         <v>685</v>
       </c>
       <c r="D427" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="E427" t="s">
         <v>25</v>
@@ -23979,16 +24353,16 @@
     </row>
     <row r="428" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="B428" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="C428" t="s">
         <v>685</v>
       </c>
       <c r="D428" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="E428" t="s">
         <v>25</v>
@@ -24017,16 +24391,16 @@
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="B429" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="C429" t="s">
         <v>685</v>
       </c>
       <c r="D429" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="E429" t="s">
         <v>25</v>
@@ -24055,16 +24429,16 @@
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="B430" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="C430" t="s">
         <v>685</v>
       </c>
       <c r="D430" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="E430" t="s">
         <v>25</v>
@@ -24093,16 +24467,16 @@
     </row>
     <row r="431" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="B431" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="C431" t="s">
         <v>685</v>
       </c>
       <c r="D431" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="E431" t="s">
         <v>25</v>
@@ -24131,16 +24505,16 @@
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="B432" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="C432" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D432" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="E432" t="s">
         <v>25</v>
@@ -24169,16 +24543,16 @@
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="B433" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="C433" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D433" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="E433" t="s">
         <v>25</v>
@@ -24207,16 +24581,16 @@
     </row>
     <row r="434" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>754</v>
+        <v>739</v>
       </c>
       <c r="B434" t="s">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="C434" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D434" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="E434" t="s">
         <v>25</v>
@@ -24245,16 +24619,16 @@
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>756</v>
+        <v>741</v>
       </c>
       <c r="B435" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="C435" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D435" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="E435" t="s">
         <v>25</v>
@@ -24283,16 +24657,16 @@
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>758</v>
+        <v>743</v>
       </c>
       <c r="B436" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
       <c r="C436" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D436" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="E436" t="s">
         <v>25</v>
@@ -24321,16 +24695,16 @@
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="B437" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="C437" t="s">
-        <v>750</v>
+        <v>685</v>
       </c>
       <c r="D437" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="E437" t="s">
         <v>25</v>
@@ -24359,10 +24733,10 @@
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
       <c r="B438" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="C438" t="s">
         <v>750</v>
@@ -24397,10 +24771,10 @@
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="B439" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="C439" t="s">
         <v>750</v>
@@ -24435,10 +24809,10 @@
     </row>
     <row r="440" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="B440" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="C440" t="s">
         <v>750</v>
@@ -24473,10 +24847,10 @@
     </row>
     <row r="441" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="B441" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="C441" t="s">
         <v>750</v>
@@ -24511,10 +24885,10 @@
     </row>
     <row r="442" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="B442" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="C442" t="s">
         <v>750</v>
@@ -24549,10 +24923,10 @@
     </row>
     <row r="443" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="B443" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="C443" t="s">
         <v>750</v>
@@ -24587,10 +24961,10 @@
     </row>
     <row r="444" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="B444" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="C444" t="s">
         <v>750</v>
@@ -24625,16 +24999,16 @@
     </row>
     <row r="445" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="B445" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="C445" t="s">
         <v>750</v>
       </c>
       <c r="D445" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="E445" t="s">
         <v>25</v>
@@ -24663,16 +25037,16 @@
     </row>
     <row r="446" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
       <c r="B446" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="C446" t="s">
         <v>750</v>
       </c>
       <c r="D446" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="E446" t="s">
         <v>25</v>
@@ -24701,16 +25075,16 @@
     </row>
     <row r="447" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="B447" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="C447" t="s">
         <v>750</v>
       </c>
       <c r="D447" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="E447" t="s">
         <v>25</v>
@@ -24739,16 +25113,16 @@
     </row>
     <row r="448" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="B448" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
       <c r="C448" t="s">
         <v>750</v>
       </c>
       <c r="D448" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="E448" t="s">
         <v>25</v>
@@ -24777,16 +25151,16 @@
     </row>
     <row r="449" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="B449" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="C449" t="s">
         <v>750</v>
       </c>
       <c r="D449" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="E449" t="s">
         <v>25</v>
@@ -24815,16 +25189,16 @@
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
       <c r="B450" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="C450" t="s">
         <v>750</v>
       </c>
       <c r="D450" t="s">
-        <v>200</v>
+        <v>751</v>
       </c>
       <c r="E450" t="s">
         <v>25</v>
@@ -24853,16 +25227,16 @@
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="B451" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="C451" t="s">
         <v>750</v>
       </c>
       <c r="D451" t="s">
-        <v>200</v>
+        <v>778</v>
       </c>
       <c r="E451" t="s">
         <v>25</v>
@@ -24891,16 +25265,16 @@
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="B452" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="C452" t="s">
         <v>750</v>
       </c>
       <c r="D452" t="s">
-        <v>200</v>
+        <v>778</v>
       </c>
       <c r="E452" t="s">
         <v>25</v>
@@ -24929,16 +25303,16 @@
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="B453" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="C453" t="s">
         <v>750</v>
       </c>
       <c r="D453" t="s">
-        <v>795</v>
+        <v>778</v>
       </c>
       <c r="E453" t="s">
         <v>25</v>
@@ -24967,16 +25341,16 @@
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="B454" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="C454" t="s">
         <v>750</v>
       </c>
       <c r="D454" t="s">
-        <v>795</v>
+        <v>778</v>
       </c>
       <c r="E454" t="s">
         <v>25</v>
@@ -25005,16 +25379,16 @@
     </row>
     <row r="455" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="B455" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
       <c r="C455" t="s">
         <v>750</v>
       </c>
       <c r="D455" t="s">
-        <v>800</v>
+        <v>778</v>
       </c>
       <c r="E455" t="s">
         <v>25</v>
@@ -25043,16 +25417,16 @@
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
       <c r="B456" t="s">
-        <v>802</v>
+        <v>788</v>
       </c>
       <c r="C456" t="s">
         <v>750</v>
       </c>
       <c r="D456" t="s">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="E456" t="s">
         <v>25</v>
@@ -25081,16 +25455,16 @@
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="B457" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
       <c r="C457" t="s">
         <v>750</v>
       </c>
       <c r="D457" t="s">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="E457" t="s">
         <v>25</v>
@@ -25119,16 +25493,16 @@
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="B458" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="C458" t="s">
         <v>750</v>
       </c>
       <c r="D458" t="s">
-        <v>807</v>
+        <v>200</v>
       </c>
       <c r="E458" t="s">
         <v>25</v>
@@ -25157,16 +25531,16 @@
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
       <c r="B459" t="s">
-        <v>809</v>
+        <v>794</v>
       </c>
       <c r="C459" t="s">
         <v>750</v>
       </c>
       <c r="D459" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="E459" t="s">
         <v>25</v>
@@ -25195,16 +25569,16 @@
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="B460" t="s">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="C460" t="s">
         <v>750</v>
       </c>
       <c r="D460" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="E460" t="s">
         <v>25</v>
@@ -25233,16 +25607,16 @@
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="B461" t="s">
-        <v>813</v>
+        <v>799</v>
       </c>
       <c r="C461" t="s">
         <v>750</v>
       </c>
       <c r="D461" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="E461" t="s">
         <v>25</v>
@@ -25271,16 +25645,16 @@
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="B462" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="C462" t="s">
         <v>750</v>
       </c>
       <c r="D462" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="E462" t="s">
         <v>25</v>
@@ -25309,16 +25683,16 @@
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>816</v>
+        <v>803</v>
       </c>
       <c r="B463" t="s">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="C463" t="s">
         <v>750</v>
       </c>
       <c r="D463" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="E463" t="s">
         <v>25</v>
@@ -25347,10 +25721,10 @@
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="B464" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
       <c r="C464" t="s">
         <v>750</v>
@@ -25385,10 +25759,10 @@
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="B465" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="C465" t="s">
         <v>750</v>
@@ -25423,10 +25797,10 @@
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="B466" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="C466" t="s">
         <v>750</v>
@@ -25461,10 +25835,10 @@
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="B467" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="C467" t="s">
         <v>750</v>
@@ -25499,10 +25873,10 @@
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="B468" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="C468" t="s">
         <v>750</v>
@@ -25537,10 +25911,10 @@
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="B469" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="C469" t="s">
         <v>750</v>
@@ -25575,16 +25949,16 @@
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="B470" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="C470" t="s">
         <v>750</v>
       </c>
       <c r="D470" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="E470" t="s">
         <v>25</v>
@@ -25613,16 +25987,16 @@
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="B471" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="C471" t="s">
         <v>750</v>
       </c>
       <c r="D471" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="E471" t="s">
         <v>25</v>
@@ -25651,16 +26025,16 @@
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="B472" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="C472" t="s">
         <v>750</v>
       </c>
       <c r="D472" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="E472" t="s">
         <v>25</v>
@@ -25689,16 +26063,16 @@
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="B473" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="C473" t="s">
         <v>750</v>
       </c>
       <c r="D473" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="E473" t="s">
         <v>25</v>
@@ -25727,16 +26101,16 @@
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="B474" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="C474" t="s">
         <v>750</v>
       </c>
       <c r="D474" t="s">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="E474" t="s">
         <v>25</v>
@@ -25765,16 +26139,16 @@
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="B475" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="C475" t="s">
         <v>750</v>
       </c>
       <c r="D475" t="s">
-        <v>843</v>
+        <v>807</v>
       </c>
       <c r="E475" t="s">
         <v>25</v>
@@ -25803,16 +26177,16 @@
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="B476" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
       <c r="C476" t="s">
         <v>750</v>
       </c>
       <c r="D476" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
       <c r="E476" t="s">
         <v>25</v>
@@ -25841,16 +26215,16 @@
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="B477" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="C477" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D477" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="E477" t="s">
         <v>25</v>
@@ -25879,16 +26253,16 @@
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>850</v>
+        <v>835</v>
       </c>
       <c r="B478" t="s">
-        <v>851</v>
+        <v>836</v>
       </c>
       <c r="C478" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D478" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="E478" t="s">
         <v>25</v>
@@ -25917,16 +26291,16 @@
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="B479" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="C479" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D479" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="E479" t="s">
         <v>25</v>
@@ -25955,16 +26329,16 @@
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>854</v>
+        <v>839</v>
       </c>
       <c r="B480" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="C480" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D480" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="E480" t="s">
         <v>25</v>
@@ -25993,16 +26367,16 @@
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="B481" t="s">
-        <v>857</v>
+        <v>842</v>
       </c>
       <c r="C481" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D481" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="E481" t="s">
         <v>25</v>
@@ -26031,16 +26405,16 @@
     </row>
     <row r="482" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>858</v>
+        <v>844</v>
       </c>
       <c r="B482" t="s">
-        <v>859</v>
+        <v>845</v>
       </c>
       <c r="C482" t="s">
-        <v>848</v>
+        <v>750</v>
       </c>
       <c r="D482" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="E482" t="s">
         <v>25</v>
@@ -26069,16 +26443,16 @@
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="B483" t="s">
-        <v>861</v>
+        <v>847</v>
       </c>
       <c r="C483" t="s">
         <v>848</v>
       </c>
       <c r="D483" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="E483" t="s">
         <v>25</v>
@@ -26107,16 +26481,16 @@
     </row>
     <row r="484" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="B484" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="C484" t="s">
         <v>848</v>
       </c>
       <c r="D484" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="E484" t="s">
         <v>25</v>
@@ -26145,16 +26519,16 @@
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="B485" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="C485" t="s">
         <v>848</v>
       </c>
       <c r="D485" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="E485" t="s">
         <v>25</v>
@@ -26183,16 +26557,16 @@
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="B486" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="C486" t="s">
         <v>848</v>
       </c>
       <c r="D486" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="E486" t="s">
         <v>25</v>
@@ -26221,16 +26595,16 @@
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>869</v>
+        <v>856</v>
       </c>
       <c r="B487" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
       <c r="C487" t="s">
         <v>848</v>
       </c>
       <c r="D487" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="E487" t="s">
         <v>25</v>
@@ -26259,16 +26633,16 @@
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>871</v>
+        <v>858</v>
       </c>
       <c r="B488" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="C488" t="s">
         <v>848</v>
       </c>
       <c r="D488" t="s">
-        <v>873</v>
+        <v>849</v>
       </c>
       <c r="E488" t="s">
         <v>25</v>
@@ -26297,16 +26671,16 @@
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>874</v>
+        <v>860</v>
       </c>
       <c r="B489" t="s">
-        <v>875</v>
+        <v>861</v>
       </c>
       <c r="C489" t="s">
         <v>848</v>
       </c>
       <c r="D489" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
       <c r="E489" t="s">
         <v>25</v>
@@ -26335,16 +26709,16 @@
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="B490" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="C490" t="s">
         <v>848</v>
       </c>
       <c r="D490" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
       <c r="E490" t="s">
         <v>25</v>
@@ -26373,16 +26747,16 @@
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="B491" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="C491" t="s">
         <v>848</v>
       </c>
       <c r="D491" t="s">
-        <v>880</v>
+        <v>862</v>
       </c>
       <c r="E491" t="s">
         <v>25</v>
@@ -26411,16 +26785,16 @@
     </row>
     <row r="492" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>881</v>
+        <v>867</v>
       </c>
       <c r="B492" t="s">
-        <v>882</v>
+        <v>868</v>
       </c>
       <c r="C492" t="s">
         <v>848</v>
       </c>
       <c r="D492" t="s">
-        <v>880</v>
+        <v>862</v>
       </c>
       <c r="E492" t="s">
         <v>25</v>
@@ -26449,16 +26823,16 @@
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>883</v>
+        <v>869</v>
       </c>
       <c r="B493" t="s">
-        <v>884</v>
+        <v>870</v>
       </c>
       <c r="C493" t="s">
         <v>848</v>
       </c>
       <c r="D493" t="s">
-        <v>885</v>
+        <v>862</v>
       </c>
       <c r="E493" t="s">
         <v>25</v>
@@ -26487,16 +26861,16 @@
     </row>
     <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>886</v>
+        <v>871</v>
       </c>
       <c r="B494" t="s">
-        <v>887</v>
+        <v>872</v>
       </c>
       <c r="C494" t="s">
         <v>848</v>
       </c>
       <c r="D494" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="E494" t="s">
         <v>25</v>
@@ -26525,16 +26899,16 @@
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>888</v>
+        <v>874</v>
       </c>
       <c r="B495" t="s">
-        <v>889</v>
+        <v>875</v>
       </c>
       <c r="C495" t="s">
         <v>848</v>
       </c>
       <c r="D495" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="E495" t="s">
         <v>25</v>
@@ -26563,16 +26937,16 @@
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>890</v>
+        <v>876</v>
       </c>
       <c r="B496" t="s">
-        <v>891</v>
+        <v>877</v>
       </c>
       <c r="C496" t="s">
         <v>848</v>
       </c>
       <c r="D496" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="E496" t="s">
         <v>25</v>
@@ -26601,16 +26975,16 @@
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>892</v>
+        <v>878</v>
       </c>
       <c r="B497" t="s">
-        <v>893</v>
+        <v>879</v>
       </c>
       <c r="C497" t="s">
         <v>848</v>
       </c>
       <c r="D497" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
       <c r="E497" t="s">
         <v>25</v>
@@ -26639,16 +27013,16 @@
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>895</v>
+        <v>881</v>
       </c>
       <c r="B498" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
       <c r="C498" t="s">
         <v>848</v>
       </c>
       <c r="D498" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
       <c r="E498" t="s">
         <v>25</v>
@@ -26677,16 +27051,16 @@
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>897</v>
+        <v>883</v>
       </c>
       <c r="B499" t="s">
-        <v>898</v>
+        <v>884</v>
       </c>
       <c r="C499" t="s">
         <v>848</v>
       </c>
       <c r="D499" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="E499" t="s">
         <v>25</v>
@@ -26715,16 +27089,16 @@
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="B500" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
       <c r="C500" t="s">
         <v>848</v>
       </c>
       <c r="D500" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="E500" t="s">
         <v>25</v>
@@ -26753,16 +27127,16 @@
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="B501" t="s">
-        <v>902</v>
+        <v>889</v>
       </c>
       <c r="C501" t="s">
         <v>848</v>
       </c>
       <c r="D501" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="E501" t="s">
         <v>25</v>
@@ -26791,16 +27165,16 @@
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>903</v>
+        <v>890</v>
       </c>
       <c r="B502" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
       <c r="C502" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D502" t="s">
-        <v>25</v>
+        <v>885</v>
       </c>
       <c r="E502" t="s">
         <v>25</v>
@@ -26829,16 +27203,16 @@
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>906</v>
+        <v>892</v>
       </c>
       <c r="B503" t="s">
-        <v>907</v>
+        <v>893</v>
       </c>
       <c r="C503" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D503" t="s">
-        <v>25</v>
+        <v>894</v>
       </c>
       <c r="E503" t="s">
         <v>25</v>
@@ -26867,16 +27241,16 @@
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>908</v>
+        <v>895</v>
       </c>
       <c r="B504" t="s">
-        <v>909</v>
+        <v>896</v>
       </c>
       <c r="C504" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D504" t="s">
-        <v>25</v>
+        <v>894</v>
       </c>
       <c r="E504" t="s">
         <v>25</v>
@@ -26905,16 +27279,16 @@
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="B505" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
       <c r="C505" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D505" t="s">
-        <v>25</v>
+        <v>894</v>
       </c>
       <c r="E505" t="s">
         <v>25</v>
@@ -26943,16 +27317,16 @@
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
       <c r="B506" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
       <c r="C506" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D506" t="s">
-        <v>25</v>
+        <v>894</v>
       </c>
       <c r="E506" t="s">
         <v>25</v>
@@ -26981,16 +27355,16 @@
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="B507" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="C507" t="s">
-        <v>905</v>
+        <v>848</v>
       </c>
       <c r="D507" t="s">
-        <v>25</v>
+        <v>894</v>
       </c>
       <c r="E507" t="s">
         <v>25</v>
@@ -27019,10 +27393,10 @@
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>916</v>
+        <v>903</v>
       </c>
       <c r="B508" t="s">
-        <v>917</v>
+        <v>904</v>
       </c>
       <c r="C508" t="s">
         <v>905</v>
@@ -27057,10 +27431,10 @@
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>918</v>
+        <v>906</v>
       </c>
       <c r="B509" t="s">
-        <v>919</v>
+        <v>907</v>
       </c>
       <c r="C509" t="s">
         <v>905</v>
@@ -27095,10 +27469,10 @@
     </row>
     <row r="510" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="B510" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="C510" t="s">
         <v>905</v>
@@ -27133,10 +27507,10 @@
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>922</v>
+        <v>910</v>
       </c>
       <c r="B511" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="C511" t="s">
         <v>905</v>
@@ -27171,10 +27545,10 @@
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="B512" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="C512" t="s">
         <v>905</v>
@@ -27209,10 +27583,10 @@
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="B513" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
       <c r="C513" t="s">
         <v>905</v>
@@ -27247,10 +27621,10 @@
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>928</v>
+        <v>916</v>
       </c>
       <c r="B514" t="s">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="C514" t="s">
         <v>905</v>
@@ -27285,10 +27659,10 @@
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>930</v>
+        <v>918</v>
       </c>
       <c r="B515" t="s">
-        <v>931</v>
+        <v>919</v>
       </c>
       <c r="C515" t="s">
         <v>905</v>
@@ -27323,10 +27697,10 @@
     </row>
     <row r="516" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>932</v>
+        <v>920</v>
       </c>
       <c r="B516" t="s">
-        <v>933</v>
+        <v>921</v>
       </c>
       <c r="C516" t="s">
         <v>905</v>
@@ -27361,16 +27735,16 @@
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>934</v>
+        <v>922</v>
       </c>
       <c r="B517" t="s">
-        <v>935</v>
+        <v>923</v>
       </c>
       <c r="C517" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D517" t="s">
-        <v>937</v>
+        <v>25</v>
       </c>
       <c r="E517" t="s">
         <v>25</v>
@@ -27399,16 +27773,16 @@
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>938</v>
+        <v>924</v>
       </c>
       <c r="B518" t="s">
-        <v>939</v>
+        <v>925</v>
       </c>
       <c r="C518" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D518" t="s">
-        <v>937</v>
+        <v>25</v>
       </c>
       <c r="E518" t="s">
         <v>25</v>
@@ -27437,16 +27811,16 @@
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>940</v>
+        <v>926</v>
       </c>
       <c r="B519" t="s">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="C519" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D519" t="s">
-        <v>937</v>
+        <v>25</v>
       </c>
       <c r="E519" t="s">
         <v>25</v>
@@ -27475,16 +27849,16 @@
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>942</v>
+        <v>928</v>
       </c>
       <c r="B520" t="s">
-        <v>943</v>
+        <v>929</v>
       </c>
       <c r="C520" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D520" t="s">
-        <v>937</v>
+        <v>25</v>
       </c>
       <c r="E520" t="s">
         <v>25</v>
@@ -27513,16 +27887,16 @@
     </row>
     <row r="521" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>944</v>
+        <v>930</v>
       </c>
       <c r="B521" t="s">
-        <v>945</v>
+        <v>931</v>
       </c>
       <c r="C521" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D521" t="s">
-        <v>946</v>
+        <v>25</v>
       </c>
       <c r="E521" t="s">
         <v>25</v>
@@ -27551,16 +27925,16 @@
     </row>
     <row r="522" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>947</v>
+        <v>932</v>
       </c>
       <c r="B522" t="s">
-        <v>948</v>
+        <v>933</v>
       </c>
       <c r="C522" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="D522" t="s">
-        <v>946</v>
+        <v>25</v>
       </c>
       <c r="E522" t="s">
         <v>25</v>
@@ -27589,16 +27963,16 @@
     </row>
     <row r="523" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
       <c r="B523" t="s">
-        <v>950</v>
+        <v>935</v>
       </c>
       <c r="C523" t="s">
         <v>936</v>
       </c>
       <c r="D523" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="E523" t="s">
         <v>25</v>
@@ -27627,16 +28001,16 @@
     </row>
     <row r="524" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>951</v>
+        <v>938</v>
       </c>
       <c r="B524" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="C524" t="s">
         <v>936</v>
       </c>
       <c r="D524" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="E524" t="s">
         <v>25</v>
@@ -27665,16 +28039,16 @@
     </row>
     <row r="525" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>953</v>
+        <v>940</v>
       </c>
       <c r="B525" t="s">
-        <v>954</v>
+        <v>941</v>
       </c>
       <c r="C525" t="s">
         <v>936</v>
       </c>
       <c r="D525" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="E525" t="s">
         <v>25</v>
@@ -27703,16 +28077,16 @@
     </row>
     <row r="526" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>955</v>
+        <v>942</v>
       </c>
       <c r="B526" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="C526" t="s">
         <v>936</v>
       </c>
       <c r="D526" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="E526" t="s">
         <v>25</v>
@@ -27741,10 +28115,10 @@
     </row>
     <row r="527" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="B527" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="C527" t="s">
         <v>936</v>
@@ -27779,16 +28153,16 @@
     </row>
     <row r="528" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="B528" t="s">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="C528" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D528" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E528" t="s">
         <v>25</v>
@@ -27817,16 +28191,16 @@
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>963</v>
+        <v>949</v>
       </c>
       <c r="B529" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="C529" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D529" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E529" t="s">
         <v>25</v>
@@ -27855,16 +28229,16 @@
     </row>
     <row r="530" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>965</v>
+        <v>951</v>
       </c>
       <c r="B530" t="s">
-        <v>966</v>
+        <v>952</v>
       </c>
       <c r="C530" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D530" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E530" t="s">
         <v>25</v>
@@ -27893,16 +28267,16 @@
     </row>
     <row r="531" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>967</v>
+        <v>953</v>
       </c>
       <c r="B531" t="s">
-        <v>968</v>
+        <v>954</v>
       </c>
       <c r="C531" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D531" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E531" t="s">
         <v>25</v>
@@ -27931,16 +28305,16 @@
     </row>
     <row r="532" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>969</v>
+        <v>955</v>
       </c>
       <c r="B532" t="s">
-        <v>970</v>
+        <v>956</v>
       </c>
       <c r="C532" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D532" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E532" t="s">
         <v>25</v>
@@ -27969,16 +28343,16 @@
     </row>
     <row r="533" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>971</v>
+        <v>957</v>
       </c>
       <c r="B533" t="s">
-        <v>972</v>
+        <v>958</v>
       </c>
       <c r="C533" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D533" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="E533" t="s">
         <v>25</v>
@@ -28007,10 +28381,10 @@
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>973</v>
+        <v>959</v>
       </c>
       <c r="B534" t="s">
-        <v>974</v>
+        <v>960</v>
       </c>
       <c r="C534" t="s">
         <v>961</v>
@@ -28045,10 +28419,10 @@
     </row>
     <row r="535" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="B535" t="s">
-        <v>976</v>
+        <v>964</v>
       </c>
       <c r="C535" t="s">
         <v>961</v>
@@ -28083,16 +28457,16 @@
     </row>
     <row r="536" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>977</v>
+        <v>965</v>
       </c>
       <c r="B536" t="s">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="C536" t="s">
         <v>961</v>
       </c>
       <c r="D536" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E536" t="s">
         <v>25</v>
@@ -28121,16 +28495,16 @@
     </row>
     <row r="537" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>980</v>
+        <v>967</v>
       </c>
       <c r="B537" t="s">
-        <v>981</v>
+        <v>968</v>
       </c>
       <c r="C537" t="s">
         <v>961</v>
       </c>
       <c r="D537" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E537" t="s">
         <v>25</v>
@@ -28159,16 +28533,16 @@
     </row>
     <row r="538" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>982</v>
+        <v>969</v>
       </c>
       <c r="B538" t="s">
-        <v>983</v>
+        <v>970</v>
       </c>
       <c r="C538" t="s">
         <v>961</v>
       </c>
       <c r="D538" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E538" t="s">
         <v>25</v>
@@ -28197,16 +28571,16 @@
     </row>
     <row r="539" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>984</v>
+        <v>971</v>
       </c>
       <c r="B539" t="s">
-        <v>985</v>
+        <v>972</v>
       </c>
       <c r="C539" t="s">
         <v>961</v>
       </c>
       <c r="D539" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E539" t="s">
         <v>25</v>
@@ -28235,16 +28609,16 @@
     </row>
     <row r="540" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>986</v>
+        <v>973</v>
       </c>
       <c r="B540" t="s">
-        <v>987</v>
+        <v>974</v>
       </c>
       <c r="C540" t="s">
         <v>961</v>
       </c>
       <c r="D540" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="E540" t="s">
         <v>25</v>
@@ -28273,16 +28647,16 @@
     </row>
     <row r="541" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>988</v>
+        <v>975</v>
       </c>
       <c r="B541" t="s">
-        <v>989</v>
+        <v>976</v>
       </c>
       <c r="C541" t="s">
         <v>961</v>
       </c>
       <c r="D541" t="s">
-        <v>990</v>
+        <v>962</v>
       </c>
       <c r="E541" t="s">
         <v>25</v>
@@ -28311,16 +28685,16 @@
     </row>
     <row r="542" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>991</v>
+        <v>977</v>
       </c>
       <c r="B542" t="s">
-        <v>992</v>
+        <v>978</v>
       </c>
       <c r="C542" t="s">
         <v>961</v>
       </c>
       <c r="D542" t="s">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="E542" t="s">
         <v>25</v>
@@ -28349,16 +28723,16 @@
     </row>
     <row r="543" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>993</v>
+        <v>980</v>
       </c>
       <c r="B543" t="s">
-        <v>994</v>
+        <v>981</v>
       </c>
       <c r="C543" t="s">
         <v>961</v>
       </c>
       <c r="D543" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="E543" t="s">
         <v>25</v>
@@ -28387,16 +28761,16 @@
     </row>
     <row r="544" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>996</v>
+        <v>982</v>
       </c>
       <c r="B544" t="s">
-        <v>997</v>
+        <v>983</v>
       </c>
       <c r="C544" t="s">
         <v>961</v>
       </c>
       <c r="D544" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="E544" t="s">
         <v>25</v>
@@ -28425,16 +28799,16 @@
     </row>
     <row r="545" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>998</v>
+        <v>984</v>
       </c>
       <c r="B545" t="s">
-        <v>999</v>
+        <v>985</v>
       </c>
       <c r="C545" t="s">
         <v>961</v>
       </c>
       <c r="D545" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="E545" t="s">
         <v>25</v>
@@ -28463,16 +28837,16 @@
     </row>
     <row r="546" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="B546" t="s">
-        <v>1001</v>
+        <v>987</v>
       </c>
       <c r="C546" t="s">
         <v>961</v>
       </c>
       <c r="D546" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="E546" t="s">
         <v>25</v>
@@ -28501,16 +28875,16 @@
     </row>
     <row r="547" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1002</v>
+        <v>988</v>
       </c>
       <c r="B547" t="s">
-        <v>1003</v>
+        <v>989</v>
       </c>
       <c r="C547" t="s">
         <v>961</v>
       </c>
       <c r="D547" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="E547" t="s">
         <v>25</v>
@@ -28539,16 +28913,16 @@
     </row>
     <row r="548" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="B548" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="C548" t="s">
         <v>961</v>
       </c>
       <c r="D548" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="E548" t="s">
         <v>25</v>
@@ -28577,16 +28951,16 @@
     </row>
     <row r="549" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="B549" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="C549" t="s">
         <v>961</v>
       </c>
       <c r="D549" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="E549" t="s">
         <v>25</v>
@@ -28615,16 +28989,16 @@
     </row>
     <row r="550" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1009</v>
+        <v>996</v>
       </c>
       <c r="B550" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="C550" t="s">
         <v>961</v>
       </c>
       <c r="D550" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="E550" t="s">
         <v>25</v>
@@ -28653,16 +29027,16 @@
     </row>
     <row r="551" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1011</v>
+        <v>998</v>
       </c>
       <c r="B551" t="s">
-        <v>1012</v>
+        <v>999</v>
       </c>
       <c r="C551" t="s">
         <v>961</v>
       </c>
       <c r="D551" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="E551" t="s">
         <v>25</v>
@@ -28691,16 +29065,16 @@
     </row>
     <row r="552" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1013</v>
+        <v>1000</v>
       </c>
       <c r="B552" t="s">
-        <v>1014</v>
+        <v>1001</v>
       </c>
       <c r="C552" t="s">
         <v>961</v>
       </c>
       <c r="D552" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="E552" t="s">
         <v>25</v>
@@ -28729,16 +29103,16 @@
     </row>
     <row r="553" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1015</v>
+        <v>1002</v>
       </c>
       <c r="B553" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
       <c r="C553" t="s">
         <v>961</v>
       </c>
       <c r="D553" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="E553" t="s">
         <v>25</v>
@@ -28767,16 +29141,16 @@
     </row>
     <row r="554" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1018</v>
+        <v>1004</v>
       </c>
       <c r="B554" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
       <c r="C554" t="s">
         <v>961</v>
       </c>
       <c r="D554" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="E554" t="s">
         <v>25</v>
@@ -28805,16 +29179,16 @@
     </row>
     <row r="555" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1020</v>
+        <v>1006</v>
       </c>
       <c r="B555" t="s">
-        <v>1021</v>
+        <v>1007</v>
       </c>
       <c r="C555" t="s">
         <v>961</v>
       </c>
       <c r="D555" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="E555" t="s">
         <v>25</v>
@@ -28843,16 +29217,16 @@
     </row>
     <row r="556" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="B556" t="s">
-        <v>1023</v>
+        <v>1010</v>
       </c>
       <c r="C556" t="s">
         <v>961</v>
       </c>
       <c r="D556" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="E556" t="s">
         <v>25</v>
@@ -28881,16 +29255,16 @@
     </row>
     <row r="557" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="B557" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="C557" t="s">
         <v>961</v>
       </c>
       <c r="D557" t="s">
-        <v>1026</v>
+        <v>1008</v>
       </c>
       <c r="E557" t="s">
         <v>25</v>
@@ -28919,16 +29293,16 @@
     </row>
     <row r="558" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>1027</v>
+        <v>1013</v>
       </c>
       <c r="B558" t="s">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="C558" t="s">
         <v>961</v>
       </c>
       <c r="D558" t="s">
-        <v>1026</v>
+        <v>1008</v>
       </c>
       <c r="E558" t="s">
         <v>25</v>
@@ -28957,16 +29331,16 @@
     </row>
     <row r="559" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>1029</v>
+        <v>1015</v>
       </c>
       <c r="B559" t="s">
-        <v>1030</v>
+        <v>1016</v>
       </c>
       <c r="C559" t="s">
         <v>961</v>
       </c>
       <c r="D559" t="s">
-        <v>1026</v>
+        <v>1017</v>
       </c>
       <c r="E559" t="s">
         <v>25</v>
@@ -28995,16 +29369,16 @@
     </row>
     <row r="560" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1031</v>
+        <v>1018</v>
       </c>
       <c r="B560" t="s">
-        <v>1032</v>
+        <v>1019</v>
       </c>
       <c r="C560" t="s">
         <v>961</v>
       </c>
       <c r="D560" t="s">
-        <v>1026</v>
+        <v>1017</v>
       </c>
       <c r="E560" t="s">
         <v>25</v>
@@ -29033,16 +29407,16 @@
     </row>
     <row r="561" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1033</v>
+        <v>1020</v>
       </c>
       <c r="B561" t="s">
-        <v>1034</v>
+        <v>1021</v>
       </c>
       <c r="C561" t="s">
         <v>961</v>
       </c>
       <c r="D561" t="s">
-        <v>1035</v>
+        <v>1017</v>
       </c>
       <c r="E561" t="s">
         <v>25</v>
@@ -29071,16 +29445,16 @@
     </row>
     <row r="562" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>1036</v>
+        <v>1022</v>
       </c>
       <c r="B562" t="s">
-        <v>1037</v>
+        <v>1023</v>
       </c>
       <c r="C562" t="s">
         <v>961</v>
       </c>
       <c r="D562" t="s">
-        <v>1035</v>
+        <v>1017</v>
       </c>
       <c r="E562" t="s">
         <v>25</v>
@@ -29109,16 +29483,16 @@
     </row>
     <row r="563" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>1038</v>
+        <v>1024</v>
       </c>
       <c r="B563" t="s">
-        <v>1039</v>
+        <v>1025</v>
       </c>
       <c r="C563" t="s">
         <v>961</v>
       </c>
       <c r="D563" t="s">
-        <v>1035</v>
+        <v>1026</v>
       </c>
       <c r="E563" t="s">
         <v>25</v>
@@ -29147,16 +29521,16 @@
     </row>
     <row r="564" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>1040</v>
+        <v>1027</v>
       </c>
       <c r="B564" t="s">
-        <v>1041</v>
+        <v>1028</v>
       </c>
       <c r="C564" t="s">
         <v>961</v>
       </c>
       <c r="D564" t="s">
-        <v>1035</v>
+        <v>1026</v>
       </c>
       <c r="E564" t="s">
         <v>25</v>
@@ -29185,16 +29559,16 @@
     </row>
     <row r="565" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>1042</v>
+        <v>1029</v>
       </c>
       <c r="B565" t="s">
-        <v>1043</v>
+        <v>1030</v>
       </c>
       <c r="C565" t="s">
         <v>961</v>
       </c>
       <c r="D565" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="E565" t="s">
         <v>25</v>
@@ -29223,16 +29597,16 @@
     </row>
     <row r="566" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>1045</v>
+        <v>1031</v>
       </c>
       <c r="B566" t="s">
-        <v>1046</v>
+        <v>1032</v>
       </c>
       <c r="C566" t="s">
         <v>961</v>
       </c>
       <c r="D566" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="E566" t="s">
         <v>25</v>
@@ -29261,16 +29635,16 @@
     </row>
     <row r="567" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>1047</v>
+        <v>1033</v>
       </c>
       <c r="B567" t="s">
-        <v>1048</v>
+        <v>1034</v>
       </c>
       <c r="C567" t="s">
         <v>961</v>
       </c>
       <c r="D567" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="E567" t="s">
         <v>25</v>
@@ -29299,16 +29673,16 @@
     </row>
     <row r="568" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>1049</v>
+        <v>1036</v>
       </c>
       <c r="B568" t="s">
-        <v>1050</v>
+        <v>1037</v>
       </c>
       <c r="C568" t="s">
         <v>961</v>
       </c>
       <c r="D568" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="E568" t="s">
         <v>25</v>
@@ -29337,16 +29711,16 @@
     </row>
     <row r="569" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>1051</v>
+        <v>1038</v>
       </c>
       <c r="B569" t="s">
-        <v>1052</v>
+        <v>1039</v>
       </c>
       <c r="C569" t="s">
         <v>961</v>
       </c>
       <c r="D569" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="E569" t="s">
         <v>25</v>
@@ -29375,39 +29749,267 @@
     </row>
     <row r="570" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>1053</v>
+        <v>1040</v>
       </c>
       <c r="B570" t="s">
-        <v>1054</v>
+        <v>1041</v>
       </c>
       <c r="C570" t="s">
         <v>961</v>
       </c>
       <c r="D570" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E570" t="s">
+        <v>25</v>
+      </c>
+      <c r="F570" t="s">
+        <v>25</v>
+      </c>
+      <c r="G570" t="s">
+        <v>25</v>
+      </c>
+      <c r="H570" t="s">
+        <v>19</v>
+      </c>
+      <c r="I570" t="s">
+        <v>25</v>
+      </c>
+      <c r="J570" t="s">
+        <v>25</v>
+      </c>
+      <c r="K570" t="s">
+        <v>25</v>
+      </c>
+      <c r="L570" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C571" t="s">
+        <v>961</v>
+      </c>
+      <c r="D571" t="s">
         <v>1044</v>
       </c>
-      <c r="E570" t="s">
-        <v>25</v>
-      </c>
-      <c r="F570" t="s">
-        <v>25</v>
-      </c>
-      <c r="G570" t="s">
-        <v>25</v>
-      </c>
-      <c r="H570" t="s">
-        <v>19</v>
-      </c>
-      <c r="I570" t="s">
-        <v>25</v>
-      </c>
-      <c r="J570" t="s">
-        <v>25</v>
-      </c>
-      <c r="K570" t="s">
-        <v>25</v>
-      </c>
-      <c r="L570" t="s">
+      <c r="E571" t="s">
+        <v>25</v>
+      </c>
+      <c r="F571" t="s">
+        <v>25</v>
+      </c>
+      <c r="G571" t="s">
+        <v>25</v>
+      </c>
+      <c r="H571" t="s">
+        <v>19</v>
+      </c>
+      <c r="I571" t="s">
+        <v>25</v>
+      </c>
+      <c r="J571" t="s">
+        <v>25</v>
+      </c>
+      <c r="K571" t="s">
+        <v>25</v>
+      </c>
+      <c r="L571" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C572" t="s">
+        <v>961</v>
+      </c>
+      <c r="D572" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E572" t="s">
+        <v>25</v>
+      </c>
+      <c r="F572" t="s">
+        <v>25</v>
+      </c>
+      <c r="G572" t="s">
+        <v>25</v>
+      </c>
+      <c r="H572" t="s">
+        <v>19</v>
+      </c>
+      <c r="I572" t="s">
+        <v>25</v>
+      </c>
+      <c r="J572" t="s">
+        <v>25</v>
+      </c>
+      <c r="K572" t="s">
+        <v>25</v>
+      </c>
+      <c r="L572" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C573" t="s">
+        <v>961</v>
+      </c>
+      <c r="D573" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E573" t="s">
+        <v>25</v>
+      </c>
+      <c r="F573" t="s">
+        <v>25</v>
+      </c>
+      <c r="G573" t="s">
+        <v>25</v>
+      </c>
+      <c r="H573" t="s">
+        <v>19</v>
+      </c>
+      <c r="I573" t="s">
+        <v>25</v>
+      </c>
+      <c r="J573" t="s">
+        <v>25</v>
+      </c>
+      <c r="K573" t="s">
+        <v>25</v>
+      </c>
+      <c r="L573" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C574" t="s">
+        <v>961</v>
+      </c>
+      <c r="D574" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E574" t="s">
+        <v>25</v>
+      </c>
+      <c r="F574" t="s">
+        <v>25</v>
+      </c>
+      <c r="G574" t="s">
+        <v>25</v>
+      </c>
+      <c r="H574" t="s">
+        <v>19</v>
+      </c>
+      <c r="I574" t="s">
+        <v>25</v>
+      </c>
+      <c r="J574" t="s">
+        <v>25</v>
+      </c>
+      <c r="K574" t="s">
+        <v>25</v>
+      </c>
+      <c r="L574" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B575" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C575" t="s">
+        <v>961</v>
+      </c>
+      <c r="D575" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E575" t="s">
+        <v>25</v>
+      </c>
+      <c r="F575" t="s">
+        <v>25</v>
+      </c>
+      <c r="G575" t="s">
+        <v>25</v>
+      </c>
+      <c r="H575" t="s">
+        <v>19</v>
+      </c>
+      <c r="I575" t="s">
+        <v>25</v>
+      </c>
+      <c r="J575" t="s">
+        <v>25</v>
+      </c>
+      <c r="K575" t="s">
+        <v>25</v>
+      </c>
+      <c r="L575" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C576" t="s">
+        <v>961</v>
+      </c>
+      <c r="D576" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E576" t="s">
+        <v>25</v>
+      </c>
+      <c r="F576" t="s">
+        <v>25</v>
+      </c>
+      <c r="G576" t="s">
+        <v>25</v>
+      </c>
+      <c r="H576" t="s">
+        <v>19</v>
+      </c>
+      <c r="I576" t="s">
+        <v>25</v>
+      </c>
+      <c r="J576" t="s">
+        <v>25</v>
+      </c>
+      <c r="K576" t="s">
+        <v>25</v>
+      </c>
+      <c r="L576" t="s">
         <v>25</v>
       </c>
     </row>
@@ -29416,7 +30018,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 G38:L38 B39:L39 B37:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 A11:D12 F10:F12 J10:L12 H10:H12 B17:D18 F17:F18 H17:H18 J17:L17 K18:L18 A28:G28 L21 F22:F24 J22:L24 A33:D36 L33 A21:D25 H21:H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F34:F36 J34:L36 H33:H36 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67:A68 J67:L68 J72:L73 F72 F73:G73 F67:G68 C67:D68 H72 A72:A74 A84 I84:L84 C72:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87 A91:D91 F91 H91:L91 A97:G99 L98 A96:D96 F96 H96:L96 A122:D122 I97:L97 I98:J98 I99:L99 A101:D101 F101 A104:D104 H104:I104 J101:L101 H101 L104 A109:D109 H109:I109 L109 A113:G113 I113:L113 A117 F117 C117:D117 A121 C121:D121 F121 J117:L117 J121:L121 A138:D138 A126:D126 K126:L126 H117 H121 H122:I122 L122 H126:I126 A127:D127 H127:I127 L127 A128:G128 I128:L128 A130:D130 F130 H130:L130 A131:G131 I131:L131 A132:G132 I132:L132 A134:D134 F134 H134:L134 A143:L570 A142:D142 F142 H138 J138:L138 H142:L142" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 G38:L38 B39:L39 B37:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 A11:D12 F10:F12 J10:L12 H10:H12 B17:D18 F17:F18 H17:H18 J17:L17 K18:L18 A28:G28 L21 F22:F24 J22:L24 A33:D36 L33 A21:D25 H21:H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F34:F36 J34:L36 H33:H36 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67:A68 J67:L68 J72:L73 F72 F73:G73 F67:G68 C67:D68 H72 A72:A74 A84 I84:L84 C72:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87 A91:D91 F91 H91:L91 A97:G99 L98 A96:D96 F96 H96:L96 A122:D122 I97:L97 I98:J98 I99:L99 A101:D101 F101 A104:D104 H104:I104 J101:L101 H101 L104 A109:D109 H109:I109 L109 A113:G113 I113:L113 A117 F117 C117:D117 A121 C121:D121 F121 J117:L117 J121:L121 A138:D138 A126:D126 K126:L126 H117 H121 H122:I122 L122 H126:I126 A127:D127 H127:I127 L127 A128:G128 I128:L128 A130:D130 F130 H130:L130 A131:G131 I131:L131 A132:G132 I132:L132 A134:D134 F134 H134:L134 A152:L154 A142:D142 F142 H138 J138:L138 H142:L142 A143:G143 I143:L143 A144:D144 H144:I144 L144 A151:D151 F151 H151:L151 A157:L576 A155:F155 H155:L155 A156:F156 H156:L156" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1165" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0A9E820-9F36-4AE2-8422-6D08439580EC}"/>
+  <xr:revisionPtr revIDLastSave="1221" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09D6B380-A4CB-4D82-ACFB-610A96CD39E8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7841" uniqueCount="1379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7964" uniqueCount="1394">
   <si>
     <t>Codigo</t>
   </si>
@@ -11441,6 +11441,402 @@
 Revisar periódicamente los frenos y mecanismos de ajuste.
 Utilizar siempre bajo la supervisión de un adulto.</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Organizador Esquinero Multiusos de 4 Niveles</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> es la solución perfecta para mantener cada espacio de tu hogar ordenado y funcional. Su diseño esquinero aprovecha al máximo los rincones, permitiendo almacenar productos de baño, cocina, lavandería u otros artículos de uso diario sin ocupar demasiado espacio.
+Fabricado con materiales resistentes y de fácil limpieza, cuenta con cuatro amplios niveles para organizar jabones, champús, cremas, productos de aseo, condimentos y mucho más. Su instalación es sencilla y no requiere herramientas, convirtiéndose en una opción práctica para cualquier ambiente.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/hogar/esquinerabaño/esquinabaño.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/hogar/esquinerabaño/esquinabaño2.webp</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Organizador Esquinero Multiusos de 4 Niveles</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ideal para aprovechar al máximo los espacios pequeños. Perfecto para baños, cocinas, lavanderías o cualquier rincón del hogar, brindando mayor organización con un diseño práctico, resistente y de fácil instalación.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Tipo: Organizador esquinero multiusos.
+Niveles: 4 bandejas.
+Material: Plástico resistente.
+Color: Blanco.
+Instalación: Fácil ensamblaje, sin herramientas.
+Uso: Interior.
+Ideal para: Baños, cocinas, lavanderías, habitaciones y oficinas.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Diseño esquinero que optimiza el espacio.
+Cuatro niveles para una mejor organización.
+Material resistente a la humedad y de fácil limpieza.
+Instalación rápida y sencilla.
+Diseño moderno que combina con diferentes estilos de decoración.
+Ideal para mantener organizados artículos de uso diario.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Contenido del empaque:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1 Organizador esquinero de 4 niveles.
+Piezas para ensamblaje.
+Manual de instalación.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Importante:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Las medidas y acabados pueden presentar ligeras variaciones según el lote de fabricación. Este producto requiere ensamblaje. Se recomienda instalarlo sobre una superficie firme y distribuir el peso de manera uniforme para garantizar una mayor estabilidad.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Limpiar con un paño húmedo y jabón suave.
+No utilizar productos abrasivos.
+No exceder la capacidad de carga recomendada.
+Distribuir el peso de forma uniforme entre los niveles.
+Mantener en una superficie estable y nivelada.
+Evitar golpes fuertes o exposición prolongada al sol para conservar su apariencia.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Carrito Organizador Multiusos de 3 Niveles</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> está diseñado para ofrecer mayor organización y funcionalidad en cualquier espacio del hogar u oficina. Gracias a su estructura metálica resistente y sus amplias bandejas, permite almacenar todo tipo de artículos manteniéndolos siempre al alcance.
+Sus ruedas giratorias de 360° con sistema de freno facilitan el desplazamiento entre diferentes ambientes, mientras que su diseño compacto aprovecha al máximo espacios reducidos. Es ideal para organizar productos de cocina, artículos de baño, herramientas, cosméticos, juguetes, útiles de oficina y mucho más.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Carrito Organizador Multiusos Metálico de 3 Niveles </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>con ruedas giratorias, ideal para mantener cualquier espacio organizado. Su diseño moderno, resistente y fácil de mover lo convierte en la solución perfecta para cocina, baño, oficina, lavandería o habitación.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Tipo: Carrito organizador multiusos.
+Niveles: 3 bandejas.
+Material de la estructura: Metal.
+Material de las bandejas: Plástico ABS resistente.
+Ruedas: 4 ruedas giratorias 360° con freno.
+Capacidad de carga: Hasta 20 kg por nivel.
+Medidas aproximadas: 86 × 36 × 42 cm.
+Uso: Interior.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Tres amplios niveles para una mejor organización.
+Estructura metálica resistente y duradera.
+Bandejas de ABS fáciles de limpiar.
+Ruedas giratorias con freno para mayor movilidad y estabilidad.
+Diseño compacto que optimiza el espacio.
+Fácil de ensamblar y mantener.
+Ideal para cocina, baño, oficina, lavandería, habitación o salón de belleza.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Contenido del empaque:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1 Carrito organizador de 3 niveles.
+4 Ruedas giratorias con freno.
+Accesorios para ensamblaje.
+Manual de instalación.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Importante:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Las medidas y acabados pueden presentar ligeras variaciones según el lote de fabricación. El producto requiere ensamblaje. Se recomienda distribuir el peso de manera uniforme entre las bandejas y bloquear las ruedas cuando el carrito permanezca en una posición fija para mayor seguridad.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Limpiar con un paño húmedo y jabón suave.
+No utilizar productos abrasivos o corrosivos.
+Distribuir el peso uniformemente para prolongar la vida útil.
+Revisar periódicamente el ajuste de las ruedas y tornillos.
+Evitar la exposición prolongada al agua o ambientes altamente corrosivos.
+Utilizar sobre superficies firmes y niveladas para un mejor desempeño.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/hogar/carroestante/estante.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/hogar/carroestante/estante3.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/hogar/carroestante/estante4.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/hogar/carroestante/estante5.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/hogar/carroestante/estante6.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/hogar/carroestante/estante7.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/hogar/carroestante/estante2.webp</t>
   </si>
 </sst>
 </file>
@@ -11836,7 +12232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L606"/>
+  <dimension ref="A1:L613"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -20021,7 +20417,7 @@
         <v>25</v>
       </c>
       <c r="H221" t="s">
-        <v>19</v>
+        <v>1125</v>
       </c>
       <c r="I221" t="s">
         <v>25</v>
@@ -20059,7 +20455,7 @@
         <v>25</v>
       </c>
       <c r="H222" t="s">
-        <v>19</v>
+        <v>1125</v>
       </c>
       <c r="I222" t="s">
         <v>25</v>
@@ -20097,7 +20493,7 @@
         <v>25</v>
       </c>
       <c r="H223" t="s">
-        <v>19</v>
+        <v>1125</v>
       </c>
       <c r="I223" t="s">
         <v>25</v>
@@ -20132,7 +20528,7 @@
         <v>25</v>
       </c>
       <c r="H224" t="s">
-        <v>19</v>
+        <v>1125</v>
       </c>
       <c r="I224" t="s">
         <v>25</v>
@@ -20167,7 +20563,7 @@
         <v>25</v>
       </c>
       <c r="H225" t="s">
-        <v>19</v>
+        <v>1125</v>
       </c>
       <c r="I225" t="s">
         <v>25</v>
@@ -20205,7 +20601,7 @@
         <v>25</v>
       </c>
       <c r="H226" t="s">
-        <v>19</v>
+        <v>1125</v>
       </c>
       <c r="I226" t="s">
         <v>25</v>
@@ -20243,7 +20639,7 @@
         <v>25</v>
       </c>
       <c r="H227" t="s">
-        <v>19</v>
+        <v>1125</v>
       </c>
       <c r="I227" t="s">
         <v>25</v>
@@ -20271,14 +20667,14 @@
       <c r="D228" t="s">
         <v>238</v>
       </c>
-      <c r="E228" t="s">
-        <v>25</v>
-      </c>
-      <c r="F228" t="s">
-        <v>25</v>
+      <c r="E228">
+        <v>65956</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>1379</v>
       </c>
       <c r="G228" t="s">
-        <v>25</v>
+        <v>1380</v>
       </c>
       <c r="H228" t="s">
         <v>19</v>
@@ -20287,10 +20683,10 @@
         <v>25</v>
       </c>
       <c r="J228" t="s">
-        <v>25</v>
-      </c>
-      <c r="K228" t="s">
-        <v>25</v>
+        <v>1382</v>
+      </c>
+      <c r="K228" s="1" t="s">
+        <v>1383</v>
       </c>
       <c r="L228" t="s">
         <v>25</v>
@@ -20298,10 +20694,10 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B229" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C229" t="s">
         <v>237</v>
@@ -20309,14 +20705,14 @@
       <c r="D229" t="s">
         <v>238</v>
       </c>
-      <c r="E229" t="s">
-        <v>25</v>
+      <c r="E229">
+        <v>65956</v>
       </c>
       <c r="F229" t="s">
         <v>25</v>
       </c>
       <c r="G229" t="s">
-        <v>25</v>
+        <v>1381</v>
       </c>
       <c r="H229" t="s">
         <v>19</v>
@@ -20336,10 +20732,10 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B230" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C230" t="s">
         <v>237</v>
@@ -20347,14 +20743,14 @@
       <c r="D230" t="s">
         <v>238</v>
       </c>
-      <c r="E230" t="s">
-        <v>25</v>
-      </c>
-      <c r="F230" t="s">
-        <v>25</v>
+      <c r="E230">
+        <v>135979</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>1384</v>
       </c>
       <c r="G230" t="s">
-        <v>25</v>
+        <v>1387</v>
       </c>
       <c r="H230" t="s">
         <v>19</v>
@@ -20363,10 +20759,10 @@
         <v>25</v>
       </c>
       <c r="J230" t="s">
-        <v>25</v>
-      </c>
-      <c r="K230" t="s">
-        <v>25</v>
+        <v>1385</v>
+      </c>
+      <c r="K230" s="1" t="s">
+        <v>1386</v>
       </c>
       <c r="L230" t="s">
         <v>25</v>
@@ -20374,10 +20770,10 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B231" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C231" t="s">
         <v>237</v>
@@ -20385,14 +20781,14 @@
       <c r="D231" t="s">
         <v>238</v>
       </c>
-      <c r="E231" t="s">
-        <v>25</v>
+      <c r="E231">
+        <v>135979</v>
       </c>
       <c r="F231" t="s">
         <v>25</v>
       </c>
       <c r="G231" t="s">
-        <v>25</v>
+        <v>1393</v>
       </c>
       <c r="H231" t="s">
         <v>19</v>
@@ -20412,10 +20808,10 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B232" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C232" t="s">
         <v>237</v>
@@ -20423,14 +20819,14 @@
       <c r="D232" t="s">
         <v>238</v>
       </c>
-      <c r="E232" t="s">
-        <v>25</v>
+      <c r="E232">
+        <v>135979</v>
       </c>
       <c r="F232" t="s">
         <v>25</v>
       </c>
       <c r="G232" t="s">
-        <v>25</v>
+        <v>1388</v>
       </c>
       <c r="H232" t="s">
         <v>19</v>
@@ -20450,10 +20846,10 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B233" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C233" t="s">
         <v>237</v>
@@ -20461,14 +20857,14 @@
       <c r="D233" t="s">
         <v>238</v>
       </c>
-      <c r="E233" t="s">
-        <v>25</v>
+      <c r="E233">
+        <v>135979</v>
       </c>
       <c r="F233" t="s">
         <v>25</v>
       </c>
       <c r="G233" t="s">
-        <v>25</v>
+        <v>1389</v>
       </c>
       <c r="H233" t="s">
         <v>19</v>
@@ -20488,10 +20884,10 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B234" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C234" t="s">
         <v>237</v>
@@ -20499,14 +20895,14 @@
       <c r="D234" t="s">
         <v>238</v>
       </c>
-      <c r="E234" t="s">
-        <v>25</v>
+      <c r="E234">
+        <v>135979</v>
       </c>
       <c r="F234" t="s">
         <v>25</v>
       </c>
       <c r="G234" t="s">
-        <v>25</v>
+        <v>1390</v>
       </c>
       <c r="H234" t="s">
         <v>19</v>
@@ -20526,10 +20922,10 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B235" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C235" t="s">
         <v>237</v>
@@ -20537,14 +20933,14 @@
       <c r="D235" t="s">
         <v>238</v>
       </c>
-      <c r="E235" t="s">
-        <v>25</v>
+      <c r="E235">
+        <v>135979</v>
       </c>
       <c r="F235" t="s">
         <v>25</v>
       </c>
       <c r="G235" t="s">
-        <v>25</v>
+        <v>1391</v>
       </c>
       <c r="H235" t="s">
         <v>19</v>
@@ -20564,10 +20960,10 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="B236" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C236" t="s">
         <v>237</v>
@@ -20575,14 +20971,14 @@
       <c r="D236" t="s">
         <v>238</v>
       </c>
-      <c r="E236" t="s">
-        <v>25</v>
+      <c r="E236">
+        <v>135979</v>
       </c>
       <c r="F236" t="s">
         <v>25</v>
       </c>
       <c r="G236" t="s">
-        <v>25</v>
+        <v>1392</v>
       </c>
       <c r="H236" t="s">
         <v>19</v>
@@ -20602,10 +20998,10 @@
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="B237" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="C237" t="s">
         <v>237</v>
@@ -20640,10 +21036,10 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="B238" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="C238" t="s">
         <v>237</v>
@@ -20678,10 +21074,10 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B239" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="C239" t="s">
         <v>237</v>
@@ -20716,10 +21112,10 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="B240" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="C240" t="s">
         <v>237</v>
@@ -20754,10 +21150,10 @@
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B241" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C241" t="s">
         <v>237</v>
@@ -20792,10 +21188,10 @@
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="B242" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="C242" t="s">
         <v>237</v>
@@ -20830,10 +21226,10 @@
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="B243" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="C243" t="s">
         <v>237</v>
@@ -20868,10 +21264,10 @@
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B244" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="C244" t="s">
         <v>237</v>
@@ -20906,10 +21302,10 @@
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="B245" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="C245" t="s">
         <v>237</v>
@@ -20944,10 +21340,10 @@
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="B246" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="C246" t="s">
         <v>237</v>
@@ -20982,10 +21378,10 @@
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B247" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="C247" t="s">
         <v>237</v>
@@ -21008,9 +21404,6 @@
       <c r="I247" t="s">
         <v>25</v>
       </c>
-      <c r="J247" t="s">
-        <v>25</v>
-      </c>
       <c r="K247" t="s">
         <v>25</v>
       </c>
@@ -21020,10 +21413,10 @@
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B248" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="C248" t="s">
         <v>237</v>
@@ -21058,10 +21451,10 @@
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B249" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="C249" t="s">
         <v>237</v>
@@ -21096,10 +21489,10 @@
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="B250" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="C250" t="s">
         <v>237</v>
@@ -21134,10 +21527,10 @@
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="B251" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="C251" t="s">
         <v>237</v>
@@ -21172,10 +21565,10 @@
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="B252" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C252" t="s">
         <v>237</v>
@@ -21210,10 +21603,10 @@
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="B253" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="C253" t="s">
         <v>237</v>
@@ -21248,10 +21641,10 @@
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B254" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="C254" t="s">
         <v>237</v>
@@ -21286,10 +21679,10 @@
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="B255" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="C255" t="s">
         <v>237</v>
@@ -21324,10 +21717,10 @@
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B256" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="C256" t="s">
         <v>237</v>
@@ -21362,10 +21755,10 @@
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="B257" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="C257" t="s">
         <v>237</v>
@@ -21400,10 +21793,10 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B258" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="C258" t="s">
         <v>237</v>
@@ -21438,16 +21831,16 @@
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="B259" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="C259" t="s">
         <v>237</v>
       </c>
       <c r="D259" t="s">
-        <v>315</v>
+        <v>238</v>
       </c>
       <c r="E259" t="s">
         <v>25</v>
@@ -21476,16 +21869,16 @@
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="B260" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="C260" t="s">
         <v>237</v>
       </c>
       <c r="D260" t="s">
-        <v>315</v>
+        <v>238</v>
       </c>
       <c r="E260" t="s">
         <v>25</v>
@@ -21514,16 +21907,16 @@
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="B261" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="C261" t="s">
         <v>237</v>
       </c>
       <c r="D261" t="s">
-        <v>315</v>
+        <v>238</v>
       </c>
       <c r="E261" t="s">
         <v>25</v>
@@ -21552,16 +21945,16 @@
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="B262" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="C262" t="s">
         <v>237</v>
       </c>
       <c r="D262" t="s">
-        <v>315</v>
+        <v>238</v>
       </c>
       <c r="E262" t="s">
         <v>25</v>
@@ -21590,16 +21983,16 @@
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="B263" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="C263" t="s">
         <v>237</v>
       </c>
       <c r="D263" t="s">
-        <v>315</v>
+        <v>238</v>
       </c>
       <c r="E263" t="s">
         <v>25</v>
@@ -21628,16 +22021,16 @@
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="B264" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="C264" t="s">
         <v>237</v>
       </c>
       <c r="D264" t="s">
-        <v>315</v>
+        <v>238</v>
       </c>
       <c r="E264" t="s">
         <v>25</v>
@@ -21666,16 +22059,16 @@
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="B265" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="C265" t="s">
         <v>237</v>
       </c>
       <c r="D265" t="s">
-        <v>315</v>
+        <v>238</v>
       </c>
       <c r="E265" t="s">
         <v>25</v>
@@ -21704,10 +22097,10 @@
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="B266" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="C266" t="s">
         <v>237</v>
@@ -21742,10 +22135,10 @@
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="B267" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="C267" t="s">
         <v>237</v>
@@ -21780,10 +22173,10 @@
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="B268" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C268" t="s">
         <v>237</v>
@@ -21818,16 +22211,16 @@
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B269" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="C269" t="s">
         <v>237</v>
       </c>
       <c r="D269" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="E269" t="s">
         <v>25</v>
@@ -21856,16 +22249,16 @@
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="B270" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="C270" t="s">
         <v>237</v>
       </c>
       <c r="D270" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="E270" t="s">
         <v>25</v>
@@ -21894,16 +22287,16 @@
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="B271" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="C271" t="s">
         <v>237</v>
       </c>
       <c r="D271" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="E271" t="s">
         <v>25</v>
@@ -21932,16 +22325,16 @@
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="B272" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="C272" t="s">
         <v>237</v>
       </c>
       <c r="D272" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="E272" t="s">
         <v>25</v>
@@ -21970,16 +22363,16 @@
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="B273" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="C273" t="s">
         <v>237</v>
       </c>
       <c r="D273" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="E273" t="s">
         <v>25</v>
@@ -22008,16 +22401,16 @@
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="B274" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="C274" t="s">
         <v>237</v>
       </c>
       <c r="D274" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="E274" t="s">
         <v>25</v>
@@ -22046,16 +22439,16 @@
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="B275" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="C275" t="s">
         <v>237</v>
       </c>
       <c r="D275" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="E275" t="s">
         <v>25</v>
@@ -22084,16 +22477,16 @@
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="B276" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C276" t="s">
         <v>237</v>
       </c>
       <c r="D276" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="E276" t="s">
         <v>25</v>
@@ -22122,16 +22515,16 @@
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="B277" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="C277" t="s">
         <v>237</v>
       </c>
       <c r="D277" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="E277" t="s">
         <v>25</v>
@@ -22160,16 +22553,16 @@
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="B278" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="C278" t="s">
         <v>237</v>
       </c>
       <c r="D278" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="E278" t="s">
         <v>25</v>
@@ -22198,16 +22591,16 @@
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="B279" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C279" t="s">
         <v>237</v>
       </c>
       <c r="D279" t="s">
-        <v>223</v>
+        <v>343</v>
       </c>
       <c r="E279" t="s">
         <v>25</v>
@@ -22236,16 +22629,16 @@
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="B280" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="C280" t="s">
         <v>237</v>
       </c>
       <c r="D280" t="s">
-        <v>223</v>
+        <v>343</v>
       </c>
       <c r="E280" t="s">
         <v>25</v>
@@ -22274,16 +22667,16 @@
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="B281" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="C281" t="s">
         <v>237</v>
       </c>
       <c r="D281" t="s">
-        <v>223</v>
+        <v>343</v>
       </c>
       <c r="E281" t="s">
         <v>25</v>
@@ -22312,16 +22705,16 @@
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="B282" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="C282" t="s">
         <v>237</v>
       </c>
       <c r="D282" t="s">
-        <v>223</v>
+        <v>343</v>
       </c>
       <c r="E282" t="s">
         <v>25</v>
@@ -22350,16 +22743,16 @@
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B283" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="C283" t="s">
         <v>237</v>
       </c>
       <c r="D283" t="s">
-        <v>223</v>
+        <v>343</v>
       </c>
       <c r="E283" t="s">
         <v>25</v>
@@ -22388,16 +22781,16 @@
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="B284" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="C284" t="s">
         <v>237</v>
       </c>
       <c r="D284" t="s">
-        <v>223</v>
+        <v>343</v>
       </c>
       <c r="E284" t="s">
         <v>25</v>
@@ -22426,16 +22819,16 @@
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="B285" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C285" t="s">
         <v>237</v>
       </c>
       <c r="D285" t="s">
-        <v>223</v>
+        <v>343</v>
       </c>
       <c r="E285" t="s">
         <v>25</v>
@@ -22464,10 +22857,10 @@
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="B286" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="C286" t="s">
         <v>237</v>
@@ -22502,10 +22895,10 @@
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="B287" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C287" t="s">
         <v>237</v>
@@ -22540,10 +22933,10 @@
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="B288" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="C288" t="s">
         <v>237</v>
@@ -22578,10 +22971,10 @@
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="B289" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C289" t="s">
         <v>237</v>
@@ -22616,10 +23009,10 @@
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B290" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C290" t="s">
         <v>237</v>
@@ -22654,10 +23047,10 @@
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="B291" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C291" t="s">
         <v>237</v>
@@ -22692,10 +23085,10 @@
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="B292" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C292" t="s">
         <v>237</v>
@@ -22730,10 +23123,10 @@
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B293" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C293" t="s">
         <v>237</v>
@@ -22768,10 +23161,10 @@
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B294" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="C294" t="s">
         <v>237</v>
@@ -22806,10 +23199,10 @@
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B295" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C295" t="s">
         <v>237</v>
@@ -22844,10 +23237,10 @@
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B296" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="C296" t="s">
         <v>237</v>
@@ -22882,10 +23275,10 @@
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="B297" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="C297" t="s">
         <v>237</v>
@@ -22920,10 +23313,10 @@
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="B298" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C298" t="s">
         <v>237</v>
@@ -22958,10 +23351,10 @@
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B299" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="C299" t="s">
         <v>237</v>
@@ -22996,10 +23389,10 @@
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="B300" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C300" t="s">
         <v>237</v>
@@ -23034,10 +23427,10 @@
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="B301" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="C301" t="s">
         <v>237</v>
@@ -23072,10 +23465,10 @@
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="B302" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="C302" t="s">
         <v>237</v>
@@ -23110,10 +23503,10 @@
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="B303" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="C303" t="s">
         <v>237</v>
@@ -23148,10 +23541,10 @@
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="B304" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="C304" t="s">
         <v>237</v>
@@ -23186,16 +23579,16 @@
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B305" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="C305" t="s">
         <v>237</v>
       </c>
       <c r="D305" t="s">
-        <v>405</v>
+        <v>223</v>
       </c>
       <c r="E305" t="s">
         <v>25</v>
@@ -23224,16 +23617,16 @@
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="B306" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="C306" t="s">
         <v>237</v>
       </c>
       <c r="D306" t="s">
-        <v>405</v>
+        <v>223</v>
       </c>
       <c r="E306" t="s">
         <v>25</v>
@@ -23262,16 +23655,16 @@
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="B307" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="C307" t="s">
         <v>237</v>
       </c>
       <c r="D307" t="s">
-        <v>405</v>
+        <v>223</v>
       </c>
       <c r="E307" t="s">
         <v>25</v>
@@ -23300,16 +23693,16 @@
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="B308" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C308" t="s">
         <v>237</v>
       </c>
       <c r="D308" t="s">
-        <v>405</v>
+        <v>223</v>
       </c>
       <c r="E308" t="s">
         <v>25</v>
@@ -23338,16 +23731,16 @@
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="B309" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="C309" t="s">
         <v>237</v>
       </c>
       <c r="D309" t="s">
-        <v>405</v>
+        <v>223</v>
       </c>
       <c r="E309" t="s">
         <v>25</v>
@@ -23376,16 +23769,16 @@
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="B310" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="C310" t="s">
         <v>237</v>
       </c>
       <c r="D310" t="s">
-        <v>405</v>
+        <v>223</v>
       </c>
       <c r="E310" t="s">
         <v>25</v>
@@ -23414,16 +23807,16 @@
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="B311" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="C311" t="s">
         <v>237</v>
       </c>
       <c r="D311" t="s">
-        <v>405</v>
+        <v>223</v>
       </c>
       <c r="E311" t="s">
         <v>25</v>
@@ -23452,10 +23845,10 @@
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="B312" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="C312" t="s">
         <v>237</v>
@@ -23490,10 +23883,10 @@
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="B313" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="C313" t="s">
         <v>237</v>
@@ -23528,10 +23921,10 @@
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="B314" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="C314" t="s">
         <v>237</v>
@@ -23566,10 +23959,10 @@
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="B315" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="C315" t="s">
         <v>237</v>
@@ -23604,10 +23997,10 @@
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="B316" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="C316" t="s">
         <v>237</v>
@@ -23642,10 +24035,10 @@
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="B317" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="C317" t="s">
         <v>237</v>
@@ -23680,10 +24073,10 @@
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="B318" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="C318" t="s">
         <v>237</v>
@@ -23718,10 +24111,10 @@
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="B319" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="C319" t="s">
         <v>237</v>
@@ -23756,10 +24149,10 @@
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="B320" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="C320" t="s">
         <v>237</v>
@@ -23794,10 +24187,10 @@
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="B321" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="C321" t="s">
         <v>237</v>
@@ -23832,10 +24225,10 @@
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="B322" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="C322" t="s">
         <v>237</v>
@@ -23870,10 +24263,10 @@
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="B323" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="C323" t="s">
         <v>237</v>
@@ -23908,10 +24301,10 @@
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="B324" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="C324" t="s">
         <v>237</v>
@@ -23946,10 +24339,10 @@
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="B325" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="C325" t="s">
         <v>237</v>
@@ -23984,10 +24377,10 @@
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="B326" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="C326" t="s">
         <v>237</v>
@@ -24022,10 +24415,10 @@
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="B327" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="C327" t="s">
         <v>237</v>
@@ -24060,10 +24453,10 @@
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="B328" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="C328" t="s">
         <v>237</v>
@@ -24098,10 +24491,10 @@
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="B329" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="C329" t="s">
         <v>237</v>
@@ -24136,10 +24529,10 @@
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="B330" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="C330" t="s">
         <v>237</v>
@@ -24174,16 +24567,16 @@
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="B331" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="C331" t="s">
-        <v>458</v>
+        <v>237</v>
       </c>
       <c r="D331" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="E331" t="s">
         <v>25</v>
@@ -24212,16 +24605,16 @@
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="B332" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="C332" t="s">
-        <v>458</v>
+        <v>237</v>
       </c>
       <c r="D332" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="E332" t="s">
         <v>25</v>
@@ -24250,16 +24643,16 @@
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="B333" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="C333" t="s">
-        <v>458</v>
+        <v>237</v>
       </c>
       <c r="D333" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="E333" t="s">
         <v>25</v>
@@ -24288,16 +24681,16 @@
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="B334" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="C334" t="s">
-        <v>458</v>
+        <v>237</v>
       </c>
       <c r="D334" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="E334" t="s">
         <v>25</v>
@@ -24326,16 +24719,16 @@
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="B335" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="C335" t="s">
-        <v>458</v>
+        <v>237</v>
       </c>
       <c r="D335" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="E335" t="s">
         <v>25</v>
@@ -24364,16 +24757,16 @@
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="B336" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="C336" t="s">
-        <v>458</v>
+        <v>237</v>
       </c>
       <c r="D336" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="E336" t="s">
         <v>25</v>
@@ -24402,16 +24795,16 @@
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="B337" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="C337" t="s">
-        <v>458</v>
+        <v>237</v>
       </c>
       <c r="D337" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="E337" t="s">
         <v>25</v>
@@ -24440,10 +24833,10 @@
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="B338" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="C338" t="s">
         <v>458</v>
@@ -24478,10 +24871,10 @@
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="B339" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="C339" t="s">
         <v>458</v>
@@ -24516,10 +24909,10 @@
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="B340" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="C340" t="s">
         <v>458</v>
@@ -24554,10 +24947,10 @@
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="B341" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="C341" t="s">
         <v>458</v>
@@ -24592,10 +24985,10 @@
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="B342" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="C342" t="s">
         <v>458</v>
@@ -24630,10 +25023,10 @@
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="B343" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="C343" t="s">
         <v>458</v>
@@ -24668,10 +25061,10 @@
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="B344" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C344" t="s">
         <v>458</v>
@@ -24706,10 +25099,10 @@
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="B345" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="C345" t="s">
         <v>458</v>
@@ -24744,10 +25137,10 @@
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="B346" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="C346" t="s">
         <v>458</v>
@@ -24782,10 +25175,10 @@
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="B347" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="C347" t="s">
         <v>458</v>
@@ -24820,10 +25213,10 @@
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="B348" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="C348" t="s">
         <v>458</v>
@@ -24858,10 +25251,10 @@
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="B349" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="C349" t="s">
         <v>458</v>
@@ -24896,10 +25289,10 @@
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="B350" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="C350" t="s">
         <v>458</v>
@@ -24934,10 +25327,10 @@
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="B351" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="C351" t="s">
         <v>458</v>
@@ -24972,10 +25365,10 @@
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="B352" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="C352" t="s">
         <v>458</v>
@@ -25010,10 +25403,10 @@
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="B353" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="C353" t="s">
         <v>458</v>
@@ -25048,10 +25441,10 @@
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="B354" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="C354" t="s">
         <v>458</v>
@@ -25086,10 +25479,10 @@
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="B355" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="C355" t="s">
         <v>458</v>
@@ -25124,10 +25517,10 @@
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="B356" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="C356" t="s">
         <v>458</v>
@@ -25162,10 +25555,10 @@
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="B357" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="C357" t="s">
         <v>458</v>
@@ -25200,10 +25593,10 @@
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="B358" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="C358" t="s">
         <v>458</v>
@@ -25238,10 +25631,10 @@
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="B359" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="C359" t="s">
         <v>458</v>
@@ -25276,10 +25669,10 @@
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="B360" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="C360" t="s">
         <v>458</v>
@@ -25314,10 +25707,10 @@
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="B361" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="C361" t="s">
         <v>458</v>
@@ -25352,10 +25745,10 @@
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="B362" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="C362" t="s">
         <v>458</v>
@@ -25390,10 +25783,10 @@
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="B363" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="C363" t="s">
         <v>458</v>
@@ -25428,10 +25821,10 @@
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="B364" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="C364" t="s">
         <v>458</v>
@@ -25466,10 +25859,10 @@
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="B365" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="C365" t="s">
         <v>458</v>
@@ -25504,10 +25897,10 @@
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="B366" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="C366" t="s">
         <v>458</v>
@@ -25542,10 +25935,10 @@
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="B367" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="C367" t="s">
         <v>458</v>
@@ -25580,10 +25973,10 @@
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="B368" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="C368" t="s">
         <v>458</v>
@@ -25618,10 +26011,10 @@
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="B369" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="C369" t="s">
         <v>458</v>
@@ -25656,10 +26049,10 @@
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="B370" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="C370" t="s">
         <v>458</v>
@@ -25694,10 +26087,10 @@
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="B371" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="C371" t="s">
         <v>458</v>
@@ -25732,10 +26125,10 @@
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="B372" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="C372" t="s">
         <v>458</v>
@@ -25770,10 +26163,10 @@
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="B373" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="C373" t="s">
         <v>458</v>
@@ -25808,10 +26201,10 @@
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="B374" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="C374" t="s">
         <v>458</v>
@@ -25846,10 +26239,10 @@
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="B375" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="C375" t="s">
         <v>458</v>
@@ -25884,10 +26277,10 @@
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="B376" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="C376" t="s">
         <v>458</v>
@@ -25922,10 +26315,10 @@
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="B377" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="C377" t="s">
         <v>458</v>
@@ -25960,16 +26353,16 @@
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="B378" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="C378" t="s">
         <v>458</v>
       </c>
       <c r="D378" t="s">
-        <v>554</v>
+        <v>459</v>
       </c>
       <c r="E378" t="s">
         <v>25</v>
@@ -25998,16 +26391,16 @@
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="B379" t="s">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="C379" t="s">
         <v>458</v>
       </c>
       <c r="D379" t="s">
-        <v>554</v>
+        <v>459</v>
       </c>
       <c r="E379" t="s">
         <v>25</v>
@@ -26036,16 +26429,16 @@
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="B380" t="s">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="C380" t="s">
         <v>458</v>
       </c>
       <c r="D380" t="s">
-        <v>554</v>
+        <v>459</v>
       </c>
       <c r="E380" t="s">
         <v>25</v>
@@ -26074,16 +26467,16 @@
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="B381" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="C381" t="s">
         <v>458</v>
       </c>
       <c r="D381" t="s">
-        <v>554</v>
+        <v>459</v>
       </c>
       <c r="E381" t="s">
         <v>25</v>
@@ -26112,16 +26505,16 @@
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="B382" t="s">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="C382" t="s">
         <v>458</v>
       </c>
       <c r="D382" t="s">
-        <v>554</v>
+        <v>459</v>
       </c>
       <c r="E382" t="s">
         <v>25</v>
@@ -26150,16 +26543,16 @@
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="B383" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="C383" t="s">
         <v>458</v>
       </c>
       <c r="D383" t="s">
-        <v>554</v>
+        <v>459</v>
       </c>
       <c r="E383" t="s">
         <v>25</v>
@@ -26188,16 +26581,16 @@
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="B384" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="C384" t="s">
         <v>458</v>
       </c>
       <c r="D384" t="s">
-        <v>554</v>
+        <v>459</v>
       </c>
       <c r="E384" t="s">
         <v>25</v>
@@ -26226,10 +26619,10 @@
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="B385" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="C385" t="s">
         <v>458</v>
@@ -26264,10 +26657,10 @@
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="B386" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="C386" t="s">
         <v>458</v>
@@ -26302,10 +26695,10 @@
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="B387" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="C387" t="s">
         <v>458</v>
@@ -26340,10 +26733,10 @@
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="B388" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="C388" t="s">
         <v>458</v>
@@ -26378,10 +26771,10 @@
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="B389" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="C389" t="s">
         <v>458</v>
@@ -26416,10 +26809,10 @@
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="B390" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="C390" t="s">
         <v>458</v>
@@ -26454,10 +26847,10 @@
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="B391" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="C391" t="s">
         <v>458</v>
@@ -26492,10 +26885,10 @@
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="B392" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="C392" t="s">
         <v>458</v>
@@ -26530,10 +26923,10 @@
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="B393" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="C393" t="s">
         <v>458</v>
@@ -26568,10 +26961,10 @@
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="B394" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="C394" t="s">
         <v>458</v>
@@ -26606,10 +26999,10 @@
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="B395" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="C395" t="s">
         <v>458</v>
@@ -26644,10 +27037,10 @@
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="B396" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="C396" t="s">
         <v>458</v>
@@ -26682,10 +27075,10 @@
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="B397" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="C397" t="s">
         <v>458</v>
@@ -26720,10 +27113,10 @@
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="B398" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="C398" t="s">
         <v>458</v>
@@ -26758,10 +27151,10 @@
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="B399" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="C399" t="s">
         <v>458</v>
@@ -26796,10 +27189,10 @@
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="B400" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="C400" t="s">
         <v>458</v>
@@ -26834,10 +27227,10 @@
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="B401" t="s">
-        <v>600</v>
+        <v>586</v>
       </c>
       <c r="C401" t="s">
         <v>458</v>
@@ -26872,10 +27265,10 @@
     </row>
     <row r="402" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="B402" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="C402" t="s">
         <v>458</v>
@@ -26910,10 +27303,10 @@
     </row>
     <row r="403" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="B403" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="C403" t="s">
         <v>458</v>
@@ -26948,10 +27341,10 @@
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="B404" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="C404" t="s">
         <v>458</v>
@@ -26986,10 +27379,10 @@
     </row>
     <row r="405" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="B405" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="C405" t="s">
         <v>458</v>
@@ -27024,10 +27417,10 @@
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="B406" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="C406" t="s">
         <v>458</v>
@@ -27062,10 +27455,10 @@
     </row>
     <row r="407" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="B407" t="s">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="C407" t="s">
         <v>458</v>
@@ -27100,10 +27493,10 @@
     </row>
     <row r="408" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="B408" t="s">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="C408" t="s">
         <v>458</v>
@@ -27138,10 +27531,10 @@
     </row>
     <row r="409" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="B409" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="C409" t="s">
         <v>458</v>
@@ -27176,10 +27569,10 @@
     </row>
     <row r="410" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="B410" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="C410" t="s">
         <v>458</v>
@@ -27214,10 +27607,10 @@
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="B411" t="s">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="C411" t="s">
         <v>458</v>
@@ -27252,16 +27645,16 @@
     </row>
     <row r="412" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="B412" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="C412" t="s">
-        <v>623</v>
+        <v>458</v>
       </c>
       <c r="D412" t="s">
-        <v>25</v>
+        <v>554</v>
       </c>
       <c r="E412" t="s">
         <v>25</v>
@@ -27290,16 +27683,16 @@
     </row>
     <row r="413" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="B413" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="C413" t="s">
-        <v>623</v>
+        <v>458</v>
       </c>
       <c r="D413" t="s">
-        <v>25</v>
+        <v>554</v>
       </c>
       <c r="E413" t="s">
         <v>25</v>
@@ -27328,16 +27721,16 @@
     </row>
     <row r="414" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="B414" t="s">
-        <v>627</v>
+        <v>612</v>
       </c>
       <c r="C414" t="s">
-        <v>623</v>
+        <v>458</v>
       </c>
       <c r="D414" t="s">
-        <v>25</v>
+        <v>554</v>
       </c>
       <c r="E414" t="s">
         <v>25</v>
@@ -27366,16 +27759,16 @@
     </row>
     <row r="415" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
       <c r="B415" t="s">
-        <v>629</v>
+        <v>614</v>
       </c>
       <c r="C415" t="s">
-        <v>623</v>
+        <v>458</v>
       </c>
       <c r="D415" t="s">
-        <v>25</v>
+        <v>554</v>
       </c>
       <c r="E415" t="s">
         <v>25</v>
@@ -27404,16 +27797,16 @@
     </row>
     <row r="416" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>630</v>
+        <v>615</v>
       </c>
       <c r="B416" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="C416" t="s">
-        <v>623</v>
+        <v>458</v>
       </c>
       <c r="D416" t="s">
-        <v>25</v>
+        <v>554</v>
       </c>
       <c r="E416" t="s">
         <v>25</v>
@@ -27442,16 +27835,16 @@
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="B417" t="s">
-        <v>633</v>
+        <v>618</v>
       </c>
       <c r="C417" t="s">
-        <v>623</v>
+        <v>458</v>
       </c>
       <c r="D417" t="s">
-        <v>25</v>
+        <v>554</v>
       </c>
       <c r="E417" t="s">
         <v>25</v>
@@ -27480,16 +27873,16 @@
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>634</v>
+        <v>619</v>
       </c>
       <c r="B418" t="s">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="C418" t="s">
-        <v>623</v>
+        <v>458</v>
       </c>
       <c r="D418" t="s">
-        <v>25</v>
+        <v>554</v>
       </c>
       <c r="E418" t="s">
         <v>25</v>
@@ -27518,10 +27911,10 @@
     </row>
     <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>636</v>
+        <v>621</v>
       </c>
       <c r="B419" t="s">
-        <v>637</v>
+        <v>622</v>
       </c>
       <c r="C419" t="s">
         <v>623</v>
@@ -27556,16 +27949,16 @@
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="B420" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="C420" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="D420" t="s">
-        <v>641</v>
+        <v>25</v>
       </c>
       <c r="E420" t="s">
         <v>25</v>
@@ -27594,16 +27987,16 @@
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
       <c r="B421" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="C421" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="D421" t="s">
-        <v>641</v>
+        <v>25</v>
       </c>
       <c r="E421" t="s">
         <v>25</v>
@@ -27632,16 +28025,16 @@
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="B422" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C422" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="D422" t="s">
-        <v>641</v>
+        <v>25</v>
       </c>
       <c r="E422" t="s">
         <v>25</v>
@@ -27670,16 +28063,16 @@
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="B423" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="C423" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="D423" t="s">
-        <v>641</v>
+        <v>25</v>
       </c>
       <c r="E423" t="s">
         <v>25</v>
@@ -27708,16 +28101,16 @@
     </row>
     <row r="424" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="B424" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="C424" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="D424" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="E424" t="s">
         <v>25</v>
@@ -27746,16 +28139,16 @@
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="B425" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C425" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="D425" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="E425" t="s">
         <v>25</v>
@@ -27784,16 +28177,16 @@
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="B426" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="C426" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="D426" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="E426" t="s">
         <v>25</v>
@@ -27822,16 +28215,16 @@
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="B427" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="C427" t="s">
         <v>640</v>
       </c>
       <c r="D427" t="s">
-        <v>138</v>
+        <v>641</v>
       </c>
       <c r="E427" t="s">
         <v>25</v>
@@ -27860,16 +28253,16 @@
     </row>
     <row r="428" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="B428" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="C428" t="s">
         <v>640</v>
       </c>
       <c r="D428" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="E428" t="s">
         <v>25</v>
@@ -27898,16 +28291,16 @@
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>659</v>
+        <v>644</v>
       </c>
       <c r="B429" t="s">
-        <v>660</v>
+        <v>645</v>
       </c>
       <c r="C429" t="s">
         <v>640</v>
       </c>
       <c r="D429" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="E429" t="s">
         <v>25</v>
@@ -27936,16 +28329,16 @@
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>661</v>
+        <v>646</v>
       </c>
       <c r="B430" t="s">
-        <v>662</v>
+        <v>647</v>
       </c>
       <c r="C430" t="s">
         <v>640</v>
       </c>
       <c r="D430" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="E430" t="s">
         <v>25</v>
@@ -27974,16 +28367,16 @@
     </row>
     <row r="431" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>663</v>
+        <v>648</v>
       </c>
       <c r="B431" t="s">
-        <v>664</v>
+        <v>649</v>
       </c>
       <c r="C431" t="s">
         <v>640</v>
       </c>
       <c r="D431" t="s">
-        <v>658</v>
+        <v>138</v>
       </c>
       <c r="E431" t="s">
         <v>25</v>
@@ -28012,16 +28405,16 @@
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>665</v>
+        <v>650</v>
       </c>
       <c r="B432" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="C432" t="s">
         <v>640</v>
       </c>
       <c r="D432" t="s">
-        <v>658</v>
+        <v>138</v>
       </c>
       <c r="E432" t="s">
         <v>25</v>
@@ -28050,16 +28443,16 @@
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="B433" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="C433" t="s">
         <v>640</v>
       </c>
       <c r="D433" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E433" t="s">
         <v>25</v>
@@ -28088,16 +28481,16 @@
     </row>
     <row r="434" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="B434" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="C434" t="s">
         <v>640</v>
       </c>
       <c r="D434" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E434" t="s">
         <v>25</v>
@@ -28126,16 +28519,16 @@
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="B435" t="s">
-        <v>672</v>
+        <v>657</v>
       </c>
       <c r="C435" t="s">
         <v>640</v>
       </c>
       <c r="D435" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="E435" t="s">
         <v>25</v>
@@ -28164,16 +28557,16 @@
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="B436" t="s">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="C436" t="s">
         <v>640</v>
       </c>
       <c r="D436" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="E436" t="s">
         <v>25</v>
@@ -28202,16 +28595,16 @@
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>676</v>
+        <v>661</v>
       </c>
       <c r="B437" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="C437" t="s">
         <v>640</v>
       </c>
       <c r="D437" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="E437" t="s">
         <v>25</v>
@@ -28240,16 +28633,16 @@
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="B438" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="C438" t="s">
         <v>640</v>
       </c>
       <c r="D438" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="E438" t="s">
         <v>25</v>
@@ -28278,16 +28671,16 @@
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="B439" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="C439" t="s">
-        <v>681</v>
+        <v>640</v>
       </c>
       <c r="D439" t="s">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="E439" t="s">
         <v>25</v>
@@ -28316,16 +28709,16 @@
     </row>
     <row r="440" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="B440" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="C440" t="s">
-        <v>681</v>
+        <v>640</v>
       </c>
       <c r="D440" t="s">
-        <v>682</v>
+        <v>128</v>
       </c>
       <c r="E440" t="s">
         <v>25</v>
@@ -28354,16 +28747,16 @@
     </row>
     <row r="441" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="B441" t="s">
-        <v>686</v>
+        <v>670</v>
       </c>
       <c r="C441" t="s">
-        <v>681</v>
+        <v>640</v>
       </c>
       <c r="D441" t="s">
-        <v>682</v>
+        <v>128</v>
       </c>
       <c r="E441" t="s">
         <v>25</v>
@@ -28392,16 +28785,16 @@
     </row>
     <row r="442" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>687</v>
+        <v>671</v>
       </c>
       <c r="B442" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="C442" t="s">
-        <v>681</v>
+        <v>640</v>
       </c>
       <c r="D442" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="E442" t="s">
         <v>25</v>
@@ -28430,16 +28823,16 @@
     </row>
     <row r="443" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>689</v>
+        <v>674</v>
       </c>
       <c r="B443" t="s">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="C443" t="s">
-        <v>681</v>
+        <v>640</v>
       </c>
       <c r="D443" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="E443" t="s">
         <v>25</v>
@@ -28468,16 +28861,16 @@
     </row>
     <row r="444" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>691</v>
+        <v>676</v>
       </c>
       <c r="B444" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="C444" t="s">
-        <v>681</v>
+        <v>640</v>
       </c>
       <c r="D444" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="E444" t="s">
         <v>25</v>
@@ -28506,16 +28899,16 @@
     </row>
     <row r="445" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>693</v>
+        <v>676</v>
       </c>
       <c r="B445" t="s">
-        <v>694</v>
+        <v>678</v>
       </c>
       <c r="C445" t="s">
-        <v>681</v>
+        <v>640</v>
       </c>
       <c r="D445" t="s">
-        <v>695</v>
+        <v>673</v>
       </c>
       <c r="E445" t="s">
         <v>25</v>
@@ -28544,16 +28937,16 @@
     </row>
     <row r="446" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
       <c r="B446" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
       <c r="C446" t="s">
         <v>681</v>
       </c>
       <c r="D446" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="E446" t="s">
         <v>25</v>
@@ -28582,16 +28975,16 @@
     </row>
     <row r="447" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>698</v>
+        <v>683</v>
       </c>
       <c r="B447" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="C447" t="s">
         <v>681</v>
       </c>
       <c r="D447" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="E447" t="s">
         <v>25</v>
@@ -28620,16 +29013,16 @@
     </row>
     <row r="448" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="B448" t="s">
-        <v>701</v>
+        <v>686</v>
       </c>
       <c r="C448" t="s">
         <v>681</v>
       </c>
       <c r="D448" t="s">
-        <v>702</v>
+        <v>682</v>
       </c>
       <c r="E448" t="s">
         <v>25</v>
@@ -28658,16 +29051,16 @@
     </row>
     <row r="449" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="B449" t="s">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="C449" t="s">
         <v>681</v>
       </c>
       <c r="D449" t="s">
-        <v>702</v>
+        <v>682</v>
       </c>
       <c r="E449" t="s">
         <v>25</v>
@@ -28696,16 +29089,16 @@
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>705</v>
+        <v>689</v>
       </c>
       <c r="B450" t="s">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="C450" t="s">
         <v>681</v>
       </c>
       <c r="D450" t="s">
-        <v>702</v>
+        <v>682</v>
       </c>
       <c r="E450" t="s">
         <v>25</v>
@@ -28734,16 +29127,16 @@
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="B451" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="C451" t="s">
         <v>681</v>
       </c>
       <c r="D451" t="s">
-        <v>702</v>
+        <v>682</v>
       </c>
       <c r="E451" t="s">
         <v>25</v>
@@ -28772,16 +29165,16 @@
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>709</v>
+        <v>693</v>
       </c>
       <c r="B452" t="s">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="C452" t="s">
         <v>681</v>
       </c>
       <c r="D452" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="E452" t="s">
         <v>25</v>
@@ -28810,16 +29203,16 @@
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="B453" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="C453" t="s">
         <v>681</v>
       </c>
       <c r="D453" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="E453" t="s">
         <v>25</v>
@@ -28848,16 +29241,16 @@
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>713</v>
+        <v>698</v>
       </c>
       <c r="B454" t="s">
-        <v>714</v>
+        <v>699</v>
       </c>
       <c r="C454" t="s">
         <v>681</v>
       </c>
       <c r="D454" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="E454" t="s">
         <v>25</v>
@@ -28886,16 +29279,16 @@
     </row>
     <row r="455" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="B455" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="C455" t="s">
         <v>681</v>
       </c>
       <c r="D455" t="s">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="E455" t="s">
         <v>25</v>
@@ -28924,16 +29317,16 @@
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>718</v>
+        <v>703</v>
       </c>
       <c r="B456" t="s">
-        <v>719</v>
+        <v>704</v>
       </c>
       <c r="C456" t="s">
         <v>681</v>
       </c>
       <c r="D456" t="s">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="E456" t="s">
         <v>25</v>
@@ -28962,16 +29355,16 @@
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>720</v>
+        <v>705</v>
       </c>
       <c r="B457" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="C457" t="s">
         <v>681</v>
       </c>
       <c r="D457" t="s">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="E457" t="s">
         <v>25</v>
@@ -29000,16 +29393,16 @@
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>722</v>
+        <v>707</v>
       </c>
       <c r="B458" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="C458" t="s">
         <v>681</v>
       </c>
       <c r="D458" t="s">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="E458" t="s">
         <v>25</v>
@@ -29038,16 +29431,16 @@
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>724</v>
+        <v>709</v>
       </c>
       <c r="B459" t="s">
-        <v>725</v>
+        <v>710</v>
       </c>
       <c r="C459" t="s">
         <v>681</v>
       </c>
       <c r="D459" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="E459" t="s">
         <v>25</v>
@@ -29076,16 +29469,16 @@
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="B460" t="s">
-        <v>727</v>
+        <v>710</v>
       </c>
       <c r="C460" t="s">
         <v>681</v>
       </c>
       <c r="D460" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="E460" t="s">
         <v>25</v>
@@ -29114,16 +29507,16 @@
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>729</v>
+        <v>713</v>
       </c>
       <c r="B461" t="s">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="C461" t="s">
         <v>681</v>
       </c>
       <c r="D461" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="E461" t="s">
         <v>25</v>
@@ -29152,16 +29545,16 @@
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>731</v>
+        <v>715</v>
       </c>
       <c r="B462" t="s">
-        <v>732</v>
+        <v>716</v>
       </c>
       <c r="C462" t="s">
         <v>681</v>
       </c>
       <c r="D462" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="E462" t="s">
         <v>25</v>
@@ -29190,16 +29583,16 @@
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
       <c r="B463" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="C463" t="s">
         <v>681</v>
       </c>
       <c r="D463" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="E463" t="s">
         <v>25</v>
@@ -29228,16 +29621,16 @@
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="B464" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="C464" t="s">
         <v>681</v>
       </c>
       <c r="D464" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="E464" t="s">
         <v>25</v>
@@ -29266,16 +29659,16 @@
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
       <c r="B465" t="s">
-        <v>738</v>
+        <v>723</v>
       </c>
       <c r="C465" t="s">
         <v>681</v>
       </c>
       <c r="D465" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="E465" t="s">
         <v>25</v>
@@ -29304,16 +29697,16 @@
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>739</v>
+        <v>724</v>
       </c>
       <c r="B466" t="s">
-        <v>740</v>
+        <v>725</v>
       </c>
       <c r="C466" t="s">
         <v>681</v>
       </c>
       <c r="D466" t="s">
-        <v>741</v>
+        <v>717</v>
       </c>
       <c r="E466" t="s">
         <v>25</v>
@@ -29342,16 +29735,16 @@
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="B467" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="C467" t="s">
         <v>681</v>
       </c>
       <c r="D467" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="E467" t="s">
         <v>25</v>
@@ -29380,16 +29773,16 @@
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="B468" t="s">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="C468" t="s">
-        <v>746</v>
+        <v>681</v>
       </c>
       <c r="D468" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="E468" t="s">
         <v>25</v>
@@ -29418,16 +29811,16 @@
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="B469" t="s">
-        <v>749</v>
+        <v>732</v>
       </c>
       <c r="C469" t="s">
-        <v>746</v>
+        <v>681</v>
       </c>
       <c r="D469" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="E469" t="s">
         <v>25</v>
@@ -29456,16 +29849,16 @@
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>750</v>
+        <v>733</v>
       </c>
       <c r="B470" t="s">
-        <v>751</v>
+        <v>734</v>
       </c>
       <c r="C470" t="s">
-        <v>746</v>
+        <v>681</v>
       </c>
       <c r="D470" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="E470" t="s">
         <v>25</v>
@@ -29494,16 +29887,16 @@
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>752</v>
+        <v>735</v>
       </c>
       <c r="B471" t="s">
-        <v>753</v>
+        <v>736</v>
       </c>
       <c r="C471" t="s">
-        <v>746</v>
+        <v>681</v>
       </c>
       <c r="D471" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="E471" t="s">
         <v>25</v>
@@ -29532,16 +29925,16 @@
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>754</v>
+        <v>737</v>
       </c>
       <c r="B472" t="s">
-        <v>755</v>
+        <v>738</v>
       </c>
       <c r="C472" t="s">
-        <v>746</v>
+        <v>681</v>
       </c>
       <c r="D472" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="E472" t="s">
         <v>25</v>
@@ -29570,16 +29963,16 @@
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>756</v>
+        <v>739</v>
       </c>
       <c r="B473" t="s">
-        <v>757</v>
+        <v>740</v>
       </c>
       <c r="C473" t="s">
-        <v>746</v>
+        <v>681</v>
       </c>
       <c r="D473" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="E473" t="s">
         <v>25</v>
@@ -29608,16 +30001,16 @@
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>758</v>
+        <v>742</v>
       </c>
       <c r="B474" t="s">
-        <v>759</v>
+        <v>743</v>
       </c>
       <c r="C474" t="s">
-        <v>746</v>
+        <v>681</v>
       </c>
       <c r="D474" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="E474" t="s">
         <v>25</v>
@@ -29646,10 +30039,10 @@
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="B475" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="C475" t="s">
         <v>746</v>
@@ -29684,10 +30077,10 @@
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
       <c r="B476" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="C476" t="s">
         <v>746</v>
@@ -29722,10 +30115,10 @@
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="B477" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="C477" t="s">
         <v>746</v>
@@ -29760,10 +30153,10 @@
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="B478" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
       <c r="C478" t="s">
         <v>746</v>
@@ -29798,10 +30191,10 @@
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="B479" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="C479" t="s">
         <v>746</v>
@@ -29836,10 +30229,10 @@
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="B480" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="C480" t="s">
         <v>746</v>
@@ -29874,16 +30267,16 @@
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>772</v>
+        <v>758</v>
       </c>
       <c r="B481" t="s">
-        <v>773</v>
+        <v>759</v>
       </c>
       <c r="C481" t="s">
         <v>746</v>
       </c>
       <c r="D481" t="s">
-        <v>774</v>
+        <v>747</v>
       </c>
       <c r="E481" t="s">
         <v>25</v>
@@ -29912,16 +30305,16 @@
     </row>
     <row r="482" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
       <c r="B482" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="C482" t="s">
         <v>746</v>
       </c>
       <c r="D482" t="s">
-        <v>774</v>
+        <v>747</v>
       </c>
       <c r="E482" t="s">
         <v>25</v>
@@ -29950,16 +30343,16 @@
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="B483" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="C483" t="s">
         <v>746</v>
       </c>
       <c r="D483" t="s">
-        <v>774</v>
+        <v>747</v>
       </c>
       <c r="E483" t="s">
         <v>25</v>
@@ -29988,16 +30381,16 @@
     </row>
     <row r="484" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="B484" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="C484" t="s">
         <v>746</v>
       </c>
       <c r="D484" t="s">
-        <v>774</v>
+        <v>747</v>
       </c>
       <c r="E484" t="s">
         <v>25</v>
@@ -30026,16 +30419,16 @@
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="B485" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="C485" t="s">
         <v>746</v>
       </c>
       <c r="D485" t="s">
-        <v>774</v>
+        <v>747</v>
       </c>
       <c r="E485" t="s">
         <v>25</v>
@@ -30064,16 +30457,16 @@
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="B486" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="C486" t="s">
         <v>746</v>
       </c>
       <c r="D486" t="s">
-        <v>196</v>
+        <v>747</v>
       </c>
       <c r="E486" t="s">
         <v>25</v>
@@ -30102,16 +30495,16 @@
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="B487" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="C487" t="s">
         <v>746</v>
       </c>
       <c r="D487" t="s">
-        <v>196</v>
+        <v>747</v>
       </c>
       <c r="E487" t="s">
         <v>25</v>
@@ -30140,16 +30533,16 @@
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
       <c r="B488" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="C488" t="s">
         <v>746</v>
       </c>
       <c r="D488" t="s">
-        <v>196</v>
+        <v>774</v>
       </c>
       <c r="E488" t="s">
         <v>25</v>
@@ -30178,16 +30571,16 @@
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="B489" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="C489" t="s">
         <v>746</v>
       </c>
       <c r="D489" t="s">
-        <v>791</v>
+        <v>774</v>
       </c>
       <c r="E489" t="s">
         <v>25</v>
@@ -30216,16 +30609,16 @@
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>792</v>
+        <v>777</v>
       </c>
       <c r="B490" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="C490" t="s">
         <v>746</v>
       </c>
       <c r="D490" t="s">
-        <v>791</v>
+        <v>774</v>
       </c>
       <c r="E490" t="s">
         <v>25</v>
@@ -30254,16 +30647,16 @@
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="B491" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="C491" t="s">
         <v>746</v>
       </c>
       <c r="D491" t="s">
-        <v>796</v>
+        <v>774</v>
       </c>
       <c r="E491" t="s">
         <v>25</v>
@@ -30292,16 +30685,16 @@
     </row>
     <row r="492" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="B492" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="C492" t="s">
         <v>746</v>
       </c>
       <c r="D492" t="s">
-        <v>796</v>
+        <v>774</v>
       </c>
       <c r="E492" t="s">
         <v>25</v>
@@ -30330,16 +30723,16 @@
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="B493" t="s">
-        <v>800</v>
+        <v>784</v>
       </c>
       <c r="C493" t="s">
         <v>746</v>
       </c>
       <c r="D493" t="s">
-        <v>796</v>
+        <v>196</v>
       </c>
       <c r="E493" t="s">
         <v>25</v>
@@ -30368,16 +30761,16 @@
     </row>
     <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="B494" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="C494" t="s">
         <v>746</v>
       </c>
       <c r="D494" t="s">
-        <v>803</v>
+        <v>196</v>
       </c>
       <c r="E494" t="s">
         <v>25</v>
@@ -30406,16 +30799,16 @@
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>804</v>
+        <v>787</v>
       </c>
       <c r="B495" t="s">
-        <v>805</v>
+        <v>788</v>
       </c>
       <c r="C495" t="s">
         <v>746</v>
       </c>
       <c r="D495" t="s">
-        <v>803</v>
+        <v>196</v>
       </c>
       <c r="E495" t="s">
         <v>25</v>
@@ -30444,16 +30837,16 @@
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>806</v>
+        <v>789</v>
       </c>
       <c r="B496" t="s">
-        <v>807</v>
+        <v>790</v>
       </c>
       <c r="C496" t="s">
         <v>746</v>
       </c>
       <c r="D496" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="E496" t="s">
         <v>25</v>
@@ -30482,16 +30875,16 @@
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="B497" t="s">
-        <v>809</v>
+        <v>793</v>
       </c>
       <c r="C497" t="s">
         <v>746</v>
       </c>
       <c r="D497" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="E497" t="s">
         <v>25</v>
@@ -30520,16 +30913,16 @@
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="B498" t="s">
-        <v>811</v>
+        <v>795</v>
       </c>
       <c r="C498" t="s">
         <v>746</v>
       </c>
       <c r="D498" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E498" t="s">
         <v>25</v>
@@ -30558,16 +30951,16 @@
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
       <c r="B499" t="s">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="C499" t="s">
         <v>746</v>
       </c>
       <c r="D499" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E499" t="s">
         <v>25</v>
@@ -30596,16 +30989,16 @@
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>814</v>
+        <v>799</v>
       </c>
       <c r="B500" t="s">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="C500" t="s">
         <v>746</v>
       </c>
       <c r="D500" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E500" t="s">
         <v>25</v>
@@ -30634,10 +31027,10 @@
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="B501" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="C501" t="s">
         <v>746</v>
@@ -30672,10 +31065,10 @@
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>818</v>
+        <v>804</v>
       </c>
       <c r="B502" t="s">
-        <v>819</v>
+        <v>805</v>
       </c>
       <c r="C502" t="s">
         <v>746</v>
@@ -30710,10 +31103,10 @@
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>820</v>
+        <v>806</v>
       </c>
       <c r="B503" t="s">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="C503" t="s">
         <v>746</v>
@@ -30748,10 +31141,10 @@
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>822</v>
+        <v>808</v>
       </c>
       <c r="B504" t="s">
-        <v>823</v>
+        <v>809</v>
       </c>
       <c r="C504" t="s">
         <v>746</v>
@@ -30786,10 +31179,10 @@
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="B505" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="C505" t="s">
         <v>746</v>
@@ -30824,16 +31217,16 @@
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="B506" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="C506" t="s">
         <v>746</v>
       </c>
       <c r="D506" t="s">
-        <v>828</v>
+        <v>803</v>
       </c>
       <c r="E506" t="s">
         <v>25</v>
@@ -30862,16 +31255,16 @@
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>829</v>
+        <v>814</v>
       </c>
       <c r="B507" t="s">
-        <v>830</v>
+        <v>815</v>
       </c>
       <c r="C507" t="s">
         <v>746</v>
       </c>
       <c r="D507" t="s">
-        <v>828</v>
+        <v>803</v>
       </c>
       <c r="E507" t="s">
         <v>25</v>
@@ -30900,16 +31293,16 @@
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="B508" t="s">
-        <v>832</v>
+        <v>817</v>
       </c>
       <c r="C508" t="s">
         <v>746</v>
       </c>
       <c r="D508" t="s">
-        <v>828</v>
+        <v>803</v>
       </c>
       <c r="E508" t="s">
         <v>25</v>
@@ -30938,16 +31331,16 @@
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>833</v>
+        <v>818</v>
       </c>
       <c r="B509" t="s">
-        <v>834</v>
+        <v>819</v>
       </c>
       <c r="C509" t="s">
         <v>746</v>
       </c>
       <c r="D509" t="s">
-        <v>828</v>
+        <v>803</v>
       </c>
       <c r="E509" t="s">
         <v>25</v>
@@ -30976,16 +31369,16 @@
     </row>
     <row r="510" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>835</v>
+        <v>820</v>
       </c>
       <c r="B510" t="s">
-        <v>836</v>
+        <v>821</v>
       </c>
       <c r="C510" t="s">
         <v>746</v>
       </c>
       <c r="D510" t="s">
-        <v>828</v>
+        <v>803</v>
       </c>
       <c r="E510" t="s">
         <v>25</v>
@@ -31014,16 +31407,16 @@
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="B511" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="C511" t="s">
         <v>746</v>
       </c>
       <c r="D511" t="s">
-        <v>839</v>
+        <v>803</v>
       </c>
       <c r="E511" t="s">
         <v>25</v>
@@ -31052,16 +31445,16 @@
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>840</v>
+        <v>824</v>
       </c>
       <c r="B512" t="s">
-        <v>841</v>
+        <v>825</v>
       </c>
       <c r="C512" t="s">
         <v>746</v>
       </c>
       <c r="D512" t="s">
-        <v>839</v>
+        <v>803</v>
       </c>
       <c r="E512" t="s">
         <v>25</v>
@@ -31090,16 +31483,16 @@
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>842</v>
+        <v>826</v>
       </c>
       <c r="B513" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
       <c r="C513" t="s">
-        <v>844</v>
+        <v>746</v>
       </c>
       <c r="D513" t="s">
-        <v>845</v>
+        <v>828</v>
       </c>
       <c r="E513" t="s">
         <v>25</v>
@@ -31128,16 +31521,16 @@
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>846</v>
+        <v>829</v>
       </c>
       <c r="B514" t="s">
-        <v>847</v>
+        <v>830</v>
       </c>
       <c r="C514" t="s">
-        <v>844</v>
+        <v>746</v>
       </c>
       <c r="D514" t="s">
-        <v>845</v>
+        <v>828</v>
       </c>
       <c r="E514" t="s">
         <v>25</v>
@@ -31166,16 +31559,16 @@
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>848</v>
+        <v>831</v>
       </c>
       <c r="B515" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
       <c r="C515" t="s">
-        <v>844</v>
+        <v>746</v>
       </c>
       <c r="D515" t="s">
-        <v>845</v>
+        <v>828</v>
       </c>
       <c r="E515" t="s">
         <v>25</v>
@@ -31204,16 +31597,16 @@
     </row>
     <row r="516" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>850</v>
+        <v>833</v>
       </c>
       <c r="B516" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="C516" t="s">
-        <v>844</v>
+        <v>746</v>
       </c>
       <c r="D516" t="s">
-        <v>845</v>
+        <v>828</v>
       </c>
       <c r="E516" t="s">
         <v>25</v>
@@ -31242,16 +31635,16 @@
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>852</v>
+        <v>835</v>
       </c>
       <c r="B517" t="s">
-        <v>853</v>
+        <v>836</v>
       </c>
       <c r="C517" t="s">
-        <v>844</v>
+        <v>746</v>
       </c>
       <c r="D517" t="s">
-        <v>845</v>
+        <v>828</v>
       </c>
       <c r="E517" t="s">
         <v>25</v>
@@ -31280,16 +31673,16 @@
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>854</v>
+        <v>837</v>
       </c>
       <c r="B518" t="s">
-        <v>855</v>
+        <v>838</v>
       </c>
       <c r="C518" t="s">
-        <v>844</v>
+        <v>746</v>
       </c>
       <c r="D518" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="E518" t="s">
         <v>25</v>
@@ -31318,16 +31711,16 @@
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>856</v>
+        <v>840</v>
       </c>
       <c r="B519" t="s">
-        <v>857</v>
+        <v>841</v>
       </c>
       <c r="C519" t="s">
-        <v>844</v>
+        <v>746</v>
       </c>
       <c r="D519" t="s">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="E519" t="s">
         <v>25</v>
@@ -31356,16 +31749,16 @@
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>859</v>
+        <v>842</v>
       </c>
       <c r="B520" t="s">
-        <v>860</v>
+        <v>843</v>
       </c>
       <c r="C520" t="s">
         <v>844</v>
       </c>
       <c r="D520" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="E520" t="s">
         <v>25</v>
@@ -31394,16 +31787,16 @@
     </row>
     <row r="521" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>861</v>
+        <v>846</v>
       </c>
       <c r="B521" t="s">
-        <v>862</v>
+        <v>847</v>
       </c>
       <c r="C521" t="s">
         <v>844</v>
       </c>
       <c r="D521" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="E521" t="s">
         <v>25</v>
@@ -31432,16 +31825,16 @@
     </row>
     <row r="522" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="B522" t="s">
-        <v>864</v>
+        <v>849</v>
       </c>
       <c r="C522" t="s">
         <v>844</v>
       </c>
       <c r="D522" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="E522" t="s">
         <v>25</v>
@@ -31470,16 +31863,16 @@
     </row>
     <row r="523" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>865</v>
+        <v>850</v>
       </c>
       <c r="B523" t="s">
-        <v>866</v>
+        <v>851</v>
       </c>
       <c r="C523" t="s">
         <v>844</v>
       </c>
       <c r="D523" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="E523" t="s">
         <v>25</v>
@@ -31508,16 +31901,16 @@
     </row>
     <row r="524" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="B524" t="s">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="C524" t="s">
         <v>844</v>
       </c>
       <c r="D524" t="s">
-        <v>869</v>
+        <v>845</v>
       </c>
       <c r="E524" t="s">
         <v>25</v>
@@ -31546,16 +31939,16 @@
     </row>
     <row r="525" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>870</v>
+        <v>854</v>
       </c>
       <c r="B525" t="s">
-        <v>871</v>
+        <v>855</v>
       </c>
       <c r="C525" t="s">
         <v>844</v>
       </c>
       <c r="D525" t="s">
-        <v>869</v>
+        <v>845</v>
       </c>
       <c r="E525" t="s">
         <v>25</v>
@@ -31584,16 +31977,16 @@
     </row>
     <row r="526" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>872</v>
+        <v>856</v>
       </c>
       <c r="B526" t="s">
-        <v>873</v>
+        <v>857</v>
       </c>
       <c r="C526" t="s">
         <v>844</v>
       </c>
       <c r="D526" t="s">
-        <v>869</v>
+        <v>858</v>
       </c>
       <c r="E526" t="s">
         <v>25</v>
@@ -31622,16 +32015,16 @@
     </row>
     <row r="527" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
       <c r="B527" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="C527" t="s">
         <v>844</v>
       </c>
       <c r="D527" t="s">
-        <v>876</v>
+        <v>858</v>
       </c>
       <c r="E527" t="s">
         <v>25</v>
@@ -31660,16 +32053,16 @@
     </row>
     <row r="528" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>877</v>
+        <v>861</v>
       </c>
       <c r="B528" t="s">
-        <v>878</v>
+        <v>862</v>
       </c>
       <c r="C528" t="s">
         <v>844</v>
       </c>
       <c r="D528" t="s">
-        <v>876</v>
+        <v>858</v>
       </c>
       <c r="E528" t="s">
         <v>25</v>
@@ -31698,16 +32091,16 @@
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>879</v>
+        <v>863</v>
       </c>
       <c r="B529" t="s">
-        <v>880</v>
+        <v>864</v>
       </c>
       <c r="C529" t="s">
         <v>844</v>
       </c>
       <c r="D529" t="s">
-        <v>881</v>
+        <v>858</v>
       </c>
       <c r="E529" t="s">
         <v>25</v>
@@ -31736,16 +32129,16 @@
     </row>
     <row r="530" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>882</v>
+        <v>865</v>
       </c>
       <c r="B530" t="s">
-        <v>883</v>
+        <v>866</v>
       </c>
       <c r="C530" t="s">
         <v>844</v>
       </c>
       <c r="D530" t="s">
-        <v>881</v>
+        <v>858</v>
       </c>
       <c r="E530" t="s">
         <v>25</v>
@@ -31774,16 +32167,16 @@
     </row>
     <row r="531" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>884</v>
+        <v>867</v>
       </c>
       <c r="B531" t="s">
-        <v>885</v>
+        <v>868</v>
       </c>
       <c r="C531" t="s">
         <v>844</v>
       </c>
       <c r="D531" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="E531" t="s">
         <v>25</v>
@@ -31812,16 +32205,16 @@
     </row>
     <row r="532" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="B532" t="s">
-        <v>887</v>
+        <v>871</v>
       </c>
       <c r="C532" t="s">
         <v>844</v>
       </c>
       <c r="D532" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="E532" t="s">
         <v>25</v>
@@ -31850,16 +32243,16 @@
     </row>
     <row r="533" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
       <c r="B533" t="s">
-        <v>889</v>
+        <v>873</v>
       </c>
       <c r="C533" t="s">
         <v>844</v>
       </c>
       <c r="D533" t="s">
-        <v>890</v>
+        <v>869</v>
       </c>
       <c r="E533" t="s">
         <v>25</v>
@@ -31888,16 +32281,16 @@
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>891</v>
+        <v>874</v>
       </c>
       <c r="B534" t="s">
-        <v>892</v>
+        <v>875</v>
       </c>
       <c r="C534" t="s">
         <v>844</v>
       </c>
       <c r="D534" t="s">
-        <v>890</v>
+        <v>876</v>
       </c>
       <c r="E534" t="s">
         <v>25</v>
@@ -31926,16 +32319,16 @@
     </row>
     <row r="535" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>893</v>
+        <v>877</v>
       </c>
       <c r="B535" t="s">
-        <v>894</v>
+        <v>878</v>
       </c>
       <c r="C535" t="s">
         <v>844</v>
       </c>
       <c r="D535" t="s">
-        <v>890</v>
+        <v>876</v>
       </c>
       <c r="E535" t="s">
         <v>25</v>
@@ -31964,16 +32357,16 @@
     </row>
     <row r="536" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
       <c r="B536" t="s">
-        <v>896</v>
+        <v>880</v>
       </c>
       <c r="C536" t="s">
         <v>844</v>
       </c>
       <c r="D536" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="E536" t="s">
         <v>25</v>
@@ -32002,16 +32395,16 @@
     </row>
     <row r="537" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>897</v>
+        <v>882</v>
       </c>
       <c r="B537" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
       <c r="C537" t="s">
         <v>844</v>
       </c>
       <c r="D537" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="E537" t="s">
         <v>25</v>
@@ -32040,16 +32433,16 @@
     </row>
     <row r="538" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>899</v>
+        <v>884</v>
       </c>
       <c r="B538" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="C538" t="s">
-        <v>901</v>
+        <v>844</v>
       </c>
       <c r="D538" t="s">
-        <v>25</v>
+        <v>881</v>
       </c>
       <c r="E538" t="s">
         <v>25</v>
@@ -32078,16 +32471,16 @@
     </row>
     <row r="539" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>902</v>
+        <v>886</v>
       </c>
       <c r="B539" t="s">
-        <v>903</v>
+        <v>887</v>
       </c>
       <c r="C539" t="s">
-        <v>901</v>
+        <v>844</v>
       </c>
       <c r="D539" t="s">
-        <v>25</v>
+        <v>881</v>
       </c>
       <c r="E539" t="s">
         <v>25</v>
@@ -32116,16 +32509,16 @@
     </row>
     <row r="540" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>904</v>
+        <v>888</v>
       </c>
       <c r="B540" t="s">
-        <v>905</v>
+        <v>889</v>
       </c>
       <c r="C540" t="s">
-        <v>901</v>
+        <v>844</v>
       </c>
       <c r="D540" t="s">
-        <v>25</v>
+        <v>890</v>
       </c>
       <c r="E540" t="s">
         <v>25</v>
@@ -32154,16 +32547,16 @@
     </row>
     <row r="541" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="B541" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
       <c r="C541" t="s">
-        <v>901</v>
+        <v>844</v>
       </c>
       <c r="D541" t="s">
-        <v>25</v>
+        <v>890</v>
       </c>
       <c r="E541" t="s">
         <v>25</v>
@@ -32192,16 +32585,16 @@
     </row>
     <row r="542" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>908</v>
+        <v>893</v>
       </c>
       <c r="B542" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="C542" t="s">
-        <v>901</v>
+        <v>844</v>
       </c>
       <c r="D542" t="s">
-        <v>25</v>
+        <v>890</v>
       </c>
       <c r="E542" t="s">
         <v>25</v>
@@ -32230,16 +32623,16 @@
     </row>
     <row r="543" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="B543" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="C543" t="s">
-        <v>901</v>
+        <v>844</v>
       </c>
       <c r="D543" t="s">
-        <v>25</v>
+        <v>890</v>
       </c>
       <c r="E543" t="s">
         <v>25</v>
@@ -32268,16 +32661,16 @@
     </row>
     <row r="544" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="B544" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="C544" t="s">
-        <v>901</v>
+        <v>844</v>
       </c>
       <c r="D544" t="s">
-        <v>25</v>
+        <v>890</v>
       </c>
       <c r="E544" t="s">
         <v>25</v>
@@ -32306,10 +32699,10 @@
     </row>
     <row r="545" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="B545" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="C545" t="s">
         <v>901</v>
@@ -32344,10 +32737,10 @@
     </row>
     <row r="546" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>916</v>
+        <v>902</v>
       </c>
       <c r="B546" t="s">
-        <v>917</v>
+        <v>903</v>
       </c>
       <c r="C546" t="s">
         <v>901</v>
@@ -32382,10 +32775,10 @@
     </row>
     <row r="547" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>918</v>
+        <v>904</v>
       </c>
       <c r="B547" t="s">
-        <v>919</v>
+        <v>905</v>
       </c>
       <c r="C547" t="s">
         <v>901</v>
@@ -32420,10 +32813,10 @@
     </row>
     <row r="548" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>920</v>
+        <v>906</v>
       </c>
       <c r="B548" t="s">
-        <v>921</v>
+        <v>907</v>
       </c>
       <c r="C548" t="s">
         <v>901</v>
@@ -32458,10 +32851,10 @@
     </row>
     <row r="549" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>922</v>
+        <v>908</v>
       </c>
       <c r="B549" t="s">
-        <v>923</v>
+        <v>909</v>
       </c>
       <c r="C549" t="s">
         <v>901</v>
@@ -32496,10 +32889,10 @@
     </row>
     <row r="550" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>924</v>
+        <v>910</v>
       </c>
       <c r="B550" t="s">
-        <v>925</v>
+        <v>911</v>
       </c>
       <c r="C550" t="s">
         <v>901</v>
@@ -32534,10 +32927,10 @@
     </row>
     <row r="551" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>926</v>
+        <v>912</v>
       </c>
       <c r="B551" t="s">
-        <v>927</v>
+        <v>913</v>
       </c>
       <c r="C551" t="s">
         <v>901</v>
@@ -32572,10 +32965,10 @@
     </row>
     <row r="552" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B552" t="s">
-        <v>929</v>
+        <v>915</v>
       </c>
       <c r="C552" t="s">
         <v>901</v>
@@ -32610,16 +33003,16 @@
     </row>
     <row r="553" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>930</v>
+        <v>916</v>
       </c>
       <c r="B553" t="s">
-        <v>931</v>
+        <v>917</v>
       </c>
       <c r="C553" t="s">
-        <v>932</v>
+        <v>901</v>
       </c>
       <c r="D553" t="s">
-        <v>933</v>
+        <v>25</v>
       </c>
       <c r="E553" t="s">
         <v>25</v>
@@ -32648,16 +33041,16 @@
     </row>
     <row r="554" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>934</v>
+        <v>918</v>
       </c>
       <c r="B554" t="s">
-        <v>935</v>
+        <v>919</v>
       </c>
       <c r="C554" t="s">
-        <v>932</v>
+        <v>901</v>
       </c>
       <c r="D554" t="s">
-        <v>933</v>
+        <v>25</v>
       </c>
       <c r="E554" t="s">
         <v>25</v>
@@ -32686,16 +33079,16 @@
     </row>
     <row r="555" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>936</v>
+        <v>920</v>
       </c>
       <c r="B555" t="s">
-        <v>937</v>
+        <v>921</v>
       </c>
       <c r="C555" t="s">
-        <v>932</v>
+        <v>901</v>
       </c>
       <c r="D555" t="s">
-        <v>933</v>
+        <v>25</v>
       </c>
       <c r="E555" t="s">
         <v>25</v>
@@ -32724,16 +33117,16 @@
     </row>
     <row r="556" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>938</v>
+        <v>922</v>
       </c>
       <c r="B556" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
       <c r="C556" t="s">
-        <v>932</v>
+        <v>901</v>
       </c>
       <c r="D556" t="s">
-        <v>933</v>
+        <v>25</v>
       </c>
       <c r="E556" t="s">
         <v>25</v>
@@ -32762,16 +33155,16 @@
     </row>
     <row r="557" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>940</v>
+        <v>924</v>
       </c>
       <c r="B557" t="s">
-        <v>941</v>
+        <v>925</v>
       </c>
       <c r="C557" t="s">
-        <v>932</v>
+        <v>901</v>
       </c>
       <c r="D557" t="s">
-        <v>942</v>
+        <v>25</v>
       </c>
       <c r="E557" t="s">
         <v>25</v>
@@ -32800,16 +33193,16 @@
     </row>
     <row r="558" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>943</v>
+        <v>926</v>
       </c>
       <c r="B558" t="s">
-        <v>944</v>
+        <v>927</v>
       </c>
       <c r="C558" t="s">
-        <v>932</v>
+        <v>901</v>
       </c>
       <c r="D558" t="s">
-        <v>942</v>
+        <v>25</v>
       </c>
       <c r="E558" t="s">
         <v>25</v>
@@ -32838,16 +33231,16 @@
     </row>
     <row r="559" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>945</v>
+        <v>928</v>
       </c>
       <c r="B559" t="s">
-        <v>946</v>
+        <v>929</v>
       </c>
       <c r="C559" t="s">
-        <v>932</v>
+        <v>901</v>
       </c>
       <c r="D559" t="s">
-        <v>942</v>
+        <v>25</v>
       </c>
       <c r="E559" t="s">
         <v>25</v>
@@ -32876,16 +33269,16 @@
     </row>
     <row r="560" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>947</v>
+        <v>930</v>
       </c>
       <c r="B560" t="s">
-        <v>948</v>
+        <v>931</v>
       </c>
       <c r="C560" t="s">
         <v>932</v>
       </c>
       <c r="D560" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="E560" t="s">
         <v>25</v>
@@ -32914,16 +33307,16 @@
     </row>
     <row r="561" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
       <c r="B561" t="s">
-        <v>950</v>
+        <v>935</v>
       </c>
       <c r="C561" t="s">
         <v>932</v>
       </c>
       <c r="D561" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="E561" t="s">
         <v>25</v>
@@ -32952,16 +33345,16 @@
     </row>
     <row r="562" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="B562" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
       <c r="C562" t="s">
         <v>932</v>
       </c>
       <c r="D562" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="E562" t="s">
         <v>25</v>
@@ -32990,16 +33383,16 @@
     </row>
     <row r="563" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="B563" t="s">
-        <v>954</v>
+        <v>939</v>
       </c>
       <c r="C563" t="s">
         <v>932</v>
       </c>
       <c r="D563" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="E563" t="s">
         <v>25</v>
@@ -33028,16 +33421,16 @@
     </row>
     <row r="564" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>955</v>
+        <v>940</v>
       </c>
       <c r="B564" t="s">
-        <v>956</v>
+        <v>941</v>
       </c>
       <c r="C564" t="s">
-        <v>957</v>
+        <v>932</v>
       </c>
       <c r="D564" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="E564" t="s">
         <v>25</v>
@@ -33066,16 +33459,16 @@
     </row>
     <row r="565" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="B565" t="s">
-        <v>960</v>
+        <v>944</v>
       </c>
       <c r="C565" t="s">
-        <v>957</v>
+        <v>932</v>
       </c>
       <c r="D565" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="E565" t="s">
         <v>25</v>
@@ -33104,16 +33497,16 @@
     </row>
     <row r="566" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>961</v>
+        <v>945</v>
       </c>
       <c r="B566" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="C566" t="s">
-        <v>957</v>
+        <v>932</v>
       </c>
       <c r="D566" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="E566" t="s">
         <v>25</v>
@@ -33142,16 +33535,16 @@
     </row>
     <row r="567" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>963</v>
+        <v>947</v>
       </c>
       <c r="B567" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="C567" t="s">
-        <v>957</v>
+        <v>932</v>
       </c>
       <c r="D567" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="E567" t="s">
         <v>25</v>
@@ -33180,16 +33573,16 @@
     </row>
     <row r="568" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="B568" t="s">
-        <v>966</v>
+        <v>950</v>
       </c>
       <c r="C568" t="s">
-        <v>957</v>
+        <v>932</v>
       </c>
       <c r="D568" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="E568" t="s">
         <v>25</v>
@@ -33218,16 +33611,16 @@
     </row>
     <row r="569" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>967</v>
+        <v>951</v>
       </c>
       <c r="B569" t="s">
-        <v>968</v>
+        <v>952</v>
       </c>
       <c r="C569" t="s">
-        <v>957</v>
+        <v>932</v>
       </c>
       <c r="D569" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="E569" t="s">
         <v>25</v>
@@ -33256,16 +33649,16 @@
     </row>
     <row r="570" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>969</v>
+        <v>953</v>
       </c>
       <c r="B570" t="s">
-        <v>970</v>
+        <v>954</v>
       </c>
       <c r="C570" t="s">
-        <v>957</v>
+        <v>932</v>
       </c>
       <c r="D570" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="E570" t="s">
         <v>25</v>
@@ -33294,10 +33687,10 @@
     </row>
     <row r="571" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="B571" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="C571" t="s">
         <v>957</v>
@@ -33332,16 +33725,16 @@
     </row>
     <row r="572" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>973</v>
+        <v>959</v>
       </c>
       <c r="B572" t="s">
-        <v>974</v>
+        <v>960</v>
       </c>
       <c r="C572" t="s">
         <v>957</v>
       </c>
       <c r="D572" t="s">
-        <v>975</v>
+        <v>958</v>
       </c>
       <c r="E572" t="s">
         <v>25</v>
@@ -33370,16 +33763,16 @@
     </row>
     <row r="573" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>976</v>
+        <v>961</v>
       </c>
       <c r="B573" t="s">
-        <v>977</v>
+        <v>962</v>
       </c>
       <c r="C573" t="s">
         <v>957</v>
       </c>
       <c r="D573" t="s">
-        <v>975</v>
+        <v>958</v>
       </c>
       <c r="E573" t="s">
         <v>25</v>
@@ -33408,16 +33801,16 @@
     </row>
     <row r="574" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="B574" t="s">
-        <v>979</v>
+        <v>964</v>
       </c>
       <c r="C574" t="s">
         <v>957</v>
       </c>
       <c r="D574" t="s">
-        <v>975</v>
+        <v>958</v>
       </c>
       <c r="E574" t="s">
         <v>25</v>
@@ -33446,16 +33839,16 @@
     </row>
     <row r="575" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>980</v>
+        <v>965</v>
       </c>
       <c r="B575" t="s">
-        <v>981</v>
+        <v>966</v>
       </c>
       <c r="C575" t="s">
         <v>957</v>
       </c>
       <c r="D575" t="s">
-        <v>975</v>
+        <v>958</v>
       </c>
       <c r="E575" t="s">
         <v>25</v>
@@ -33484,16 +33877,16 @@
     </row>
     <row r="576" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
       <c r="B576" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="C576" t="s">
         <v>957</v>
       </c>
       <c r="D576" t="s">
-        <v>975</v>
+        <v>958</v>
       </c>
       <c r="E576" t="s">
         <v>25</v>
@@ -33522,16 +33915,16 @@
     </row>
     <row r="577" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>984</v>
+        <v>969</v>
       </c>
       <c r="B577" t="s">
-        <v>985</v>
+        <v>970</v>
       </c>
       <c r="C577" t="s">
         <v>957</v>
       </c>
       <c r="D577" t="s">
-        <v>986</v>
+        <v>958</v>
       </c>
       <c r="E577" t="s">
         <v>25</v>
@@ -33560,16 +33953,16 @@
     </row>
     <row r="578" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="B578" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="C578" t="s">
         <v>957</v>
       </c>
       <c r="D578" t="s">
-        <v>986</v>
+        <v>958</v>
       </c>
       <c r="E578" t="s">
         <v>25</v>
@@ -33598,16 +33991,16 @@
     </row>
     <row r="579" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="B579" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="C579" t="s">
         <v>957</v>
       </c>
       <c r="D579" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="E579" t="s">
         <v>25</v>
@@ -33636,16 +34029,16 @@
     </row>
     <row r="580" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
       <c r="B580" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="C580" t="s">
         <v>957</v>
       </c>
       <c r="D580" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="E580" t="s">
         <v>25</v>
@@ -33674,16 +34067,16 @@
     </row>
     <row r="581" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="B581" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="C581" t="s">
         <v>957</v>
       </c>
       <c r="D581" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="E581" t="s">
         <v>25</v>
@@ -33712,16 +34105,16 @@
     </row>
     <row r="582" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="B582" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="C582" t="s">
         <v>957</v>
       </c>
       <c r="D582" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="E582" t="s">
         <v>25</v>
@@ -33750,16 +34143,16 @@
     </row>
     <row r="583" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="B583" t="s">
-        <v>999</v>
+        <v>983</v>
       </c>
       <c r="C583" t="s">
         <v>957</v>
       </c>
       <c r="D583" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="E583" t="s">
         <v>25</v>
@@ -33788,16 +34181,16 @@
     </row>
     <row r="584" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="B584" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="C584" t="s">
         <v>957</v>
       </c>
       <c r="D584" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="E584" t="s">
         <v>25</v>
@@ -33826,16 +34219,16 @@
     </row>
     <row r="585" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="B585" t="s">
-        <v>1003</v>
+        <v>988</v>
       </c>
       <c r="C585" t="s">
         <v>957</v>
       </c>
       <c r="D585" t="s">
-        <v>1004</v>
+        <v>986</v>
       </c>
       <c r="E585" t="s">
         <v>25</v>
@@ -33864,16 +34257,16 @@
     </row>
     <row r="586" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="B586" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="C586" t="s">
         <v>957</v>
       </c>
       <c r="D586" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="E586" t="s">
         <v>25</v>
@@ -33902,16 +34295,16 @@
     </row>
     <row r="587" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>1007</v>
+        <v>992</v>
       </c>
       <c r="B587" t="s">
-        <v>1008</v>
+        <v>993</v>
       </c>
       <c r="C587" t="s">
         <v>957</v>
       </c>
       <c r="D587" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="E587" t="s">
         <v>25</v>
@@ -33940,16 +34333,16 @@
     </row>
     <row r="588" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>1009</v>
+        <v>994</v>
       </c>
       <c r="B588" t="s">
-        <v>1010</v>
+        <v>995</v>
       </c>
       <c r="C588" t="s">
         <v>957</v>
       </c>
       <c r="D588" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="E588" t="s">
         <v>25</v>
@@ -33978,16 +34371,16 @@
     </row>
     <row r="589" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>1011</v>
+        <v>996</v>
       </c>
       <c r="B589" t="s">
-        <v>1012</v>
+        <v>997</v>
       </c>
       <c r="C589" t="s">
         <v>957</v>
       </c>
       <c r="D589" t="s">
-        <v>1013</v>
+        <v>991</v>
       </c>
       <c r="E589" t="s">
         <v>25</v>
@@ -34016,16 +34409,16 @@
     </row>
     <row r="590" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="B590" t="s">
-        <v>1015</v>
+        <v>999</v>
       </c>
       <c r="C590" t="s">
         <v>957</v>
       </c>
       <c r="D590" t="s">
-        <v>1013</v>
+        <v>991</v>
       </c>
       <c r="E590" t="s">
         <v>25</v>
@@ -34054,16 +34447,16 @@
     </row>
     <row r="591" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="B591" t="s">
-        <v>1017</v>
+        <v>1001</v>
       </c>
       <c r="C591" t="s">
         <v>957</v>
       </c>
       <c r="D591" t="s">
-        <v>1013</v>
+        <v>991</v>
       </c>
       <c r="E591" t="s">
         <v>25</v>
@@ -34092,16 +34485,16 @@
     </row>
     <row r="592" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="B592" t="s">
-        <v>1019</v>
+        <v>1003</v>
       </c>
       <c r="C592" t="s">
         <v>957</v>
       </c>
       <c r="D592" t="s">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="E592" t="s">
         <v>25</v>
@@ -34130,16 +34523,16 @@
     </row>
     <row r="593" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>1020</v>
+        <v>1005</v>
       </c>
       <c r="B593" t="s">
-        <v>1021</v>
+        <v>1006</v>
       </c>
       <c r="C593" t="s">
         <v>957</v>
       </c>
       <c r="D593" t="s">
-        <v>1022</v>
+        <v>1004</v>
       </c>
       <c r="E593" t="s">
         <v>25</v>
@@ -34168,16 +34561,16 @@
     </row>
     <row r="594" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>1023</v>
+        <v>1007</v>
       </c>
       <c r="B594" t="s">
-        <v>1024</v>
+        <v>1008</v>
       </c>
       <c r="C594" t="s">
         <v>957</v>
       </c>
       <c r="D594" t="s">
-        <v>1022</v>
+        <v>1004</v>
       </c>
       <c r="E594" t="s">
         <v>25</v>
@@ -34206,16 +34599,16 @@
     </row>
     <row r="595" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>1025</v>
+        <v>1009</v>
       </c>
       <c r="B595" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
       <c r="C595" t="s">
         <v>957</v>
       </c>
       <c r="D595" t="s">
-        <v>1022</v>
+        <v>1004</v>
       </c>
       <c r="E595" t="s">
         <v>25</v>
@@ -34244,16 +34637,16 @@
     </row>
     <row r="596" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
       <c r="B596" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="C596" t="s">
         <v>957</v>
       </c>
       <c r="D596" t="s">
-        <v>1022</v>
+        <v>1013</v>
       </c>
       <c r="E596" t="s">
         <v>25</v>
@@ -34282,16 +34675,16 @@
     </row>
     <row r="597" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>1029</v>
+        <v>1014</v>
       </c>
       <c r="B597" t="s">
-        <v>1030</v>
+        <v>1015</v>
       </c>
       <c r="C597" t="s">
         <v>957</v>
       </c>
       <c r="D597" t="s">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="E597" t="s">
         <v>25</v>
@@ -34320,16 +34713,16 @@
     </row>
     <row r="598" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
       <c r="B598" t="s">
-        <v>1033</v>
+        <v>1017</v>
       </c>
       <c r="C598" t="s">
         <v>957</v>
       </c>
       <c r="D598" t="s">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="E598" t="s">
         <v>25</v>
@@ -34358,16 +34751,16 @@
     </row>
     <row r="599" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="B599" t="s">
-        <v>1035</v>
+        <v>1019</v>
       </c>
       <c r="C599" t="s">
         <v>957</v>
       </c>
       <c r="D599" t="s">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="E599" t="s">
         <v>25</v>
@@ -34396,16 +34789,16 @@
     </row>
     <row r="600" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>1036</v>
+        <v>1020</v>
       </c>
       <c r="B600" t="s">
-        <v>1037</v>
+        <v>1021</v>
       </c>
       <c r="C600" t="s">
         <v>957</v>
       </c>
       <c r="D600" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
       <c r="E600" t="s">
         <v>25</v>
@@ -34434,16 +34827,16 @@
     </row>
     <row r="601" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>1038</v>
+        <v>1023</v>
       </c>
       <c r="B601" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="C601" t="s">
         <v>957</v>
       </c>
       <c r="D601" t="s">
-        <v>1040</v>
+        <v>1022</v>
       </c>
       <c r="E601" t="s">
         <v>25</v>
@@ -34472,16 +34865,16 @@
     </row>
     <row r="602" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
       <c r="B602" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="C602" t="s">
         <v>957</v>
       </c>
       <c r="D602" t="s">
-        <v>1040</v>
+        <v>1022</v>
       </c>
       <c r="E602" t="s">
         <v>25</v>
@@ -34510,16 +34903,16 @@
     </row>
     <row r="603" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="B603" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
       <c r="C603" t="s">
         <v>957</v>
       </c>
       <c r="D603" t="s">
-        <v>1040</v>
+        <v>1022</v>
       </c>
       <c r="E603" t="s">
         <v>25</v>
@@ -34548,16 +34941,16 @@
     </row>
     <row r="604" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1045</v>
+        <v>1029</v>
       </c>
       <c r="B604" t="s">
-        <v>1046</v>
+        <v>1030</v>
       </c>
       <c r="C604" t="s">
         <v>957</v>
       </c>
       <c r="D604" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="E604" t="s">
         <v>25</v>
@@ -34586,16 +34979,16 @@
     </row>
     <row r="605" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="B605" t="s">
-        <v>1048</v>
+        <v>1033</v>
       </c>
       <c r="C605" t="s">
         <v>957</v>
       </c>
       <c r="D605" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="E605" t="s">
         <v>25</v>
@@ -34624,39 +35017,305 @@
     </row>
     <row r="606" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="B606" t="s">
-        <v>1050</v>
+        <v>1035</v>
       </c>
       <c r="C606" t="s">
         <v>957</v>
       </c>
       <c r="D606" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E606" t="s">
+        <v>25</v>
+      </c>
+      <c r="F606" t="s">
+        <v>25</v>
+      </c>
+      <c r="G606" t="s">
+        <v>25</v>
+      </c>
+      <c r="H606" t="s">
+        <v>19</v>
+      </c>
+      <c r="I606" t="s">
+        <v>25</v>
+      </c>
+      <c r="J606" t="s">
+        <v>25</v>
+      </c>
+      <c r="K606" t="s">
+        <v>25</v>
+      </c>
+      <c r="L606" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A607" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C607" t="s">
+        <v>957</v>
+      </c>
+      <c r="D607" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E607" t="s">
+        <v>25</v>
+      </c>
+      <c r="F607" t="s">
+        <v>25</v>
+      </c>
+      <c r="G607" t="s">
+        <v>25</v>
+      </c>
+      <c r="H607" t="s">
+        <v>19</v>
+      </c>
+      <c r="I607" t="s">
+        <v>25</v>
+      </c>
+      <c r="J607" t="s">
+        <v>25</v>
+      </c>
+      <c r="K607" t="s">
+        <v>25</v>
+      </c>
+      <c r="L607" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A608" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C608" t="s">
+        <v>957</v>
+      </c>
+      <c r="D608" t="s">
         <v>1040</v>
       </c>
-      <c r="E606" t="s">
-        <v>25</v>
-      </c>
-      <c r="F606" t="s">
-        <v>25</v>
-      </c>
-      <c r="G606" t="s">
-        <v>25</v>
-      </c>
-      <c r="H606" t="s">
-        <v>19</v>
-      </c>
-      <c r="I606" t="s">
-        <v>25</v>
-      </c>
-      <c r="J606" t="s">
-        <v>25</v>
-      </c>
-      <c r="K606" t="s">
-        <v>25</v>
-      </c>
-      <c r="L606" t="s">
+      <c r="E608" t="s">
+        <v>25</v>
+      </c>
+      <c r="F608" t="s">
+        <v>25</v>
+      </c>
+      <c r="G608" t="s">
+        <v>25</v>
+      </c>
+      <c r="H608" t="s">
+        <v>19</v>
+      </c>
+      <c r="I608" t="s">
+        <v>25</v>
+      </c>
+      <c r="J608" t="s">
+        <v>25</v>
+      </c>
+      <c r="K608" t="s">
+        <v>25</v>
+      </c>
+      <c r="L608" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A609" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B609" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C609" t="s">
+        <v>957</v>
+      </c>
+      <c r="D609" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E609" t="s">
+        <v>25</v>
+      </c>
+      <c r="F609" t="s">
+        <v>25</v>
+      </c>
+      <c r="G609" t="s">
+        <v>25</v>
+      </c>
+      <c r="H609" t="s">
+        <v>19</v>
+      </c>
+      <c r="I609" t="s">
+        <v>25</v>
+      </c>
+      <c r="J609" t="s">
+        <v>25</v>
+      </c>
+      <c r="K609" t="s">
+        <v>25</v>
+      </c>
+      <c r="L609" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A610" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B610" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C610" t="s">
+        <v>957</v>
+      </c>
+      <c r="D610" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E610" t="s">
+        <v>25</v>
+      </c>
+      <c r="F610" t="s">
+        <v>25</v>
+      </c>
+      <c r="G610" t="s">
+        <v>25</v>
+      </c>
+      <c r="H610" t="s">
+        <v>19</v>
+      </c>
+      <c r="I610" t="s">
+        <v>25</v>
+      </c>
+      <c r="J610" t="s">
+        <v>25</v>
+      </c>
+      <c r="K610" t="s">
+        <v>25</v>
+      </c>
+      <c r="L610" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C611" t="s">
+        <v>957</v>
+      </c>
+      <c r="D611" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E611" t="s">
+        <v>25</v>
+      </c>
+      <c r="F611" t="s">
+        <v>25</v>
+      </c>
+      <c r="G611" t="s">
+        <v>25</v>
+      </c>
+      <c r="H611" t="s">
+        <v>19</v>
+      </c>
+      <c r="I611" t="s">
+        <v>25</v>
+      </c>
+      <c r="J611" t="s">
+        <v>25</v>
+      </c>
+      <c r="K611" t="s">
+        <v>25</v>
+      </c>
+      <c r="L611" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C612" t="s">
+        <v>957</v>
+      </c>
+      <c r="D612" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E612" t="s">
+        <v>25</v>
+      </c>
+      <c r="F612" t="s">
+        <v>25</v>
+      </c>
+      <c r="G612" t="s">
+        <v>25</v>
+      </c>
+      <c r="H612" t="s">
+        <v>19</v>
+      </c>
+      <c r="I612" t="s">
+        <v>25</v>
+      </c>
+      <c r="J612" t="s">
+        <v>25</v>
+      </c>
+      <c r="K612" t="s">
+        <v>25</v>
+      </c>
+      <c r="L612" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A613" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C613" t="s">
+        <v>957</v>
+      </c>
+      <c r="D613" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E613" t="s">
+        <v>25</v>
+      </c>
+      <c r="F613" t="s">
+        <v>25</v>
+      </c>
+      <c r="G613" t="s">
+        <v>25</v>
+      </c>
+      <c r="H613" t="s">
+        <v>19</v>
+      </c>
+      <c r="I613" t="s">
+        <v>25</v>
+      </c>
+      <c r="J613" t="s">
+        <v>25</v>
+      </c>
+      <c r="K613" t="s">
+        <v>25</v>
+      </c>
+      <c r="L613" t="s">
         <v>25</v>
       </c>
     </row>
@@ -34665,7 +35324,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 G38:L38 B39:L39 B37:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 A11:D12 F10:F12 J10:L12 H10:H12 B17:D18 F17:F18 H17:H18 J17:L17 K18:L18 A28:G28 L21 F22:F24 J22:L24 A33:D36 L33 A21:D25 H21:H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F34:F36 J34:L36 H33:H36 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67:A68 J67:L68 J72:L73 F72 F73:G73 F67:G68 C67:D68 H72 A72:A74 A84 I84:L84 C72:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87 A91:D91 F91 H91:L91 A97:G99 L98 A96:D96 F96 H96:L96 A122:D122 I97:L97 I98:J98 I99:L99 A101:D101 F101 A104:D104 H104:I104 J101:L101 H101 L104 A109:D109 H109:I109 L109 A113:G113 I113:L113 A117 F117 C117:D117 A121 C121:D121 F121 J117:L117 J121:L121 A138:D138 A126:D126 K126:L126 H117 H121 H122:I122 L122 H126:I126 A127:D127 H127:I127 L127 A128:G128 I128:L128 A130:D130 F130 H130:L130 A131:G131 I131:L131 A132:G132 I132:L132 A134:D134 F134 H134:L134 A153:G154 A142:D142 F142 H138 J138:L138 H142:L142 A143:G143 I143:L143 A144:D144 H144:I144 L144 A151:D151 F151 H151:L151 A162 A155:F155 I155:L155 A156:F156 I156:L156 A152:G152 I152:L152 I153:L154 A157:G157 I157:L157 A159:D159 F159 H159:L159 A167:D167 A163 C163:G163 C162:D162 J163:L163 L162 H162 A165:D165 F165 H165:L165 A181:L181 A172:D172 I172:L172 A168:G168 I168:L168 F167 H167:L167 F172 A176:D176 F176 H176:L176 A177:G177 I177:L177 A178:G178 I178:L178 A179:G179 I179:L179 A180:E180 G180:I180 L180 A206:D206 A182:G182 I182:L182 A188:D188 F188 H188:L188 A189:G189 I189:L189 A191:D191 F191 H191:L191 A192:D192 H192:I192 L192 A196:D196 F196 A225:L606 A223:I223 K223:L223 H196:L196 A197:D197 H197:I197 L197 A198:G198 I198:L198 A200:D200 F200 H200:L200 A202:D202 F202 H202:L202 A210:G210 A209:D209 H209:L209 A203:D203 H203:I203 L203 A224:I224 K224:L224 F206 H206:L206 F209 A221:L222 A213:F213 I213:L213 A212:G212 A211:F211 I211:L211 I210:L210 I212:L212 A214:G214 I214:L214 A217:D217 F217 H217 A220:D220 F220 H220 J217:L217 J220:L220" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L3 A50:D50 L37 G37:I37 G38:L38 B39:L39 B37:E38 A81 A56:D56 L56 A59:D59 J59:L59 A62:D62 J62:L62 H56 F59 F62 H59 H62 A53:D53 H53:I53 A5:L7 A4:E4 G4:L4 L53 F50 H50:L50 A19:L20 B10:D10 A11:D12 F10:F12 J10:L12 H10:H12 B17:D18 F17:F18 H17:H18 J17:L17 K18:L18 A28:G28 L21 F22:F24 J22:L24 A33:D36 L33 A21:D25 H21:H25 L25 A29:D29 H29:I29 L29 K28:L28 I28 F34:F36 J34:L36 H33:H36 A63:G63 I63:L63 A66:D66 F66 H66:L66 A67:A68 J67:L68 J72:L73 F72 F73:G73 F67:G68 C67:D68 H72 A72:A74 A84 I84:L84 C72:D74 A77 C77:D77 C81:D81 L74 J77:L77 J81:L81 F84:G84 F77 F81 H74 H77 H81 C84:D84 A85:D85 L85 A87 J87:L87 H85 F87 H87 C87:D87 A91:D91 F91 H91:L91 A97:G99 L98 A96:D96 F96 H96:L96 A122:D122 I97:L97 I98:J98 I99:L99 A101:D101 F101 A104:D104 H104:I104 J101:L101 H101 L104 A109:D109 H109:I109 L109 A113:G113 I113:L113 A117 F117 C117:D117 A121 C121:D121 F121 J117:L117 J121:L121 A138:D138 A126:D126 K126:L126 H117 H121 H122:I122 L122 H126:I126 A127:D127 H127:I127 L127 A128:G128 I128:L128 A130:D130 F130 H130:L130 A131:G131 I131:L131 A132:G132 I132:L132 A134:D134 F134 H134:L134 A153:G154 A142:D142 F142 H138 J138:L138 H142:L142 A143:G143 I143:L143 A144:D144 H144:I144 L144 A151:D151 F151 H151:L151 A162 A155:F155 I155:L155 A156:F156 I156:L156 A152:G152 I152:L152 I153:L154 A157:G157 I157:L157 A159:D159 F159 H159:L159 A167:D167 A163 C163:G163 C162:D162 J163:L163 L162 H162 A165:D165 F165 H165:L165 A181:L181 A172:D172 I172:L172 A168:G168 I168:L168 F167 H167:L167 F172 A176:D176 F176 H176:L176 A177:G177 I177:L177 A178:G178 I178:L178 A179:G179 I179:L179 A180:E180 G180:I180 L180 A206:D206 A182:G182 I182:L182 A188:D188 F188 H188:L188 A189:G189 I189:L189 A191:D191 F191 H191:L191 A192:D192 H192:I192 L192 A196:D196 F196 A237:L246 A223:G223 K223:L223 H196:L196 A197:D197 H197:I197 L197 A198:G198 I198:L198 A200:D200 F200 H200:L200 A202:D202 F202 H202:L202 A210:G210 A209:D209 H209:L209 A203:D203 H203:I203 L203 A224:G224 K224:L224 F206 H206:L206 F209 A222:G222 A213:F213 I213:L213 A212:G212 A211:F211 I211:L211 I210:L210 I212:L212 A214:G214 I214:L214 A217:D217 F217 H217 A220:D220 F220 H220 J217:L217 J220:L220 A221:G221 I221:L221 I222:L222 I223 A225:G225 I225:L225 I224 A226:G226 I226:L226 A227:G227 I227:L227 A229:D229 F229 H229:L229 A248:L613 A247:I247 K247:L247 A236:D236 F236 H236:L236" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/BD/Catalogo_Bloopia_Estructurado.xlsx
+++ b/BD/Catalogo_Bloopia_Estructurado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimilitareduco-my.sharepoint.com/personal/est_tatiana_castillo_unimilitar_edu_co/Documents/Backup/Descargas/copiaBloopia (2)/copiaBloopia/Bloopia/BD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1272" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{002A7DE1-D384-4EA7-9C26-FC5F6E0139C7}"/>
+  <xr:revisionPtr revIDLastSave="1288" documentId="11_39DF2C4B9F61F837F4C1046A4016A4F540A1B085" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{554D9022-7F6D-41B7-A97A-38C83D927FCF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8001" uniqueCount="1401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8080" uniqueCount="1407">
   <si>
     <t>Codigo</t>
   </si>
@@ -12032,6 +12032,199 @@
 Evitar sobrecargarla con exceso de peso.
 Instalar únicamente sobre superficies resistentes y niveladas.
 Mantener libre de residuos para conservar el acabado del acero inoxidable.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mantén tu ropa limpia, seca y perfectamente organizada con este </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tendedero Plegable Multifuncional.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Su diseño de varios niveles ofrece una gran capacidad de secado sin ocupar demasiado espacio, convirtiéndose en el aliado ideal para apartamentos, casas, balcones, patios o zonas de lavandería.
+Fabricado con una estructura resistente de acero y plástico de alta calidad, proporciona estabilidad y durabilidad para el uso diario. Además, su diseño plegable permite guardarlo fácilmente cuando no esté en uso, optimizando el espacio en tu hogar.</t>
+    </r>
+  </si>
+  <si>
+    <t>assets/productos/hogar/tendedero/tendedero.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/hogar/tendedero/tendedero2.webp</t>
+  </si>
+  <si>
+    <t>assets/productos/hogar/tendedero/tendedero3.webp</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tendedero Plegable Multifuncional de 3 Niveles,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ideal para secar y organizar ropa aprovechando al máximo el espacio. Resistente, ligero, fácil de mover y perfecto para uso en interiores o exteriores.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Especificaciones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Tipo: Tendedero plegable multifuncional.
+Material: Acero y plástico de alta resistencia.
+Uso: Interior y exterior.
+Alto: 140 cm.
+Ancho: 60 cm.
+Largo: 75 cm.
+Peso neto: 2 a 2.5 kg.
+Color: Según disponibilidad.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beneficios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Diseño plegable para ahorrar espacio.
+Gran capacidad para secar varias prendas al mismo tiempo.
+Estructura resistente y estable.
+Ideal para interiores, balcones, patios y lavanderías.
+Fácil de armar, mover y almacenar.
+Materiales resistentes a la humedad y al uso diario.
+Aprovecha el espacio vertical para una mejor organización.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Contenido del empaque:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1 Tendedero plegable multifuncional.
+Manual de armado (si aplica).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Importante:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Las medidas son aproximadas y pueden variar ligeramente según el lote de fabricación. Se recomienda distribuir el peso de forma uniforme para garantizar una mayor estabilidad y prolongar la vida útil del producto.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cuidados:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Limpiar con un paño húmedo y secar después de la limpieza.
+Evitar sobrecargar el tendedero con peso excesivo.
+Guardar completamente seco cuando no esté en uso.
+Utilizar sobre superficies planas y estables.
+Revisar periódicamente las uniones y sistema de plegado.
+Evitar la exposición prolongada a condiciones climáticas extremas para conservar su acabado y durabilidad.</t>
     </r>
   </si>
 </sst>
@@ -12428,7 +12621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M613"/>
+  <dimension ref="A1:M615"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -21273,14 +21466,14 @@
       <c r="D239" t="s">
         <v>238</v>
       </c>
-      <c r="E239" t="s">
-        <v>25</v>
-      </c>
-      <c r="F239" t="s">
-        <v>25</v>
+      <c r="E239">
+        <v>77167</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>1401</v>
       </c>
       <c r="G239" t="s">
-        <v>25</v>
+        <v>1402</v>
       </c>
       <c r="H239" t="s">
         <v>19</v>
@@ -21289,10 +21482,10 @@
         <v>25</v>
       </c>
       <c r="J239" t="s">
-        <v>25</v>
-      </c>
-      <c r="K239" t="s">
-        <v>25</v>
+        <v>1405</v>
+      </c>
+      <c r="K239" s="1" t="s">
+        <v>1406</v>
       </c>
       <c r="L239" t="s">
         <v>25</v>
@@ -21300,10 +21493,10 @@
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B240" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C240" t="s">
         <v>237</v>
@@ -21311,14 +21504,14 @@
       <c r="D240" t="s">
         <v>238</v>
       </c>
-      <c r="E240" t="s">
-        <v>25</v>
+      <c r="E240">
+        <v>77167</v>
       </c>
       <c r="F240" t="s">
         <v>25</v>
       </c>
       <c r="G240" t="s">
-        <v>25</v>
+        <v>1403</v>
       </c>
       <c r="H240" t="s">
         <v>19</v>
@@ -21338,10 +21531,10 @@
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B241" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C241" t="s">
         <v>237</v>
@@ -21349,14 +21542,14 @@
       <c r="D241" t="s">
         <v>238</v>
       </c>
-      <c r="E241" t="s">
-        <v>25</v>
+      <c r="E241">
+        <v>77167</v>
       </c>
       <c r="F241" t="s">
         <v>25</v>
       </c>
       <c r="G241" t="s">
-        <v>25</v>
+        <v>1404</v>
       </c>
       <c r="H241" t="s">
         <v>19</v>
@@ -21376,10 +21569,10 @@
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B242" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C242" t="s">
         <v>237</v>
@@ -21414,10 +21607,10 @@
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B243" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C243" t="s">
         <v>237</v>
@@ -21452,10 +21645,10 @@
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B244" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C244" t="s">
         <v>237</v>
@@ -21490,10 +21683,10 @@
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B245" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C245" t="s">
         <v>237</v>
@@ -21528,10 +21721,10 @@
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B246" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C246" t="s">
         <v>237</v>
@@ -21566,10 +21759,10 @@
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B247" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C247" t="s">
         <v>237</v>
@@ -21592,6 +21785,9 @@
       <c r="I247" t="s">
         <v>25</v>
       </c>
+      <c r="J247" t="s">
+        <v>25</v>
+      </c>
       <c r="K247" t="s">
         <v>25</v>
       </c>
@@ -21601,10 +21797,10 @@
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B248" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C248" t="s">
         <v>237</v>
@@ -21639,10 +21835,10 @@
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B249" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C249" t="s">
         <v>237</v>
@@ -21665,9 +21861,6 @@
       <c r="I249" t="s">
         <v>25</v>
       </c>
-      <c r="J249" t="s">
-        <v>25</v>
-      </c>
       <c r="K249" t="s">
         <v>25</v>
       </c>
@@ -21677,10 +21870,10 @@
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B250" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C250" t="s">
         <v>237</v>
@@ -21715,10 +21908,10 @@
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B251" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C251" t="s">
         <v>237</v>
@@ -21753,10 +21946,10 @@
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B252" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C252" t="s">
         <v>237</v>
@@ -21779,9 +21972,6 @@
       <c r="I252" t="s">
         <v>25</v>
       </c>
-      <c r="J252" t="s">
-        <v>25</v>
-      </c>
       <c r="K252" t="s">
         <v>25</v>
       </c>
@@ -21791,10 +21981,10 @@
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B253" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C253" t="s">
         <v>237</v>
@@ -21829,10 +22019,10 @@
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B254" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C254" t="s">
         <v>237</v>
@@ -21867,10 +22057,10 @@
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B255" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C255" t="s">
         <v>237</v>
@@ -21905,10 +22095,10 @@
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B256" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C256" t="s">
         <v>237</v>
@@ -21943,10 +22133,10 @@
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B257" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C257" t="s">
         <v>237</v>
@@ -21981,10 +22171,10 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B258" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C258" t="s">
         <v>237</v>
@@ -22019,10 +22209,10 @@
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B259" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C259" t="s">
         <v>237</v>
@@ -22057,10 +22247,10 @@
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B260" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C260" t="s">
         <v>237</v>
@@ -22095,10 +22285,10 @@
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B261" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C261" t="s">
         <v>237</v>
@@ -22133,10 +22323,10 @@
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B262" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C262" t="s">
         <v>237</v>
@@ -22171,10 +22361,10 @@
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B263" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C263" t="s">
         <v>237</v>
@@ -22209,10 +22399,10 @@
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B264" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C264" t="s">
         <v>237</v>
@@ -22247,10 +22437,10 @@
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B265" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C265" t="s">
         <v>237</v>
@@ -22285,16 +22475,16 @@
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B266" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C266" t="s">
         <v>237</v>
       </c>
       <c r="D266" t="s">
-        <v>313</v>
+        <v>238</v>
       </c>
       <c r="E266" t="s">
         <v>25</v>
@@ -22323,16 +22513,16 @@
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B267" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C267" t="s">
         <v>237</v>
       </c>
       <c r="D267" t="s">
-        <v>313</v>
+        <v>238</v>
       </c>
       <c r="E267" t="s">
         <v>25</v>
@@ -22361,10 +22551,10 @@
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B268" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C268" t="s">
         <v>237</v>
@@ -22399,10 +22589,10 @@
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B269" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C269" t="s">
         <v>237</v>
@@ -22437,10 +22627,10 @@
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B270" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C270" t="s">
         <v>237</v>
@@ -22475,10 +22665,10 @@
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B271" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C271" t="s">
         <v>237</v>
@@ -22513,10 +22703,10 @@
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B272" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C272" t="s">
         <v>237</v>
@@ -22551,10 +22741,10 @@
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B273" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C273" t="s">
         <v>237</v>
@@ -22589,10 +22779,10 @@
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B274" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C274" t="s">
         <v>237</v>
@@ -22627,10 +22817,10 @@
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B275" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C275" t="s">
         <v>237</v>
@@ -22665,16 +22855,16 @@
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B276" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C276" t="s">
         <v>237</v>
       </c>
       <c r="D276" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="E276" t="s">
         <v>25</v>
@@ -22703,16 +22893,16 @@
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B277" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C277" t="s">
         <v>237</v>
       </c>
       <c r="D277" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="E277" t="s">
         <v>25</v>
@@ -22741,10 +22931,10 @@
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B278" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C278" t="s">
         <v>237</v>
@@ -22779,16 +22969,16 @@
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B279" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C279" t="s">
         <v>237</v>
       </c>
       <c r="D279" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="E279" t="s">
         <v>25</v>
@@ -22817,16 +23007,16 @@
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B280" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C280" t="s">
         <v>237</v>
       </c>
       <c r="D280" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="E280" t="s">
         <v>25</v>
@@ -22855,10 +23045,10 @@
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B281" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C281" t="s">
         <v>237</v>
@@ -22893,10 +23083,10 @@
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B282" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C282" t="s">
         <v>237</v>
@@ -22931,10 +23121,10 @@
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B283" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C283" t="s">
         <v>237</v>
@@ -22969,10 +23159,10 @@
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B284" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C284" t="s">
         <v>237</v>
@@ -23007,10 +23197,10 @@
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B285" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C285" t="s">
         <v>237</v>
@@ -23045,16 +23235,16 @@
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B286" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C286" t="s">
         <v>237</v>
       </c>
       <c r="D286" t="s">
-        <v>223</v>
+        <v>341</v>
       </c>
       <c r="E286" t="s">
         <v>25</v>
@@ -23083,16 +23273,16 @@
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B287" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C287" t="s">
         <v>237</v>
       </c>
       <c r="D287" t="s">
-        <v>223</v>
+        <v>341</v>
       </c>
       <c r="E287" t="s">
         <v>25</v>
@@ -23121,10 +23311,10 @@
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B288" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C288" t="s">
         <v>237</v>
@@ -23159,10 +23349,10 @@
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B289" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C289" t="s">
         <v>237</v>
@@ -23197,10 +23387,10 @@
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B290" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C290" t="s">
         <v>237</v>
@@ -23235,10 +23425,10 @@
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B291" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C291" t="s">
         <v>237</v>
@@ -23273,10 +23463,10 @@
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B292" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C292" t="s">
         <v>237</v>
@@ -23311,10 +23501,10 @@
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B293" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C293" t="s">
         <v>237</v>
@@ -23349,10 +23539,10 @@
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B294" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C294" t="s">
         <v>237</v>
@@ -23387,10 +23577,10 @@
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B295" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C295" t="s">
         <v>237</v>
@@ -23425,10 +23615,10 @@
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B296" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C296" t="s">
         <v>237</v>
@@ -23463,7 +23653,7 @@
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B297" t="s">
         <v>372</v>
@@ -23501,7 +23691,7 @@
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B298" t="s">
         <v>372</v>
@@ -23539,7 +23729,7 @@
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B299" t="s">
         <v>372</v>
@@ -23577,10 +23767,10 @@
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B300" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C300" t="s">
         <v>237</v>
@@ -23615,10 +23805,10 @@
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B301" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C301" t="s">
         <v>237</v>
@@ -23653,10 +23843,10 @@
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B302" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C302" t="s">
         <v>237</v>
@@ -23691,10 +23881,10 @@
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B303" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C303" t="s">
         <v>237</v>
@@ -23729,10 +23919,10 @@
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B304" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C304" t="s">
         <v>237</v>
@@ -23767,10 +23957,10 @@
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B305" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C305" t="s">
         <v>237</v>
@@ -23805,10 +23995,10 @@
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B306" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C306" t="s">
         <v>237</v>
@@ -23843,10 +24033,10 @@
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B307" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C307" t="s">
         <v>237</v>
@@ -23881,10 +24071,10 @@
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B308" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C308" t="s">
         <v>237</v>
@@ -23919,10 +24109,10 @@
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B309" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C309" t="s">
         <v>237</v>
@@ -23957,10 +24147,10 @@
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B310" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C310" t="s">
         <v>237</v>
@@ -23995,10 +24185,10 @@
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B311" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C311" t="s">
         <v>237</v>
@@ -24033,16 +24223,16 @@
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B312" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C312" t="s">
         <v>237</v>
       </c>
       <c r="D312" t="s">
-        <v>403</v>
+        <v>223</v>
       </c>
       <c r="E312" t="s">
         <v>25</v>
@@ -24071,16 +24261,16 @@
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B313" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C313" t="s">
         <v>237</v>
       </c>
       <c r="D313" t="s">
-        <v>403</v>
+        <v>223</v>
       </c>
       <c r="E313" t="s">
         <v>25</v>
@@ -24109,10 +24299,10 @@
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B314" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C314" t="s">
         <v>237</v>
@@ -24147,10 +24337,10 @@
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B315" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C315" t="s">
         <v>237</v>
@@ -24185,10 +24375,10 @@
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B316" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C316" t="s">
         <v>237</v>
@@ -24223,10 +24413,10 @@
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B317" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C317" t="s">
         <v>237</v>
@@ -24261,10 +24451,10 @@
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B318" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C318" t="s">
         <v>237</v>
@@ -24299,10 +24489,10 @@
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B319" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C319" t="s">
         <v>237</v>
@@ -24337,10 +24527,10 @@
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B320" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C320" t="s">
         <v>237</v>
@@ -24375,10 +24565,10 @@
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B321" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C321" t="s">
         <v>237</v>
@@ -24413,10 +24603,10 @@
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B322" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C322" t="s">
         <v>237</v>
@@ -24451,10 +24641,10 @@
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B323" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C323" t="s">
         <v>237</v>
@@ -24489,10 +24679,10 @@
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B324" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C324" t="s">
         <v>237</v>
@@ -24527,10 +24717,10 @@
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B325" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C325" t="s">
         <v>237</v>
@@ -24565,10 +24755,10 @@
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B326" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C326" t="s">
         <v>237</v>
@@ -24603,10 +24793,10 @@
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B327" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C327" t="s">
         <v>237</v>
@@ -24641,10 +24831,10 @@
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B328" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C328" t="s">
         <v>237</v>
@@ -24679,10 +24869,10 @@
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B329" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C329" t="s">
         <v>237</v>
@@ -24717,10 +24907,10 @@
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B330" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C330" t="s">
         <v>237</v>
@@ -24755,10 +24945,10 @@
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B331" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C331" t="s">
         <v>237</v>
@@ -24793,10 +24983,10 @@
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B332" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C332" t="s">
         <v>237</v>
@@ -24831,10 +25021,10 @@
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B333" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C333" t="s">
         <v>237</v>
@@ -24869,10 +25059,10 @@
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B334" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C334" t="s">
         <v>237</v>
@@ -24907,10 +25097,10 @@
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B335" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C335" t="s">
         <v>237</v>
@@ -24945,10 +25135,10 @@
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B336" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C336" t="s">
         <v>237</v>
@@ -24983,10 +25173,10 @@
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B337" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C337" t="s">
         <v>237</v>
@@ -25021,16 +25211,16 @@
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B338" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C338" t="s">
-        <v>456</v>
+        <v>237</v>
       </c>
       <c r="D338" t="s">
-        <v>457</v>
+        <v>403</v>
       </c>
       <c r="E338" t="s">
         <v>25</v>
@@ -25059,16 +25249,16 @@
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B339" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C339" t="s">
-        <v>456</v>
+        <v>237</v>
       </c>
       <c r="D339" t="s">
-        <v>457</v>
+        <v>403</v>
       </c>
       <c r="E339" t="s">
         <v>25</v>
@@ -25097,10 +25287,10 @@
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B340" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C340" t="s">
         <v>456</v>
@@ -25135,10 +25325,10 @@
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B341" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C341" t="s">
         <v>456</v>
@@ -25173,10 +25363,10 @@
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B342" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C342" t="s">
         <v>456</v>
@@ -25211,10 +25401,10 @@
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B343" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C343" t="s">
         <v>456</v>
@@ -25249,10 +25439,10 @@
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B344" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C344" t="s">
         <v>456</v>
@@ -25287,10 +25477,10 @@
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B345" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C345" t="s">
         <v>456</v>
@@ -25325,10 +25515,10 @@
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B346" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C346" t="s">
         <v>456</v>
@@ -25363,10 +25553,10 @@
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B347" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C347" t="s">
         <v>456</v>
@@ -25401,10 +25591,10 @@
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B348" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C348" t="s">
         <v>456</v>
@@ -25439,10 +25629,10 @@
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B349" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C349" t="s">
         <v>456</v>
@@ -25477,10 +25667,10 @@
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B350" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C350" t="s">
         <v>456</v>
@@ -25515,10 +25705,10 @@
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B351" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C351" t="s">
         <v>456</v>
@@ -25553,10 +25743,10 @@
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B352" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C352" t="s">
         <v>456</v>
@@ -25591,10 +25781,10 @@
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B353" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C353" t="s">
         <v>456</v>
@@ -25629,10 +25819,10 @@
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B354" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C354" t="s">
         <v>456</v>
@@ -25667,10 +25857,10 @@
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B355" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C355" t="s">
         <v>456</v>
@@ -25705,10 +25895,10 @@
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B356" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C356" t="s">
         <v>456</v>
@@ -25743,10 +25933,10 @@
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B357" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C357" t="s">
         <v>456</v>
@@ -25781,10 +25971,10 @@
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B358" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C358" t="s">
         <v>456</v>
@@ -25819,10 +26009,10 @@
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B359" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C359" t="s">
         <v>456</v>
@@ -25857,10 +26047,10 @@
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B360" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C360" t="s">
         <v>456</v>
@@ -25895,10 +26085,10 @@
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B361" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C361" t="s">
         <v>456</v>
@@ -25933,10 +26123,10 @@
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B362" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C362" t="s">
         <v>456</v>
@@ -25971,10 +26161,10 @@
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B363" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C363" t="s">
         <v>456</v>
@@ -26009,10 +26199,10 @@
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B364" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C364" t="s">
         <v>456</v>
@@ -26047,10 +26237,10 @@
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B365" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C365" t="s">
         <v>456</v>
@@ -26085,10 +26275,10 @@
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B366" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C366" t="s">
         <v>456</v>
@@ -26123,10 +26313,10 @@
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B367" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C367" t="s">
         <v>456</v>
@@ -26161,10 +26351,10 @@
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B368" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C368" t="s">
         <v>456</v>
@@ -26199,10 +26389,10 @@
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B369" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C369" t="s">
         <v>456</v>
@@ -26237,10 +26427,10 @@
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B370" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C370" t="s">
         <v>456</v>
@@ -26275,10 +26465,10 @@
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B371" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C371" t="s">
         <v>456</v>
@@ -26313,10 +26503,10 @@
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B372" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C372" t="s">
         <v>456</v>
@@ -26351,10 +26541,10 @@
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B373" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C373" t="s">
         <v>456</v>
@@ -26389,10 +26579,10 @@
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B374" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C374" t="s">
         <v>456</v>
@@ -26427,10 +26617,10 @@
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B375" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C375" t="s">
         <v>456</v>
@@ -26465,10 +26655,10 @@
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B376" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C376" t="s">
         <v>456</v>
@@ -26503,10 +26693,10 @@
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B377" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C377" t="s">
         <v>456</v>
@@ -26541,10 +26731,10 @@
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B378" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C378" t="s">
         <v>456</v>
@@ -26579,10 +26769,10 @@
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B379" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C379" t="s">
         <v>456</v>
@@ -26617,10 +26807,10 @@
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B380" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C380" t="s">
         <v>456</v>
@@ -26655,10 +26845,10 @@
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B381" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C381" t="s">
         <v>456</v>
@@ -26693,10 +26883,10 @@
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B382" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C382" t="s">
         <v>456</v>
@@ -26731,10 +26921,10 @@
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B383" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C383" t="s">
         <v>456</v>
@@ -26769,10 +26959,10 @@
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B384" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C384" t="s">
         <v>456</v>
@@ -26807,16 +26997,16 @@
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B385" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C385" t="s">
         <v>456</v>
       </c>
       <c r="D385" t="s">
-        <v>552</v>
+        <v>457</v>
       </c>
       <c r="E385" t="s">
         <v>25</v>
@@ -26845,16 +27035,16 @@
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="B386" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="C386" t="s">
         <v>456</v>
       </c>
       <c r="D386" t="s">
-        <v>552</v>
+        <v>457</v>
       </c>
       <c r="E386" t="s">
         <v>25</v>
@@ -26883,10 +27073,10 @@
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="B387" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C387" t="s">
         <v>456</v>
@@ -26921,10 +27111,10 @@
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B388" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C388" t="s">
         <v>456</v>
@@ -26959,10 +27149,10 @@
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B389" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C389" t="s">
         <v>456</v>
@@ -26997,10 +27187,10 @@
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B390" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C390" t="s">
         <v>456</v>
@@ -27035,10 +27225,10 @@
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B391" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C391" t="s">
         <v>456</v>
@@ -27073,10 +27263,10 @@
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B392" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C392" t="s">
         <v>456</v>
@@ -27111,10 +27301,10 @@
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B393" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C393" t="s">
         <v>456</v>
@@ -27149,10 +27339,10 @@
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B394" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C394" t="s">
         <v>456</v>
@@ -27187,10 +27377,10 @@
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B395" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C395" t="s">
         <v>456</v>
@@ -27225,10 +27415,10 @@
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B396" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C396" t="s">
         <v>456</v>
@@ -27263,10 +27453,10 @@
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B397" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C397" t="s">
         <v>456</v>
@@ -27301,10 +27491,10 @@
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B398" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C398" t="s">
         <v>456</v>
@@ -27339,10 +27529,10 @@
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B399" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C399" t="s">
         <v>456</v>
@@ -27377,10 +27567,10 @@
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B400" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C400" t="s">
         <v>456</v>
@@ -27415,10 +27605,10 @@
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B401" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C401" t="s">
         <v>456</v>
@@ -27453,10 +27643,10 @@
     </row>
     <row r="402" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B402" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C402" t="s">
         <v>456</v>
@@ -27491,10 +27681,10 @@
     </row>
     <row r="403" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B403" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C403" t="s">
         <v>456</v>
@@ -27529,10 +27719,10 @@
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B404" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C404" t="s">
         <v>456</v>
@@ -27567,10 +27757,10 @@
     </row>
     <row r="405" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B405" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C405" t="s">
         <v>456</v>
@@ -27605,10 +27795,10 @@
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B406" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C406" t="s">
         <v>456</v>
@@ -27643,10 +27833,10 @@
     </row>
     <row r="407" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B407" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C407" t="s">
         <v>456</v>
@@ -27681,10 +27871,10 @@
     </row>
     <row r="408" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B408" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C408" t="s">
         <v>456</v>
@@ -27719,10 +27909,10 @@
     </row>
     <row r="409" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B409" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C409" t="s">
         <v>456</v>
@@ -27757,10 +27947,10 @@
     </row>
     <row r="410" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B410" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C410" t="s">
         <v>456</v>
@@ -27795,10 +27985,10 @@
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B411" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C411" t="s">
         <v>456</v>
@@ -27833,10 +28023,10 @@
     </row>
     <row r="412" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B412" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C412" t="s">
         <v>456</v>
@@ -27871,10 +28061,10 @@
     </row>
     <row r="413" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B413" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C413" t="s">
         <v>456</v>
@@ -27909,10 +28099,10 @@
     </row>
     <row r="414" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B414" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C414" t="s">
         <v>456</v>
@@ -27947,10 +28137,10 @@
     </row>
     <row r="415" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B415" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C415" t="s">
         <v>456</v>
@@ -27985,10 +28175,10 @@
     </row>
     <row r="416" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B416" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C416" t="s">
         <v>456</v>
@@ -28023,10 +28213,10 @@
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B417" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C417" t="s">
         <v>456</v>
@@ -28061,10 +28251,10 @@
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B418" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C418" t="s">
         <v>456</v>
@@ -28099,16 +28289,16 @@
     </row>
     <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B419" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C419" t="s">
-        <v>621</v>
+        <v>456</v>
       </c>
       <c r="D419" t="s">
-        <v>25</v>
+        <v>552</v>
       </c>
       <c r="E419" t="s">
         <v>25</v>
@@ -28137,16 +28327,16 @@
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B420" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C420" t="s">
-        <v>621</v>
+        <v>456</v>
       </c>
       <c r="D420" t="s">
-        <v>25</v>
+        <v>552</v>
       </c>
       <c r="E420" t="s">
         <v>25</v>
@@ -28175,10 +28365,10 @@
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B421" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C421" t="s">
         <v>621</v>
@@ -28213,10 +28403,10 @@
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B422" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C422" t="s">
         <v>621</v>
@@ -28251,10 +28441,10 @@
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B423" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C423" t="s">
         <v>621</v>
@@ -28289,10 +28479,10 @@
     </row>
     <row r="424" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B424" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C424" t="s">
         <v>621</v>
@@ -28327,10 +28517,10 @@
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B425" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C425" t="s">
         <v>621</v>
@@ -28365,10 +28555,10 @@
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B426" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C426" t="s">
         <v>621</v>
@@ -28403,16 +28593,16 @@
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B427" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C427" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="D427" t="s">
-        <v>639</v>
+        <v>25</v>
       </c>
       <c r="E427" t="s">
         <v>25</v>
@@ -28441,16 +28631,16 @@
     </row>
     <row r="428" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="B428" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C428" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="D428" t="s">
-        <v>639</v>
+        <v>25</v>
       </c>
       <c r="E428" t="s">
         <v>25</v>
@@ -28479,10 +28669,10 @@
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B429" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C429" t="s">
         <v>638</v>
@@ -28517,10 +28707,10 @@
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B430" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C430" t="s">
         <v>638</v>
@@ -28555,16 +28745,16 @@
     </row>
     <row r="431" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B431" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C431" t="s">
         <v>638</v>
       </c>
       <c r="D431" t="s">
-        <v>138</v>
+        <v>639</v>
       </c>
       <c r="E431" t="s">
         <v>25</v>
@@ -28593,16 +28783,16 @@
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B432" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C432" t="s">
         <v>638</v>
       </c>
       <c r="D432" t="s">
-        <v>138</v>
+        <v>639</v>
       </c>
       <c r="E432" t="s">
         <v>25</v>
@@ -28631,10 +28821,10 @@
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B433" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C433" t="s">
         <v>638</v>
@@ -28669,10 +28859,10 @@
     </row>
     <row r="434" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B434" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C434" t="s">
         <v>638</v>
@@ -28707,16 +28897,16 @@
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B435" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C435" t="s">
         <v>638</v>
       </c>
       <c r="D435" t="s">
-        <v>656</v>
+        <v>138</v>
       </c>
       <c r="E435" t="s">
         <v>25</v>
@@ -28745,16 +28935,16 @@
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="B436" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C436" t="s">
         <v>638</v>
       </c>
       <c r="D436" t="s">
-        <v>656</v>
+        <v>138</v>
       </c>
       <c r="E436" t="s">
         <v>25</v>
@@ -28783,10 +28973,10 @@
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="B437" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C437" t="s">
         <v>638</v>
@@ -28821,10 +29011,10 @@
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B438" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C438" t="s">
         <v>638</v>
@@ -28859,10 +29049,10 @@
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B439" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C439" t="s">
         <v>638</v>
@@ -28897,16 +29087,16 @@
     </row>
     <row r="440" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B440" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C440" t="s">
         <v>638</v>
       </c>
       <c r="D440" t="s">
-        <v>128</v>
+        <v>656</v>
       </c>
       <c r="E440" t="s">
         <v>25</v>
@@ -28935,16 +29125,16 @@
     </row>
     <row r="441" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B441" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C441" t="s">
         <v>638</v>
       </c>
       <c r="D441" t="s">
-        <v>128</v>
+        <v>656</v>
       </c>
       <c r="E441" t="s">
         <v>25</v>
@@ -28973,16 +29163,16 @@
     </row>
     <row r="442" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B442" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C442" t="s">
         <v>638</v>
       </c>
       <c r="D442" t="s">
-        <v>671</v>
+        <v>128</v>
       </c>
       <c r="E442" t="s">
         <v>25</v>
@@ -29011,16 +29201,16 @@
     </row>
     <row r="443" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="B443" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="C443" t="s">
         <v>638</v>
       </c>
       <c r="D443" t="s">
-        <v>671</v>
+        <v>128</v>
       </c>
       <c r="E443" t="s">
         <v>25</v>
@@ -29049,10 +29239,10 @@
     </row>
     <row r="444" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="B444" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="C444" t="s">
         <v>638</v>
@@ -29087,10 +29277,10 @@
     </row>
     <row r="445" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B445" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C445" t="s">
         <v>638</v>
@@ -29125,16 +29315,16 @@
     </row>
     <row r="446" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="B446" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C446" t="s">
-        <v>679</v>
+        <v>638</v>
       </c>
       <c r="D446" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="E446" t="s">
         <v>25</v>
@@ -29163,16 +29353,16 @@
     </row>
     <row r="447" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="B447" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="C447" t="s">
-        <v>679</v>
+        <v>638</v>
       </c>
       <c r="D447" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="E447" t="s">
         <v>25</v>
@@ -29201,10 +29391,10 @@
     </row>
     <row r="448" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="B448" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C448" t="s">
         <v>679</v>
@@ -29239,10 +29429,10 @@
     </row>
     <row r="449" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B449" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C449" t="s">
         <v>679</v>
@@ -29277,10 +29467,10 @@
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B450" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C450" t="s">
         <v>679</v>
@@ -29315,10 +29505,10 @@
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B451" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C451" t="s">
         <v>679</v>
@@ -29353,16 +29543,16 @@
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B452" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C452" t="s">
         <v>679</v>
       </c>
       <c r="D452" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="E452" t="s">
         <v>25</v>
@@ -29391,16 +29581,16 @@
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="B453" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="C453" t="s">
         <v>679</v>
       </c>
       <c r="D453" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="E453" t="s">
         <v>25</v>
@@ -29429,10 +29619,10 @@
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="B454" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C454" t="s">
         <v>679</v>
@@ -29467,16 +29657,16 @@
     </row>
     <row r="455" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B455" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C455" t="s">
         <v>679</v>
       </c>
       <c r="D455" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="E455" t="s">
         <v>25</v>
@@ -29505,16 +29695,16 @@
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="B456" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="C456" t="s">
         <v>679</v>
       </c>
       <c r="D456" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="E456" t="s">
         <v>25</v>
@@ -29543,10 +29733,10 @@
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="B457" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="C457" t="s">
         <v>679</v>
@@ -29581,10 +29771,10 @@
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B458" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C458" t="s">
         <v>679</v>
@@ -29619,16 +29809,16 @@
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B459" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C459" t="s">
         <v>679</v>
       </c>
       <c r="D459" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="E459" t="s">
         <v>25</v>
@@ -29657,16 +29847,16 @@
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B460" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C460" t="s">
         <v>679</v>
       </c>
       <c r="D460" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="E460" t="s">
         <v>25</v>
@@ -29695,10 +29885,10 @@
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B461" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C461" t="s">
         <v>679</v>
@@ -29733,16 +29923,16 @@
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B462" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="C462" t="s">
         <v>679</v>
       </c>
       <c r="D462" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="E462" t="s">
         <v>25</v>
@@ -29771,16 +29961,16 @@
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="B463" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="C463" t="s">
         <v>679</v>
       </c>
       <c r="D463" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="E463" t="s">
         <v>25</v>
@@ -29809,10 +29999,10 @@
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B464" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="C464" t="s">
         <v>679</v>
@@ -29847,10 +30037,10 @@
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B465" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="C465" t="s">
         <v>679</v>
@@ -29885,10 +30075,10 @@
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B466" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C466" t="s">
         <v>679</v>
@@ -29923,16 +30113,16 @@
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B467" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C467" t="s">
         <v>679</v>
       </c>
       <c r="D467" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="E467" t="s">
         <v>25</v>
@@ -29961,16 +30151,16 @@
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="B468" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="C468" t="s">
         <v>679</v>
       </c>
       <c r="D468" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="E468" t="s">
         <v>25</v>
@@ -29999,10 +30189,10 @@
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="B469" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C469" t="s">
         <v>679</v>
@@ -30037,10 +30227,10 @@
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B470" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C470" t="s">
         <v>679</v>
@@ -30075,10 +30265,10 @@
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B471" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="C471" t="s">
         <v>679</v>
@@ -30113,10 +30303,10 @@
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B472" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C472" t="s">
         <v>679</v>
@@ -30151,16 +30341,16 @@
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B473" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C473" t="s">
         <v>679</v>
       </c>
       <c r="D473" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="E473" t="s">
         <v>25</v>
@@ -30189,16 +30379,16 @@
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="B474" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="C474" t="s">
         <v>679</v>
       </c>
       <c r="D474" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="E474" t="s">
         <v>25</v>
@@ -30227,16 +30417,16 @@
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="B475" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C475" t="s">
-        <v>744</v>
+        <v>679</v>
       </c>
       <c r="D475" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="E475" t="s">
         <v>25</v>
@@ -30265,16 +30455,16 @@
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="B476" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="C476" t="s">
-        <v>744</v>
+        <v>679</v>
       </c>
       <c r="D476" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="E476" t="s">
         <v>25</v>
@@ -30303,10 +30493,10 @@
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B477" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="C477" t="s">
         <v>744</v>
@@ -30341,10 +30531,10 @@
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B478" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C478" t="s">
         <v>744</v>
@@ -30379,10 +30569,10 @@
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B479" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C479" t="s">
         <v>744</v>
@@ -30417,10 +30607,10 @@
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B480" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="C480" t="s">
         <v>744</v>
@@ -30455,10 +30645,10 @@
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B481" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="C481" t="s">
         <v>744</v>
@@ -30493,10 +30683,10 @@
     </row>
     <row r="482" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B482" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="C482" t="s">
         <v>744</v>
@@ -30531,10 +30721,10 @@
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B483" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="C483" t="s">
         <v>744</v>
@@ -30569,10 +30759,10 @@
     </row>
     <row r="484" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B484" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="C484" t="s">
         <v>744</v>
@@ -30607,10 +30797,10 @@
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B485" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C485" t="s">
         <v>744</v>
@@ -30645,10 +30835,10 @@
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B486" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C486" t="s">
         <v>744</v>
@@ -30683,10 +30873,10 @@
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="B487" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="C487" t="s">
         <v>744</v>
@@ -30721,16 +30911,16 @@
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B488" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C488" t="s">
         <v>744</v>
       </c>
       <c r="D488" t="s">
-        <v>772</v>
+        <v>745</v>
       </c>
       <c r="E488" t="s">
         <v>25</v>
@@ -30759,16 +30949,16 @@
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="B489" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C489" t="s">
         <v>744</v>
       </c>
       <c r="D489" t="s">
-        <v>772</v>
+        <v>745</v>
       </c>
       <c r="E489" t="s">
         <v>25</v>
@@ -30797,10 +30987,10 @@
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="B490" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="C490" t="s">
         <v>744</v>
@@ -30835,10 +31025,10 @@
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B491" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="C491" t="s">
         <v>744</v>
@@ -30873,10 +31063,10 @@
     </row>
     <row r="492" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B492" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C492" t="s">
         <v>744</v>
@@ -30911,16 +31101,16 @@
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B493" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C493" t="s">
         <v>744</v>
       </c>
       <c r="D493" t="s">
-        <v>196</v>
+        <v>772</v>
       </c>
       <c r="E493" t="s">
         <v>25</v>
@@ -30949,16 +31139,16 @@
     </row>
     <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B494" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C494" t="s">
         <v>744</v>
       </c>
       <c r="D494" t="s">
-        <v>196</v>
+        <v>772</v>
       </c>
       <c r="E494" t="s">
         <v>25</v>
@@ -30987,10 +31177,10 @@
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B495" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C495" t="s">
         <v>744</v>
@@ -31025,16 +31215,16 @@
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B496" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C496" t="s">
         <v>744</v>
       </c>
       <c r="D496" t="s">
-        <v>789</v>
+        <v>196</v>
       </c>
       <c r="E496" t="s">
         <v>25</v>
@@ -31063,16 +31253,16 @@
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="B497" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="C497" t="s">
         <v>744</v>
       </c>
       <c r="D497" t="s">
-        <v>789</v>
+        <v>196</v>
       </c>
       <c r="E497" t="s">
         <v>25</v>
@@ -31101,16 +31291,16 @@
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="B498" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C498" t="s">
         <v>744</v>
       </c>
       <c r="D498" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="E498" t="s">
         <v>25</v>
@@ -31139,16 +31329,16 @@
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="B499" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="C499" t="s">
         <v>744</v>
       </c>
       <c r="D499" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="E499" t="s">
         <v>25</v>
@@ -31177,10 +31367,10 @@
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="B500" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="C500" t="s">
         <v>744</v>
@@ -31215,16 +31405,16 @@
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B501" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="C501" t="s">
         <v>744</v>
       </c>
       <c r="D501" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="E501" t="s">
         <v>25</v>
@@ -31253,16 +31443,16 @@
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="B502" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C502" t="s">
         <v>744</v>
       </c>
       <c r="D502" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="E502" t="s">
         <v>25</v>
@@ -31291,10 +31481,10 @@
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="B503" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C503" t="s">
         <v>744</v>
@@ -31329,10 +31519,10 @@
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="B504" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="C504" t="s">
         <v>744</v>
@@ -31367,10 +31557,10 @@
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B505" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="C505" t="s">
         <v>744</v>
@@ -31405,10 +31595,10 @@
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B506" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="C506" t="s">
         <v>744</v>
@@ -31443,10 +31633,10 @@
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B507" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C507" t="s">
         <v>744</v>
@@ -31481,10 +31671,10 @@
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B508" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="C508" t="s">
         <v>744</v>
@@ -31519,10 +31709,10 @@
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B509" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C509" t="s">
         <v>744</v>
@@ -31557,10 +31747,10 @@
     </row>
     <row r="510" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B510" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="C510" t="s">
         <v>744</v>
@@ -31595,10 +31785,10 @@
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B511" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="C511" t="s">
         <v>744</v>
@@ -31633,10 +31823,10 @@
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B512" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="C512" t="s">
         <v>744</v>
@@ -31671,16 +31861,16 @@
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B513" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="C513" t="s">
         <v>744</v>
       </c>
       <c r="D513" t="s">
-        <v>826</v>
+        <v>801</v>
       </c>
       <c r="E513" t="s">
         <v>25</v>
@@ -31709,16 +31899,16 @@
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="B514" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="C514" t="s">
         <v>744</v>
       </c>
       <c r="D514" t="s">
-        <v>826</v>
+        <v>801</v>
       </c>
       <c r="E514" t="s">
         <v>25</v>
@@ -31747,10 +31937,10 @@
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="B515" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="C515" t="s">
         <v>744</v>
@@ -31785,10 +31975,10 @@
     </row>
     <row r="516" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B516" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="C516" t="s">
         <v>744</v>
@@ -31823,10 +32013,10 @@
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B517" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C517" t="s">
         <v>744</v>
@@ -31861,16 +32051,16 @@
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B518" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="C518" t="s">
         <v>744</v>
       </c>
       <c r="D518" t="s">
-        <v>837</v>
+        <v>826</v>
       </c>
       <c r="E518" t="s">
         <v>25</v>
@@ -31899,16 +32089,16 @@
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="B519" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="C519" t="s">
         <v>744</v>
       </c>
       <c r="D519" t="s">
-        <v>837</v>
+        <v>826</v>
       </c>
       <c r="E519" t="s">
         <v>25</v>
@@ -31937,16 +32127,16 @@
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="B520" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="C520" t="s">
-        <v>842</v>
+        <v>744</v>
       </c>
       <c r="D520" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="E520" t="s">
         <v>25</v>
@@ -31975,16 +32165,16 @@
     </row>
     <row r="521" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="B521" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="C521" t="s">
-        <v>842</v>
+        <v>744</v>
       </c>
       <c r="D521" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="E521" t="s">
         <v>25</v>
@@ -32013,10 +32203,10 @@
     </row>
     <row r="522" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="B522" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="C522" t="s">
         <v>842</v>
@@ -32051,10 +32241,10 @@
     </row>
     <row r="523" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B523" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C523" t="s">
         <v>842</v>
@@ -32089,10 +32279,10 @@
     </row>
     <row r="524" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B524" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="C524" t="s">
         <v>842</v>
@@ -32127,10 +32317,10 @@
     </row>
     <row r="525" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B525" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C525" t="s">
         <v>842</v>
@@ -32165,16 +32355,16 @@
     </row>
     <row r="526" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="B526" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="C526" t="s">
         <v>842</v>
       </c>
       <c r="D526" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
       <c r="E526" t="s">
         <v>25</v>
@@ -32203,16 +32393,16 @@
     </row>
     <row r="527" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="B527" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="C527" t="s">
         <v>842</v>
       </c>
       <c r="D527" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
       <c r="E527" t="s">
         <v>25</v>
@@ -32241,10 +32431,10 @@
     </row>
     <row r="528" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="B528" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="C528" t="s">
         <v>842</v>
@@ -32279,10 +32469,10 @@
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B529" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C529" t="s">
         <v>842</v>
@@ -32317,10 +32507,10 @@
     </row>
     <row r="530" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="B530" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="C530" t="s">
         <v>842</v>
@@ -32355,16 +32545,16 @@
     </row>
     <row r="531" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B531" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="C531" t="s">
         <v>842</v>
       </c>
       <c r="D531" t="s">
-        <v>867</v>
+        <v>856</v>
       </c>
       <c r="E531" t="s">
         <v>25</v>
@@ -32393,16 +32583,16 @@
     </row>
     <row r="532" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="B532" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="C532" t="s">
         <v>842</v>
       </c>
       <c r="D532" t="s">
-        <v>867</v>
+        <v>856</v>
       </c>
       <c r="E532" t="s">
         <v>25</v>
@@ -32431,10 +32621,10 @@
     </row>
     <row r="533" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="B533" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="C533" t="s">
         <v>842</v>
@@ -32469,16 +32659,16 @@
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="B534" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="C534" t="s">
         <v>842</v>
       </c>
       <c r="D534" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="E534" t="s">
         <v>25</v>
@@ -32507,16 +32697,16 @@
     </row>
     <row r="535" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="B535" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="C535" t="s">
         <v>842</v>
       </c>
       <c r="D535" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="E535" t="s">
         <v>25</v>
@@ -32545,16 +32735,16 @@
     </row>
     <row r="536" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="B536" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="C536" t="s">
         <v>842</v>
       </c>
       <c r="D536" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="E536" t="s">
         <v>25</v>
@@ -32583,16 +32773,16 @@
     </row>
     <row r="537" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="B537" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="C537" t="s">
         <v>842</v>
       </c>
       <c r="D537" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="E537" t="s">
         <v>25</v>
@@ -32621,10 +32811,10 @@
     </row>
     <row r="538" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="B538" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="C538" t="s">
         <v>842</v>
@@ -32659,10 +32849,10 @@
     </row>
     <row r="539" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B539" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="C539" t="s">
         <v>842</v>
@@ -32697,16 +32887,16 @@
     </row>
     <row r="540" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="B540" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="C540" t="s">
         <v>842</v>
       </c>
       <c r="D540" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="E540" t="s">
         <v>25</v>
@@ -32735,16 +32925,16 @@
     </row>
     <row r="541" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B541" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="C541" t="s">
         <v>842</v>
       </c>
       <c r="D541" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="E541" t="s">
         <v>25</v>
@@ -32773,10 +32963,10 @@
     </row>
     <row r="542" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="B542" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="C542" t="s">
         <v>842</v>
@@ -32811,10 +33001,10 @@
     </row>
     <row r="543" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B543" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C543" t="s">
         <v>842</v>
@@ -32849,10 +33039,10 @@
     </row>
     <row r="544" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="B544" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="C544" t="s">
         <v>842</v>
@@ -32887,16 +33077,16 @@
     </row>
     <row r="545" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="B545" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="C545" t="s">
-        <v>899</v>
+        <v>842</v>
       </c>
       <c r="D545" t="s">
-        <v>25</v>
+        <v>888</v>
       </c>
       <c r="E545" t="s">
         <v>25</v>
@@ -32925,16 +33115,16 @@
     </row>
     <row r="546" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="B546" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="C546" t="s">
-        <v>899</v>
+        <v>842</v>
       </c>
       <c r="D546" t="s">
-        <v>25</v>
+        <v>888</v>
       </c>
       <c r="E546" t="s">
         <v>25</v>
@@ -32963,10 +33153,10 @@
     </row>
     <row r="547" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="B547" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="C547" t="s">
         <v>899</v>
@@ -33001,10 +33191,10 @@
     </row>
     <row r="548" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B548" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="C548" t="s">
         <v>899</v>
@@ -33039,10 +33229,10 @@
     </row>
     <row r="549" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B549" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="C549" t="s">
         <v>899</v>
@@ -33077,10 +33267,10 @@
     </row>
     <row r="550" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="B550" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="C550" t="s">
         <v>899</v>
@@ -33115,10 +33305,10 @@
     </row>
     <row r="551" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B551" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="C551" t="s">
         <v>899</v>
@@ -33153,10 +33343,10 @@
     </row>
     <row r="552" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B552" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C552" t="s">
         <v>899</v>
@@ -33191,10 +33381,10 @@
     </row>
     <row r="553" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B553" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="C553" t="s">
         <v>899</v>
@@ -33229,10 +33419,10 @@
     </row>
     <row r="554" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B554" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="C554" t="s">
         <v>899</v>
@@ -33267,10 +33457,10 @@
     </row>
     <row r="555" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B555" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="C555" t="s">
         <v>899</v>
@@ -33305,10 +33495,10 @@
     </row>
     <row r="556" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B556" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="C556" t="s">
         <v>899</v>
@@ -33343,10 +33533,10 @@
     </row>
     <row r="557" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B557" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C557" t="s">
         <v>899</v>
@@ -33381,10 +33571,10 @@
     </row>
     <row r="558" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B558" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="C558" t="s">
         <v>899</v>
@@ -33419,10 +33609,10 @@
     </row>
     <row r="559" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B559" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C559" t="s">
         <v>899</v>
@@ -33457,16 +33647,16 @@
     </row>
     <row r="560" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B560" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C560" t="s">
-        <v>930</v>
+        <v>899</v>
       </c>
       <c r="D560" t="s">
-        <v>931</v>
+        <v>25</v>
       </c>
       <c r="E560" t="s">
         <v>25</v>
@@ -33495,16 +33685,16 @@
     </row>
     <row r="561" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="B561" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="C561" t="s">
-        <v>930</v>
+        <v>899</v>
       </c>
       <c r="D561" t="s">
-        <v>931</v>
+        <v>25</v>
       </c>
       <c r="E561" t="s">
         <v>25</v>
@@ -33533,10 +33723,10 @@
     </row>
     <row r="562" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="B562" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="C562" t="s">
         <v>930</v>
@@ -33571,10 +33761,10 @@
     </row>
     <row r="563" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="B563" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="C563" t="s">
         <v>930</v>
@@ -33609,16 +33799,16 @@
     </row>
     <row r="564" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B564" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="C564" t="s">
         <v>930</v>
       </c>
       <c r="D564" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="E564" t="s">
         <v>25</v>
@@ -33647,16 +33837,16 @@
     </row>
     <row r="565" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="B565" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="C565" t="s">
         <v>930</v>
       </c>
       <c r="D565" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="E565" t="s">
         <v>25</v>
@@ -33685,10 +33875,10 @@
     </row>
     <row r="566" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B566" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="C566" t="s">
         <v>930</v>
@@ -33723,10 +33913,10 @@
     </row>
     <row r="567" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B567" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C567" t="s">
         <v>930</v>
@@ -33761,10 +33951,10 @@
     </row>
     <row r="568" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B568" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="C568" t="s">
         <v>930</v>
@@ -33799,10 +33989,10 @@
     </row>
     <row r="569" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B569" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="C569" t="s">
         <v>930</v>
@@ -33837,10 +34027,10 @@
     </row>
     <row r="570" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B570" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="C570" t="s">
         <v>930</v>
@@ -33875,16 +34065,16 @@
     </row>
     <row r="571" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B571" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C571" t="s">
-        <v>955</v>
+        <v>930</v>
       </c>
       <c r="D571" t="s">
-        <v>956</v>
+        <v>940</v>
       </c>
       <c r="E571" t="s">
         <v>25</v>
@@ -33913,16 +34103,16 @@
     </row>
     <row r="572" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="B572" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="C572" t="s">
-        <v>955</v>
+        <v>930</v>
       </c>
       <c r="D572" t="s">
-        <v>956</v>
+        <v>940</v>
       </c>
       <c r="E572" t="s">
         <v>25</v>
@@ -33951,10 +34141,10 @@
     </row>
     <row r="573" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="B573" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="C573" t="s">
         <v>955</v>
@@ -33989,10 +34179,10 @@
     </row>
     <row r="574" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B574" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C574" t="s">
         <v>955</v>
@@ -34027,10 +34217,10 @@
     </row>
     <row r="575" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="B575" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="C575" t="s">
         <v>955</v>
@@ -34065,10 +34255,10 @@
     </row>
     <row r="576" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B576" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="C576" t="s">
         <v>955</v>
@@ -34103,10 +34293,10 @@
     </row>
     <row r="577" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B577" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="C577" t="s">
         <v>955</v>
@@ -34141,10 +34331,10 @@
     </row>
     <row r="578" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B578" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C578" t="s">
         <v>955</v>
@@ -34179,16 +34369,16 @@
     </row>
     <row r="579" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B579" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="C579" t="s">
         <v>955</v>
       </c>
       <c r="D579" t="s">
-        <v>973</v>
+        <v>956</v>
       </c>
       <c r="E579" t="s">
         <v>25</v>
@@ -34217,16 +34407,16 @@
     </row>
     <row r="580" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="B580" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="C580" t="s">
         <v>955</v>
       </c>
       <c r="D580" t="s">
-        <v>973</v>
+        <v>956</v>
       </c>
       <c r="E580" t="s">
         <v>25</v>
@@ -34255,10 +34445,10 @@
     </row>
     <row r="581" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="B581" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="C581" t="s">
         <v>955</v>
@@ -34293,10 +34483,10 @@
     </row>
     <row r="582" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B582" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="C582" t="s">
         <v>955</v>
@@ -34331,10 +34521,10 @@
     </row>
     <row r="583" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B583" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="C583" t="s">
         <v>955</v>
@@ -34369,16 +34559,16 @@
     </row>
     <row r="584" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B584" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="C584" t="s">
         <v>955</v>
       </c>
       <c r="D584" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="E584" t="s">
         <v>25</v>
@@ -34407,16 +34597,16 @@
     </row>
     <row r="585" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="B585" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="C585" t="s">
         <v>955</v>
       </c>
       <c r="D585" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="E585" t="s">
         <v>25</v>
@@ -34445,16 +34635,16 @@
     </row>
     <row r="586" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="B586" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="C586" t="s">
         <v>955</v>
       </c>
       <c r="D586" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="E586" t="s">
         <v>25</v>
@@ -34483,16 +34673,16 @@
     </row>
     <row r="587" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="B587" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="C587